--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="376">
   <si>
     <t>STORM SPLIT — Balance Model</t>
   </si>
@@ -454,7 +454,7 @@
     <t>TOWER UPGRADES — 5 towers x 3 paths x 5 tiers</t>
   </si>
   <si>
-    <t>Multipliers are blue because they define each path's character. Costs are formulas off Tuning. Range x multiplies the tower's base range (range-focus paths only).</t>
+    <t>Multipliers are blue because they define each path's character. Costs are formulas off Tuning. Range x multiplies the tower's base range (range-focus paths only). Name is the tier's in-game name (full design: UPGRADES.md).</t>
   </si>
   <si>
     <t>Path</t>
@@ -490,51 +490,234 @@
     <t>Range x</t>
   </si>
   <si>
-    <t>Range</t>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Lookout</t>
   </si>
   <si>
     <t>range</t>
   </si>
   <si>
-    <t>Rate</t>
+    <t>Keen Eyes</t>
+  </si>
+  <si>
+    <t>Long Barrel</t>
+  </si>
+  <si>
+    <t>Flare Gun</t>
+  </si>
+  <si>
+    <t>Watch Post</t>
+  </si>
+  <si>
+    <t>Signal Tower</t>
+  </si>
+  <si>
+    <t>Trigger Happy</t>
   </si>
   <si>
     <t>rate</t>
   </si>
   <si>
+    <t>Quick Hands</t>
+  </si>
+  <si>
+    <t>Extended Mag</t>
+  </si>
+  <si>
+    <t>Double Tap</t>
+  </si>
+  <si>
+    <t>Bullet Hose</t>
+  </si>
+  <si>
+    <t>Stormgunner</t>
+  </si>
+  <si>
+    <t>Hardliner</t>
+  </si>
+  <si>
     <t>damage</t>
   </si>
   <si>
-    <t>Pierce</t>
+    <t>Heavy Slugs</t>
+  </si>
+  <si>
+    <t>Armor Breaker</t>
+  </si>
+  <si>
+    <t>Hollow Points</t>
+  </si>
+  <si>
+    <t>Railshot</t>
+  </si>
+  <si>
+    <t>Tank Buster</t>
+  </si>
+  <si>
+    <t>Deadeye</t>
   </si>
   <si>
     <t>targets</t>
   </si>
   <si>
+    <t>Full Metal Jacket</t>
+  </si>
+  <si>
+    <t>Through-and-Through</t>
+  </si>
+  <si>
+    <t>Ricochet</t>
+  </si>
+  <si>
+    <t>Tungsten Core</t>
+  </si>
+  <si>
+    <t>Linebreaker</t>
+  </si>
+  <si>
     <t>Spotter</t>
   </si>
   <si>
+    <t>Steady Breath</t>
+  </si>
+  <si>
+    <t>Bolt Racking</t>
+  </si>
+  <si>
+    <t>Marked Target</t>
+  </si>
+  <si>
+    <t>Tactical Spotter</t>
+  </si>
+  <si>
+    <t>Eye in the Sky</t>
+  </si>
+  <si>
     <t>Siege</t>
   </si>
   <si>
+    <t>Large Calibre</t>
+  </si>
+  <si>
+    <t>Anti-Materiel</t>
+  </si>
+  <si>
+    <t>Concussion Round</t>
+  </si>
+  <si>
+    <t>Siege Gun</t>
+  </si>
+  <si>
+    <t>Skybreaker</t>
+  </si>
+  <si>
     <t>Blast</t>
   </si>
   <si>
+    <t>Bigger Bang</t>
+  </si>
+  <si>
+    <t>Shrapnel</t>
+  </si>
+  <si>
+    <t>Napalm</t>
+  </si>
+  <si>
+    <t>Firestorm</t>
+  </si>
+  <si>
+    <t>Scorched Earth</t>
+  </si>
+  <si>
     <t>Cluster</t>
   </si>
   <si>
+    <t>Cluster Shell</t>
+  </si>
+  <si>
+    <t>Rapid Loader</t>
+  </si>
+  <si>
+    <t>Chain Reaction</t>
+  </si>
+  <si>
+    <t>Carpet Shelling</t>
+  </si>
+  <si>
+    <t>Storm of Steel</t>
+  </si>
+  <si>
     <t>Concussive</t>
   </si>
   <si>
+    <t>Shockwave</t>
+  </si>
+  <si>
+    <t>Armor Crack</t>
+  </si>
+  <si>
+    <t>Stun Grenade</t>
+  </si>
+  <si>
+    <t>Earthshaker</t>
+  </si>
+  <si>
+    <t>Tectonic Slam</t>
+  </si>
+  <si>
     <t>Field</t>
   </si>
   <si>
+    <t>Cold Snap</t>
+  </si>
+  <si>
+    <t>Frostbite</t>
+  </si>
+  <si>
+    <t>Permafrost</t>
+  </si>
+  <si>
+    <t>Glacier Zone</t>
+  </si>
+  <si>
+    <t>Absolute Zero</t>
+  </si>
+  <si>
     <t>Freeze</t>
   </si>
   <si>
+    <t>Flash Freeze</t>
+  </si>
+  <si>
+    <t>Deep Freeze</t>
+  </si>
+  <si>
+    <t>Ice Shards</t>
+  </si>
+  <si>
+    <t>Cryo Pulse</t>
+  </si>
+  <si>
+    <t>Stasis</t>
+  </si>
+  <si>
     <t>Brittle</t>
   </si>
   <si>
+    <t>Shatter</t>
+  </si>
+  <si>
+    <t>Cold Front</t>
+  </si>
+  <si>
+    <t>Frozen Core</t>
+  </si>
+  <si>
+    <t>Winter's Edge</t>
+  </si>
+  <si>
     <t>Yield</t>
   </si>
   <si>
@@ -544,10 +727,55 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>Supply Crate</t>
+  </si>
+  <si>
+    <t>Bigger Budget</t>
+  </si>
+  <si>
+    <t>Trade Route</t>
+  </si>
+  <si>
+    <t>War Chest</t>
+  </si>
+  <si>
+    <t>Storm Bank</t>
+  </si>
+  <si>
     <t>Airdrop</t>
   </si>
   <si>
+    <t>Air Drop</t>
+  </si>
+  <si>
+    <t>Double Drop</t>
+  </si>
+  <si>
+    <t>Care Package</t>
+  </si>
+  <si>
+    <t>Supply Chain</t>
+  </si>
+  <si>
+    <t>Treasure Barge</t>
+  </si>
+  <si>
     <t>Logistics</t>
+  </si>
+  <si>
+    <t>Bulk Order</t>
+  </si>
+  <si>
+    <t>Field Engineer</t>
+  </si>
+  <si>
+    <t>Recycler</t>
+  </si>
+  <si>
+    <t>Forward Base</t>
+  </si>
+  <si>
+    <t>Command Center</t>
   </si>
   <si>
     <t>PLAYER WEAPONS — in-round track</t>
@@ -3745,7 +3973,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="15" style="49" customWidth="1"/>
@@ -3760,7 +3988,8 @@
     <col min="10" max="10" width="13" style="49" customWidth="1"/>
     <col min="11" max="11" width="12" style="49" customWidth="1"/>
     <col min="12" max="12" width="10" style="49" customWidth="1"/>
-    <col min="13" max="16384" width="8.67188" style="49" customWidth="1"/>
+    <col min="13" max="13" width="22" style="49" customWidth="1"/>
+    <col min="14" max="16384" width="8.67188" style="49" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.5" customHeight="1">
@@ -3778,6 +4007,7 @@
       <c r="J1" s="3"/>
       <c r="K1" s="4"/>
       <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
     </row>
     <row r="2" ht="13.65" customHeight="1">
       <c r="A2" t="s" s="5">
@@ -3794,6 +4024,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="7"/>
       <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
     </row>
     <row r="3" ht="13.55" customHeight="1">
       <c r="A3" s="19"/>
@@ -3808,6 +4039,7 @@
       <c r="J3" s="20"/>
       <c r="K3" s="37"/>
       <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
     </row>
     <row r="4" ht="27.75" customHeight="1">
       <c r="A4" t="s" s="21">
@@ -3846,16 +4078,19 @@
       <c r="L4" t="s" s="21">
         <v>148</v>
       </c>
+      <c r="M4" t="s" s="21">
+        <v>149</v>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1">
       <c r="A5" t="s" s="38">
         <v>117</v>
       </c>
       <c r="B5" t="s" s="38">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C5" t="s" s="38">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D5" s="53">
         <v>1</v>
@@ -3888,16 +4123,19 @@
       <c r="L5" s="54">
         <v>1.15</v>
       </c>
+      <c r="M5" t="s" s="38">
+        <v>152</v>
+      </c>
     </row>
     <row r="6" ht="13.65" customHeight="1">
       <c r="A6" t="s" s="38">
         <v>117</v>
       </c>
       <c r="B6" t="s" s="38">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C6" t="s" s="38">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D6" s="53">
         <v>2</v>
@@ -3930,16 +4168,19 @@
       <c r="L6" s="54">
         <v>1.3</v>
       </c>
+      <c r="M6" t="s" s="38">
+        <v>153</v>
+      </c>
     </row>
     <row r="7" ht="13.65" customHeight="1">
       <c r="A7" t="s" s="38">
         <v>117</v>
       </c>
       <c r="B7" t="s" s="38">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C7" t="s" s="38">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D7" s="53">
         <v>3</v>
@@ -3972,16 +4213,19 @@
       <c r="L7" s="54">
         <v>1.5</v>
       </c>
+      <c r="M7" t="s" s="38">
+        <v>154</v>
+      </c>
     </row>
     <row r="8" ht="13.65" customHeight="1">
       <c r="A8" t="s" s="38">
         <v>117</v>
       </c>
       <c r="B8" t="s" s="38">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C8" t="s" s="38">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D8" s="53">
         <v>4</v>
@@ -4014,16 +4258,19 @@
       <c r="L8" s="54">
         <v>1.75</v>
       </c>
+      <c r="M8" t="s" s="38">
+        <v>155</v>
+      </c>
     </row>
     <row r="9" ht="13.65" customHeight="1">
       <c r="A9" t="s" s="38">
         <v>117</v>
       </c>
       <c r="B9" t="s" s="38">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s" s="38">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D9" s="53">
         <v>5</v>
@@ -4056,16 +4303,19 @@
       <c r="L9" s="54">
         <v>2</v>
       </c>
+      <c r="M9" t="s" s="38">
+        <v>156</v>
+      </c>
     </row>
     <row r="10" ht="13.65" customHeight="1">
       <c r="A10" t="s" s="38">
         <v>117</v>
       </c>
       <c r="B10" t="s" s="38">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C10" t="s" s="38">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D10" s="53">
         <v>1</v>
@@ -4098,16 +4348,19 @@
       <c r="L10" s="54">
         <v>1</v>
       </c>
+      <c r="M10" t="s" s="38">
+        <v>159</v>
+      </c>
     </row>
     <row r="11" ht="13.65" customHeight="1">
       <c r="A11" t="s" s="38">
         <v>117</v>
       </c>
       <c r="B11" t="s" s="38">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C11" t="s" s="38">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D11" s="53">
         <v>2</v>
@@ -4140,16 +4393,19 @@
       <c r="L11" s="54">
         <v>1</v>
       </c>
+      <c r="M11" t="s" s="38">
+        <v>160</v>
+      </c>
     </row>
     <row r="12" ht="13.65" customHeight="1">
       <c r="A12" t="s" s="38">
         <v>117</v>
       </c>
       <c r="B12" t="s" s="38">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C12" t="s" s="38">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D12" s="53">
         <v>3</v>
@@ -4182,16 +4438,19 @@
       <c r="L12" s="54">
         <v>1</v>
       </c>
+      <c r="M12" t="s" s="38">
+        <v>161</v>
+      </c>
     </row>
     <row r="13" ht="13.65" customHeight="1">
       <c r="A13" t="s" s="38">
         <v>117</v>
       </c>
       <c r="B13" t="s" s="38">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C13" t="s" s="38">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D13" s="53">
         <v>4</v>
@@ -4224,16 +4483,19 @@
       <c r="L13" s="54">
         <v>1</v>
       </c>
+      <c r="M13" t="s" s="38">
+        <v>162</v>
+      </c>
     </row>
     <row r="14" ht="13.65" customHeight="1">
       <c r="A14" t="s" s="38">
         <v>117</v>
       </c>
       <c r="B14" t="s" s="38">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C14" t="s" s="38">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D14" s="53">
         <v>5</v>
@@ -4266,16 +4528,19 @@
       <c r="L14" s="54">
         <v>1</v>
       </c>
+      <c r="M14" t="s" s="38">
+        <v>163</v>
+      </c>
     </row>
     <row r="15" ht="13.65" customHeight="1">
       <c r="A15" t="s" s="38">
         <v>117</v>
       </c>
       <c r="B15" t="s" s="38">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="C15" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D15" s="53">
         <v>1</v>
@@ -4308,16 +4573,19 @@
       <c r="L15" s="54">
         <v>1</v>
       </c>
+      <c r="M15" t="s" s="38">
+        <v>166</v>
+      </c>
     </row>
     <row r="16" ht="13.65" customHeight="1">
       <c r="A16" t="s" s="38">
         <v>117</v>
       </c>
       <c r="B16" t="s" s="38">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="C16" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D16" s="53">
         <v>2</v>
@@ -4350,16 +4618,19 @@
       <c r="L16" s="54">
         <v>1</v>
       </c>
+      <c r="M16" t="s" s="38">
+        <v>167</v>
+      </c>
     </row>
     <row r="17" ht="13.65" customHeight="1">
       <c r="A17" t="s" s="38">
         <v>117</v>
       </c>
       <c r="B17" t="s" s="38">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="C17" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D17" s="53">
         <v>3</v>
@@ -4392,16 +4663,19 @@
       <c r="L17" s="54">
         <v>1</v>
       </c>
+      <c r="M17" t="s" s="38">
+        <v>168</v>
+      </c>
     </row>
     <row r="18" ht="13.65" customHeight="1">
       <c r="A18" t="s" s="38">
         <v>117</v>
       </c>
       <c r="B18" t="s" s="38">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="C18" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D18" s="53">
         <v>4</v>
@@ -4434,16 +4708,19 @@
       <c r="L18" s="54">
         <v>1</v>
       </c>
+      <c r="M18" t="s" s="38">
+        <v>169</v>
+      </c>
     </row>
     <row r="19" ht="13.65" customHeight="1">
       <c r="A19" t="s" s="38">
         <v>117</v>
       </c>
       <c r="B19" t="s" s="38">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="C19" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D19" s="53">
         <v>5</v>
@@ -4476,16 +4753,19 @@
       <c r="L19" s="54">
         <v>1</v>
       </c>
+      <c r="M19" t="s" s="38">
+        <v>170</v>
+      </c>
     </row>
     <row r="20" ht="13.65" customHeight="1">
       <c r="A20" t="s" s="38">
         <v>121</v>
       </c>
       <c r="B20" t="s" s="38">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="C20" t="s" s="38">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D20" s="53">
         <v>1</v>
@@ -4518,16 +4798,19 @@
       <c r="L20" s="54">
         <v>1</v>
       </c>
+      <c r="M20" t="s" s="38">
+        <v>173</v>
+      </c>
     </row>
     <row r="21" ht="13.65" customHeight="1">
       <c r="A21" t="s" s="38">
         <v>121</v>
       </c>
       <c r="B21" t="s" s="38">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="C21" t="s" s="38">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D21" s="53">
         <v>2</v>
@@ -4560,16 +4843,19 @@
       <c r="L21" s="54">
         <v>1</v>
       </c>
+      <c r="M21" t="s" s="38">
+        <v>174</v>
+      </c>
     </row>
     <row r="22" ht="13.65" customHeight="1">
       <c r="A22" t="s" s="38">
         <v>121</v>
       </c>
       <c r="B22" t="s" s="38">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="C22" t="s" s="38">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D22" s="53">
         <v>3</v>
@@ -4602,16 +4888,19 @@
       <c r="L22" s="54">
         <v>1</v>
       </c>
+      <c r="M22" t="s" s="38">
+        <v>175</v>
+      </c>
     </row>
     <row r="23" ht="13.65" customHeight="1">
       <c r="A23" t="s" s="38">
         <v>121</v>
       </c>
       <c r="B23" t="s" s="38">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="C23" t="s" s="38">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D23" s="53">
         <v>4</v>
@@ -4644,16 +4933,19 @@
       <c r="L23" s="54">
         <v>1</v>
       </c>
+      <c r="M23" t="s" s="38">
+        <v>176</v>
+      </c>
     </row>
     <row r="24" ht="13.65" customHeight="1">
       <c r="A24" t="s" s="38">
         <v>121</v>
       </c>
       <c r="B24" t="s" s="38">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="C24" t="s" s="38">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D24" s="53">
         <v>5</v>
@@ -4686,16 +4978,19 @@
       <c r="L24" s="54">
         <v>1</v>
       </c>
+      <c r="M24" t="s" s="38">
+        <v>177</v>
+      </c>
     </row>
     <row r="25" ht="13.65" customHeight="1">
       <c r="A25" t="s" s="38">
         <v>121</v>
       </c>
       <c r="B25" t="s" s="38">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C25" t="s" s="38">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D25" s="53">
         <v>1</v>
@@ -4728,16 +5023,19 @@
       <c r="L25" s="54">
         <v>1</v>
       </c>
+      <c r="M25" t="s" s="38">
+        <v>179</v>
+      </c>
     </row>
     <row r="26" ht="13.65" customHeight="1">
       <c r="A26" t="s" s="38">
         <v>121</v>
       </c>
       <c r="B26" t="s" s="38">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C26" t="s" s="38">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D26" s="53">
         <v>2</v>
@@ -4770,16 +5068,19 @@
       <c r="L26" s="54">
         <v>1</v>
       </c>
+      <c r="M26" t="s" s="38">
+        <v>180</v>
+      </c>
     </row>
     <row r="27" ht="13.65" customHeight="1">
       <c r="A27" t="s" s="38">
         <v>121</v>
       </c>
       <c r="B27" t="s" s="38">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C27" t="s" s="38">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D27" s="53">
         <v>3</v>
@@ -4812,16 +5113,19 @@
       <c r="L27" s="54">
         <v>1</v>
       </c>
+      <c r="M27" t="s" s="38">
+        <v>181</v>
+      </c>
     </row>
     <row r="28" ht="13.65" customHeight="1">
       <c r="A28" t="s" s="38">
         <v>121</v>
       </c>
       <c r="B28" t="s" s="38">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C28" t="s" s="38">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D28" s="53">
         <v>4</v>
@@ -4854,16 +5158,19 @@
       <c r="L28" s="54">
         <v>1</v>
       </c>
+      <c r="M28" t="s" s="38">
+        <v>182</v>
+      </c>
     </row>
     <row r="29" ht="13.65" customHeight="1">
       <c r="A29" t="s" s="38">
         <v>121</v>
       </c>
       <c r="B29" t="s" s="38">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C29" t="s" s="38">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D29" s="53">
         <v>5</v>
@@ -4896,16 +5203,19 @@
       <c r="L29" s="54">
         <v>1</v>
       </c>
+      <c r="M29" t="s" s="38">
+        <v>183</v>
+      </c>
     </row>
     <row r="30" ht="13.65" customHeight="1">
       <c r="A30" t="s" s="38">
         <v>121</v>
       </c>
       <c r="B30" t="s" s="38">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="C30" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D30" s="53">
         <v>1</v>
@@ -4938,16 +5248,19 @@
       <c r="L30" s="54">
         <v>1</v>
       </c>
+      <c r="M30" t="s" s="38">
+        <v>185</v>
+      </c>
     </row>
     <row r="31" ht="13.65" customHeight="1">
       <c r="A31" t="s" s="38">
         <v>121</v>
       </c>
       <c r="B31" t="s" s="38">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="C31" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D31" s="53">
         <v>2</v>
@@ -4980,16 +5293,19 @@
       <c r="L31" s="54">
         <v>1</v>
       </c>
+      <c r="M31" t="s" s="38">
+        <v>186</v>
+      </c>
     </row>
     <row r="32" ht="13.65" customHeight="1">
       <c r="A32" t="s" s="38">
         <v>121</v>
       </c>
       <c r="B32" t="s" s="38">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="C32" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D32" s="53">
         <v>3</v>
@@ -5022,16 +5338,19 @@
       <c r="L32" s="54">
         <v>1</v>
       </c>
+      <c r="M32" t="s" s="38">
+        <v>187</v>
+      </c>
     </row>
     <row r="33" ht="13.65" customHeight="1">
       <c r="A33" t="s" s="38">
         <v>121</v>
       </c>
       <c r="B33" t="s" s="38">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="C33" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D33" s="53">
         <v>4</v>
@@ -5064,16 +5383,19 @@
       <c r="L33" s="54">
         <v>1</v>
       </c>
+      <c r="M33" t="s" s="38">
+        <v>188</v>
+      </c>
     </row>
     <row r="34" ht="13.65" customHeight="1">
       <c r="A34" t="s" s="38">
         <v>121</v>
       </c>
       <c r="B34" t="s" s="38">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="C34" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D34" s="53">
         <v>5</v>
@@ -5106,16 +5428,19 @@
       <c r="L34" s="54">
         <v>1</v>
       </c>
+      <c r="M34" t="s" s="38">
+        <v>189</v>
+      </c>
     </row>
     <row r="35" ht="13.65" customHeight="1">
       <c r="A35" t="s" s="38">
         <v>124</v>
       </c>
       <c r="B35" t="s" s="38">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="C35" t="s" s="38">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D35" s="53">
         <v>1</v>
@@ -5148,16 +5473,19 @@
       <c r="L35" s="54">
         <v>1</v>
       </c>
+      <c r="M35" t="s" s="38">
+        <v>191</v>
+      </c>
     </row>
     <row r="36" ht="13.65" customHeight="1">
       <c r="A36" t="s" s="38">
         <v>124</v>
       </c>
       <c r="B36" t="s" s="38">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="C36" t="s" s="38">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D36" s="53">
         <v>2</v>
@@ -5190,16 +5518,19 @@
       <c r="L36" s="54">
         <v>1</v>
       </c>
+      <c r="M36" t="s" s="38">
+        <v>192</v>
+      </c>
     </row>
     <row r="37" ht="13.65" customHeight="1">
       <c r="A37" t="s" s="38">
         <v>124</v>
       </c>
       <c r="B37" t="s" s="38">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="C37" t="s" s="38">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D37" s="53">
         <v>3</v>
@@ -5232,16 +5563,19 @@
       <c r="L37" s="54">
         <v>1</v>
       </c>
+      <c r="M37" t="s" s="38">
+        <v>193</v>
+      </c>
     </row>
     <row r="38" ht="13.65" customHeight="1">
       <c r="A38" t="s" s="38">
         <v>124</v>
       </c>
       <c r="B38" t="s" s="38">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="C38" t="s" s="38">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D38" s="53">
         <v>4</v>
@@ -5274,16 +5608,19 @@
       <c r="L38" s="54">
         <v>1</v>
       </c>
+      <c r="M38" t="s" s="38">
+        <v>194</v>
+      </c>
     </row>
     <row r="39" ht="13.65" customHeight="1">
       <c r="A39" t="s" s="38">
         <v>124</v>
       </c>
       <c r="B39" t="s" s="38">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="C39" t="s" s="38">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D39" s="53">
         <v>5</v>
@@ -5316,16 +5653,19 @@
       <c r="L39" s="54">
         <v>1</v>
       </c>
+      <c r="M39" t="s" s="38">
+        <v>195</v>
+      </c>
     </row>
     <row r="40" ht="13.65" customHeight="1">
       <c r="A40" t="s" s="38">
         <v>124</v>
       </c>
       <c r="B40" t="s" s="38">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="C40" t="s" s="38">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D40" s="53">
         <v>1</v>
@@ -5358,16 +5698,19 @@
       <c r="L40" s="54">
         <v>1</v>
       </c>
+      <c r="M40" t="s" s="38">
+        <v>197</v>
+      </c>
     </row>
     <row r="41" ht="13.65" customHeight="1">
       <c r="A41" t="s" s="38">
         <v>124</v>
       </c>
       <c r="B41" t="s" s="38">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="C41" t="s" s="38">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D41" s="53">
         <v>2</v>
@@ -5400,16 +5743,19 @@
       <c r="L41" s="54">
         <v>1</v>
       </c>
+      <c r="M41" t="s" s="38">
+        <v>198</v>
+      </c>
     </row>
     <row r="42" ht="13.65" customHeight="1">
       <c r="A42" t="s" s="38">
         <v>124</v>
       </c>
       <c r="B42" t="s" s="38">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="C42" t="s" s="38">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D42" s="53">
         <v>3</v>
@@ -5442,16 +5788,19 @@
       <c r="L42" s="54">
         <v>1</v>
       </c>
+      <c r="M42" t="s" s="38">
+        <v>199</v>
+      </c>
     </row>
     <row r="43" ht="13.65" customHeight="1">
       <c r="A43" t="s" s="38">
         <v>124</v>
       </c>
       <c r="B43" t="s" s="38">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="C43" t="s" s="38">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D43" s="53">
         <v>4</v>
@@ -5484,16 +5833,19 @@
       <c r="L43" s="54">
         <v>1</v>
       </c>
+      <c r="M43" t="s" s="38">
+        <v>200</v>
+      </c>
     </row>
     <row r="44" ht="13.65" customHeight="1">
       <c r="A44" t="s" s="38">
         <v>124</v>
       </c>
       <c r="B44" t="s" s="38">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="C44" t="s" s="38">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D44" s="53">
         <v>5</v>
@@ -5526,16 +5878,19 @@
       <c r="L44" s="54">
         <v>1</v>
       </c>
+      <c r="M44" t="s" s="38">
+        <v>201</v>
+      </c>
     </row>
     <row r="45" ht="13.65" customHeight="1">
       <c r="A45" t="s" s="38">
         <v>124</v>
       </c>
       <c r="B45" t="s" s="38">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="C45" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D45" s="53">
         <v>1</v>
@@ -5568,16 +5923,19 @@
       <c r="L45" s="54">
         <v>1</v>
       </c>
+      <c r="M45" t="s" s="38">
+        <v>203</v>
+      </c>
     </row>
     <row r="46" ht="13.65" customHeight="1">
       <c r="A46" t="s" s="38">
         <v>124</v>
       </c>
       <c r="B46" t="s" s="38">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="C46" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D46" s="53">
         <v>2</v>
@@ -5610,16 +5968,19 @@
       <c r="L46" s="54">
         <v>1</v>
       </c>
+      <c r="M46" t="s" s="38">
+        <v>204</v>
+      </c>
     </row>
     <row r="47" ht="13.65" customHeight="1">
       <c r="A47" t="s" s="38">
         <v>124</v>
       </c>
       <c r="B47" t="s" s="38">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="C47" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D47" s="53">
         <v>3</v>
@@ -5652,16 +6013,19 @@
       <c r="L47" s="54">
         <v>1</v>
       </c>
+      <c r="M47" t="s" s="38">
+        <v>205</v>
+      </c>
     </row>
     <row r="48" ht="13.65" customHeight="1">
       <c r="A48" t="s" s="38">
         <v>124</v>
       </c>
       <c r="B48" t="s" s="38">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="C48" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D48" s="53">
         <v>4</v>
@@ -5694,16 +6058,19 @@
       <c r="L48" s="54">
         <v>1</v>
       </c>
+      <c r="M48" t="s" s="38">
+        <v>206</v>
+      </c>
     </row>
     <row r="49" ht="13.65" customHeight="1">
       <c r="A49" t="s" s="38">
         <v>124</v>
       </c>
       <c r="B49" t="s" s="38">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="C49" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D49" s="53">
         <v>5</v>
@@ -5736,16 +6103,19 @@
       <c r="L49" s="54">
         <v>1</v>
       </c>
+      <c r="M49" t="s" s="38">
+        <v>207</v>
+      </c>
     </row>
     <row r="50" ht="13.65" customHeight="1">
       <c r="A50" t="s" s="38">
         <v>128</v>
       </c>
       <c r="B50" t="s" s="38">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="C50" t="s" s="38">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D50" s="53">
         <v>1</v>
@@ -5778,16 +6148,19 @@
       <c r="L50" s="54">
         <v>1.15</v>
       </c>
+      <c r="M50" t="s" s="38">
+        <v>209</v>
+      </c>
     </row>
     <row r="51" ht="13.65" customHeight="1">
       <c r="A51" t="s" s="38">
         <v>128</v>
       </c>
       <c r="B51" t="s" s="38">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="C51" t="s" s="38">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D51" s="53">
         <v>2</v>
@@ -5820,16 +6193,19 @@
       <c r="L51" s="54">
         <v>1.3</v>
       </c>
+      <c r="M51" t="s" s="38">
+        <v>210</v>
+      </c>
     </row>
     <row r="52" ht="13.65" customHeight="1">
       <c r="A52" t="s" s="38">
         <v>128</v>
       </c>
       <c r="B52" t="s" s="38">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="C52" t="s" s="38">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D52" s="53">
         <v>3</v>
@@ -5862,16 +6238,19 @@
       <c r="L52" s="54">
         <v>1.5</v>
       </c>
+      <c r="M52" t="s" s="38">
+        <v>211</v>
+      </c>
     </row>
     <row r="53" ht="13.65" customHeight="1">
       <c r="A53" t="s" s="38">
         <v>128</v>
       </c>
       <c r="B53" t="s" s="38">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="C53" t="s" s="38">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D53" s="53">
         <v>4</v>
@@ -5904,16 +6283,19 @@
       <c r="L53" s="54">
         <v>1.75</v>
       </c>
+      <c r="M53" t="s" s="38">
+        <v>212</v>
+      </c>
     </row>
     <row r="54" ht="13.65" customHeight="1">
       <c r="A54" t="s" s="38">
         <v>128</v>
       </c>
       <c r="B54" t="s" s="38">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="C54" t="s" s="38">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D54" s="53">
         <v>5</v>
@@ -5946,16 +6328,19 @@
       <c r="L54" s="54">
         <v>2</v>
       </c>
+      <c r="M54" t="s" s="38">
+        <v>213</v>
+      </c>
     </row>
     <row r="55" ht="13.65" customHeight="1">
       <c r="A55" t="s" s="38">
         <v>128</v>
       </c>
       <c r="B55" t="s" s="38">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="C55" t="s" s="38">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D55" s="53">
         <v>1</v>
@@ -5988,16 +6373,19 @@
       <c r="L55" s="54">
         <v>1</v>
       </c>
+      <c r="M55" t="s" s="38">
+        <v>215</v>
+      </c>
     </row>
     <row r="56" ht="13.65" customHeight="1">
       <c r="A56" t="s" s="38">
         <v>128</v>
       </c>
       <c r="B56" t="s" s="38">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="C56" t="s" s="38">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D56" s="53">
         <v>2</v>
@@ -6030,16 +6418,19 @@
       <c r="L56" s="54">
         <v>1</v>
       </c>
+      <c r="M56" t="s" s="38">
+        <v>216</v>
+      </c>
     </row>
     <row r="57" ht="13.65" customHeight="1">
       <c r="A57" t="s" s="38">
         <v>128</v>
       </c>
       <c r="B57" t="s" s="38">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="C57" t="s" s="38">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D57" s="53">
         <v>3</v>
@@ -6072,16 +6463,19 @@
       <c r="L57" s="54">
         <v>1</v>
       </c>
+      <c r="M57" t="s" s="38">
+        <v>217</v>
+      </c>
     </row>
     <row r="58" ht="13.65" customHeight="1">
       <c r="A58" t="s" s="38">
         <v>128</v>
       </c>
       <c r="B58" t="s" s="38">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="C58" t="s" s="38">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D58" s="53">
         <v>4</v>
@@ -6114,16 +6508,19 @@
       <c r="L58" s="54">
         <v>1</v>
       </c>
+      <c r="M58" t="s" s="38">
+        <v>218</v>
+      </c>
     </row>
     <row r="59" ht="13.65" customHeight="1">
       <c r="A59" t="s" s="38">
         <v>128</v>
       </c>
       <c r="B59" t="s" s="38">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="C59" t="s" s="38">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D59" s="53">
         <v>5</v>
@@ -6156,16 +6553,19 @@
       <c r="L59" s="54">
         <v>1</v>
       </c>
+      <c r="M59" t="s" s="38">
+        <v>219</v>
+      </c>
     </row>
     <row r="60" ht="13.65" customHeight="1">
       <c r="A60" t="s" s="38">
         <v>128</v>
       </c>
       <c r="B60" t="s" s="38">
-        <v>163</v>
+        <v>220</v>
       </c>
       <c r="C60" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D60" s="53">
         <v>1</v>
@@ -6198,16 +6598,19 @@
       <c r="L60" s="54">
         <v>1</v>
       </c>
+      <c r="M60" t="s" s="38">
+        <v>220</v>
+      </c>
     </row>
     <row r="61" ht="13.65" customHeight="1">
       <c r="A61" t="s" s="38">
         <v>128</v>
       </c>
       <c r="B61" t="s" s="38">
-        <v>163</v>
+        <v>220</v>
       </c>
       <c r="C61" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D61" s="53">
         <v>2</v>
@@ -6240,16 +6643,19 @@
       <c r="L61" s="54">
         <v>1</v>
       </c>
+      <c r="M61" t="s" s="38">
+        <v>221</v>
+      </c>
     </row>
     <row r="62" ht="13.65" customHeight="1">
       <c r="A62" t="s" s="38">
         <v>128</v>
       </c>
       <c r="B62" t="s" s="38">
-        <v>163</v>
+        <v>220</v>
       </c>
       <c r="C62" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D62" s="53">
         <v>3</v>
@@ -6282,16 +6688,19 @@
       <c r="L62" s="54">
         <v>1</v>
       </c>
+      <c r="M62" t="s" s="38">
+        <v>222</v>
+      </c>
     </row>
     <row r="63" ht="13.65" customHeight="1">
       <c r="A63" t="s" s="38">
         <v>128</v>
       </c>
       <c r="B63" t="s" s="38">
-        <v>163</v>
+        <v>220</v>
       </c>
       <c r="C63" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D63" s="53">
         <v>4</v>
@@ -6324,16 +6733,19 @@
       <c r="L63" s="54">
         <v>1</v>
       </c>
+      <c r="M63" t="s" s="38">
+        <v>223</v>
+      </c>
     </row>
     <row r="64" ht="13.65" customHeight="1">
       <c r="A64" t="s" s="38">
         <v>128</v>
       </c>
       <c r="B64" t="s" s="38">
-        <v>163</v>
+        <v>220</v>
       </c>
       <c r="C64" t="s" s="38">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D64" s="53">
         <v>5</v>
@@ -6366,16 +6778,19 @@
       <c r="L64" s="54">
         <v>1</v>
       </c>
+      <c r="M64" t="s" s="38">
+        <v>224</v>
+      </c>
     </row>
     <row r="65" ht="13.65" customHeight="1">
       <c r="A65" t="s" s="38">
         <v>131</v>
       </c>
       <c r="B65" t="s" s="38">
-        <v>164</v>
+        <v>225</v>
       </c>
       <c r="C65" t="s" s="38">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="D65" s="53">
         <v>1</v>
@@ -6401,10 +6816,13 @@
         <v>0</v>
       </c>
       <c r="K65" t="s" s="38">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="L65" s="54">
         <v>1</v>
+      </c>
+      <c r="M65" t="s" s="38">
+        <v>228</v>
       </c>
     </row>
     <row r="66" ht="13.65" customHeight="1">
@@ -6412,10 +6830,10 @@
         <v>131</v>
       </c>
       <c r="B66" t="s" s="38">
-        <v>164</v>
+        <v>225</v>
       </c>
       <c r="C66" t="s" s="38">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="D66" s="53">
         <v>2</v>
@@ -6441,10 +6859,13 @@
         <v>0</v>
       </c>
       <c r="K66" t="s" s="38">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="L66" s="54">
         <v>1</v>
+      </c>
+      <c r="M66" t="s" s="38">
+        <v>229</v>
       </c>
     </row>
     <row r="67" ht="13.65" customHeight="1">
@@ -6452,10 +6873,10 @@
         <v>131</v>
       </c>
       <c r="B67" t="s" s="38">
-        <v>164</v>
+        <v>225</v>
       </c>
       <c r="C67" t="s" s="38">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="D67" s="53">
         <v>3</v>
@@ -6481,10 +6902,13 @@
         <v>0</v>
       </c>
       <c r="K67" t="s" s="38">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="L67" s="54">
         <v>1</v>
+      </c>
+      <c r="M67" t="s" s="38">
+        <v>230</v>
       </c>
     </row>
     <row r="68" ht="13.65" customHeight="1">
@@ -6492,10 +6916,10 @@
         <v>131</v>
       </c>
       <c r="B68" t="s" s="38">
-        <v>164</v>
+        <v>225</v>
       </c>
       <c r="C68" t="s" s="38">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="D68" s="53">
         <v>4</v>
@@ -6521,10 +6945,13 @@
         <v>0</v>
       </c>
       <c r="K68" t="s" s="38">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="L68" s="54">
         <v>1</v>
+      </c>
+      <c r="M68" t="s" s="38">
+        <v>231</v>
       </c>
     </row>
     <row r="69" ht="13.65" customHeight="1">
@@ -6532,10 +6959,10 @@
         <v>131</v>
       </c>
       <c r="B69" t="s" s="38">
-        <v>164</v>
+        <v>225</v>
       </c>
       <c r="C69" t="s" s="38">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="D69" s="53">
         <v>5</v>
@@ -6561,10 +6988,13 @@
         <v>0</v>
       </c>
       <c r="K69" t="s" s="38">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="L69" s="54">
         <v>1</v>
+      </c>
+      <c r="M69" t="s" s="38">
+        <v>232</v>
       </c>
     </row>
     <row r="70" ht="13.65" customHeight="1">
@@ -6572,10 +7002,10 @@
         <v>131</v>
       </c>
       <c r="B70" t="s" s="38">
-        <v>167</v>
+        <v>233</v>
       </c>
       <c r="C70" t="s" s="38">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="D70" s="53">
         <v>1</v>
@@ -6601,10 +7031,13 @@
         <v>0</v>
       </c>
       <c r="K70" t="s" s="38">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="L70" s="54">
         <v>1</v>
+      </c>
+      <c r="M70" t="s" s="38">
+        <v>234</v>
       </c>
     </row>
     <row r="71" ht="13.65" customHeight="1">
@@ -6612,10 +7045,10 @@
         <v>131</v>
       </c>
       <c r="B71" t="s" s="38">
-        <v>167</v>
+        <v>233</v>
       </c>
       <c r="C71" t="s" s="38">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="D71" s="53">
         <v>2</v>
@@ -6641,10 +7074,13 @@
         <v>0</v>
       </c>
       <c r="K71" t="s" s="38">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="L71" s="54">
         <v>1</v>
+      </c>
+      <c r="M71" t="s" s="38">
+        <v>235</v>
       </c>
     </row>
     <row r="72" ht="13.65" customHeight="1">
@@ -6652,10 +7088,10 @@
         <v>131</v>
       </c>
       <c r="B72" t="s" s="38">
-        <v>167</v>
+        <v>233</v>
       </c>
       <c r="C72" t="s" s="38">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="D72" s="53">
         <v>3</v>
@@ -6681,10 +7117,13 @@
         <v>0</v>
       </c>
       <c r="K72" t="s" s="38">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="L72" s="54">
         <v>1</v>
+      </c>
+      <c r="M72" t="s" s="38">
+        <v>236</v>
       </c>
     </row>
     <row r="73" ht="13.65" customHeight="1">
@@ -6692,10 +7131,10 @@
         <v>131</v>
       </c>
       <c r="B73" t="s" s="38">
-        <v>167</v>
+        <v>233</v>
       </c>
       <c r="C73" t="s" s="38">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="D73" s="53">
         <v>4</v>
@@ -6721,10 +7160,13 @@
         <v>0</v>
       </c>
       <c r="K73" t="s" s="38">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="L73" s="54">
         <v>1</v>
+      </c>
+      <c r="M73" t="s" s="38">
+        <v>237</v>
       </c>
     </row>
     <row r="74" ht="13.65" customHeight="1">
@@ -6732,10 +7174,10 @@
         <v>131</v>
       </c>
       <c r="B74" t="s" s="38">
-        <v>167</v>
+        <v>233</v>
       </c>
       <c r="C74" t="s" s="38">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="D74" s="53">
         <v>5</v>
@@ -6761,10 +7203,13 @@
         <v>0</v>
       </c>
       <c r="K74" t="s" s="38">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="L74" s="54">
         <v>1</v>
+      </c>
+      <c r="M74" t="s" s="38">
+        <v>238</v>
       </c>
     </row>
     <row r="75" ht="13.65" customHeight="1">
@@ -6772,10 +7217,10 @@
         <v>131</v>
       </c>
       <c r="B75" t="s" s="38">
-        <v>168</v>
+        <v>239</v>
       </c>
       <c r="C75" t="s" s="38">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="D75" s="53">
         <v>1</v>
@@ -6801,10 +7246,13 @@
         <v>0</v>
       </c>
       <c r="K75" t="s" s="38">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="L75" s="54">
         <v>1</v>
+      </c>
+      <c r="M75" t="s" s="38">
+        <v>240</v>
       </c>
     </row>
     <row r="76" ht="13.65" customHeight="1">
@@ -6812,10 +7260,10 @@
         <v>131</v>
       </c>
       <c r="B76" t="s" s="38">
-        <v>168</v>
+        <v>239</v>
       </c>
       <c r="C76" t="s" s="38">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="D76" s="53">
         <v>2</v>
@@ -6841,10 +7289,13 @@
         <v>0</v>
       </c>
       <c r="K76" t="s" s="38">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="L76" s="54">
         <v>1</v>
+      </c>
+      <c r="M76" t="s" s="38">
+        <v>241</v>
       </c>
     </row>
     <row r="77" ht="13.65" customHeight="1">
@@ -6852,10 +7303,10 @@
         <v>131</v>
       </c>
       <c r="B77" t="s" s="38">
-        <v>168</v>
+        <v>239</v>
       </c>
       <c r="C77" t="s" s="38">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="D77" s="53">
         <v>3</v>
@@ -6881,10 +7332,13 @@
         <v>0</v>
       </c>
       <c r="K77" t="s" s="38">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="L77" s="54">
         <v>1</v>
+      </c>
+      <c r="M77" t="s" s="38">
+        <v>242</v>
       </c>
     </row>
     <row r="78" ht="13.65" customHeight="1">
@@ -6892,10 +7346,10 @@
         <v>131</v>
       </c>
       <c r="B78" t="s" s="38">
-        <v>168</v>
+        <v>239</v>
       </c>
       <c r="C78" t="s" s="38">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="D78" s="53">
         <v>4</v>
@@ -6921,10 +7375,13 @@
         <v>0</v>
       </c>
       <c r="K78" t="s" s="38">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="L78" s="54">
         <v>1</v>
+      </c>
+      <c r="M78" t="s" s="38">
+        <v>243</v>
       </c>
     </row>
     <row r="79" ht="13.65" customHeight="1">
@@ -6932,10 +7389,10 @@
         <v>131</v>
       </c>
       <c r="B79" t="s" s="38">
-        <v>168</v>
+        <v>239</v>
       </c>
       <c r="C79" t="s" s="38">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="D79" s="53">
         <v>5</v>
@@ -6961,10 +7418,13 @@
         <v>0</v>
       </c>
       <c r="K79" t="s" s="38">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="L79" s="54">
         <v>1</v>
+      </c>
+      <c r="M79" t="s" s="38">
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -6998,7 +7458,7 @@
   <sheetData>
     <row r="1" ht="18.5" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>169</v>
+        <v>245</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -7014,7 +7474,7 @@
     </row>
     <row r="2" ht="13.65" customHeight="1">
       <c r="A2" t="s" s="5">
-        <v>170</v>
+        <v>246</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -7044,22 +7504,22 @@
     </row>
     <row r="4" ht="27.75" customHeight="1">
       <c r="A4" t="s" s="21">
-        <v>171</v>
+        <v>247</v>
       </c>
       <c r="B4" t="s" s="21">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="C4" t="s" s="21">
         <v>140</v>
       </c>
       <c r="D4" t="s" s="21">
-        <v>173</v>
+        <v>249</v>
       </c>
       <c r="E4" t="s" s="21">
         <v>108</v>
       </c>
       <c r="F4" t="s" s="21">
-        <v>174</v>
+        <v>250</v>
       </c>
       <c r="G4" t="s" s="21">
         <v>109</v>
@@ -7068,30 +7528,30 @@
         <v>110</v>
       </c>
       <c r="I4" t="s" s="21">
-        <v>175</v>
+        <v>251</v>
       </c>
       <c r="J4" t="s" s="21">
-        <v>176</v>
+        <v>252</v>
       </c>
       <c r="K4" t="s" s="21">
-        <v>177</v>
+        <v>253</v>
       </c>
       <c r="L4" t="s" s="21">
-        <v>178</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" ht="13.65" customHeight="1">
       <c r="A5" t="s" s="38">
-        <v>179</v>
+        <v>255</v>
       </c>
       <c r="B5" t="s" s="56">
-        <v>180</v>
+        <v>256</v>
       </c>
       <c r="C5" s="53">
         <v>1</v>
       </c>
       <c r="D5" t="s" s="38">
-        <v>181</v>
+        <v>257</v>
       </c>
       <c r="E5" s="53" cm="1">
         <f t="array" ref="E5">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C5-1),0)</f>
@@ -7117,21 +7577,21 @@
       </c>
       <c r="K5" s="53"/>
       <c r="L5" t="s" s="42">
-        <v>182</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" ht="13.65" customHeight="1">
       <c r="A6" t="s" s="38">
-        <v>179</v>
+        <v>255</v>
       </c>
       <c r="B6" t="s" s="38">
-        <v>183</v>
+        <v>259</v>
       </c>
       <c r="C6" s="53">
         <v>2</v>
       </c>
       <c r="D6" t="s" s="38">
-        <v>184</v>
+        <v>260</v>
       </c>
       <c r="E6" s="53" cm="1">
         <f t="array" ref="E6">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C6-1),0)</f>
@@ -7162,16 +7622,16 @@
     </row>
     <row r="7" ht="13.65" customHeight="1">
       <c r="A7" t="s" s="38">
-        <v>179</v>
+        <v>255</v>
       </c>
       <c r="B7" t="s" s="38">
-        <v>183</v>
+        <v>259</v>
       </c>
       <c r="C7" s="53">
         <v>3</v>
       </c>
       <c r="D7" t="s" s="38">
-        <v>185</v>
+        <v>261</v>
       </c>
       <c r="E7" s="53" cm="1">
         <f t="array" ref="E7">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C7-1),0)</f>
@@ -7202,16 +7662,16 @@
     </row>
     <row r="8" ht="13.65" customHeight="1">
       <c r="A8" t="s" s="38">
-        <v>179</v>
+        <v>255</v>
       </c>
       <c r="B8" t="s" s="38">
-        <v>183</v>
+        <v>259</v>
       </c>
       <c r="C8" s="53">
         <v>4</v>
       </c>
       <c r="D8" t="s" s="38">
-        <v>186</v>
+        <v>262</v>
       </c>
       <c r="E8" s="53" cm="1">
         <f t="array" ref="E8">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C8-1),0)</f>
@@ -7242,16 +7702,16 @@
     </row>
     <row r="9" ht="13.65" customHeight="1">
       <c r="A9" t="s" s="38">
-        <v>179</v>
+        <v>255</v>
       </c>
       <c r="B9" t="s" s="38">
-        <v>183</v>
+        <v>259</v>
       </c>
       <c r="C9" s="53">
         <v>5</v>
       </c>
       <c r="D9" t="s" s="38">
-        <v>187</v>
+        <v>263</v>
       </c>
       <c r="E9" s="53" cm="1">
         <f t="array" ref="E9">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C9-1),0)</f>
@@ -7282,16 +7742,16 @@
     </row>
     <row r="10" ht="13.65" customHeight="1">
       <c r="A10" t="s" s="38">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="B10" t="s" s="56">
-        <v>180</v>
+        <v>256</v>
       </c>
       <c r="C10" s="53">
         <v>1</v>
       </c>
       <c r="D10" t="s" s="38">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="E10" s="53" cm="1">
         <f t="array" ref="E10">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C10-1),0)</f>
@@ -7317,21 +7777,21 @@
       </c>
       <c r="K10" s="53"/>
       <c r="L10" t="s" s="42">
-        <v>190</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" ht="13.65" customHeight="1">
       <c r="A11" t="s" s="38">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="B11" t="s" s="38">
-        <v>191</v>
+        <v>267</v>
       </c>
       <c r="C11" s="53">
         <v>2</v>
       </c>
       <c r="D11" t="s" s="38">
-        <v>192</v>
+        <v>268</v>
       </c>
       <c r="E11" s="53" cm="1">
         <f t="array" ref="E11">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C11-1),0)</f>
@@ -7362,16 +7822,16 @@
     </row>
     <row r="12" ht="13.65" customHeight="1">
       <c r="A12" t="s" s="38">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="B12" t="s" s="38">
-        <v>191</v>
+        <v>267</v>
       </c>
       <c r="C12" s="53">
         <v>3</v>
       </c>
       <c r="D12" t="s" s="38">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="E12" s="53" cm="1">
         <f t="array" ref="E12">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C12-1),0)</f>
@@ -7402,16 +7862,16 @@
     </row>
     <row r="13" ht="13.65" customHeight="1">
       <c r="A13" t="s" s="38">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="B13" t="s" s="38">
-        <v>191</v>
+        <v>267</v>
       </c>
       <c r="C13" s="53">
         <v>4</v>
       </c>
       <c r="D13" t="s" s="38">
-        <v>194</v>
+        <v>270</v>
       </c>
       <c r="E13" s="53" cm="1">
         <f t="array" ref="E13">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C13-1),0)</f>
@@ -7442,16 +7902,16 @@
     </row>
     <row r="14" ht="13.65" customHeight="1">
       <c r="A14" t="s" s="38">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="B14" t="s" s="38">
-        <v>191</v>
+        <v>267</v>
       </c>
       <c r="C14" s="53">
         <v>5</v>
       </c>
       <c r="D14" t="s" s="38">
-        <v>195</v>
+        <v>271</v>
       </c>
       <c r="E14" s="53" cm="1">
         <f t="array" ref="E14">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C14-1),0)</f>
@@ -7482,16 +7942,16 @@
     </row>
     <row r="15" ht="13.65" customHeight="1">
       <c r="A15" t="s" s="38">
-        <v>196</v>
+        <v>272</v>
       </c>
       <c r="B15" t="s" s="56">
-        <v>180</v>
+        <v>256</v>
       </c>
       <c r="C15" s="53">
         <v>1</v>
       </c>
       <c r="D15" t="s" s="38">
-        <v>197</v>
+        <v>273</v>
       </c>
       <c r="E15" s="53" cm="1">
         <f t="array" ref="E15">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C15-1),0)</f>
@@ -7517,21 +7977,21 @@
       </c>
       <c r="K15" s="53"/>
       <c r="L15" t="s" s="42">
-        <v>198</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" ht="13.65" customHeight="1">
       <c r="A16" t="s" s="38">
-        <v>196</v>
+        <v>272</v>
       </c>
       <c r="B16" t="s" s="38">
-        <v>199</v>
+        <v>275</v>
       </c>
       <c r="C16" s="53">
         <v>2</v>
       </c>
       <c r="D16" t="s" s="38">
-        <v>200</v>
+        <v>276</v>
       </c>
       <c r="E16" s="53" cm="1">
         <f t="array" ref="E16">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C16-1),0)</f>
@@ -7562,16 +8022,16 @@
     </row>
     <row r="17" ht="13.65" customHeight="1">
       <c r="A17" t="s" s="38">
-        <v>196</v>
+        <v>272</v>
       </c>
       <c r="B17" t="s" s="38">
-        <v>199</v>
+        <v>275</v>
       </c>
       <c r="C17" s="53">
         <v>3</v>
       </c>
       <c r="D17" t="s" s="38">
-        <v>201</v>
+        <v>277</v>
       </c>
       <c r="E17" s="53" cm="1">
         <f t="array" ref="E17">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C17-1),0)</f>
@@ -7602,16 +8062,16 @@
     </row>
     <row r="18" ht="13.65" customHeight="1">
       <c r="A18" t="s" s="38">
-        <v>196</v>
+        <v>272</v>
       </c>
       <c r="B18" t="s" s="38">
-        <v>199</v>
+        <v>275</v>
       </c>
       <c r="C18" s="53">
         <v>4</v>
       </c>
       <c r="D18" t="s" s="38">
-        <v>202</v>
+        <v>278</v>
       </c>
       <c r="E18" s="53" cm="1">
         <f t="array" ref="E18">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C18-1),0)</f>
@@ -7642,16 +8102,16 @@
     </row>
     <row r="19" ht="13.65" customHeight="1">
       <c r="A19" t="s" s="38">
-        <v>196</v>
+        <v>272</v>
       </c>
       <c r="B19" t="s" s="38">
-        <v>199</v>
+        <v>275</v>
       </c>
       <c r="C19" s="53">
         <v>5</v>
       </c>
       <c r="D19" t="s" s="38">
-        <v>203</v>
+        <v>279</v>
       </c>
       <c r="E19" s="53" cm="1">
         <f t="array" ref="E19">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C19-1),0)</f>
@@ -7696,7 +8156,7 @@
     </row>
     <row r="21" ht="14.6" customHeight="1">
       <c r="A21" t="s" s="11">
-        <v>204</v>
+        <v>280</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -7712,7 +8172,7 @@
     </row>
     <row r="22" ht="13.55" customHeight="1">
       <c r="A22" t="s" s="60">
-        <v>205</v>
+        <v>281</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -7750,7 +8210,7 @@
   <sheetData>
     <row r="1" ht="18.5" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>206</v>
+        <v>282</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -7759,7 +8219,7 @@
     </row>
     <row r="2" ht="13.65" customHeight="1">
       <c r="A2" t="s" s="5">
-        <v>207</v>
+        <v>283</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -7775,19 +8235,19 @@
     </row>
     <row r="4" ht="27.75" customHeight="1">
       <c r="A4" t="s" s="21">
-        <v>208</v>
+        <v>284</v>
       </c>
       <c r="B4" t="s" s="21">
-        <v>209</v>
+        <v>285</v>
       </c>
       <c r="C4" t="s" s="21">
-        <v>210</v>
+        <v>286</v>
       </c>
       <c r="D4" t="s" s="21">
-        <v>211</v>
+        <v>287</v>
       </c>
       <c r="E4" t="s" s="21">
-        <v>212</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" ht="13.65" customHeight="1">
@@ -7807,7 +8267,7 @@
         <v>0.6</v>
       </c>
       <c r="E5" t="s" s="62">
-        <v>213</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" ht="13.65" customHeight="1">
@@ -7827,7 +8287,7 @@
         <v>1.3</v>
       </c>
       <c r="E6" t="s" s="62">
-        <v>214</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" ht="13.65" customHeight="1">
@@ -7847,7 +8307,7 @@
         <v>2.1</v>
       </c>
       <c r="E7" t="s" s="62">
-        <v>215</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" ht="13.65" customHeight="1">
@@ -7867,7 +8327,7 @@
         <v>3.1</v>
       </c>
       <c r="E8" t="s" s="62">
-        <v>216</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" ht="13.65" customHeight="1">
@@ -7887,7 +8347,7 @@
         <v>4.2</v>
       </c>
       <c r="E9" t="s" s="65">
-        <v>217</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" ht="13.65" customHeight="1">
@@ -7979,7 +8439,7 @@
         <v>13.8</v>
       </c>
       <c r="E14" t="s" s="65">
-        <v>218</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" ht="13.65" customHeight="1">
@@ -8071,7 +8531,7 @@
         <v>35.9</v>
       </c>
       <c r="E19" t="s" s="65">
-        <v>219</v>
+        <v>295</v>
       </c>
     </row>
     <row r="20" ht="13.65" customHeight="1">
@@ -8163,7 +8623,7 @@
         <v>86.2</v>
       </c>
       <c r="E24" t="s" s="65">
-        <v>220</v>
+        <v>296</v>
       </c>
     </row>
     <row r="25" ht="13.55" customHeight="1">
@@ -8175,7 +8635,7 @@
     </row>
     <row r="26" ht="13.55" customHeight="1">
       <c r="A26" t="s" s="67">
-        <v>221</v>
+        <v>297</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -8212,7 +8672,7 @@
   <sheetData>
     <row r="1" ht="18.5" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>222</v>
+        <v>298</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -8227,7 +8687,7 @@
     </row>
     <row r="2" ht="13.65" customHeight="1">
       <c r="A2" t="s" s="5">
-        <v>223</v>
+        <v>299</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -8255,45 +8715,45 @@
     </row>
     <row r="4" ht="27.75" customHeight="1">
       <c r="A4" t="s" s="21">
-        <v>224</v>
+        <v>300</v>
       </c>
       <c r="B4" t="s" s="21">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C4" t="s" s="21">
-        <v>226</v>
+        <v>302</v>
       </c>
       <c r="D4" t="s" s="21">
-        <v>227</v>
+        <v>303</v>
       </c>
       <c r="E4" t="s" s="21">
-        <v>228</v>
+        <v>304</v>
       </c>
       <c r="F4" t="s" s="21">
-        <v>229</v>
+        <v>305</v>
       </c>
       <c r="G4" t="s" s="21">
-        <v>230</v>
+        <v>306</v>
       </c>
       <c r="H4" t="s" s="21">
-        <v>231</v>
+        <v>307</v>
       </c>
       <c r="I4" t="s" s="21">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="J4" t="s" s="21">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="K4" t="s" s="21">
-        <v>234</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" ht="13.65" customHeight="1">
       <c r="A5" t="s" s="62">
-        <v>235</v>
+        <v>311</v>
       </c>
       <c r="B5" t="s" s="38">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="C5" s="27">
         <v>1</v>
@@ -8306,7 +8766,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="s" s="38">
-        <v>237</v>
+        <v>313</v>
       </c>
       <c r="G5" s="57">
         <v>0</v>
@@ -8323,15 +8783,15 @@
         <v>126</v>
       </c>
       <c r="K5" t="s" s="42">
-        <v>238</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" ht="13.65" customHeight="1">
       <c r="A6" t="s" s="62">
-        <v>239</v>
+        <v>315</v>
       </c>
       <c r="B6" t="s" s="38">
-        <v>240</v>
+        <v>316</v>
       </c>
       <c r="C6" s="27">
         <v>1</v>
@@ -8344,7 +8804,7 @@
         <v>1.2</v>
       </c>
       <c r="F6" t="s" s="38">
-        <v>235</v>
+        <v>311</v>
       </c>
       <c r="G6" s="57">
         <v>2</v>
@@ -8364,10 +8824,10 @@
     </row>
     <row r="7" ht="13.65" customHeight="1">
       <c r="A7" t="s" s="62">
-        <v>241</v>
+        <v>317</v>
       </c>
       <c r="B7" t="s" s="38">
-        <v>242</v>
+        <v>318</v>
       </c>
       <c r="C7" s="27">
         <v>2</v>
@@ -8380,7 +8840,7 @@
         <v>1</v>
       </c>
       <c r="F7" t="s" s="38">
-        <v>239</v>
+        <v>315</v>
       </c>
       <c r="G7" s="57">
         <v>2</v>
@@ -8400,10 +8860,10 @@
     </row>
     <row r="8" ht="13.65" customHeight="1">
       <c r="A8" t="s" s="62">
-        <v>243</v>
+        <v>319</v>
       </c>
       <c r="B8" t="s" s="38">
-        <v>244</v>
+        <v>320</v>
       </c>
       <c r="C8" s="27">
         <v>3</v>
@@ -8416,7 +8876,7 @@
         <v>0.8</v>
       </c>
       <c r="F8" t="s" s="38">
-        <v>241</v>
+        <v>317</v>
       </c>
       <c r="G8" s="57">
         <v>2</v>
@@ -8433,15 +8893,15 @@
         <v>126</v>
       </c>
       <c r="K8" t="s" s="42">
-        <v>245</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" ht="13.65" customHeight="1">
       <c r="A9" t="s" s="62">
-        <v>246</v>
+        <v>322</v>
       </c>
       <c r="B9" t="s" s="38">
-        <v>247</v>
+        <v>323</v>
       </c>
       <c r="C9" s="27">
         <v>4</v>
@@ -8454,7 +8914,7 @@
         <v>1.4</v>
       </c>
       <c r="F9" t="s" s="38">
-        <v>243</v>
+        <v>319</v>
       </c>
       <c r="G9" s="57">
         <v>3</v>
@@ -8471,15 +8931,15 @@
         <v>126</v>
       </c>
       <c r="K9" t="s" s="42">
-        <v>248</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" ht="13.65" customHeight="1">
       <c r="A10" t="s" s="62">
-        <v>249</v>
+        <v>325</v>
       </c>
       <c r="B10" t="s" s="38">
-        <v>250</v>
+        <v>326</v>
       </c>
       <c r="C10" s="27">
         <v>4</v>
@@ -8492,7 +8952,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" t="s" s="38">
-        <v>241</v>
+        <v>317</v>
       </c>
       <c r="G10" s="57">
         <v>2</v>
@@ -8509,15 +8969,15 @@
         <v>119</v>
       </c>
       <c r="K10" t="s" s="42">
-        <v>251</v>
+        <v>327</v>
       </c>
     </row>
     <row r="11" ht="13.65" customHeight="1">
       <c r="A11" t="s" s="62">
-        <v>252</v>
+        <v>328</v>
       </c>
       <c r="B11" t="s" s="38">
-        <v>253</v>
+        <v>329</v>
       </c>
       <c r="C11" s="27">
         <v>200</v>
@@ -8530,7 +8990,7 @@
         <v>0.5</v>
       </c>
       <c r="F11" t="s" s="38">
-        <v>249</v>
+        <v>325</v>
       </c>
       <c r="G11" s="57">
         <v>4</v>
@@ -8547,15 +9007,15 @@
         <v>119</v>
       </c>
       <c r="K11" t="s" s="42">
-        <v>254</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" ht="13.65" customHeight="1">
       <c r="A12" t="s" s="62">
-        <v>255</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s" s="38">
-        <v>256</v>
+        <v>332</v>
       </c>
       <c r="C12" s="27">
         <v>700</v>
@@ -8568,7 +9028,7 @@
         <v>0.4</v>
       </c>
       <c r="F12" t="s" s="38">
-        <v>252</v>
+        <v>328</v>
       </c>
       <c r="G12" s="57">
         <v>4</v>
@@ -8585,7 +9045,7 @@
         <v>119</v>
       </c>
       <c r="K12" t="s" s="42">
-        <v>257</v>
+        <v>333</v>
       </c>
     </row>
     <row r="13" ht="13.55" customHeight="1">
@@ -8603,7 +9063,7 @@
     </row>
     <row r="14" ht="14.6" customHeight="1">
       <c r="A14" t="s" s="11">
-        <v>258</v>
+        <v>334</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -8618,7 +9078,7 @@
     </row>
     <row r="15" ht="13.55" customHeight="1">
       <c r="A15" t="s" s="60">
-        <v>259</v>
+        <v>335</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -8661,7 +9121,7 @@
   <sheetData>
     <row r="1" ht="18.5" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>260</v>
+        <v>336</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -8684,7 +9144,7 @@
     </row>
     <row r="2" ht="13.65" customHeight="1">
       <c r="A2" t="s" s="5">
-        <v>261</v>
+        <v>337</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -8728,61 +9188,61 @@
     </row>
     <row r="4" ht="27.75" customHeight="1">
       <c r="A4" t="s" s="21">
-        <v>262</v>
+        <v>338</v>
       </c>
       <c r="B4" t="s" s="21">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="C4" t="s" s="21">
-        <v>263</v>
+        <v>339</v>
       </c>
       <c r="D4" t="s" s="21">
-        <v>264</v>
+        <v>340</v>
       </c>
       <c r="E4" t="s" s="21">
-        <v>265</v>
+        <v>341</v>
       </c>
       <c r="F4" t="s" s="21">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="G4" t="s" s="21">
-        <v>267</v>
+        <v>343</v>
       </c>
       <c r="H4" t="s" s="21">
-        <v>268</v>
+        <v>344</v>
       </c>
       <c r="I4" t="s" s="21">
-        <v>269</v>
+        <v>345</v>
       </c>
       <c r="J4" t="s" s="21">
         <v>22</v>
       </c>
       <c r="K4" t="s" s="21">
-        <v>270</v>
+        <v>346</v>
       </c>
       <c r="L4" t="s" s="21">
-        <v>271</v>
+        <v>347</v>
       </c>
       <c r="M4" t="s" s="21">
-        <v>272</v>
+        <v>348</v>
       </c>
       <c r="N4" t="s" s="21">
-        <v>273</v>
+        <v>349</v>
       </c>
       <c r="O4" t="s" s="21">
-        <v>274</v>
+        <v>350</v>
       </c>
       <c r="P4" t="s" s="21">
-        <v>275</v>
+        <v>351</v>
       </c>
       <c r="Q4" t="s" s="21">
-        <v>276</v>
+        <v>352</v>
       </c>
       <c r="R4" t="s" s="21">
-        <v>277</v>
+        <v>353</v>
       </c>
       <c r="S4" t="s" s="21">
-        <v>278</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" ht="13.65" customHeight="1">
@@ -11528,7 +11988,7 @@
     </row>
     <row r="46" ht="13.55" customHeight="1">
       <c r="A46" t="s" s="76">
-        <v>279</v>
+        <v>355</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -11551,7 +12011,7 @@
     </row>
     <row r="47" ht="13.55" customHeight="1">
       <c r="A47" t="s" s="76">
-        <v>280</v>
+        <v>356</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -11574,7 +12034,7 @@
     </row>
     <row r="48" ht="13.55" customHeight="1">
       <c r="A48" t="s" s="67">
-        <v>281</v>
+        <v>357</v>
       </c>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
@@ -11621,7 +12081,7 @@
   <sheetData>
     <row r="1" ht="18.5" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -11634,7 +12094,7 @@
     </row>
     <row r="2" ht="13.65" customHeight="1">
       <c r="A2" t="s" s="5">
-        <v>283</v>
+        <v>359</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -11658,31 +12118,31 @@
     </row>
     <row r="4" ht="27.75" customHeight="1">
       <c r="A4" t="s" s="21">
-        <v>262</v>
+        <v>338</v>
       </c>
       <c r="B4" t="s" s="21">
-        <v>274</v>
+        <v>350</v>
       </c>
       <c r="C4" t="s" s="21">
-        <v>284</v>
+        <v>360</v>
       </c>
       <c r="D4" t="s" s="21">
         <v>147</v>
       </c>
       <c r="E4" t="s" s="21">
-        <v>285</v>
+        <v>361</v>
       </c>
       <c r="F4" t="s" s="21">
-        <v>278</v>
+        <v>354</v>
       </c>
       <c r="G4" t="s" s="21">
-        <v>286</v>
+        <v>362</v>
       </c>
       <c r="H4" t="s" s="21">
-        <v>287</v>
+        <v>363</v>
       </c>
       <c r="I4" t="s" s="21">
-        <v>288</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" ht="13.65" customHeight="1">
@@ -13178,7 +13638,7 @@
     </row>
     <row r="46" ht="14.6" customHeight="1">
       <c r="A46" t="s" s="11">
-        <v>292</v>
+        <v>368</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -13191,7 +13651,7 @@
     </row>
     <row r="47" ht="13.55" customHeight="1">
       <c r="A47" t="s" s="84">
-        <v>293</v>
+        <v>369</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -13215,7 +13675,7 @@
     </row>
     <row r="49" ht="13.55" customHeight="1">
       <c r="A49" t="s" s="84">
-        <v>294</v>
+        <v>370</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -13228,7 +13688,7 @@
     </row>
     <row r="50" ht="13.55" customHeight="1">
       <c r="A50" t="s" s="84">
-        <v>295</v>
+        <v>371</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -13241,7 +13701,7 @@
     </row>
     <row r="51" ht="13.55" customHeight="1">
       <c r="A51" t="s" s="84">
-        <v>296</v>
+        <v>372</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -13265,7 +13725,7 @@
     </row>
     <row r="53" ht="14.6" customHeight="1">
       <c r="A53" t="s" s="11">
-        <v>297</v>
+        <v>373</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -13278,7 +13738,7 @@
     </row>
     <row r="54" ht="13.55" customHeight="1">
       <c r="A54" t="s" s="84">
-        <v>298</v>
+        <v>374</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -13291,7 +13751,7 @@
     </row>
     <row r="55" ht="13.55" customHeight="1">
       <c r="A55" t="s" s="60">
-        <v>299</v>
+        <v>375</v>
       </c>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -3964,7 +3964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -4723,6 +4723,76 @@
       <c r="D43" s="29" t="inlineStr">
         <is>
           <t>Added to the shared pot once for each player beyond the first, whenever they join.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="inlineStr">
+        <is>
+          <t>HERO</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="n"/>
+      <c r="C45" s="32" t="n"/>
+      <c r="D45" s="32" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>Weapon aim assist</t>
+        </is>
+      </c>
+      <c r="B46" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" s="28" t="inlineStr">
+        <is>
+          <t>studs</t>
+        </is>
+      </c>
+      <c r="D46" s="29" t="inlineStr">
+        <is>
+          <t>A shot hits the enemy nearest to where you aimed, if one is this close to it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>Overdrive fire rate x</t>
+        </is>
+      </c>
+      <c r="B47" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="28" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D47" s="29" t="inlineStr">
+        <is>
+          <t>Your own fire rate during Overdrive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>Airburst delay</t>
+        </is>
+      </c>
+      <c r="B48" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D48" s="29" t="inlineStr">
+        <is>
+          <t>Time between calling an Airburst and the strike landing.</t>
         </is>
       </c>
     </row>
@@ -10896,7 +10966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="81" min="1" max="1"/>
@@ -10911,7 +10981,13 @@
     <col width="10" customWidth="1" style="81" min="10" max="10"/>
     <col width="12" customWidth="1" style="81" min="11" max="11"/>
     <col width="46" customWidth="1" style="81" min="12" max="12"/>
-    <col width="8.67188" customWidth="1" style="81" min="13" max="16384"/>
+    <col width="13" customWidth="1" style="81" min="13" max="16384"/>
+    <col width="13" customWidth="1" style="90" min="14" max="14"/>
+    <col width="13" customWidth="1" style="90" min="15" max="15"/>
+    <col width="13" customWidth="1" style="90" min="16" max="16"/>
+    <col width="13" customWidth="1" style="90" min="17" max="17"/>
+    <col width="13" customWidth="1" style="90" min="18" max="18"/>
+    <col width="13" customWidth="1" style="90" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.5" customHeight="1" s="90">
@@ -11025,6 +11101,41 @@
           <t>Trade-off</t>
         </is>
       </c>
+      <c r="M4" s="21" t="inlineStr">
+        <is>
+          <t>Pierces armour</t>
+        </is>
+      </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t>Hits air</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="inlineStr">
+        <is>
+          <t>Range (m)</t>
+        </is>
+      </c>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t>Splash radius (m)</t>
+        </is>
+      </c>
+      <c r="Q4" s="21" t="inlineStr">
+        <is>
+          <t>Ability power</t>
+        </is>
+      </c>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t>Ability (s)</t>
+        </is>
+      </c>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>Ability radius (m)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -11073,6 +11184,25 @@
           <t>Huge single-target damage. Useless against swarms. Railgun pierces 2 in a lane.</t>
         </is>
       </c>
+      <c r="M5" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N5" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O5" s="60" t="n">
+        <v>60</v>
+      </c>
+      <c r="P5" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="60" t="n"/>
+      <c r="R5" s="60" t="n"/>
+      <c r="S5" s="60" t="n"/>
     </row>
     <row r="6" ht="13.65" customHeight="1" s="90">
       <c r="A6" s="43" t="inlineStr">
@@ -11119,6 +11249,31 @@
         <v>40</v>
       </c>
       <c r="L6" s="61" t="n"/>
+      <c r="M6" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N6" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O6" s="60" t="n">
+        <v>60</v>
+      </c>
+      <c r="P6" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="60" t="n">
+        <v>50</v>
+      </c>
+      <c r="R6" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="S6" s="60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="13.65" customHeight="1" s="90">
       <c r="A7" s="43" t="inlineStr">
@@ -11165,6 +11320,31 @@
         <v>35</v>
       </c>
       <c r="L7" s="61" t="n"/>
+      <c r="M7" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N7" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O7" s="60" t="n">
+        <v>60</v>
+      </c>
+      <c r="P7" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="60" t="n">
+        <v>55</v>
+      </c>
+      <c r="R7" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="S7" s="60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="13.65" customHeight="1" s="90">
       <c r="A8" s="43" t="inlineStr">
@@ -11211,6 +11391,31 @@
         <v>30</v>
       </c>
       <c r="L8" s="61" t="n"/>
+      <c r="M8" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N8" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O8" s="60" t="n">
+        <v>60</v>
+      </c>
+      <c r="P8" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="60" t="n">
+        <v>65</v>
+      </c>
+      <c r="R8" s="60" t="n">
+        <v>9</v>
+      </c>
+      <c r="S8" s="60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
       <c r="A9" s="43" t="inlineStr">
@@ -11257,6 +11462,31 @@
         <v>25</v>
       </c>
       <c r="L9" s="61" t="n"/>
+      <c r="M9" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N9" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O9" s="60" t="n">
+        <v>60</v>
+      </c>
+      <c r="P9" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="60" t="n">
+        <v>80</v>
+      </c>
+      <c r="R9" s="60" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" s="60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" ht="13.65" customHeight="1" s="90">
       <c r="A10" s="43" t="inlineStr">
@@ -11305,6 +11535,25 @@
           <t>Shreds crowds. Stopped cold by armor.</t>
         </is>
       </c>
+      <c r="M10" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N10" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O10" s="60" t="n">
+        <v>35</v>
+      </c>
+      <c r="P10" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="60" t="n"/>
+      <c r="R10" s="60" t="n"/>
+      <c r="S10" s="60" t="n"/>
     </row>
     <row r="11" ht="13.65" customHeight="1" s="90">
       <c r="A11" s="43" t="inlineStr">
@@ -11351,6 +11600,31 @@
         <v>40</v>
       </c>
       <c r="L11" s="61" t="n"/>
+      <c r="M11" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N11" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O11" s="60" t="n">
+        <v>35</v>
+      </c>
+      <c r="P11" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="60" t="n">
+        <v>40</v>
+      </c>
+      <c r="R11" s="60" t="n">
+        <v>10</v>
+      </c>
+      <c r="S11" s="60" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="12" ht="13.65" customHeight="1" s="90">
       <c r="A12" s="43" t="inlineStr">
@@ -11397,6 +11671,31 @@
         <v>35</v>
       </c>
       <c r="L12" s="61" t="n"/>
+      <c r="M12" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N12" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O12" s="60" t="n">
+        <v>35</v>
+      </c>
+      <c r="P12" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="60" t="n">
+        <v>45</v>
+      </c>
+      <c r="R12" s="60" t="n">
+        <v>10</v>
+      </c>
+      <c r="S12" s="60" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="13" ht="13.65" customHeight="1" s="90">
       <c r="A13" s="43" t="inlineStr">
@@ -11443,6 +11742,31 @@
         <v>30</v>
       </c>
       <c r="L13" s="61" t="n"/>
+      <c r="M13" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N13" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O13" s="60" t="n">
+        <v>35</v>
+      </c>
+      <c r="P13" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="60" t="n">
+        <v>55</v>
+      </c>
+      <c r="R13" s="60" t="n">
+        <v>11</v>
+      </c>
+      <c r="S13" s="60" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="14" ht="13.65" customHeight="1" s="90">
       <c r="A14" s="43" t="inlineStr">
@@ -11489,6 +11813,31 @@
         <v>25</v>
       </c>
       <c r="L14" s="61" t="n"/>
+      <c r="M14" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N14" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O14" s="60" t="n">
+        <v>35</v>
+      </c>
+      <c r="P14" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="60" t="n">
+        <v>70</v>
+      </c>
+      <c r="R14" s="60" t="n">
+        <v>12</v>
+      </c>
+      <c r="S14" s="60" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="15" ht="13.65" customHeight="1" s="90">
       <c r="A15" s="43" t="inlineStr">
@@ -11537,6 +11886,25 @@
           <t>Best clear in the game. Cannot hit air at all.</t>
         </is>
       </c>
+      <c r="M15" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N15" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O15" s="60" t="n">
+        <v>40</v>
+      </c>
+      <c r="P15" s="60" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="60" t="n"/>
+      <c r="R15" s="60" t="n"/>
+      <c r="S15" s="60" t="n"/>
     </row>
     <row r="16" ht="13.65" customHeight="1" s="90">
       <c r="A16" s="43" t="inlineStr">
@@ -11583,6 +11951,31 @@
         <v>40</v>
       </c>
       <c r="L16" s="61" t="n"/>
+      <c r="M16" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N16" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" s="60" t="n">
+        <v>40</v>
+      </c>
+      <c r="P16" s="60" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="60" t="n">
+        <v>30</v>
+      </c>
+      <c r="R16" s="60" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" s="60" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="17" ht="13.65" customHeight="1" s="90">
       <c r="A17" s="43" t="inlineStr">
@@ -11629,6 +12022,31 @@
         <v>35</v>
       </c>
       <c r="L17" s="61" t="n"/>
+      <c r="M17" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N17" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O17" s="60" t="n">
+        <v>40</v>
+      </c>
+      <c r="P17" s="60" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="60" t="n">
+        <v>50</v>
+      </c>
+      <c r="R17" s="60" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" s="60" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="18" ht="13.65" customHeight="1" s="90">
       <c r="A18" s="43" t="inlineStr">
@@ -11675,6 +12093,31 @@
         <v>30</v>
       </c>
       <c r="L18" s="61" t="n"/>
+      <c r="M18" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N18" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" s="60" t="n">
+        <v>40</v>
+      </c>
+      <c r="P18" s="60" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="60" t="n">
+        <v>80</v>
+      </c>
+      <c r="R18" s="60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S18" s="60" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="19" ht="13.65" customHeight="1" s="90">
       <c r="A19" s="43" t="inlineStr">
@@ -11721,6 +12164,31 @@
         <v>25</v>
       </c>
       <c r="L19" s="61" t="n"/>
+      <c r="M19" s="60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N19" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O19" s="60" t="n">
+        <v>40</v>
+      </c>
+      <c r="P19" s="60" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="60" t="n">
+        <v>130</v>
+      </c>
+      <c r="R19" s="60" t="n">
+        <v>3</v>
+      </c>
+      <c r="S19" s="60" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="20" ht="13.55" customHeight="1" s="90">
       <c r="A20" s="62" t="n"/>
@@ -11771,6 +12239,13 @@
       <c r="J22" s="16" t="n"/>
       <c r="K22" s="16" t="n"/>
       <c r="L22" s="17" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="63" t="inlineStr">
+        <is>
+          <t>Ability columns, by type — Precision/Mark: power = +% damage the marked enemy takes, (s) = mark length. Sustained/Overdrive: power = +% fire rate for towers within the radius, (s) = duration (your own fire rate x 'Overdrive fire rate x' on Tuning). Ordnance/Airburst: power = damage, (s) = stun, radius = blast radius on the track. Tier 1 has no ability.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -10,12 +10,13 @@
     <sheet name="Tuning" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Towers" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Tower Upgrades" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Weapons" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Mastery" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Enemies" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Rounds" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Difficulty" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Balance Check" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Heroes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Hero Upgrades" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Mastery" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Enemies" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Rounds" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Difficulty" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Balance Check" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1996,12 +1997,12 @@
     <row r="15" ht="13.65" customHeight="1" s="90">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Heroes</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>3 weapon types x 5 in-round tiers. The player's own upgrade track.</t>
+          <t>3 free heroes (Pistol, Assault Rifle, Shotgun): base gun and ability. Hero Upgrades: 3 paths x 5 tiers each.</t>
         </is>
       </c>
       <c r="C15" s="6" t="n"/>
@@ -2210,6 +2211,223 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="90" min="1" max="1"/>
+    <col width="11" customWidth="1" style="90" min="2" max="2"/>
+    <col width="13" customWidth="1" style="90" min="3" max="3"/>
+    <col width="13" customWidth="1" style="90" min="4" max="4"/>
+    <col width="14" customWidth="1" style="90" min="5" max="5"/>
+    <col width="9" customWidth="1" style="90" min="6" max="6"/>
+    <col width="13" customWidth="1" style="90" min="7" max="7"/>
+    <col width="40" customWidth="1" style="90" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>DIFFICULTY — Easy is the baseline; every other level scales from it</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Chosen before round 1. Player-count scaling (Tuning, CO-OP) applies on top.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Difficulty</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Enemy HP x</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Enemy count x</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Enemy speed x</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Promote chance</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Cash x</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>Starting lives</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" s="47" t="inlineStr">
+        <is>
+          <t>The baseline. Current balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D6" s="27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="47" t="inlineStr">
+        <is>
+          <t>10% of enemies spawn one tier tougher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" s="47" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Chaos</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" s="47" t="inlineStr">
+        <is>
+          <t>Meant for big lobbies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Enemy count x raises density: the round's spawn gap shrinks by the same factor, so rounds get busier, not longer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Promote chance: each spawn has this chance to become the next ground tier up (Husk &gt; Brute &gt; Shielded &gt; Armored &gt; Storm). Air and bosses are never promoted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Cash x scales kill income and the round bonus.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
@@ -3964,7 +4182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -4325,11 +4543,11 @@
     <row r="21" ht="13.65" customHeight="1" s="90">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>Weapon tier 1 cost</t>
+          <t>Hero upgrade base cost</t>
         </is>
       </c>
       <c r="B21" s="27" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
@@ -4338,7 +4556,7 @@
       </c>
       <c r="D21" s="29" t="inlineStr">
         <is>
-          <t>Entry price of the player's own upgrade track.</t>
+          <t>Tier 1 of any hero path. Picking a hero is free.</t>
         </is>
       </c>
       <c r="E21" s="7" t="n"/>
@@ -4346,11 +4564,11 @@
     <row r="22" ht="13.65" customHeight="1" s="90">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>Weapon cost growth</t>
+          <t>Hero upgrade cost growth</t>
         </is>
       </c>
       <c r="B22" s="30" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
@@ -4359,30 +4577,16 @@
       </c>
       <c r="D22" s="29" t="inlineStr">
         <is>
-          <t>Compounding multiple per weapon tier.</t>
+          <t>Each hero upgrade tier costs this multiple of the one before.</t>
         </is>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
     <row r="23" ht="13.65" customHeight="1" s="90">
-      <c r="A23" s="26" t="inlineStr">
-        <is>
-          <t>Weapon damage growth</t>
-        </is>
-      </c>
-      <c r="B23" s="30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="C23" s="28" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D23" s="29" t="inlineStr">
-        <is>
-          <t>Far below tower tier damage growth (1.90x) on purpose. A maxed weapon must land near 50% of a maxed tower's DPS, never above it.</t>
-        </is>
-      </c>
+      <c r="A23" s="26" t="n"/>
+      <c r="B23" s="30" t="n"/>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="29" t="n"/>
       <c r="E23" s="7" t="n"/>
     </row>
     <row r="24" ht="14.6" customHeight="1" s="90">
@@ -4743,7 +4947,7 @@
         </is>
       </c>
       <c r="B46" s="30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C46" s="28" t="inlineStr">
         <is>
@@ -4752,7 +4956,7 @@
       </c>
       <c r="D46" s="29" t="inlineStr">
         <is>
-          <t>A shot hits the enemy nearest to where you aimed, if one is this close to it.</t>
+          <t>A shot hits the enemy nearest its (recoil-spread) ray, if one is this close to it.</t>
         </is>
       </c>
     </row>
@@ -4779,18 +4983,98 @@
     <row r="48">
       <c r="A48" s="26" t="inlineStr">
         <is>
+          <t>Spin-up time</t>
+        </is>
+      </c>
+      <c r="B48" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D48" s="29" t="inlineStr">
+        <is>
+          <t>Holding the trigger this long takes Spin-Up to full speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>Ricochet reach</t>
+        </is>
+      </c>
+      <c r="B49" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="C49" s="28" t="inlineStr">
+        <is>
+          <t>studs</t>
+        </is>
+      </c>
+      <c r="D49" s="29" t="inlineStr">
+        <is>
+          <t>How far a ricochet can jump to the next enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>Still speed</t>
+        </is>
+      </c>
+      <c r="B50" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="28" t="inlineStr">
+        <is>
+          <t>studs/s</t>
+        </is>
+      </c>
+      <c r="D50" s="29" t="inlineStr">
+        <is>
+          <t>Moving slower than this counts as standing still (Bipod).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>Airburst reach</t>
+        </is>
+      </c>
+      <c r="B51" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" s="28" t="inlineStr">
+        <is>
+          <t>studs</t>
+        </is>
+      </c>
+      <c r="D51" s="29" t="inlineStr">
+        <is>
+          <t>How far from you an Airburst can be called in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="26" t="inlineStr">
+        <is>
           <t>Airburst delay</t>
         </is>
       </c>
-      <c r="B48" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="28" t="inlineStr">
+      <c r="B52" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="28" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="D48" s="29" t="inlineStr">
+      <c r="D52" s="29" t="inlineStr">
         <is>
           <t>Time between calling an Airburst and the strike landing.</t>
         </is>
@@ -10966,1302 +11250,3572 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
+  <dimension ref="A1:W7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" style="81" min="1" max="1"/>
-    <col width="11" customWidth="1" style="81" min="2" max="2"/>
-    <col width="7" customWidth="1" style="81" min="3" max="3"/>
-    <col width="20" customWidth="1" style="81" min="4" max="4"/>
-    <col width="11" customWidth="1" style="81" min="5" max="5"/>
-    <col width="12" customWidth="1" style="81" min="6" max="6"/>
-    <col width="10" customWidth="1" style="81" min="7" max="7"/>
-    <col width="12" customWidth="1" style="81" min="8" max="8"/>
-    <col width="9" customWidth="1" style="81" min="9" max="9"/>
-    <col width="10" customWidth="1" style="81" min="10" max="10"/>
-    <col width="12" customWidth="1" style="81" min="11" max="11"/>
-    <col width="46" customWidth="1" style="81" min="12" max="12"/>
-    <col width="13" customWidth="1" style="81" min="13" max="16384"/>
-    <col width="13" customWidth="1" style="90" min="14" max="14"/>
-    <col width="13" customWidth="1" style="90" min="15" max="15"/>
-    <col width="13" customWidth="1" style="90" min="16" max="16"/>
-    <col width="13" customWidth="1" style="90" min="17" max="17"/>
-    <col width="13" customWidth="1" style="90" min="18" max="18"/>
-    <col width="13" customWidth="1" style="90" min="19" max="19"/>
+    <col width="12" customWidth="1" style="90" min="1" max="1"/>
+    <col width="12" customWidth="1" style="90" min="2" max="2"/>
+    <col width="12" customWidth="1" style="90" min="3" max="3"/>
+    <col width="12" customWidth="1" style="90" min="4" max="4"/>
+    <col width="12" customWidth="1" style="90" min="5" max="5"/>
+    <col width="12" customWidth="1" style="90" min="6" max="6"/>
+    <col width="12" customWidth="1" style="90" min="7" max="7"/>
+    <col width="12" customWidth="1" style="90" min="8" max="8"/>
+    <col width="12" customWidth="1" style="90" min="9" max="9"/>
+    <col width="12" customWidth="1" style="90" min="10" max="10"/>
+    <col width="12" customWidth="1" style="90" min="11" max="11"/>
+    <col width="12" customWidth="1" style="90" min="12" max="12"/>
+    <col width="12" customWidth="1" style="90" min="13" max="13"/>
+    <col width="12" customWidth="1" style="90" min="14" max="14"/>
+    <col width="12" customWidth="1" style="90" min="15" max="15"/>
+    <col width="12" customWidth="1" style="90" min="16" max="16"/>
+    <col width="12" customWidth="1" style="90" min="17" max="17"/>
+    <col width="12" customWidth="1" style="90" min="18" max="18"/>
+    <col width="12" customWidth="1" style="90" min="19" max="19"/>
+    <col width="12" customWidth="1" style="90" min="20" max="20"/>
+    <col width="12" customWidth="1" style="90" min="21" max="21"/>
+    <col width="12" customWidth="1" style="90" min="22" max="22"/>
+    <col width="60" customWidth="1" style="90" min="23" max="23"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.5" customHeight="1" s="90">
+    <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>PLAYER WEAPONS — in-round track</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
-      <c r="L1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="13.65" customHeight="1" s="90">
+          <t>HEROES — free to pick; each hero is a gun plus an ability (HEROES.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Resets every match. Bought from the same shared cash as towers. Abilities unlock at tier 2.</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="6" t="n"/>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="6" t="n"/>
-      <c r="G2" s="6" t="n"/>
-      <c r="H2" s="6" t="n"/>
-      <c r="I2" s="6" t="n"/>
-      <c r="J2" s="6" t="n"/>
-      <c r="K2" s="6" t="n"/>
-      <c r="L2" s="7" t="n"/>
-    </row>
-    <row r="3" ht="13.55" customHeight="1" s="90">
-      <c r="A3" s="19" t="n"/>
-      <c r="B3" s="20" t="n"/>
-      <c r="C3" s="20" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="20" t="n"/>
-      <c r="G3" s="20" t="n"/>
-      <c r="H3" s="20" t="n"/>
-      <c r="I3" s="20" t="n"/>
-      <c r="J3" s="20" t="n"/>
-      <c r="K3" s="20" t="n"/>
-      <c r="L3" s="41" t="n"/>
-    </row>
-    <row r="4" ht="27.75" customHeight="1" s="90">
+          <t>Base gun before any upgrade. Hero Upgrades multiplies or overrides these. More heroes = more rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>Weapon type</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
           <t>Ability</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t>Cumulative</t>
+          <t>Fire rate /s</t>
         </is>
       </c>
       <c r="G4" s="21" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Fire mode</t>
         </is>
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t>Fire rate /s</t>
+          <t>Magazine</t>
         </is>
       </c>
       <c r="I4" s="21" t="inlineStr">
         <is>
-          <t>Targets</t>
+          <t>Reload (s)</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>Pellets</t>
         </is>
       </c>
       <c r="K4" s="21" t="inlineStr">
         <is>
-          <t>Cooldown (s)</t>
+          <t>Spread (deg)</t>
         </is>
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t>Trade-off</t>
+          <t>Recoil per shot (deg)</t>
         </is>
       </c>
       <c r="M4" s="21" t="inlineStr">
         <is>
+          <t>Recoil max (deg)</t>
+        </is>
+      </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t>Recoil recovery (deg/s)</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="inlineStr">
+        <is>
+          <t>Range (m)</t>
+        </is>
+      </c>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
           <t>Pierces armour</t>
         </is>
       </c>
-      <c r="N4" s="21" t="inlineStr">
+      <c r="Q4" s="21" t="inlineStr">
         <is>
           <t>Hits air</t>
         </is>
       </c>
-      <c r="O4" s="21" t="inlineStr">
-        <is>
-          <t>Range (m)</t>
-        </is>
-      </c>
-      <c r="P4" s="21" t="inlineStr">
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t>Splash radius (m)</t>
         </is>
       </c>
-      <c r="Q4" s="21" t="inlineStr">
+      <c r="S4" s="21" t="inlineStr">
         <is>
           <t>Ability power</t>
         </is>
       </c>
-      <c r="R4" s="21" t="inlineStr">
+      <c r="T4" s="21" t="inlineStr">
         <is>
           <t>Ability (s)</t>
         </is>
       </c>
-      <c r="S4" s="21" t="inlineStr">
+      <c r="U4" s="21" t="inlineStr">
         <is>
           <t>Ability radius (m)</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="13.65" customHeight="1" s="90">
+      <c r="V4" s="21" t="inlineStr">
+        <is>
+          <t>Ability cooldown (s)</t>
+        </is>
+      </c>
+      <c r="W4" s="21" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="43" t="inlineStr">
         <is>
+          <t>PISTOL</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="B5" s="59" t="inlineStr">
-        <is>
-          <t>— locked —</t>
-        </is>
-      </c>
-      <c r="C5" s="56" t="n">
-        <v>1</v>
-      </c>
       <c r="D5" s="43" t="inlineStr">
         <is>
-          <t>Scoped pistol</t>
-        </is>
-      </c>
-      <c r="E5" s="56">
-        <f t="array" ref="E5">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C5-1),0)</f>
-        <v/>
-      </c>
-      <c r="F5" s="56">
-        <f t="array" ref="F5">E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="92">
-        <f t="array" ref="G5">ROUND(6*POWER('Tuning'!$B$23,C5-1),1)</f>
-        <v/>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="E5" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F5" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="43" t="inlineStr">
+        <is>
+          <t>semi</t>
+        </is>
       </c>
       <c r="H5" s="57" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I5" s="60" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="92">
-        <f t="array" ref="J5">G5*H5*I5</f>
-        <v/>
-      </c>
-      <c r="K5" s="56" t="n"/>
-      <c r="L5" s="47" t="inlineStr">
-        <is>
-          <t>Huge single-target damage. Useless against swarms. Railgun pierces 2 in a lane.</t>
-        </is>
-      </c>
-      <c r="M5" s="60" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="I5" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J5" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L5" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M5" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" s="57" t="n">
+        <v>12</v>
+      </c>
+      <c r="O5" s="57" t="n">
+        <v>55</v>
+      </c>
+      <c r="P5" s="43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q5" s="43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N5" s="60" t="inlineStr">
+      <c r="R5" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="57" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="U5" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="57" t="n">
+        <v>45</v>
+      </c>
+      <c r="W5" s="43" t="inlineStr">
+        <is>
+          <t>Mark: power = +% damage taken, (s) = length. Passes to splits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>RIFLE</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>Sustained</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>Overdrive</t>
+        </is>
+      </c>
+      <c r="E6" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F6" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" s="43" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H6" s="57" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M6" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="N6" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" s="57" t="n">
+        <v>40</v>
+      </c>
+      <c r="P6" s="43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q6" s="43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="O5" s="60" t="n">
-        <v>60</v>
-      </c>
-      <c r="P5" s="60" t="n">
+      <c r="R6" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="60" t="n"/>
-      <c r="R5" s="60" t="n"/>
-      <c r="S5" s="60" t="n"/>
-    </row>
-    <row r="6" ht="13.65" customHeight="1" s="90">
-      <c r="A6" s="43" t="inlineStr">
-        <is>
-          <t>Precision</t>
-        </is>
-      </c>
-      <c r="B6" s="43" t="inlineStr">
-        <is>
-          <t>Mark</t>
-        </is>
-      </c>
-      <c r="C6" s="56" t="n">
+      <c r="S6" s="57" t="n">
+        <v>40</v>
+      </c>
+      <c r="T6" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="U6" s="57" t="n">
+        <v>25</v>
+      </c>
+      <c r="V6" s="57" t="n">
+        <v>45</v>
+      </c>
+      <c r="W6" s="43" t="inlineStr">
+        <is>
+          <t>Overdrive: your fire rate x Tuning, towers in radius +power% fire rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>SHOTGUN</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>Ordnance</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>Airburst</t>
+        </is>
+      </c>
+      <c r="E7" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F7" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G7" s="43" t="inlineStr">
+        <is>
+          <t>semi</t>
+        </is>
+      </c>
+      <c r="H7" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" s="57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J7" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" s="57" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="N7" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="O7" s="57" t="n">
+        <v>25</v>
+      </c>
+      <c r="P7" s="43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q7" s="43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R7" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="57" t="n">
+        <v>30</v>
+      </c>
+      <c r="T7" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="43" t="inlineStr">
-        <is>
-          <t>Marksman rifle</t>
-        </is>
-      </c>
-      <c r="E6" s="56">
-        <f t="array" ref="E6">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C6-1),0)</f>
-        <v/>
-      </c>
-      <c r="F6" s="56">
-        <f t="array" ref="F6">F5+E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="92">
-        <f t="array" ref="G6">ROUND(6*POWER('Tuning'!$B$23,C6-1),1)</f>
-        <v/>
-      </c>
-      <c r="H6" s="57" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I6" s="60" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="92">
-        <f t="array" ref="J6">G6*H6*I6</f>
-        <v/>
-      </c>
-      <c r="K6" s="60" t="n">
-        <v>40</v>
-      </c>
-      <c r="L6" s="61" t="n"/>
-      <c r="M6" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N6" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O6" s="60" t="n">
-        <v>60</v>
-      </c>
-      <c r="P6" s="60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="60" t="n">
-        <v>50</v>
-      </c>
-      <c r="R6" s="60" t="n">
-        <v>8</v>
-      </c>
-      <c r="S6" s="60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="13.65" customHeight="1" s="90">
-      <c r="A7" s="43" t="inlineStr">
-        <is>
-          <t>Precision</t>
-        </is>
-      </c>
-      <c r="B7" s="43" t="inlineStr">
-        <is>
-          <t>Mark</t>
-        </is>
-      </c>
-      <c r="C7" s="56" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="43" t="inlineStr">
-        <is>
-          <t>Heavy marksman</t>
-        </is>
-      </c>
-      <c r="E7" s="56">
-        <f t="array" ref="E7">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C7-1),0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="56">
-        <f t="array" ref="F7">F6+E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="92">
-        <f t="array" ref="G7">ROUND(6*POWER('Tuning'!$B$23,C7-1),1)</f>
-        <v/>
-      </c>
-      <c r="H7" s="57" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I7" s="60" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="92">
-        <f t="array" ref="J7">G7*H7*I7</f>
-        <v/>
-      </c>
-      <c r="K7" s="60" t="n">
-        <v>35</v>
-      </c>
-      <c r="L7" s="61" t="n"/>
-      <c r="M7" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N7" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O7" s="60" t="n">
-        <v>60</v>
-      </c>
-      <c r="P7" s="60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="60" t="n">
-        <v>55</v>
-      </c>
-      <c r="R7" s="60" t="n">
-        <v>8</v>
-      </c>
-      <c r="S7" s="60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="13.65" customHeight="1" s="90">
-      <c r="A8" s="43" t="inlineStr">
-        <is>
-          <t>Precision</t>
-        </is>
-      </c>
-      <c r="B8" s="43" t="inlineStr">
-        <is>
-          <t>Mark</t>
-        </is>
-      </c>
-      <c r="C8" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="43" t="inlineStr">
-        <is>
-          <t>Anti-materiel rifle</t>
-        </is>
-      </c>
-      <c r="E8" s="56">
-        <f t="array" ref="E8">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C8-1),0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="56">
-        <f t="array" ref="F8">F7+E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="92">
-        <f t="array" ref="G8">ROUND(6*POWER('Tuning'!$B$23,C8-1),1)</f>
-        <v/>
-      </c>
-      <c r="H8" s="57" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I8" s="60" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="92">
-        <f t="array" ref="J8">G8*H8*I8</f>
-        <v/>
-      </c>
-      <c r="K8" s="60" t="n">
-        <v>30</v>
-      </c>
-      <c r="L8" s="61" t="n"/>
-      <c r="M8" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N8" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O8" s="60" t="n">
-        <v>60</v>
-      </c>
-      <c r="P8" s="60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="60" t="n">
-        <v>65</v>
-      </c>
-      <c r="R8" s="60" t="n">
-        <v>9</v>
-      </c>
-      <c r="S8" s="60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="13.65" customHeight="1" s="90">
-      <c r="A9" s="43" t="inlineStr">
-        <is>
-          <t>Precision</t>
-        </is>
-      </c>
-      <c r="B9" s="43" t="inlineStr">
-        <is>
-          <t>Mark</t>
-        </is>
-      </c>
-      <c r="C9" s="56" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" s="43" t="inlineStr">
-        <is>
-          <t>Railgun</t>
-        </is>
-      </c>
-      <c r="E9" s="56">
-        <f t="array" ref="E9">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C9-1),0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="56">
-        <f t="array" ref="F9">F8+E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="92">
-        <f t="array" ref="G9">ROUND(6*POWER('Tuning'!$B$23,C9-1),1)</f>
-        <v/>
-      </c>
-      <c r="H9" s="57" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I9" s="60" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="92">
-        <f t="array" ref="J9">G9*H9*I9</f>
-        <v/>
-      </c>
-      <c r="K9" s="60" t="n">
-        <v>25</v>
-      </c>
-      <c r="L9" s="61" t="n"/>
-      <c r="M9" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N9" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O9" s="60" t="n">
-        <v>60</v>
-      </c>
-      <c r="P9" s="60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="60" t="n">
-        <v>80</v>
-      </c>
-      <c r="R9" s="60" t="n">
+      <c r="U7" s="57" t="n">
         <v>10</v>
       </c>
-      <c r="S9" s="60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="13.65" customHeight="1" s="90">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t>Sustained</t>
-        </is>
-      </c>
-      <c r="B10" s="59" t="inlineStr">
-        <is>
-          <t>— locked —</t>
-        </is>
-      </c>
-      <c r="C10" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="43" t="inlineStr">
-        <is>
-          <t>SMG</t>
-        </is>
-      </c>
-      <c r="E10" s="56">
-        <f t="array" ref="E10">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C10-1),0)</f>
-        <v/>
-      </c>
-      <c r="F10" s="56">
-        <f t="array" ref="F10">E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="92">
-        <f t="array" ref="G10">ROUND(1.2*POWER('Tuning'!$B$23,C10-1),1)</f>
-        <v/>
-      </c>
-      <c r="H10" s="57" t="n">
-        <v>8</v>
-      </c>
-      <c r="I10" s="60" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="92">
-        <f t="array" ref="J10">G10*H10*I10</f>
-        <v/>
-      </c>
-      <c r="K10" s="56" t="n"/>
-      <c r="L10" s="47" t="inlineStr">
-        <is>
-          <t>Shreds crowds. Stopped cold by armor.</t>
-        </is>
-      </c>
-      <c r="M10" s="60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N10" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O10" s="60" t="n">
-        <v>35</v>
-      </c>
-      <c r="P10" s="60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="60" t="n"/>
-      <c r="R10" s="60" t="n"/>
-      <c r="S10" s="60" t="n"/>
-    </row>
-    <row r="11" ht="13.65" customHeight="1" s="90">
-      <c r="A11" s="43" t="inlineStr">
-        <is>
-          <t>Sustained</t>
-        </is>
-      </c>
-      <c r="B11" s="43" t="inlineStr">
-        <is>
-          <t>Overdrive</t>
-        </is>
-      </c>
-      <c r="C11" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="43" t="inlineStr">
-        <is>
-          <t>Assault rifle</t>
-        </is>
-      </c>
-      <c r="E11" s="56">
-        <f t="array" ref="E11">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C11-1),0)</f>
-        <v/>
-      </c>
-      <c r="F11" s="56">
-        <f t="array" ref="F11">F10+E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="92">
-        <f t="array" ref="G11">ROUND(1.2*POWER('Tuning'!$B$23,C11-1),1)</f>
-        <v/>
-      </c>
-      <c r="H11" s="57" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" s="60" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="92">
-        <f t="array" ref="J11">G11*H11*I11</f>
-        <v/>
-      </c>
-      <c r="K11" s="60" t="n">
-        <v>40</v>
-      </c>
-      <c r="L11" s="61" t="n"/>
-      <c r="M11" s="60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N11" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O11" s="60" t="n">
-        <v>35</v>
-      </c>
-      <c r="P11" s="60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="60" t="n">
-        <v>40</v>
-      </c>
-      <c r="R11" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="S11" s="60" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" ht="13.65" customHeight="1" s="90">
-      <c r="A12" s="43" t="inlineStr">
-        <is>
-          <t>Sustained</t>
-        </is>
-      </c>
-      <c r="B12" s="43" t="inlineStr">
-        <is>
-          <t>Overdrive</t>
-        </is>
-      </c>
-      <c r="C12" s="56" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" s="43" t="inlineStr">
-        <is>
-          <t>Heavy AR</t>
-        </is>
-      </c>
-      <c r="E12" s="56">
-        <f t="array" ref="E12">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C12-1),0)</f>
-        <v/>
-      </c>
-      <c r="F12" s="56">
-        <f t="array" ref="F12">F11+E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="92">
-        <f t="array" ref="G12">ROUND(1.2*POWER('Tuning'!$B$23,C12-1),1)</f>
-        <v/>
-      </c>
-      <c r="H12" s="57" t="n">
-        <v>8</v>
-      </c>
-      <c r="I12" s="60" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="92">
-        <f t="array" ref="J12">G12*H12*I12</f>
-        <v/>
-      </c>
-      <c r="K12" s="60" t="n">
-        <v>35</v>
-      </c>
-      <c r="L12" s="61" t="n"/>
-      <c r="M12" s="60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N12" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O12" s="60" t="n">
-        <v>35</v>
-      </c>
-      <c r="P12" s="60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="60" t="n">
+      <c r="V7" s="57" t="n">
         <v>45</v>
       </c>
-      <c r="R12" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="S12" s="60" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" ht="13.65" customHeight="1" s="90">
-      <c r="A13" s="43" t="inlineStr">
-        <is>
-          <t>Sustained</t>
-        </is>
-      </c>
-      <c r="B13" s="43" t="inlineStr">
-        <is>
-          <t>Overdrive</t>
-        </is>
-      </c>
-      <c r="C13" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" s="43" t="inlineStr">
-        <is>
-          <t>LMG</t>
-        </is>
-      </c>
-      <c r="E13" s="56">
-        <f t="array" ref="E13">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C13-1),0)</f>
-        <v/>
-      </c>
-      <c r="F13" s="56">
-        <f t="array" ref="F13">F12+E13</f>
-        <v/>
-      </c>
-      <c r="G13" s="92">
-        <f t="array" ref="G13">ROUND(1.2*POWER('Tuning'!$B$23,C13-1),1)</f>
-        <v/>
-      </c>
-      <c r="H13" s="57" t="n">
-        <v>8</v>
-      </c>
-      <c r="I13" s="60" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="92">
-        <f t="array" ref="J13">G13*H13*I13</f>
-        <v/>
-      </c>
-      <c r="K13" s="60" t="n">
-        <v>30</v>
-      </c>
-      <c r="L13" s="61" t="n"/>
-      <c r="M13" s="60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N13" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O13" s="60" t="n">
-        <v>35</v>
-      </c>
-      <c r="P13" s="60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="60" t="n">
-        <v>55</v>
-      </c>
-      <c r="R13" s="60" t="n">
-        <v>11</v>
-      </c>
-      <c r="S13" s="60" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" ht="13.65" customHeight="1" s="90">
-      <c r="A14" s="43" t="inlineStr">
-        <is>
-          <t>Sustained</t>
-        </is>
-      </c>
-      <c r="B14" s="43" t="inlineStr">
-        <is>
-          <t>Overdrive</t>
-        </is>
-      </c>
-      <c r="C14" s="56" t="n">
-        <v>5</v>
-      </c>
-      <c r="D14" s="43" t="inlineStr">
-        <is>
-          <t>Minigun</t>
-        </is>
-      </c>
-      <c r="E14" s="56">
-        <f t="array" ref="E14">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C14-1),0)</f>
-        <v/>
-      </c>
-      <c r="F14" s="56">
-        <f t="array" ref="F14">F13+E14</f>
-        <v/>
-      </c>
-      <c r="G14" s="92">
-        <f t="array" ref="G14">ROUND(1.2*POWER('Tuning'!$B$23,C14-1),1)</f>
-        <v/>
-      </c>
-      <c r="H14" s="57" t="n">
-        <v>8</v>
-      </c>
-      <c r="I14" s="60" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="92">
-        <f t="array" ref="J14">G14*H14*I14</f>
-        <v/>
-      </c>
-      <c r="K14" s="60" t="n">
-        <v>25</v>
-      </c>
-      <c r="L14" s="61" t="n"/>
-      <c r="M14" s="60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N14" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O14" s="60" t="n">
-        <v>35</v>
-      </c>
-      <c r="P14" s="60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="60" t="n">
-        <v>70</v>
-      </c>
-      <c r="R14" s="60" t="n">
-        <v>12</v>
-      </c>
-      <c r="S14" s="60" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" ht="13.65" customHeight="1" s="90">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t>Ordnance</t>
-        </is>
-      </c>
-      <c r="B15" s="59" t="inlineStr">
-        <is>
-          <t>— locked —</t>
-        </is>
-      </c>
-      <c r="C15" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="43" t="inlineStr">
-        <is>
-          <t>Shotgun</t>
-        </is>
-      </c>
-      <c r="E15" s="56">
-        <f t="array" ref="E15">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C15-1),0)</f>
-        <v/>
-      </c>
-      <c r="F15" s="56">
-        <f t="array" ref="F15">E15</f>
-        <v/>
-      </c>
-      <c r="G15" s="92">
-        <f t="array" ref="G15">ROUND(4*POWER('Tuning'!$B$23,C15-1),1)</f>
-        <v/>
-      </c>
-      <c r="H15" s="57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I15" s="60" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="92">
-        <f t="array" ref="J15">G15*H15*I15</f>
-        <v/>
-      </c>
-      <c r="K15" s="56" t="n"/>
-      <c r="L15" s="47" t="inlineStr">
-        <is>
-          <t>Best clear in the game. Cannot hit air at all.</t>
-        </is>
-      </c>
-      <c r="M15" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N15" s="60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O15" s="60" t="n">
-        <v>40</v>
-      </c>
-      <c r="P15" s="60" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q15" s="60" t="n"/>
-      <c r="R15" s="60" t="n"/>
-      <c r="S15" s="60" t="n"/>
-    </row>
-    <row r="16" ht="13.65" customHeight="1" s="90">
-      <c r="A16" s="43" t="inlineStr">
-        <is>
-          <t>Ordnance</t>
-        </is>
-      </c>
-      <c r="B16" s="43" t="inlineStr">
-        <is>
-          <t>Airburst</t>
-        </is>
-      </c>
-      <c r="C16" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="43" t="inlineStr">
-        <is>
-          <t>Grenade launcher</t>
-        </is>
-      </c>
-      <c r="E16" s="56">
-        <f t="array" ref="E16">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C16-1),0)</f>
-        <v/>
-      </c>
-      <c r="F16" s="56">
-        <f t="array" ref="F16">F15+E16</f>
-        <v/>
-      </c>
-      <c r="G16" s="92">
-        <f t="array" ref="G16">ROUND(4*POWER('Tuning'!$B$23,C16-1),1)</f>
-        <v/>
-      </c>
-      <c r="H16" s="57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I16" s="60" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="92">
-        <f t="array" ref="J16">G16*H16*I16</f>
-        <v/>
-      </c>
-      <c r="K16" s="60" t="n">
-        <v>40</v>
-      </c>
-      <c r="L16" s="61" t="n"/>
-      <c r="M16" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N16" s="60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O16" s="60" t="n">
-        <v>40</v>
-      </c>
-      <c r="P16" s="60" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q16" s="60" t="n">
-        <v>30</v>
-      </c>
-      <c r="R16" s="60" t="n">
-        <v>2</v>
-      </c>
-      <c r="S16" s="60" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" ht="13.65" customHeight="1" s="90">
-      <c r="A17" s="43" t="inlineStr">
-        <is>
-          <t>Ordnance</t>
-        </is>
-      </c>
-      <c r="B17" s="43" t="inlineStr">
-        <is>
-          <t>Airburst</t>
-        </is>
-      </c>
-      <c r="C17" s="56" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" s="43" t="inlineStr">
-        <is>
-          <t>Twin launcher</t>
-        </is>
-      </c>
-      <c r="E17" s="56">
-        <f t="array" ref="E17">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C17-1),0)</f>
-        <v/>
-      </c>
-      <c r="F17" s="56">
-        <f t="array" ref="F17">F16+E17</f>
-        <v/>
-      </c>
-      <c r="G17" s="92">
-        <f t="array" ref="G17">ROUND(4*POWER('Tuning'!$B$23,C17-1),1)</f>
-        <v/>
-      </c>
-      <c r="H17" s="57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I17" s="60" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" s="92">
-        <f t="array" ref="J17">G17*H17*I17</f>
-        <v/>
-      </c>
-      <c r="K17" s="60" t="n">
-        <v>35</v>
-      </c>
-      <c r="L17" s="61" t="n"/>
-      <c r="M17" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N17" s="60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O17" s="60" t="n">
-        <v>40</v>
-      </c>
-      <c r="P17" s="60" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="60" t="n">
-        <v>50</v>
-      </c>
-      <c r="R17" s="60" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" s="60" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" ht="13.65" customHeight="1" s="90">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>Ordnance</t>
-        </is>
-      </c>
-      <c r="B18" s="43" t="inlineStr">
-        <is>
-          <t>Airburst</t>
-        </is>
-      </c>
-      <c r="C18" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" s="43" t="inlineStr">
-        <is>
-          <t>Mortar</t>
-        </is>
-      </c>
-      <c r="E18" s="56">
-        <f t="array" ref="E18">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C18-1),0)</f>
-        <v/>
-      </c>
-      <c r="F18" s="56">
-        <f t="array" ref="F18">F17+E18</f>
-        <v/>
-      </c>
-      <c r="G18" s="92">
-        <f t="array" ref="G18">ROUND(4*POWER('Tuning'!$B$23,C18-1),1)</f>
-        <v/>
-      </c>
-      <c r="H18" s="57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I18" s="60" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="92">
-        <f t="array" ref="J18">G18*H18*I18</f>
-        <v/>
-      </c>
-      <c r="K18" s="60" t="n">
-        <v>30</v>
-      </c>
-      <c r="L18" s="61" t="n"/>
-      <c r="M18" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N18" s="60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O18" s="60" t="n">
-        <v>40</v>
-      </c>
-      <c r="P18" s="60" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="60" t="n">
-        <v>80</v>
-      </c>
-      <c r="R18" s="60" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S18" s="60" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" ht="13.65" customHeight="1" s="90">
-      <c r="A19" s="43" t="inlineStr">
-        <is>
-          <t>Ordnance</t>
-        </is>
-      </c>
-      <c r="B19" s="43" t="inlineStr">
-        <is>
-          <t>Airburst</t>
-        </is>
-      </c>
-      <c r="C19" s="56" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" s="43" t="inlineStr">
-        <is>
-          <t>Rocket launcher</t>
-        </is>
-      </c>
-      <c r="E19" s="56">
-        <f t="array" ref="E19">ROUND('Tuning'!$B$21*POWER('Tuning'!$B$22,C19-1),0)</f>
-        <v/>
-      </c>
-      <c r="F19" s="56">
-        <f t="array" ref="F19">F18+E19</f>
-        <v/>
-      </c>
-      <c r="G19" s="92">
-        <f t="array" ref="G19">ROUND(4*POWER('Tuning'!$B$23,C19-1),1)</f>
-        <v/>
-      </c>
-      <c r="H19" s="57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I19" s="60" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" s="92">
-        <f t="array" ref="J19">G19*H19*I19</f>
-        <v/>
-      </c>
-      <c r="K19" s="60" t="n">
-        <v>25</v>
-      </c>
-      <c r="L19" s="61" t="n"/>
-      <c r="M19" s="60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N19" s="60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O19" s="60" t="n">
-        <v>40</v>
-      </c>
-      <c r="P19" s="60" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q19" s="60" t="n">
-        <v>130</v>
-      </c>
-      <c r="R19" s="60" t="n">
-        <v>3</v>
-      </c>
-      <c r="S19" s="60" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" ht="13.55" customHeight="1" s="90">
-      <c r="A20" s="62" t="n"/>
-      <c r="B20" s="49" t="n"/>
-      <c r="C20" s="49" t="n"/>
-      <c r="D20" s="49" t="n"/>
-      <c r="E20" s="49" t="n"/>
-      <c r="F20" s="49" t="n"/>
-      <c r="G20" s="49" t="n"/>
-      <c r="H20" s="49" t="n"/>
-      <c r="I20" s="49" t="n"/>
-      <c r="J20" s="49" t="n"/>
-      <c r="K20" s="49" t="n"/>
-      <c r="L20" s="50" t="n"/>
-    </row>
-    <row r="21" ht="14.6" customHeight="1" s="90">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>CROSSOVER RULE</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="13.55" customHeight="1" s="90">
-      <c r="A22" s="63" t="inlineStr">
-        <is>
-          <t>Max one path to tier 5. Second path caps at tier 2. Third stays locked. Mastery 20 raises that cap to 3 for one weapon.</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n"/>
-      <c r="H22" s="16" t="n"/>
-      <c r="I22" s="16" t="n"/>
-      <c r="J22" s="16" t="n"/>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="17" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="63" t="inlineStr">
-        <is>
-          <t>Ability columns, by type — Precision/Mark: power = +% damage the marked enemy takes, (s) = mark length. Sustained/Overdrive: power = +% fire rate for towers within the radius, (s) = duration (your own fire rate x 'Overdrive fire rate x' on Tuning). Ordnance/Airburst: power = damage, (s) = stun, radius = blast radius on the track. Tier 1 has no ability.</t>
+      <c r="W7" s="43" t="inlineStr">
+        <is>
+          <t>Airburst: power = damage, (s) = stun, radius on the track.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
-  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AG49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" style="90" min="1" max="1"/>
+    <col width="11" customWidth="1" style="90" min="2" max="2"/>
+    <col width="11" customWidth="1" style="90" min="3" max="3"/>
+    <col width="11" customWidth="1" style="90" min="4" max="4"/>
+    <col width="18" customWidth="1" style="90" min="5" max="5"/>
+    <col width="11" customWidth="1" style="90" min="6" max="6"/>
+    <col width="11" customWidth="1" style="90" min="7" max="7"/>
+    <col width="11" customWidth="1" style="90" min="8" max="8"/>
+    <col width="11" customWidth="1" style="90" min="9" max="9"/>
+    <col width="11" customWidth="1" style="90" min="10" max="10"/>
+    <col width="11" customWidth="1" style="90" min="11" max="11"/>
+    <col width="11" customWidth="1" style="90" min="12" max="12"/>
+    <col width="11" customWidth="1" style="90" min="13" max="13"/>
+    <col width="11" customWidth="1" style="90" min="14" max="14"/>
+    <col width="11" customWidth="1" style="90" min="15" max="15"/>
+    <col width="11" customWidth="1" style="90" min="16" max="16"/>
+    <col width="11" customWidth="1" style="90" min="17" max="17"/>
+    <col width="11" customWidth="1" style="90" min="18" max="18"/>
+    <col width="11" customWidth="1" style="90" min="19" max="19"/>
+    <col width="11" customWidth="1" style="90" min="20" max="20"/>
+    <col width="11" customWidth="1" style="90" min="21" max="21"/>
+    <col width="11" customWidth="1" style="90" min="22" max="22"/>
+    <col width="11" customWidth="1" style="90" min="23" max="23"/>
+    <col width="11" customWidth="1" style="90" min="24" max="24"/>
+    <col width="11" customWidth="1" style="90" min="25" max="25"/>
+    <col width="11" customWidth="1" style="90" min="26" max="26"/>
+    <col width="11" customWidth="1" style="90" min="27" max="27"/>
+    <col width="11" customWidth="1" style="90" min="28" max="28"/>
+    <col width="11" customWidth="1" style="90" min="29" max="29"/>
+    <col width="11" customWidth="1" style="90" min="30" max="30"/>
+    <col width="11" customWidth="1" style="90" min="31" max="31"/>
+    <col width="11" customWidth="1" style="90" min="32" max="32"/>
+    <col width="11" customWidth="1" style="90" min="33" max="33"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>HERO UPGRADES — 3 heroes x 3 paths x 5 tiers (HEROES.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Effect columns are cumulative per tier (like Tower Upgrades); blank = no change. x columns multiply the hero's base; Fire mode / Guns / Pellets / Pierce / Bounces override it. Crossover rule as towers: two paths, one past tier 2. Damage is per shot: pellets share the hero's base damage x its base pellet count, so more pellets spread the same damage wider and a slug concentrates it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Focus</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>Fire rate x</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>Magazine x</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>Reload x</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>Spread x</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>Recoil x</t>
+        </is>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t>Range x</t>
+        </is>
+      </c>
+      <c r="M4" s="21" t="inlineStr">
+        <is>
+          <t>Damage x</t>
+        </is>
+      </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t>Fire mode</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="inlineStr">
+        <is>
+          <t>Burst count</t>
+        </is>
+      </c>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t>Guns</t>
+        </is>
+      </c>
+      <c r="Q4" s="21" t="inlineStr">
+        <is>
+          <t>Pellets</t>
+        </is>
+      </c>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t>Shots per trigger</t>
+        </is>
+      </c>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="T4" s="21" t="inlineStr">
+        <is>
+          <t>Bounces</t>
+        </is>
+      </c>
+      <c r="U4" s="21" t="inlineStr">
+        <is>
+          <t>Pierces armour</t>
+        </is>
+      </c>
+      <c r="V4" s="21" t="inlineStr">
+        <is>
+          <t>Hits air</t>
+        </is>
+      </c>
+      <c r="W4" s="21" t="inlineStr">
+        <is>
+          <t>Burn DPS</t>
+        </is>
+      </c>
+      <c r="X4" s="21" t="inlineStr">
+        <is>
+          <t>Burn (s)</t>
+        </is>
+      </c>
+      <c r="Y4" s="21" t="inlineStr">
+        <is>
+          <t>Splash radius (m)</t>
+        </is>
+      </c>
+      <c r="Z4" s="21" t="inlineStr">
+        <is>
+          <t>Knockback (studs)</t>
+        </is>
+      </c>
+      <c r="AA4" s="21" t="inlineStr">
+        <is>
+          <t>Mark %</t>
+        </is>
+      </c>
+      <c r="AB4" s="21" t="inlineStr">
+        <is>
+          <t>Marked damage x</t>
+        </is>
+      </c>
+      <c r="AC4" s="21" t="inlineStr">
+        <is>
+          <t>Ability cooldown x</t>
+        </is>
+      </c>
+      <c r="AD4" s="21" t="inlineStr">
+        <is>
+          <t>Belt fed</t>
+        </is>
+      </c>
+      <c r="AE4" s="21" t="inlineStr">
+        <is>
+          <t>Still recoil x</t>
+        </is>
+      </c>
+      <c r="AF4" s="21" t="inlineStr">
+        <is>
+          <t>Spin-up x</t>
+        </is>
+      </c>
+      <c r="AG4" s="21" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>Gunslinger</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D5" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="43" t="inlineStr">
+        <is>
+          <t>Quick Draw</t>
+        </is>
+      </c>
+      <c r="F5" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D5-1),0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="57" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H5" s="57" t="n"/>
+      <c r="I5" s="57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J5" s="57" t="n"/>
+      <c r="K5" s="57" t="n"/>
+      <c r="L5" s="57" t="n"/>
+      <c r="M5" s="57" t="n"/>
+      <c r="N5" s="57" t="n"/>
+      <c r="O5" s="57" t="n"/>
+      <c r="P5" s="57" t="n"/>
+      <c r="Q5" s="57" t="n"/>
+      <c r="R5" s="57" t="n"/>
+      <c r="S5" s="57" t="n"/>
+      <c r="T5" s="57" t="n"/>
+      <c r="U5" s="57" t="n"/>
+      <c r="V5" s="57" t="n"/>
+      <c r="W5" s="57" t="n"/>
+      <c r="X5" s="57" t="n"/>
+      <c r="Y5" s="57" t="n"/>
+      <c r="Z5" s="57" t="n"/>
+      <c r="AA5" s="57" t="n"/>
+      <c r="AB5" s="57" t="n"/>
+      <c r="AC5" s="57" t="n"/>
+      <c r="AD5" s="57" t="n"/>
+      <c r="AE5" s="57" t="n"/>
+      <c r="AF5" s="57" t="n"/>
+      <c r="AG5" s="57" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>Gunslinger</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>Hair Trigger</t>
+        </is>
+      </c>
+      <c r="F6" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D6-1),0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H6" s="57" t="n"/>
+      <c r="I6" s="57" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J6" s="57" t="n"/>
+      <c r="K6" s="57" t="n"/>
+      <c r="L6" s="57" t="n"/>
+      <c r="M6" s="57" t="n"/>
+      <c r="N6" s="57" t="n"/>
+      <c r="O6" s="57" t="n"/>
+      <c r="P6" s="57" t="n"/>
+      <c r="Q6" s="57" t="n"/>
+      <c r="R6" s="57" t="n"/>
+      <c r="S6" s="57" t="n"/>
+      <c r="T6" s="57" t="n"/>
+      <c r="U6" s="57" t="n"/>
+      <c r="V6" s="57" t="n"/>
+      <c r="W6" s="57" t="n"/>
+      <c r="X6" s="57" t="n"/>
+      <c r="Y6" s="57" t="n"/>
+      <c r="Z6" s="57" t="n"/>
+      <c r="AA6" s="57" t="n"/>
+      <c r="AB6" s="57" t="n"/>
+      <c r="AC6" s="57" t="n"/>
+      <c r="AD6" s="57" t="n"/>
+      <c r="AE6" s="57" t="n"/>
+      <c r="AF6" s="57" t="n"/>
+      <c r="AG6" s="57" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>Gunslinger</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>Dual Pistols</t>
+        </is>
+      </c>
+      <c r="F7" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D7-1),0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H7" s="57" t="n"/>
+      <c r="I7" s="57" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J7" s="57" t="n"/>
+      <c r="K7" s="57" t="n"/>
+      <c r="L7" s="57" t="n"/>
+      <c r="M7" s="57" t="n"/>
+      <c r="N7" s="57" t="n"/>
+      <c r="O7" s="57" t="n"/>
+      <c r="P7" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="57" t="n"/>
+      <c r="R7" s="57" t="n"/>
+      <c r="S7" s="57" t="n"/>
+      <c r="T7" s="57" t="n"/>
+      <c r="U7" s="57" t="n"/>
+      <c r="V7" s="57" t="n"/>
+      <c r="W7" s="57" t="n"/>
+      <c r="X7" s="57" t="n"/>
+      <c r="Y7" s="57" t="n"/>
+      <c r="Z7" s="57" t="n"/>
+      <c r="AA7" s="57" t="n"/>
+      <c r="AB7" s="57" t="n"/>
+      <c r="AC7" s="57" t="n"/>
+      <c r="AD7" s="57" t="n"/>
+      <c r="AE7" s="57" t="n"/>
+      <c r="AF7" s="57" t="n"/>
+      <c r="AG7" s="57" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>Gunslinger</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>Fan the Hammer</t>
+        </is>
+      </c>
+      <c r="F8" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D8-1),0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H8" s="57" t="n"/>
+      <c r="I8" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J8" s="57" t="n"/>
+      <c r="K8" s="57" t="n"/>
+      <c r="L8" s="57" t="n"/>
+      <c r="M8" s="57" t="n"/>
+      <c r="N8" s="57" t="n"/>
+      <c r="O8" s="57" t="n"/>
+      <c r="P8" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="57" t="n"/>
+      <c r="R8" s="57" t="n"/>
+      <c r="S8" s="57" t="n"/>
+      <c r="T8" s="57" t="n"/>
+      <c r="U8" s="57" t="n"/>
+      <c r="V8" s="57" t="n"/>
+      <c r="W8" s="57" t="n"/>
+      <c r="X8" s="57" t="n"/>
+      <c r="Y8" s="57" t="n"/>
+      <c r="Z8" s="57" t="n"/>
+      <c r="AA8" s="57" t="n"/>
+      <c r="AB8" s="57" t="n"/>
+      <c r="AC8" s="57" t="n"/>
+      <c r="AD8" s="57" t="n"/>
+      <c r="AE8" s="57" t="n"/>
+      <c r="AF8" s="57" t="n"/>
+      <c r="AG8" s="57" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>Gunslinger</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>Akimbo Storm</t>
+        </is>
+      </c>
+      <c r="F9" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D9-1),0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I9" s="57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J9" s="57" t="n"/>
+      <c r="K9" s="57" t="n"/>
+      <c r="L9" s="57" t="n"/>
+      <c r="M9" s="57" t="n"/>
+      <c r="N9" s="57" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="O9" s="57" t="n"/>
+      <c r="P9" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="57" t="n"/>
+      <c r="R9" s="57" t="n"/>
+      <c r="S9" s="57" t="n"/>
+      <c r="T9" s="57" t="n"/>
+      <c r="U9" s="57" t="n"/>
+      <c r="V9" s="57" t="n"/>
+      <c r="W9" s="57" t="n"/>
+      <c r="X9" s="57" t="n"/>
+      <c r="Y9" s="57" t="n"/>
+      <c r="Z9" s="57" t="n"/>
+      <c r="AA9" s="57" t="n"/>
+      <c r="AB9" s="57" t="n"/>
+      <c r="AC9" s="57" t="n"/>
+      <c r="AD9" s="57" t="n"/>
+      <c r="AE9" s="57" t="n"/>
+      <c r="AF9" s="57" t="n"/>
+      <c r="AG9" s="57" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>Marksman</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="43" t="inlineStr">
+        <is>
+          <t>Match Barrel</t>
+        </is>
+      </c>
+      <c r="F10" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D10-1),0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="57" t="n"/>
+      <c r="H10" s="57" t="n"/>
+      <c r="I10" s="57" t="n"/>
+      <c r="J10" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K10" s="57" t="n"/>
+      <c r="L10" s="57" t="n"/>
+      <c r="M10" s="57" t="n"/>
+      <c r="N10" s="57" t="n"/>
+      <c r="O10" s="57" t="n"/>
+      <c r="P10" s="57" t="n"/>
+      <c r="Q10" s="57" t="n"/>
+      <c r="R10" s="57" t="n"/>
+      <c r="S10" s="57" t="n"/>
+      <c r="T10" s="57" t="n"/>
+      <c r="U10" s="57" t="n"/>
+      <c r="V10" s="57" t="n"/>
+      <c r="W10" s="57" t="n"/>
+      <c r="X10" s="57" t="n"/>
+      <c r="Y10" s="57" t="n"/>
+      <c r="Z10" s="57" t="n"/>
+      <c r="AA10" s="57" t="n"/>
+      <c r="AB10" s="57" t="n"/>
+      <c r="AC10" s="57" t="n"/>
+      <c r="AD10" s="57" t="n"/>
+      <c r="AE10" s="57" t="n"/>
+      <c r="AF10" s="57" t="n"/>
+      <c r="AG10" s="57" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>Marksman</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>Steady Hands</t>
+        </is>
+      </c>
+      <c r="F11" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D11-1),0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="57" t="n"/>
+      <c r="H11" s="57" t="n"/>
+      <c r="I11" s="57" t="n"/>
+      <c r="J11" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K11" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L11" s="57" t="n"/>
+      <c r="M11" s="57" t="n"/>
+      <c r="N11" s="57" t="n"/>
+      <c r="O11" s="57" t="n"/>
+      <c r="P11" s="57" t="n"/>
+      <c r="Q11" s="57" t="n"/>
+      <c r="R11" s="57" t="n"/>
+      <c r="S11" s="57" t="n"/>
+      <c r="T11" s="57" t="n"/>
+      <c r="U11" s="57" t="n"/>
+      <c r="V11" s="57" t="n"/>
+      <c r="W11" s="57" t="n"/>
+      <c r="X11" s="57" t="n"/>
+      <c r="Y11" s="57" t="n"/>
+      <c r="Z11" s="57" t="n"/>
+      <c r="AA11" s="57" t="n"/>
+      <c r="AB11" s="57" t="n"/>
+      <c r="AC11" s="57" t="n"/>
+      <c r="AD11" s="57" t="n"/>
+      <c r="AE11" s="57" t="n"/>
+      <c r="AF11" s="57" t="n"/>
+      <c r="AG11" s="57" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>Marksman</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="F12" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D12-1),0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="57" t="n"/>
+      <c r="H12" s="57" t="n"/>
+      <c r="I12" s="57" t="n"/>
+      <c r="J12" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K12" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L12" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M12" s="57" t="n"/>
+      <c r="N12" s="57" t="n"/>
+      <c r="O12" s="57" t="n"/>
+      <c r="P12" s="57" t="n"/>
+      <c r="Q12" s="57" t="n"/>
+      <c r="R12" s="57" t="n"/>
+      <c r="S12" s="57" t="n"/>
+      <c r="T12" s="57" t="n"/>
+      <c r="U12" s="57" t="n"/>
+      <c r="V12" s="57" t="n"/>
+      <c r="W12" s="57" t="n"/>
+      <c r="X12" s="57" t="n"/>
+      <c r="Y12" s="57" t="n"/>
+      <c r="Z12" s="57" t="n"/>
+      <c r="AA12" s="57" t="n"/>
+      <c r="AB12" s="57" t="n"/>
+      <c r="AC12" s="57" t="n"/>
+      <c r="AD12" s="57" t="n"/>
+      <c r="AE12" s="57" t="n"/>
+      <c r="AF12" s="57" t="n"/>
+      <c r="AG12" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>Marksman</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="43" t="inlineStr">
+        <is>
+          <t>Hollow Tips</t>
+        </is>
+      </c>
+      <c r="F13" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D13-1),0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="57" t="n"/>
+      <c r="H13" s="57" t="n"/>
+      <c r="I13" s="57" t="n"/>
+      <c r="J13" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K13" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L13" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M13" s="57" t="n"/>
+      <c r="N13" s="57" t="n"/>
+      <c r="O13" s="57" t="n"/>
+      <c r="P13" s="57" t="n"/>
+      <c r="Q13" s="57" t="n"/>
+      <c r="R13" s="57" t="n"/>
+      <c r="S13" s="57" t="n"/>
+      <c r="T13" s="57" t="n"/>
+      <c r="U13" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V13" s="57" t="n"/>
+      <c r="W13" s="57" t="n"/>
+      <c r="X13" s="57" t="n"/>
+      <c r="Y13" s="57" t="n"/>
+      <c r="Z13" s="57" t="n"/>
+      <c r="AA13" s="57" t="n"/>
+      <c r="AB13" s="57" t="n"/>
+      <c r="AC13" s="57" t="n"/>
+      <c r="AD13" s="57" t="n"/>
+      <c r="AE13" s="57" t="n"/>
+      <c r="AF13" s="57" t="n"/>
+      <c r="AG13" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>Marksman</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="43" t="inlineStr">
+        <is>
+          <t>Deadshot</t>
+        </is>
+      </c>
+      <c r="F14" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D14-1),0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="57" t="n"/>
+      <c r="H14" s="57" t="n"/>
+      <c r="I14" s="57" t="n"/>
+      <c r="J14" s="57" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K14" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L14" s="57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M14" s="57" t="n"/>
+      <c r="N14" s="57" t="n"/>
+      <c r="O14" s="57" t="n"/>
+      <c r="P14" s="57" t="n"/>
+      <c r="Q14" s="57" t="n"/>
+      <c r="R14" s="57" t="n"/>
+      <c r="S14" s="57" t="n"/>
+      <c r="T14" s="57" t="n"/>
+      <c r="U14" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V14" s="57" t="n"/>
+      <c r="W14" s="57" t="n"/>
+      <c r="X14" s="57" t="n"/>
+      <c r="Y14" s="57" t="n"/>
+      <c r="Z14" s="57" t="n"/>
+      <c r="AA14" s="57" t="n"/>
+      <c r="AB14" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC14" s="57" t="n"/>
+      <c r="AD14" s="57" t="n"/>
+      <c r="AE14" s="57" t="n"/>
+      <c r="AF14" s="57" t="n"/>
+      <c r="AG14" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>Trick Shot</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="D15" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="43" t="inlineStr">
+        <is>
+          <t>Speed Loader</t>
+        </is>
+      </c>
+      <c r="F15" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D15-1),0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="57" t="n"/>
+      <c r="H15" s="57" t="n"/>
+      <c r="I15" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J15" s="57" t="n"/>
+      <c r="K15" s="57" t="n"/>
+      <c r="L15" s="57" t="n"/>
+      <c r="M15" s="57" t="n"/>
+      <c r="N15" s="57" t="n"/>
+      <c r="O15" s="57" t="n"/>
+      <c r="P15" s="57" t="n"/>
+      <c r="Q15" s="57" t="n"/>
+      <c r="R15" s="57" t="n"/>
+      <c r="S15" s="57" t="n"/>
+      <c r="T15" s="57" t="n"/>
+      <c r="U15" s="57" t="n"/>
+      <c r="V15" s="57" t="n"/>
+      <c r="W15" s="57" t="n"/>
+      <c r="X15" s="57" t="n"/>
+      <c r="Y15" s="57" t="n"/>
+      <c r="Z15" s="57" t="n"/>
+      <c r="AA15" s="57" t="n"/>
+      <c r="AB15" s="57" t="n"/>
+      <c r="AC15" s="57" t="n"/>
+      <c r="AD15" s="57" t="n"/>
+      <c r="AE15" s="57" t="n"/>
+      <c r="AF15" s="57" t="n"/>
+      <c r="AG15" s="57" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>Trick Shot</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="43" t="inlineStr">
+        <is>
+          <t>Extended Mag</t>
+        </is>
+      </c>
+      <c r="F16" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D16-1),0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="57" t="n"/>
+      <c r="H16" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I16" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J16" s="57" t="n"/>
+      <c r="K16" s="57" t="n"/>
+      <c r="L16" s="57" t="n"/>
+      <c r="M16" s="57" t="n"/>
+      <c r="N16" s="57" t="n"/>
+      <c r="O16" s="57" t="n"/>
+      <c r="P16" s="57" t="n"/>
+      <c r="Q16" s="57" t="n"/>
+      <c r="R16" s="57" t="n"/>
+      <c r="S16" s="57" t="n"/>
+      <c r="T16" s="57" t="n"/>
+      <c r="U16" s="57" t="n"/>
+      <c r="V16" s="57" t="n"/>
+      <c r="W16" s="57" t="n"/>
+      <c r="X16" s="57" t="n"/>
+      <c r="Y16" s="57" t="n"/>
+      <c r="Z16" s="57" t="n"/>
+      <c r="AA16" s="57" t="n"/>
+      <c r="AB16" s="57" t="n"/>
+      <c r="AC16" s="57" t="n"/>
+      <c r="AD16" s="57" t="n"/>
+      <c r="AE16" s="57" t="n"/>
+      <c r="AF16" s="57" t="n"/>
+      <c r="AG16" s="57" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>Trick Shot</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="43" t="inlineStr">
+        <is>
+          <t>Ricochet</t>
+        </is>
+      </c>
+      <c r="F17" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D17-1),0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="57" t="n"/>
+      <c r="H17" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I17" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J17" s="57" t="n"/>
+      <c r="K17" s="57" t="n"/>
+      <c r="L17" s="57" t="n"/>
+      <c r="M17" s="57" t="n"/>
+      <c r="N17" s="57" t="n"/>
+      <c r="O17" s="57" t="n"/>
+      <c r="P17" s="57" t="n"/>
+      <c r="Q17" s="57" t="n"/>
+      <c r="R17" s="57" t="n"/>
+      <c r="S17" s="57" t="n"/>
+      <c r="T17" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" s="57" t="n"/>
+      <c r="V17" s="57" t="n"/>
+      <c r="W17" s="57" t="n"/>
+      <c r="X17" s="57" t="n"/>
+      <c r="Y17" s="57" t="n"/>
+      <c r="Z17" s="57" t="n"/>
+      <c r="AA17" s="57" t="n"/>
+      <c r="AB17" s="57" t="n"/>
+      <c r="AC17" s="57" t="n"/>
+      <c r="AD17" s="57" t="n"/>
+      <c r="AE17" s="57" t="n"/>
+      <c r="AF17" s="57" t="n"/>
+      <c r="AG17" s="57" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>Trick Shot</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="D18" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="43" t="inlineStr">
+        <is>
+          <t>Quick Mark</t>
+        </is>
+      </c>
+      <c r="F18" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D18-1),0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="57" t="n"/>
+      <c r="H18" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I18" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J18" s="57" t="n"/>
+      <c r="K18" s="57" t="n"/>
+      <c r="L18" s="57" t="n"/>
+      <c r="M18" s="57" t="n"/>
+      <c r="N18" s="57" t="n"/>
+      <c r="O18" s="57" t="n"/>
+      <c r="P18" s="57" t="n"/>
+      <c r="Q18" s="57" t="n"/>
+      <c r="R18" s="57" t="n"/>
+      <c r="S18" s="57" t="n"/>
+      <c r="T18" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="57" t="n"/>
+      <c r="V18" s="57" t="n"/>
+      <c r="W18" s="57" t="n"/>
+      <c r="X18" s="57" t="n"/>
+      <c r="Y18" s="57" t="n"/>
+      <c r="Z18" s="57" t="n"/>
+      <c r="AA18" s="57" t="n"/>
+      <c r="AB18" s="57" t="n"/>
+      <c r="AC18" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD18" s="57" t="n"/>
+      <c r="AE18" s="57" t="n"/>
+      <c r="AF18" s="57" t="n"/>
+      <c r="AG18" s="57" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>Pistol</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>Trick Shot</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="43" t="inlineStr">
+        <is>
+          <t>Chain Shot</t>
+        </is>
+      </c>
+      <c r="F19" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D19-1),0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="57" t="n"/>
+      <c r="H19" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I19" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J19" s="57" t="n"/>
+      <c r="K19" s="57" t="n"/>
+      <c r="L19" s="57" t="n"/>
+      <c r="M19" s="57" t="n"/>
+      <c r="N19" s="57" t="n"/>
+      <c r="O19" s="57" t="n"/>
+      <c r="P19" s="57" t="n"/>
+      <c r="Q19" s="57" t="n"/>
+      <c r="R19" s="57" t="n"/>
+      <c r="S19" s="57" t="n"/>
+      <c r="T19" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" s="57" t="n"/>
+      <c r="V19" s="57" t="n"/>
+      <c r="W19" s="57" t="n"/>
+      <c r="X19" s="57" t="n"/>
+      <c r="Y19" s="57" t="n"/>
+      <c r="Z19" s="57" t="n"/>
+      <c r="AA19" s="57" t="n"/>
+      <c r="AB19" s="57" t="n"/>
+      <c r="AC19" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD19" s="57" t="n"/>
+      <c r="AE19" s="57" t="n"/>
+      <c r="AF19" s="57" t="n"/>
+      <c r="AG19" s="57" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D20" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="43" t="inlineStr">
+        <is>
+          <t>Foregrip</t>
+        </is>
+      </c>
+      <c r="F20" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D20-1),0)</f>
+        <v/>
+      </c>
+      <c r="G20" s="57" t="n"/>
+      <c r="H20" s="57" t="n"/>
+      <c r="I20" s="57" t="n"/>
+      <c r="J20" s="57" t="n"/>
+      <c r="K20" s="57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L20" s="57" t="n"/>
+      <c r="M20" s="57" t="n"/>
+      <c r="N20" s="57" t="n"/>
+      <c r="O20" s="57" t="n"/>
+      <c r="P20" s="57" t="n"/>
+      <c r="Q20" s="57" t="n"/>
+      <c r="R20" s="57" t="n"/>
+      <c r="S20" s="57" t="n"/>
+      <c r="T20" s="57" t="n"/>
+      <c r="U20" s="57" t="n"/>
+      <c r="V20" s="57" t="n"/>
+      <c r="W20" s="57" t="n"/>
+      <c r="X20" s="57" t="n"/>
+      <c r="Y20" s="57" t="n"/>
+      <c r="Z20" s="57" t="n"/>
+      <c r="AA20" s="57" t="n"/>
+      <c r="AB20" s="57" t="n"/>
+      <c r="AC20" s="57" t="n"/>
+      <c r="AD20" s="57" t="n"/>
+      <c r="AE20" s="57" t="n"/>
+      <c r="AF20" s="57" t="n"/>
+      <c r="AG20" s="57" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D21" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="43" t="inlineStr">
+        <is>
+          <t>Compensator</t>
+        </is>
+      </c>
+      <c r="F21" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D21-1),0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="57" t="n"/>
+      <c r="H21" s="57" t="n"/>
+      <c r="I21" s="57" t="n"/>
+      <c r="J21" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K21" s="57" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L21" s="57" t="n"/>
+      <c r="M21" s="57" t="n"/>
+      <c r="N21" s="57" t="n"/>
+      <c r="O21" s="57" t="n"/>
+      <c r="P21" s="57" t="n"/>
+      <c r="Q21" s="57" t="n"/>
+      <c r="R21" s="57" t="n"/>
+      <c r="S21" s="57" t="n"/>
+      <c r="T21" s="57" t="n"/>
+      <c r="U21" s="57" t="n"/>
+      <c r="V21" s="57" t="n"/>
+      <c r="W21" s="57" t="n"/>
+      <c r="X21" s="57" t="n"/>
+      <c r="Y21" s="57" t="n"/>
+      <c r="Z21" s="57" t="n"/>
+      <c r="AA21" s="57" t="n"/>
+      <c r="AB21" s="57" t="n"/>
+      <c r="AC21" s="57" t="n"/>
+      <c r="AD21" s="57" t="n"/>
+      <c r="AE21" s="57" t="n"/>
+      <c r="AF21" s="57" t="n"/>
+      <c r="AG21" s="57" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="C22" s="43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D22" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="43" t="inlineStr">
+        <is>
+          <t>Burst Fire</t>
+        </is>
+      </c>
+      <c r="F22" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D22-1),0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H22" s="57" t="n"/>
+      <c r="I22" s="57" t="n"/>
+      <c r="J22" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K22" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L22" s="57" t="n"/>
+      <c r="M22" s="57" t="n"/>
+      <c r="N22" s="57" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="O22" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="P22" s="57" t="n"/>
+      <c r="Q22" s="57" t="n"/>
+      <c r="R22" s="57" t="n"/>
+      <c r="S22" s="57" t="n"/>
+      <c r="T22" s="57" t="n"/>
+      <c r="U22" s="57" t="n"/>
+      <c r="V22" s="57" t="n"/>
+      <c r="W22" s="57" t="n"/>
+      <c r="X22" s="57" t="n"/>
+      <c r="Y22" s="57" t="n"/>
+      <c r="Z22" s="57" t="n"/>
+      <c r="AA22" s="57" t="n"/>
+      <c r="AB22" s="57" t="n"/>
+      <c r="AC22" s="57" t="n"/>
+      <c r="AD22" s="57" t="n"/>
+      <c r="AE22" s="57" t="n"/>
+      <c r="AF22" s="57" t="n"/>
+      <c r="AG22" s="57" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="B23" s="43" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D23" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="43" t="inlineStr">
+        <is>
+          <t>Trigger Discipline</t>
+        </is>
+      </c>
+      <c r="F23" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D23-1),0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H23" s="57" t="n"/>
+      <c r="I23" s="57" t="n"/>
+      <c r="J23" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K23" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L23" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M23" s="57" t="n"/>
+      <c r="N23" s="57" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="O23" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="P23" s="57" t="n"/>
+      <c r="Q23" s="57" t="n"/>
+      <c r="R23" s="57" t="n"/>
+      <c r="S23" s="57" t="n"/>
+      <c r="T23" s="57" t="n"/>
+      <c r="U23" s="57" t="n"/>
+      <c r="V23" s="57" t="n"/>
+      <c r="W23" s="57" t="n"/>
+      <c r="X23" s="57" t="n"/>
+      <c r="Y23" s="57" t="n"/>
+      <c r="Z23" s="57" t="n"/>
+      <c r="AA23" s="57" t="n"/>
+      <c r="AB23" s="57" t="n"/>
+      <c r="AC23" s="57" t="n"/>
+      <c r="AD23" s="57" t="n"/>
+      <c r="AE23" s="57" t="n"/>
+      <c r="AF23" s="57" t="n"/>
+      <c r="AG23" s="57" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D24" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" s="43" t="inlineStr">
+        <is>
+          <t>Precision Burst</t>
+        </is>
+      </c>
+      <c r="F24" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D24-1),0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H24" s="57" t="n"/>
+      <c r="I24" s="57" t="n"/>
+      <c r="J24" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K24" s="57" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L24" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M24" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N24" s="57" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="O24" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="P24" s="57" t="n"/>
+      <c r="Q24" s="57" t="n"/>
+      <c r="R24" s="57" t="n"/>
+      <c r="S24" s="57" t="n"/>
+      <c r="T24" s="57" t="n"/>
+      <c r="U24" s="57" t="n"/>
+      <c r="V24" s="57" t="n"/>
+      <c r="W24" s="57" t="n"/>
+      <c r="X24" s="57" t="n"/>
+      <c r="Y24" s="57" t="n"/>
+      <c r="Z24" s="57" t="n"/>
+      <c r="AA24" s="57" t="n"/>
+      <c r="AB24" s="57" t="n"/>
+      <c r="AC24" s="57" t="n"/>
+      <c r="AD24" s="57" t="n"/>
+      <c r="AE24" s="57" t="n"/>
+      <c r="AF24" s="57" t="n"/>
+      <c r="AG24" s="57" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C25" s="43" t="inlineStr">
+        <is>
+          <t>sustain</t>
+        </is>
+      </c>
+      <c r="D25" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="43" t="inlineStr">
+        <is>
+          <t>Drum Mag</t>
+        </is>
+      </c>
+      <c r="F25" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D25-1),0)</f>
+        <v/>
+      </c>
+      <c r="G25" s="57" t="n"/>
+      <c r="H25" s="57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I25" s="57" t="n"/>
+      <c r="J25" s="57" t="n"/>
+      <c r="K25" s="57" t="n"/>
+      <c r="L25" s="57" t="n"/>
+      <c r="M25" s="57" t="n"/>
+      <c r="N25" s="57" t="n"/>
+      <c r="O25" s="57" t="n"/>
+      <c r="P25" s="57" t="n"/>
+      <c r="Q25" s="57" t="n"/>
+      <c r="R25" s="57" t="n"/>
+      <c r="S25" s="57" t="n"/>
+      <c r="T25" s="57" t="n"/>
+      <c r="U25" s="57" t="n"/>
+      <c r="V25" s="57" t="n"/>
+      <c r="W25" s="57" t="n"/>
+      <c r="X25" s="57" t="n"/>
+      <c r="Y25" s="57" t="n"/>
+      <c r="Z25" s="57" t="n"/>
+      <c r="AA25" s="57" t="n"/>
+      <c r="AB25" s="57" t="n"/>
+      <c r="AC25" s="57" t="n"/>
+      <c r="AD25" s="57" t="n"/>
+      <c r="AE25" s="57" t="n"/>
+      <c r="AF25" s="57" t="n"/>
+      <c r="AG25" s="57" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C26" s="43" t="inlineStr">
+        <is>
+          <t>sustain</t>
+        </is>
+      </c>
+      <c r="D26" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="43" t="inlineStr">
+        <is>
+          <t>Fast Hands</t>
+        </is>
+      </c>
+      <c r="F26" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D26-1),0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="57" t="n"/>
+      <c r="H26" s="57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I26" s="57" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J26" s="57" t="n"/>
+      <c r="K26" s="57" t="n"/>
+      <c r="L26" s="57" t="n"/>
+      <c r="M26" s="57" t="n"/>
+      <c r="N26" s="57" t="n"/>
+      <c r="O26" s="57" t="n"/>
+      <c r="P26" s="57" t="n"/>
+      <c r="Q26" s="57" t="n"/>
+      <c r="R26" s="57" t="n"/>
+      <c r="S26" s="57" t="n"/>
+      <c r="T26" s="57" t="n"/>
+      <c r="U26" s="57" t="n"/>
+      <c r="V26" s="57" t="n"/>
+      <c r="W26" s="57" t="n"/>
+      <c r="X26" s="57" t="n"/>
+      <c r="Y26" s="57" t="n"/>
+      <c r="Z26" s="57" t="n"/>
+      <c r="AA26" s="57" t="n"/>
+      <c r="AB26" s="57" t="n"/>
+      <c r="AC26" s="57" t="n"/>
+      <c r="AD26" s="57" t="n"/>
+      <c r="AE26" s="57" t="n"/>
+      <c r="AF26" s="57" t="n"/>
+      <c r="AG26" s="57" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="B27" s="43" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C27" s="43" t="inlineStr">
+        <is>
+          <t>sustain</t>
+        </is>
+      </c>
+      <c r="D27" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="43" t="inlineStr">
+        <is>
+          <t>Belt Fed</t>
+        </is>
+      </c>
+      <c r="F27" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D27-1),0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="57" t="n"/>
+      <c r="H27" s="57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I27" s="57" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J27" s="57" t="n"/>
+      <c r="K27" s="57" t="n"/>
+      <c r="L27" s="57" t="n"/>
+      <c r="M27" s="57" t="n"/>
+      <c r="N27" s="57" t="n"/>
+      <c r="O27" s="57" t="n"/>
+      <c r="P27" s="57" t="n"/>
+      <c r="Q27" s="57" t="n"/>
+      <c r="R27" s="57" t="n"/>
+      <c r="S27" s="57" t="n"/>
+      <c r="T27" s="57" t="n"/>
+      <c r="U27" s="57" t="n"/>
+      <c r="V27" s="57" t="n"/>
+      <c r="W27" s="57" t="n"/>
+      <c r="X27" s="57" t="n"/>
+      <c r="Y27" s="57" t="n"/>
+      <c r="Z27" s="57" t="n"/>
+      <c r="AA27" s="57" t="n"/>
+      <c r="AB27" s="57" t="n"/>
+      <c r="AC27" s="57" t="n"/>
+      <c r="AD27" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE27" s="57" t="n"/>
+      <c r="AF27" s="57" t="n"/>
+      <c r="AG27" s="57" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C28" s="43" t="inlineStr">
+        <is>
+          <t>sustain</t>
+        </is>
+      </c>
+      <c r="D28" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="43" t="inlineStr">
+        <is>
+          <t>Bipod</t>
+        </is>
+      </c>
+      <c r="F28" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D28-1),0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="57" t="n"/>
+      <c r="H28" s="57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I28" s="57" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J28" s="57" t="n"/>
+      <c r="K28" s="57" t="n"/>
+      <c r="L28" s="57" t="n"/>
+      <c r="M28" s="57" t="n"/>
+      <c r="N28" s="57" t="n"/>
+      <c r="O28" s="57" t="n"/>
+      <c r="P28" s="57" t="n"/>
+      <c r="Q28" s="57" t="n"/>
+      <c r="R28" s="57" t="n"/>
+      <c r="S28" s="57" t="n"/>
+      <c r="T28" s="57" t="n"/>
+      <c r="U28" s="57" t="n"/>
+      <c r="V28" s="57" t="n"/>
+      <c r="W28" s="57" t="n"/>
+      <c r="X28" s="57" t="n"/>
+      <c r="Y28" s="57" t="n"/>
+      <c r="Z28" s="57" t="n"/>
+      <c r="AA28" s="57" t="n"/>
+      <c r="AB28" s="57" t="n"/>
+      <c r="AC28" s="57" t="n"/>
+      <c r="AD28" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE28" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF28" s="57" t="n"/>
+      <c r="AG28" s="57" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C29" s="43" t="inlineStr">
+        <is>
+          <t>sustain</t>
+        </is>
+      </c>
+      <c r="D29" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="43" t="inlineStr">
+        <is>
+          <t>Spin-Up</t>
+        </is>
+      </c>
+      <c r="F29" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D29-1),0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="57" t="n"/>
+      <c r="H29" s="57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I29" s="57" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J29" s="57" t="n"/>
+      <c r="K29" s="57" t="n"/>
+      <c r="L29" s="57" t="n"/>
+      <c r="M29" s="57" t="n"/>
+      <c r="N29" s="57" t="n"/>
+      <c r="O29" s="57" t="n"/>
+      <c r="P29" s="57" t="n"/>
+      <c r="Q29" s="57" t="n"/>
+      <c r="R29" s="57" t="n"/>
+      <c r="S29" s="57" t="n"/>
+      <c r="T29" s="57" t="n"/>
+      <c r="U29" s="57" t="n"/>
+      <c r="V29" s="57" t="n"/>
+      <c r="W29" s="57" t="n"/>
+      <c r="X29" s="57" t="n"/>
+      <c r="Y29" s="57" t="n"/>
+      <c r="Z29" s="57" t="n"/>
+      <c r="AA29" s="57" t="n"/>
+      <c r="AB29" s="57" t="n"/>
+      <c r="AC29" s="57" t="n"/>
+      <c r="AD29" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE29" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF29" s="57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG29" s="57" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>Special Ammo</t>
+        </is>
+      </c>
+      <c r="C30" s="43" t="inlineStr">
+        <is>
+          <t>rounds</t>
+        </is>
+      </c>
+      <c r="D30" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="43" t="inlineStr">
+        <is>
+          <t>Tracer Rounds</t>
+        </is>
+      </c>
+      <c r="F30" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D30-1),0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="57" t="n"/>
+      <c r="H30" s="57" t="n"/>
+      <c r="I30" s="57" t="n"/>
+      <c r="J30" s="57" t="n"/>
+      <c r="K30" s="57" t="n"/>
+      <c r="L30" s="57" t="n"/>
+      <c r="M30" s="57" t="n"/>
+      <c r="N30" s="57" t="n"/>
+      <c r="O30" s="57" t="n"/>
+      <c r="P30" s="57" t="n"/>
+      <c r="Q30" s="57" t="n"/>
+      <c r="R30" s="57" t="n"/>
+      <c r="S30" s="57" t="n"/>
+      <c r="T30" s="57" t="n"/>
+      <c r="U30" s="57" t="n"/>
+      <c r="V30" s="57" t="n"/>
+      <c r="W30" s="57" t="n"/>
+      <c r="X30" s="57" t="n"/>
+      <c r="Y30" s="57" t="n"/>
+      <c r="Z30" s="57" t="n"/>
+      <c r="AA30" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB30" s="57" t="n"/>
+      <c r="AC30" s="57" t="n"/>
+      <c r="AD30" s="57" t="n"/>
+      <c r="AE30" s="57" t="n"/>
+      <c r="AF30" s="57" t="n"/>
+      <c r="AG30" s="57" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="B31" s="43" t="inlineStr">
+        <is>
+          <t>Special Ammo</t>
+        </is>
+      </c>
+      <c r="C31" s="43" t="inlineStr">
+        <is>
+          <t>rounds</t>
+        </is>
+      </c>
+      <c r="D31" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="43" t="inlineStr">
+        <is>
+          <t>Incendiary</t>
+        </is>
+      </c>
+      <c r="F31" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D31-1),0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="57" t="n"/>
+      <c r="H31" s="57" t="n"/>
+      <c r="I31" s="57" t="n"/>
+      <c r="J31" s="57" t="n"/>
+      <c r="K31" s="57" t="n"/>
+      <c r="L31" s="57" t="n"/>
+      <c r="M31" s="57" t="n"/>
+      <c r="N31" s="57" t="n"/>
+      <c r="O31" s="57" t="n"/>
+      <c r="P31" s="57" t="n"/>
+      <c r="Q31" s="57" t="n"/>
+      <c r="R31" s="57" t="n"/>
+      <c r="S31" s="57" t="n"/>
+      <c r="T31" s="57" t="n"/>
+      <c r="U31" s="57" t="n"/>
+      <c r="V31" s="57" t="n"/>
+      <c r="W31" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y31" s="57" t="n"/>
+      <c r="Z31" s="57" t="n"/>
+      <c r="AA31" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB31" s="57" t="n"/>
+      <c r="AC31" s="57" t="n"/>
+      <c r="AD31" s="57" t="n"/>
+      <c r="AE31" s="57" t="n"/>
+      <c r="AF31" s="57" t="n"/>
+      <c r="AG31" s="57" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="inlineStr">
+        <is>
+          <t>Special Ammo</t>
+        </is>
+      </c>
+      <c r="C32" s="43" t="inlineStr">
+        <is>
+          <t>rounds</t>
+        </is>
+      </c>
+      <c r="D32" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="43" t="inlineStr">
+        <is>
+          <t>AP Rounds</t>
+        </is>
+      </c>
+      <c r="F32" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D32-1),0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="57" t="n"/>
+      <c r="H32" s="57" t="n"/>
+      <c r="I32" s="57" t="n"/>
+      <c r="J32" s="57" t="n"/>
+      <c r="K32" s="57" t="n"/>
+      <c r="L32" s="57" t="n"/>
+      <c r="M32" s="57" t="n"/>
+      <c r="N32" s="57" t="n"/>
+      <c r="O32" s="57" t="n"/>
+      <c r="P32" s="57" t="n"/>
+      <c r="Q32" s="57" t="n"/>
+      <c r="R32" s="57" t="n"/>
+      <c r="S32" s="57" t="n"/>
+      <c r="T32" s="57" t="n"/>
+      <c r="U32" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V32" s="57" t="n"/>
+      <c r="W32" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y32" s="57" t="n"/>
+      <c r="Z32" s="57" t="n"/>
+      <c r="AA32" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB32" s="57" t="n"/>
+      <c r="AC32" s="57" t="n"/>
+      <c r="AD32" s="57" t="n"/>
+      <c r="AE32" s="57" t="n"/>
+      <c r="AF32" s="57" t="n"/>
+      <c r="AG32" s="57" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>Special Ammo</t>
+        </is>
+      </c>
+      <c r="C33" s="43" t="inlineStr">
+        <is>
+          <t>rounds</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" s="43" t="inlineStr">
+        <is>
+          <t>Hot Load</t>
+        </is>
+      </c>
+      <c r="F33" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D33-1),0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="57" t="n"/>
+      <c r="H33" s="57" t="n"/>
+      <c r="I33" s="57" t="n"/>
+      <c r="J33" s="57" t="n"/>
+      <c r="K33" s="57" t="n"/>
+      <c r="L33" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M33" s="57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N33" s="57" t="n"/>
+      <c r="O33" s="57" t="n"/>
+      <c r="P33" s="57" t="n"/>
+      <c r="Q33" s="57" t="n"/>
+      <c r="R33" s="57" t="n"/>
+      <c r="S33" s="57" t="n"/>
+      <c r="T33" s="57" t="n"/>
+      <c r="U33" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V33" s="57" t="n"/>
+      <c r="W33" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y33" s="57" t="n"/>
+      <c r="Z33" s="57" t="n"/>
+      <c r="AA33" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB33" s="57" t="n"/>
+      <c r="AC33" s="57" t="n"/>
+      <c r="AD33" s="57" t="n"/>
+      <c r="AE33" s="57" t="n"/>
+      <c r="AF33" s="57" t="n"/>
+      <c r="AG33" s="57" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="B34" s="43" t="inlineStr">
+        <is>
+          <t>Special Ammo</t>
+        </is>
+      </c>
+      <c r="C34" s="43" t="inlineStr">
+        <is>
+          <t>rounds</t>
+        </is>
+      </c>
+      <c r="D34" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" s="43" t="inlineStr">
+        <is>
+          <t>Explosive Tips</t>
+        </is>
+      </c>
+      <c r="F34" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D34-1),0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="57" t="n"/>
+      <c r="H34" s="57" t="n"/>
+      <c r="I34" s="57" t="n"/>
+      <c r="J34" s="57" t="n"/>
+      <c r="K34" s="57" t="n"/>
+      <c r="L34" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M34" s="57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N34" s="57" t="n"/>
+      <c r="O34" s="57" t="n"/>
+      <c r="P34" s="57" t="n"/>
+      <c r="Q34" s="57" t="n"/>
+      <c r="R34" s="57" t="n"/>
+      <c r="S34" s="57" t="n"/>
+      <c r="T34" s="57" t="n"/>
+      <c r="U34" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V34" s="57" t="n"/>
+      <c r="W34" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X34" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y34" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z34" s="57" t="n"/>
+      <c r="AA34" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB34" s="57" t="n"/>
+      <c r="AC34" s="57" t="n"/>
+      <c r="AD34" s="57" t="n"/>
+      <c r="AE34" s="57" t="n"/>
+      <c r="AF34" s="57" t="n"/>
+      <c r="AG34" s="57" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="B35" s="43" t="inlineStr">
+        <is>
+          <t>Slug</t>
+        </is>
+      </c>
+      <c r="C35" s="43" t="inlineStr">
+        <is>
+          <t>reach</t>
+        </is>
+      </c>
+      <c r="D35" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="43" t="inlineStr">
+        <is>
+          <t>Slug Rounds</t>
+        </is>
+      </c>
+      <c r="F35" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D35-1),0)</f>
+        <v/>
+      </c>
+      <c r="G35" s="57" t="n"/>
+      <c r="H35" s="57" t="n"/>
+      <c r="I35" s="57" t="n"/>
+      <c r="J35" s="57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K35" s="57" t="n"/>
+      <c r="L35" s="57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M35" s="57" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N35" s="57" t="n"/>
+      <c r="O35" s="57" t="n"/>
+      <c r="P35" s="57" t="n"/>
+      <c r="Q35" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" s="57" t="n"/>
+      <c r="S35" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" s="57" t="n"/>
+      <c r="U35" s="57" t="n"/>
+      <c r="V35" s="57" t="n"/>
+      <c r="W35" s="57" t="n"/>
+      <c r="X35" s="57" t="n"/>
+      <c r="Y35" s="57" t="n"/>
+      <c r="Z35" s="57" t="n"/>
+      <c r="AA35" s="57" t="n"/>
+      <c r="AB35" s="57" t="n"/>
+      <c r="AC35" s="57" t="n"/>
+      <c r="AD35" s="57" t="n"/>
+      <c r="AE35" s="57" t="n"/>
+      <c r="AF35" s="57" t="n"/>
+      <c r="AG35" s="57" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="B36" s="43" t="inlineStr">
+        <is>
+          <t>Slug</t>
+        </is>
+      </c>
+      <c r="C36" s="43" t="inlineStr">
+        <is>
+          <t>reach</t>
+        </is>
+      </c>
+      <c r="D36" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="43" t="inlineStr">
+        <is>
+          <t>Rifled Barrel</t>
+        </is>
+      </c>
+      <c r="F36" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D36-1),0)</f>
+        <v/>
+      </c>
+      <c r="G36" s="57" t="n"/>
+      <c r="H36" s="57" t="n"/>
+      <c r="I36" s="57" t="n"/>
+      <c r="J36" s="57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K36" s="57" t="n"/>
+      <c r="L36" s="57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M36" s="57" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N36" s="57" t="n"/>
+      <c r="O36" s="57" t="n"/>
+      <c r="P36" s="57" t="n"/>
+      <c r="Q36" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" s="57" t="n"/>
+      <c r="S36" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="T36" s="57" t="n"/>
+      <c r="U36" s="57" t="n"/>
+      <c r="V36" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W36" s="57" t="n"/>
+      <c r="X36" s="57" t="n"/>
+      <c r="Y36" s="57" t="n"/>
+      <c r="Z36" s="57" t="n"/>
+      <c r="AA36" s="57" t="n"/>
+      <c r="AB36" s="57" t="n"/>
+      <c r="AC36" s="57" t="n"/>
+      <c r="AD36" s="57" t="n"/>
+      <c r="AE36" s="57" t="n"/>
+      <c r="AF36" s="57" t="n"/>
+      <c r="AG36" s="57" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="inlineStr">
+        <is>
+          <t>Slug</t>
+        </is>
+      </c>
+      <c r="C37" s="43" t="inlineStr">
+        <is>
+          <t>reach</t>
+        </is>
+      </c>
+      <c r="D37" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="43" t="inlineStr">
+        <is>
+          <t>Sabot</t>
+        </is>
+      </c>
+      <c r="F37" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D37-1),0)</f>
+        <v/>
+      </c>
+      <c r="G37" s="57" t="n"/>
+      <c r="H37" s="57" t="n"/>
+      <c r="I37" s="57" t="n"/>
+      <c r="J37" s="57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K37" s="57" t="n"/>
+      <c r="L37" s="57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M37" s="57" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N37" s="57" t="n"/>
+      <c r="O37" s="57" t="n"/>
+      <c r="P37" s="57" t="n"/>
+      <c r="Q37" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" s="57" t="n"/>
+      <c r="S37" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="T37" s="57" t="n"/>
+      <c r="U37" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V37" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W37" s="57" t="n"/>
+      <c r="X37" s="57" t="n"/>
+      <c r="Y37" s="57" t="n"/>
+      <c r="Z37" s="57" t="n"/>
+      <c r="AA37" s="57" t="n"/>
+      <c r="AB37" s="57" t="n"/>
+      <c r="AC37" s="57" t="n"/>
+      <c r="AD37" s="57" t="n"/>
+      <c r="AE37" s="57" t="n"/>
+      <c r="AF37" s="57" t="n"/>
+      <c r="AG37" s="57" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="B38" s="43" t="inlineStr">
+        <is>
+          <t>Slug</t>
+        </is>
+      </c>
+      <c r="C38" s="43" t="inlineStr">
+        <is>
+          <t>reach</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" s="43" t="inlineStr">
+        <is>
+          <t>Long Barrel</t>
+        </is>
+      </c>
+      <c r="F38" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D38-1),0)</f>
+        <v/>
+      </c>
+      <c r="G38" s="57" t="n"/>
+      <c r="H38" s="57" t="n"/>
+      <c r="I38" s="57" t="n"/>
+      <c r="J38" s="57" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K38" s="57" t="n"/>
+      <c r="L38" s="57" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M38" s="57" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N38" s="57" t="n"/>
+      <c r="O38" s="57" t="n"/>
+      <c r="P38" s="57" t="n"/>
+      <c r="Q38" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" s="57" t="n"/>
+      <c r="S38" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" s="57" t="n"/>
+      <c r="U38" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V38" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W38" s="57" t="n"/>
+      <c r="X38" s="57" t="n"/>
+      <c r="Y38" s="57" t="n"/>
+      <c r="Z38" s="57" t="n"/>
+      <c r="AA38" s="57" t="n"/>
+      <c r="AB38" s="57" t="n"/>
+      <c r="AC38" s="57" t="n"/>
+      <c r="AD38" s="57" t="n"/>
+      <c r="AE38" s="57" t="n"/>
+      <c r="AF38" s="57" t="n"/>
+      <c r="AG38" s="57" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="B39" s="43" t="inlineStr">
+        <is>
+          <t>Slug</t>
+        </is>
+      </c>
+      <c r="C39" s="43" t="inlineStr">
+        <is>
+          <t>reach</t>
+        </is>
+      </c>
+      <c r="D39" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" s="43" t="inlineStr">
+        <is>
+          <t>Railslug</t>
+        </is>
+      </c>
+      <c r="F39" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D39-1),0)</f>
+        <v/>
+      </c>
+      <c r="G39" s="57" t="n"/>
+      <c r="H39" s="57" t="n"/>
+      <c r="I39" s="57" t="n"/>
+      <c r="J39" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K39" s="57" t="n"/>
+      <c r="L39" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="M39" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" s="57" t="n"/>
+      <c r="O39" s="57" t="n"/>
+      <c r="P39" s="57" t="n"/>
+      <c r="Q39" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" s="57" t="n"/>
+      <c r="S39" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="T39" s="57" t="n"/>
+      <c r="U39" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V39" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W39" s="57" t="n"/>
+      <c r="X39" s="57" t="n"/>
+      <c r="Y39" s="57" t="n"/>
+      <c r="Z39" s="57" t="n"/>
+      <c r="AA39" s="57" t="n"/>
+      <c r="AB39" s="57" t="n"/>
+      <c r="AC39" s="57" t="n"/>
+      <c r="AD39" s="57" t="n"/>
+      <c r="AE39" s="57" t="n"/>
+      <c r="AF39" s="57" t="n"/>
+      <c r="AG39" s="57" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="B40" s="43" t="inlineStr">
+        <is>
+          <t>Buckshot</t>
+        </is>
+      </c>
+      <c r="C40" s="43" t="inlineStr">
+        <is>
+          <t>crowds</t>
+        </is>
+      </c>
+      <c r="D40" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="43" t="inlineStr">
+        <is>
+          <t>Tight Choke</t>
+        </is>
+      </c>
+      <c r="F40" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D40-1),0)</f>
+        <v/>
+      </c>
+      <c r="G40" s="57" t="n"/>
+      <c r="H40" s="57" t="n"/>
+      <c r="I40" s="57" t="n"/>
+      <c r="J40" s="57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K40" s="57" t="n"/>
+      <c r="L40" s="57" t="n"/>
+      <c r="M40" s="57" t="n"/>
+      <c r="N40" s="57" t="n"/>
+      <c r="O40" s="57" t="n"/>
+      <c r="P40" s="57" t="n"/>
+      <c r="Q40" s="57" t="n"/>
+      <c r="R40" s="57" t="n"/>
+      <c r="S40" s="57" t="n"/>
+      <c r="T40" s="57" t="n"/>
+      <c r="U40" s="57" t="n"/>
+      <c r="V40" s="57" t="n"/>
+      <c r="W40" s="57" t="n"/>
+      <c r="X40" s="57" t="n"/>
+      <c r="Y40" s="57" t="n"/>
+      <c r="Z40" s="57" t="n"/>
+      <c r="AA40" s="57" t="n"/>
+      <c r="AB40" s="57" t="n"/>
+      <c r="AC40" s="57" t="n"/>
+      <c r="AD40" s="57" t="n"/>
+      <c r="AE40" s="57" t="n"/>
+      <c r="AF40" s="57" t="n"/>
+      <c r="AG40" s="57" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="B41" s="43" t="inlineStr">
+        <is>
+          <t>Buckshot</t>
+        </is>
+      </c>
+      <c r="C41" s="43" t="inlineStr">
+        <is>
+          <t>crowds</t>
+        </is>
+      </c>
+      <c r="D41" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" s="43" t="inlineStr">
+        <is>
+          <t>Extra Pellets</t>
+        </is>
+      </c>
+      <c r="F41" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D41-1),0)</f>
+        <v/>
+      </c>
+      <c r="G41" s="57" t="n"/>
+      <c r="H41" s="57" t="n"/>
+      <c r="I41" s="57" t="n"/>
+      <c r="J41" s="57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K41" s="57" t="n"/>
+      <c r="L41" s="57" t="n"/>
+      <c r="M41" s="57" t="n"/>
+      <c r="N41" s="57" t="n"/>
+      <c r="O41" s="57" t="n"/>
+      <c r="P41" s="57" t="n"/>
+      <c r="Q41" s="57" t="n">
+        <v>9</v>
+      </c>
+      <c r="R41" s="57" t="n"/>
+      <c r="S41" s="57" t="n"/>
+      <c r="T41" s="57" t="n"/>
+      <c r="U41" s="57" t="n"/>
+      <c r="V41" s="57" t="n"/>
+      <c r="W41" s="57" t="n"/>
+      <c r="X41" s="57" t="n"/>
+      <c r="Y41" s="57" t="n"/>
+      <c r="Z41" s="57" t="n"/>
+      <c r="AA41" s="57" t="n"/>
+      <c r="AB41" s="57" t="n"/>
+      <c r="AC41" s="57" t="n"/>
+      <c r="AD41" s="57" t="n"/>
+      <c r="AE41" s="57" t="n"/>
+      <c r="AF41" s="57" t="n"/>
+      <c r="AG41" s="57" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="B42" s="43" t="inlineStr">
+        <is>
+          <t>Buckshot</t>
+        </is>
+      </c>
+      <c r="C42" s="43" t="inlineStr">
+        <is>
+          <t>crowds</t>
+        </is>
+      </c>
+      <c r="D42" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="43" t="inlineStr">
+        <is>
+          <t>Dragon's Breath</t>
+        </is>
+      </c>
+      <c r="F42" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D42-1),0)</f>
+        <v/>
+      </c>
+      <c r="G42" s="57" t="n"/>
+      <c r="H42" s="57" t="n"/>
+      <c r="I42" s="57" t="n"/>
+      <c r="J42" s="57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K42" s="57" t="n"/>
+      <c r="L42" s="57" t="n"/>
+      <c r="M42" s="57" t="n"/>
+      <c r="N42" s="57" t="n"/>
+      <c r="O42" s="57" t="n"/>
+      <c r="P42" s="57" t="n"/>
+      <c r="Q42" s="57" t="n">
+        <v>9</v>
+      </c>
+      <c r="R42" s="57" t="n"/>
+      <c r="S42" s="57" t="n"/>
+      <c r="T42" s="57" t="n"/>
+      <c r="U42" s="57" t="n"/>
+      <c r="V42" s="57" t="n"/>
+      <c r="W42" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X42" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y42" s="57" t="n"/>
+      <c r="Z42" s="57" t="n"/>
+      <c r="AA42" s="57" t="n"/>
+      <c r="AB42" s="57" t="n"/>
+      <c r="AC42" s="57" t="n"/>
+      <c r="AD42" s="57" t="n"/>
+      <c r="AE42" s="57" t="n"/>
+      <c r="AF42" s="57" t="n"/>
+      <c r="AG42" s="57" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="B43" s="43" t="inlineStr">
+        <is>
+          <t>Buckshot</t>
+        </is>
+      </c>
+      <c r="C43" s="43" t="inlineStr">
+        <is>
+          <t>crowds</t>
+        </is>
+      </c>
+      <c r="D43" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" s="43" t="inlineStr">
+        <is>
+          <t>Auto-Loader</t>
+        </is>
+      </c>
+      <c r="F43" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D43-1),0)</f>
+        <v/>
+      </c>
+      <c r="G43" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H43" s="57" t="n"/>
+      <c r="I43" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J43" s="57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K43" s="57" t="n"/>
+      <c r="L43" s="57" t="n"/>
+      <c r="M43" s="57" t="n"/>
+      <c r="N43" s="57" t="n"/>
+      <c r="O43" s="57" t="n"/>
+      <c r="P43" s="57" t="n"/>
+      <c r="Q43" s="57" t="n">
+        <v>9</v>
+      </c>
+      <c r="R43" s="57" t="n"/>
+      <c r="S43" s="57" t="n"/>
+      <c r="T43" s="57" t="n"/>
+      <c r="U43" s="57" t="n"/>
+      <c r="V43" s="57" t="n"/>
+      <c r="W43" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X43" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="57" t="n"/>
+      <c r="Z43" s="57" t="n"/>
+      <c r="AA43" s="57" t="n"/>
+      <c r="AB43" s="57" t="n"/>
+      <c r="AC43" s="57" t="n"/>
+      <c r="AD43" s="57" t="n"/>
+      <c r="AE43" s="57" t="n"/>
+      <c r="AF43" s="57" t="n"/>
+      <c r="AG43" s="57" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="B44" s="43" t="inlineStr">
+        <is>
+          <t>Buckshot</t>
+        </is>
+      </c>
+      <c r="C44" s="43" t="inlineStr">
+        <is>
+          <t>crowds</t>
+        </is>
+      </c>
+      <c r="D44" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" s="43" t="inlineStr">
+        <is>
+          <t>Street Sweeper</t>
+        </is>
+      </c>
+      <c r="F44" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D44-1),0)</f>
+        <v/>
+      </c>
+      <c r="G44" s="57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H44" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J44" s="57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K44" s="57" t="n"/>
+      <c r="L44" s="57" t="n"/>
+      <c r="M44" s="57" t="n"/>
+      <c r="N44" s="57" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="O44" s="57" t="n"/>
+      <c r="P44" s="57" t="n"/>
+      <c r="Q44" s="57" t="n">
+        <v>9</v>
+      </c>
+      <c r="R44" s="57" t="n"/>
+      <c r="S44" s="57" t="n"/>
+      <c r="T44" s="57" t="n"/>
+      <c r="U44" s="57" t="n"/>
+      <c r="V44" s="57" t="n"/>
+      <c r="W44" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X44" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y44" s="57" t="n"/>
+      <c r="Z44" s="57" t="n"/>
+      <c r="AA44" s="57" t="n"/>
+      <c r="AB44" s="57" t="n"/>
+      <c r="AC44" s="57" t="n"/>
+      <c r="AD44" s="57" t="n"/>
+      <c r="AE44" s="57" t="n"/>
+      <c r="AF44" s="57" t="n"/>
+      <c r="AG44" s="57" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="B45" s="43" t="inlineStr">
+        <is>
+          <t>Breacher</t>
+        </is>
+      </c>
+      <c r="C45" s="43" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="D45" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="43" t="inlineStr">
+        <is>
+          <t>Speed Shells</t>
+        </is>
+      </c>
+      <c r="F45" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D45-1),0)</f>
+        <v/>
+      </c>
+      <c r="G45" s="57" t="n"/>
+      <c r="H45" s="57" t="n"/>
+      <c r="I45" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J45" s="57" t="n"/>
+      <c r="K45" s="57" t="n"/>
+      <c r="L45" s="57" t="n"/>
+      <c r="M45" s="57" t="n"/>
+      <c r="N45" s="57" t="n"/>
+      <c r="O45" s="57" t="n"/>
+      <c r="P45" s="57" t="n"/>
+      <c r="Q45" s="57" t="n"/>
+      <c r="R45" s="57" t="n"/>
+      <c r="S45" s="57" t="n"/>
+      <c r="T45" s="57" t="n"/>
+      <c r="U45" s="57" t="n"/>
+      <c r="V45" s="57" t="n"/>
+      <c r="W45" s="57" t="n"/>
+      <c r="X45" s="57" t="n"/>
+      <c r="Y45" s="57" t="n"/>
+      <c r="Z45" s="57" t="n"/>
+      <c r="AA45" s="57" t="n"/>
+      <c r="AB45" s="57" t="n"/>
+      <c r="AC45" s="57" t="n"/>
+      <c r="AD45" s="57" t="n"/>
+      <c r="AE45" s="57" t="n"/>
+      <c r="AF45" s="57" t="n"/>
+      <c r="AG45" s="57" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="B46" s="43" t="inlineStr">
+        <is>
+          <t>Breacher</t>
+        </is>
+      </c>
+      <c r="C46" s="43" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="D46" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" s="43" t="inlineStr">
+        <is>
+          <t>Extended Tube</t>
+        </is>
+      </c>
+      <c r="F46" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D46-1),0)</f>
+        <v/>
+      </c>
+      <c r="G46" s="57" t="n"/>
+      <c r="H46" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I46" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J46" s="57" t="n"/>
+      <c r="K46" s="57" t="n"/>
+      <c r="L46" s="57" t="n"/>
+      <c r="M46" s="57" t="n"/>
+      <c r="N46" s="57" t="n"/>
+      <c r="O46" s="57" t="n"/>
+      <c r="P46" s="57" t="n"/>
+      <c r="Q46" s="57" t="n"/>
+      <c r="R46" s="57" t="n"/>
+      <c r="S46" s="57" t="n"/>
+      <c r="T46" s="57" t="n"/>
+      <c r="U46" s="57" t="n"/>
+      <c r="V46" s="57" t="n"/>
+      <c r="W46" s="57" t="n"/>
+      <c r="X46" s="57" t="n"/>
+      <c r="Y46" s="57" t="n"/>
+      <c r="Z46" s="57" t="n"/>
+      <c r="AA46" s="57" t="n"/>
+      <c r="AB46" s="57" t="n"/>
+      <c r="AC46" s="57" t="n"/>
+      <c r="AD46" s="57" t="n"/>
+      <c r="AE46" s="57" t="n"/>
+      <c r="AF46" s="57" t="n"/>
+      <c r="AG46" s="57" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="B47" s="43" t="inlineStr">
+        <is>
+          <t>Breacher</t>
+        </is>
+      </c>
+      <c r="C47" s="43" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="D47" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="43" t="inlineStr">
+        <is>
+          <t>Double Barrel</t>
+        </is>
+      </c>
+      <c r="F47" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D47-1),0)</f>
+        <v/>
+      </c>
+      <c r="G47" s="57" t="n"/>
+      <c r="H47" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I47" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J47" s="57" t="n"/>
+      <c r="K47" s="57" t="n"/>
+      <c r="L47" s="57" t="n"/>
+      <c r="M47" s="57" t="n"/>
+      <c r="N47" s="57" t="n"/>
+      <c r="O47" s="57" t="n"/>
+      <c r="P47" s="57" t="n"/>
+      <c r="Q47" s="57" t="n"/>
+      <c r="R47" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="S47" s="57" t="n"/>
+      <c r="T47" s="57" t="n"/>
+      <c r="U47" s="57" t="n"/>
+      <c r="V47" s="57" t="n"/>
+      <c r="W47" s="57" t="n"/>
+      <c r="X47" s="57" t="n"/>
+      <c r="Y47" s="57" t="n"/>
+      <c r="Z47" s="57" t="n"/>
+      <c r="AA47" s="57" t="n"/>
+      <c r="AB47" s="57" t="n"/>
+      <c r="AC47" s="57" t="n"/>
+      <c r="AD47" s="57" t="n"/>
+      <c r="AE47" s="57" t="n"/>
+      <c r="AF47" s="57" t="n"/>
+      <c r="AG47" s="57" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="B48" s="43" t="inlineStr">
+        <is>
+          <t>Breacher</t>
+        </is>
+      </c>
+      <c r="C48" s="43" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="D48" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="43" t="inlineStr">
+        <is>
+          <t>Kickback</t>
+        </is>
+      </c>
+      <c r="F48" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D48-1),0)</f>
+        <v/>
+      </c>
+      <c r="G48" s="57" t="n"/>
+      <c r="H48" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I48" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J48" s="57" t="n"/>
+      <c r="K48" s="57" t="n"/>
+      <c r="L48" s="57" t="n"/>
+      <c r="M48" s="57" t="n"/>
+      <c r="N48" s="57" t="n"/>
+      <c r="O48" s="57" t="n"/>
+      <c r="P48" s="57" t="n"/>
+      <c r="Q48" s="57" t="n"/>
+      <c r="R48" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="S48" s="57" t="n"/>
+      <c r="T48" s="57" t="n"/>
+      <c r="U48" s="57" t="n"/>
+      <c r="V48" s="57" t="n"/>
+      <c r="W48" s="57" t="n"/>
+      <c r="X48" s="57" t="n"/>
+      <c r="Y48" s="57" t="n"/>
+      <c r="Z48" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA48" s="57" t="n"/>
+      <c r="AB48" s="57" t="n"/>
+      <c r="AC48" s="57" t="n"/>
+      <c r="AD48" s="57" t="n"/>
+      <c r="AE48" s="57" t="n"/>
+      <c r="AF48" s="57" t="n"/>
+      <c r="AG48" s="57" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="B49" s="43" t="inlineStr">
+        <is>
+          <t>Breacher</t>
+        </is>
+      </c>
+      <c r="C49" s="43" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="D49" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E49" s="43" t="inlineStr">
+        <is>
+          <t>Frag Shells</t>
+        </is>
+      </c>
+      <c r="F49" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D49-1),0)</f>
+        <v/>
+      </c>
+      <c r="G49" s="57" t="n"/>
+      <c r="H49" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I49" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J49" s="57" t="n"/>
+      <c r="K49" s="57" t="n"/>
+      <c r="L49" s="57" t="n"/>
+      <c r="M49" s="57" t="n"/>
+      <c r="N49" s="57" t="n"/>
+      <c r="O49" s="57" t="n"/>
+      <c r="P49" s="57" t="n"/>
+      <c r="Q49" s="57" t="n"/>
+      <c r="R49" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="S49" s="57" t="n"/>
+      <c r="T49" s="57" t="n"/>
+      <c r="U49" s="57" t="n"/>
+      <c r="V49" s="57" t="n"/>
+      <c r="W49" s="57" t="n"/>
+      <c r="X49" s="57" t="n"/>
+      <c r="Y49" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z49" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA49" s="57" t="n"/>
+      <c r="AB49" s="57" t="n"/>
+      <c r="AC49" s="57" t="n"/>
+      <c r="AD49" s="57" t="n"/>
+      <c r="AE49" s="57" t="n"/>
+      <c r="AF49" s="57" t="n"/>
+      <c r="AG49" s="57" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12758,7 +15312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13425,7 +15979,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16444,221 +18998,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" style="90" min="1" max="1"/>
-    <col width="11" customWidth="1" style="90" min="2" max="2"/>
-    <col width="13" customWidth="1" style="90" min="3" max="3"/>
-    <col width="13" customWidth="1" style="90" min="4" max="4"/>
-    <col width="14" customWidth="1" style="90" min="5" max="5"/>
-    <col width="9" customWidth="1" style="90" min="6" max="6"/>
-    <col width="13" customWidth="1" style="90" min="7" max="7"/>
-    <col width="40" customWidth="1" style="90" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>DIFFICULTY — Easy is the baseline; every other level scales from it</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Chosen before round 1. Player-count scaling (Tuning, CO-OP) applies on top.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>Enemy HP x</t>
-        </is>
-      </c>
-      <c r="C4" s="21" t="inlineStr">
-        <is>
-          <t>Enemy count x</t>
-        </is>
-      </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>Enemy speed x</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>Promote chance</t>
-        </is>
-      </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t>Cash x</t>
-        </is>
-      </c>
-      <c r="G4" s="21" t="inlineStr">
-        <is>
-          <t>Starting lives</t>
-        </is>
-      </c>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="43" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>40</v>
-      </c>
-      <c r="H5" s="47" t="inlineStr">
-        <is>
-          <t>The baseline. Current balance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="43" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="B6" s="27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" s="47" t="inlineStr">
-        <is>
-          <t>10% of enemies spawn one tier tougher.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="B7" s="27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="H7" s="47" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="inlineStr">
-        <is>
-          <t>Chaos</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="H8" s="47" t="inlineStr">
-        <is>
-          <t>Meant for big lobbies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Enemy count x raises density: the round's spawn gap shrinks by the same factor, so rounds get busier, not longer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Promote chance: each spawn has this chance to become the next ground tier up (Husk &gt; Brute &gt; Shielded &gt; Armored &gt; Storm). Air and bosses are never promoted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Cash x scales kill income and the round bonus.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -4182,7 +4182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -5077,6 +5077,56 @@
       <c r="D52" s="29" t="inlineStr">
         <is>
           <t>Time between calling an Airburst and the strike landing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="31" t="inlineStr">
+        <is>
+          <t>QUARTERMASTER / CHILLER</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="n"/>
+      <c r="C54" s="32" t="n"/>
+      <c r="D54" s="32" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="26" t="inlineStr">
+        <is>
+          <t>Chest lifetime</t>
+        </is>
+      </c>
+      <c r="B55" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="C55" s="28" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D55" s="29" t="inlineStr">
+        <is>
+          <t>Airdrop chests vanish if nobody collects them in time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="26" t="inlineStr">
+        <is>
+          <t>Chest spread</t>
+        </is>
+      </c>
+      <c r="B56" s="30" t="n">
+        <v>25</v>
+      </c>
+      <c r="C56" s="28" t="inlineStr">
+        <is>
+          <t>studs</t>
+        </is>
+      </c>
+      <c r="D56" s="29" t="inlineStr">
+        <is>
+          <t>Chests land this far around their Quartermaster at most.</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -5229,6 +5279,11 @@
           <t>Splash radius (m)</t>
         </is>
       </c>
+      <c r="M4" s="21" t="inlineStr">
+        <is>
+          <t>Slow %</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -5276,6 +5331,9 @@
       <c r="L5" s="27" t="n">
         <v>0</v>
       </c>
+      <c r="M5" s="27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="13.65" customHeight="1" s="90">
       <c r="A6" s="43" t="inlineStr">
@@ -5323,6 +5381,9 @@
       <c r="L6" s="27" t="n">
         <v>0</v>
       </c>
+      <c r="M6" s="27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="13.65" customHeight="1" s="90">
       <c r="A7" s="43" t="inlineStr">
@@ -5370,6 +5431,9 @@
       <c r="L7" s="27" t="n">
         <v>6</v>
       </c>
+      <c r="M7" s="27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="13.65" customHeight="1" s="90">
       <c r="A8" s="43" t="inlineStr">
@@ -5417,6 +5481,9 @@
       <c r="L8" s="27" t="n">
         <v>6</v>
       </c>
+      <c r="M8" s="27" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
       <c r="A9" s="43" t="inlineStr">
@@ -5446,7 +5513,7 @@
         <v/>
       </c>
       <c r="H9" s="27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I9" s="46" t="inlineStr">
         <is>
@@ -5462,6 +5529,9 @@
         </is>
       </c>
       <c r="L9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5524,7 +5594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD79"/>
+  <dimension ref="A1:AT79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -5541,7 +5611,22 @@
     <col width="10" customWidth="1" style="81" min="12" max="12"/>
     <col width="22" customWidth="1" style="81" min="13" max="13"/>
     <col width="12" customWidth="1" style="81" min="14" max="30"/>
-    <col width="8.67188" customWidth="1" style="81" min="31" max="16384"/>
+    <col width="12" customWidth="1" style="81" min="31" max="16384"/>
+    <col width="12" customWidth="1" style="90" min="32" max="32"/>
+    <col width="12" customWidth="1" style="90" min="33" max="33"/>
+    <col width="12" customWidth="1" style="90" min="34" max="34"/>
+    <col width="12" customWidth="1" style="90" min="35" max="35"/>
+    <col width="12" customWidth="1" style="90" min="36" max="36"/>
+    <col width="12" customWidth="1" style="90" min="37" max="37"/>
+    <col width="12" customWidth="1" style="90" min="38" max="38"/>
+    <col width="12" customWidth="1" style="90" min="39" max="39"/>
+    <col width="12" customWidth="1" style="90" min="40" max="40"/>
+    <col width="12" customWidth="1" style="90" min="41" max="41"/>
+    <col width="12" customWidth="1" style="90" min="42" max="42"/>
+    <col width="12" customWidth="1" style="90" min="43" max="43"/>
+    <col width="12" customWidth="1" style="90" min="44" max="44"/>
+    <col width="12" customWidth="1" style="90" min="45" max="45"/>
+    <col width="12" customWidth="1" style="90" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.5" customHeight="1" s="90">
@@ -5799,6 +5884,86 @@
           <t>Aura pierces armour</t>
         </is>
       </c>
+      <c r="AE4" s="21" t="inlineStr">
+        <is>
+          <t>Slow %</t>
+        </is>
+      </c>
+      <c r="AF4" s="21" t="inlineStr">
+        <is>
+          <t>Slow linger (s)</t>
+        </is>
+      </c>
+      <c r="AG4" s="21" t="inlineStr">
+        <is>
+          <t>Slows bosses</t>
+        </is>
+      </c>
+      <c r="AH4" s="21" t="inlineStr">
+        <is>
+          <t>Freeze every (s)</t>
+        </is>
+      </c>
+      <c r="AI4" s="21" t="inlineStr">
+        <is>
+          <t>Freeze (s)</t>
+        </is>
+      </c>
+      <c r="AJ4" s="21" t="inlineStr">
+        <is>
+          <t>Freeze damage</t>
+        </is>
+      </c>
+      <c r="AK4" s="21" t="inlineStr">
+        <is>
+          <t>Freeze holds bosses</t>
+        </is>
+      </c>
+      <c r="AL4" s="21" t="inlineStr">
+        <is>
+          <t>Brittle %</t>
+        </is>
+      </c>
+      <c r="AM4" s="21" t="inlineStr">
+        <is>
+          <t>Strips armour</t>
+        </is>
+      </c>
+      <c r="AN4" s="21" t="inlineStr">
+        <is>
+          <t>Income x</t>
+        </is>
+      </c>
+      <c r="AO4" s="21" t="inlineStr">
+        <is>
+          <t>Interest %</t>
+        </is>
+      </c>
+      <c r="AP4" s="21" t="inlineStr">
+        <is>
+          <t>Interest cap</t>
+        </is>
+      </c>
+      <c r="AQ4" s="21" t="inlineStr">
+        <is>
+          <t>Chests</t>
+        </is>
+      </c>
+      <c r="AR4" s="21" t="inlineStr">
+        <is>
+          <t>Chest cash</t>
+        </is>
+      </c>
+      <c r="AS4" s="21" t="inlineStr">
+        <is>
+          <t>Upgrade discount %</t>
+        </is>
+      </c>
+      <c r="AT4" s="21" t="inlineStr">
+        <is>
+          <t>Sell refund</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -5869,6 +6034,22 @@
       <c r="AB5" s="57" t="n"/>
       <c r="AC5" s="57" t="n"/>
       <c r="AD5" s="57" t="n"/>
+      <c r="AE5" s="57" t="n"/>
+      <c r="AF5" s="57" t="n"/>
+      <c r="AG5" s="57" t="n"/>
+      <c r="AH5" s="57" t="n"/>
+      <c r="AI5" s="57" t="n"/>
+      <c r="AJ5" s="57" t="n"/>
+      <c r="AK5" s="57" t="n"/>
+      <c r="AL5" s="57" t="n"/>
+      <c r="AM5" s="57" t="n"/>
+      <c r="AN5" s="57" t="n"/>
+      <c r="AO5" s="57" t="n"/>
+      <c r="AP5" s="57" t="n"/>
+      <c r="AQ5" s="57" t="n"/>
+      <c r="AR5" s="57" t="n"/>
+      <c r="AS5" s="57" t="n"/>
+      <c r="AT5" s="57" t="n"/>
     </row>
     <row r="6" ht="13.65" customHeight="1" s="90">
       <c r="A6" s="43" t="inlineStr">
@@ -5939,6 +6120,22 @@
       <c r="AB6" s="57" t="n"/>
       <c r="AC6" s="57" t="n"/>
       <c r="AD6" s="57" t="n"/>
+      <c r="AE6" s="57" t="n"/>
+      <c r="AF6" s="57" t="n"/>
+      <c r="AG6" s="57" t="n"/>
+      <c r="AH6" s="57" t="n"/>
+      <c r="AI6" s="57" t="n"/>
+      <c r="AJ6" s="57" t="n"/>
+      <c r="AK6" s="57" t="n"/>
+      <c r="AL6" s="57" t="n"/>
+      <c r="AM6" s="57" t="n"/>
+      <c r="AN6" s="57" t="n"/>
+      <c r="AO6" s="57" t="n"/>
+      <c r="AP6" s="57" t="n"/>
+      <c r="AQ6" s="57" t="n"/>
+      <c r="AR6" s="57" t="n"/>
+      <c r="AS6" s="57" t="n"/>
+      <c r="AT6" s="57" t="n"/>
     </row>
     <row r="7" ht="13.65" customHeight="1" s="90">
       <c r="A7" s="43" t="inlineStr">
@@ -6011,6 +6208,22 @@
       </c>
       <c r="AC7" s="57" t="n"/>
       <c r="AD7" s="57" t="n"/>
+      <c r="AE7" s="57" t="n"/>
+      <c r="AF7" s="57" t="n"/>
+      <c r="AG7" s="57" t="n"/>
+      <c r="AH7" s="57" t="n"/>
+      <c r="AI7" s="57" t="n"/>
+      <c r="AJ7" s="57" t="n"/>
+      <c r="AK7" s="57" t="n"/>
+      <c r="AL7" s="57" t="n"/>
+      <c r="AM7" s="57" t="n"/>
+      <c r="AN7" s="57" t="n"/>
+      <c r="AO7" s="57" t="n"/>
+      <c r="AP7" s="57" t="n"/>
+      <c r="AQ7" s="57" t="n"/>
+      <c r="AR7" s="57" t="n"/>
+      <c r="AS7" s="57" t="n"/>
+      <c r="AT7" s="57" t="n"/>
     </row>
     <row r="8" ht="13.65" customHeight="1" s="90">
       <c r="A8" s="43" t="inlineStr">
@@ -6083,6 +6296,22 @@
       </c>
       <c r="AC8" s="57" t="n"/>
       <c r="AD8" s="57" t="n"/>
+      <c r="AE8" s="57" t="n"/>
+      <c r="AF8" s="57" t="n"/>
+      <c r="AG8" s="57" t="n"/>
+      <c r="AH8" s="57" t="n"/>
+      <c r="AI8" s="57" t="n"/>
+      <c r="AJ8" s="57" t="n"/>
+      <c r="AK8" s="57" t="n"/>
+      <c r="AL8" s="57" t="n"/>
+      <c r="AM8" s="57" t="n"/>
+      <c r="AN8" s="57" t="n"/>
+      <c r="AO8" s="57" t="n"/>
+      <c r="AP8" s="57" t="n"/>
+      <c r="AQ8" s="57" t="n"/>
+      <c r="AR8" s="57" t="n"/>
+      <c r="AS8" s="57" t="n"/>
+      <c r="AT8" s="57" t="n"/>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
       <c r="A9" s="43" t="inlineStr">
@@ -6161,6 +6390,22 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AE9" s="57" t="n"/>
+      <c r="AF9" s="57" t="n"/>
+      <c r="AG9" s="57" t="n"/>
+      <c r="AH9" s="57" t="n"/>
+      <c r="AI9" s="57" t="n"/>
+      <c r="AJ9" s="57" t="n"/>
+      <c r="AK9" s="57" t="n"/>
+      <c r="AL9" s="57" t="n"/>
+      <c r="AM9" s="57" t="n"/>
+      <c r="AN9" s="57" t="n"/>
+      <c r="AO9" s="57" t="n"/>
+      <c r="AP9" s="57" t="n"/>
+      <c r="AQ9" s="57" t="n"/>
+      <c r="AR9" s="57" t="n"/>
+      <c r="AS9" s="57" t="n"/>
+      <c r="AT9" s="57" t="n"/>
     </row>
     <row r="10" ht="13.65" customHeight="1" s="90">
       <c r="A10" s="43" t="inlineStr">
@@ -6231,6 +6476,22 @@
       <c r="AB10" s="57" t="n"/>
       <c r="AC10" s="57" t="n"/>
       <c r="AD10" s="57" t="n"/>
+      <c r="AE10" s="57" t="n"/>
+      <c r="AF10" s="57" t="n"/>
+      <c r="AG10" s="57" t="n"/>
+      <c r="AH10" s="57" t="n"/>
+      <c r="AI10" s="57" t="n"/>
+      <c r="AJ10" s="57" t="n"/>
+      <c r="AK10" s="57" t="n"/>
+      <c r="AL10" s="57" t="n"/>
+      <c r="AM10" s="57" t="n"/>
+      <c r="AN10" s="57" t="n"/>
+      <c r="AO10" s="57" t="n"/>
+      <c r="AP10" s="57" t="n"/>
+      <c r="AQ10" s="57" t="n"/>
+      <c r="AR10" s="57" t="n"/>
+      <c r="AS10" s="57" t="n"/>
+      <c r="AT10" s="57" t="n"/>
     </row>
     <row r="11" ht="13.65" customHeight="1" s="90">
       <c r="A11" s="43" t="inlineStr">
@@ -6301,6 +6562,22 @@
       <c r="AB11" s="57" t="n"/>
       <c r="AC11" s="57" t="n"/>
       <c r="AD11" s="57" t="n"/>
+      <c r="AE11" s="57" t="n"/>
+      <c r="AF11" s="57" t="n"/>
+      <c r="AG11" s="57" t="n"/>
+      <c r="AH11" s="57" t="n"/>
+      <c r="AI11" s="57" t="n"/>
+      <c r="AJ11" s="57" t="n"/>
+      <c r="AK11" s="57" t="n"/>
+      <c r="AL11" s="57" t="n"/>
+      <c r="AM11" s="57" t="n"/>
+      <c r="AN11" s="57" t="n"/>
+      <c r="AO11" s="57" t="n"/>
+      <c r="AP11" s="57" t="n"/>
+      <c r="AQ11" s="57" t="n"/>
+      <c r="AR11" s="57" t="n"/>
+      <c r="AS11" s="57" t="n"/>
+      <c r="AT11" s="57" t="n"/>
     </row>
     <row r="12" ht="13.65" customHeight="1" s="90">
       <c r="A12" s="43" t="inlineStr">
@@ -6373,6 +6650,22 @@
       <c r="AB12" s="57" t="n"/>
       <c r="AC12" s="57" t="n"/>
       <c r="AD12" s="57" t="n"/>
+      <c r="AE12" s="57" t="n"/>
+      <c r="AF12" s="57" t="n"/>
+      <c r="AG12" s="57" t="n"/>
+      <c r="AH12" s="57" t="n"/>
+      <c r="AI12" s="57" t="n"/>
+      <c r="AJ12" s="57" t="n"/>
+      <c r="AK12" s="57" t="n"/>
+      <c r="AL12" s="57" t="n"/>
+      <c r="AM12" s="57" t="n"/>
+      <c r="AN12" s="57" t="n"/>
+      <c r="AO12" s="57" t="n"/>
+      <c r="AP12" s="57" t="n"/>
+      <c r="AQ12" s="57" t="n"/>
+      <c r="AR12" s="57" t="n"/>
+      <c r="AS12" s="57" t="n"/>
+      <c r="AT12" s="57" t="n"/>
     </row>
     <row r="13" ht="13.65" customHeight="1" s="90">
       <c r="A13" s="43" t="inlineStr">
@@ -6445,6 +6738,22 @@
       <c r="AB13" s="57" t="n"/>
       <c r="AC13" s="57" t="n"/>
       <c r="AD13" s="57" t="n"/>
+      <c r="AE13" s="57" t="n"/>
+      <c r="AF13" s="57" t="n"/>
+      <c r="AG13" s="57" t="n"/>
+      <c r="AH13" s="57" t="n"/>
+      <c r="AI13" s="57" t="n"/>
+      <c r="AJ13" s="57" t="n"/>
+      <c r="AK13" s="57" t="n"/>
+      <c r="AL13" s="57" t="n"/>
+      <c r="AM13" s="57" t="n"/>
+      <c r="AN13" s="57" t="n"/>
+      <c r="AO13" s="57" t="n"/>
+      <c r="AP13" s="57" t="n"/>
+      <c r="AQ13" s="57" t="n"/>
+      <c r="AR13" s="57" t="n"/>
+      <c r="AS13" s="57" t="n"/>
+      <c r="AT13" s="57" t="n"/>
     </row>
     <row r="14" ht="13.65" customHeight="1" s="90">
       <c r="A14" s="43" t="inlineStr">
@@ -6517,6 +6826,22 @@
       <c r="AB14" s="57" t="n"/>
       <c r="AC14" s="57" t="n"/>
       <c r="AD14" s="57" t="n"/>
+      <c r="AE14" s="57" t="n"/>
+      <c r="AF14" s="57" t="n"/>
+      <c r="AG14" s="57" t="n"/>
+      <c r="AH14" s="57" t="n"/>
+      <c r="AI14" s="57" t="n"/>
+      <c r="AJ14" s="57" t="n"/>
+      <c r="AK14" s="57" t="n"/>
+      <c r="AL14" s="57" t="n"/>
+      <c r="AM14" s="57" t="n"/>
+      <c r="AN14" s="57" t="n"/>
+      <c r="AO14" s="57" t="n"/>
+      <c r="AP14" s="57" t="n"/>
+      <c r="AQ14" s="57" t="n"/>
+      <c r="AR14" s="57" t="n"/>
+      <c r="AS14" s="57" t="n"/>
+      <c r="AT14" s="57" t="n"/>
     </row>
     <row r="15" ht="13.65" customHeight="1" s="90">
       <c r="A15" s="43" t="inlineStr">
@@ -6587,6 +6912,22 @@
       <c r="AB15" s="57" t="n"/>
       <c r="AC15" s="57" t="n"/>
       <c r="AD15" s="57" t="n"/>
+      <c r="AE15" s="57" t="n"/>
+      <c r="AF15" s="57" t="n"/>
+      <c r="AG15" s="57" t="n"/>
+      <c r="AH15" s="57" t="n"/>
+      <c r="AI15" s="57" t="n"/>
+      <c r="AJ15" s="57" t="n"/>
+      <c r="AK15" s="57" t="n"/>
+      <c r="AL15" s="57" t="n"/>
+      <c r="AM15" s="57" t="n"/>
+      <c r="AN15" s="57" t="n"/>
+      <c r="AO15" s="57" t="n"/>
+      <c r="AP15" s="57" t="n"/>
+      <c r="AQ15" s="57" t="n"/>
+      <c r="AR15" s="57" t="n"/>
+      <c r="AS15" s="57" t="n"/>
+      <c r="AT15" s="57" t="n"/>
     </row>
     <row r="16" ht="13.65" customHeight="1" s="90">
       <c r="A16" s="43" t="inlineStr">
@@ -6661,6 +7002,22 @@
       <c r="AB16" s="57" t="n"/>
       <c r="AC16" s="57" t="n"/>
       <c r="AD16" s="57" t="n"/>
+      <c r="AE16" s="57" t="n"/>
+      <c r="AF16" s="57" t="n"/>
+      <c r="AG16" s="57" t="n"/>
+      <c r="AH16" s="57" t="n"/>
+      <c r="AI16" s="57" t="n"/>
+      <c r="AJ16" s="57" t="n"/>
+      <c r="AK16" s="57" t="n"/>
+      <c r="AL16" s="57" t="n"/>
+      <c r="AM16" s="57" t="n"/>
+      <c r="AN16" s="57" t="n"/>
+      <c r="AO16" s="57" t="n"/>
+      <c r="AP16" s="57" t="n"/>
+      <c r="AQ16" s="57" t="n"/>
+      <c r="AR16" s="57" t="n"/>
+      <c r="AS16" s="57" t="n"/>
+      <c r="AT16" s="57" t="n"/>
     </row>
     <row r="17" ht="13.65" customHeight="1" s="90">
       <c r="A17" s="43" t="inlineStr">
@@ -6737,6 +7094,22 @@
       <c r="AB17" s="57" t="n"/>
       <c r="AC17" s="57" t="n"/>
       <c r="AD17" s="57" t="n"/>
+      <c r="AE17" s="57" t="n"/>
+      <c r="AF17" s="57" t="n"/>
+      <c r="AG17" s="57" t="n"/>
+      <c r="AH17" s="57" t="n"/>
+      <c r="AI17" s="57" t="n"/>
+      <c r="AJ17" s="57" t="n"/>
+      <c r="AK17" s="57" t="n"/>
+      <c r="AL17" s="57" t="n"/>
+      <c r="AM17" s="57" t="n"/>
+      <c r="AN17" s="57" t="n"/>
+      <c r="AO17" s="57" t="n"/>
+      <c r="AP17" s="57" t="n"/>
+      <c r="AQ17" s="57" t="n"/>
+      <c r="AR17" s="57" t="n"/>
+      <c r="AS17" s="57" t="n"/>
+      <c r="AT17" s="57" t="n"/>
     </row>
     <row r="18" ht="13.65" customHeight="1" s="90">
       <c r="A18" s="43" t="inlineStr">
@@ -6815,6 +7188,22 @@
       <c r="AB18" s="57" t="n"/>
       <c r="AC18" s="57" t="n"/>
       <c r="AD18" s="57" t="n"/>
+      <c r="AE18" s="57" t="n"/>
+      <c r="AF18" s="57" t="n"/>
+      <c r="AG18" s="57" t="n"/>
+      <c r="AH18" s="57" t="n"/>
+      <c r="AI18" s="57" t="n"/>
+      <c r="AJ18" s="57" t="n"/>
+      <c r="AK18" s="57" t="n"/>
+      <c r="AL18" s="57" t="n"/>
+      <c r="AM18" s="57" t="n"/>
+      <c r="AN18" s="57" t="n"/>
+      <c r="AO18" s="57" t="n"/>
+      <c r="AP18" s="57" t="n"/>
+      <c r="AQ18" s="57" t="n"/>
+      <c r="AR18" s="57" t="n"/>
+      <c r="AS18" s="57" t="n"/>
+      <c r="AT18" s="57" t="n"/>
     </row>
     <row r="19" ht="13.65" customHeight="1" s="90">
       <c r="A19" s="43" t="inlineStr">
@@ -6895,6 +7284,22 @@
       <c r="AB19" s="57" t="n"/>
       <c r="AC19" s="57" t="n"/>
       <c r="AD19" s="57" t="n"/>
+      <c r="AE19" s="57" t="n"/>
+      <c r="AF19" s="57" t="n"/>
+      <c r="AG19" s="57" t="n"/>
+      <c r="AH19" s="57" t="n"/>
+      <c r="AI19" s="57" t="n"/>
+      <c r="AJ19" s="57" t="n"/>
+      <c r="AK19" s="57" t="n"/>
+      <c r="AL19" s="57" t="n"/>
+      <c r="AM19" s="57" t="n"/>
+      <c r="AN19" s="57" t="n"/>
+      <c r="AO19" s="57" t="n"/>
+      <c r="AP19" s="57" t="n"/>
+      <c r="AQ19" s="57" t="n"/>
+      <c r="AR19" s="57" t="n"/>
+      <c r="AS19" s="57" t="n"/>
+      <c r="AT19" s="57" t="n"/>
     </row>
     <row r="20" ht="13.65" customHeight="1" s="90">
       <c r="A20" s="43" t="inlineStr">
@@ -6967,6 +7372,22 @@
       <c r="AB20" s="57" t="n"/>
       <c r="AC20" s="57" t="n"/>
       <c r="AD20" s="57" t="n"/>
+      <c r="AE20" s="57" t="n"/>
+      <c r="AF20" s="57" t="n"/>
+      <c r="AG20" s="57" t="n"/>
+      <c r="AH20" s="57" t="n"/>
+      <c r="AI20" s="57" t="n"/>
+      <c r="AJ20" s="57" t="n"/>
+      <c r="AK20" s="57" t="n"/>
+      <c r="AL20" s="57" t="n"/>
+      <c r="AM20" s="57" t="n"/>
+      <c r="AN20" s="57" t="n"/>
+      <c r="AO20" s="57" t="n"/>
+      <c r="AP20" s="57" t="n"/>
+      <c r="AQ20" s="57" t="n"/>
+      <c r="AR20" s="57" t="n"/>
+      <c r="AS20" s="57" t="n"/>
+      <c r="AT20" s="57" t="n"/>
     </row>
     <row r="21" ht="13.65" customHeight="1" s="90">
       <c r="A21" s="43" t="inlineStr">
@@ -7043,6 +7464,22 @@
       <c r="AB21" s="57" t="n"/>
       <c r="AC21" s="57" t="n"/>
       <c r="AD21" s="57" t="n"/>
+      <c r="AE21" s="57" t="n"/>
+      <c r="AF21" s="57" t="n"/>
+      <c r="AG21" s="57" t="n"/>
+      <c r="AH21" s="57" t="n"/>
+      <c r="AI21" s="57" t="n"/>
+      <c r="AJ21" s="57" t="n"/>
+      <c r="AK21" s="57" t="n"/>
+      <c r="AL21" s="57" t="n"/>
+      <c r="AM21" s="57" t="n"/>
+      <c r="AN21" s="57" t="n"/>
+      <c r="AO21" s="57" t="n"/>
+      <c r="AP21" s="57" t="n"/>
+      <c r="AQ21" s="57" t="n"/>
+      <c r="AR21" s="57" t="n"/>
+      <c r="AS21" s="57" t="n"/>
+      <c r="AT21" s="57" t="n"/>
     </row>
     <row r="22" ht="13.65" customHeight="1" s="90">
       <c r="A22" s="43" t="inlineStr">
@@ -7119,6 +7556,22 @@
       <c r="AB22" s="57" t="n"/>
       <c r="AC22" s="57" t="n"/>
       <c r="AD22" s="57" t="n"/>
+      <c r="AE22" s="57" t="n"/>
+      <c r="AF22" s="57" t="n"/>
+      <c r="AG22" s="57" t="n"/>
+      <c r="AH22" s="57" t="n"/>
+      <c r="AI22" s="57" t="n"/>
+      <c r="AJ22" s="57" t="n"/>
+      <c r="AK22" s="57" t="n"/>
+      <c r="AL22" s="57" t="n"/>
+      <c r="AM22" s="57" t="n"/>
+      <c r="AN22" s="57" t="n"/>
+      <c r="AO22" s="57" t="n"/>
+      <c r="AP22" s="57" t="n"/>
+      <c r="AQ22" s="57" t="n"/>
+      <c r="AR22" s="57" t="n"/>
+      <c r="AS22" s="57" t="n"/>
+      <c r="AT22" s="57" t="n"/>
     </row>
     <row r="23" ht="13.65" customHeight="1" s="90">
       <c r="A23" s="43" t="inlineStr">
@@ -7195,6 +7648,22 @@
       <c r="AB23" s="57" t="n"/>
       <c r="AC23" s="57" t="n"/>
       <c r="AD23" s="57" t="n"/>
+      <c r="AE23" s="57" t="n"/>
+      <c r="AF23" s="57" t="n"/>
+      <c r="AG23" s="57" t="n"/>
+      <c r="AH23" s="57" t="n"/>
+      <c r="AI23" s="57" t="n"/>
+      <c r="AJ23" s="57" t="n"/>
+      <c r="AK23" s="57" t="n"/>
+      <c r="AL23" s="57" t="n"/>
+      <c r="AM23" s="57" t="n"/>
+      <c r="AN23" s="57" t="n"/>
+      <c r="AO23" s="57" t="n"/>
+      <c r="AP23" s="57" t="n"/>
+      <c r="AQ23" s="57" t="n"/>
+      <c r="AR23" s="57" t="n"/>
+      <c r="AS23" s="57" t="n"/>
+      <c r="AT23" s="57" t="n"/>
     </row>
     <row r="24" ht="13.65" customHeight="1" s="90">
       <c r="A24" s="43" t="inlineStr">
@@ -7271,6 +7740,22 @@
       <c r="AB24" s="57" t="n"/>
       <c r="AC24" s="57" t="n"/>
       <c r="AD24" s="57" t="n"/>
+      <c r="AE24" s="57" t="n"/>
+      <c r="AF24" s="57" t="n"/>
+      <c r="AG24" s="57" t="n"/>
+      <c r="AH24" s="57" t="n"/>
+      <c r="AI24" s="57" t="n"/>
+      <c r="AJ24" s="57" t="n"/>
+      <c r="AK24" s="57" t="n"/>
+      <c r="AL24" s="57" t="n"/>
+      <c r="AM24" s="57" t="n"/>
+      <c r="AN24" s="57" t="n"/>
+      <c r="AO24" s="57" t="n"/>
+      <c r="AP24" s="57" t="n"/>
+      <c r="AQ24" s="57" t="n"/>
+      <c r="AR24" s="57" t="n"/>
+      <c r="AS24" s="57" t="n"/>
+      <c r="AT24" s="57" t="n"/>
     </row>
     <row r="25" ht="13.65" customHeight="1" s="90">
       <c r="A25" s="43" t="inlineStr">
@@ -7341,6 +7826,22 @@
       <c r="AB25" s="57" t="n"/>
       <c r="AC25" s="57" t="n"/>
       <c r="AD25" s="57" t="n"/>
+      <c r="AE25" s="57" t="n"/>
+      <c r="AF25" s="57" t="n"/>
+      <c r="AG25" s="57" t="n"/>
+      <c r="AH25" s="57" t="n"/>
+      <c r="AI25" s="57" t="n"/>
+      <c r="AJ25" s="57" t="n"/>
+      <c r="AK25" s="57" t="n"/>
+      <c r="AL25" s="57" t="n"/>
+      <c r="AM25" s="57" t="n"/>
+      <c r="AN25" s="57" t="n"/>
+      <c r="AO25" s="57" t="n"/>
+      <c r="AP25" s="57" t="n"/>
+      <c r="AQ25" s="57" t="n"/>
+      <c r="AR25" s="57" t="n"/>
+      <c r="AS25" s="57" t="n"/>
+      <c r="AT25" s="57" t="n"/>
     </row>
     <row r="26" ht="13.65" customHeight="1" s="90">
       <c r="A26" s="43" t="inlineStr">
@@ -7411,6 +7912,22 @@
       <c r="AB26" s="57" t="n"/>
       <c r="AC26" s="57" t="n"/>
       <c r="AD26" s="57" t="n"/>
+      <c r="AE26" s="57" t="n"/>
+      <c r="AF26" s="57" t="n"/>
+      <c r="AG26" s="57" t="n"/>
+      <c r="AH26" s="57" t="n"/>
+      <c r="AI26" s="57" t="n"/>
+      <c r="AJ26" s="57" t="n"/>
+      <c r="AK26" s="57" t="n"/>
+      <c r="AL26" s="57" t="n"/>
+      <c r="AM26" s="57" t="n"/>
+      <c r="AN26" s="57" t="n"/>
+      <c r="AO26" s="57" t="n"/>
+      <c r="AP26" s="57" t="n"/>
+      <c r="AQ26" s="57" t="n"/>
+      <c r="AR26" s="57" t="n"/>
+      <c r="AS26" s="57" t="n"/>
+      <c r="AT26" s="57" t="n"/>
     </row>
     <row r="27" ht="13.65" customHeight="1" s="90">
       <c r="A27" s="43" t="inlineStr">
@@ -7483,6 +8000,22 @@
       <c r="AB27" s="57" t="n"/>
       <c r="AC27" s="57" t="n"/>
       <c r="AD27" s="57" t="n"/>
+      <c r="AE27" s="57" t="n"/>
+      <c r="AF27" s="57" t="n"/>
+      <c r="AG27" s="57" t="n"/>
+      <c r="AH27" s="57" t="n"/>
+      <c r="AI27" s="57" t="n"/>
+      <c r="AJ27" s="57" t="n"/>
+      <c r="AK27" s="57" t="n"/>
+      <c r="AL27" s="57" t="n"/>
+      <c r="AM27" s="57" t="n"/>
+      <c r="AN27" s="57" t="n"/>
+      <c r="AO27" s="57" t="n"/>
+      <c r="AP27" s="57" t="n"/>
+      <c r="AQ27" s="57" t="n"/>
+      <c r="AR27" s="57" t="n"/>
+      <c r="AS27" s="57" t="n"/>
+      <c r="AT27" s="57" t="n"/>
     </row>
     <row r="28" ht="13.65" customHeight="1" s="90">
       <c r="A28" s="43" t="inlineStr">
@@ -7555,6 +8088,22 @@
       <c r="AB28" s="57" t="n"/>
       <c r="AC28" s="57" t="n"/>
       <c r="AD28" s="57" t="n"/>
+      <c r="AE28" s="57" t="n"/>
+      <c r="AF28" s="57" t="n"/>
+      <c r="AG28" s="57" t="n"/>
+      <c r="AH28" s="57" t="n"/>
+      <c r="AI28" s="57" t="n"/>
+      <c r="AJ28" s="57" t="n"/>
+      <c r="AK28" s="57" t="n"/>
+      <c r="AL28" s="57" t="n"/>
+      <c r="AM28" s="57" t="n"/>
+      <c r="AN28" s="57" t="n"/>
+      <c r="AO28" s="57" t="n"/>
+      <c r="AP28" s="57" t="n"/>
+      <c r="AQ28" s="57" t="n"/>
+      <c r="AR28" s="57" t="n"/>
+      <c r="AS28" s="57" t="n"/>
+      <c r="AT28" s="57" t="n"/>
     </row>
     <row r="29" ht="13.65" customHeight="1" s="90">
       <c r="A29" s="43" t="inlineStr">
@@ -7629,6 +8178,22 @@
       </c>
       <c r="AC29" s="57" t="n"/>
       <c r="AD29" s="57" t="n"/>
+      <c r="AE29" s="57" t="n"/>
+      <c r="AF29" s="57" t="n"/>
+      <c r="AG29" s="57" t="n"/>
+      <c r="AH29" s="57" t="n"/>
+      <c r="AI29" s="57" t="n"/>
+      <c r="AJ29" s="57" t="n"/>
+      <c r="AK29" s="57" t="n"/>
+      <c r="AL29" s="57" t="n"/>
+      <c r="AM29" s="57" t="n"/>
+      <c r="AN29" s="57" t="n"/>
+      <c r="AO29" s="57" t="n"/>
+      <c r="AP29" s="57" t="n"/>
+      <c r="AQ29" s="57" t="n"/>
+      <c r="AR29" s="57" t="n"/>
+      <c r="AS29" s="57" t="n"/>
+      <c r="AT29" s="57" t="n"/>
     </row>
     <row r="30" ht="13.65" customHeight="1" s="90">
       <c r="A30" s="43" t="inlineStr">
@@ -7699,6 +8264,22 @@
       <c r="AB30" s="57" t="n"/>
       <c r="AC30" s="57" t="n"/>
       <c r="AD30" s="57" t="n"/>
+      <c r="AE30" s="57" t="n"/>
+      <c r="AF30" s="57" t="n"/>
+      <c r="AG30" s="57" t="n"/>
+      <c r="AH30" s="57" t="n"/>
+      <c r="AI30" s="57" t="n"/>
+      <c r="AJ30" s="57" t="n"/>
+      <c r="AK30" s="57" t="n"/>
+      <c r="AL30" s="57" t="n"/>
+      <c r="AM30" s="57" t="n"/>
+      <c r="AN30" s="57" t="n"/>
+      <c r="AO30" s="57" t="n"/>
+      <c r="AP30" s="57" t="n"/>
+      <c r="AQ30" s="57" t="n"/>
+      <c r="AR30" s="57" t="n"/>
+      <c r="AS30" s="57" t="n"/>
+      <c r="AT30" s="57" t="n"/>
     </row>
     <row r="31" ht="13.65" customHeight="1" s="90">
       <c r="A31" s="43" t="inlineStr">
@@ -7771,6 +8352,22 @@
       <c r="AB31" s="57" t="n"/>
       <c r="AC31" s="57" t="n"/>
       <c r="AD31" s="57" t="n"/>
+      <c r="AE31" s="57" t="n"/>
+      <c r="AF31" s="57" t="n"/>
+      <c r="AG31" s="57" t="n"/>
+      <c r="AH31" s="57" t="n"/>
+      <c r="AI31" s="57" t="n"/>
+      <c r="AJ31" s="57" t="n"/>
+      <c r="AK31" s="57" t="n"/>
+      <c r="AL31" s="57" t="n"/>
+      <c r="AM31" s="57" t="n"/>
+      <c r="AN31" s="57" t="n"/>
+      <c r="AO31" s="57" t="n"/>
+      <c r="AP31" s="57" t="n"/>
+      <c r="AQ31" s="57" t="n"/>
+      <c r="AR31" s="57" t="n"/>
+      <c r="AS31" s="57" t="n"/>
+      <c r="AT31" s="57" t="n"/>
     </row>
     <row r="32" ht="13.65" customHeight="1" s="90">
       <c r="A32" s="43" t="inlineStr">
@@ -7845,6 +8442,22 @@
       <c r="AB32" s="57" t="n"/>
       <c r="AC32" s="57" t="n"/>
       <c r="AD32" s="57" t="n"/>
+      <c r="AE32" s="57" t="n"/>
+      <c r="AF32" s="57" t="n"/>
+      <c r="AG32" s="57" t="n"/>
+      <c r="AH32" s="57" t="n"/>
+      <c r="AI32" s="57" t="n"/>
+      <c r="AJ32" s="57" t="n"/>
+      <c r="AK32" s="57" t="n"/>
+      <c r="AL32" s="57" t="n"/>
+      <c r="AM32" s="57" t="n"/>
+      <c r="AN32" s="57" t="n"/>
+      <c r="AO32" s="57" t="n"/>
+      <c r="AP32" s="57" t="n"/>
+      <c r="AQ32" s="57" t="n"/>
+      <c r="AR32" s="57" t="n"/>
+      <c r="AS32" s="57" t="n"/>
+      <c r="AT32" s="57" t="n"/>
     </row>
     <row r="33" ht="13.65" customHeight="1" s="90">
       <c r="A33" s="43" t="inlineStr">
@@ -7919,6 +8532,22 @@
       <c r="AB33" s="57" t="n"/>
       <c r="AC33" s="57" t="n"/>
       <c r="AD33" s="57" t="n"/>
+      <c r="AE33" s="57" t="n"/>
+      <c r="AF33" s="57" t="n"/>
+      <c r="AG33" s="57" t="n"/>
+      <c r="AH33" s="57" t="n"/>
+      <c r="AI33" s="57" t="n"/>
+      <c r="AJ33" s="57" t="n"/>
+      <c r="AK33" s="57" t="n"/>
+      <c r="AL33" s="57" t="n"/>
+      <c r="AM33" s="57" t="n"/>
+      <c r="AN33" s="57" t="n"/>
+      <c r="AO33" s="57" t="n"/>
+      <c r="AP33" s="57" t="n"/>
+      <c r="AQ33" s="57" t="n"/>
+      <c r="AR33" s="57" t="n"/>
+      <c r="AS33" s="57" t="n"/>
+      <c r="AT33" s="57" t="n"/>
     </row>
     <row r="34" ht="13.65" customHeight="1" s="90">
       <c r="A34" s="43" t="inlineStr">
@@ -7997,6 +8626,22 @@
       <c r="AB34" s="57" t="n"/>
       <c r="AC34" s="57" t="n"/>
       <c r="AD34" s="57" t="n"/>
+      <c r="AE34" s="57" t="n"/>
+      <c r="AF34" s="57" t="n"/>
+      <c r="AG34" s="57" t="n"/>
+      <c r="AH34" s="57" t="n"/>
+      <c r="AI34" s="57" t="n"/>
+      <c r="AJ34" s="57" t="n"/>
+      <c r="AK34" s="57" t="n"/>
+      <c r="AL34" s="57" t="n"/>
+      <c r="AM34" s="57" t="n"/>
+      <c r="AN34" s="57" t="n"/>
+      <c r="AO34" s="57" t="n"/>
+      <c r="AP34" s="57" t="n"/>
+      <c r="AQ34" s="57" t="n"/>
+      <c r="AR34" s="57" t="n"/>
+      <c r="AS34" s="57" t="n"/>
+      <c r="AT34" s="57" t="n"/>
     </row>
     <row r="35" ht="13.65" customHeight="1" s="90">
       <c r="A35" s="43" t="inlineStr">
@@ -8069,6 +8714,22 @@
       <c r="AB35" s="57" t="n"/>
       <c r="AC35" s="57" t="n"/>
       <c r="AD35" s="57" t="n"/>
+      <c r="AE35" s="57" t="n"/>
+      <c r="AF35" s="57" t="n"/>
+      <c r="AG35" s="57" t="n"/>
+      <c r="AH35" s="57" t="n"/>
+      <c r="AI35" s="57" t="n"/>
+      <c r="AJ35" s="57" t="n"/>
+      <c r="AK35" s="57" t="n"/>
+      <c r="AL35" s="57" t="n"/>
+      <c r="AM35" s="57" t="n"/>
+      <c r="AN35" s="57" t="n"/>
+      <c r="AO35" s="57" t="n"/>
+      <c r="AP35" s="57" t="n"/>
+      <c r="AQ35" s="57" t="n"/>
+      <c r="AR35" s="57" t="n"/>
+      <c r="AS35" s="57" t="n"/>
+      <c r="AT35" s="57" t="n"/>
     </row>
     <row r="36" ht="13.65" customHeight="1" s="90">
       <c r="A36" s="43" t="inlineStr">
@@ -8141,6 +8802,22 @@
       <c r="AB36" s="57" t="n"/>
       <c r="AC36" s="57" t="n"/>
       <c r="AD36" s="57" t="n"/>
+      <c r="AE36" s="57" t="n"/>
+      <c r="AF36" s="57" t="n"/>
+      <c r="AG36" s="57" t="n"/>
+      <c r="AH36" s="57" t="n"/>
+      <c r="AI36" s="57" t="n"/>
+      <c r="AJ36" s="57" t="n"/>
+      <c r="AK36" s="57" t="n"/>
+      <c r="AL36" s="57" t="n"/>
+      <c r="AM36" s="57" t="n"/>
+      <c r="AN36" s="57" t="n"/>
+      <c r="AO36" s="57" t="n"/>
+      <c r="AP36" s="57" t="n"/>
+      <c r="AQ36" s="57" t="n"/>
+      <c r="AR36" s="57" t="n"/>
+      <c r="AS36" s="57" t="n"/>
+      <c r="AT36" s="57" t="n"/>
     </row>
     <row r="37" ht="13.65" customHeight="1" s="90">
       <c r="A37" s="43" t="inlineStr">
@@ -8217,6 +8894,22 @@
       <c r="AB37" s="57" t="n"/>
       <c r="AC37" s="57" t="n"/>
       <c r="AD37" s="57" t="n"/>
+      <c r="AE37" s="57" t="n"/>
+      <c r="AF37" s="57" t="n"/>
+      <c r="AG37" s="57" t="n"/>
+      <c r="AH37" s="57" t="n"/>
+      <c r="AI37" s="57" t="n"/>
+      <c r="AJ37" s="57" t="n"/>
+      <c r="AK37" s="57" t="n"/>
+      <c r="AL37" s="57" t="n"/>
+      <c r="AM37" s="57" t="n"/>
+      <c r="AN37" s="57" t="n"/>
+      <c r="AO37" s="57" t="n"/>
+      <c r="AP37" s="57" t="n"/>
+      <c r="AQ37" s="57" t="n"/>
+      <c r="AR37" s="57" t="n"/>
+      <c r="AS37" s="57" t="n"/>
+      <c r="AT37" s="57" t="n"/>
     </row>
     <row r="38" ht="13.65" customHeight="1" s="90">
       <c r="A38" s="43" t="inlineStr">
@@ -8293,6 +8986,22 @@
       <c r="AB38" s="57" t="n"/>
       <c r="AC38" s="57" t="n"/>
       <c r="AD38" s="57" t="n"/>
+      <c r="AE38" s="57" t="n"/>
+      <c r="AF38" s="57" t="n"/>
+      <c r="AG38" s="57" t="n"/>
+      <c r="AH38" s="57" t="n"/>
+      <c r="AI38" s="57" t="n"/>
+      <c r="AJ38" s="57" t="n"/>
+      <c r="AK38" s="57" t="n"/>
+      <c r="AL38" s="57" t="n"/>
+      <c r="AM38" s="57" t="n"/>
+      <c r="AN38" s="57" t="n"/>
+      <c r="AO38" s="57" t="n"/>
+      <c r="AP38" s="57" t="n"/>
+      <c r="AQ38" s="57" t="n"/>
+      <c r="AR38" s="57" t="n"/>
+      <c r="AS38" s="57" t="n"/>
+      <c r="AT38" s="57" t="n"/>
     </row>
     <row r="39" ht="13.65" customHeight="1" s="90">
       <c r="A39" s="43" t="inlineStr">
@@ -8369,6 +9078,22 @@
       <c r="AB39" s="57" t="n"/>
       <c r="AC39" s="57" t="n"/>
       <c r="AD39" s="57" t="n"/>
+      <c r="AE39" s="57" t="n"/>
+      <c r="AF39" s="57" t="n"/>
+      <c r="AG39" s="57" t="n"/>
+      <c r="AH39" s="57" t="n"/>
+      <c r="AI39" s="57" t="n"/>
+      <c r="AJ39" s="57" t="n"/>
+      <c r="AK39" s="57" t="n"/>
+      <c r="AL39" s="57" t="n"/>
+      <c r="AM39" s="57" t="n"/>
+      <c r="AN39" s="57" t="n"/>
+      <c r="AO39" s="57" t="n"/>
+      <c r="AP39" s="57" t="n"/>
+      <c r="AQ39" s="57" t="n"/>
+      <c r="AR39" s="57" t="n"/>
+      <c r="AS39" s="57" t="n"/>
+      <c r="AT39" s="57" t="n"/>
     </row>
     <row r="40" ht="13.65" customHeight="1" s="90">
       <c r="A40" s="43" t="inlineStr">
@@ -8443,6 +9168,22 @@
       <c r="AB40" s="57" t="n"/>
       <c r="AC40" s="57" t="n"/>
       <c r="AD40" s="57" t="n"/>
+      <c r="AE40" s="57" t="n"/>
+      <c r="AF40" s="57" t="n"/>
+      <c r="AG40" s="57" t="n"/>
+      <c r="AH40" s="57" t="n"/>
+      <c r="AI40" s="57" t="n"/>
+      <c r="AJ40" s="57" t="n"/>
+      <c r="AK40" s="57" t="n"/>
+      <c r="AL40" s="57" t="n"/>
+      <c r="AM40" s="57" t="n"/>
+      <c r="AN40" s="57" t="n"/>
+      <c r="AO40" s="57" t="n"/>
+      <c r="AP40" s="57" t="n"/>
+      <c r="AQ40" s="57" t="n"/>
+      <c r="AR40" s="57" t="n"/>
+      <c r="AS40" s="57" t="n"/>
+      <c r="AT40" s="57" t="n"/>
     </row>
     <row r="41" ht="13.65" customHeight="1" s="90">
       <c r="A41" s="43" t="inlineStr">
@@ -8517,6 +9258,22 @@
       <c r="AB41" s="57" t="n"/>
       <c r="AC41" s="57" t="n"/>
       <c r="AD41" s="57" t="n"/>
+      <c r="AE41" s="57" t="n"/>
+      <c r="AF41" s="57" t="n"/>
+      <c r="AG41" s="57" t="n"/>
+      <c r="AH41" s="57" t="n"/>
+      <c r="AI41" s="57" t="n"/>
+      <c r="AJ41" s="57" t="n"/>
+      <c r="AK41" s="57" t="n"/>
+      <c r="AL41" s="57" t="n"/>
+      <c r="AM41" s="57" t="n"/>
+      <c r="AN41" s="57" t="n"/>
+      <c r="AO41" s="57" t="n"/>
+      <c r="AP41" s="57" t="n"/>
+      <c r="AQ41" s="57" t="n"/>
+      <c r="AR41" s="57" t="n"/>
+      <c r="AS41" s="57" t="n"/>
+      <c r="AT41" s="57" t="n"/>
     </row>
     <row r="42" ht="13.65" customHeight="1" s="90">
       <c r="A42" s="43" t="inlineStr">
@@ -8591,6 +9348,22 @@
       <c r="AB42" s="57" t="n"/>
       <c r="AC42" s="57" t="n"/>
       <c r="AD42" s="57" t="n"/>
+      <c r="AE42" s="57" t="n"/>
+      <c r="AF42" s="57" t="n"/>
+      <c r="AG42" s="57" t="n"/>
+      <c r="AH42" s="57" t="n"/>
+      <c r="AI42" s="57" t="n"/>
+      <c r="AJ42" s="57" t="n"/>
+      <c r="AK42" s="57" t="n"/>
+      <c r="AL42" s="57" t="n"/>
+      <c r="AM42" s="57" t="n"/>
+      <c r="AN42" s="57" t="n"/>
+      <c r="AO42" s="57" t="n"/>
+      <c r="AP42" s="57" t="n"/>
+      <c r="AQ42" s="57" t="n"/>
+      <c r="AR42" s="57" t="n"/>
+      <c r="AS42" s="57" t="n"/>
+      <c r="AT42" s="57" t="n"/>
     </row>
     <row r="43" ht="13.65" customHeight="1" s="90">
       <c r="A43" s="43" t="inlineStr">
@@ -8665,6 +9438,22 @@
       <c r="AB43" s="57" t="n"/>
       <c r="AC43" s="57" t="n"/>
       <c r="AD43" s="57" t="n"/>
+      <c r="AE43" s="57" t="n"/>
+      <c r="AF43" s="57" t="n"/>
+      <c r="AG43" s="57" t="n"/>
+      <c r="AH43" s="57" t="n"/>
+      <c r="AI43" s="57" t="n"/>
+      <c r="AJ43" s="57" t="n"/>
+      <c r="AK43" s="57" t="n"/>
+      <c r="AL43" s="57" t="n"/>
+      <c r="AM43" s="57" t="n"/>
+      <c r="AN43" s="57" t="n"/>
+      <c r="AO43" s="57" t="n"/>
+      <c r="AP43" s="57" t="n"/>
+      <c r="AQ43" s="57" t="n"/>
+      <c r="AR43" s="57" t="n"/>
+      <c r="AS43" s="57" t="n"/>
+      <c r="AT43" s="57" t="n"/>
     </row>
     <row r="44" ht="13.65" customHeight="1" s="90">
       <c r="A44" s="43" t="inlineStr">
@@ -8739,6 +9528,22 @@
       <c r="AB44" s="57" t="n"/>
       <c r="AC44" s="57" t="n"/>
       <c r="AD44" s="57" t="n"/>
+      <c r="AE44" s="57" t="n"/>
+      <c r="AF44" s="57" t="n"/>
+      <c r="AG44" s="57" t="n"/>
+      <c r="AH44" s="57" t="n"/>
+      <c r="AI44" s="57" t="n"/>
+      <c r="AJ44" s="57" t="n"/>
+      <c r="AK44" s="57" t="n"/>
+      <c r="AL44" s="57" t="n"/>
+      <c r="AM44" s="57" t="n"/>
+      <c r="AN44" s="57" t="n"/>
+      <c r="AO44" s="57" t="n"/>
+      <c r="AP44" s="57" t="n"/>
+      <c r="AQ44" s="57" t="n"/>
+      <c r="AR44" s="57" t="n"/>
+      <c r="AS44" s="57" t="n"/>
+      <c r="AT44" s="57" t="n"/>
     </row>
     <row r="45" ht="13.65" customHeight="1" s="90">
       <c r="A45" s="43" t="inlineStr">
@@ -8811,6 +9616,22 @@
       <c r="AB45" s="57" t="n"/>
       <c r="AC45" s="57" t="n"/>
       <c r="AD45" s="57" t="n"/>
+      <c r="AE45" s="57" t="n"/>
+      <c r="AF45" s="57" t="n"/>
+      <c r="AG45" s="57" t="n"/>
+      <c r="AH45" s="57" t="n"/>
+      <c r="AI45" s="57" t="n"/>
+      <c r="AJ45" s="57" t="n"/>
+      <c r="AK45" s="57" t="n"/>
+      <c r="AL45" s="57" t="n"/>
+      <c r="AM45" s="57" t="n"/>
+      <c r="AN45" s="57" t="n"/>
+      <c r="AO45" s="57" t="n"/>
+      <c r="AP45" s="57" t="n"/>
+      <c r="AQ45" s="57" t="n"/>
+      <c r="AR45" s="57" t="n"/>
+      <c r="AS45" s="57" t="n"/>
+      <c r="AT45" s="57" t="n"/>
     </row>
     <row r="46" ht="13.65" customHeight="1" s="90">
       <c r="A46" s="43" t="inlineStr">
@@ -8889,6 +9710,22 @@
       <c r="AB46" s="57" t="n"/>
       <c r="AC46" s="57" t="n"/>
       <c r="AD46" s="57" t="n"/>
+      <c r="AE46" s="57" t="n"/>
+      <c r="AF46" s="57" t="n"/>
+      <c r="AG46" s="57" t="n"/>
+      <c r="AH46" s="57" t="n"/>
+      <c r="AI46" s="57" t="n"/>
+      <c r="AJ46" s="57" t="n"/>
+      <c r="AK46" s="57" t="n"/>
+      <c r="AL46" s="57" t="n"/>
+      <c r="AM46" s="57" t="n"/>
+      <c r="AN46" s="57" t="n"/>
+      <c r="AO46" s="57" t="n"/>
+      <c r="AP46" s="57" t="n"/>
+      <c r="AQ46" s="57" t="n"/>
+      <c r="AR46" s="57" t="n"/>
+      <c r="AS46" s="57" t="n"/>
+      <c r="AT46" s="57" t="n"/>
     </row>
     <row r="47" ht="13.65" customHeight="1" s="90">
       <c r="A47" s="43" t="inlineStr">
@@ -8969,6 +9806,22 @@
       <c r="AB47" s="57" t="n"/>
       <c r="AC47" s="57" t="n"/>
       <c r="AD47" s="57" t="n"/>
+      <c r="AE47" s="57" t="n"/>
+      <c r="AF47" s="57" t="n"/>
+      <c r="AG47" s="57" t="n"/>
+      <c r="AH47" s="57" t="n"/>
+      <c r="AI47" s="57" t="n"/>
+      <c r="AJ47" s="57" t="n"/>
+      <c r="AK47" s="57" t="n"/>
+      <c r="AL47" s="57" t="n"/>
+      <c r="AM47" s="57" t="n"/>
+      <c r="AN47" s="57" t="n"/>
+      <c r="AO47" s="57" t="n"/>
+      <c r="AP47" s="57" t="n"/>
+      <c r="AQ47" s="57" t="n"/>
+      <c r="AR47" s="57" t="n"/>
+      <c r="AS47" s="57" t="n"/>
+      <c r="AT47" s="57" t="n"/>
     </row>
     <row r="48" ht="13.65" customHeight="1" s="90">
       <c r="A48" s="43" t="inlineStr">
@@ -9049,6 +9902,22 @@
       <c r="AB48" s="57" t="n"/>
       <c r="AC48" s="57" t="n"/>
       <c r="AD48" s="57" t="n"/>
+      <c r="AE48" s="57" t="n"/>
+      <c r="AF48" s="57" t="n"/>
+      <c r="AG48" s="57" t="n"/>
+      <c r="AH48" s="57" t="n"/>
+      <c r="AI48" s="57" t="n"/>
+      <c r="AJ48" s="57" t="n"/>
+      <c r="AK48" s="57" t="n"/>
+      <c r="AL48" s="57" t="n"/>
+      <c r="AM48" s="57" t="n"/>
+      <c r="AN48" s="57" t="n"/>
+      <c r="AO48" s="57" t="n"/>
+      <c r="AP48" s="57" t="n"/>
+      <c r="AQ48" s="57" t="n"/>
+      <c r="AR48" s="57" t="n"/>
+      <c r="AS48" s="57" t="n"/>
+      <c r="AT48" s="57" t="n"/>
     </row>
     <row r="49" ht="13.65" customHeight="1" s="90">
       <c r="A49" s="43" t="inlineStr">
@@ -9129,6 +9998,22 @@
       <c r="AB49" s="57" t="n"/>
       <c r="AC49" s="57" t="n"/>
       <c r="AD49" s="57" t="n"/>
+      <c r="AE49" s="57" t="n"/>
+      <c r="AF49" s="57" t="n"/>
+      <c r="AG49" s="57" t="n"/>
+      <c r="AH49" s="57" t="n"/>
+      <c r="AI49" s="57" t="n"/>
+      <c r="AJ49" s="57" t="n"/>
+      <c r="AK49" s="57" t="n"/>
+      <c r="AL49" s="57" t="n"/>
+      <c r="AM49" s="57" t="n"/>
+      <c r="AN49" s="57" t="n"/>
+      <c r="AO49" s="57" t="n"/>
+      <c r="AP49" s="57" t="n"/>
+      <c r="AQ49" s="57" t="n"/>
+      <c r="AR49" s="57" t="n"/>
+      <c r="AS49" s="57" t="n"/>
+      <c r="AT49" s="57" t="n"/>
     </row>
     <row r="50" ht="13.65" customHeight="1" s="90">
       <c r="A50" s="43" t="inlineStr">
@@ -9199,6 +10084,24 @@
       <c r="AB50" s="57" t="n"/>
       <c r="AC50" s="57" t="n"/>
       <c r="AD50" s="57" t="n"/>
+      <c r="AE50" s="57" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF50" s="57" t="n"/>
+      <c r="AG50" s="57" t="n"/>
+      <c r="AH50" s="57" t="n"/>
+      <c r="AI50" s="57" t="n"/>
+      <c r="AJ50" s="57" t="n"/>
+      <c r="AK50" s="57" t="n"/>
+      <c r="AL50" s="57" t="n"/>
+      <c r="AM50" s="57" t="n"/>
+      <c r="AN50" s="57" t="n"/>
+      <c r="AO50" s="57" t="n"/>
+      <c r="AP50" s="57" t="n"/>
+      <c r="AQ50" s="57" t="n"/>
+      <c r="AR50" s="57" t="n"/>
+      <c r="AS50" s="57" t="n"/>
+      <c r="AT50" s="57" t="n"/>
     </row>
     <row r="51" ht="13.65" customHeight="1" s="90">
       <c r="A51" s="43" t="inlineStr">
@@ -9269,6 +10172,24 @@
       <c r="AB51" s="57" t="n"/>
       <c r="AC51" s="57" t="n"/>
       <c r="AD51" s="57" t="n"/>
+      <c r="AE51" s="57" t="n">
+        <v>45</v>
+      </c>
+      <c r="AF51" s="57" t="n"/>
+      <c r="AG51" s="57" t="n"/>
+      <c r="AH51" s="57" t="n"/>
+      <c r="AI51" s="57" t="n"/>
+      <c r="AJ51" s="57" t="n"/>
+      <c r="AK51" s="57" t="n"/>
+      <c r="AL51" s="57" t="n"/>
+      <c r="AM51" s="57" t="n"/>
+      <c r="AN51" s="57" t="n"/>
+      <c r="AO51" s="57" t="n"/>
+      <c r="AP51" s="57" t="n"/>
+      <c r="AQ51" s="57" t="n"/>
+      <c r="AR51" s="57" t="n"/>
+      <c r="AS51" s="57" t="n"/>
+      <c r="AT51" s="57" t="n"/>
     </row>
     <row r="52" ht="13.65" customHeight="1" s="90">
       <c r="A52" s="43" t="inlineStr">
@@ -9339,6 +10260,26 @@
       <c r="AB52" s="57" t="n"/>
       <c r="AC52" s="57" t="n"/>
       <c r="AD52" s="57" t="n"/>
+      <c r="AE52" s="57" t="n">
+        <v>45</v>
+      </c>
+      <c r="AF52" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG52" s="57" t="n"/>
+      <c r="AH52" s="57" t="n"/>
+      <c r="AI52" s="57" t="n"/>
+      <c r="AJ52" s="57" t="n"/>
+      <c r="AK52" s="57" t="n"/>
+      <c r="AL52" s="57" t="n"/>
+      <c r="AM52" s="57" t="n"/>
+      <c r="AN52" s="57" t="n"/>
+      <c r="AO52" s="57" t="n"/>
+      <c r="AP52" s="57" t="n"/>
+      <c r="AQ52" s="57" t="n"/>
+      <c r="AR52" s="57" t="n"/>
+      <c r="AS52" s="57" t="n"/>
+      <c r="AT52" s="57" t="n"/>
     </row>
     <row r="53" ht="13.65" customHeight="1" s="90">
       <c r="A53" s="43" t="inlineStr">
@@ -9409,6 +10350,26 @@
       <c r="AB53" s="57" t="n"/>
       <c r="AC53" s="57" t="n"/>
       <c r="AD53" s="57" t="n"/>
+      <c r="AE53" s="57" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF53" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG53" s="57" t="n"/>
+      <c r="AH53" s="57" t="n"/>
+      <c r="AI53" s="57" t="n"/>
+      <c r="AJ53" s="57" t="n"/>
+      <c r="AK53" s="57" t="n"/>
+      <c r="AL53" s="57" t="n"/>
+      <c r="AM53" s="57" t="n"/>
+      <c r="AN53" s="57" t="n"/>
+      <c r="AO53" s="57" t="n"/>
+      <c r="AP53" s="57" t="n"/>
+      <c r="AQ53" s="57" t="n"/>
+      <c r="AR53" s="57" t="n"/>
+      <c r="AS53" s="57" t="n"/>
+      <c r="AT53" s="57" t="n"/>
     </row>
     <row r="54" ht="13.65" customHeight="1" s="90">
       <c r="A54" s="43" t="inlineStr">
@@ -9479,6 +10440,30 @@
       <c r="AB54" s="57" t="n"/>
       <c r="AC54" s="57" t="n"/>
       <c r="AD54" s="57" t="n"/>
+      <c r="AE54" s="57" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF54" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG54" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AH54" s="57" t="n"/>
+      <c r="AI54" s="57" t="n"/>
+      <c r="AJ54" s="57" t="n"/>
+      <c r="AK54" s="57" t="n"/>
+      <c r="AL54" s="57" t="n"/>
+      <c r="AM54" s="57" t="n"/>
+      <c r="AN54" s="57" t="n"/>
+      <c r="AO54" s="57" t="n"/>
+      <c r="AP54" s="57" t="n"/>
+      <c r="AQ54" s="57" t="n"/>
+      <c r="AR54" s="57" t="n"/>
+      <c r="AS54" s="57" t="n"/>
+      <c r="AT54" s="57" t="n"/>
     </row>
     <row r="55" ht="13.65" customHeight="1" s="90">
       <c r="A55" s="43" t="inlineStr">
@@ -9549,6 +10534,26 @@
       <c r="AB55" s="57" t="n"/>
       <c r="AC55" s="57" t="n"/>
       <c r="AD55" s="57" t="n"/>
+      <c r="AE55" s="57" t="n"/>
+      <c r="AF55" s="57" t="n"/>
+      <c r="AG55" s="57" t="n"/>
+      <c r="AH55" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI55" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ55" s="57" t="n"/>
+      <c r="AK55" s="57" t="n"/>
+      <c r="AL55" s="57" t="n"/>
+      <c r="AM55" s="57" t="n"/>
+      <c r="AN55" s="57" t="n"/>
+      <c r="AO55" s="57" t="n"/>
+      <c r="AP55" s="57" t="n"/>
+      <c r="AQ55" s="57" t="n"/>
+      <c r="AR55" s="57" t="n"/>
+      <c r="AS55" s="57" t="n"/>
+      <c r="AT55" s="57" t="n"/>
     </row>
     <row r="56" ht="13.65" customHeight="1" s="90">
       <c r="A56" s="43" t="inlineStr">
@@ -9619,6 +10624,26 @@
       <c r="AB56" s="57" t="n"/>
       <c r="AC56" s="57" t="n"/>
       <c r="AD56" s="57" t="n"/>
+      <c r="AE56" s="57" t="n"/>
+      <c r="AF56" s="57" t="n"/>
+      <c r="AG56" s="57" t="n"/>
+      <c r="AH56" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI56" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ56" s="57" t="n"/>
+      <c r="AK56" s="57" t="n"/>
+      <c r="AL56" s="57" t="n"/>
+      <c r="AM56" s="57" t="n"/>
+      <c r="AN56" s="57" t="n"/>
+      <c r="AO56" s="57" t="n"/>
+      <c r="AP56" s="57" t="n"/>
+      <c r="AQ56" s="57" t="n"/>
+      <c r="AR56" s="57" t="n"/>
+      <c r="AS56" s="57" t="n"/>
+      <c r="AT56" s="57" t="n"/>
     </row>
     <row r="57" ht="13.65" customHeight="1" s="90">
       <c r="A57" s="43" t="inlineStr">
@@ -9689,6 +10714,28 @@
       <c r="AB57" s="57" t="n"/>
       <c r="AC57" s="57" t="n"/>
       <c r="AD57" s="57" t="n"/>
+      <c r="AE57" s="57" t="n"/>
+      <c r="AF57" s="57" t="n"/>
+      <c r="AG57" s="57" t="n"/>
+      <c r="AH57" s="57" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI57" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ57" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK57" s="57" t="n"/>
+      <c r="AL57" s="57" t="n"/>
+      <c r="AM57" s="57" t="n"/>
+      <c r="AN57" s="57" t="n"/>
+      <c r="AO57" s="57" t="n"/>
+      <c r="AP57" s="57" t="n"/>
+      <c r="AQ57" s="57" t="n"/>
+      <c r="AR57" s="57" t="n"/>
+      <c r="AS57" s="57" t="n"/>
+      <c r="AT57" s="57" t="n"/>
     </row>
     <row r="58" ht="13.65" customHeight="1" s="90">
       <c r="A58" s="43" t="inlineStr">
@@ -9759,6 +10806,28 @@
       <c r="AB58" s="57" t="n"/>
       <c r="AC58" s="57" t="n"/>
       <c r="AD58" s="57" t="n"/>
+      <c r="AE58" s="57" t="n"/>
+      <c r="AF58" s="57" t="n"/>
+      <c r="AG58" s="57" t="n"/>
+      <c r="AH58" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI58" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ58" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK58" s="57" t="n"/>
+      <c r="AL58" s="57" t="n"/>
+      <c r="AM58" s="57" t="n"/>
+      <c r="AN58" s="57" t="n"/>
+      <c r="AO58" s="57" t="n"/>
+      <c r="AP58" s="57" t="n"/>
+      <c r="AQ58" s="57" t="n"/>
+      <c r="AR58" s="57" t="n"/>
+      <c r="AS58" s="57" t="n"/>
+      <c r="AT58" s="57" t="n"/>
     </row>
     <row r="59" ht="13.65" customHeight="1" s="90">
       <c r="A59" s="43" t="inlineStr">
@@ -9829,6 +10898,32 @@
       <c r="AB59" s="57" t="n"/>
       <c r="AC59" s="57" t="n"/>
       <c r="AD59" s="57" t="n"/>
+      <c r="AE59" s="57" t="n"/>
+      <c r="AF59" s="57" t="n"/>
+      <c r="AG59" s="57" t="n"/>
+      <c r="AH59" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI59" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ59" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK59" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AL59" s="57" t="n"/>
+      <c r="AM59" s="57" t="n"/>
+      <c r="AN59" s="57" t="n"/>
+      <c r="AO59" s="57" t="n"/>
+      <c r="AP59" s="57" t="n"/>
+      <c r="AQ59" s="57" t="n"/>
+      <c r="AR59" s="57" t="n"/>
+      <c r="AS59" s="57" t="n"/>
+      <c r="AT59" s="57" t="n"/>
     </row>
     <row r="60" ht="13.65" customHeight="1" s="90">
       <c r="A60" s="43" t="inlineStr">
@@ -9899,6 +10994,24 @@
       <c r="AB60" s="57" t="n"/>
       <c r="AC60" s="57" t="n"/>
       <c r="AD60" s="57" t="n"/>
+      <c r="AE60" s="57" t="n"/>
+      <c r="AF60" s="57" t="n"/>
+      <c r="AG60" s="57" t="n"/>
+      <c r="AH60" s="57" t="n"/>
+      <c r="AI60" s="57" t="n"/>
+      <c r="AJ60" s="57" t="n"/>
+      <c r="AK60" s="57" t="n"/>
+      <c r="AL60" s="57" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM60" s="57" t="n"/>
+      <c r="AN60" s="57" t="n"/>
+      <c r="AO60" s="57" t="n"/>
+      <c r="AP60" s="57" t="n"/>
+      <c r="AQ60" s="57" t="n"/>
+      <c r="AR60" s="57" t="n"/>
+      <c r="AS60" s="57" t="n"/>
+      <c r="AT60" s="57" t="n"/>
     </row>
     <row r="61" ht="13.65" customHeight="1" s="90">
       <c r="A61" s="43" t="inlineStr">
@@ -9969,6 +11082,28 @@
       <c r="AB61" s="57" t="n"/>
       <c r="AC61" s="57" t="n"/>
       <c r="AD61" s="57" t="n"/>
+      <c r="AE61" s="57" t="n"/>
+      <c r="AF61" s="57" t="n"/>
+      <c r="AG61" s="57" t="n"/>
+      <c r="AH61" s="57" t="n"/>
+      <c r="AI61" s="57" t="n"/>
+      <c r="AJ61" s="57" t="n"/>
+      <c r="AK61" s="57" t="n"/>
+      <c r="AL61" s="57" t="n">
+        <v>35</v>
+      </c>
+      <c r="AM61" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AN61" s="57" t="n"/>
+      <c r="AO61" s="57" t="n"/>
+      <c r="AP61" s="57" t="n"/>
+      <c r="AQ61" s="57" t="n"/>
+      <c r="AR61" s="57" t="n"/>
+      <c r="AS61" s="57" t="n"/>
+      <c r="AT61" s="57" t="n"/>
     </row>
     <row r="62" ht="13.65" customHeight="1" s="90">
       <c r="A62" s="43" t="inlineStr">
@@ -10036,9 +11171,33 @@
       <c r="Y62" s="57" t="n"/>
       <c r="Z62" s="57" t="n"/>
       <c r="AA62" s="57" t="n"/>
-      <c r="AB62" s="57" t="n"/>
+      <c r="AB62" s="57" t="n">
+        <v>10</v>
+      </c>
       <c r="AC62" s="57" t="n"/>
       <c r="AD62" s="57" t="n"/>
+      <c r="AE62" s="57" t="n"/>
+      <c r="AF62" s="57" t="n"/>
+      <c r="AG62" s="57" t="n"/>
+      <c r="AH62" s="57" t="n"/>
+      <c r="AI62" s="57" t="n"/>
+      <c r="AJ62" s="57" t="n"/>
+      <c r="AK62" s="57" t="n"/>
+      <c r="AL62" s="57" t="n">
+        <v>35</v>
+      </c>
+      <c r="AM62" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AN62" s="57" t="n"/>
+      <c r="AO62" s="57" t="n"/>
+      <c r="AP62" s="57" t="n"/>
+      <c r="AQ62" s="57" t="n"/>
+      <c r="AR62" s="57" t="n"/>
+      <c r="AS62" s="57" t="n"/>
+      <c r="AT62" s="57" t="n"/>
     </row>
     <row r="63" ht="13.65" customHeight="1" s="90">
       <c r="A63" s="43" t="inlineStr">
@@ -10106,9 +11265,33 @@
       <c r="Y63" s="57" t="n"/>
       <c r="Z63" s="57" t="n"/>
       <c r="AA63" s="57" t="n"/>
-      <c r="AB63" s="57" t="n"/>
+      <c r="AB63" s="57" t="n">
+        <v>10</v>
+      </c>
       <c r="AC63" s="57" t="n"/>
       <c r="AD63" s="57" t="n"/>
+      <c r="AE63" s="57" t="n"/>
+      <c r="AF63" s="57" t="n"/>
+      <c r="AG63" s="57" t="n"/>
+      <c r="AH63" s="57" t="n"/>
+      <c r="AI63" s="57" t="n"/>
+      <c r="AJ63" s="57" t="n"/>
+      <c r="AK63" s="57" t="n"/>
+      <c r="AL63" s="57" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM63" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AN63" s="57" t="n"/>
+      <c r="AO63" s="57" t="n"/>
+      <c r="AP63" s="57" t="n"/>
+      <c r="AQ63" s="57" t="n"/>
+      <c r="AR63" s="57" t="n"/>
+      <c r="AS63" s="57" t="n"/>
+      <c r="AT63" s="57" t="n"/>
     </row>
     <row r="64" ht="13.65" customHeight="1" s="90">
       <c r="A64" s="43" t="inlineStr">
@@ -10176,9 +11359,35 @@
       <c r="Y64" s="57" t="n"/>
       <c r="Z64" s="57" t="n"/>
       <c r="AA64" s="57" t="n"/>
-      <c r="AB64" s="57" t="n"/>
-      <c r="AC64" s="57" t="n"/>
+      <c r="AB64" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC64" s="57" t="n">
+        <v>20</v>
+      </c>
       <c r="AD64" s="57" t="n"/>
+      <c r="AE64" s="57" t="n"/>
+      <c r="AF64" s="57" t="n"/>
+      <c r="AG64" s="57" t="n"/>
+      <c r="AH64" s="57" t="n"/>
+      <c r="AI64" s="57" t="n"/>
+      <c r="AJ64" s="57" t="n"/>
+      <c r="AK64" s="57" t="n"/>
+      <c r="AL64" s="57" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM64" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AN64" s="57" t="n"/>
+      <c r="AO64" s="57" t="n"/>
+      <c r="AP64" s="57" t="n"/>
+      <c r="AQ64" s="57" t="n"/>
+      <c r="AR64" s="57" t="n"/>
+      <c r="AS64" s="57" t="n"/>
+      <c r="AT64" s="57" t="n"/>
     </row>
     <row r="65" ht="13.65" customHeight="1" s="90">
       <c r="A65" s="43" t="inlineStr">
@@ -10249,6 +11458,24 @@
       <c r="AB65" s="57" t="n"/>
       <c r="AC65" s="57" t="n"/>
       <c r="AD65" s="57" t="n"/>
+      <c r="AE65" s="57" t="n"/>
+      <c r="AF65" s="57" t="n"/>
+      <c r="AG65" s="57" t="n"/>
+      <c r="AH65" s="57" t="n"/>
+      <c r="AI65" s="57" t="n"/>
+      <c r="AJ65" s="57" t="n"/>
+      <c r="AK65" s="57" t="n"/>
+      <c r="AL65" s="57" t="n"/>
+      <c r="AM65" s="57" t="n"/>
+      <c r="AN65" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO65" s="57" t="n"/>
+      <c r="AP65" s="57" t="n"/>
+      <c r="AQ65" s="57" t="n"/>
+      <c r="AR65" s="57" t="n"/>
+      <c r="AS65" s="57" t="n"/>
+      <c r="AT65" s="57" t="n"/>
     </row>
     <row r="66" ht="13.65" customHeight="1" s="90">
       <c r="A66" s="43" t="inlineStr">
@@ -10319,6 +11546,24 @@
       <c r="AB66" s="57" t="n"/>
       <c r="AC66" s="57" t="n"/>
       <c r="AD66" s="57" t="n"/>
+      <c r="AE66" s="57" t="n"/>
+      <c r="AF66" s="57" t="n"/>
+      <c r="AG66" s="57" t="n"/>
+      <c r="AH66" s="57" t="n"/>
+      <c r="AI66" s="57" t="n"/>
+      <c r="AJ66" s="57" t="n"/>
+      <c r="AK66" s="57" t="n"/>
+      <c r="AL66" s="57" t="n"/>
+      <c r="AM66" s="57" t="n"/>
+      <c r="AN66" s="57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO66" s="57" t="n"/>
+      <c r="AP66" s="57" t="n"/>
+      <c r="AQ66" s="57" t="n"/>
+      <c r="AR66" s="57" t="n"/>
+      <c r="AS66" s="57" t="n"/>
+      <c r="AT66" s="57" t="n"/>
     </row>
     <row r="67" ht="13.65" customHeight="1" s="90">
       <c r="A67" s="43" t="inlineStr">
@@ -10389,6 +11634,24 @@
       <c r="AB67" s="57" t="n"/>
       <c r="AC67" s="57" t="n"/>
       <c r="AD67" s="57" t="n"/>
+      <c r="AE67" s="57" t="n"/>
+      <c r="AF67" s="57" t="n"/>
+      <c r="AG67" s="57" t="n"/>
+      <c r="AH67" s="57" t="n"/>
+      <c r="AI67" s="57" t="n"/>
+      <c r="AJ67" s="57" t="n"/>
+      <c r="AK67" s="57" t="n"/>
+      <c r="AL67" s="57" t="n"/>
+      <c r="AM67" s="57" t="n"/>
+      <c r="AN67" s="57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO67" s="57" t="n"/>
+      <c r="AP67" s="57" t="n"/>
+      <c r="AQ67" s="57" t="n"/>
+      <c r="AR67" s="57" t="n"/>
+      <c r="AS67" s="57" t="n"/>
+      <c r="AT67" s="57" t="n"/>
     </row>
     <row r="68" ht="13.65" customHeight="1" s="90">
       <c r="A68" s="43" t="inlineStr">
@@ -10459,6 +11722,24 @@
       <c r="AB68" s="57" t="n"/>
       <c r="AC68" s="57" t="n"/>
       <c r="AD68" s="57" t="n"/>
+      <c r="AE68" s="57" t="n"/>
+      <c r="AF68" s="57" t="n"/>
+      <c r="AG68" s="57" t="n"/>
+      <c r="AH68" s="57" t="n"/>
+      <c r="AI68" s="57" t="n"/>
+      <c r="AJ68" s="57" t="n"/>
+      <c r="AK68" s="57" t="n"/>
+      <c r="AL68" s="57" t="n"/>
+      <c r="AM68" s="57" t="n"/>
+      <c r="AN68" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO68" s="57" t="n"/>
+      <c r="AP68" s="57" t="n"/>
+      <c r="AQ68" s="57" t="n"/>
+      <c r="AR68" s="57" t="n"/>
+      <c r="AS68" s="57" t="n"/>
+      <c r="AT68" s="57" t="n"/>
     </row>
     <row r="69" ht="13.65" customHeight="1" s="90">
       <c r="A69" s="43" t="inlineStr">
@@ -10529,6 +11810,28 @@
       <c r="AB69" s="57" t="n"/>
       <c r="AC69" s="57" t="n"/>
       <c r="AD69" s="57" t="n"/>
+      <c r="AE69" s="57" t="n"/>
+      <c r="AF69" s="57" t="n"/>
+      <c r="AG69" s="57" t="n"/>
+      <c r="AH69" s="57" t="n"/>
+      <c r="AI69" s="57" t="n"/>
+      <c r="AJ69" s="57" t="n"/>
+      <c r="AK69" s="57" t="n"/>
+      <c r="AL69" s="57" t="n"/>
+      <c r="AM69" s="57" t="n"/>
+      <c r="AN69" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO69" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP69" s="57" t="n">
+        <v>500</v>
+      </c>
+      <c r="AQ69" s="57" t="n"/>
+      <c r="AR69" s="57" t="n"/>
+      <c r="AS69" s="57" t="n"/>
+      <c r="AT69" s="57" t="n"/>
     </row>
     <row r="70" ht="13.65" customHeight="1" s="90">
       <c r="A70" s="43" t="inlineStr">
@@ -10599,6 +11902,26 @@
       <c r="AB70" s="57" t="n"/>
       <c r="AC70" s="57" t="n"/>
       <c r="AD70" s="57" t="n"/>
+      <c r="AE70" s="57" t="n"/>
+      <c r="AF70" s="57" t="n"/>
+      <c r="AG70" s="57" t="n"/>
+      <c r="AH70" s="57" t="n"/>
+      <c r="AI70" s="57" t="n"/>
+      <c r="AJ70" s="57" t="n"/>
+      <c r="AK70" s="57" t="n"/>
+      <c r="AL70" s="57" t="n"/>
+      <c r="AM70" s="57" t="n"/>
+      <c r="AN70" s="57" t="n"/>
+      <c r="AO70" s="57" t="n"/>
+      <c r="AP70" s="57" t="n"/>
+      <c r="AQ70" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR70" s="57" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS70" s="57" t="n"/>
+      <c r="AT70" s="57" t="n"/>
     </row>
     <row r="71" ht="13.65" customHeight="1" s="90">
       <c r="A71" s="43" t="inlineStr">
@@ -10669,6 +11992,26 @@
       <c r="AB71" s="57" t="n"/>
       <c r="AC71" s="57" t="n"/>
       <c r="AD71" s="57" t="n"/>
+      <c r="AE71" s="57" t="n"/>
+      <c r="AF71" s="57" t="n"/>
+      <c r="AG71" s="57" t="n"/>
+      <c r="AH71" s="57" t="n"/>
+      <c r="AI71" s="57" t="n"/>
+      <c r="AJ71" s="57" t="n"/>
+      <c r="AK71" s="57" t="n"/>
+      <c r="AL71" s="57" t="n"/>
+      <c r="AM71" s="57" t="n"/>
+      <c r="AN71" s="57" t="n"/>
+      <c r="AO71" s="57" t="n"/>
+      <c r="AP71" s="57" t="n"/>
+      <c r="AQ71" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR71" s="57" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS71" s="57" t="n"/>
+      <c r="AT71" s="57" t="n"/>
     </row>
     <row r="72" ht="13.65" customHeight="1" s="90">
       <c r="A72" s="43" t="inlineStr">
@@ -10739,6 +12082,26 @@
       <c r="AB72" s="57" t="n"/>
       <c r="AC72" s="57" t="n"/>
       <c r="AD72" s="57" t="n"/>
+      <c r="AE72" s="57" t="n"/>
+      <c r="AF72" s="57" t="n"/>
+      <c r="AG72" s="57" t="n"/>
+      <c r="AH72" s="57" t="n"/>
+      <c r="AI72" s="57" t="n"/>
+      <c r="AJ72" s="57" t="n"/>
+      <c r="AK72" s="57" t="n"/>
+      <c r="AL72" s="57" t="n"/>
+      <c r="AM72" s="57" t="n"/>
+      <c r="AN72" s="57" t="n"/>
+      <c r="AO72" s="57" t="n"/>
+      <c r="AP72" s="57" t="n"/>
+      <c r="AQ72" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR72" s="57" t="n">
+        <v>120</v>
+      </c>
+      <c r="AS72" s="57" t="n"/>
+      <c r="AT72" s="57" t="n"/>
     </row>
     <row r="73" ht="13.65" customHeight="1" s="90">
       <c r="A73" s="43" t="inlineStr">
@@ -10809,6 +12172,26 @@
       <c r="AB73" s="57" t="n"/>
       <c r="AC73" s="57" t="n"/>
       <c r="AD73" s="57" t="n"/>
+      <c r="AE73" s="57" t="n"/>
+      <c r="AF73" s="57" t="n"/>
+      <c r="AG73" s="57" t="n"/>
+      <c r="AH73" s="57" t="n"/>
+      <c r="AI73" s="57" t="n"/>
+      <c r="AJ73" s="57" t="n"/>
+      <c r="AK73" s="57" t="n"/>
+      <c r="AL73" s="57" t="n"/>
+      <c r="AM73" s="57" t="n"/>
+      <c r="AN73" s="57" t="n"/>
+      <c r="AO73" s="57" t="n"/>
+      <c r="AP73" s="57" t="n"/>
+      <c r="AQ73" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR73" s="57" t="n">
+        <v>120</v>
+      </c>
+      <c r="AS73" s="57" t="n"/>
+      <c r="AT73" s="57" t="n"/>
     </row>
     <row r="74" ht="13.65" customHeight="1" s="90">
       <c r="A74" s="43" t="inlineStr">
@@ -10879,6 +12262,26 @@
       <c r="AB74" s="57" t="n"/>
       <c r="AC74" s="57" t="n"/>
       <c r="AD74" s="57" t="n"/>
+      <c r="AE74" s="57" t="n"/>
+      <c r="AF74" s="57" t="n"/>
+      <c r="AG74" s="57" t="n"/>
+      <c r="AH74" s="57" t="n"/>
+      <c r="AI74" s="57" t="n"/>
+      <c r="AJ74" s="57" t="n"/>
+      <c r="AK74" s="57" t="n"/>
+      <c r="AL74" s="57" t="n"/>
+      <c r="AM74" s="57" t="n"/>
+      <c r="AN74" s="57" t="n"/>
+      <c r="AO74" s="57" t="n"/>
+      <c r="AP74" s="57" t="n"/>
+      <c r="AQ74" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR74" s="57" t="n">
+        <v>250</v>
+      </c>
+      <c r="AS74" s="57" t="n"/>
+      <c r="AT74" s="57" t="n"/>
     </row>
     <row r="75" ht="13.65" customHeight="1" s="90">
       <c r="A75" s="43" t="inlineStr">
@@ -10949,6 +12352,24 @@
       <c r="AB75" s="57" t="n"/>
       <c r="AC75" s="57" t="n"/>
       <c r="AD75" s="57" t="n"/>
+      <c r="AE75" s="57" t="n"/>
+      <c r="AF75" s="57" t="n"/>
+      <c r="AG75" s="57" t="n"/>
+      <c r="AH75" s="57" t="n"/>
+      <c r="AI75" s="57" t="n"/>
+      <c r="AJ75" s="57" t="n"/>
+      <c r="AK75" s="57" t="n"/>
+      <c r="AL75" s="57" t="n"/>
+      <c r="AM75" s="57" t="n"/>
+      <c r="AN75" s="57" t="n"/>
+      <c r="AO75" s="57" t="n"/>
+      <c r="AP75" s="57" t="n"/>
+      <c r="AQ75" s="57" t="n"/>
+      <c r="AR75" s="57" t="n"/>
+      <c r="AS75" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT75" s="57" t="n"/>
     </row>
     <row r="76" ht="13.65" customHeight="1" s="90">
       <c r="A76" s="43" t="inlineStr">
@@ -11019,6 +12440,24 @@
       <c r="AB76" s="57" t="n"/>
       <c r="AC76" s="57" t="n"/>
       <c r="AD76" s="57" t="n"/>
+      <c r="AE76" s="57" t="n"/>
+      <c r="AF76" s="57" t="n"/>
+      <c r="AG76" s="57" t="n"/>
+      <c r="AH76" s="57" t="n"/>
+      <c r="AI76" s="57" t="n"/>
+      <c r="AJ76" s="57" t="n"/>
+      <c r="AK76" s="57" t="n"/>
+      <c r="AL76" s="57" t="n"/>
+      <c r="AM76" s="57" t="n"/>
+      <c r="AN76" s="57" t="n"/>
+      <c r="AO76" s="57" t="n"/>
+      <c r="AP76" s="57" t="n"/>
+      <c r="AQ76" s="57" t="n"/>
+      <c r="AR76" s="57" t="n"/>
+      <c r="AS76" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT76" s="57" t="n"/>
     </row>
     <row r="77" ht="13.65" customHeight="1" s="90">
       <c r="A77" s="43" t="inlineStr">
@@ -11089,6 +12528,26 @@
       <c r="AB77" s="57" t="n"/>
       <c r="AC77" s="57" t="n"/>
       <c r="AD77" s="57" t="n"/>
+      <c r="AE77" s="57" t="n"/>
+      <c r="AF77" s="57" t="n"/>
+      <c r="AG77" s="57" t="n"/>
+      <c r="AH77" s="57" t="n"/>
+      <c r="AI77" s="57" t="n"/>
+      <c r="AJ77" s="57" t="n"/>
+      <c r="AK77" s="57" t="n"/>
+      <c r="AL77" s="57" t="n"/>
+      <c r="AM77" s="57" t="n"/>
+      <c r="AN77" s="57" t="n"/>
+      <c r="AO77" s="57" t="n"/>
+      <c r="AP77" s="57" t="n"/>
+      <c r="AQ77" s="57" t="n"/>
+      <c r="AR77" s="57" t="n"/>
+      <c r="AS77" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT77" s="57" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="78" ht="13.65" customHeight="1" s="90">
       <c r="A78" s="43" t="inlineStr">
@@ -11156,9 +12615,31 @@
       <c r="Y78" s="57" t="n"/>
       <c r="Z78" s="57" t="n"/>
       <c r="AA78" s="57" t="n"/>
-      <c r="AB78" s="57" t="n"/>
+      <c r="AB78" s="57" t="n">
+        <v>10</v>
+      </c>
       <c r="AC78" s="57" t="n"/>
       <c r="AD78" s="57" t="n"/>
+      <c r="AE78" s="57" t="n"/>
+      <c r="AF78" s="57" t="n"/>
+      <c r="AG78" s="57" t="n"/>
+      <c r="AH78" s="57" t="n"/>
+      <c r="AI78" s="57" t="n"/>
+      <c r="AJ78" s="57" t="n"/>
+      <c r="AK78" s="57" t="n"/>
+      <c r="AL78" s="57" t="n"/>
+      <c r="AM78" s="57" t="n"/>
+      <c r="AN78" s="57" t="n"/>
+      <c r="AO78" s="57" t="n"/>
+      <c r="AP78" s="57" t="n"/>
+      <c r="AQ78" s="57" t="n"/>
+      <c r="AR78" s="57" t="n"/>
+      <c r="AS78" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT78" s="57" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="79" ht="13.65" customHeight="1" s="90">
       <c r="A79" s="43" t="inlineStr">
@@ -11226,9 +12707,31 @@
       <c r="Y79" s="57" t="n"/>
       <c r="Z79" s="57" t="n"/>
       <c r="AA79" s="57" t="n"/>
-      <c r="AB79" s="57" t="n"/>
+      <c r="AB79" s="57" t="n">
+        <v>10</v>
+      </c>
       <c r="AC79" s="57" t="n"/>
       <c r="AD79" s="57" t="n"/>
+      <c r="AE79" s="57" t="n"/>
+      <c r="AF79" s="57" t="n"/>
+      <c r="AG79" s="57" t="n"/>
+      <c r="AH79" s="57" t="n"/>
+      <c r="AI79" s="57" t="n"/>
+      <c r="AJ79" s="57" t="n"/>
+      <c r="AK79" s="57" t="n"/>
+      <c r="AL79" s="57" t="n"/>
+      <c r="AM79" s="57" t="n"/>
+      <c r="AN79" s="57" t="n"/>
+      <c r="AO79" s="57" t="n"/>
+      <c r="AP79" s="57" t="n"/>
+      <c r="AQ79" s="57" t="n"/>
+      <c r="AR79" s="57" t="n"/>
+      <c r="AS79" s="57" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT79" s="57" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -5482,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
@@ -10085,7 +10085,7 @@
       <c r="AC50" s="57" t="n"/>
       <c r="AD50" s="57" t="n"/>
       <c r="AE50" s="57" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="AF50" s="57" t="n"/>
       <c r="AG50" s="57" t="n"/>
@@ -10173,7 +10173,7 @@
       <c r="AC51" s="57" t="n"/>
       <c r="AD51" s="57" t="n"/>
       <c r="AE51" s="57" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AF51" s="57" t="n"/>
       <c r="AG51" s="57" t="n"/>
@@ -10261,7 +10261,7 @@
       <c r="AC52" s="57" t="n"/>
       <c r="AD52" s="57" t="n"/>
       <c r="AE52" s="57" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AF52" s="57" t="n">
         <v>2</v>
@@ -10351,7 +10351,7 @@
       <c r="AC53" s="57" t="n"/>
       <c r="AD53" s="57" t="n"/>
       <c r="AE53" s="57" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AF53" s="57" t="n">
         <v>2</v>
@@ -10441,7 +10441,7 @@
       <c r="AC54" s="57" t="n"/>
       <c r="AD54" s="57" t="n"/>
       <c r="AE54" s="57" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AF54" s="57" t="n">
         <v>3</v>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -13184,7 +13184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG49"/>
+  <dimension ref="A1:AH49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="90" min="1" max="1"/>
@@ -13232,7 +13232,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Effect columns are cumulative per tier (like Tower Upgrades); blank = no change. x columns multiply the hero's base; Fire mode / Guns / Pellets / Pierce / Bounces override it. Crossover rule as towers: two paths, one past tier 2. Damage is per shot: pellets share the hero's base damage x its base pellet count, so more pellets spread the same damage wider and a slug concentrates it.</t>
+          <t>Effect columns are cumulative per tier (like Tower Upgrades); blank = no change. x columns multiply the hero's base; Fire mode / Guns / Pellets / Pierce / Bounces override it. Crossover rule as towers: two paths, one past tier 2. Damage is per shot: pellets share the hero's base damage x its base pellet count, so more pellets spread the same damage wider and a slug concentrates it. Ignite (s): an enemy hit burns (Burn DPS) for this long, then loses its current layer if it's still alive (not bosses).</t>
         </is>
       </c>
     </row>
@@ -13400,6 +13400,11 @@
       <c r="AG4" s="21" t="inlineStr">
         <is>
           <t>Scope</t>
+        </is>
+      </c>
+      <c r="AH4" s="21" t="inlineStr">
+        <is>
+          <t>Ignite (s)</t>
         </is>
       </c>
     </row>
@@ -13462,6 +13467,7 @@
       <c r="AE5" s="57" t="n"/>
       <c r="AF5" s="57" t="n"/>
       <c r="AG5" s="57" t="n"/>
+      <c r="AH5" s="57" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
@@ -13522,6 +13528,7 @@
       <c r="AE6" s="57" t="n"/>
       <c r="AF6" s="57" t="n"/>
       <c r="AG6" s="57" t="n"/>
+      <c r="AH6" s="57" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="43" t="inlineStr">
@@ -13584,6 +13591,7 @@
       <c r="AE7" s="57" t="n"/>
       <c r="AF7" s="57" t="n"/>
       <c r="AG7" s="57" t="n"/>
+      <c r="AH7" s="57" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
@@ -13646,6 +13654,7 @@
       <c r="AE8" s="57" t="n"/>
       <c r="AF8" s="57" t="n"/>
       <c r="AG8" s="57" t="n"/>
+      <c r="AH8" s="57" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="43" t="inlineStr">
@@ -13714,6 +13723,7 @@
       <c r="AE9" s="57" t="n"/>
       <c r="AF9" s="57" t="n"/>
       <c r="AG9" s="57" t="n"/>
+      <c r="AH9" s="57" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="43" t="inlineStr">
@@ -13772,6 +13782,7 @@
       <c r="AE10" s="57" t="n"/>
       <c r="AF10" s="57" t="n"/>
       <c r="AG10" s="57" t="n"/>
+      <c r="AH10" s="57" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="43" t="inlineStr">
@@ -13832,6 +13843,7 @@
       <c r="AE11" s="57" t="n"/>
       <c r="AF11" s="57" t="n"/>
       <c r="AG11" s="57" t="n"/>
+      <c r="AH11" s="57" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="43" t="inlineStr">
@@ -13898,6 +13910,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AH12" s="57" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
@@ -13968,6 +13981,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AH13" s="57" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="43" t="inlineStr">
@@ -14040,6 +14054,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AH14" s="57" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
@@ -14098,6 +14113,7 @@
       <c r="AE15" s="57" t="n"/>
       <c r="AF15" s="57" t="n"/>
       <c r="AG15" s="57" t="n"/>
+      <c r="AH15" s="57" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="43" t="inlineStr">
@@ -14158,6 +14174,7 @@
       <c r="AE16" s="57" t="n"/>
       <c r="AF16" s="57" t="n"/>
       <c r="AG16" s="57" t="n"/>
+      <c r="AH16" s="57" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="43" t="inlineStr">
@@ -14220,6 +14237,7 @@
       <c r="AE17" s="57" t="n"/>
       <c r="AF17" s="57" t="n"/>
       <c r="AG17" s="57" t="n"/>
+      <c r="AH17" s="57" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="43" t="inlineStr">
@@ -14284,6 +14302,7 @@
       <c r="AE18" s="57" t="n"/>
       <c r="AF18" s="57" t="n"/>
       <c r="AG18" s="57" t="n"/>
+      <c r="AH18" s="57" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="43" t="inlineStr">
@@ -14348,6 +14367,7 @@
       <c r="AE19" s="57" t="n"/>
       <c r="AF19" s="57" t="n"/>
       <c r="AG19" s="57" t="n"/>
+      <c r="AH19" s="57" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="43" t="inlineStr">
@@ -14406,6 +14426,7 @@
       <c r="AE20" s="57" t="n"/>
       <c r="AF20" s="57" t="n"/>
       <c r="AG20" s="57" t="n"/>
+      <c r="AH20" s="57" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="43" t="inlineStr">
@@ -14466,6 +14487,7 @@
       <c r="AE21" s="57" t="n"/>
       <c r="AF21" s="57" t="n"/>
       <c r="AG21" s="57" t="n"/>
+      <c r="AH21" s="57" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="43" t="inlineStr">
@@ -14534,6 +14556,7 @@
       <c r="AE22" s="57" t="n"/>
       <c r="AF22" s="57" t="n"/>
       <c r="AG22" s="57" t="n"/>
+      <c r="AH22" s="57" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="43" t="inlineStr">
@@ -14604,6 +14627,7 @@
       <c r="AE23" s="57" t="n"/>
       <c r="AF23" s="57" t="n"/>
       <c r="AG23" s="57" t="n"/>
+      <c r="AH23" s="57" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="43" t="inlineStr">
@@ -14676,6 +14700,7 @@
       <c r="AE24" s="57" t="n"/>
       <c r="AF24" s="57" t="n"/>
       <c r="AG24" s="57" t="n"/>
+      <c r="AH24" s="57" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="43" t="inlineStr">
@@ -14734,6 +14759,7 @@
       <c r="AE25" s="57" t="n"/>
       <c r="AF25" s="57" t="n"/>
       <c r="AG25" s="57" t="n"/>
+      <c r="AH25" s="57" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="43" t="inlineStr">
@@ -14794,6 +14820,7 @@
       <c r="AE26" s="57" t="n"/>
       <c r="AF26" s="57" t="n"/>
       <c r="AG26" s="57" t="n"/>
+      <c r="AH26" s="57" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="43" t="inlineStr">
@@ -14858,6 +14885,7 @@
       <c r="AE27" s="57" t="n"/>
       <c r="AF27" s="57" t="n"/>
       <c r="AG27" s="57" t="n"/>
+      <c r="AH27" s="57" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="43" t="inlineStr">
@@ -14924,6 +14952,7 @@
       </c>
       <c r="AF28" s="57" t="n"/>
       <c r="AG28" s="57" t="n"/>
+      <c r="AH28" s="57" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="43" t="inlineStr">
@@ -14992,6 +15021,7 @@
         <v>2.5</v>
       </c>
       <c r="AG29" s="57" t="n"/>
+      <c r="AH29" s="57" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="43" t="inlineStr">
@@ -15050,6 +15080,7 @@
       <c r="AE30" s="57" t="n"/>
       <c r="AF30" s="57" t="n"/>
       <c r="AG30" s="57" t="n"/>
+      <c r="AH30" s="57" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="43" t="inlineStr">
@@ -15112,6 +15143,7 @@
       <c r="AE31" s="57" t="n"/>
       <c r="AF31" s="57" t="n"/>
       <c r="AG31" s="57" t="n"/>
+      <c r="AH31" s="57" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="43" t="inlineStr">
@@ -15178,6 +15210,7 @@
       <c r="AE32" s="57" t="n"/>
       <c r="AF32" s="57" t="n"/>
       <c r="AG32" s="57" t="n"/>
+      <c r="AH32" s="57" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="43" t="inlineStr">
@@ -15248,6 +15281,7 @@
       <c r="AE33" s="57" t="n"/>
       <c r="AF33" s="57" t="n"/>
       <c r="AG33" s="57" t="n"/>
+      <c r="AH33" s="57" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="43" t="inlineStr">
@@ -15320,6 +15354,7 @@
       <c r="AE34" s="57" t="n"/>
       <c r="AF34" s="57" t="n"/>
       <c r="AG34" s="57" t="n"/>
+      <c r="AH34" s="57" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="43" t="inlineStr">
@@ -15386,6 +15421,7 @@
       <c r="AE35" s="57" t="n"/>
       <c r="AF35" s="57" t="n"/>
       <c r="AG35" s="57" t="n"/>
+      <c r="AH35" s="57" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="43" t="inlineStr">
@@ -15456,6 +15492,7 @@
       <c r="AE36" s="57" t="n"/>
       <c r="AF36" s="57" t="n"/>
       <c r="AG36" s="57" t="n"/>
+      <c r="AH36" s="57" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="43" t="inlineStr">
@@ -15530,6 +15567,7 @@
       <c r="AE37" s="57" t="n"/>
       <c r="AF37" s="57" t="n"/>
       <c r="AG37" s="57" t="n"/>
+      <c r="AH37" s="57" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="43" t="inlineStr">
@@ -15604,6 +15642,7 @@
       <c r="AE38" s="57" t="n"/>
       <c r="AF38" s="57" t="n"/>
       <c r="AG38" s="57" t="n"/>
+      <c r="AH38" s="57" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="43" t="inlineStr">
@@ -15678,6 +15717,7 @@
       <c r="AE39" s="57" t="n"/>
       <c r="AF39" s="57" t="n"/>
       <c r="AG39" s="57" t="n"/>
+      <c r="AH39" s="57" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="43" t="inlineStr">
@@ -15736,6 +15776,7 @@
       <c r="AE40" s="57" t="n"/>
       <c r="AF40" s="57" t="n"/>
       <c r="AG40" s="57" t="n"/>
+      <c r="AH40" s="57" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="43" t="inlineStr">
@@ -15796,6 +15837,7 @@
       <c r="AE41" s="57" t="n"/>
       <c r="AF41" s="57" t="n"/>
       <c r="AG41" s="57" t="n"/>
+      <c r="AH41" s="57" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="43" t="inlineStr">
@@ -15860,6 +15902,9 @@
       <c r="AE42" s="57" t="n"/>
       <c r="AF42" s="57" t="n"/>
       <c r="AG42" s="57" t="n"/>
+      <c r="AH42" s="57" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="43" t="inlineStr">
@@ -15928,6 +15973,9 @@
       <c r="AE43" s="57" t="n"/>
       <c r="AF43" s="57" t="n"/>
       <c r="AG43" s="57" t="n"/>
+      <c r="AH43" s="57" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="43" t="inlineStr">
@@ -16002,6 +16050,9 @@
       <c r="AE44" s="57" t="n"/>
       <c r="AF44" s="57" t="n"/>
       <c r="AG44" s="57" t="n"/>
+      <c r="AH44" s="57" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="43" t="inlineStr">
@@ -16060,6 +16111,7 @@
       <c r="AE45" s="57" t="n"/>
       <c r="AF45" s="57" t="n"/>
       <c r="AG45" s="57" t="n"/>
+      <c r="AH45" s="57" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="43" t="inlineStr">
@@ -16120,6 +16172,7 @@
       <c r="AE46" s="57" t="n"/>
       <c r="AF46" s="57" t="n"/>
       <c r="AG46" s="57" t="n"/>
+      <c r="AH46" s="57" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="43" t="inlineStr">
@@ -16182,6 +16235,7 @@
       <c r="AE47" s="57" t="n"/>
       <c r="AF47" s="57" t="n"/>
       <c r="AG47" s="57" t="n"/>
+      <c r="AH47" s="57" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="43" t="inlineStr">
@@ -16246,6 +16300,7 @@
       <c r="AE48" s="57" t="n"/>
       <c r="AF48" s="57" t="n"/>
       <c r="AG48" s="57" t="n"/>
+      <c r="AH48" s="57" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="43" t="inlineStr">
@@ -16312,6 +16367,7 @@
       <c r="AE49" s="57" t="n"/>
       <c r="AF49" s="57" t="n"/>
       <c r="AG49" s="57" t="n"/>
+      <c r="AH49" s="57" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -13184,7 +13184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH49"/>
+  <dimension ref="A1:AI49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="90" min="1" max="1"/>
@@ -13232,7 +13232,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Effect columns are cumulative per tier (like Tower Upgrades); blank = no change. x columns multiply the hero's base; Fire mode / Guns / Pellets / Pierce / Bounces override it. Crossover rule as towers: two paths, one past tier 2. Damage is per shot: pellets share the hero's base damage x its base pellet count, so more pellets spread the same damage wider and a slug concentrates it. Ignite (s): an enemy hit burns (Burn DPS) for this long, then loses its current layer if it's still alive (not bosses).</t>
+          <t>Effect columns are cumulative per tier (like Tower Upgrades); blank = no change. x columns multiply the hero's base; Fire mode / Guns / Pellets / Pierce / Bounces override it. Crossover rule as towers: two paths, one past tier 2. Damage is per shot: pellets share the hero's base damage x its base pellet count, so more pellets spread the same damage wider and a slug concentrates it. Ignite: an enemy hit burns for Ignite (s), then takes one tick of Ignite tick x the whole shot's damage.</t>
         </is>
       </c>
     </row>
@@ -13405,6 +13405,11 @@
       <c r="AH4" s="21" t="inlineStr">
         <is>
           <t>Ignite (s)</t>
+        </is>
+      </c>
+      <c r="AI4" s="21" t="inlineStr">
+        <is>
+          <t>Ignite tick (x shot)</t>
         </is>
       </c>
     </row>
@@ -13468,6 +13473,7 @@
       <c r="AF5" s="57" t="n"/>
       <c r="AG5" s="57" t="n"/>
       <c r="AH5" s="57" t="n"/>
+      <c r="AI5" s="57" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
@@ -13529,6 +13535,7 @@
       <c r="AF6" s="57" t="n"/>
       <c r="AG6" s="57" t="n"/>
       <c r="AH6" s="57" t="n"/>
+      <c r="AI6" s="57" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="43" t="inlineStr">
@@ -13592,6 +13599,7 @@
       <c r="AF7" s="57" t="n"/>
       <c r="AG7" s="57" t="n"/>
       <c r="AH7" s="57" t="n"/>
+      <c r="AI7" s="57" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
@@ -13655,6 +13663,7 @@
       <c r="AF8" s="57" t="n"/>
       <c r="AG8" s="57" t="n"/>
       <c r="AH8" s="57" t="n"/>
+      <c r="AI8" s="57" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="43" t="inlineStr">
@@ -13724,6 +13733,7 @@
       <c r="AF9" s="57" t="n"/>
       <c r="AG9" s="57" t="n"/>
       <c r="AH9" s="57" t="n"/>
+      <c r="AI9" s="57" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="43" t="inlineStr">
@@ -13783,6 +13793,7 @@
       <c r="AF10" s="57" t="n"/>
       <c r="AG10" s="57" t="n"/>
       <c r="AH10" s="57" t="n"/>
+      <c r="AI10" s="57" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="43" t="inlineStr">
@@ -13844,6 +13855,7 @@
       <c r="AF11" s="57" t="n"/>
       <c r="AG11" s="57" t="n"/>
       <c r="AH11" s="57" t="n"/>
+      <c r="AI11" s="57" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="43" t="inlineStr">
@@ -13911,6 +13923,7 @@
         </is>
       </c>
       <c r="AH12" s="57" t="n"/>
+      <c r="AI12" s="57" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
@@ -13982,6 +13995,7 @@
         </is>
       </c>
       <c r="AH13" s="57" t="n"/>
+      <c r="AI13" s="57" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="43" t="inlineStr">
@@ -14055,6 +14069,7 @@
         </is>
       </c>
       <c r="AH14" s="57" t="n"/>
+      <c r="AI14" s="57" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
@@ -14114,6 +14129,7 @@
       <c r="AF15" s="57" t="n"/>
       <c r="AG15" s="57" t="n"/>
       <c r="AH15" s="57" t="n"/>
+      <c r="AI15" s="57" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="43" t="inlineStr">
@@ -14175,6 +14191,7 @@
       <c r="AF16" s="57" t="n"/>
       <c r="AG16" s="57" t="n"/>
       <c r="AH16" s="57" t="n"/>
+      <c r="AI16" s="57" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="43" t="inlineStr">
@@ -14238,6 +14255,7 @@
       <c r="AF17" s="57" t="n"/>
       <c r="AG17" s="57" t="n"/>
       <c r="AH17" s="57" t="n"/>
+      <c r="AI17" s="57" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="43" t="inlineStr">
@@ -14303,6 +14321,7 @@
       <c r="AF18" s="57" t="n"/>
       <c r="AG18" s="57" t="n"/>
       <c r="AH18" s="57" t="n"/>
+      <c r="AI18" s="57" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="43" t="inlineStr">
@@ -14368,6 +14387,7 @@
       <c r="AF19" s="57" t="n"/>
       <c r="AG19" s="57" t="n"/>
       <c r="AH19" s="57" t="n"/>
+      <c r="AI19" s="57" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="43" t="inlineStr">
@@ -14427,6 +14447,7 @@
       <c r="AF20" s="57" t="n"/>
       <c r="AG20" s="57" t="n"/>
       <c r="AH20" s="57" t="n"/>
+      <c r="AI20" s="57" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="43" t="inlineStr">
@@ -14488,6 +14509,7 @@
       <c r="AF21" s="57" t="n"/>
       <c r="AG21" s="57" t="n"/>
       <c r="AH21" s="57" t="n"/>
+      <c r="AI21" s="57" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="43" t="inlineStr">
@@ -14557,6 +14579,7 @@
       <c r="AF22" s="57" t="n"/>
       <c r="AG22" s="57" t="n"/>
       <c r="AH22" s="57" t="n"/>
+      <c r="AI22" s="57" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="43" t="inlineStr">
@@ -14628,6 +14651,7 @@
       <c r="AF23" s="57" t="n"/>
       <c r="AG23" s="57" t="n"/>
       <c r="AH23" s="57" t="n"/>
+      <c r="AI23" s="57" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="43" t="inlineStr">
@@ -14701,6 +14725,7 @@
       <c r="AF24" s="57" t="n"/>
       <c r="AG24" s="57" t="n"/>
       <c r="AH24" s="57" t="n"/>
+      <c r="AI24" s="57" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="43" t="inlineStr">
@@ -14760,6 +14785,7 @@
       <c r="AF25" s="57" t="n"/>
       <c r="AG25" s="57" t="n"/>
       <c r="AH25" s="57" t="n"/>
+      <c r="AI25" s="57" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="43" t="inlineStr">
@@ -14821,6 +14847,7 @@
       <c r="AF26" s="57" t="n"/>
       <c r="AG26" s="57" t="n"/>
       <c r="AH26" s="57" t="n"/>
+      <c r="AI26" s="57" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="43" t="inlineStr">
@@ -14886,6 +14913,7 @@
       <c r="AF27" s="57" t="n"/>
       <c r="AG27" s="57" t="n"/>
       <c r="AH27" s="57" t="n"/>
+      <c r="AI27" s="57" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="43" t="inlineStr">
@@ -14953,6 +14981,7 @@
       <c r="AF28" s="57" t="n"/>
       <c r="AG28" s="57" t="n"/>
       <c r="AH28" s="57" t="n"/>
+      <c r="AI28" s="57" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="43" t="inlineStr">
@@ -15022,6 +15051,7 @@
       </c>
       <c r="AG29" s="57" t="n"/>
       <c r="AH29" s="57" t="n"/>
+      <c r="AI29" s="57" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="43" t="inlineStr">
@@ -15081,6 +15111,7 @@
       <c r="AF30" s="57" t="n"/>
       <c r="AG30" s="57" t="n"/>
       <c r="AH30" s="57" t="n"/>
+      <c r="AI30" s="57" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="43" t="inlineStr">
@@ -15144,6 +15175,7 @@
       <c r="AF31" s="57" t="n"/>
       <c r="AG31" s="57" t="n"/>
       <c r="AH31" s="57" t="n"/>
+      <c r="AI31" s="57" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="43" t="inlineStr">
@@ -15211,6 +15243,7 @@
       <c r="AF32" s="57" t="n"/>
       <c r="AG32" s="57" t="n"/>
       <c r="AH32" s="57" t="n"/>
+      <c r="AI32" s="57" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="43" t="inlineStr">
@@ -15282,6 +15315,7 @@
       <c r="AF33" s="57" t="n"/>
       <c r="AG33" s="57" t="n"/>
       <c r="AH33" s="57" t="n"/>
+      <c r="AI33" s="57" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="43" t="inlineStr">
@@ -15355,6 +15389,7 @@
       <c r="AF34" s="57" t="n"/>
       <c r="AG34" s="57" t="n"/>
       <c r="AH34" s="57" t="n"/>
+      <c r="AI34" s="57" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="43" t="inlineStr">
@@ -15422,6 +15457,7 @@
       <c r="AF35" s="57" t="n"/>
       <c r="AG35" s="57" t="n"/>
       <c r="AH35" s="57" t="n"/>
+      <c r="AI35" s="57" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="43" t="inlineStr">
@@ -15493,6 +15529,7 @@
       <c r="AF36" s="57" t="n"/>
       <c r="AG36" s="57" t="n"/>
       <c r="AH36" s="57" t="n"/>
+      <c r="AI36" s="57" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="43" t="inlineStr">
@@ -15568,6 +15605,7 @@
       <c r="AF37" s="57" t="n"/>
       <c r="AG37" s="57" t="n"/>
       <c r="AH37" s="57" t="n"/>
+      <c r="AI37" s="57" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="43" t="inlineStr">
@@ -15643,6 +15681,7 @@
       <c r="AF38" s="57" t="n"/>
       <c r="AG38" s="57" t="n"/>
       <c r="AH38" s="57" t="n"/>
+      <c r="AI38" s="57" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="43" t="inlineStr">
@@ -15718,6 +15757,7 @@
       <c r="AF39" s="57" t="n"/>
       <c r="AG39" s="57" t="n"/>
       <c r="AH39" s="57" t="n"/>
+      <c r="AI39" s="57" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="43" t="inlineStr">
@@ -15777,6 +15817,7 @@
       <c r="AF40" s="57" t="n"/>
       <c r="AG40" s="57" t="n"/>
       <c r="AH40" s="57" t="n"/>
+      <c r="AI40" s="57" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="43" t="inlineStr">
@@ -15838,6 +15879,7 @@
       <c r="AF41" s="57" t="n"/>
       <c r="AG41" s="57" t="n"/>
       <c r="AH41" s="57" t="n"/>
+      <c r="AI41" s="57" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="43" t="inlineStr">
@@ -15905,6 +15947,9 @@
       <c r="AH42" s="57" t="n">
         <v>1.5</v>
       </c>
+      <c r="AI42" s="57" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="43" t="inlineStr">
@@ -15976,6 +16021,9 @@
       <c r="AH43" s="57" t="n">
         <v>1.5</v>
       </c>
+      <c r="AI43" s="57" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="43" t="inlineStr">
@@ -16052,6 +16100,9 @@
       <c r="AG44" s="57" t="n"/>
       <c r="AH44" s="57" t="n">
         <v>1.5</v>
+      </c>
+      <c r="AI44" s="57" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="45">
@@ -16112,6 +16163,7 @@
       <c r="AF45" s="57" t="n"/>
       <c r="AG45" s="57" t="n"/>
       <c r="AH45" s="57" t="n"/>
+      <c r="AI45" s="57" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="43" t="inlineStr">
@@ -16173,6 +16225,7 @@
       <c r="AF46" s="57" t="n"/>
       <c r="AG46" s="57" t="n"/>
       <c r="AH46" s="57" t="n"/>
+      <c r="AI46" s="57" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="43" t="inlineStr">
@@ -16236,6 +16289,7 @@
       <c r="AF47" s="57" t="n"/>
       <c r="AG47" s="57" t="n"/>
       <c r="AH47" s="57" t="n"/>
+      <c r="AI47" s="57" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="43" t="inlineStr">
@@ -16301,6 +16355,7 @@
       <c r="AF48" s="57" t="n"/>
       <c r="AG48" s="57" t="n"/>
       <c r="AH48" s="57" t="n"/>
+      <c r="AI48" s="57" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="43" t="inlineStr">
@@ -16368,6 +16423,7 @@
       <c r="AF49" s="57" t="n"/>
       <c r="AG49" s="57" t="n"/>
       <c r="AH49" s="57" t="n"/>
+      <c r="AI49" s="57" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -13232,7 +13232,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Effect columns are cumulative per tier (like Tower Upgrades); blank = no change. x columns multiply the hero's base; Fire mode / Guns / Pellets / Pierce / Bounces override it. Crossover rule as towers: two paths, one past tier 2. Damage is per shot: pellets share the hero's base damage x its base pellet count, so more pellets spread the same damage wider and a slug concentrates it. Ignite: an enemy hit burns for Ignite (s), then takes one tick of Ignite tick x the whole shot's damage.</t>
+          <t>Effect columns are cumulative per tier (like Tower Upgrades); blank = no change. x columns multiply the hero's base; Fire mode / Guns / Pellets / Pierce / Bounces override it. Crossover rule as towers: two paths, one past tier 2. Damage is per shot: pellets share the hero's base damage x its base pellet count, so more pellets spread the same damage wider and a slug concentrates it. Ignite: an enemy hit burns for Ignite (s), then takes one tick of Ignite tick x the whole shot's damage. The fire passes to the enemy's split children, so a Brute shot down to Husks sees them burn out together.</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
         <v>1.5</v>
       </c>
       <c r="AI42" s="57" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="43">
@@ -16022,7 +16022,7 @@
         <v>1.5</v>
       </c>
       <c r="AI43" s="57" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="44">
@@ -16102,7 +16102,7 @@
         <v>1.5</v>
       </c>
       <c r="AI44" s="57" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="45">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -4182,7 +4182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -5127,6 +5127,76 @@
       <c r="D56" s="29" t="inlineStr">
         <is>
           <t>Chests land this far around their Quartermaster at most.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="31" t="inlineStr">
+        <is>
+          <t>HERO LEVELS</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="n"/>
+      <c r="C58" s="32" t="n"/>
+      <c r="D58" s="32" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="26" t="inlineStr">
+        <is>
+          <t>Rounds per level</t>
+        </is>
+      </c>
+      <c r="B59" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C59" s="28" t="inlineStr">
+        <is>
+          <t>rounds</t>
+        </is>
+      </c>
+      <c r="D59" s="29" t="inlineStr">
+        <is>
+          <t>Every this many rounds cleared, heroes level up and towers get stronger. (Later: hero XP from pops.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="26" t="inlineStr">
+        <is>
+          <t>Hero damage per level</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C60" s="28" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D60" s="29" t="inlineStr">
+        <is>
+          <t>Each hero level multiplies all hero damage by 1 + this (compounding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="26" t="inlineStr">
+        <is>
+          <t>Tower damage per level</t>
+        </is>
+      </c>
+      <c r="B61" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C61" s="28" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D61" s="29" t="inlineStr">
+        <is>
+          <t>Each level multiplies all tower damage by 1 + this (compounding).</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>20 permanent levels per weapon type, bought with Storm Cores.</t>
+          <t>20 permanent levels per hero, bought with Storm Cores. Cheaper upgrades, cooldowns, head starts — never damage.</t>
         </is>
       </c>
       <c r="C16" s="6" t="n"/>
@@ -5220,7 +5220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -5354,6 +5354,11 @@
           <t>Slow %</t>
         </is>
       </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t>Unlock round</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -5404,6 +5409,9 @@
       <c r="M5" s="27" t="n">
         <v>0</v>
       </c>
+      <c r="N5" s="27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="13.65" customHeight="1" s="90">
       <c r="A6" s="43" t="inlineStr">
@@ -5454,6 +5462,9 @@
       <c r="M6" s="27" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="13.65" customHeight="1" s="90">
       <c r="A7" s="43" t="inlineStr">
@@ -5504,6 +5515,9 @@
       <c r="M7" s="27" t="n">
         <v>0</v>
       </c>
+      <c r="N7" s="27" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" ht="13.65" customHeight="1" s="90">
       <c r="A8" s="43" t="inlineStr">
@@ -5554,6 +5568,9 @@
       <c r="M8" s="27" t="n">
         <v>40</v>
       </c>
+      <c r="N8" s="27" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
       <c r="A9" s="43" t="inlineStr">
@@ -5603,6 +5620,9 @@
       </c>
       <c r="M9" s="27" t="n">
         <v>0</v>
+      </c>
+      <c r="N9" s="27" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="13.55" customHeight="1" s="90">
@@ -16506,7 +16526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="81" min="1" max="1"/>
@@ -16514,13 +16534,16 @@
     <col width="18" customWidth="1" style="81" min="3" max="3"/>
     <col width="16" customWidth="1" style="81" min="4" max="4"/>
     <col width="86" customWidth="1" style="81" min="5" max="5"/>
-    <col width="8.67188" customWidth="1" style="81" min="6" max="16384"/>
+    <col width="14" customWidth="1" style="81" min="6" max="16384"/>
+    <col width="14" customWidth="1" style="90" min="7" max="7"/>
+    <col width="14" customWidth="1" style="90" min="8" max="8"/>
+    <col width="14" customWidth="1" style="90" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.5" customHeight="1" s="90">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>WEAPON MASTERY — permanent, per weapon type</t>
+          <t>HERO MASTERY — permanent, per hero</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -16572,6 +16595,26 @@
           <t>Unlock at this level</t>
         </is>
       </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Upgrade discount %</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>Ability cooldown x</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>Free first upgrade</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>Crossover cap</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="56" t="n">
@@ -16591,8 +16634,22 @@
       </c>
       <c r="E5" s="65" t="inlineStr">
         <is>
-          <t>-5% on this weapon's in-round upgrade costs</t>
-        </is>
+          <t>-5% on this hero's upgrade costs</t>
+        </is>
+      </c>
+      <c r="F5" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I5" s="56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6" ht="13.65" customHeight="1" s="90">
@@ -16616,6 +16673,20 @@
           <t>-10% cumulative</t>
         </is>
       </c>
+      <c r="F6" s="56" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I6" s="56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" ht="13.65" customHeight="1" s="90">
       <c r="A7" s="56" t="n">
@@ -16638,6 +16709,20 @@
           <t>-15% cumulative</t>
         </is>
       </c>
+      <c r="F7" s="56" t="n">
+        <v>15</v>
+      </c>
+      <c r="G7" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I7" s="56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" ht="13.65" customHeight="1" s="90">
       <c r="A8" s="56" t="n">
@@ -16660,6 +16745,20 @@
           <t>-20% cumulative (cap on cost reduction)</t>
         </is>
       </c>
+      <c r="F8" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G8" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" s="56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
       <c r="A9" s="66" t="n">
@@ -16682,6 +16781,20 @@
           <t>Ability cooldown -15%</t>
         </is>
       </c>
+      <c r="F9" s="66" t="n">
+        <v>20</v>
+      </c>
+      <c r="G9" s="66" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H9" s="66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I9" s="66" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" ht="13.65" customHeight="1" s="90">
       <c r="A10" s="56" t="n">
@@ -16700,6 +16813,20 @@
         <v/>
       </c>
       <c r="E10" s="69" t="n"/>
+      <c r="F10" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G10" s="56" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H10" s="56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I10" s="56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" ht="13.65" customHeight="1" s="90">
       <c r="A11" s="56" t="n">
@@ -16718,6 +16845,20 @@
         <v/>
       </c>
       <c r="E11" s="69" t="n"/>
+      <c r="F11" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G11" s="56" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H11" s="56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I11" s="56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" ht="13.65" customHeight="1" s="90">
       <c r="A12" s="56" t="n">
@@ -16736,6 +16877,20 @@
         <v/>
       </c>
       <c r="E12" s="69" t="n"/>
+      <c r="F12" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G12" s="56" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H12" s="56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I12" s="56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" ht="13.65" customHeight="1" s="90">
       <c r="A13" s="56" t="n">
@@ -16754,6 +16909,20 @@
         <v/>
       </c>
       <c r="E13" s="69" t="n"/>
+      <c r="F13" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G13" s="56" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H13" s="56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I13" s="56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" ht="13.65" customHeight="1" s="90">
       <c r="A14" s="66" t="n">
@@ -16773,8 +16942,22 @@
       </c>
       <c r="E14" s="68" t="inlineStr">
         <is>
-          <t>Start every match at tier 1, and unlock a second ability variant chosen at match start</t>
-        </is>
+          <t>Start every match with your first upgrade free (a second ability variant: coming later)</t>
+        </is>
+      </c>
+      <c r="F14" s="66" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" s="66" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H14" s="66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" s="66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15" ht="13.65" customHeight="1" s="90">
@@ -16794,6 +16977,20 @@
         <v/>
       </c>
       <c r="E15" s="69" t="n"/>
+      <c r="F15" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G15" s="56" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H15" s="56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" ht="13.65" customHeight="1" s="90">
       <c r="A16" s="56" t="n">
@@ -16812,6 +17009,20 @@
         <v/>
       </c>
       <c r="E16" s="69" t="n"/>
+      <c r="F16" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G16" s="56" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H16" s="56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I16" s="56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" ht="13.65" customHeight="1" s="90">
       <c r="A17" s="56" t="n">
@@ -16830,6 +17041,20 @@
         <v/>
       </c>
       <c r="E17" s="69" t="n"/>
+      <c r="F17" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" s="56" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H17" s="56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18" ht="13.65" customHeight="1" s="90">
       <c r="A18" s="56" t="n">
@@ -16848,6 +17073,20 @@
         <v/>
       </c>
       <c r="E18" s="69" t="n"/>
+      <c r="F18" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G18" s="56" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H18" s="56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" s="56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19" ht="13.65" customHeight="1" s="90">
       <c r="A19" s="66" t="n">
@@ -16867,8 +17106,22 @@
       </c>
       <c r="E19" s="68" t="inlineStr">
         <is>
-          <t>Ability cooldown -30%, and the ability gains a secondary effect</t>
-        </is>
+          <t>Ability cooldown -30% (a secondary ability effect: coming later)</t>
+        </is>
+      </c>
+      <c r="F19" s="66" t="n">
+        <v>20</v>
+      </c>
+      <c r="G19" s="66" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H19" s="66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I19" s="66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="13.65" customHeight="1" s="90">
@@ -16888,6 +17141,20 @@
         <v/>
       </c>
       <c r="E20" s="69" t="n"/>
+      <c r="F20" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G20" s="56" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H20" s="56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I20" s="56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21" ht="13.65" customHeight="1" s="90">
       <c r="A21" s="56" t="n">
@@ -16906,6 +17173,20 @@
         <v/>
       </c>
       <c r="E21" s="69" t="n"/>
+      <c r="F21" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" s="56" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H21" s="56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I21" s="56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="22" ht="13.65" customHeight="1" s="90">
       <c r="A22" s="56" t="n">
@@ -16924,6 +17205,20 @@
         <v/>
       </c>
       <c r="E22" s="69" t="n"/>
+      <c r="F22" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G22" s="56" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H22" s="56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I22" s="56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23" ht="13.65" customHeight="1" s="90">
       <c r="A23" s="56" t="n">
@@ -16942,6 +17237,20 @@
         <v/>
       </c>
       <c r="E23" s="69" t="n"/>
+      <c r="F23" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G23" s="56" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H23" s="56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I23" s="56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24" ht="13.65" customHeight="1" s="90">
       <c r="A24" s="66" t="n">
@@ -16961,8 +17270,22 @@
       </c>
       <c r="E24" s="68" t="inlineStr">
         <is>
-          <t>Mastery skin, and the crossover cap rises to tier 3 for this weapon only</t>
-        </is>
+          <t>Mastery skin (gold gun), and this hero's second upgrade path can reach tier 3</t>
+        </is>
+      </c>
+      <c r="F24" s="66" t="n">
+        <v>20</v>
+      </c>
+      <c r="G24" s="66" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H24" s="66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I24" s="66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25" ht="13.55" customHeight="1" s="90">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -2211,7 +2211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="90" min="1" max="1"/>
@@ -2279,6 +2279,11 @@
           <t>Note</t>
         </is>
       </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>Clear reward (cores)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="43" t="inlineStr">
@@ -2309,6 +2314,9 @@
           <t>The baseline. Current balance.</t>
         </is>
       </c>
+      <c r="I5" s="27" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
@@ -2339,6 +2347,9 @@
           <t>10% of enemies spawn one tier tougher.</t>
         </is>
       </c>
+      <c r="I6" s="27" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="43" t="inlineStr">
@@ -2365,6 +2376,9 @@
         <v>20</v>
       </c>
       <c r="H7" s="47" t="inlineStr"/>
+      <c r="I7" s="27" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
@@ -2394,6 +2408,9 @@
         <is>
           <t>Meant for big lobbies.</t>
         </is>
+      </c>
+      <c r="I8" s="27" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -4603,7 +4620,7 @@
     <row r="25" ht="13.65" customHeight="1" s="90">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>Core payout base</t>
+          <t>Multiplayer loss payout</t>
         </is>
       </c>
       <c r="B25" s="27" t="n">
@@ -4616,7 +4633,7 @@
       </c>
       <c r="D25" s="29" t="inlineStr">
         <is>
-          <t>Storm Cores awarded for finishing a match at all.</t>
+          <t>Every player in a multiplayer match that ends without a clear. Clears pay the Difficulty sheet reward; solo losses pay nothing.</t>
         </is>
       </c>
       <c r="E25" s="7" t="n"/>
@@ -4624,11 +4641,11 @@
     <row r="26" ht="13.65" customHeight="1" s="90">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>Core payout per round</t>
+          <t>Typical cores per match</t>
         </is>
       </c>
       <c r="B26" s="30" t="n">
-        <v>1.5</v>
+        <v>50</v>
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
@@ -4637,7 +4654,7 @@
       </c>
       <c r="D26" s="29" t="inlineStr">
         <is>
-          <t>Cores per round reached. A loss at round 27 still pays.</t>
+          <t>Planning estimate only (Mastery "Matches to earn"). Not paid out by the game.</t>
         </is>
       </c>
       <c r="E26" s="7" t="n"/>
@@ -5356,7 +5373,7 @@
       </c>
       <c r="N4" s="21" t="inlineStr">
         <is>
-          <t>Unlock round</t>
+          <t>Unlock cost (cores)</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="13.65" customHeight="1" s="90">
@@ -5569,7 +5586,7 @@
         <v>40</v>
       </c>
       <c r="N8" s="27" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
@@ -5622,7 +5639,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="27" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" ht="13.55" customHeight="1" s="90">
@@ -12843,7 +12860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:AM7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="90" min="1" max="1"/>
@@ -13001,6 +13018,11 @@
           <t>Note</t>
         </is>
       </c>
+      <c r="X4" s="21" t="inlineStr">
+        <is>
+          <t>Unlock cost (cores)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="43" t="inlineStr">
@@ -13088,6 +13110,9 @@
           <t>Mark: power = +% damage taken, (s) = length. Passes to splits.</t>
         </is>
       </c>
+      <c r="X5" s="57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
@@ -13175,6 +13200,9 @@
           <t>Overdrive: your fire rate x Tuning, towers in radius +power% fire rate.</t>
         </is>
       </c>
+      <c r="X6" s="57" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="43" t="inlineStr">
@@ -13261,6 +13289,9 @@
         <is>
           <t>Airburst: power = damage, (s) = stun, radius on the track.</t>
         </is>
+      </c>
+      <c r="X7" s="57" t="n">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -16629,7 +16660,7 @@
         <v/>
       </c>
       <c r="D5" s="92">
-        <f t="array" ref="D5">ROUND(C5/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C5/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E5" s="65" t="inlineStr">
@@ -16665,7 +16696,7 @@
         <v/>
       </c>
       <c r="D6" s="92">
-        <f t="array" ref="D6">ROUND(C6/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C6/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E6" s="65" t="inlineStr">
@@ -16701,7 +16732,7 @@
         <v/>
       </c>
       <c r="D7" s="92">
-        <f t="array" ref="D7">ROUND(C7/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C7/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E7" s="65" t="inlineStr">
@@ -16737,7 +16768,7 @@
         <v/>
       </c>
       <c r="D8" s="92">
-        <f t="array" ref="D8">ROUND(C8/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C8/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E8" s="65" t="inlineStr">
@@ -16773,7 +16804,7 @@
         <v/>
       </c>
       <c r="D9" s="93">
-        <f t="array" ref="D9">ROUND(C9/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C9/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E9" s="68" t="inlineStr">
@@ -16809,7 +16840,7 @@
         <v/>
       </c>
       <c r="D10" s="92">
-        <f t="array" ref="D10">ROUND(C10/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C10/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E10" s="69" t="n"/>
@@ -16841,7 +16872,7 @@
         <v/>
       </c>
       <c r="D11" s="92">
-        <f t="array" ref="D11">ROUND(C11/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C11/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E11" s="69" t="n"/>
@@ -16873,7 +16904,7 @@
         <v/>
       </c>
       <c r="D12" s="92">
-        <f t="array" ref="D12">ROUND(C12/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C12/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E12" s="69" t="n"/>
@@ -16905,7 +16936,7 @@
         <v/>
       </c>
       <c r="D13" s="92">
-        <f t="array" ref="D13">ROUND(C13/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C13/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E13" s="69" t="n"/>
@@ -16937,7 +16968,7 @@
         <v/>
       </c>
       <c r="D14" s="93">
-        <f t="array" ref="D14">ROUND(C14/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C14/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E14" s="68" t="inlineStr">
@@ -16973,7 +17004,7 @@
         <v/>
       </c>
       <c r="D15" s="92">
-        <f t="array" ref="D15">ROUND(C15/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C15/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E15" s="69" t="n"/>
@@ -17005,7 +17036,7 @@
         <v/>
       </c>
       <c r="D16" s="92">
-        <f t="array" ref="D16">ROUND(C16/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C16/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E16" s="69" t="n"/>
@@ -17037,7 +17068,7 @@
         <v/>
       </c>
       <c r="D17" s="92">
-        <f t="array" ref="D17">ROUND(C17/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C17/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E17" s="69" t="n"/>
@@ -17069,7 +17100,7 @@
         <v/>
       </c>
       <c r="D18" s="92">
-        <f t="array" ref="D18">ROUND(C18/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C18/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E18" s="69" t="n"/>
@@ -17101,7 +17132,7 @@
         <v/>
       </c>
       <c r="D19" s="93">
-        <f t="array" ref="D19">ROUND(C19/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C19/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E19" s="68" t="inlineStr">
@@ -17137,7 +17168,7 @@
         <v/>
       </c>
       <c r="D20" s="92">
-        <f t="array" ref="D20">ROUND(C20/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C20/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E20" s="69" t="n"/>
@@ -17169,7 +17200,7 @@
         <v/>
       </c>
       <c r="D21" s="92">
-        <f t="array" ref="D21">ROUND(C21/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C21/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E21" s="69" t="n"/>
@@ -17201,7 +17232,7 @@
         <v/>
       </c>
       <c r="D22" s="92">
-        <f t="array" ref="D22">ROUND(C22/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C22/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E22" s="69" t="n"/>
@@ -17233,7 +17264,7 @@
         <v/>
       </c>
       <c r="D23" s="92">
-        <f t="array" ref="D23">ROUND(C23/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C23/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E23" s="69" t="n"/>
@@ -17265,7 +17296,7 @@
         <v/>
       </c>
       <c r="D24" s="93">
-        <f t="array" ref="D24">ROUND(C24/('Tuning'!$B$25+'Tuning'!$B$26*25),1)</f>
+        <f>ROUND(C24/Tuning!$B$26,1)</f>
         <v/>
       </c>
       <c r="E24" s="68" t="inlineStr">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -4199,7 +4199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -5214,6 +5214,56 @@
       <c r="D61" s="29" t="inlineStr">
         <is>
           <t>Each level multiplies all tower damage by 1 + this (compounding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t>MATCH FLOW</t>
+        </is>
+      </c>
+      <c r="B63" s="24" t="n"/>
+      <c r="C63" s="32" t="n"/>
+      <c r="D63" s="32" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="26" t="inlineStr">
+        <is>
+          <t>Respawn time</t>
+        </is>
+      </c>
+      <c r="B64" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" s="28" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D64" s="29" t="inlineStr">
+        <is>
+          <t>How long after dying a player respawns during a match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="26" t="inlineStr">
+        <is>
+          <t>Results time</t>
+        </is>
+      </c>
+      <c r="B65" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C65" s="28" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D65" s="29" t="inlineStr">
+        <is>
+          <t>How long the result screen shows before everyone returns home.</t>
         </is>
       </c>
     </row>
@@ -12860,7 +12910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM7"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="90" min="1" max="1"/>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>20 permanent levels per hero, bought with Storm Cores. Cheaper upgrades, cooldowns, head starts — never damage.</t>
+          <t>20 permanent levels per hero, bought with Amber. Cheaper upgrades, cooldowns, head starts — never damage.</t>
         </is>
       </c>
       <c r="C16" s="6" t="n"/>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="I4" s="21" t="inlineStr">
         <is>
-          <t>Clear reward (cores)</t>
+          <t>Clear reward (amber)</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Promote chance: each spawn has this chance to become the next ground tier up (Husk &gt; Brute &gt; Shielded &gt; Armored &gt; Storm). Air and bosses are never promoted.</t>
+          <t>Promote chance: each spawn has this chance to become the next ground species up (Compy &gt; Raptor &gt; Pachy &gt; Ankylosaurus &gt; Gallimimus). Flyers and bosses are never promoted.</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>cores</t>
+          <t>amber</t>
         </is>
       </c>
       <c r="D25" s="29" t="inlineStr">
@@ -4641,7 +4641,7 @@
     <row r="26" ht="13.65" customHeight="1" s="90">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>Typical cores per match</t>
+          <t>Typical amber per match</t>
         </is>
       </c>
       <c r="B26" s="30" t="n">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>cores</t>
+          <t>amber</t>
         </is>
       </c>
       <c r="D26" s="29" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>cores</t>
+          <t>amber</t>
         </is>
       </c>
       <c r="D27" s="29" t="inlineStr">
@@ -5287,7 +5287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -5423,14 +5423,19 @@
       </c>
       <c r="N4" s="21" t="inlineStr">
         <is>
-          <t>Unlock cost (cores)</t>
+          <t>Unlock cost (amber)</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="inlineStr">
+        <is>
+          <t>Key</t>
         </is>
       </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B5" s="43" t="inlineStr">
@@ -5479,11 +5484,16 @@
       <c r="N5" s="27" t="n">
         <v>0</v>
       </c>
+      <c r="O5" s="43" t="inlineStr">
+        <is>
+          <t>SCOUT</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="13.65" customHeight="1" s="90">
       <c r="A6" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B6" s="43" t="inlineStr">
@@ -5532,11 +5542,16 @@
       <c r="N6" s="27" t="n">
         <v>0</v>
       </c>
+      <c r="O6" s="43" t="inlineStr">
+        <is>
+          <t>SNIPER</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="13.65" customHeight="1" s="90">
       <c r="A7" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B7" s="43" t="inlineStr">
@@ -5585,16 +5600,21 @@
       <c r="N7" s="27" t="n">
         <v>0</v>
       </c>
+      <c r="O7" s="43" t="inlineStr">
+        <is>
+          <t>GRENADIER</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="13.65" customHeight="1" s="90">
       <c r="A8" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B8" s="43" t="inlineStr">
         <is>
-          <t>Support / crowd control</t>
+          <t>Tranquilizer darts: slows and knocks out</t>
         </is>
       </c>
       <c r="C8" s="27" t="n">
@@ -5638,11 +5658,16 @@
       <c r="N8" s="27" t="n">
         <v>100</v>
       </c>
+      <c r="O8" s="43" t="inlineStr">
+        <is>
+          <t>CHILLER</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
       <c r="A9" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B9" s="43" t="inlineStr">
@@ -5690,6 +5715,11 @@
       </c>
       <c r="N9" s="27" t="n">
         <v>150</v>
+      </c>
+      <c r="O9" s="43" t="inlineStr">
+        <is>
+          <t>QUARTERMASTER</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="13.55" customHeight="1" s="90">
@@ -6125,7 +6155,7 @@
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B5" s="43" t="inlineStr">
@@ -6211,7 +6241,7 @@
     <row r="6" ht="13.65" customHeight="1" s="90">
       <c r="A6" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B6" s="43" t="inlineStr">
@@ -6297,7 +6327,7 @@
     <row r="7" ht="13.65" customHeight="1" s="90">
       <c r="A7" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B7" s="43" t="inlineStr">
@@ -6385,7 +6415,7 @@
     <row r="8" ht="13.65" customHeight="1" s="90">
       <c r="A8" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B8" s="43" t="inlineStr">
@@ -6473,7 +6503,7 @@
     <row r="9" ht="13.65" customHeight="1" s="90">
       <c r="A9" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B9" s="43" t="inlineStr">
@@ -6567,7 +6597,7 @@
     <row r="10" ht="13.65" customHeight="1" s="90">
       <c r="A10" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B10" s="43" t="inlineStr">
@@ -6653,7 +6683,7 @@
     <row r="11" ht="13.65" customHeight="1" s="90">
       <c r="A11" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B11" s="43" t="inlineStr">
@@ -6739,7 +6769,7 @@
     <row r="12" ht="13.65" customHeight="1" s="90">
       <c r="A12" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B12" s="43" t="inlineStr">
@@ -6827,7 +6857,7 @@
     <row r="13" ht="13.65" customHeight="1" s="90">
       <c r="A13" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B13" s="43" t="inlineStr">
@@ -6915,7 +6945,7 @@
     <row r="14" ht="13.65" customHeight="1" s="90">
       <c r="A14" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B14" s="43" t="inlineStr">
@@ -6961,7 +6991,7 @@
       </c>
       <c r="M14" s="43" t="inlineStr">
         <is>
-          <t>Stormgunner</t>
+          <t>Lead Rain</t>
         </is>
       </c>
       <c r="N14" s="57" t="n"/>
@@ -7003,7 +7033,7 @@
     <row r="15" ht="13.65" customHeight="1" s="90">
       <c r="A15" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B15" s="43" t="inlineStr">
@@ -7089,7 +7119,7 @@
     <row r="16" ht="13.65" customHeight="1" s="90">
       <c r="A16" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B16" s="43" t="inlineStr">
@@ -7179,7 +7209,7 @@
     <row r="17" ht="13.65" customHeight="1" s="90">
       <c r="A17" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B17" s="43" t="inlineStr">
@@ -7271,7 +7301,7 @@
     <row r="18" ht="13.65" customHeight="1" s="90">
       <c r="A18" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B18" s="43" t="inlineStr">
@@ -7365,7 +7395,7 @@
     <row r="19" ht="13.65" customHeight="1" s="90">
       <c r="A19" s="43" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Hunting Blind</t>
         </is>
       </c>
       <c r="B19" s="43" t="inlineStr">
@@ -7411,7 +7441,7 @@
       </c>
       <c r="M19" s="43" t="inlineStr">
         <is>
-          <t>Tank Buster</t>
+          <t>Hide Buster</t>
         </is>
       </c>
       <c r="N19" s="46" t="inlineStr">
@@ -7461,7 +7491,7 @@
     <row r="20" ht="13.65" customHeight="1" s="90">
       <c r="A20" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B20" s="43" t="inlineStr">
@@ -7549,7 +7579,7 @@
     <row r="21" ht="13.65" customHeight="1" s="90">
       <c r="A21" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B21" s="43" t="inlineStr">
@@ -7641,7 +7671,7 @@
     <row r="22" ht="13.65" customHeight="1" s="90">
       <c r="A22" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B22" s="43" t="inlineStr">
@@ -7733,7 +7763,7 @@
     <row r="23" ht="13.65" customHeight="1" s="90">
       <c r="A23" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B23" s="43" t="inlineStr">
@@ -7825,7 +7855,7 @@
     <row r="24" ht="13.65" customHeight="1" s="90">
       <c r="A24" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B24" s="43" t="inlineStr">
@@ -7917,7 +7947,7 @@
     <row r="25" ht="13.65" customHeight="1" s="90">
       <c r="A25" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B25" s="43" t="inlineStr">
@@ -8003,7 +8033,7 @@
     <row r="26" ht="13.65" customHeight="1" s="90">
       <c r="A26" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B26" s="43" t="inlineStr">
@@ -8089,7 +8119,7 @@
     <row r="27" ht="13.65" customHeight="1" s="90">
       <c r="A27" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B27" s="43" t="inlineStr">
@@ -8177,7 +8207,7 @@
     <row r="28" ht="13.65" customHeight="1" s="90">
       <c r="A28" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B28" s="43" t="inlineStr">
@@ -8265,7 +8295,7 @@
     <row r="29" ht="13.65" customHeight="1" s="90">
       <c r="A29" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B29" s="43" t="inlineStr">
@@ -8355,7 +8385,7 @@
     <row r="30" ht="13.65" customHeight="1" s="90">
       <c r="A30" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B30" s="43" t="inlineStr">
@@ -8441,7 +8471,7 @@
     <row r="31" ht="13.65" customHeight="1" s="90">
       <c r="A31" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B31" s="43" t="inlineStr">
@@ -8529,7 +8559,7 @@
     <row r="32" ht="13.65" customHeight="1" s="90">
       <c r="A32" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B32" s="43" t="inlineStr">
@@ -8619,7 +8649,7 @@
     <row r="33" ht="13.65" customHeight="1" s="90">
       <c r="A33" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B33" s="43" t="inlineStr">
@@ -8709,7 +8739,7 @@
     <row r="34" ht="13.65" customHeight="1" s="90">
       <c r="A34" s="43" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Longshot Perch</t>
         </is>
       </c>
       <c r="B34" s="43" t="inlineStr">
@@ -8803,7 +8833,7 @@
     <row r="35" ht="13.65" customHeight="1" s="90">
       <c r="A35" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B35" s="43" t="inlineStr">
@@ -8891,7 +8921,7 @@
     <row r="36" ht="13.65" customHeight="1" s="90">
       <c r="A36" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B36" s="43" t="inlineStr">
@@ -8979,7 +9009,7 @@
     <row r="37" ht="13.65" customHeight="1" s="90">
       <c r="A37" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B37" s="43" t="inlineStr">
@@ -9071,7 +9101,7 @@
     <row r="38" ht="13.65" customHeight="1" s="90">
       <c r="A38" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B38" s="43" t="inlineStr">
@@ -9163,7 +9193,7 @@
     <row r="39" ht="13.65" customHeight="1" s="90">
       <c r="A39" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B39" s="43" t="inlineStr">
@@ -9255,7 +9285,7 @@
     <row r="40" ht="13.65" customHeight="1" s="90">
       <c r="A40" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B40" s="43" t="inlineStr">
@@ -9345,7 +9375,7 @@
     <row r="41" ht="13.65" customHeight="1" s="90">
       <c r="A41" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B41" s="43" t="inlineStr">
@@ -9435,7 +9465,7 @@
     <row r="42" ht="13.65" customHeight="1" s="90">
       <c r="A42" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B42" s="43" t="inlineStr">
@@ -9525,7 +9555,7 @@
     <row r="43" ht="13.65" customHeight="1" s="90">
       <c r="A43" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B43" s="43" t="inlineStr">
@@ -9615,7 +9645,7 @@
     <row r="44" ht="13.65" customHeight="1" s="90">
       <c r="A44" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B44" s="43" t="inlineStr">
@@ -9705,7 +9735,7 @@
     <row r="45" ht="13.65" customHeight="1" s="90">
       <c r="A45" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B45" s="43" t="inlineStr">
@@ -9793,7 +9823,7 @@
     <row r="46" ht="13.65" customHeight="1" s="90">
       <c r="A46" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B46" s="43" t="inlineStr">
@@ -9887,7 +9917,7 @@
     <row r="47" ht="13.65" customHeight="1" s="90">
       <c r="A47" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B47" s="43" t="inlineStr">
@@ -9983,7 +10013,7 @@
     <row r="48" ht="13.65" customHeight="1" s="90">
       <c r="A48" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B48" s="43" t="inlineStr">
@@ -10079,7 +10109,7 @@
     <row r="49" ht="13.65" customHeight="1" s="90">
       <c r="A49" s="43" t="inlineStr">
         <is>
-          <t>Grenadier</t>
+          <t>Mortar Pit</t>
         </is>
       </c>
       <c r="B49" s="43" t="inlineStr">
@@ -10175,12 +10205,12 @@
     <row r="50" ht="13.65" customHeight="1" s="90">
       <c r="A50" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B50" s="43" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Sedate</t>
         </is>
       </c>
       <c r="C50" s="43" t="inlineStr">
@@ -10221,7 +10251,7 @@
       </c>
       <c r="M50" s="43" t="inlineStr">
         <is>
-          <t>Cold Snap</t>
+          <t>Mild Dose</t>
         </is>
       </c>
       <c r="N50" s="57" t="n"/>
@@ -10263,12 +10293,12 @@
     <row r="51" ht="13.65" customHeight="1" s="90">
       <c r="A51" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B51" s="43" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Sedate</t>
         </is>
       </c>
       <c r="C51" s="43" t="inlineStr">
@@ -10309,7 +10339,7 @@
       </c>
       <c r="M51" s="43" t="inlineStr">
         <is>
-          <t>Frostbite</t>
+          <t>Heavy Dose</t>
         </is>
       </c>
       <c r="N51" s="57" t="n"/>
@@ -10351,12 +10381,12 @@
     <row r="52" ht="13.65" customHeight="1" s="90">
       <c r="A52" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B52" s="43" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Sedate</t>
         </is>
       </c>
       <c r="C52" s="43" t="inlineStr">
@@ -10397,7 +10427,7 @@
       </c>
       <c r="M52" s="43" t="inlineStr">
         <is>
-          <t>Permafrost</t>
+          <t>Lingering Dose</t>
         </is>
       </c>
       <c r="N52" s="57" t="n"/>
@@ -10441,12 +10471,12 @@
     <row r="53" ht="13.65" customHeight="1" s="90">
       <c r="A53" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B53" s="43" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Sedate</t>
         </is>
       </c>
       <c r="C53" s="43" t="inlineStr">
@@ -10487,7 +10517,7 @@
       </c>
       <c r="M53" s="43" t="inlineStr">
         <is>
-          <t>Glacier Zone</t>
+          <t>Sedative Cloud</t>
         </is>
       </c>
       <c r="N53" s="57" t="n"/>
@@ -10531,12 +10561,12 @@
     <row r="54" ht="13.65" customHeight="1" s="90">
       <c r="A54" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B54" s="43" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Sedate</t>
         </is>
       </c>
       <c r="C54" s="43" t="inlineStr">
@@ -10577,7 +10607,7 @@
       </c>
       <c r="M54" s="43" t="inlineStr">
         <is>
-          <t>Absolute Zero</t>
+          <t>Hibernation</t>
         </is>
       </c>
       <c r="N54" s="57" t="n"/>
@@ -10625,12 +10655,12 @@
     <row r="55" ht="13.65" customHeight="1" s="90">
       <c r="A55" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B55" s="43" t="inlineStr">
         <is>
-          <t>Freeze</t>
+          <t>Knockout</t>
         </is>
       </c>
       <c r="C55" s="43" t="inlineStr">
@@ -10671,7 +10701,7 @@
       </c>
       <c r="M55" s="43" t="inlineStr">
         <is>
-          <t>Flash Freeze</t>
+          <t>Knockout Dart</t>
         </is>
       </c>
       <c r="N55" s="57" t="n"/>
@@ -10715,12 +10745,12 @@
     <row r="56" ht="13.65" customHeight="1" s="90">
       <c r="A56" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B56" s="43" t="inlineStr">
         <is>
-          <t>Freeze</t>
+          <t>Knockout</t>
         </is>
       </c>
       <c r="C56" s="43" t="inlineStr">
@@ -10761,7 +10791,7 @@
       </c>
       <c r="M56" s="43" t="inlineStr">
         <is>
-          <t>Deep Freeze</t>
+          <t>Heavy Sedative</t>
         </is>
       </c>
       <c r="N56" s="57" t="n"/>
@@ -10805,12 +10835,12 @@
     <row r="57" ht="13.65" customHeight="1" s="90">
       <c r="A57" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B57" s="43" t="inlineStr">
         <is>
-          <t>Freeze</t>
+          <t>Knockout</t>
         </is>
       </c>
       <c r="C57" s="43" t="inlineStr">
@@ -10851,7 +10881,7 @@
       </c>
       <c r="M57" s="43" t="inlineStr">
         <is>
-          <t>Ice Shards</t>
+          <t>Barbed Darts</t>
         </is>
       </c>
       <c r="N57" s="57" t="n"/>
@@ -10897,12 +10927,12 @@
     <row r="58" ht="13.65" customHeight="1" s="90">
       <c r="A58" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B58" s="43" t="inlineStr">
         <is>
-          <t>Freeze</t>
+          <t>Knockout</t>
         </is>
       </c>
       <c r="C58" s="43" t="inlineStr">
@@ -10943,7 +10973,7 @@
       </c>
       <c r="M58" s="43" t="inlineStr">
         <is>
-          <t>Cryo Pulse</t>
+          <t>Quick Cycle</t>
         </is>
       </c>
       <c r="N58" s="57" t="n"/>
@@ -10989,12 +11019,12 @@
     <row r="59" ht="13.65" customHeight="1" s="90">
       <c r="A59" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B59" s="43" t="inlineStr">
         <is>
-          <t>Freeze</t>
+          <t>Knockout</t>
         </is>
       </c>
       <c r="C59" s="43" t="inlineStr">
@@ -11035,7 +11065,7 @@
       </c>
       <c r="M59" s="43" t="inlineStr">
         <is>
-          <t>Stasis</t>
+          <t>Big Game Tranq</t>
         </is>
       </c>
       <c r="N59" s="57" t="n"/>
@@ -11085,12 +11115,12 @@
     <row r="60" ht="13.65" customHeight="1" s="90">
       <c r="A60" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B60" s="43" t="inlineStr">
         <is>
-          <t>Brittle</t>
+          <t>Weak Spot</t>
         </is>
       </c>
       <c r="C60" s="43" t="inlineStr">
@@ -11131,7 +11161,7 @@
       </c>
       <c r="M60" s="43" t="inlineStr">
         <is>
-          <t>Brittle</t>
+          <t>Exposed Hide</t>
         </is>
       </c>
       <c r="N60" s="57" t="n"/>
@@ -11173,12 +11203,12 @@
     <row r="61" ht="13.65" customHeight="1" s="90">
       <c r="A61" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B61" s="43" t="inlineStr">
         <is>
-          <t>Brittle</t>
+          <t>Weak Spot</t>
         </is>
       </c>
       <c r="C61" s="43" t="inlineStr">
@@ -11219,7 +11249,7 @@
       </c>
       <c r="M61" s="43" t="inlineStr">
         <is>
-          <t>Shatter</t>
+          <t>Crack Armor</t>
         </is>
       </c>
       <c r="N61" s="57" t="n"/>
@@ -11265,12 +11295,12 @@
     <row r="62" ht="13.65" customHeight="1" s="90">
       <c r="A62" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B62" s="43" t="inlineStr">
         <is>
-          <t>Brittle</t>
+          <t>Weak Spot</t>
         </is>
       </c>
       <c r="C62" s="43" t="inlineStr">
@@ -11311,7 +11341,7 @@
       </c>
       <c r="M62" s="43" t="inlineStr">
         <is>
-          <t>Cold Front</t>
+          <t>Hunter's Call</t>
         </is>
       </c>
       <c r="N62" s="57" t="n"/>
@@ -11359,12 +11389,12 @@
     <row r="63" ht="13.65" customHeight="1" s="90">
       <c r="A63" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B63" s="43" t="inlineStr">
         <is>
-          <t>Brittle</t>
+          <t>Weak Spot</t>
         </is>
       </c>
       <c r="C63" s="43" t="inlineStr">
@@ -11405,7 +11435,7 @@
       </c>
       <c r="M63" s="43" t="inlineStr">
         <is>
-          <t>Frozen Core</t>
+          <t>Vital Points</t>
         </is>
       </c>
       <c r="N63" s="57" t="n"/>
@@ -11453,12 +11483,12 @@
     <row r="64" ht="13.65" customHeight="1" s="90">
       <c r="A64" s="43" t="inlineStr">
         <is>
-          <t>Chiller</t>
+          <t>Tranq Station</t>
         </is>
       </c>
       <c r="B64" s="43" t="inlineStr">
         <is>
-          <t>Brittle</t>
+          <t>Weak Spot</t>
         </is>
       </c>
       <c r="C64" s="43" t="inlineStr">
@@ -11499,7 +11529,7 @@
       </c>
       <c r="M64" s="43" t="inlineStr">
         <is>
-          <t>Winter's Edge</t>
+          <t>Apex Predator</t>
         </is>
       </c>
       <c r="N64" s="57" t="n"/>
@@ -11549,7 +11579,7 @@
     <row r="65" ht="13.65" customHeight="1" s="90">
       <c r="A65" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B65" s="43" t="inlineStr">
@@ -11637,7 +11667,7 @@
     <row r="66" ht="13.65" customHeight="1" s="90">
       <c r="A66" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B66" s="43" t="inlineStr">
@@ -11725,7 +11755,7 @@
     <row r="67" ht="13.65" customHeight="1" s="90">
       <c r="A67" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B67" s="43" t="inlineStr">
@@ -11813,7 +11843,7 @@
     <row r="68" ht="13.65" customHeight="1" s="90">
       <c r="A68" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B68" s="43" t="inlineStr">
@@ -11901,7 +11931,7 @@
     <row r="69" ht="13.65" customHeight="1" s="90">
       <c r="A69" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B69" s="43" t="inlineStr">
@@ -11947,7 +11977,7 @@
       </c>
       <c r="M69" s="43" t="inlineStr">
         <is>
-          <t>Storm Bank</t>
+          <t>Amber Vault</t>
         </is>
       </c>
       <c r="N69" s="57" t="n"/>
@@ -11993,7 +12023,7 @@
     <row r="70" ht="13.65" customHeight="1" s="90">
       <c r="A70" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B70" s="43" t="inlineStr">
@@ -12083,7 +12113,7 @@
     <row r="71" ht="13.65" customHeight="1" s="90">
       <c r="A71" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B71" s="43" t="inlineStr">
@@ -12173,7 +12203,7 @@
     <row r="72" ht="13.65" customHeight="1" s="90">
       <c r="A72" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B72" s="43" t="inlineStr">
@@ -12263,7 +12293,7 @@
     <row r="73" ht="13.65" customHeight="1" s="90">
       <c r="A73" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B73" s="43" t="inlineStr">
@@ -12353,7 +12383,7 @@
     <row r="74" ht="13.65" customHeight="1" s="90">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B74" s="43" t="inlineStr">
@@ -12399,7 +12429,7 @@
       </c>
       <c r="M74" s="43" t="inlineStr">
         <is>
-          <t>Treasure Barge</t>
+          <t>Treasure Haul</t>
         </is>
       </c>
       <c r="N74" s="57" t="n"/>
@@ -12443,7 +12473,7 @@
     <row r="75" ht="13.65" customHeight="1" s="90">
       <c r="A75" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B75" s="43" t="inlineStr">
@@ -12531,7 +12561,7 @@
     <row r="76" ht="13.65" customHeight="1" s="90">
       <c r="A76" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B76" s="43" t="inlineStr">
@@ -12619,7 +12649,7 @@
     <row r="77" ht="13.65" customHeight="1" s="90">
       <c r="A77" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B77" s="43" t="inlineStr">
@@ -12709,7 +12739,7 @@
     <row r="78" ht="13.65" customHeight="1" s="90">
       <c r="A78" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B78" s="43" t="inlineStr">
@@ -12801,7 +12831,7 @@
     <row r="79" ht="13.65" customHeight="1" s="90">
       <c r="A79" s="43" t="inlineStr">
         <is>
-          <t>Quartermaster</t>
+          <t>Supply Camp</t>
         </is>
       </c>
       <c r="B79" s="43" t="inlineStr">
@@ -12910,7 +12940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="90" min="1" max="1"/>
@@ -12941,7 +12971,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>HEROES — free to pick; each hero is a gun plus an ability (HEROES.md)</t>
+          <t>HEROES — hunter classes, free to pick once owned; each is a weapon plus an ability (HEROES.md)</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13100,17 @@
       </c>
       <c r="X4" s="21" t="inlineStr">
         <is>
-          <t>Unlock cost (cores)</t>
+          <t>Unlock cost (amber)</t>
+        </is>
+      </c>
+      <c r="Y4" s="21" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="Z4" s="21" t="inlineStr">
+        <is>
+          <t>Ability kind</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13122,7 @@
       </c>
       <c r="B5" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="C5" s="43" t="inlineStr">
@@ -13092,7 +13132,7 @@
       </c>
       <c r="D5" s="43" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Tracking Dart</t>
         </is>
       </c>
       <c r="E5" s="57" t="n">
@@ -13163,6 +13203,16 @@
       <c r="X5" s="57" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" s="43" t="inlineStr">
+        <is>
+          <t>Revolver</t>
+        </is>
+      </c>
+      <c r="Z5" s="43" t="inlineStr">
+        <is>
+          <t>MARK</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
@@ -13172,7 +13222,7 @@
       </c>
       <c r="B6" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="C6" s="43" t="inlineStr">
@@ -13182,7 +13232,7 @@
       </c>
       <c r="D6" s="43" t="inlineStr">
         <is>
-          <t>Overdrive</t>
+          <t>Rally Cry</t>
         </is>
       </c>
       <c r="E6" s="57" t="n">
@@ -13253,6 +13303,16 @@
       <c r="X6" s="57" t="n">
         <v>75</v>
       </c>
+      <c r="Y6" s="43" t="inlineStr">
+        <is>
+          <t>Hunting Rifle</t>
+        </is>
+      </c>
+      <c r="Z6" s="43" t="inlineStr">
+        <is>
+          <t>OVERDRIVE</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="43" t="inlineStr">
@@ -13262,7 +13322,7 @@
       </c>
       <c r="B7" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="C7" s="43" t="inlineStr">
@@ -13272,7 +13332,7 @@
       </c>
       <c r="D7" s="43" t="inlineStr">
         <is>
-          <t>Airburst</t>
+          <t>Flare Strike</t>
         </is>
       </c>
       <c r="E7" s="57" t="n">
@@ -13342,6 +13402,16 @@
       </c>
       <c r="X7" s="57" t="n">
         <v>75</v>
+      </c>
+      <c r="Y7" s="43" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="Z7" s="43" t="inlineStr">
+        <is>
+          <t>AIRBURST</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -13587,7 +13657,7 @@
     <row r="5">
       <c r="A5" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B5" s="43" t="inlineStr">
@@ -13649,7 +13719,7 @@
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B6" s="43" t="inlineStr">
@@ -13711,7 +13781,7 @@
     <row r="7">
       <c r="A7" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B7" s="43" t="inlineStr">
@@ -13775,7 +13845,7 @@
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B8" s="43" t="inlineStr">
@@ -13839,7 +13909,7 @@
     <row r="9">
       <c r="A9" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B9" s="43" t="inlineStr">
@@ -13857,7 +13927,7 @@
       </c>
       <c r="E9" s="43" t="inlineStr">
         <is>
-          <t>Akimbo Storm</t>
+          <t>Akimbo Frenzy</t>
         </is>
       </c>
       <c r="F9" s="56">
@@ -13909,7 +13979,7 @@
     <row r="10">
       <c r="A10" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B10" s="43" t="inlineStr">
@@ -13969,7 +14039,7 @@
     <row r="11">
       <c r="A11" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B11" s="43" t="inlineStr">
@@ -14031,7 +14101,7 @@
     <row r="12">
       <c r="A12" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B12" s="43" t="inlineStr">
@@ -14099,7 +14169,7 @@
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B13" s="43" t="inlineStr">
@@ -14171,7 +14241,7 @@
     <row r="14">
       <c r="A14" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B14" s="43" t="inlineStr">
@@ -14245,7 +14315,7 @@
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B15" s="43" t="inlineStr">
@@ -14305,7 +14375,7 @@
     <row r="16">
       <c r="A16" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B16" s="43" t="inlineStr">
@@ -14367,7 +14437,7 @@
     <row r="17">
       <c r="A17" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B17" s="43" t="inlineStr">
@@ -14431,7 +14501,7 @@
     <row r="18">
       <c r="A18" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B18" s="43" t="inlineStr">
@@ -14497,7 +14567,7 @@
     <row r="19">
       <c r="A19" s="43" t="inlineStr">
         <is>
-          <t>Pistol</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B19" s="43" t="inlineStr">
@@ -14563,7 +14633,7 @@
     <row r="20">
       <c r="A20" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="B20" s="43" t="inlineStr">
@@ -14623,7 +14693,7 @@
     <row r="21">
       <c r="A21" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="B21" s="43" t="inlineStr">
@@ -14685,7 +14755,7 @@
     <row r="22">
       <c r="A22" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="B22" s="43" t="inlineStr">
@@ -14755,7 +14825,7 @@
     <row r="23">
       <c r="A23" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="B23" s="43" t="inlineStr">
@@ -14827,7 +14897,7 @@
     <row r="24">
       <c r="A24" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="B24" s="43" t="inlineStr">
@@ -14901,7 +14971,7 @@
     <row r="25">
       <c r="A25" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="B25" s="43" t="inlineStr">
@@ -14961,7 +15031,7 @@
     <row r="26">
       <c r="A26" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="B26" s="43" t="inlineStr">
@@ -15023,7 +15093,7 @@
     <row r="27">
       <c r="A27" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="B27" s="43" t="inlineStr">
@@ -15089,7 +15159,7 @@
     <row r="28">
       <c r="A28" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="B28" s="43" t="inlineStr">
@@ -15157,7 +15227,7 @@
     <row r="29">
       <c r="A29" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="B29" s="43" t="inlineStr">
@@ -15227,7 +15297,7 @@
     <row r="30">
       <c r="A30" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="B30" s="43" t="inlineStr">
@@ -15287,7 +15357,7 @@
     <row r="31">
       <c r="A31" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="B31" s="43" t="inlineStr">
@@ -15351,7 +15421,7 @@
     <row r="32">
       <c r="A32" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="B32" s="43" t="inlineStr">
@@ -15419,7 +15489,7 @@
     <row r="33">
       <c r="A33" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="B33" s="43" t="inlineStr">
@@ -15491,7 +15561,7 @@
     <row r="34">
       <c r="A34" s="43" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Big Game Hunter</t>
         </is>
       </c>
       <c r="B34" s="43" t="inlineStr">
@@ -15565,7 +15635,7 @@
     <row r="35">
       <c r="A35" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="B35" s="43" t="inlineStr">
@@ -15633,7 +15703,7 @@
     <row r="36">
       <c r="A36" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="B36" s="43" t="inlineStr">
@@ -15705,7 +15775,7 @@
     <row r="37">
       <c r="A37" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="B37" s="43" t="inlineStr">
@@ -15781,7 +15851,7 @@
     <row r="38">
       <c r="A38" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="B38" s="43" t="inlineStr">
@@ -15857,7 +15927,7 @@
     <row r="39">
       <c r="A39" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="B39" s="43" t="inlineStr">
@@ -15933,7 +16003,7 @@
     <row r="40">
       <c r="A40" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="B40" s="43" t="inlineStr">
@@ -15993,7 +16063,7 @@
     <row r="41">
       <c r="A41" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="B41" s="43" t="inlineStr">
@@ -16055,7 +16125,7 @@
     <row r="42">
       <c r="A42" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="B42" s="43" t="inlineStr">
@@ -16125,7 +16195,7 @@
     <row r="43">
       <c r="A43" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="B43" s="43" t="inlineStr">
@@ -16199,7 +16269,7 @@
     <row r="44">
       <c r="A44" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="B44" s="43" t="inlineStr">
@@ -16279,7 +16349,7 @@
     <row r="45">
       <c r="A45" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="B45" s="43" t="inlineStr">
@@ -16339,7 +16409,7 @@
     <row r="46">
       <c r="A46" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="B46" s="43" t="inlineStr">
@@ -16401,7 +16471,7 @@
     <row r="47">
       <c r="A47" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="B47" s="43" t="inlineStr">
@@ -16465,7 +16535,7 @@
     <row r="48">
       <c r="A48" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="B48" s="43" t="inlineStr">
@@ -16531,7 +16601,7 @@
     <row r="49">
       <c r="A49" s="43" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Brush Beater</t>
         </is>
       </c>
       <c r="B49" s="43" t="inlineStr">
@@ -16635,7 +16705,7 @@
     <row r="2" ht="13.65" customHeight="1" s="90">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Bought with Storm Cores. Head starts and unlocks only — never damage multipliers.</t>
+          <t>Bought with Amber. Head starts and unlocks only — never damage multipliers.</t>
         </is>
       </c>
       <c r="B2" s="6" t="n"/>
@@ -16658,12 +16728,12 @@
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>Core cost</t>
+          <t>Amber cost</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Cumulative cores</t>
+          <t>Cumulative amber</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -17407,7 +17477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="81" min="1" max="1"/>
@@ -17428,7 +17498,7 @@
     <row r="1" ht="18.5" customHeight="1" s="90">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>ENEMY LADDER — the splitting chain</t>
+          <t>DINOSAURS — each tier is its own species</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -17447,7 +17517,7 @@
     <row r="2" ht="13.65" customHeight="1" s="90">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Ordered bottom-up so each row's effective HP can reference its children. Do not reorder these rows.</t>
+          <t>Base HP is the species' total HP across all its sizes. A hit that empties a size shrinks the dino one size (same species, HP split evenly across sizes); the smallest size dies. Keys stay internal.</t>
         </is>
       </c>
       <c r="B2" s="6" t="n"/>
@@ -17544,6 +17614,11 @@
           <t>Boss</t>
         </is>
       </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t>Sizes</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="65" t="inlineStr">
@@ -17553,7 +17628,7 @@
       </c>
       <c r="B5" s="43" t="inlineStr">
         <is>
-          <t>Husk</t>
+          <t>Compy</t>
         </is>
       </c>
       <c r="C5" s="27" t="n">
@@ -17589,7 +17664,7 @@
       </c>
       <c r="K5" s="47" t="inlineStr">
         <is>
-          <t>Baseline. Everything else is measured in these.</t>
+          <t>Tiny pack hunter. The baseline.</t>
         </is>
       </c>
       <c r="L5" s="46" t="inlineStr">
@@ -17601,6 +17676,9 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="N5" s="60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="13.65" customHeight="1" s="90">
@@ -17611,11 +17689,11 @@
       </c>
       <c r="B6" s="43" t="inlineStr">
         <is>
-          <t>Brute Husk</t>
+          <t>Raptor</t>
         </is>
       </c>
       <c r="C6" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" s="92">
         <f t="array" ref="D6">ROUND(C6*'Tuning'!$B$16,1)</f>
@@ -17626,11 +17704,11 @@
       </c>
       <c r="F6" s="43" t="inlineStr">
         <is>
-          <t>HUSK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" s="92">
         <f t="array" ref="H6">D6+G6*H5</f>
@@ -17656,6 +17734,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="N6" s="60" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" ht="13.65" customHeight="1" s="90">
       <c r="A7" s="65" t="inlineStr">
@@ -17665,11 +17746,11 @@
       </c>
       <c r="B7" s="43" t="inlineStr">
         <is>
-          <t>Shielded Husk</t>
+          <t>Pachycephalosaurus</t>
         </is>
       </c>
       <c r="C7" s="27" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D7" s="92">
         <f t="array" ref="D7">ROUND(C7*'Tuning'!$B$16,1)</f>
@@ -17680,11 +17761,11 @@
       </c>
       <c r="F7" s="43" t="inlineStr">
         <is>
-          <t>BRUTE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" s="92">
         <f t="array" ref="H7">D7+G7*H6</f>
@@ -17699,7 +17780,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K7" s="61" t="n"/>
+      <c r="K7" s="61" t="inlineStr">
+        <is>
+          <t>Head-butter.</t>
+        </is>
+      </c>
       <c r="L7" s="46" t="inlineStr">
         <is>
           <t>No</t>
@@ -17709,6 +17794,9 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="N7" s="60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="13.65" customHeight="1" s="90">
@@ -17719,11 +17807,11 @@
       </c>
       <c r="B8" s="43" t="inlineStr">
         <is>
-          <t>Armored Husk</t>
+          <t>Ankylosaurus</t>
         </is>
       </c>
       <c r="C8" s="27" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D8" s="92">
         <f t="array" ref="D8">ROUND(C8*'Tuning'!$B$16,1)</f>
@@ -17734,11 +17822,11 @@
       </c>
       <c r="F8" s="43" t="inlineStr">
         <is>
-          <t>SHIELD</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" s="92">
         <f t="array" ref="H8">D8+G8*H7</f>
@@ -17755,7 +17843,7 @@
       </c>
       <c r="K8" s="47" t="inlineStr">
         <is>
-          <t>Immune to base Scout. Forces a damage-path purchase.</t>
+          <t>Armoured: needs armour-piercing (or a stripping Tranq) to hurt.</t>
         </is>
       </c>
       <c r="L8" s="46" t="inlineStr">
@@ -17767,6 +17855,9 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="N8" s="60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
@@ -17777,11 +17868,11 @@
       </c>
       <c r="B9" s="43" t="inlineStr">
         <is>
-          <t>Storm Husk</t>
+          <t>Gallimimus</t>
         </is>
       </c>
       <c r="C9" s="27" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="D9" s="92">
         <f t="array" ref="D9">ROUND(C9*'Tuning'!$B$16,1)</f>
@@ -17792,11 +17883,11 @@
       </c>
       <c r="F9" s="43" t="inlineStr">
         <is>
-          <t>ARMOR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H9" s="92">
         <f t="array" ref="H9">D9+G9*H8</f>
@@ -17813,7 +17904,7 @@
       </c>
       <c r="K9" s="47" t="inlineStr">
         <is>
-          <t>Fast and dense. Slow becomes mandatory here.</t>
+          <t>Fast. Slows matter.</t>
         </is>
       </c>
       <c r="L9" s="46" t="inlineStr">
@@ -17825,6 +17916,9 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="N9" s="60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="13.65" customHeight="1" s="90">
@@ -17835,11 +17929,11 @@
       </c>
       <c r="B10" s="43" t="inlineStr">
         <is>
-          <t>Drifter Llama</t>
+          <t>Pteranodon</t>
         </is>
       </c>
       <c r="C10" s="27" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D10" s="92">
         <f t="array" ref="D10">ROUND(C10*'Tuning'!$B$16,1)</f>
@@ -17850,11 +17944,11 @@
       </c>
       <c r="F10" s="43" t="inlineStr">
         <is>
-          <t>SHIELD</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="92">
         <f t="array" ref="H10">D10+G10*H7</f>
@@ -17871,7 +17965,7 @@
       </c>
       <c r="K10" s="47" t="inlineStr">
         <is>
-          <t>Flying. Grenadier cannot touch it.</t>
+          <t>Flying. The Mortar Pit cannot hit it.</t>
         </is>
       </c>
       <c r="L10" s="46" t="inlineStr">
@@ -17883,6 +17977,9 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="N10" s="60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11" ht="13.65" customHeight="1" s="90">
@@ -17893,11 +17990,11 @@
       </c>
       <c r="B11" s="43" t="inlineStr">
         <is>
-          <t>Loot Zeppelin</t>
+          <t>Triceratops</t>
         </is>
       </c>
       <c r="C11" s="27" t="n">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="D11" s="92">
         <f t="array" ref="D11">ROUND(C11*'Tuning'!$B$16,1)</f>
@@ -17908,11 +18005,11 @@
       </c>
       <c r="F11" s="43" t="inlineStr">
         <is>
-          <t>LLAMA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H11" s="92">
         <f t="array" ref="H11">D11+G11*H10</f>
@@ -17924,23 +18021,26 @@
       </c>
       <c r="J11" s="46" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K11" s="47" t="inlineStr">
+        <is>
+          <t>Ground boss.</t>
+        </is>
+      </c>
+      <c r="L11" s="46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M11" s="46" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K11" s="47" t="inlineStr">
-        <is>
-          <t>MOAB-class. Bursts into loot on death.</t>
-        </is>
-      </c>
-      <c r="L11" s="46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M11" s="46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+      <c r="N11" s="60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12" ht="13.65" customHeight="1" s="90">
@@ -17951,11 +18051,11 @@
       </c>
       <c r="B12" s="43" t="inlineStr">
         <is>
-          <t>Storm Barge</t>
+          <t>T-Rex</t>
         </is>
       </c>
       <c r="C12" s="27" t="n">
-        <v>700</v>
+        <v>1820</v>
       </c>
       <c r="D12" s="92">
         <f t="array" ref="D12">ROUND(C12*'Tuning'!$B$16,1)</f>
@@ -17966,11 +18066,11 @@
       </c>
       <c r="F12" s="43" t="inlineStr">
         <is>
-          <t>ZEP</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H12" s="92">
         <f t="array" ref="H12">D12+G12*H11</f>
@@ -17982,23 +18082,26 @@
       </c>
       <c r="J12" s="46" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" s="47" t="inlineStr">
+        <is>
+          <t>Ground boss. Round 40 finale.</t>
+        </is>
+      </c>
+      <c r="L12" s="46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M12" s="46" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K12" s="47" t="inlineStr">
-        <is>
-          <t>Round 40 finale.</t>
-        </is>
-      </c>
-      <c r="L12" s="46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M12" s="46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+      <c r="N12" s="60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13" ht="13.55" customHeight="1" s="90">
@@ -18038,7 +18141,7 @@
     <row r="15" ht="13.55" customHeight="1" s="90">
       <c r="A15" s="63" t="inlineStr">
         <is>
-          <t>Total damage needed to fully clear one enemy including every descendant it splits into. This is the number that matters for balance — a Storm Husk's 4 HP is irrelevant next to the 57 HP of husks it leaves behind.</t>
+          <t>Effective HP: total damage to clear one dino, every size included.</t>
         </is>
       </c>
       <c r="B15" s="16" t="n"/>
@@ -18170,42 +18273,42 @@
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>Husk</t>
+          <t>Compy</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Raptor</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Pachy</t>
         </is>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>Ankylosaurus</t>
         </is>
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t>Storm</t>
+          <t>Gallimimus</t>
         </is>
       </c>
       <c r="G4" s="21" t="inlineStr">
         <is>
-          <t>Llama</t>
+          <t>Pteranodon</t>
         </is>
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t>Zeppelin</t>
+          <t>Triceratops</t>
         </is>
       </c>
       <c r="I4" s="21" t="inlineStr">
         <is>
-          <t>Barge</t>
+          <t>T-Rex</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -4309,7 +4309,7 @@
       </c>
       <c r="D7" s="29" t="inlineStr">
         <is>
-          <t>Low on purpose. 40 makes a leak hurt, which is what makes Chiller worth buying.</t>
+          <t>Not used by the game: lives come from Difficulty → Starting lives (Easy 40).</t>
         </is>
       </c>
       <c r="E7" s="7" t="n"/>
@@ -21156,7 +21156,7 @@
     <row r="48" ht="13.55" customHeight="1" s="90">
       <c r="A48" s="70" t="inlineStr">
         <is>
-          <t>Round length assumes spawn gap x enemy count plus 14s of walk time. Rough, but consistent across rounds, which is what matters for comparison.</t>
+          <t>Round length assumes spawn gap x enemy count plus 14s of clear time: measured 2026-09-28, a round ends ~14s after its last spawn when nothing leaks. A dino that leaks walks the whole track (~44s), which only matters for leaks. Rough, but consistent across rounds, which is what matters for comparison.</t>
         </is>
       </c>
       <c r="B48" s="16" t="n"/>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -4199,7 +4199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -5264,6 +5264,157 @@
       <c r="D65" s="29" t="inlineStr">
         <is>
           <t>How long the result screen shows before everyone returns home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>PLAYER HEALTH / COMBAT</t>
+        </is>
+      </c>
+      <c r="B67" s="24" t="n"/>
+      <c r="C67" s="32" t="n"/>
+      <c r="D67" s="32" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="26" t="inlineStr">
+        <is>
+          <t>Player max health</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="C68" s="28" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>Every player's health. Fixed: harder rounds hurt through tougher dinos, not bigger numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="26" t="inlineStr">
+        <is>
+          <t>Heal per round</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="n">
+        <v>25</v>
+      </c>
+      <c r="C69" s="28" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="D69" s="29" t="inlineStr">
+        <is>
+          <t>Every living player heals this much when a round is cleared (capped at max).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="26" t="inlineStr">
+        <is>
+          <t>Spawn protection</t>
+        </is>
+      </c>
+      <c r="B70" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" s="28" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D70" s="29" t="inlineStr">
+        <is>
+          <t>A force field on respawn, so a player isn't bitten again the instant they're back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="26" t="inlineStr">
+        <is>
+          <t>Max resist</t>
+        </is>
+      </c>
+      <c r="B71" s="30" t="n">
+        <v>60</v>
+      </c>
+      <c r="C71" s="28" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D71" s="29" t="inlineStr">
+        <is>
+          <t>Damage resistance never goes above this. Sources don't stack: the strongest wins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="26" t="inlineStr">
+        <is>
+          <t>Max projectiles</t>
+        </is>
+      </c>
+      <c r="B72" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="C72" s="28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D72" s="29" t="inlineStr">
+        <is>
+          <t>Dino projectiles in flight at once; past this the oldest is dropped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="26" t="inlineStr">
+        <is>
+          <t>Tower HP per tier</t>
+        </is>
+      </c>
+      <c r="B73" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C73" s="28" t="inlineStr">
+        <is>
+          <t>x base</t>
+        </is>
+      </c>
+      <c r="D73" s="29" t="inlineStr">
+        <is>
+          <t>Each upgrade tier bought (any path) adds this share of the tower's base max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="26" t="inlineStr">
+        <is>
+          <t>Repair cost</t>
+        </is>
+      </c>
+      <c r="B74" s="30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C74" s="28" t="inlineStr">
+        <is>
+          <t>x spent</t>
+        </is>
+      </c>
+      <c r="D74" s="29" t="inlineStr">
+        <is>
+          <t>Repairing a tower from 0 HP costs this share of the cash put into it (less for partial damage).</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -5267,7 +5267,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
@@ -5438,7 +5437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -5454,6 +5453,8 @@
     <col width="54" customWidth="1" style="81" min="11" max="11"/>
     <col width="8.67188" customWidth="1" style="81" min="12" max="12"/>
     <col width="8.67188" customWidth="1" style="81" min="13" max="16384"/>
+    <col width="13" customWidth="1" style="90" min="14" max="14"/>
+    <col width="13" customWidth="1" style="90" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.5" customHeight="1" s="90">
@@ -5582,6 +5583,11 @@
           <t>Key</t>
         </is>
       </c>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t>Max HP</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -5640,6 +5646,9 @@
           <t>SCOUT</t>
         </is>
       </c>
+      <c r="P5" s="27" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6" ht="13.65" customHeight="1" s="90">
       <c r="A6" s="43" t="inlineStr">
@@ -5698,6 +5707,9 @@
           <t>SNIPER</t>
         </is>
       </c>
+      <c r="P6" s="27" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="7" ht="13.65" customHeight="1" s="90">
       <c r="A7" s="43" t="inlineStr">
@@ -5756,6 +5768,9 @@
           <t>GRENADIER</t>
         </is>
       </c>
+      <c r="P7" s="27" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="8" ht="13.65" customHeight="1" s="90">
       <c r="A8" s="43" t="inlineStr">
@@ -5814,6 +5829,9 @@
           <t>CHILLER</t>
         </is>
       </c>
+      <c r="P8" s="27" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
       <c r="A9" s="43" t="inlineStr">
@@ -5871,6 +5889,9 @@
         <is>
           <t>QUARTERMASTER</t>
         </is>
+      </c>
+      <c r="P9" s="27" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="10" ht="13.55" customHeight="1" s="90">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -4199,7 +4199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -5414,6 +5414,26 @@
       <c r="D74" s="29" t="inlineStr">
         <is>
           <t>Repairing a tower from 0 HP costs this share of the cash put into it (less for partial damage).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="26" t="inlineStr">
+        <is>
+          <t>Burn patch min reach</t>
+        </is>
+      </c>
+      <c r="B75" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C75" s="28" t="inlineStr">
+        <is>
+          <t>studs</t>
+        </is>
+      </c>
+      <c r="D75" s="29" t="inlineStr">
+        <is>
+          <t>Burning ground is at least this wide either side, so a hero patch with no splash (Incendiary) is visible.</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -2211,7 +2211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="90" min="1" max="1"/>
@@ -2284,6 +2284,11 @@
           <t>Clear reward (amber)</t>
         </is>
       </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>Dino damage x</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="43" t="inlineStr">
@@ -2317,6 +2322,9 @@
       <c r="I5" s="27" t="n">
         <v>50</v>
       </c>
+      <c r="J5" s="27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
@@ -2349,6 +2357,9 @@
       </c>
       <c r="I6" s="27" t="n">
         <v>100</v>
+      </c>
+      <c r="J6" s="27" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="7">
@@ -2379,6 +2390,9 @@
       <c r="I7" s="27" t="n">
         <v>150</v>
       </c>
+      <c r="J7" s="27" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
@@ -2411,6 +2425,9 @@
       </c>
       <c r="I8" s="27" t="n">
         <v>200</v>
+      </c>
+      <c r="J8" s="27" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -17669,7 +17686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="81" min="1" max="1"/>
@@ -17685,6 +17702,10 @@
     <col width="46" customWidth="1" style="81" min="11" max="11"/>
     <col width="8.67188" customWidth="1" style="81" min="12" max="13"/>
     <col width="8.67188" customWidth="1" style="81" min="14" max="16384"/>
+    <col width="14" customWidth="1" style="90" min="15" max="15"/>
+    <col width="14" customWidth="1" style="90" min="16" max="16"/>
+    <col width="14" customWidth="1" style="90" min="17" max="17"/>
+    <col width="14" customWidth="1" style="90" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.5" customHeight="1" s="90">
@@ -17811,6 +17832,26 @@
           <t>Sizes</t>
         </is>
       </c>
+      <c r="O4" s="21" t="inlineStr">
+        <is>
+          <t>Melee name</t>
+        </is>
+      </c>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t>Melee damage</t>
+        </is>
+      </c>
+      <c r="Q4" s="21" t="inlineStr">
+        <is>
+          <t>Melee every (s)</t>
+        </is>
+      </c>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t>Melee reach (studs)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="65" t="inlineStr">
@@ -17872,6 +17913,20 @@
       <c r="N5" s="60" t="n">
         <v>1</v>
       </c>
+      <c r="O5" s="43" t="inlineStr">
+        <is>
+          <t>Nip</t>
+        </is>
+      </c>
+      <c r="P5" s="60" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="60" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6" ht="13.65" customHeight="1" s="90">
       <c r="A6" s="65" t="inlineStr">
@@ -17929,6 +17984,20 @@
       <c r="N6" s="60" t="n">
         <v>2</v>
       </c>
+      <c r="O6" s="43" t="inlineStr">
+        <is>
+          <t>Slash</t>
+        </is>
+      </c>
+      <c r="P6" s="60" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="60" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R6" s="60" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="7" ht="13.65" customHeight="1" s="90">
       <c r="A7" s="65" t="inlineStr">
@@ -17990,6 +18059,20 @@
       <c r="N7" s="60" t="n">
         <v>3</v>
       </c>
+      <c r="O7" s="43" t="inlineStr">
+        <is>
+          <t>Head-Butt</t>
+        </is>
+      </c>
+      <c r="P7" s="60" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R7" s="60" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="8" ht="13.65" customHeight="1" s="90">
       <c r="A8" s="65" t="inlineStr">
@@ -18051,6 +18134,20 @@
       <c r="N8" s="60" t="n">
         <v>3</v>
       </c>
+      <c r="O8" s="43" t="inlineStr">
+        <is>
+          <t>Tail Club</t>
+        </is>
+      </c>
+      <c r="P8" s="60" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="60" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" s="60" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
       <c r="A9" s="65" t="inlineStr">
@@ -18112,6 +18209,20 @@
       <c r="N9" s="60" t="n">
         <v>3</v>
       </c>
+      <c r="O9" s="43" t="inlineStr">
+        <is>
+          <t>Kick</t>
+        </is>
+      </c>
+      <c r="P9" s="60" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="60" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="10" ht="13.65" customHeight="1" s="90">
       <c r="A10" s="65" t="inlineStr">
@@ -18173,6 +18284,16 @@
       <c r="N10" s="60" t="n">
         <v>3</v>
       </c>
+      <c r="O10" s="43" t="n"/>
+      <c r="P10" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" ht="13.65" customHeight="1" s="90">
       <c r="A11" s="65" t="inlineStr">
@@ -18234,6 +18355,20 @@
       <c r="N11" s="60" t="n">
         <v>4</v>
       </c>
+      <c r="O11" s="43" t="inlineStr">
+        <is>
+          <t>Gore</t>
+        </is>
+      </c>
+      <c r="P11" s="60" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q11" s="60" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" s="60" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" ht="13.65" customHeight="1" s="90">
       <c r="A12" s="65" t="inlineStr">
@@ -18294,6 +18429,20 @@
       </c>
       <c r="N12" s="60" t="n">
         <v>5</v>
+      </c>
+      <c r="O12" s="43" t="inlineStr">
+        <is>
+          <t>Chomp</t>
+        </is>
+      </c>
+      <c r="P12" s="60" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q12" s="60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R12" s="60" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="13.55" customHeight="1" s="90">
@@ -18348,6 +18497,13 @@
       <c r="K15" s="17" t="n"/>
       <c r="L15" s="72" t="n"/>
       <c r="M15" s="17" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="63" t="inlineStr">
+        <is>
+          <t>Melee: every dino bites the nearest tower or hunter within reach (studs sideways from the track), dealing damage x size/sizes x Difficulty Dino damage x. The Pteranodon only has a ranged attack.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -17686,7 +17686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="81" min="1" max="1"/>
@@ -17706,6 +17706,12 @@
     <col width="14" customWidth="1" style="90" min="16" max="16"/>
     <col width="14" customWidth="1" style="90" min="17" max="17"/>
     <col width="14" customWidth="1" style="90" min="18" max="18"/>
+    <col width="14" customWidth="1" style="90" min="19" max="19"/>
+    <col width="14" customWidth="1" style="90" min="20" max="20"/>
+    <col width="14" customWidth="1" style="90" min="21" max="21"/>
+    <col width="14" customWidth="1" style="90" min="22" max="22"/>
+    <col width="14" customWidth="1" style="90" min="23" max="23"/>
+    <col width="14" customWidth="1" style="90" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.5" customHeight="1" s="90">
@@ -17852,6 +17858,36 @@
           <t>Melee reach (studs)</t>
         </is>
       </c>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>Ranged name</t>
+        </is>
+      </c>
+      <c r="T4" s="21" t="inlineStr">
+        <is>
+          <t>Ranged damage</t>
+        </is>
+      </c>
+      <c r="U4" s="21" t="inlineStr">
+        <is>
+          <t>Ranged every (s)</t>
+        </is>
+      </c>
+      <c r="V4" s="21" t="inlineStr">
+        <is>
+          <t>Ranged reach (studs)</t>
+        </is>
+      </c>
+      <c r="W4" s="21" t="inlineStr">
+        <is>
+          <t>Projectile speed (studs/s)</t>
+        </is>
+      </c>
+      <c r="X4" s="21" t="inlineStr">
+        <is>
+          <t>Impact radius (studs)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="65" t="inlineStr">
@@ -17927,6 +17963,22 @@
       <c r="R5" s="60" t="n">
         <v>8</v>
       </c>
+      <c r="S5" s="43" t="n"/>
+      <c r="T5" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="13.65" customHeight="1" s="90">
       <c r="A6" s="65" t="inlineStr">
@@ -17998,6 +18050,22 @@
       <c r="R6" s="60" t="n">
         <v>9</v>
       </c>
+      <c r="S6" s="43" t="n"/>
+      <c r="T6" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="13.65" customHeight="1" s="90">
       <c r="A7" s="65" t="inlineStr">
@@ -18073,6 +18141,26 @@
       <c r="R7" s="60" t="n">
         <v>9</v>
       </c>
+      <c r="S7" s="43" t="inlineStr">
+        <is>
+          <t>Skull Toss</t>
+        </is>
+      </c>
+      <c r="T7" s="60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" s="60" t="n">
+        <v>5</v>
+      </c>
+      <c r="V7" s="60" t="n">
+        <v>22</v>
+      </c>
+      <c r="W7" s="60" t="n">
+        <v>40</v>
+      </c>
+      <c r="X7" s="60" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" ht="13.65" customHeight="1" s="90">
       <c r="A8" s="65" t="inlineStr">
@@ -18148,6 +18236,26 @@
       <c r="R8" s="60" t="n">
         <v>10</v>
       </c>
+      <c r="S8" s="43" t="inlineStr">
+        <is>
+          <t>Spike Flick</t>
+        </is>
+      </c>
+      <c r="T8" s="60" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" s="60" t="n">
+        <v>5</v>
+      </c>
+      <c r="V8" s="60" t="n">
+        <v>20</v>
+      </c>
+      <c r="W8" s="60" t="n">
+        <v>50</v>
+      </c>
+      <c r="X8" s="60" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
       <c r="A9" s="65" t="inlineStr">
@@ -18222,6 +18330,26 @@
       </c>
       <c r="R9" s="60" t="n">
         <v>9</v>
+      </c>
+      <c r="S9" s="43" t="inlineStr">
+        <is>
+          <t>Gravel Spray</t>
+        </is>
+      </c>
+      <c r="T9" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="U9" s="60" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" s="60" t="n">
+        <v>25</v>
+      </c>
+      <c r="W9" s="60" t="n">
+        <v>70</v>
+      </c>
+      <c r="X9" s="60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="13.65" customHeight="1" s="90">
@@ -18294,6 +18422,26 @@
       <c r="R10" s="60" t="n">
         <v>0</v>
       </c>
+      <c r="S10" s="43" t="inlineStr">
+        <is>
+          <t>Stone Drop</t>
+        </is>
+      </c>
+      <c r="T10" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="U10" s="60" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="60" t="n">
+        <v>18</v>
+      </c>
+      <c r="W10" s="60" t="n">
+        <v>35</v>
+      </c>
+      <c r="X10" s="60" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" ht="13.65" customHeight="1" s="90">
       <c r="A11" s="65" t="inlineStr">
@@ -18369,6 +18517,26 @@
       <c r="R11" s="60" t="n">
         <v>12</v>
       </c>
+      <c r="S11" s="43" t="inlineStr">
+        <is>
+          <t>Horn Toss</t>
+        </is>
+      </c>
+      <c r="T11" s="60" t="n">
+        <v>20</v>
+      </c>
+      <c r="U11" s="60" t="n">
+        <v>5</v>
+      </c>
+      <c r="V11" s="60" t="n">
+        <v>30</v>
+      </c>
+      <c r="W11" s="60" t="n">
+        <v>45</v>
+      </c>
+      <c r="X11" s="60" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" ht="13.65" customHeight="1" s="90">
       <c r="A12" s="65" t="inlineStr">
@@ -18443,6 +18611,26 @@
       </c>
       <c r="R12" s="60" t="n">
         <v>14</v>
+      </c>
+      <c r="S12" s="43" t="inlineStr">
+        <is>
+          <t>Bone Spit</t>
+        </is>
+      </c>
+      <c r="T12" s="60" t="n">
+        <v>35</v>
+      </c>
+      <c r="U12" s="60" t="n">
+        <v>6</v>
+      </c>
+      <c r="V12" s="60" t="n">
+        <v>35</v>
+      </c>
+      <c r="W12" s="60" t="n">
+        <v>35</v>
+      </c>
+      <c r="X12" s="60" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="13" ht="13.55" customHeight="1" s="90">
@@ -18502,6 +18690,13 @@
       <c r="A16" s="63" t="inlineStr">
         <is>
           <t>Melee: every dino bites the nearest tower or hunter within reach (studs sideways from the track), dealing damage x size/sizes x Difficulty Dino damage x. The Pteranodon only has a ranged attack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="63" t="inlineStr">
+        <is>
+          <t>Ranged: mid and high tiers also throw something at the nearest tower or hunter in reach. It flies in a straight line (no homing) to where the target was, and hurts every hunter and standing tower within the impact radius. Values are at the dino's largest size, on Easy.</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -18147,10 +18147,10 @@
         </is>
       </c>
       <c r="T7" s="60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U7" s="60" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V7" s="60" t="n">
         <v>22</v>
@@ -18242,10 +18242,10 @@
         </is>
       </c>
       <c r="T8" s="60" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U8" s="60" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V8" s="60" t="n">
         <v>20</v>
@@ -18337,10 +18337,10 @@
         </is>
       </c>
       <c r="T9" s="60" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U9" s="60" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="V9" s="60" t="n">
         <v>25</v>
@@ -18428,10 +18428,10 @@
         </is>
       </c>
       <c r="T10" s="60" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U10" s="60" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="V10" s="60" t="n">
         <v>18</v>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -2238,6 +2238,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -2430,6 +2431,8 @@
         <v>2.2</v>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -2576,7 +2579,7 @@
         <v/>
       </c>
       <c r="D5" s="92">
-        <f t="array" ref="D5">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C5),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C5),1)</f>
         <v/>
       </c>
       <c r="E5" s="56">
@@ -2613,7 +2616,7 @@
         <v/>
       </c>
       <c r="D6" s="92">
-        <f t="array" ref="D6">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C6),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C6),1)</f>
         <v/>
       </c>
       <c r="E6" s="56">
@@ -2650,7 +2653,7 @@
         <v/>
       </c>
       <c r="D7" s="92">
-        <f t="array" ref="D7">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C7),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C7),1)</f>
         <v/>
       </c>
       <c r="E7" s="56">
@@ -2687,7 +2690,7 @@
         <v/>
       </c>
       <c r="D8" s="92">
-        <f t="array" ref="D8">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C8),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C8),1)</f>
         <v/>
       </c>
       <c r="E8" s="56">
@@ -2724,7 +2727,7 @@
         <v/>
       </c>
       <c r="D9" s="92">
-        <f t="array" ref="D9">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C9),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C9),1)</f>
         <v/>
       </c>
       <c r="E9" s="56">
@@ -2761,7 +2764,7 @@
         <v/>
       </c>
       <c r="D10" s="92">
-        <f t="array" ref="D10">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C10),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C10),1)</f>
         <v/>
       </c>
       <c r="E10" s="56">
@@ -2798,7 +2801,7 @@
         <v/>
       </c>
       <c r="D11" s="92">
-        <f t="array" ref="D11">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C11),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C11),1)</f>
         <v/>
       </c>
       <c r="E11" s="56">
@@ -2835,7 +2838,7 @@
         <v/>
       </c>
       <c r="D12" s="92">
-        <f t="array" ref="D12">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C12),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C12),1)</f>
         <v/>
       </c>
       <c r="E12" s="56">
@@ -2872,7 +2875,7 @@
         <v/>
       </c>
       <c r="D13" s="92">
-        <f t="array" ref="D13">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C13),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C13),1)</f>
         <v/>
       </c>
       <c r="E13" s="56">
@@ -2909,7 +2912,7 @@
         <v/>
       </c>
       <c r="D14" s="92">
-        <f t="array" ref="D14">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C14),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C14),1)</f>
         <v/>
       </c>
       <c r="E14" s="56">
@@ -2946,7 +2949,7 @@
         <v/>
       </c>
       <c r="D15" s="93">
-        <f t="array" ref="D15">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C15),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C15),1)</f>
         <v/>
       </c>
       <c r="E15" s="66">
@@ -2983,7 +2986,7 @@
         <v/>
       </c>
       <c r="D16" s="92">
-        <f t="array" ref="D16">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C16),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C16),1)</f>
         <v/>
       </c>
       <c r="E16" s="56">
@@ -3020,7 +3023,7 @@
         <v/>
       </c>
       <c r="D17" s="92">
-        <f t="array" ref="D17">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C17),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C17),1)</f>
         <v/>
       </c>
       <c r="E17" s="56">
@@ -3057,7 +3060,7 @@
         <v/>
       </c>
       <c r="D18" s="92">
-        <f t="array" ref="D18">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C18),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C18),1)</f>
         <v/>
       </c>
       <c r="E18" s="56">
@@ -3094,7 +3097,7 @@
         <v/>
       </c>
       <c r="D19" s="92">
-        <f t="array" ref="D19">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C19),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C19),1)</f>
         <v/>
       </c>
       <c r="E19" s="56">
@@ -3131,7 +3134,7 @@
         <v/>
       </c>
       <c r="D20" s="92">
-        <f t="array" ref="D20">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C20),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C20),1)</f>
         <v/>
       </c>
       <c r="E20" s="56">
@@ -3168,7 +3171,7 @@
         <v/>
       </c>
       <c r="D21" s="92">
-        <f t="array" ref="D21">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C21),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C21),1)</f>
         <v/>
       </c>
       <c r="E21" s="56">
@@ -3205,7 +3208,7 @@
         <v/>
       </c>
       <c r="D22" s="92">
-        <f t="array" ref="D22">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C22),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C22),1)</f>
         <v/>
       </c>
       <c r="E22" s="56">
@@ -3242,7 +3245,7 @@
         <v/>
       </c>
       <c r="D23" s="92">
-        <f t="array" ref="D23">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C23),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C23),1)</f>
         <v/>
       </c>
       <c r="E23" s="56">
@@ -3279,7 +3282,7 @@
         <v/>
       </c>
       <c r="D24" s="92">
-        <f t="array" ref="D24">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C24),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C24),1)</f>
         <v/>
       </c>
       <c r="E24" s="56">
@@ -3316,7 +3319,7 @@
         <v/>
       </c>
       <c r="D25" s="93">
-        <f t="array" ref="D25">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C25),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C25),1)</f>
         <v/>
       </c>
       <c r="E25" s="66">
@@ -3353,7 +3356,7 @@
         <v/>
       </c>
       <c r="D26" s="92">
-        <f t="array" ref="D26">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C26),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C26),1)</f>
         <v/>
       </c>
       <c r="E26" s="56">
@@ -3390,7 +3393,7 @@
         <v/>
       </c>
       <c r="D27" s="92">
-        <f t="array" ref="D27">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C27),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C27),1)</f>
         <v/>
       </c>
       <c r="E27" s="56">
@@ -3427,7 +3430,7 @@
         <v/>
       </c>
       <c r="D28" s="92">
-        <f t="array" ref="D28">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C28),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C28),1)</f>
         <v/>
       </c>
       <c r="E28" s="56">
@@ -3464,7 +3467,7 @@
         <v/>
       </c>
       <c r="D29" s="92">
-        <f t="array" ref="D29">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C29),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C29),1)</f>
         <v/>
       </c>
       <c r="E29" s="56">
@@ -3501,7 +3504,7 @@
         <v/>
       </c>
       <c r="D30" s="92">
-        <f t="array" ref="D30">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C30),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C30),1)</f>
         <v/>
       </c>
       <c r="E30" s="56">
@@ -3538,7 +3541,7 @@
         <v/>
       </c>
       <c r="D31" s="92">
-        <f t="array" ref="D31">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C31),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C31),1)</f>
         <v/>
       </c>
       <c r="E31" s="56">
@@ -3575,7 +3578,7 @@
         <v/>
       </c>
       <c r="D32" s="92">
-        <f t="array" ref="D32">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C32),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C32),1)</f>
         <v/>
       </c>
       <c r="E32" s="56">
@@ -3612,7 +3615,7 @@
         <v/>
       </c>
       <c r="D33" s="92">
-        <f t="array" ref="D33">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C33),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C33),1)</f>
         <v/>
       </c>
       <c r="E33" s="56">
@@ -3649,7 +3652,7 @@
         <v/>
       </c>
       <c r="D34" s="92">
-        <f t="array" ref="D34">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C34),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C34),1)</f>
         <v/>
       </c>
       <c r="E34" s="56">
@@ -3686,7 +3689,7 @@
         <v/>
       </c>
       <c r="D35" s="93">
-        <f t="array" ref="D35">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C35),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C35),1)</f>
         <v/>
       </c>
       <c r="E35" s="66">
@@ -3723,7 +3726,7 @@
         <v/>
       </c>
       <c r="D36" s="92">
-        <f t="array" ref="D36">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C36),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C36),1)</f>
         <v/>
       </c>
       <c r="E36" s="56">
@@ -3760,7 +3763,7 @@
         <v/>
       </c>
       <c r="D37" s="92">
-        <f t="array" ref="D37">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C37),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C37),1)</f>
         <v/>
       </c>
       <c r="E37" s="56">
@@ -3797,7 +3800,7 @@
         <v/>
       </c>
       <c r="D38" s="92">
-        <f t="array" ref="D38">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C38),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C38),1)</f>
         <v/>
       </c>
       <c r="E38" s="56">
@@ -3834,7 +3837,7 @@
         <v/>
       </c>
       <c r="D39" s="92">
-        <f t="array" ref="D39">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C39),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C39),1)</f>
         <v/>
       </c>
       <c r="E39" s="56">
@@ -3871,7 +3874,7 @@
         <v/>
       </c>
       <c r="D40" s="92">
-        <f t="array" ref="D40">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C40),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C40),1)</f>
         <v/>
       </c>
       <c r="E40" s="56">
@@ -3908,7 +3911,7 @@
         <v/>
       </c>
       <c r="D41" s="92">
-        <f t="array" ref="D41">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C41),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C41),1)</f>
         <v/>
       </c>
       <c r="E41" s="56">
@@ -3945,7 +3948,7 @@
         <v/>
       </c>
       <c r="D42" s="92">
-        <f t="array" ref="D42">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C42),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C42),1)</f>
         <v/>
       </c>
       <c r="E42" s="56">
@@ -3982,7 +3985,7 @@
         <v/>
       </c>
       <c r="D43" s="92">
-        <f t="array" ref="D43">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C43),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C43),1)</f>
         <v/>
       </c>
       <c r="E43" s="56">
@@ -4019,7 +4022,7 @@
         <v/>
       </c>
       <c r="D44" s="93">
-        <f t="array" ref="D44">ROUND('Towers'!$C$11*POWER('Tuning'!$B$12/'Tuning'!$B$13,C44),1)</f>
+        <f>ROUND('Towers'!$C$13*POWER('Tuning'!$B$12/'Tuning'!$B$13,C44),1)</f>
         <v/>
       </c>
       <c r="E44" s="66">
@@ -4894,6 +4897,7 @@
       </c>
       <c r="E38" s="17" t="n"/>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="31" t="inlineStr">
         <is>
@@ -4964,6 +4968,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="31" t="inlineStr">
         <is>
@@ -5114,6 +5119,7 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
         <is>
@@ -5164,6 +5170,7 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="31" t="inlineStr">
         <is>
@@ -5234,6 +5241,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
@@ -5284,6 +5292,7 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
@@ -5474,7 +5483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -5492,6 +5501,8 @@
     <col width="8.67188" customWidth="1" style="81" min="13" max="16384"/>
     <col width="13" customWidth="1" style="90" min="14" max="14"/>
     <col width="13" customWidth="1" style="90" min="16" max="16"/>
+    <col width="13" customWidth="1" style="90" min="17" max="17"/>
+    <col width="13" customWidth="1" style="90" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.5" customHeight="1" s="90">
@@ -5625,6 +5636,16 @@
           <t>Max HP</t>
         </is>
       </c>
+      <c r="Q4" s="21" t="inlineStr">
+        <is>
+          <t>Heal /s</t>
+        </is>
+      </c>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t>Resist %</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -5686,6 +5707,12 @@
       <c r="P5" s="27" t="n">
         <v>100</v>
       </c>
+      <c r="Q5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="13.65" customHeight="1" s="90">
       <c r="A6" s="43" t="inlineStr">
@@ -5747,6 +5774,12 @@
       <c r="P6" s="27" t="n">
         <v>80</v>
       </c>
+      <c r="Q6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="13.65" customHeight="1" s="90">
       <c r="A7" s="43" t="inlineStr">
@@ -5808,6 +5841,12 @@
       <c r="P7" s="27" t="n">
         <v>150</v>
       </c>
+      <c r="Q7" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="13.65" customHeight="1" s="90">
       <c r="A8" s="43" t="inlineStr">
@@ -5869,6 +5908,12 @@
       <c r="P8" s="27" t="n">
         <v>120</v>
       </c>
+      <c r="Q8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
       <c r="A9" s="43" t="inlineStr">
@@ -5929,6 +5974,12 @@
       </c>
       <c r="P9" s="27" t="n">
         <v>200</v>
+      </c>
+      <c r="Q9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="13.55" customHeight="1" s="90">
@@ -5948,27 +5999,87 @@
     <row r="11" ht="13.65" customHeight="1" s="90">
       <c r="A11" s="43" t="inlineStr">
         <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>Defence: damage resistance, no attack</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>600</v>
+      </c>
+      <c r="D11" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="92">
+        <f t="array" ref="G11">D11*E11*F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="I11" s="46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="47" t="inlineStr">
+        <is>
+          <t>Never shoots. Towers and hunters in range take less damage; its paths add thorns, tower buffs and hunter handling.</t>
+        </is>
+      </c>
+      <c r="L11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="27" t="n">
+        <v>150</v>
+      </c>
+      <c r="O11" s="43" t="inlineStr">
+        <is>
+          <t>ARMORY</t>
+        </is>
+      </c>
+      <c r="P11" s="27" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="27" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
           <t>Cost per DPS (Scout baseline)</t>
         </is>
       </c>
-      <c r="B11" s="52" t="n"/>
-      <c r="C11" s="92">
-        <f t="array" ref="C11">C5/G5</f>
-        <v/>
-      </c>
-      <c r="D11" s="53" t="inlineStr">
+      <c r="B13" s="52" t="n"/>
+      <c r="C13" s="92">
+        <f t="array" ref="C13">C5/G5</f>
+        <v/>
+      </c>
+      <c r="D13" s="53" t="inlineStr">
         <is>
           <t>Cash needed to buy 1 DPS at tier 0. Balance Check uses this.</t>
         </is>
       </c>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="16" t="n"/>
-      <c r="K11" s="17" t="n"/>
-      <c r="L11" s="54" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
@@ -5990,7 +6101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT79"/>
+  <dimension ref="A1:BA94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -6360,6 +6471,41 @@
           <t>Sell refund</t>
         </is>
       </c>
+      <c r="AU4" s="21" t="inlineStr">
+        <is>
+          <t>Resist %</t>
+        </is>
+      </c>
+      <c r="AV4" s="21" t="inlineStr">
+        <is>
+          <t>Thorns damage</t>
+        </is>
+      </c>
+      <c r="AW4" s="21" t="inlineStr">
+        <is>
+          <t>Stuns biters (s)</t>
+        </is>
+      </c>
+      <c r="AX4" s="21" t="inlineStr">
+        <is>
+          <t>Hunter recoil x</t>
+        </is>
+      </c>
+      <c r="AY4" s="21" t="inlineStr">
+        <is>
+          <t>Hunter reload x</t>
+        </is>
+      </c>
+      <c r="AZ4" s="21" t="inlineStr">
+        <is>
+          <t>Hunter spread x</t>
+        </is>
+      </c>
+      <c r="BA4" s="21" t="inlineStr">
+        <is>
+          <t>Hunter fire rate %</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -13127,6 +13273,1469 @@
       </c>
       <c r="AT79" s="57" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="43" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B80" s="43" t="inlineStr">
+        <is>
+          <t>Plating</t>
+        </is>
+      </c>
+      <c r="C80" s="43" t="inlineStr">
+        <is>
+          <t>resistance</t>
+        </is>
+      </c>
+      <c r="D80" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="56">
+        <f>ROUND('Towers'!$C$11*POWER('Tuning'!$B$12,D80),0)</f>
+        <v/>
+      </c>
+      <c r="F80" s="56">
+        <f>'Towers'!$C$11+E80</f>
+        <v/>
+      </c>
+      <c r="G80" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L80" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" s="43" t="inlineStr">
+        <is>
+          <t>Hide Padding</t>
+        </is>
+      </c>
+      <c r="N80" s="57" t="n"/>
+      <c r="O80" s="57" t="n"/>
+      <c r="P80" s="57" t="n"/>
+      <c r="Q80" s="57" t="n"/>
+      <c r="R80" s="57" t="n"/>
+      <c r="S80" s="57" t="n"/>
+      <c r="T80" s="57" t="n"/>
+      <c r="U80" s="57" t="n"/>
+      <c r="V80" s="57" t="n"/>
+      <c r="W80" s="57" t="n"/>
+      <c r="X80" s="57" t="n"/>
+      <c r="Y80" s="57" t="n"/>
+      <c r="Z80" s="57" t="n"/>
+      <c r="AA80" s="57" t="n"/>
+      <c r="AB80" s="57" t="n"/>
+      <c r="AC80" s="57" t="n"/>
+      <c r="AD80" s="57" t="n"/>
+      <c r="AE80" s="57" t="n"/>
+      <c r="AF80" s="57" t="n"/>
+      <c r="AG80" s="57" t="n"/>
+      <c r="AH80" s="57" t="n"/>
+      <c r="AI80" s="57" t="n"/>
+      <c r="AJ80" s="57" t="n"/>
+      <c r="AK80" s="57" t="n"/>
+      <c r="AL80" s="57" t="n"/>
+      <c r="AM80" s="57" t="n"/>
+      <c r="AN80" s="57" t="n"/>
+      <c r="AO80" s="57" t="n"/>
+      <c r="AP80" s="57" t="n"/>
+      <c r="AQ80" s="57" t="n"/>
+      <c r="AR80" s="57" t="n"/>
+      <c r="AS80" s="57" t="n"/>
+      <c r="AT80" s="57" t="n"/>
+      <c r="AU80" s="57" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV80" s="57" t="n"/>
+      <c r="AW80" s="57" t="n"/>
+      <c r="AX80" s="57" t="n"/>
+      <c r="AY80" s="57" t="n"/>
+      <c r="AZ80" s="57" t="n"/>
+      <c r="BA80" s="57" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="43" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B81" s="43" t="inlineStr">
+        <is>
+          <t>Plating</t>
+        </is>
+      </c>
+      <c r="C81" s="43" t="inlineStr">
+        <is>
+          <t>resistance</t>
+        </is>
+      </c>
+      <c r="D81" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" s="56">
+        <f>ROUND('Towers'!$C$11*POWER('Tuning'!$B$12,D81),0)</f>
+        <v/>
+      </c>
+      <c r="F81" s="56">
+        <f>F80+E81</f>
+        <v/>
+      </c>
+      <c r="G81" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L81" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" s="43" t="inlineStr">
+        <is>
+          <t>Iron Plates</t>
+        </is>
+      </c>
+      <c r="N81" s="57" t="n"/>
+      <c r="O81" s="57" t="n"/>
+      <c r="P81" s="57" t="n"/>
+      <c r="Q81" s="57" t="n"/>
+      <c r="R81" s="57" t="n"/>
+      <c r="S81" s="57" t="n"/>
+      <c r="T81" s="57" t="n"/>
+      <c r="U81" s="57" t="n"/>
+      <c r="V81" s="57" t="n"/>
+      <c r="W81" s="57" t="n"/>
+      <c r="X81" s="57" t="n"/>
+      <c r="Y81" s="57" t="n"/>
+      <c r="Z81" s="57" t="n"/>
+      <c r="AA81" s="57" t="n"/>
+      <c r="AB81" s="57" t="n"/>
+      <c r="AC81" s="57" t="n"/>
+      <c r="AD81" s="57" t="n"/>
+      <c r="AE81" s="57" t="n"/>
+      <c r="AF81" s="57" t="n"/>
+      <c r="AG81" s="57" t="n"/>
+      <c r="AH81" s="57" t="n"/>
+      <c r="AI81" s="57" t="n"/>
+      <c r="AJ81" s="57" t="n"/>
+      <c r="AK81" s="57" t="n"/>
+      <c r="AL81" s="57" t="n"/>
+      <c r="AM81" s="57" t="n"/>
+      <c r="AN81" s="57" t="n"/>
+      <c r="AO81" s="57" t="n"/>
+      <c r="AP81" s="57" t="n"/>
+      <c r="AQ81" s="57" t="n"/>
+      <c r="AR81" s="57" t="n"/>
+      <c r="AS81" s="57" t="n"/>
+      <c r="AT81" s="57" t="n"/>
+      <c r="AU81" s="57" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV81" s="57" t="n"/>
+      <c r="AW81" s="57" t="n"/>
+      <c r="AX81" s="57" t="n"/>
+      <c r="AY81" s="57" t="n"/>
+      <c r="AZ81" s="57" t="n"/>
+      <c r="BA81" s="57" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="43" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B82" s="43" t="inlineStr">
+        <is>
+          <t>Plating</t>
+        </is>
+      </c>
+      <c r="C82" s="43" t="inlineStr">
+        <is>
+          <t>resistance</t>
+        </is>
+      </c>
+      <c r="D82" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" s="56">
+        <f>ROUND('Towers'!$C$11*POWER('Tuning'!$B$12,D82),0)</f>
+        <v/>
+      </c>
+      <c r="F82" s="56">
+        <f>F81+E82</f>
+        <v/>
+      </c>
+      <c r="G82" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L82" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" s="43" t="inlineStr">
+        <is>
+          <t>Thorn Plating</t>
+        </is>
+      </c>
+      <c r="N82" s="57" t="n"/>
+      <c r="O82" s="57" t="n"/>
+      <c r="P82" s="57" t="n"/>
+      <c r="Q82" s="57" t="n"/>
+      <c r="R82" s="57" t="n"/>
+      <c r="S82" s="57" t="n"/>
+      <c r="T82" s="57" t="n"/>
+      <c r="U82" s="57" t="n"/>
+      <c r="V82" s="57" t="n"/>
+      <c r="W82" s="57" t="n"/>
+      <c r="X82" s="57" t="n"/>
+      <c r="Y82" s="57" t="n"/>
+      <c r="Z82" s="57" t="n"/>
+      <c r="AA82" s="57" t="n"/>
+      <c r="AB82" s="57" t="n"/>
+      <c r="AC82" s="57" t="n"/>
+      <c r="AD82" s="57" t="n"/>
+      <c r="AE82" s="57" t="n"/>
+      <c r="AF82" s="57" t="n"/>
+      <c r="AG82" s="57" t="n"/>
+      <c r="AH82" s="57" t="n"/>
+      <c r="AI82" s="57" t="n"/>
+      <c r="AJ82" s="57" t="n"/>
+      <c r="AK82" s="57" t="n"/>
+      <c r="AL82" s="57" t="n"/>
+      <c r="AM82" s="57" t="n"/>
+      <c r="AN82" s="57" t="n"/>
+      <c r="AO82" s="57" t="n"/>
+      <c r="AP82" s="57" t="n"/>
+      <c r="AQ82" s="57" t="n"/>
+      <c r="AR82" s="57" t="n"/>
+      <c r="AS82" s="57" t="n"/>
+      <c r="AT82" s="57" t="n"/>
+      <c r="AU82" s="57" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV82" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW82" s="57" t="n"/>
+      <c r="AX82" s="57" t="n"/>
+      <c r="AY82" s="57" t="n"/>
+      <c r="AZ82" s="57" t="n"/>
+      <c r="BA82" s="57" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="43" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B83" s="43" t="inlineStr">
+        <is>
+          <t>Plating</t>
+        </is>
+      </c>
+      <c r="C83" s="43" t="inlineStr">
+        <is>
+          <t>resistance</t>
+        </is>
+      </c>
+      <c r="D83" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" s="56">
+        <f>ROUND('Towers'!$C$11*POWER('Tuning'!$B$12,D83),0)</f>
+        <v/>
+      </c>
+      <c r="F83" s="56">
+        <f>F82+E83</f>
+        <v/>
+      </c>
+      <c r="G83" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L83" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" s="43" t="inlineStr">
+        <is>
+          <t>Tempered Steel</t>
+        </is>
+      </c>
+      <c r="N83" s="57" t="n"/>
+      <c r="O83" s="57" t="n"/>
+      <c r="P83" s="57" t="n"/>
+      <c r="Q83" s="57" t="n"/>
+      <c r="R83" s="57" t="n"/>
+      <c r="S83" s="57" t="n"/>
+      <c r="T83" s="57" t="n"/>
+      <c r="U83" s="57" t="n"/>
+      <c r="V83" s="57" t="n"/>
+      <c r="W83" s="57" t="n"/>
+      <c r="X83" s="57" t="n"/>
+      <c r="Y83" s="57" t="n"/>
+      <c r="Z83" s="57" t="n"/>
+      <c r="AA83" s="57" t="n"/>
+      <c r="AB83" s="57" t="n"/>
+      <c r="AC83" s="57" t="n"/>
+      <c r="AD83" s="57" t="n"/>
+      <c r="AE83" s="57" t="n"/>
+      <c r="AF83" s="57" t="n"/>
+      <c r="AG83" s="57" t="n"/>
+      <c r="AH83" s="57" t="n"/>
+      <c r="AI83" s="57" t="n"/>
+      <c r="AJ83" s="57" t="n"/>
+      <c r="AK83" s="57" t="n"/>
+      <c r="AL83" s="57" t="n"/>
+      <c r="AM83" s="57" t="n"/>
+      <c r="AN83" s="57" t="n"/>
+      <c r="AO83" s="57" t="n"/>
+      <c r="AP83" s="57" t="n"/>
+      <c r="AQ83" s="57" t="n"/>
+      <c r="AR83" s="57" t="n"/>
+      <c r="AS83" s="57" t="n"/>
+      <c r="AT83" s="57" t="n"/>
+      <c r="AU83" s="57" t="n">
+        <v>35</v>
+      </c>
+      <c r="AV83" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW83" s="57" t="n"/>
+      <c r="AX83" s="57" t="n"/>
+      <c r="AY83" s="57" t="n"/>
+      <c r="AZ83" s="57" t="n"/>
+      <c r="BA83" s="57" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="43" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B84" s="43" t="inlineStr">
+        <is>
+          <t>Plating</t>
+        </is>
+      </c>
+      <c r="C84" s="43" t="inlineStr">
+        <is>
+          <t>resistance</t>
+        </is>
+      </c>
+      <c r="D84" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E84" s="56">
+        <f>ROUND('Towers'!$C$11*POWER('Tuning'!$B$12,D84),0)</f>
+        <v/>
+      </c>
+      <c r="F84" s="56">
+        <f>F83+E84</f>
+        <v/>
+      </c>
+      <c r="G84" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L84" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" s="43" t="inlineStr">
+        <is>
+          <t>Bulwark</t>
+        </is>
+      </c>
+      <c r="N84" s="57" t="n"/>
+      <c r="O84" s="57" t="n"/>
+      <c r="P84" s="57" t="n"/>
+      <c r="Q84" s="57" t="n"/>
+      <c r="R84" s="57" t="n"/>
+      <c r="S84" s="57" t="n"/>
+      <c r="T84" s="57" t="n"/>
+      <c r="U84" s="57" t="n"/>
+      <c r="V84" s="57" t="n"/>
+      <c r="W84" s="57" t="n"/>
+      <c r="X84" s="57" t="n"/>
+      <c r="Y84" s="57" t="n"/>
+      <c r="Z84" s="57" t="n"/>
+      <c r="AA84" s="57" t="n"/>
+      <c r="AB84" s="57" t="n"/>
+      <c r="AC84" s="57" t="n"/>
+      <c r="AD84" s="57" t="n"/>
+      <c r="AE84" s="57" t="n"/>
+      <c r="AF84" s="57" t="n"/>
+      <c r="AG84" s="57" t="n"/>
+      <c r="AH84" s="57" t="n"/>
+      <c r="AI84" s="57" t="n"/>
+      <c r="AJ84" s="57" t="n"/>
+      <c r="AK84" s="57" t="n"/>
+      <c r="AL84" s="57" t="n"/>
+      <c r="AM84" s="57" t="n"/>
+      <c r="AN84" s="57" t="n"/>
+      <c r="AO84" s="57" t="n"/>
+      <c r="AP84" s="57" t="n"/>
+      <c r="AQ84" s="57" t="n"/>
+      <c r="AR84" s="57" t="n"/>
+      <c r="AS84" s="57" t="n"/>
+      <c r="AT84" s="57" t="n"/>
+      <c r="AU84" s="57" t="n">
+        <v>45</v>
+      </c>
+      <c r="AV84" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW84" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX84" s="57" t="n"/>
+      <c r="AY84" s="57" t="n"/>
+      <c r="AZ84" s="57" t="n"/>
+      <c r="BA84" s="57" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="43" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B85" s="43" t="inlineStr">
+        <is>
+          <t>Gunsmith</t>
+        </is>
+      </c>
+      <c r="C85" s="43" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D85" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="56">
+        <f>ROUND('Towers'!$C$11*POWER('Tuning'!$B$12,D85),0)</f>
+        <v/>
+      </c>
+      <c r="F85" s="56">
+        <f>'Towers'!$C$11+E85</f>
+        <v/>
+      </c>
+      <c r="G85" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L85" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" s="43" t="inlineStr">
+        <is>
+          <t>Oiled Actions</t>
+        </is>
+      </c>
+      <c r="N85" s="57" t="n"/>
+      <c r="O85" s="57" t="n"/>
+      <c r="P85" s="57" t="n"/>
+      <c r="Q85" s="57" t="n"/>
+      <c r="R85" s="57" t="n"/>
+      <c r="S85" s="57" t="n"/>
+      <c r="T85" s="57" t="n"/>
+      <c r="U85" s="57" t="n"/>
+      <c r="V85" s="57" t="n"/>
+      <c r="W85" s="57" t="n"/>
+      <c r="X85" s="57" t="n"/>
+      <c r="Y85" s="57" t="n"/>
+      <c r="Z85" s="57" t="n"/>
+      <c r="AA85" s="57" t="n"/>
+      <c r="AB85" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC85" s="57" t="n"/>
+      <c r="AD85" s="57" t="n"/>
+      <c r="AE85" s="57" t="n"/>
+      <c r="AF85" s="57" t="n"/>
+      <c r="AG85" s="57" t="n"/>
+      <c r="AH85" s="57" t="n"/>
+      <c r="AI85" s="57" t="n"/>
+      <c r="AJ85" s="57" t="n"/>
+      <c r="AK85" s="57" t="n"/>
+      <c r="AL85" s="57" t="n"/>
+      <c r="AM85" s="57" t="n"/>
+      <c r="AN85" s="57" t="n"/>
+      <c r="AO85" s="57" t="n"/>
+      <c r="AP85" s="57" t="n"/>
+      <c r="AQ85" s="57" t="n"/>
+      <c r="AR85" s="57" t="n"/>
+      <c r="AS85" s="57" t="n"/>
+      <c r="AT85" s="57" t="n"/>
+      <c r="AU85" s="57" t="n"/>
+      <c r="AV85" s="57" t="n"/>
+      <c r="AW85" s="57" t="n"/>
+      <c r="AX85" s="57" t="n"/>
+      <c r="AY85" s="57" t="n"/>
+      <c r="AZ85" s="57" t="n"/>
+      <c r="BA85" s="57" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="43" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B86" s="43" t="inlineStr">
+        <is>
+          <t>Gunsmith</t>
+        </is>
+      </c>
+      <c r="C86" s="43" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D86" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" s="56">
+        <f>ROUND('Towers'!$C$11*POWER('Tuning'!$B$12,D86),0)</f>
+        <v/>
+      </c>
+      <c r="F86" s="56">
+        <f>F85+E86</f>
+        <v/>
+      </c>
+      <c r="G86" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L86" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" s="43" t="inlineStr">
+        <is>
+          <t>Hand Loads</t>
+        </is>
+      </c>
+      <c r="N86" s="57" t="n"/>
+      <c r="O86" s="57" t="n"/>
+      <c r="P86" s="57" t="n"/>
+      <c r="Q86" s="57" t="n"/>
+      <c r="R86" s="57" t="n"/>
+      <c r="S86" s="57" t="n"/>
+      <c r="T86" s="57" t="n"/>
+      <c r="U86" s="57" t="n"/>
+      <c r="V86" s="57" t="n"/>
+      <c r="W86" s="57" t="n"/>
+      <c r="X86" s="57" t="n"/>
+      <c r="Y86" s="57" t="n"/>
+      <c r="Z86" s="57" t="n"/>
+      <c r="AA86" s="57" t="n"/>
+      <c r="AB86" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC86" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD86" s="57" t="n"/>
+      <c r="AE86" s="57" t="n"/>
+      <c r="AF86" s="57" t="n"/>
+      <c r="AG86" s="57" t="n"/>
+      <c r="AH86" s="57" t="n"/>
+      <c r="AI86" s="57" t="n"/>
+      <c r="AJ86" s="57" t="n"/>
+      <c r="AK86" s="57" t="n"/>
+      <c r="AL86" s="57" t="n"/>
+      <c r="AM86" s="57" t="n"/>
+      <c r="AN86" s="57" t="n"/>
+      <c r="AO86" s="57" t="n"/>
+      <c r="AP86" s="57" t="n"/>
+      <c r="AQ86" s="57" t="n"/>
+      <c r="AR86" s="57" t="n"/>
+      <c r="AS86" s="57" t="n"/>
+      <c r="AT86" s="57" t="n"/>
+      <c r="AU86" s="57" t="n"/>
+      <c r="AV86" s="57" t="n"/>
+      <c r="AW86" s="57" t="n"/>
+      <c r="AX86" s="57" t="n"/>
+      <c r="AY86" s="57" t="n"/>
+      <c r="AZ86" s="57" t="n"/>
+      <c r="BA86" s="57" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="43" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B87" s="43" t="inlineStr">
+        <is>
+          <t>Gunsmith</t>
+        </is>
+      </c>
+      <c r="C87" s="43" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D87" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E87" s="56">
+        <f>ROUND('Towers'!$C$11*POWER('Tuning'!$B$12,D87),0)</f>
+        <v/>
+      </c>
+      <c r="F87" s="56">
+        <f>F86+E87</f>
+        <v/>
+      </c>
+      <c r="G87" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L87" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" s="43" t="inlineStr">
+        <is>
+          <t>Piercing Rounds</t>
+        </is>
+      </c>
+      <c r="N87" s="57" t="n"/>
+      <c r="O87" s="57" t="n"/>
+      <c r="P87" s="57" t="n"/>
+      <c r="Q87" s="57" t="n"/>
+      <c r="R87" s="57" t="n"/>
+      <c r="S87" s="57" t="n"/>
+      <c r="T87" s="57" t="n"/>
+      <c r="U87" s="57" t="n"/>
+      <c r="V87" s="57" t="n"/>
+      <c r="W87" s="57" t="n"/>
+      <c r="X87" s="57" t="n"/>
+      <c r="Y87" s="57" t="n"/>
+      <c r="Z87" s="57" t="n"/>
+      <c r="AA87" s="57" t="n"/>
+      <c r="AB87" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC87" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD87" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE87" s="57" t="n"/>
+      <c r="AF87" s="57" t="n"/>
+      <c r="AG87" s="57" t="n"/>
+      <c r="AH87" s="57" t="n"/>
+      <c r="AI87" s="57" t="n"/>
+      <c r="AJ87" s="57" t="n"/>
+      <c r="AK87" s="57" t="n"/>
+      <c r="AL87" s="57" t="n"/>
+      <c r="AM87" s="57" t="n"/>
+      <c r="AN87" s="57" t="n"/>
+      <c r="AO87" s="57" t="n"/>
+      <c r="AP87" s="57" t="n"/>
+      <c r="AQ87" s="57" t="n"/>
+      <c r="AR87" s="57" t="n"/>
+      <c r="AS87" s="57" t="n"/>
+      <c r="AT87" s="57" t="n"/>
+      <c r="AU87" s="57" t="n"/>
+      <c r="AV87" s="57" t="n"/>
+      <c r="AW87" s="57" t="n"/>
+      <c r="AX87" s="57" t="n"/>
+      <c r="AY87" s="57" t="n"/>
+      <c r="AZ87" s="57" t="n"/>
+      <c r="BA87" s="57" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="43" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B88" s="43" t="inlineStr">
+        <is>
+          <t>Gunsmith</t>
+        </is>
+      </c>
+      <c r="C88" s="43" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D88" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" s="56">
+        <f>ROUND('Towers'!$C$11*POWER('Tuning'!$B$12,D88),0)</f>
+        <v/>
+      </c>
+      <c r="F88" s="56">
+        <f>F87+E88</f>
+        <v/>
+      </c>
+      <c r="G88" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L88" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" s="43" t="inlineStr">
+        <is>
+          <t>Match Grade</t>
+        </is>
+      </c>
+      <c r="N88" s="57" t="n"/>
+      <c r="O88" s="57" t="n"/>
+      <c r="P88" s="57" t="n"/>
+      <c r="Q88" s="57" t="n"/>
+      <c r="R88" s="57" t="n"/>
+      <c r="S88" s="57" t="n"/>
+      <c r="T88" s="57" t="n"/>
+      <c r="U88" s="57" t="n"/>
+      <c r="V88" s="57" t="n"/>
+      <c r="W88" s="57" t="n"/>
+      <c r="X88" s="57" t="n"/>
+      <c r="Y88" s="57" t="n"/>
+      <c r="Z88" s="57" t="n"/>
+      <c r="AA88" s="57" t="n"/>
+      <c r="AB88" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC88" s="57" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD88" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE88" s="57" t="n"/>
+      <c r="AF88" s="57" t="n"/>
+      <c r="AG88" s="57" t="n"/>
+      <c r="AH88" s="57" t="n"/>
+      <c r="AI88" s="57" t="n"/>
+      <c r="AJ88" s="57" t="n"/>
+      <c r="AK88" s="57" t="n"/>
+      <c r="AL88" s="57" t="n"/>
+      <c r="AM88" s="57" t="n"/>
+      <c r="AN88" s="57" t="n"/>
+      <c r="AO88" s="57" t="n"/>
+      <c r="AP88" s="57" t="n"/>
+      <c r="AQ88" s="57" t="n"/>
+      <c r="AR88" s="57" t="n"/>
+      <c r="AS88" s="57" t="n"/>
+      <c r="AT88" s="57" t="n"/>
+      <c r="AU88" s="57" t="n"/>
+      <c r="AV88" s="57" t="n"/>
+      <c r="AW88" s="57" t="n"/>
+      <c r="AX88" s="57" t="n"/>
+      <c r="AY88" s="57" t="n"/>
+      <c r="AZ88" s="57" t="n"/>
+      <c r="BA88" s="57" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="43" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B89" s="43" t="inlineStr">
+        <is>
+          <t>Gunsmith</t>
+        </is>
+      </c>
+      <c r="C89" s="43" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D89" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E89" s="56">
+        <f>ROUND('Towers'!$C$11*POWER('Tuning'!$B$12,D89),0)</f>
+        <v/>
+      </c>
+      <c r="F89" s="56">
+        <f>F88+E89</f>
+        <v/>
+      </c>
+      <c r="G89" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L89" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" s="43" t="inlineStr">
+        <is>
+          <t>Master Gunsmith</t>
+        </is>
+      </c>
+      <c r="N89" s="57" t="n"/>
+      <c r="O89" s="57" t="n"/>
+      <c r="P89" s="57" t="n"/>
+      <c r="Q89" s="57" t="n"/>
+      <c r="R89" s="57" t="n"/>
+      <c r="S89" s="57" t="n"/>
+      <c r="T89" s="57" t="n"/>
+      <c r="U89" s="57" t="n"/>
+      <c r="V89" s="57" t="n"/>
+      <c r="W89" s="57" t="n"/>
+      <c r="X89" s="57" t="n"/>
+      <c r="Y89" s="57" t="n"/>
+      <c r="Z89" s="57" t="n"/>
+      <c r="AA89" s="57" t="n"/>
+      <c r="AB89" s="57" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC89" s="57" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD89" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE89" s="57" t="n"/>
+      <c r="AF89" s="57" t="n"/>
+      <c r="AG89" s="57" t="n"/>
+      <c r="AH89" s="57" t="n"/>
+      <c r="AI89" s="57" t="n"/>
+      <c r="AJ89" s="57" t="n"/>
+      <c r="AK89" s="57" t="n"/>
+      <c r="AL89" s="57" t="n"/>
+      <c r="AM89" s="57" t="n"/>
+      <c r="AN89" s="57" t="n"/>
+      <c r="AO89" s="57" t="n"/>
+      <c r="AP89" s="57" t="n"/>
+      <c r="AQ89" s="57" t="n"/>
+      <c r="AR89" s="57" t="n"/>
+      <c r="AS89" s="57" t="n"/>
+      <c r="AT89" s="57" t="n"/>
+      <c r="AU89" s="57" t="n"/>
+      <c r="AV89" s="57" t="n"/>
+      <c r="AW89" s="57" t="n"/>
+      <c r="AX89" s="57" t="n"/>
+      <c r="AY89" s="57" t="n"/>
+      <c r="AZ89" s="57" t="n"/>
+      <c r="BA89" s="57" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="43" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B90" s="43" t="inlineStr">
+        <is>
+          <t>Outfitter</t>
+        </is>
+      </c>
+      <c r="C90" s="43" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D90" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="56">
+        <f>ROUND('Towers'!$C$11*POWER('Tuning'!$B$12,D90),0)</f>
+        <v/>
+      </c>
+      <c r="F90" s="56">
+        <f>'Towers'!$C$11+E90</f>
+        <v/>
+      </c>
+      <c r="G90" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L90" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M90" s="43" t="inlineStr">
+        <is>
+          <t>Wide Rack</t>
+        </is>
+      </c>
+      <c r="N90" s="57" t="n"/>
+      <c r="O90" s="57" t="n"/>
+      <c r="P90" s="57" t="n"/>
+      <c r="Q90" s="57" t="n"/>
+      <c r="R90" s="57" t="n"/>
+      <c r="S90" s="57" t="n"/>
+      <c r="T90" s="57" t="n"/>
+      <c r="U90" s="57" t="n"/>
+      <c r="V90" s="57" t="n"/>
+      <c r="W90" s="57" t="n"/>
+      <c r="X90" s="57" t="n"/>
+      <c r="Y90" s="57" t="n"/>
+      <c r="Z90" s="57" t="n"/>
+      <c r="AA90" s="57" t="n"/>
+      <c r="AB90" s="57" t="n"/>
+      <c r="AC90" s="57" t="n"/>
+      <c r="AD90" s="57" t="n"/>
+      <c r="AE90" s="57" t="n"/>
+      <c r="AF90" s="57" t="n"/>
+      <c r="AG90" s="57" t="n"/>
+      <c r="AH90" s="57" t="n"/>
+      <c r="AI90" s="57" t="n"/>
+      <c r="AJ90" s="57" t="n"/>
+      <c r="AK90" s="57" t="n"/>
+      <c r="AL90" s="57" t="n"/>
+      <c r="AM90" s="57" t="n"/>
+      <c r="AN90" s="57" t="n"/>
+      <c r="AO90" s="57" t="n"/>
+      <c r="AP90" s="57" t="n"/>
+      <c r="AQ90" s="57" t="n"/>
+      <c r="AR90" s="57" t="n"/>
+      <c r="AS90" s="57" t="n"/>
+      <c r="AT90" s="57" t="n"/>
+      <c r="AU90" s="57" t="n"/>
+      <c r="AV90" s="57" t="n"/>
+      <c r="AW90" s="57" t="n"/>
+      <c r="AX90" s="57" t="n"/>
+      <c r="AY90" s="57" t="n"/>
+      <c r="AZ90" s="57" t="n"/>
+      <c r="BA90" s="57" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="43" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B91" s="43" t="inlineStr">
+        <is>
+          <t>Outfitter</t>
+        </is>
+      </c>
+      <c r="C91" s="43" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D91" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" s="56">
+        <f>ROUND('Towers'!$C$11*POWER('Tuning'!$B$12,D91),0)</f>
+        <v/>
+      </c>
+      <c r="F91" s="56">
+        <f>F90+E91</f>
+        <v/>
+      </c>
+      <c r="G91" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L91" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M91" s="43" t="inlineStr">
+        <is>
+          <t>Recoil Pads</t>
+        </is>
+      </c>
+      <c r="N91" s="57" t="n"/>
+      <c r="O91" s="57" t="n"/>
+      <c r="P91" s="57" t="n"/>
+      <c r="Q91" s="57" t="n"/>
+      <c r="R91" s="57" t="n"/>
+      <c r="S91" s="57" t="n"/>
+      <c r="T91" s="57" t="n"/>
+      <c r="U91" s="57" t="n"/>
+      <c r="V91" s="57" t="n"/>
+      <c r="W91" s="57" t="n"/>
+      <c r="X91" s="57" t="n"/>
+      <c r="Y91" s="57" t="n"/>
+      <c r="Z91" s="57" t="n"/>
+      <c r="AA91" s="57" t="n"/>
+      <c r="AB91" s="57" t="n"/>
+      <c r="AC91" s="57" t="n"/>
+      <c r="AD91" s="57" t="n"/>
+      <c r="AE91" s="57" t="n"/>
+      <c r="AF91" s="57" t="n"/>
+      <c r="AG91" s="57" t="n"/>
+      <c r="AH91" s="57" t="n"/>
+      <c r="AI91" s="57" t="n"/>
+      <c r="AJ91" s="57" t="n"/>
+      <c r="AK91" s="57" t="n"/>
+      <c r="AL91" s="57" t="n"/>
+      <c r="AM91" s="57" t="n"/>
+      <c r="AN91" s="57" t="n"/>
+      <c r="AO91" s="57" t="n"/>
+      <c r="AP91" s="57" t="n"/>
+      <c r="AQ91" s="57" t="n"/>
+      <c r="AR91" s="57" t="n"/>
+      <c r="AS91" s="57" t="n"/>
+      <c r="AT91" s="57" t="n"/>
+      <c r="AU91" s="57" t="n"/>
+      <c r="AV91" s="57" t="n"/>
+      <c r="AW91" s="57" t="n"/>
+      <c r="AX91" s="57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY91" s="57" t="n"/>
+      <c r="AZ91" s="57" t="n"/>
+      <c r="BA91" s="57" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="43" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B92" s="43" t="inlineStr">
+        <is>
+          <t>Outfitter</t>
+        </is>
+      </c>
+      <c r="C92" s="43" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D92" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" s="56">
+        <f>ROUND('Towers'!$C$11*POWER('Tuning'!$B$12,D92),0)</f>
+        <v/>
+      </c>
+      <c r="F92" s="56">
+        <f>F91+E92</f>
+        <v/>
+      </c>
+      <c r="G92" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L92" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M92" s="43" t="inlineStr">
+        <is>
+          <t>Ammo Crate</t>
+        </is>
+      </c>
+      <c r="N92" s="57" t="n"/>
+      <c r="O92" s="57" t="n"/>
+      <c r="P92" s="57" t="n"/>
+      <c r="Q92" s="57" t="n"/>
+      <c r="R92" s="57" t="n"/>
+      <c r="S92" s="57" t="n"/>
+      <c r="T92" s="57" t="n"/>
+      <c r="U92" s="57" t="n"/>
+      <c r="V92" s="57" t="n"/>
+      <c r="W92" s="57" t="n"/>
+      <c r="X92" s="57" t="n"/>
+      <c r="Y92" s="57" t="n"/>
+      <c r="Z92" s="57" t="n"/>
+      <c r="AA92" s="57" t="n"/>
+      <c r="AB92" s="57" t="n"/>
+      <c r="AC92" s="57" t="n"/>
+      <c r="AD92" s="57" t="n"/>
+      <c r="AE92" s="57" t="n"/>
+      <c r="AF92" s="57" t="n"/>
+      <c r="AG92" s="57" t="n"/>
+      <c r="AH92" s="57" t="n"/>
+      <c r="AI92" s="57" t="n"/>
+      <c r="AJ92" s="57" t="n"/>
+      <c r="AK92" s="57" t="n"/>
+      <c r="AL92" s="57" t="n"/>
+      <c r="AM92" s="57" t="n"/>
+      <c r="AN92" s="57" t="n"/>
+      <c r="AO92" s="57" t="n"/>
+      <c r="AP92" s="57" t="n"/>
+      <c r="AQ92" s="57" t="n"/>
+      <c r="AR92" s="57" t="n"/>
+      <c r="AS92" s="57" t="n"/>
+      <c r="AT92" s="57" t="n"/>
+      <c r="AU92" s="57" t="n"/>
+      <c r="AV92" s="57" t="n"/>
+      <c r="AW92" s="57" t="n"/>
+      <c r="AX92" s="57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY92" s="57" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AZ92" s="57" t="n"/>
+      <c r="BA92" s="57" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="43" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B93" s="43" t="inlineStr">
+        <is>
+          <t>Outfitter</t>
+        </is>
+      </c>
+      <c r="C93" s="43" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D93" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E93" s="56">
+        <f>ROUND('Towers'!$C$11*POWER('Tuning'!$B$12,D93),0)</f>
+        <v/>
+      </c>
+      <c r="F93" s="56">
+        <f>F92+E93</f>
+        <v/>
+      </c>
+      <c r="G93" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L93" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M93" s="43" t="inlineStr">
+        <is>
+          <t>Steady Rests</t>
+        </is>
+      </c>
+      <c r="N93" s="57" t="n"/>
+      <c r="O93" s="57" t="n"/>
+      <c r="P93" s="57" t="n"/>
+      <c r="Q93" s="57" t="n"/>
+      <c r="R93" s="57" t="n"/>
+      <c r="S93" s="57" t="n"/>
+      <c r="T93" s="57" t="n"/>
+      <c r="U93" s="57" t="n"/>
+      <c r="V93" s="57" t="n"/>
+      <c r="W93" s="57" t="n"/>
+      <c r="X93" s="57" t="n"/>
+      <c r="Y93" s="57" t="n"/>
+      <c r="Z93" s="57" t="n"/>
+      <c r="AA93" s="57" t="n"/>
+      <c r="AB93" s="57" t="n"/>
+      <c r="AC93" s="57" t="n"/>
+      <c r="AD93" s="57" t="n"/>
+      <c r="AE93" s="57" t="n"/>
+      <c r="AF93" s="57" t="n"/>
+      <c r="AG93" s="57" t="n"/>
+      <c r="AH93" s="57" t="n"/>
+      <c r="AI93" s="57" t="n"/>
+      <c r="AJ93" s="57" t="n"/>
+      <c r="AK93" s="57" t="n"/>
+      <c r="AL93" s="57" t="n"/>
+      <c r="AM93" s="57" t="n"/>
+      <c r="AN93" s="57" t="n"/>
+      <c r="AO93" s="57" t="n"/>
+      <c r="AP93" s="57" t="n"/>
+      <c r="AQ93" s="57" t="n"/>
+      <c r="AR93" s="57" t="n"/>
+      <c r="AS93" s="57" t="n"/>
+      <c r="AT93" s="57" t="n"/>
+      <c r="AU93" s="57" t="n"/>
+      <c r="AV93" s="57" t="n"/>
+      <c r="AW93" s="57" t="n"/>
+      <c r="AX93" s="57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY93" s="57" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AZ93" s="57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BA93" s="57" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="43" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B94" s="43" t="inlineStr">
+        <is>
+          <t>Outfitter</t>
+        </is>
+      </c>
+      <c r="C94" s="43" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D94" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E94" s="56">
+        <f>ROUND('Towers'!$C$11*POWER('Tuning'!$B$12,D94),0)</f>
+        <v/>
+      </c>
+      <c r="F94" s="56">
+        <f>F93+E94</f>
+        <v/>
+      </c>
+      <c r="G94" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L94" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M94" s="43" t="inlineStr">
+        <is>
+          <t>Full Kit</t>
+        </is>
+      </c>
+      <c r="N94" s="57" t="n"/>
+      <c r="O94" s="57" t="n"/>
+      <c r="P94" s="57" t="n"/>
+      <c r="Q94" s="57" t="n"/>
+      <c r="R94" s="57" t="n"/>
+      <c r="S94" s="57" t="n"/>
+      <c r="T94" s="57" t="n"/>
+      <c r="U94" s="57" t="n"/>
+      <c r="V94" s="57" t="n"/>
+      <c r="W94" s="57" t="n"/>
+      <c r="X94" s="57" t="n"/>
+      <c r="Y94" s="57" t="n"/>
+      <c r="Z94" s="57" t="n"/>
+      <c r="AA94" s="57" t="n"/>
+      <c r="AB94" s="57" t="n"/>
+      <c r="AC94" s="57" t="n"/>
+      <c r="AD94" s="57" t="n"/>
+      <c r="AE94" s="57" t="n"/>
+      <c r="AF94" s="57" t="n"/>
+      <c r="AG94" s="57" t="n"/>
+      <c r="AH94" s="57" t="n"/>
+      <c r="AI94" s="57" t="n"/>
+      <c r="AJ94" s="57" t="n"/>
+      <c r="AK94" s="57" t="n"/>
+      <c r="AL94" s="57" t="n"/>
+      <c r="AM94" s="57" t="n"/>
+      <c r="AN94" s="57" t="n"/>
+      <c r="AO94" s="57" t="n"/>
+      <c r="AP94" s="57" t="n"/>
+      <c r="AQ94" s="57" t="n"/>
+      <c r="AR94" s="57" t="n"/>
+      <c r="AS94" s="57" t="n"/>
+      <c r="AT94" s="57" t="n"/>
+      <c r="AU94" s="57" t="n"/>
+      <c r="AV94" s="57" t="n"/>
+      <c r="AW94" s="57" t="n"/>
+      <c r="AX94" s="57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY94" s="57" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AZ94" s="57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BA94" s="57" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -13191,6 +14800,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -13686,6 +15296,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -2238,7 +2238,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -2431,8 +2430,6 @@
         <v>2.2</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -4897,7 +4894,6 @@
       </c>
       <c r="E38" s="17" t="n"/>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="31" t="inlineStr">
         <is>
@@ -4968,7 +4964,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="31" t="inlineStr">
         <is>
@@ -5119,7 +5114,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
         <is>
@@ -5170,7 +5164,6 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="31" t="inlineStr">
         <is>
@@ -5241,7 +5234,6 @@
         </is>
       </c>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
@@ -5292,7 +5284,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
@@ -5983,18 +5974,71 @@
       </c>
     </row>
     <row r="10" ht="13.55" customHeight="1" s="90">
-      <c r="A10" s="48" t="n"/>
-      <c r="B10" s="49" t="n"/>
-      <c r="C10" s="37" t="n"/>
-      <c r="D10" s="49" t="n"/>
-      <c r="E10" s="49" t="n"/>
-      <c r="F10" s="49" t="n"/>
-      <c r="G10" s="49" t="n"/>
-      <c r="H10" s="49" t="n"/>
-      <c r="I10" s="49" t="n"/>
-      <c r="J10" s="49" t="n"/>
-      <c r="K10" s="50" t="n"/>
-      <c r="L10" s="51" t="n"/>
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>Support: heals towers and hunters, no attack</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="n">
+        <v>450</v>
+      </c>
+      <c r="D10" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="92">
+        <f t="array" ref="G10">D10*E10*F10</f>
+        <v/>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="I10" s="46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="47" t="inlineStr">
+        <is>
+          <t>Never shoots. Heals standing towers and hunters in range; its paths revive trampled towers, drop med kits and toughen towers.</t>
+        </is>
+      </c>
+      <c r="L10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="O10" s="43" t="inlineStr">
+        <is>
+          <t>HOSPITAL</t>
+        </is>
+      </c>
+      <c r="P10" s="27" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q10" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" s="27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" ht="13.65" customHeight="1" s="90">
       <c r="A11" s="43" t="inlineStr">
@@ -6063,7 +6107,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
         <is>
@@ -6101,7 +6144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA94"/>
+  <dimension ref="A1:BI109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -6504,6 +6547,46 @@
       <c r="BA4" s="21" t="inlineStr">
         <is>
           <t>Hunter fire rate %</t>
+        </is>
+      </c>
+      <c r="BB4" s="21" t="inlineStr">
+        <is>
+          <t>Heal x</t>
+        </is>
+      </c>
+      <c r="BC4" s="21" t="inlineStr">
+        <is>
+          <t>Revives</t>
+        </is>
+      </c>
+      <c r="BD4" s="21" t="inlineStr">
+        <is>
+          <t>Revive speed x</t>
+        </is>
+      </c>
+      <c r="BE4" s="21" t="inlineStr">
+        <is>
+          <t>Med kits</t>
+        </is>
+      </c>
+      <c r="BF4" s="21" t="inlineStr">
+        <is>
+          <t>Med kit heal</t>
+        </is>
+      </c>
+      <c r="BG4" s="21" t="inlineStr">
+        <is>
+          <t>Rescue beacon (respawn x)</t>
+        </is>
+      </c>
+      <c r="BH4" s="21" t="inlineStr">
+        <is>
+          <t>Aura HP %</t>
+        </is>
+      </c>
+      <c r="BI4" s="21" t="inlineStr">
+        <is>
+          <t>Last stand</t>
         </is>
       </c>
     </row>
@@ -14736,6 +14819,1583 @@
       </c>
       <c r="BA94" s="57" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B95" s="43" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="C95" s="43" t="inlineStr">
+        <is>
+          <t>healing</t>
+        </is>
+      </c>
+      <c r="D95" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="56">
+        <f>ROUND('Towers'!$C$10*POWER('Tuning'!$B$12,D95),0)</f>
+        <v/>
+      </c>
+      <c r="F95" s="56">
+        <f>'Towers'!$C$10+E95</f>
+        <v/>
+      </c>
+      <c r="G95" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L95" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" s="43" t="inlineStr">
+        <is>
+          <t>Clean Linens</t>
+        </is>
+      </c>
+      <c r="N95" s="57" t="n"/>
+      <c r="O95" s="57" t="n"/>
+      <c r="P95" s="57" t="n"/>
+      <c r="Q95" s="57" t="n"/>
+      <c r="R95" s="57" t="n"/>
+      <c r="S95" s="57" t="n"/>
+      <c r="T95" s="57" t="n"/>
+      <c r="U95" s="57" t="n"/>
+      <c r="V95" s="57" t="n"/>
+      <c r="W95" s="57" t="n"/>
+      <c r="X95" s="57" t="n"/>
+      <c r="Y95" s="57" t="n"/>
+      <c r="Z95" s="57" t="n"/>
+      <c r="AA95" s="57" t="n"/>
+      <c r="AB95" s="57" t="n"/>
+      <c r="AC95" s="57" t="n"/>
+      <c r="AD95" s="57" t="n"/>
+      <c r="AE95" s="57" t="n"/>
+      <c r="AF95" s="57" t="n"/>
+      <c r="AG95" s="57" t="n"/>
+      <c r="AH95" s="57" t="n"/>
+      <c r="AI95" s="57" t="n"/>
+      <c r="AJ95" s="57" t="n"/>
+      <c r="AK95" s="57" t="n"/>
+      <c r="AL95" s="57" t="n"/>
+      <c r="AM95" s="57" t="n"/>
+      <c r="AN95" s="57" t="n"/>
+      <c r="AO95" s="57" t="n"/>
+      <c r="AP95" s="57" t="n"/>
+      <c r="AQ95" s="57" t="n"/>
+      <c r="AR95" s="57" t="n"/>
+      <c r="AS95" s="57" t="n"/>
+      <c r="AT95" s="57" t="n"/>
+      <c r="AU95" s="57" t="n"/>
+      <c r="AV95" s="57" t="n"/>
+      <c r="AW95" s="57" t="n"/>
+      <c r="AX95" s="57" t="n"/>
+      <c r="AY95" s="57" t="n"/>
+      <c r="AZ95" s="57" t="n"/>
+      <c r="BA95" s="57" t="n"/>
+      <c r="BB95" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BC95" s="57" t="n"/>
+      <c r="BD95" s="57" t="n"/>
+      <c r="BE95" s="57" t="n"/>
+      <c r="BF95" s="57" t="n"/>
+      <c r="BG95" s="57" t="n"/>
+      <c r="BH95" s="57" t="n"/>
+      <c r="BI95" s="57" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B96" s="43" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="C96" s="43" t="inlineStr">
+        <is>
+          <t>healing</t>
+        </is>
+      </c>
+      <c r="D96" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" s="56">
+        <f>ROUND('Towers'!$C$10*POWER('Tuning'!$B$12,D96),0)</f>
+        <v/>
+      </c>
+      <c r="F96" s="56">
+        <f>F95+E96</f>
+        <v/>
+      </c>
+      <c r="G96" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L96" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" s="43" t="inlineStr">
+        <is>
+          <t>Extra Cots</t>
+        </is>
+      </c>
+      <c r="N96" s="57" t="n"/>
+      <c r="O96" s="57" t="n"/>
+      <c r="P96" s="57" t="n"/>
+      <c r="Q96" s="57" t="n"/>
+      <c r="R96" s="57" t="n"/>
+      <c r="S96" s="57" t="n"/>
+      <c r="T96" s="57" t="n"/>
+      <c r="U96" s="57" t="n"/>
+      <c r="V96" s="57" t="n"/>
+      <c r="W96" s="57" t="n"/>
+      <c r="X96" s="57" t="n"/>
+      <c r="Y96" s="57" t="n"/>
+      <c r="Z96" s="57" t="n"/>
+      <c r="AA96" s="57" t="n"/>
+      <c r="AB96" s="57" t="n"/>
+      <c r="AC96" s="57" t="n"/>
+      <c r="AD96" s="57" t="n"/>
+      <c r="AE96" s="57" t="n"/>
+      <c r="AF96" s="57" t="n"/>
+      <c r="AG96" s="57" t="n"/>
+      <c r="AH96" s="57" t="n"/>
+      <c r="AI96" s="57" t="n"/>
+      <c r="AJ96" s="57" t="n"/>
+      <c r="AK96" s="57" t="n"/>
+      <c r="AL96" s="57" t="n"/>
+      <c r="AM96" s="57" t="n"/>
+      <c r="AN96" s="57" t="n"/>
+      <c r="AO96" s="57" t="n"/>
+      <c r="AP96" s="57" t="n"/>
+      <c r="AQ96" s="57" t="n"/>
+      <c r="AR96" s="57" t="n"/>
+      <c r="AS96" s="57" t="n"/>
+      <c r="AT96" s="57" t="n"/>
+      <c r="AU96" s="57" t="n"/>
+      <c r="AV96" s="57" t="n"/>
+      <c r="AW96" s="57" t="n"/>
+      <c r="AX96" s="57" t="n"/>
+      <c r="AY96" s="57" t="n"/>
+      <c r="AZ96" s="57" t="n"/>
+      <c r="BA96" s="57" t="n"/>
+      <c r="BB96" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC96" s="57" t="n"/>
+      <c r="BD96" s="57" t="n"/>
+      <c r="BE96" s="57" t="n"/>
+      <c r="BF96" s="57" t="n"/>
+      <c r="BG96" s="57" t="n"/>
+      <c r="BH96" s="57" t="n"/>
+      <c r="BI96" s="57" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B97" s="43" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="C97" s="43" t="inlineStr">
+        <is>
+          <t>healing</t>
+        </is>
+      </c>
+      <c r="D97" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" s="56">
+        <f>ROUND('Towers'!$C$10*POWER('Tuning'!$B$12,D97),0)</f>
+        <v/>
+      </c>
+      <c r="F97" s="56">
+        <f>F96+E97</f>
+        <v/>
+      </c>
+      <c r="G97" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L97" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" s="43" t="inlineStr">
+        <is>
+          <t>Stitch-Up</t>
+        </is>
+      </c>
+      <c r="N97" s="57" t="n"/>
+      <c r="O97" s="57" t="n"/>
+      <c r="P97" s="57" t="n"/>
+      <c r="Q97" s="57" t="n"/>
+      <c r="R97" s="57" t="n"/>
+      <c r="S97" s="57" t="n"/>
+      <c r="T97" s="57" t="n"/>
+      <c r="U97" s="57" t="n"/>
+      <c r="V97" s="57" t="n"/>
+      <c r="W97" s="57" t="n"/>
+      <c r="X97" s="57" t="n"/>
+      <c r="Y97" s="57" t="n"/>
+      <c r="Z97" s="57" t="n"/>
+      <c r="AA97" s="57" t="n"/>
+      <c r="AB97" s="57" t="n"/>
+      <c r="AC97" s="57" t="n"/>
+      <c r="AD97" s="57" t="n"/>
+      <c r="AE97" s="57" t="n"/>
+      <c r="AF97" s="57" t="n"/>
+      <c r="AG97" s="57" t="n"/>
+      <c r="AH97" s="57" t="n"/>
+      <c r="AI97" s="57" t="n"/>
+      <c r="AJ97" s="57" t="n"/>
+      <c r="AK97" s="57" t="n"/>
+      <c r="AL97" s="57" t="n"/>
+      <c r="AM97" s="57" t="n"/>
+      <c r="AN97" s="57" t="n"/>
+      <c r="AO97" s="57" t="n"/>
+      <c r="AP97" s="57" t="n"/>
+      <c r="AQ97" s="57" t="n"/>
+      <c r="AR97" s="57" t="n"/>
+      <c r="AS97" s="57" t="n"/>
+      <c r="AT97" s="57" t="n"/>
+      <c r="AU97" s="57" t="n"/>
+      <c r="AV97" s="57" t="n"/>
+      <c r="AW97" s="57" t="n"/>
+      <c r="AX97" s="57" t="n"/>
+      <c r="AY97" s="57" t="n"/>
+      <c r="AZ97" s="57" t="n"/>
+      <c r="BA97" s="57" t="n"/>
+      <c r="BB97" s="57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BC97" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BD97" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BE97" s="57" t="n"/>
+      <c r="BF97" s="57" t="n"/>
+      <c r="BG97" s="57" t="n"/>
+      <c r="BH97" s="57" t="n"/>
+      <c r="BI97" s="57" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B98" s="43" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="C98" s="43" t="inlineStr">
+        <is>
+          <t>healing</t>
+        </is>
+      </c>
+      <c r="D98" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E98" s="56">
+        <f>ROUND('Towers'!$C$10*POWER('Tuning'!$B$12,D98),0)</f>
+        <v/>
+      </c>
+      <c r="F98" s="56">
+        <f>F97+E98</f>
+        <v/>
+      </c>
+      <c r="G98" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L98" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" s="43" t="inlineStr">
+        <is>
+          <t>Night Shift</t>
+        </is>
+      </c>
+      <c r="N98" s="57" t="n"/>
+      <c r="O98" s="57" t="n"/>
+      <c r="P98" s="57" t="n"/>
+      <c r="Q98" s="57" t="n"/>
+      <c r="R98" s="57" t="n"/>
+      <c r="S98" s="57" t="n"/>
+      <c r="T98" s="57" t="n"/>
+      <c r="U98" s="57" t="n"/>
+      <c r="V98" s="57" t="n"/>
+      <c r="W98" s="57" t="n"/>
+      <c r="X98" s="57" t="n"/>
+      <c r="Y98" s="57" t="n"/>
+      <c r="Z98" s="57" t="n"/>
+      <c r="AA98" s="57" t="n"/>
+      <c r="AB98" s="57" t="n"/>
+      <c r="AC98" s="57" t="n"/>
+      <c r="AD98" s="57" t="n"/>
+      <c r="AE98" s="57" t="n"/>
+      <c r="AF98" s="57" t="n"/>
+      <c r="AG98" s="57" t="n"/>
+      <c r="AH98" s="57" t="n"/>
+      <c r="AI98" s="57" t="n"/>
+      <c r="AJ98" s="57" t="n"/>
+      <c r="AK98" s="57" t="n"/>
+      <c r="AL98" s="57" t="n"/>
+      <c r="AM98" s="57" t="n"/>
+      <c r="AN98" s="57" t="n"/>
+      <c r="AO98" s="57" t="n"/>
+      <c r="AP98" s="57" t="n"/>
+      <c r="AQ98" s="57" t="n"/>
+      <c r="AR98" s="57" t="n"/>
+      <c r="AS98" s="57" t="n"/>
+      <c r="AT98" s="57" t="n"/>
+      <c r="AU98" s="57" t="n"/>
+      <c r="AV98" s="57" t="n"/>
+      <c r="AW98" s="57" t="n"/>
+      <c r="AX98" s="57" t="n"/>
+      <c r="AY98" s="57" t="n"/>
+      <c r="AZ98" s="57" t="n"/>
+      <c r="BA98" s="57" t="n"/>
+      <c r="BB98" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC98" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BD98" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BE98" s="57" t="n"/>
+      <c r="BF98" s="57" t="n"/>
+      <c r="BG98" s="57" t="n"/>
+      <c r="BH98" s="57" t="n"/>
+      <c r="BI98" s="57" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B99" s="43" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="C99" s="43" t="inlineStr">
+        <is>
+          <t>healing</t>
+        </is>
+      </c>
+      <c r="D99" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E99" s="56">
+        <f>ROUND('Towers'!$C$10*POWER('Tuning'!$B$12,D99),0)</f>
+        <v/>
+      </c>
+      <c r="F99" s="56">
+        <f>F98+E99</f>
+        <v/>
+      </c>
+      <c r="G99" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L99" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M99" s="43" t="inlineStr">
+        <is>
+          <t>Miracle Ward</t>
+        </is>
+      </c>
+      <c r="N99" s="57" t="n"/>
+      <c r="O99" s="57" t="n"/>
+      <c r="P99" s="57" t="n"/>
+      <c r="Q99" s="57" t="n"/>
+      <c r="R99" s="57" t="n"/>
+      <c r="S99" s="57" t="n"/>
+      <c r="T99" s="57" t="n"/>
+      <c r="U99" s="57" t="n"/>
+      <c r="V99" s="57" t="n"/>
+      <c r="W99" s="57" t="n"/>
+      <c r="X99" s="57" t="n"/>
+      <c r="Y99" s="57" t="n"/>
+      <c r="Z99" s="57" t="n"/>
+      <c r="AA99" s="57" t="n"/>
+      <c r="AB99" s="57" t="n"/>
+      <c r="AC99" s="57" t="n"/>
+      <c r="AD99" s="57" t="n"/>
+      <c r="AE99" s="57" t="n"/>
+      <c r="AF99" s="57" t="n"/>
+      <c r="AG99" s="57" t="n"/>
+      <c r="AH99" s="57" t="n"/>
+      <c r="AI99" s="57" t="n"/>
+      <c r="AJ99" s="57" t="n"/>
+      <c r="AK99" s="57" t="n"/>
+      <c r="AL99" s="57" t="n"/>
+      <c r="AM99" s="57" t="n"/>
+      <c r="AN99" s="57" t="n"/>
+      <c r="AO99" s="57" t="n"/>
+      <c r="AP99" s="57" t="n"/>
+      <c r="AQ99" s="57" t="n"/>
+      <c r="AR99" s="57" t="n"/>
+      <c r="AS99" s="57" t="n"/>
+      <c r="AT99" s="57" t="n"/>
+      <c r="AU99" s="57" t="n"/>
+      <c r="AV99" s="57" t="n"/>
+      <c r="AW99" s="57" t="n"/>
+      <c r="AX99" s="57" t="n"/>
+      <c r="AY99" s="57" t="n"/>
+      <c r="AZ99" s="57" t="n"/>
+      <c r="BA99" s="57" t="n"/>
+      <c r="BB99" s="57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC99" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BD99" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE99" s="57" t="n"/>
+      <c r="BF99" s="57" t="n"/>
+      <c r="BG99" s="57" t="n"/>
+      <c r="BH99" s="57" t="n"/>
+      <c r="BI99" s="57" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B100" s="43" t="inlineStr">
+        <is>
+          <t>Rescue</t>
+        </is>
+      </c>
+      <c r="C100" s="43" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D100" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="56">
+        <f>ROUND('Towers'!$C$10*POWER('Tuning'!$B$12,D100),0)</f>
+        <v/>
+      </c>
+      <c r="F100" s="56">
+        <f>'Towers'!$C$10+E100</f>
+        <v/>
+      </c>
+      <c r="G100" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L100" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M100" s="43" t="inlineStr">
+        <is>
+          <t>Stretcher Team</t>
+        </is>
+      </c>
+      <c r="N100" s="57" t="n"/>
+      <c r="O100" s="57" t="n"/>
+      <c r="P100" s="57" t="n"/>
+      <c r="Q100" s="57" t="n"/>
+      <c r="R100" s="57" t="n"/>
+      <c r="S100" s="57" t="n"/>
+      <c r="T100" s="57" t="n"/>
+      <c r="U100" s="57" t="n"/>
+      <c r="V100" s="57" t="n"/>
+      <c r="W100" s="57" t="n"/>
+      <c r="X100" s="57" t="n"/>
+      <c r="Y100" s="57" t="n"/>
+      <c r="Z100" s="57" t="n"/>
+      <c r="AA100" s="57" t="n"/>
+      <c r="AB100" s="57" t="n"/>
+      <c r="AC100" s="57" t="n"/>
+      <c r="AD100" s="57" t="n"/>
+      <c r="AE100" s="57" t="n"/>
+      <c r="AF100" s="57" t="n"/>
+      <c r="AG100" s="57" t="n"/>
+      <c r="AH100" s="57" t="n"/>
+      <c r="AI100" s="57" t="n"/>
+      <c r="AJ100" s="57" t="n"/>
+      <c r="AK100" s="57" t="n"/>
+      <c r="AL100" s="57" t="n"/>
+      <c r="AM100" s="57" t="n"/>
+      <c r="AN100" s="57" t="n"/>
+      <c r="AO100" s="57" t="n"/>
+      <c r="AP100" s="57" t="n"/>
+      <c r="AQ100" s="57" t="n"/>
+      <c r="AR100" s="57" t="n"/>
+      <c r="AS100" s="57" t="n"/>
+      <c r="AT100" s="57" t="n"/>
+      <c r="AU100" s="57" t="n"/>
+      <c r="AV100" s="57" t="n"/>
+      <c r="AW100" s="57" t="n"/>
+      <c r="AX100" s="57" t="n"/>
+      <c r="AY100" s="57" t="n"/>
+      <c r="AZ100" s="57" t="n"/>
+      <c r="BA100" s="57" t="n"/>
+      <c r="BB100" s="57" t="n"/>
+      <c r="BC100" s="57" t="n"/>
+      <c r="BD100" s="57" t="n"/>
+      <c r="BE100" s="57" t="n"/>
+      <c r="BF100" s="57" t="n"/>
+      <c r="BG100" s="57" t="n"/>
+      <c r="BH100" s="57" t="n"/>
+      <c r="BI100" s="57" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B101" s="43" t="inlineStr">
+        <is>
+          <t>Rescue</t>
+        </is>
+      </c>
+      <c r="C101" s="43" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D101" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" s="56">
+        <f>ROUND('Towers'!$C$10*POWER('Tuning'!$B$12,D101),0)</f>
+        <v/>
+      </c>
+      <c r="F101" s="56">
+        <f>F100+E101</f>
+        <v/>
+      </c>
+      <c r="G101" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L101" s="57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M101" s="43" t="inlineStr">
+        <is>
+          <t>Signal Whistle</t>
+        </is>
+      </c>
+      <c r="N101" s="57" t="n"/>
+      <c r="O101" s="57" t="n"/>
+      <c r="P101" s="57" t="n"/>
+      <c r="Q101" s="57" t="n"/>
+      <c r="R101" s="57" t="n"/>
+      <c r="S101" s="57" t="n"/>
+      <c r="T101" s="57" t="n"/>
+      <c r="U101" s="57" t="n"/>
+      <c r="V101" s="57" t="n"/>
+      <c r="W101" s="57" t="n"/>
+      <c r="X101" s="57" t="n"/>
+      <c r="Y101" s="57" t="n"/>
+      <c r="Z101" s="57" t="n"/>
+      <c r="AA101" s="57" t="n"/>
+      <c r="AB101" s="57" t="n"/>
+      <c r="AC101" s="57" t="n"/>
+      <c r="AD101" s="57" t="n"/>
+      <c r="AE101" s="57" t="n"/>
+      <c r="AF101" s="57" t="n"/>
+      <c r="AG101" s="57" t="n"/>
+      <c r="AH101" s="57" t="n"/>
+      <c r="AI101" s="57" t="n"/>
+      <c r="AJ101" s="57" t="n"/>
+      <c r="AK101" s="57" t="n"/>
+      <c r="AL101" s="57" t="n"/>
+      <c r="AM101" s="57" t="n"/>
+      <c r="AN101" s="57" t="n"/>
+      <c r="AO101" s="57" t="n"/>
+      <c r="AP101" s="57" t="n"/>
+      <c r="AQ101" s="57" t="n"/>
+      <c r="AR101" s="57" t="n"/>
+      <c r="AS101" s="57" t="n"/>
+      <c r="AT101" s="57" t="n"/>
+      <c r="AU101" s="57" t="n"/>
+      <c r="AV101" s="57" t="n"/>
+      <c r="AW101" s="57" t="n"/>
+      <c r="AX101" s="57" t="n"/>
+      <c r="AY101" s="57" t="n"/>
+      <c r="AZ101" s="57" t="n"/>
+      <c r="BA101" s="57" t="n"/>
+      <c r="BB101" s="57" t="n"/>
+      <c r="BC101" s="57" t="n"/>
+      <c r="BD101" s="57" t="n"/>
+      <c r="BE101" s="57" t="n"/>
+      <c r="BF101" s="57" t="n"/>
+      <c r="BG101" s="57" t="n"/>
+      <c r="BH101" s="57" t="n"/>
+      <c r="BI101" s="57" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B102" s="43" t="inlineStr">
+        <is>
+          <t>Rescue</t>
+        </is>
+      </c>
+      <c r="C102" s="43" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D102" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E102" s="56">
+        <f>ROUND('Towers'!$C$10*POWER('Tuning'!$B$12,D102),0)</f>
+        <v/>
+      </c>
+      <c r="F102" s="56">
+        <f>F101+E102</f>
+        <v/>
+      </c>
+      <c r="G102" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L102" s="57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M102" s="43" t="inlineStr">
+        <is>
+          <t>Med Kits</t>
+        </is>
+      </c>
+      <c r="N102" s="57" t="n"/>
+      <c r="O102" s="57" t="n"/>
+      <c r="P102" s="57" t="n"/>
+      <c r="Q102" s="57" t="n"/>
+      <c r="R102" s="57" t="n"/>
+      <c r="S102" s="57" t="n"/>
+      <c r="T102" s="57" t="n"/>
+      <c r="U102" s="57" t="n"/>
+      <c r="V102" s="57" t="n"/>
+      <c r="W102" s="57" t="n"/>
+      <c r="X102" s="57" t="n"/>
+      <c r="Y102" s="57" t="n"/>
+      <c r="Z102" s="57" t="n"/>
+      <c r="AA102" s="57" t="n"/>
+      <c r="AB102" s="57" t="n"/>
+      <c r="AC102" s="57" t="n"/>
+      <c r="AD102" s="57" t="n"/>
+      <c r="AE102" s="57" t="n"/>
+      <c r="AF102" s="57" t="n"/>
+      <c r="AG102" s="57" t="n"/>
+      <c r="AH102" s="57" t="n"/>
+      <c r="AI102" s="57" t="n"/>
+      <c r="AJ102" s="57" t="n"/>
+      <c r="AK102" s="57" t="n"/>
+      <c r="AL102" s="57" t="n"/>
+      <c r="AM102" s="57" t="n"/>
+      <c r="AN102" s="57" t="n"/>
+      <c r="AO102" s="57" t="n"/>
+      <c r="AP102" s="57" t="n"/>
+      <c r="AQ102" s="57" t="n"/>
+      <c r="AR102" s="57" t="n"/>
+      <c r="AS102" s="57" t="n"/>
+      <c r="AT102" s="57" t="n"/>
+      <c r="AU102" s="57" t="n"/>
+      <c r="AV102" s="57" t="n"/>
+      <c r="AW102" s="57" t="n"/>
+      <c r="AX102" s="57" t="n"/>
+      <c r="AY102" s="57" t="n"/>
+      <c r="AZ102" s="57" t="n"/>
+      <c r="BA102" s="57" t="n"/>
+      <c r="BB102" s="57" t="n"/>
+      <c r="BC102" s="57" t="n"/>
+      <c r="BD102" s="57" t="n"/>
+      <c r="BE102" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF102" s="57" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG102" s="57" t="n"/>
+      <c r="BH102" s="57" t="n"/>
+      <c r="BI102" s="57" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B103" s="43" t="inlineStr">
+        <is>
+          <t>Rescue</t>
+        </is>
+      </c>
+      <c r="C103" s="43" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D103" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E103" s="56">
+        <f>ROUND('Towers'!$C$10*POWER('Tuning'!$B$12,D103),0)</f>
+        <v/>
+      </c>
+      <c r="F103" s="56">
+        <f>F102+E103</f>
+        <v/>
+      </c>
+      <c r="G103" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L103" s="57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M103" s="43" t="inlineStr">
+        <is>
+          <t>Supply Runs</t>
+        </is>
+      </c>
+      <c r="N103" s="57" t="n"/>
+      <c r="O103" s="57" t="n"/>
+      <c r="P103" s="57" t="n"/>
+      <c r="Q103" s="57" t="n"/>
+      <c r="R103" s="57" t="n"/>
+      <c r="S103" s="57" t="n"/>
+      <c r="T103" s="57" t="n"/>
+      <c r="U103" s="57" t="n"/>
+      <c r="V103" s="57" t="n"/>
+      <c r="W103" s="57" t="n"/>
+      <c r="X103" s="57" t="n"/>
+      <c r="Y103" s="57" t="n"/>
+      <c r="Z103" s="57" t="n"/>
+      <c r="AA103" s="57" t="n"/>
+      <c r="AB103" s="57" t="n"/>
+      <c r="AC103" s="57" t="n"/>
+      <c r="AD103" s="57" t="n"/>
+      <c r="AE103" s="57" t="n"/>
+      <c r="AF103" s="57" t="n"/>
+      <c r="AG103" s="57" t="n"/>
+      <c r="AH103" s="57" t="n"/>
+      <c r="AI103" s="57" t="n"/>
+      <c r="AJ103" s="57" t="n"/>
+      <c r="AK103" s="57" t="n"/>
+      <c r="AL103" s="57" t="n"/>
+      <c r="AM103" s="57" t="n"/>
+      <c r="AN103" s="57" t="n"/>
+      <c r="AO103" s="57" t="n"/>
+      <c r="AP103" s="57" t="n"/>
+      <c r="AQ103" s="57" t="n"/>
+      <c r="AR103" s="57" t="n"/>
+      <c r="AS103" s="57" t="n"/>
+      <c r="AT103" s="57" t="n"/>
+      <c r="AU103" s="57" t="n"/>
+      <c r="AV103" s="57" t="n"/>
+      <c r="AW103" s="57" t="n"/>
+      <c r="AX103" s="57" t="n"/>
+      <c r="AY103" s="57" t="n"/>
+      <c r="AZ103" s="57" t="n"/>
+      <c r="BA103" s="57" t="n"/>
+      <c r="BB103" s="57" t="n"/>
+      <c r="BC103" s="57" t="n"/>
+      <c r="BD103" s="57" t="n"/>
+      <c r="BE103" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF103" s="57" t="n">
+        <v>40</v>
+      </c>
+      <c r="BG103" s="57" t="n"/>
+      <c r="BH103" s="57" t="n"/>
+      <c r="BI103" s="57" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B104" s="43" t="inlineStr">
+        <is>
+          <t>Rescue</t>
+        </is>
+      </c>
+      <c r="C104" s="43" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D104" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E104" s="56">
+        <f>ROUND('Towers'!$C$10*POWER('Tuning'!$B$12,D104),0)</f>
+        <v/>
+      </c>
+      <c r="F104" s="56">
+        <f>F103+E104</f>
+        <v/>
+      </c>
+      <c r="G104" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L104" s="57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M104" s="43" t="inlineStr">
+        <is>
+          <t>Rescue Beacon</t>
+        </is>
+      </c>
+      <c r="N104" s="57" t="n"/>
+      <c r="O104" s="57" t="n"/>
+      <c r="P104" s="57" t="n"/>
+      <c r="Q104" s="57" t="n"/>
+      <c r="R104" s="57" t="n"/>
+      <c r="S104" s="57" t="n"/>
+      <c r="T104" s="57" t="n"/>
+      <c r="U104" s="57" t="n"/>
+      <c r="V104" s="57" t="n"/>
+      <c r="W104" s="57" t="n"/>
+      <c r="X104" s="57" t="n"/>
+      <c r="Y104" s="57" t="n"/>
+      <c r="Z104" s="57" t="n"/>
+      <c r="AA104" s="57" t="n"/>
+      <c r="AB104" s="57" t="n"/>
+      <c r="AC104" s="57" t="n"/>
+      <c r="AD104" s="57" t="n"/>
+      <c r="AE104" s="57" t="n"/>
+      <c r="AF104" s="57" t="n"/>
+      <c r="AG104" s="57" t="n"/>
+      <c r="AH104" s="57" t="n"/>
+      <c r="AI104" s="57" t="n"/>
+      <c r="AJ104" s="57" t="n"/>
+      <c r="AK104" s="57" t="n"/>
+      <c r="AL104" s="57" t="n"/>
+      <c r="AM104" s="57" t="n"/>
+      <c r="AN104" s="57" t="n"/>
+      <c r="AO104" s="57" t="n"/>
+      <c r="AP104" s="57" t="n"/>
+      <c r="AQ104" s="57" t="n"/>
+      <c r="AR104" s="57" t="n"/>
+      <c r="AS104" s="57" t="n"/>
+      <c r="AT104" s="57" t="n"/>
+      <c r="AU104" s="57" t="n"/>
+      <c r="AV104" s="57" t="n"/>
+      <c r="AW104" s="57" t="n"/>
+      <c r="AX104" s="57" t="n"/>
+      <c r="AY104" s="57" t="n"/>
+      <c r="AZ104" s="57" t="n"/>
+      <c r="BA104" s="57" t="n"/>
+      <c r="BB104" s="57" t="n"/>
+      <c r="BC104" s="57" t="n"/>
+      <c r="BD104" s="57" t="n"/>
+      <c r="BE104" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF104" s="57" t="n">
+        <v>50</v>
+      </c>
+      <c r="BG104" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BH104" s="57" t="n"/>
+      <c r="BI104" s="57" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B105" s="43" t="inlineStr">
+        <is>
+          <t>Tonic</t>
+        </is>
+      </c>
+      <c r="C105" s="43" t="inlineStr">
+        <is>
+          <t>tougher towers</t>
+        </is>
+      </c>
+      <c r="D105" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="56">
+        <f>ROUND('Towers'!$C$10*POWER('Tuning'!$B$12,D105),0)</f>
+        <v/>
+      </c>
+      <c r="F105" s="56">
+        <f>'Towers'!$C$10+E105</f>
+        <v/>
+      </c>
+      <c r="G105" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L105" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" s="43" t="inlineStr">
+        <is>
+          <t>Camp Rations</t>
+        </is>
+      </c>
+      <c r="N105" s="57" t="n"/>
+      <c r="O105" s="57" t="n"/>
+      <c r="P105" s="57" t="n"/>
+      <c r="Q105" s="57" t="n"/>
+      <c r="R105" s="57" t="n"/>
+      <c r="S105" s="57" t="n"/>
+      <c r="T105" s="57" t="n"/>
+      <c r="U105" s="57" t="n"/>
+      <c r="V105" s="57" t="n"/>
+      <c r="W105" s="57" t="n"/>
+      <c r="X105" s="57" t="n"/>
+      <c r="Y105" s="57" t="n"/>
+      <c r="Z105" s="57" t="n"/>
+      <c r="AA105" s="57" t="n"/>
+      <c r="AB105" s="57" t="n"/>
+      <c r="AC105" s="57" t="n"/>
+      <c r="AD105" s="57" t="n"/>
+      <c r="AE105" s="57" t="n"/>
+      <c r="AF105" s="57" t="n"/>
+      <c r="AG105" s="57" t="n"/>
+      <c r="AH105" s="57" t="n"/>
+      <c r="AI105" s="57" t="n"/>
+      <c r="AJ105" s="57" t="n"/>
+      <c r="AK105" s="57" t="n"/>
+      <c r="AL105" s="57" t="n"/>
+      <c r="AM105" s="57" t="n"/>
+      <c r="AN105" s="57" t="n"/>
+      <c r="AO105" s="57" t="n"/>
+      <c r="AP105" s="57" t="n"/>
+      <c r="AQ105" s="57" t="n"/>
+      <c r="AR105" s="57" t="n"/>
+      <c r="AS105" s="57" t="n"/>
+      <c r="AT105" s="57" t="n"/>
+      <c r="AU105" s="57" t="n"/>
+      <c r="AV105" s="57" t="n"/>
+      <c r="AW105" s="57" t="n"/>
+      <c r="AX105" s="57" t="n"/>
+      <c r="AY105" s="57" t="n"/>
+      <c r="AZ105" s="57" t="n"/>
+      <c r="BA105" s="57" t="n"/>
+      <c r="BB105" s="57" t="n"/>
+      <c r="BC105" s="57" t="n"/>
+      <c r="BD105" s="57" t="n"/>
+      <c r="BE105" s="57" t="n"/>
+      <c r="BF105" s="57" t="n"/>
+      <c r="BG105" s="57" t="n"/>
+      <c r="BH105" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI105" s="57" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B106" s="43" t="inlineStr">
+        <is>
+          <t>Tonic</t>
+        </is>
+      </c>
+      <c r="C106" s="43" t="inlineStr">
+        <is>
+          <t>tougher towers</t>
+        </is>
+      </c>
+      <c r="D106" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E106" s="56">
+        <f>ROUND('Towers'!$C$10*POWER('Tuning'!$B$12,D106),0)</f>
+        <v/>
+      </c>
+      <c r="F106" s="56">
+        <f>F105+E106</f>
+        <v/>
+      </c>
+      <c r="G106" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L106" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" s="43" t="inlineStr">
+        <is>
+          <t>Iron Tonic</t>
+        </is>
+      </c>
+      <c r="N106" s="57" t="n"/>
+      <c r="O106" s="57" t="n"/>
+      <c r="P106" s="57" t="n"/>
+      <c r="Q106" s="57" t="n"/>
+      <c r="R106" s="57" t="n"/>
+      <c r="S106" s="57" t="n"/>
+      <c r="T106" s="57" t="n"/>
+      <c r="U106" s="57" t="n"/>
+      <c r="V106" s="57" t="n"/>
+      <c r="W106" s="57" t="n"/>
+      <c r="X106" s="57" t="n"/>
+      <c r="Y106" s="57" t="n"/>
+      <c r="Z106" s="57" t="n"/>
+      <c r="AA106" s="57" t="n"/>
+      <c r="AB106" s="57" t="n"/>
+      <c r="AC106" s="57" t="n"/>
+      <c r="AD106" s="57" t="n"/>
+      <c r="AE106" s="57" t="n"/>
+      <c r="AF106" s="57" t="n"/>
+      <c r="AG106" s="57" t="n"/>
+      <c r="AH106" s="57" t="n"/>
+      <c r="AI106" s="57" t="n"/>
+      <c r="AJ106" s="57" t="n"/>
+      <c r="AK106" s="57" t="n"/>
+      <c r="AL106" s="57" t="n"/>
+      <c r="AM106" s="57" t="n"/>
+      <c r="AN106" s="57" t="n"/>
+      <c r="AO106" s="57" t="n"/>
+      <c r="AP106" s="57" t="n"/>
+      <c r="AQ106" s="57" t="n"/>
+      <c r="AR106" s="57" t="n"/>
+      <c r="AS106" s="57" t="n"/>
+      <c r="AT106" s="57" t="n"/>
+      <c r="AU106" s="57" t="n"/>
+      <c r="AV106" s="57" t="n"/>
+      <c r="AW106" s="57" t="n"/>
+      <c r="AX106" s="57" t="n"/>
+      <c r="AY106" s="57" t="n"/>
+      <c r="AZ106" s="57" t="n"/>
+      <c r="BA106" s="57" t="n"/>
+      <c r="BB106" s="57" t="n"/>
+      <c r="BC106" s="57" t="n"/>
+      <c r="BD106" s="57" t="n"/>
+      <c r="BE106" s="57" t="n"/>
+      <c r="BF106" s="57" t="n"/>
+      <c r="BG106" s="57" t="n"/>
+      <c r="BH106" s="57" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI106" s="57" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B107" s="43" t="inlineStr">
+        <is>
+          <t>Tonic</t>
+        </is>
+      </c>
+      <c r="C107" s="43" t="inlineStr">
+        <is>
+          <t>tougher towers</t>
+        </is>
+      </c>
+      <c r="D107" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" s="56">
+        <f>ROUND('Towers'!$C$10*POWER('Tuning'!$B$12,D107),0)</f>
+        <v/>
+      </c>
+      <c r="F107" s="56">
+        <f>F106+E107</f>
+        <v/>
+      </c>
+      <c r="G107" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L107" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M107" s="43" t="inlineStr">
+        <is>
+          <t>Adrenaline</t>
+        </is>
+      </c>
+      <c r="N107" s="57" t="n"/>
+      <c r="O107" s="57" t="n"/>
+      <c r="P107" s="57" t="n"/>
+      <c r="Q107" s="57" t="n"/>
+      <c r="R107" s="57" t="n"/>
+      <c r="S107" s="57" t="n"/>
+      <c r="T107" s="57" t="n"/>
+      <c r="U107" s="57" t="n"/>
+      <c r="V107" s="57" t="n"/>
+      <c r="W107" s="57" t="n"/>
+      <c r="X107" s="57" t="n"/>
+      <c r="Y107" s="57" t="n"/>
+      <c r="Z107" s="57" t="n"/>
+      <c r="AA107" s="57" t="n"/>
+      <c r="AB107" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC107" s="57" t="n"/>
+      <c r="AD107" s="57" t="n"/>
+      <c r="AE107" s="57" t="n"/>
+      <c r="AF107" s="57" t="n"/>
+      <c r="AG107" s="57" t="n"/>
+      <c r="AH107" s="57" t="n"/>
+      <c r="AI107" s="57" t="n"/>
+      <c r="AJ107" s="57" t="n"/>
+      <c r="AK107" s="57" t="n"/>
+      <c r="AL107" s="57" t="n"/>
+      <c r="AM107" s="57" t="n"/>
+      <c r="AN107" s="57" t="n"/>
+      <c r="AO107" s="57" t="n"/>
+      <c r="AP107" s="57" t="n"/>
+      <c r="AQ107" s="57" t="n"/>
+      <c r="AR107" s="57" t="n"/>
+      <c r="AS107" s="57" t="n"/>
+      <c r="AT107" s="57" t="n"/>
+      <c r="AU107" s="57" t="n"/>
+      <c r="AV107" s="57" t="n"/>
+      <c r="AW107" s="57" t="n"/>
+      <c r="AX107" s="57" t="n"/>
+      <c r="AY107" s="57" t="n"/>
+      <c r="AZ107" s="57" t="n"/>
+      <c r="BA107" s="57" t="n"/>
+      <c r="BB107" s="57" t="n"/>
+      <c r="BC107" s="57" t="n"/>
+      <c r="BD107" s="57" t="n"/>
+      <c r="BE107" s="57" t="n"/>
+      <c r="BF107" s="57" t="n"/>
+      <c r="BG107" s="57" t="n"/>
+      <c r="BH107" s="57" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI107" s="57" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B108" s="43" t="inlineStr">
+        <is>
+          <t>Tonic</t>
+        </is>
+      </c>
+      <c r="C108" s="43" t="inlineStr">
+        <is>
+          <t>tougher towers</t>
+        </is>
+      </c>
+      <c r="D108" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E108" s="56">
+        <f>ROUND('Towers'!$C$10*POWER('Tuning'!$B$12,D108),0)</f>
+        <v/>
+      </c>
+      <c r="F108" s="56">
+        <f>F107+E108</f>
+        <v/>
+      </c>
+      <c r="G108" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L108" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M108" s="43" t="inlineStr">
+        <is>
+          <t>Bone Broth</t>
+        </is>
+      </c>
+      <c r="N108" s="57" t="n"/>
+      <c r="O108" s="57" t="n"/>
+      <c r="P108" s="57" t="n"/>
+      <c r="Q108" s="57" t="n"/>
+      <c r="R108" s="57" t="n"/>
+      <c r="S108" s="57" t="n"/>
+      <c r="T108" s="57" t="n"/>
+      <c r="U108" s="57" t="n"/>
+      <c r="V108" s="57" t="n"/>
+      <c r="W108" s="57" t="n"/>
+      <c r="X108" s="57" t="n"/>
+      <c r="Y108" s="57" t="n"/>
+      <c r="Z108" s="57" t="n"/>
+      <c r="AA108" s="57" t="n"/>
+      <c r="AB108" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC108" s="57" t="n"/>
+      <c r="AD108" s="57" t="n"/>
+      <c r="AE108" s="57" t="n"/>
+      <c r="AF108" s="57" t="n"/>
+      <c r="AG108" s="57" t="n"/>
+      <c r="AH108" s="57" t="n"/>
+      <c r="AI108" s="57" t="n"/>
+      <c r="AJ108" s="57" t="n"/>
+      <c r="AK108" s="57" t="n"/>
+      <c r="AL108" s="57" t="n"/>
+      <c r="AM108" s="57" t="n"/>
+      <c r="AN108" s="57" t="n"/>
+      <c r="AO108" s="57" t="n"/>
+      <c r="AP108" s="57" t="n"/>
+      <c r="AQ108" s="57" t="n"/>
+      <c r="AR108" s="57" t="n"/>
+      <c r="AS108" s="57" t="n"/>
+      <c r="AT108" s="57" t="n"/>
+      <c r="AU108" s="57" t="n"/>
+      <c r="AV108" s="57" t="n"/>
+      <c r="AW108" s="57" t="n"/>
+      <c r="AX108" s="57" t="n"/>
+      <c r="AY108" s="57" t="n"/>
+      <c r="AZ108" s="57" t="n"/>
+      <c r="BA108" s="57" t="n"/>
+      <c r="BB108" s="57" t="n"/>
+      <c r="BC108" s="57" t="n"/>
+      <c r="BD108" s="57" t="n"/>
+      <c r="BE108" s="57" t="n"/>
+      <c r="BF108" s="57" t="n"/>
+      <c r="BG108" s="57" t="n"/>
+      <c r="BH108" s="57" t="n">
+        <v>35</v>
+      </c>
+      <c r="BI108" s="57" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="43" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B109" s="43" t="inlineStr">
+        <is>
+          <t>Tonic</t>
+        </is>
+      </c>
+      <c r="C109" s="43" t="inlineStr">
+        <is>
+          <t>tougher towers</t>
+        </is>
+      </c>
+      <c r="D109" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E109" s="56">
+        <f>ROUND('Towers'!$C$10*POWER('Tuning'!$B$12,D109),0)</f>
+        <v/>
+      </c>
+      <c r="F109" s="56">
+        <f>F108+E109</f>
+        <v/>
+      </c>
+      <c r="G109" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="43" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L109" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M109" s="43" t="inlineStr">
+        <is>
+          <t>Last Stand</t>
+        </is>
+      </c>
+      <c r="N109" s="57" t="n"/>
+      <c r="O109" s="57" t="n"/>
+      <c r="P109" s="57" t="n"/>
+      <c r="Q109" s="57" t="n"/>
+      <c r="R109" s="57" t="n"/>
+      <c r="S109" s="57" t="n"/>
+      <c r="T109" s="57" t="n"/>
+      <c r="U109" s="57" t="n"/>
+      <c r="V109" s="57" t="n"/>
+      <c r="W109" s="57" t="n"/>
+      <c r="X109" s="57" t="n"/>
+      <c r="Y109" s="57" t="n"/>
+      <c r="Z109" s="57" t="n"/>
+      <c r="AA109" s="57" t="n"/>
+      <c r="AB109" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC109" s="57" t="n"/>
+      <c r="AD109" s="57" t="n"/>
+      <c r="AE109" s="57" t="n"/>
+      <c r="AF109" s="57" t="n"/>
+      <c r="AG109" s="57" t="n"/>
+      <c r="AH109" s="57" t="n"/>
+      <c r="AI109" s="57" t="n"/>
+      <c r="AJ109" s="57" t="n"/>
+      <c r="AK109" s="57" t="n"/>
+      <c r="AL109" s="57" t="n"/>
+      <c r="AM109" s="57" t="n"/>
+      <c r="AN109" s="57" t="n"/>
+      <c r="AO109" s="57" t="n"/>
+      <c r="AP109" s="57" t="n"/>
+      <c r="AQ109" s="57" t="n"/>
+      <c r="AR109" s="57" t="n"/>
+      <c r="AS109" s="57" t="n"/>
+      <c r="AT109" s="57" t="n"/>
+      <c r="AU109" s="57" t="n"/>
+      <c r="AV109" s="57" t="n"/>
+      <c r="AW109" s="57" t="n"/>
+      <c r="AX109" s="57" t="n"/>
+      <c r="AY109" s="57" t="n"/>
+      <c r="AZ109" s="57" t="n"/>
+      <c r="BA109" s="57" t="n"/>
+      <c r="BB109" s="57" t="n"/>
+      <c r="BC109" s="57" t="n"/>
+      <c r="BD109" s="57" t="n"/>
+      <c r="BE109" s="57" t="n"/>
+      <c r="BF109" s="57" t="n"/>
+      <c r="BG109" s="57" t="n"/>
+      <c r="BH109" s="57" t="n">
+        <v>50</v>
+      </c>
+      <c r="BI109" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -14800,7 +16460,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -15296,7 +16955,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -4216,7 +4216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -5451,6 +5451,26 @@
       <c r="D75" s="29" t="inlineStr">
         <is>
           <t>Burning ground is at least this wide either side, so a hero patch with no splash (Incendiary) is visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="26" t="inlineStr">
+        <is>
+          <t>Boss jaw lock x</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C76" s="28" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
+        <is>
+          <t>A boss hit by Jaw Lock is locked this share of the lock time (bosses also ignore the Medic slow).</t>
         </is>
       </c>
     </row>
@@ -16418,7 +16438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:AM8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="90" min="1" max="1"/>
@@ -16892,6 +16912,106 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>MEDIC</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>Triage Kit</t>
+        </is>
+      </c>
+      <c r="E8" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="43" t="inlineStr">
+        <is>
+          <t>semi</t>
+        </is>
+      </c>
+      <c r="H8" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" s="57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J8" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L8" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" s="57" t="n">
+        <v>12</v>
+      </c>
+      <c r="O8" s="57" t="n">
+        <v>45</v>
+      </c>
+      <c r="P8" s="43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q8" s="43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R8" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="57" t="n">
+        <v>40</v>
+      </c>
+      <c r="T8" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="57" t="n">
+        <v>20</v>
+      </c>
+      <c r="V8" s="57" t="n">
+        <v>35</v>
+      </c>
+      <c r="W8" s="43" t="inlineStr">
+        <is>
+          <t>Heal: power = HP healed (flat, not scaled by hero levels) to you and every hunter within radius. Triage adds tower repair (Patch Up) and Second Wind guard.</t>
+        </is>
+      </c>
+      <c r="X8" s="57" t="n">
+        <v>75</v>
+      </c>
+      <c r="Y8" s="43" t="inlineStr">
+        <is>
+          <t>Lever-Action Carbine</t>
+        </is>
+      </c>
+      <c r="Z8" s="43" t="inlineStr">
+        <is>
+          <t>HEAL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16903,7 +17023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI49"/>
+  <dimension ref="A1:AW69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="90" min="1" max="1"/>
@@ -16944,7 +17064,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>HERO UPGRADES — 3 heroes x 3 paths x 5 tiers (HEROES.md)</t>
+          <t>HERO UPGRADES — 4 heroes x 3 paths x 5 tiers (HEROES.md)</t>
         </is>
       </c>
     </row>
@@ -17129,6 +17249,51 @@
       <c r="AI4" s="21" t="inlineStr">
         <is>
           <t>Ignite tick (x shot)</t>
+        </is>
+      </c>
+      <c r="AJ4" s="21" t="inlineStr">
+        <is>
+          <t>Heal x</t>
+        </is>
+      </c>
+      <c r="AK4" s="21" t="inlineStr">
+        <is>
+          <t>Heal radius x</t>
+        </is>
+      </c>
+      <c r="AL4" s="21" t="inlineStr">
+        <is>
+          <t>Heal repairs towers</t>
+        </is>
+      </c>
+      <c r="AM4" s="21" t="inlineStr">
+        <is>
+          <t>Guard %</t>
+        </is>
+      </c>
+      <c r="AN4" s="21" t="inlineStr">
+        <is>
+          <t>Guard (s)</t>
+        </is>
+      </c>
+      <c r="AO4" s="21" t="inlineStr">
+        <is>
+          <t>Slow on hit %</t>
+        </is>
+      </c>
+      <c r="AP4" s="21" t="inlineStr">
+        <is>
+          <t>Slow on hit (s)</t>
+        </is>
+      </c>
+      <c r="AQ4" s="21" t="inlineStr">
+        <is>
+          <t>Jaw lock (s)</t>
+        </is>
+      </c>
+      <c r="AR4" s="21" t="inlineStr">
+        <is>
+          <t>Jaw lock spread (studs)</t>
         </is>
       </c>
     </row>
@@ -20144,6 +20309,1019 @@
       <c r="AH49" s="57" t="n"/>
       <c r="AI49" s="57" t="n"/>
     </row>
+    <row r="50">
+      <c r="A50" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B50" s="43" t="inlineStr">
+        <is>
+          <t>Triage</t>
+        </is>
+      </c>
+      <c r="C50" s="43" t="inlineStr">
+        <is>
+          <t>ability</t>
+        </is>
+      </c>
+      <c r="D50" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="43" t="inlineStr">
+        <is>
+          <t>Clean Bandages</t>
+        </is>
+      </c>
+      <c r="F50" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D50-1),0)</f>
+        <v/>
+      </c>
+      <c r="G50" s="57" t="n"/>
+      <c r="H50" s="57" t="n"/>
+      <c r="I50" s="57" t="n"/>
+      <c r="J50" s="57" t="n"/>
+      <c r="K50" s="57" t="n"/>
+      <c r="L50" s="57" t="n"/>
+      <c r="M50" s="57" t="n"/>
+      <c r="N50" s="57" t="n"/>
+      <c r="O50" s="57" t="n"/>
+      <c r="P50" s="57" t="n"/>
+      <c r="Q50" s="57" t="n"/>
+      <c r="R50" s="57" t="n"/>
+      <c r="S50" s="57" t="n"/>
+      <c r="T50" s="57" t="n"/>
+      <c r="U50" s="57" t="n"/>
+      <c r="V50" s="57" t="n"/>
+      <c r="W50" s="57" t="n"/>
+      <c r="X50" s="57" t="n"/>
+      <c r="Y50" s="57" t="n"/>
+      <c r="Z50" s="57" t="n"/>
+      <c r="AA50" s="57" t="n"/>
+      <c r="AB50" s="57" t="n"/>
+      <c r="AC50" s="57" t="n"/>
+      <c r="AD50" s="57" t="n"/>
+      <c r="AE50" s="57" t="n"/>
+      <c r="AF50" s="57" t="n"/>
+      <c r="AG50" s="57" t="n"/>
+      <c r="AH50" s="57" t="n"/>
+      <c r="AI50" s="57" t="n"/>
+      <c r="AJ50" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B51" s="43" t="inlineStr">
+        <is>
+          <t>Triage</t>
+        </is>
+      </c>
+      <c r="C51" s="43" t="inlineStr">
+        <is>
+          <t>ability</t>
+        </is>
+      </c>
+      <c r="D51" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="43" t="inlineStr">
+        <is>
+          <t>Belt Pouch</t>
+        </is>
+      </c>
+      <c r="F51" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D51-1),0)</f>
+        <v/>
+      </c>
+      <c r="G51" s="57" t="n"/>
+      <c r="H51" s="57" t="n"/>
+      <c r="I51" s="57" t="n"/>
+      <c r="J51" s="57" t="n"/>
+      <c r="K51" s="57" t="n"/>
+      <c r="L51" s="57" t="n"/>
+      <c r="M51" s="57" t="n"/>
+      <c r="N51" s="57" t="n"/>
+      <c r="O51" s="57" t="n"/>
+      <c r="P51" s="57" t="n"/>
+      <c r="Q51" s="57" t="n"/>
+      <c r="R51" s="57" t="n"/>
+      <c r="S51" s="57" t="n"/>
+      <c r="T51" s="57" t="n"/>
+      <c r="U51" s="57" t="n"/>
+      <c r="V51" s="57" t="n"/>
+      <c r="W51" s="57" t="n"/>
+      <c r="X51" s="57" t="n"/>
+      <c r="Y51" s="57" t="n"/>
+      <c r="Z51" s="57" t="n"/>
+      <c r="AA51" s="57" t="n"/>
+      <c r="AB51" s="57" t="n"/>
+      <c r="AC51" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD51" s="57" t="n"/>
+      <c r="AE51" s="57" t="n"/>
+      <c r="AF51" s="57" t="n"/>
+      <c r="AG51" s="57" t="n"/>
+      <c r="AH51" s="57" t="n"/>
+      <c r="AI51" s="57" t="n"/>
+      <c r="AJ51" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B52" s="43" t="inlineStr">
+        <is>
+          <t>Triage</t>
+        </is>
+      </c>
+      <c r="C52" s="43" t="inlineStr">
+        <is>
+          <t>ability</t>
+        </is>
+      </c>
+      <c r="D52" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="43" t="inlineStr">
+        <is>
+          <t>Patch Up</t>
+        </is>
+      </c>
+      <c r="F52" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D52-1),0)</f>
+        <v/>
+      </c>
+      <c r="G52" s="57" t="n"/>
+      <c r="H52" s="57" t="n"/>
+      <c r="I52" s="57" t="n"/>
+      <c r="J52" s="57" t="n"/>
+      <c r="K52" s="57" t="n"/>
+      <c r="L52" s="57" t="n"/>
+      <c r="M52" s="57" t="n"/>
+      <c r="N52" s="57" t="n"/>
+      <c r="O52" s="57" t="n"/>
+      <c r="P52" s="57" t="n"/>
+      <c r="Q52" s="57" t="n"/>
+      <c r="R52" s="57" t="n"/>
+      <c r="S52" s="57" t="n"/>
+      <c r="T52" s="57" t="n"/>
+      <c r="U52" s="57" t="n"/>
+      <c r="V52" s="57" t="n"/>
+      <c r="W52" s="57" t="n"/>
+      <c r="X52" s="57" t="n"/>
+      <c r="Y52" s="57" t="n"/>
+      <c r="Z52" s="57" t="n"/>
+      <c r="AA52" s="57" t="n"/>
+      <c r="AB52" s="57" t="n"/>
+      <c r="AC52" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD52" s="57" t="n"/>
+      <c r="AE52" s="57" t="n"/>
+      <c r="AF52" s="57" t="n"/>
+      <c r="AG52" s="57" t="n"/>
+      <c r="AH52" s="57" t="n"/>
+      <c r="AI52" s="57" t="n"/>
+      <c r="AJ52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B53" s="43" t="inlineStr">
+        <is>
+          <t>Triage</t>
+        </is>
+      </c>
+      <c r="C53" s="43" t="inlineStr">
+        <is>
+          <t>ability</t>
+        </is>
+      </c>
+      <c r="D53" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" s="43" t="inlineStr">
+        <is>
+          <t>Triage Tent</t>
+        </is>
+      </c>
+      <c r="F53" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D53-1),0)</f>
+        <v/>
+      </c>
+      <c r="G53" s="57" t="n"/>
+      <c r="H53" s="57" t="n"/>
+      <c r="I53" s="57" t="n"/>
+      <c r="J53" s="57" t="n"/>
+      <c r="K53" s="57" t="n"/>
+      <c r="L53" s="57" t="n"/>
+      <c r="M53" s="57" t="n"/>
+      <c r="N53" s="57" t="n"/>
+      <c r="O53" s="57" t="n"/>
+      <c r="P53" s="57" t="n"/>
+      <c r="Q53" s="57" t="n"/>
+      <c r="R53" s="57" t="n"/>
+      <c r="S53" s="57" t="n"/>
+      <c r="T53" s="57" t="n"/>
+      <c r="U53" s="57" t="n"/>
+      <c r="V53" s="57" t="n"/>
+      <c r="W53" s="57" t="n"/>
+      <c r="X53" s="57" t="n"/>
+      <c r="Y53" s="57" t="n"/>
+      <c r="Z53" s="57" t="n"/>
+      <c r="AA53" s="57" t="n"/>
+      <c r="AB53" s="57" t="n"/>
+      <c r="AC53" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD53" s="57" t="n"/>
+      <c r="AE53" s="57" t="n"/>
+      <c r="AF53" s="57" t="n"/>
+      <c r="AG53" s="57" t="n"/>
+      <c r="AH53" s="57" t="n"/>
+      <c r="AI53" s="57" t="n"/>
+      <c r="AJ53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B54" s="43" t="inlineStr">
+        <is>
+          <t>Triage</t>
+        </is>
+      </c>
+      <c r="C54" s="43" t="inlineStr">
+        <is>
+          <t>ability</t>
+        </is>
+      </c>
+      <c r="D54" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E54" s="43" t="inlineStr">
+        <is>
+          <t>Second Wind</t>
+        </is>
+      </c>
+      <c r="F54" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D54-1),0)</f>
+        <v/>
+      </c>
+      <c r="G54" s="57" t="n"/>
+      <c r="H54" s="57" t="n"/>
+      <c r="I54" s="57" t="n"/>
+      <c r="J54" s="57" t="n"/>
+      <c r="K54" s="57" t="n"/>
+      <c r="L54" s="57" t="n"/>
+      <c r="M54" s="57" t="n"/>
+      <c r="N54" s="57" t="n"/>
+      <c r="O54" s="57" t="n"/>
+      <c r="P54" s="57" t="n"/>
+      <c r="Q54" s="57" t="n"/>
+      <c r="R54" s="57" t="n"/>
+      <c r="S54" s="57" t="n"/>
+      <c r="T54" s="57" t="n"/>
+      <c r="U54" s="57" t="n"/>
+      <c r="V54" s="57" t="n"/>
+      <c r="W54" s="57" t="n"/>
+      <c r="X54" s="57" t="n"/>
+      <c r="Y54" s="57" t="n"/>
+      <c r="Z54" s="57" t="n"/>
+      <c r="AA54" s="57" t="n"/>
+      <c r="AB54" s="57" t="n"/>
+      <c r="AC54" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD54" s="57" t="n"/>
+      <c r="AE54" s="57" t="n"/>
+      <c r="AF54" s="57" t="n"/>
+      <c r="AG54" s="57" t="n"/>
+      <c r="AH54" s="57" t="n"/>
+      <c r="AI54" s="57" t="n"/>
+      <c r="AJ54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM54" t="n">
+        <v>30</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B55" s="43" t="inlineStr">
+        <is>
+          <t>Lever Action</t>
+        </is>
+      </c>
+      <c r="C55" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D55" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="43" t="inlineStr">
+        <is>
+          <t>Oiled Lever</t>
+        </is>
+      </c>
+      <c r="F55" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D55-1),0)</f>
+        <v/>
+      </c>
+      <c r="G55" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H55" s="57" t="n"/>
+      <c r="I55" s="57" t="n"/>
+      <c r="J55" s="57" t="n"/>
+      <c r="K55" s="57" t="n"/>
+      <c r="L55" s="57" t="n"/>
+      <c r="M55" s="57" t="n"/>
+      <c r="N55" s="57" t="n"/>
+      <c r="O55" s="57" t="n"/>
+      <c r="P55" s="57" t="n"/>
+      <c r="Q55" s="57" t="n"/>
+      <c r="R55" s="57" t="n"/>
+      <c r="S55" s="57" t="n"/>
+      <c r="T55" s="57" t="n"/>
+      <c r="U55" s="57" t="n"/>
+      <c r="V55" s="57" t="n"/>
+      <c r="W55" s="57" t="n"/>
+      <c r="X55" s="57" t="n"/>
+      <c r="Y55" s="57" t="n"/>
+      <c r="Z55" s="57" t="n"/>
+      <c r="AA55" s="57" t="n"/>
+      <c r="AB55" s="57" t="n"/>
+      <c r="AC55" s="57" t="n"/>
+      <c r="AD55" s="57" t="n"/>
+      <c r="AE55" s="57" t="n"/>
+      <c r="AF55" s="57" t="n"/>
+      <c r="AG55" s="57" t="n"/>
+      <c r="AH55" s="57" t="n"/>
+      <c r="AI55" s="57" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B56" s="43" t="inlineStr">
+        <is>
+          <t>Lever Action</t>
+        </is>
+      </c>
+      <c r="C56" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D56" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" s="43" t="inlineStr">
+        <is>
+          <t>Loading Gate</t>
+        </is>
+      </c>
+      <c r="F56" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D56-1),0)</f>
+        <v/>
+      </c>
+      <c r="G56" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H56" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I56" s="57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J56" s="57" t="n"/>
+      <c r="K56" s="57" t="n"/>
+      <c r="L56" s="57" t="n"/>
+      <c r="M56" s="57" t="n"/>
+      <c r="N56" s="57" t="n"/>
+      <c r="O56" s="57" t="n"/>
+      <c r="P56" s="57" t="n"/>
+      <c r="Q56" s="57" t="n"/>
+      <c r="R56" s="57" t="n"/>
+      <c r="S56" s="57" t="n"/>
+      <c r="T56" s="57" t="n"/>
+      <c r="U56" s="57" t="n"/>
+      <c r="V56" s="57" t="n"/>
+      <c r="W56" s="57" t="n"/>
+      <c r="X56" s="57" t="n"/>
+      <c r="Y56" s="57" t="n"/>
+      <c r="Z56" s="57" t="n"/>
+      <c r="AA56" s="57" t="n"/>
+      <c r="AB56" s="57" t="n"/>
+      <c r="AC56" s="57" t="n"/>
+      <c r="AD56" s="57" t="n"/>
+      <c r="AE56" s="57" t="n"/>
+      <c r="AF56" s="57" t="n"/>
+      <c r="AG56" s="57" t="n"/>
+      <c r="AH56" s="57" t="n"/>
+      <c r="AI56" s="57" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B57" s="43" t="inlineStr">
+        <is>
+          <t>Lever Action</t>
+        </is>
+      </c>
+      <c r="C57" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D57" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" s="43" t="inlineStr">
+        <is>
+          <t>Rapid Cycle</t>
+        </is>
+      </c>
+      <c r="F57" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D57-1),0)</f>
+        <v/>
+      </c>
+      <c r="G57" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H57" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I57" s="57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J57" s="57" t="n"/>
+      <c r="K57" s="57" t="n"/>
+      <c r="L57" s="57" t="n"/>
+      <c r="M57" s="57" t="n"/>
+      <c r="N57" s="57" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="O57" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="P57" s="57" t="n"/>
+      <c r="Q57" s="57" t="n"/>
+      <c r="R57" s="57" t="n"/>
+      <c r="S57" s="57" t="n"/>
+      <c r="T57" s="57" t="n"/>
+      <c r="U57" s="57" t="n"/>
+      <c r="V57" s="57" t="n"/>
+      <c r="W57" s="57" t="n"/>
+      <c r="X57" s="57" t="n"/>
+      <c r="Y57" s="57" t="n"/>
+      <c r="Z57" s="57" t="n"/>
+      <c r="AA57" s="57" t="n"/>
+      <c r="AB57" s="57" t="n"/>
+      <c r="AC57" s="57" t="n"/>
+      <c r="AD57" s="57" t="n"/>
+      <c r="AE57" s="57" t="n"/>
+      <c r="AF57" s="57" t="n"/>
+      <c r="AG57" s="57" t="n"/>
+      <c r="AH57" s="57" t="n"/>
+      <c r="AI57" s="57" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B58" s="43" t="inlineStr">
+        <is>
+          <t>Lever Action</t>
+        </is>
+      </c>
+      <c r="C58" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D58" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" s="43" t="inlineStr">
+        <is>
+          <t>Smooth Action</t>
+        </is>
+      </c>
+      <c r="F58" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D58-1),0)</f>
+        <v/>
+      </c>
+      <c r="G58" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H58" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I58" s="57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J58" s="57" t="n"/>
+      <c r="K58" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L58" s="57" t="n"/>
+      <c r="M58" s="57" t="n"/>
+      <c r="N58" s="57" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="O58" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="P58" s="57" t="n"/>
+      <c r="Q58" s="57" t="n"/>
+      <c r="R58" s="57" t="n"/>
+      <c r="S58" s="57" t="n"/>
+      <c r="T58" s="57" t="n"/>
+      <c r="U58" s="57" t="n"/>
+      <c r="V58" s="57" t="n"/>
+      <c r="W58" s="57" t="n"/>
+      <c r="X58" s="57" t="n"/>
+      <c r="Y58" s="57" t="n"/>
+      <c r="Z58" s="57" t="n"/>
+      <c r="AA58" s="57" t="n"/>
+      <c r="AB58" s="57" t="n"/>
+      <c r="AC58" s="57" t="n"/>
+      <c r="AD58" s="57" t="n"/>
+      <c r="AE58" s="57" t="n"/>
+      <c r="AF58" s="57" t="n"/>
+      <c r="AG58" s="57" t="n"/>
+      <c r="AH58" s="57" t="n"/>
+      <c r="AI58" s="57" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B59" s="43" t="inlineStr">
+        <is>
+          <t>Lever Action</t>
+        </is>
+      </c>
+      <c r="C59" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D59" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E59" s="43" t="inlineStr">
+        <is>
+          <t>Hip Fire</t>
+        </is>
+      </c>
+      <c r="F59" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D59-1),0)</f>
+        <v/>
+      </c>
+      <c r="G59" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H59" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I59" s="57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J59" s="57" t="n"/>
+      <c r="K59" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L59" s="57" t="n"/>
+      <c r="M59" s="57" t="n"/>
+      <c r="N59" s="57" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="O59" s="57" t="n"/>
+      <c r="P59" s="57" t="n"/>
+      <c r="Q59" s="57" t="n"/>
+      <c r="R59" s="57" t="n"/>
+      <c r="S59" s="57" t="n"/>
+      <c r="T59" s="57" t="n"/>
+      <c r="U59" s="57" t="n"/>
+      <c r="V59" s="57" t="n"/>
+      <c r="W59" s="57" t="n"/>
+      <c r="X59" s="57" t="n"/>
+      <c r="Y59" s="57" t="n"/>
+      <c r="Z59" s="57" t="n"/>
+      <c r="AA59" s="57" t="n"/>
+      <c r="AB59" s="57" t="n"/>
+      <c r="AC59" s="57" t="n"/>
+      <c r="AD59" s="57" t="n"/>
+      <c r="AE59" s="57" t="n"/>
+      <c r="AF59" s="57" t="n"/>
+      <c r="AG59" s="57" t="n"/>
+      <c r="AH59" s="57" t="n"/>
+      <c r="AI59" s="57" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B60" s="43" t="inlineStr">
+        <is>
+          <t>Muzzle</t>
+        </is>
+      </c>
+      <c r="C60" s="43" t="inlineStr">
+        <is>
+          <t>protective rounds</t>
+        </is>
+      </c>
+      <c r="D60" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="43" t="inlineStr">
+        <is>
+          <t>Tranq Tips</t>
+        </is>
+      </c>
+      <c r="F60" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D60-1),0)</f>
+        <v/>
+      </c>
+      <c r="G60" s="57" t="n"/>
+      <c r="H60" s="57" t="n"/>
+      <c r="I60" s="57" t="n"/>
+      <c r="J60" s="57" t="n"/>
+      <c r="K60" s="57" t="n"/>
+      <c r="L60" s="57" t="n"/>
+      <c r="M60" s="57" t="n"/>
+      <c r="N60" s="57" t="n"/>
+      <c r="O60" s="57" t="n"/>
+      <c r="P60" s="57" t="n"/>
+      <c r="Q60" s="57" t="n"/>
+      <c r="R60" s="57" t="n"/>
+      <c r="S60" s="57" t="n"/>
+      <c r="T60" s="57" t="n"/>
+      <c r="U60" s="57" t="n"/>
+      <c r="V60" s="57" t="n"/>
+      <c r="W60" s="57" t="n"/>
+      <c r="X60" s="57" t="n"/>
+      <c r="Y60" s="57" t="n"/>
+      <c r="Z60" s="57" t="n"/>
+      <c r="AA60" s="57" t="n"/>
+      <c r="AB60" s="57" t="n"/>
+      <c r="AC60" s="57" t="n"/>
+      <c r="AD60" s="57" t="n"/>
+      <c r="AE60" s="57" t="n"/>
+      <c r="AF60" s="57" t="n"/>
+      <c r="AG60" s="57" t="n"/>
+      <c r="AH60" s="57" t="n"/>
+      <c r="AI60" s="57" t="n"/>
+      <c r="AO60" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B61" s="43" t="inlineStr">
+        <is>
+          <t>Muzzle</t>
+        </is>
+      </c>
+      <c r="C61" s="43" t="inlineStr">
+        <is>
+          <t>protective rounds</t>
+        </is>
+      </c>
+      <c r="D61" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="43" t="inlineStr">
+        <is>
+          <t>Double Dose</t>
+        </is>
+      </c>
+      <c r="F61" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D61-1),0)</f>
+        <v/>
+      </c>
+      <c r="G61" s="57" t="n"/>
+      <c r="H61" s="57" t="n"/>
+      <c r="I61" s="57" t="n"/>
+      <c r="J61" s="57" t="n"/>
+      <c r="K61" s="57" t="n"/>
+      <c r="L61" s="57" t="n"/>
+      <c r="M61" s="57" t="n"/>
+      <c r="N61" s="57" t="n"/>
+      <c r="O61" s="57" t="n"/>
+      <c r="P61" s="57" t="n"/>
+      <c r="Q61" s="57" t="n"/>
+      <c r="R61" s="57" t="n"/>
+      <c r="S61" s="57" t="n"/>
+      <c r="T61" s="57" t="n"/>
+      <c r="U61" s="57" t="n"/>
+      <c r="V61" s="57" t="n"/>
+      <c r="W61" s="57" t="n"/>
+      <c r="X61" s="57" t="n"/>
+      <c r="Y61" s="57" t="n"/>
+      <c r="Z61" s="57" t="n"/>
+      <c r="AA61" s="57" t="n"/>
+      <c r="AB61" s="57" t="n"/>
+      <c r="AC61" s="57" t="n"/>
+      <c r="AD61" s="57" t="n"/>
+      <c r="AE61" s="57" t="n"/>
+      <c r="AF61" s="57" t="n"/>
+      <c r="AG61" s="57" t="n"/>
+      <c r="AH61" s="57" t="n"/>
+      <c r="AI61" s="57" t="n"/>
+      <c r="AO61" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B62" s="43" t="inlineStr">
+        <is>
+          <t>Muzzle</t>
+        </is>
+      </c>
+      <c r="C62" s="43" t="inlineStr">
+        <is>
+          <t>protective rounds</t>
+        </is>
+      </c>
+      <c r="D62" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" s="43" t="inlineStr">
+        <is>
+          <t>Jaw Lock</t>
+        </is>
+      </c>
+      <c r="F62" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D62-1),0)</f>
+        <v/>
+      </c>
+      <c r="G62" s="57" t="n"/>
+      <c r="H62" s="57" t="n"/>
+      <c r="I62" s="57" t="n"/>
+      <c r="J62" s="57" t="n"/>
+      <c r="K62" s="57" t="n"/>
+      <c r="L62" s="57" t="n"/>
+      <c r="M62" s="57" t="n"/>
+      <c r="N62" s="57" t="n"/>
+      <c r="O62" s="57" t="n"/>
+      <c r="P62" s="57" t="n"/>
+      <c r="Q62" s="57" t="n"/>
+      <c r="R62" s="57" t="n"/>
+      <c r="S62" s="57" t="n"/>
+      <c r="T62" s="57" t="n"/>
+      <c r="U62" s="57" t="n"/>
+      <c r="V62" s="57" t="n"/>
+      <c r="W62" s="57" t="n"/>
+      <c r="X62" s="57" t="n"/>
+      <c r="Y62" s="57" t="n"/>
+      <c r="Z62" s="57" t="n"/>
+      <c r="AA62" s="57" t="n"/>
+      <c r="AB62" s="57" t="n"/>
+      <c r="AC62" s="57" t="n"/>
+      <c r="AD62" s="57" t="n"/>
+      <c r="AE62" s="57" t="n"/>
+      <c r="AF62" s="57" t="n"/>
+      <c r="AG62" s="57" t="n"/>
+      <c r="AH62" s="57" t="n"/>
+      <c r="AI62" s="57" t="n"/>
+      <c r="AO62" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B63" s="43" t="inlineStr">
+        <is>
+          <t>Muzzle</t>
+        </is>
+      </c>
+      <c r="C63" s="43" t="inlineStr">
+        <is>
+          <t>protective rounds</t>
+        </is>
+      </c>
+      <c r="D63" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" s="43" t="inlineStr">
+        <is>
+          <t>Long Dose</t>
+        </is>
+      </c>
+      <c r="F63" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D63-1),0)</f>
+        <v/>
+      </c>
+      <c r="G63" s="57" t="n"/>
+      <c r="H63" s="57" t="n"/>
+      <c r="I63" s="57" t="n"/>
+      <c r="J63" s="57" t="n"/>
+      <c r="K63" s="57" t="n"/>
+      <c r="L63" s="57" t="n"/>
+      <c r="M63" s="57" t="n"/>
+      <c r="N63" s="57" t="n"/>
+      <c r="O63" s="57" t="n"/>
+      <c r="P63" s="57" t="n"/>
+      <c r="Q63" s="57" t="n"/>
+      <c r="R63" s="57" t="n"/>
+      <c r="S63" s="57" t="n"/>
+      <c r="T63" s="57" t="n"/>
+      <c r="U63" s="57" t="n"/>
+      <c r="V63" s="57" t="n"/>
+      <c r="W63" s="57" t="n"/>
+      <c r="X63" s="57" t="n"/>
+      <c r="Y63" s="57" t="n"/>
+      <c r="Z63" s="57" t="n"/>
+      <c r="AA63" s="57" t="n"/>
+      <c r="AB63" s="57" t="n"/>
+      <c r="AC63" s="57" t="n"/>
+      <c r="AD63" s="57" t="n"/>
+      <c r="AE63" s="57" t="n"/>
+      <c r="AF63" s="57" t="n"/>
+      <c r="AG63" s="57" t="n"/>
+      <c r="AH63" s="57" t="n"/>
+      <c r="AI63" s="57" t="n"/>
+      <c r="AO63" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B64" s="43" t="inlineStr">
+        <is>
+          <t>Muzzle</t>
+        </is>
+      </c>
+      <c r="C64" s="43" t="inlineStr">
+        <is>
+          <t>protective rounds</t>
+        </is>
+      </c>
+      <c r="D64" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" s="43" t="inlineStr">
+        <is>
+          <t>Lullaby Rounds</t>
+        </is>
+      </c>
+      <c r="F64" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D64-1),0)</f>
+        <v/>
+      </c>
+      <c r="G64" s="57" t="n"/>
+      <c r="H64" s="57" t="n"/>
+      <c r="I64" s="57" t="n"/>
+      <c r="J64" s="57" t="n"/>
+      <c r="K64" s="57" t="n"/>
+      <c r="L64" s="57" t="n"/>
+      <c r="M64" s="57" t="n"/>
+      <c r="N64" s="57" t="n"/>
+      <c r="O64" s="57" t="n"/>
+      <c r="P64" s="57" t="n"/>
+      <c r="Q64" s="57" t="n"/>
+      <c r="R64" s="57" t="n"/>
+      <c r="S64" s="57" t="n"/>
+      <c r="T64" s="57" t="n"/>
+      <c r="U64" s="57" t="n"/>
+      <c r="V64" s="57" t="n"/>
+      <c r="W64" s="57" t="n"/>
+      <c r="X64" s="57" t="n"/>
+      <c r="Y64" s="57" t="n"/>
+      <c r="Z64" s="57" t="n"/>
+      <c r="AA64" s="57" t="n"/>
+      <c r="AB64" s="57" t="n"/>
+      <c r="AC64" s="57" t="n"/>
+      <c r="AD64" s="57" t="n"/>
+      <c r="AE64" s="57" t="n"/>
+      <c r="AF64" s="57" t="n"/>
+      <c r="AG64" s="57" t="n"/>
+      <c r="AH64" s="57" t="n"/>
+      <c r="AI64" s="57" t="n"/>
+      <c r="AO64" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -6202,7 +6202,7 @@
     <row r="1" ht="18.5" customHeight="1" s="90">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>TOWER UPGRADES — 5 towers x 3 paths x 5 tiers</t>
+          <t>TOWER UPGRADES — 7 towers x 3 paths x 5 tiers</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -15730,7 +15730,7 @@
       </c>
       <c r="M103" s="43" t="inlineStr">
         <is>
-          <t>Supply Runs</t>
+          <t>Pack Mules</t>
         </is>
       </c>
       <c r="N103" s="57" t="n"/>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="M107" s="43" t="inlineStr">
         <is>
-          <t>Adrenaline</t>
+          <t>Smelling Salts</t>
         </is>
       </c>
       <c r="N107" s="57" t="n"/>
@@ -16438,7 +16438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="90" min="1" max="1"/>
@@ -17023,7 +17023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW69"/>
+  <dimension ref="A1:AR64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="90" min="1" max="1"/>
@@ -20366,7 +20366,7 @@
       <c r="AG50" s="57" t="n"/>
       <c r="AH50" s="57" t="n"/>
       <c r="AI50" s="57" t="n"/>
-      <c r="AJ50" t="n">
+      <c r="AJ50" s="81" t="n">
         <v>1.25</v>
       </c>
     </row>
@@ -20429,7 +20429,7 @@
       <c r="AG51" s="57" t="n"/>
       <c r="AH51" s="57" t="n"/>
       <c r="AI51" s="57" t="n"/>
-      <c r="AJ51" t="n">
+      <c r="AJ51" s="81" t="n">
         <v>1.25</v>
       </c>
     </row>
@@ -20492,10 +20492,10 @@
       <c r="AG52" s="57" t="n"/>
       <c r="AH52" s="57" t="n"/>
       <c r="AI52" s="57" t="n"/>
-      <c r="AJ52" t="n">
+      <c r="AJ52" s="81" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL52" t="inlineStr">
+      <c r="AL52" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -20560,13 +20560,13 @@
       <c r="AG53" s="57" t="n"/>
       <c r="AH53" s="57" t="n"/>
       <c r="AI53" s="57" t="n"/>
-      <c r="AJ53" t="n">
+      <c r="AJ53" s="81" t="n">
         <v>1.25</v>
       </c>
-      <c r="AK53" t="n">
+      <c r="AK53" s="81" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL53" t="inlineStr">
+      <c r="AL53" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -20631,21 +20631,21 @@
       <c r="AG54" s="57" t="n"/>
       <c r="AH54" s="57" t="n"/>
       <c r="AI54" s="57" t="n"/>
-      <c r="AJ54" t="n">
+      <c r="AJ54" s="81" t="n">
         <v>1.25</v>
       </c>
-      <c r="AK54" t="n">
+      <c r="AK54" s="81" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL54" t="inlineStr">
+      <c r="AL54" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AM54" t="n">
+      <c r="AM54" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="AN54" t="n">
+      <c r="AN54" s="81" t="n">
         <v>8</v>
       </c>
     </row>
@@ -21042,10 +21042,10 @@
       <c r="AG60" s="57" t="n"/>
       <c r="AH60" s="57" t="n"/>
       <c r="AI60" s="57" t="n"/>
-      <c r="AO60" t="n">
+      <c r="AO60" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="AP60" t="n">
+      <c r="AP60" s="81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21106,10 +21106,10 @@
       <c r="AG61" s="57" t="n"/>
       <c r="AH61" s="57" t="n"/>
       <c r="AI61" s="57" t="n"/>
-      <c r="AO61" t="n">
+      <c r="AO61" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="AP61" t="n">
+      <c r="AP61" s="81" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -21170,13 +21170,13 @@
       <c r="AG62" s="57" t="n"/>
       <c r="AH62" s="57" t="n"/>
       <c r="AI62" s="57" t="n"/>
-      <c r="AO62" t="n">
+      <c r="AO62" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="AP62" t="n">
+      <c r="AP62" s="81" t="n">
         <v>1.5</v>
       </c>
-      <c r="AQ62" t="n">
+      <c r="AQ62" s="81" t="n">
         <v>2</v>
       </c>
     </row>
@@ -21237,13 +21237,13 @@
       <c r="AG63" s="57" t="n"/>
       <c r="AH63" s="57" t="n"/>
       <c r="AI63" s="57" t="n"/>
-      <c r="AO63" t="n">
+      <c r="AO63" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="AP63" t="n">
+      <c r="AP63" s="81" t="n">
         <v>1.5</v>
       </c>
-      <c r="AQ63" t="n">
+      <c r="AQ63" s="81" t="n">
         <v>3</v>
       </c>
     </row>
@@ -21304,24 +21304,19 @@
       <c r="AG64" s="57" t="n"/>
       <c r="AH64" s="57" t="n"/>
       <c r="AI64" s="57" t="n"/>
-      <c r="AO64" t="n">
+      <c r="AO64" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="AP64" t="n">
+      <c r="AP64" s="81" t="n">
         <v>1.5</v>
       </c>
-      <c r="AQ64" t="n">
+      <c r="AQ64" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="AR64" t="n">
+      <c r="AR64" s="81" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -20936,7 +20936,7 @@
       </c>
       <c r="E59" s="43" t="inlineStr">
         <is>
-          <t>Hip Fire</t>
+          <t>Runaway Lever</t>
         </is>
       </c>
       <c r="F59" s="56">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9243,7 +9243,7 @@
       </c>
       <c r="M34" s="43" t="inlineStr">
         <is>
-          <t>Skybreaker</t>
+          <t>Extinction Round</t>
         </is>
       </c>
       <c r="N34" s="57" t="n"/>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="M44" s="43" t="inlineStr">
         <is>
-          <t>Storm of Steel</t>
+          <t>Meteor Shower</t>
         </is>
       </c>
       <c r="N44" s="57" t="n"/>
@@ -11707,7 +11707,7 @@
       </c>
       <c r="M61" s="43" t="inlineStr">
         <is>
-          <t>Crack Armor</t>
+          <t>Find the Gap</t>
         </is>
       </c>
       <c r="N61" s="57" t="n"/>
@@ -18162,7 +18162,7 @@
       </c>
       <c r="E18" s="43" t="inlineStr">
         <is>
-          <t>Quick Mark</t>
+          <t>Quick Dart</t>
         </is>
       </c>
       <c r="F18" s="56">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -24,9 +24,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0#"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -460,7 +461,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -751,6 +752,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -5494,7 +5498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -5657,6 +5661,11 @@
           <t>Resist %</t>
         </is>
       </c>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>Upgrade cost growth</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -5992,6 +6001,9 @@
       <c r="R9" s="27" t="n">
         <v>0</v>
       </c>
+      <c r="S9" s="98" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="10" ht="13.55" customHeight="1" s="90">
       <c r="A10" s="43" t="inlineStr">
@@ -6127,6 +6139,7 @@
         <v>15</v>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
         <is>
@@ -12054,7 +12067,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="56">
-        <f t="array" ref="E65">ROUND('Towers'!$C$9*POWER('Tuning'!$B$12,D65),0)</f>
+        <f t="array" ref="E65">ROUND('Towers'!$C$9*POWER('Towers'!$S$9,D65),0)</f>
         <v/>
       </c>
       <c r="F65" s="56">
@@ -12113,7 +12126,7 @@
       <c r="AL65" s="57" t="n"/>
       <c r="AM65" s="57" t="n"/>
       <c r="AN65" s="57" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AO65" s="57" t="n"/>
       <c r="AP65" s="57" t="n"/>
@@ -12142,7 +12155,7 @@
         <v>2</v>
       </c>
       <c r="E66" s="56">
-        <f t="array" ref="E66">ROUND('Towers'!$C$9*POWER('Tuning'!$B$12,D66),0)</f>
+        <f t="array" ref="E66">ROUND('Towers'!$C$9*POWER('Towers'!$S$9,D66),0)</f>
         <v/>
       </c>
       <c r="F66" s="56">
@@ -12201,7 +12214,7 @@
       <c r="AL66" s="57" t="n"/>
       <c r="AM66" s="57" t="n"/>
       <c r="AN66" s="57" t="n">
-        <v>1.7</v>
+        <v>3.85</v>
       </c>
       <c r="AO66" s="57" t="n"/>
       <c r="AP66" s="57" t="n"/>
@@ -12230,7 +12243,7 @@
         <v>3</v>
       </c>
       <c r="E67" s="56">
-        <f t="array" ref="E67">ROUND('Towers'!$C$9*POWER('Tuning'!$B$12,D67),0)</f>
+        <f t="array" ref="E67">ROUND('Towers'!$C$9*POWER('Towers'!$S$9,D67),0)</f>
         <v/>
       </c>
       <c r="F67" s="56">
@@ -12289,7 +12302,7 @@
       <c r="AL67" s="57" t="n"/>
       <c r="AM67" s="57" t="n"/>
       <c r="AN67" s="57" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="AO67" s="57" t="n"/>
       <c r="AP67" s="57" t="n"/>
@@ -12318,7 +12331,7 @@
         <v>4</v>
       </c>
       <c r="E68" s="56">
-        <f t="array" ref="E68">ROUND('Towers'!$C$9*POWER('Tuning'!$B$12,D68),0)</f>
+        <f t="array" ref="E68">ROUND('Towers'!$C$9*POWER('Towers'!$S$9,D68),0)</f>
         <v/>
       </c>
       <c r="F68" s="56">
@@ -12377,7 +12390,7 @@
       <c r="AL68" s="57" t="n"/>
       <c r="AM68" s="57" t="n"/>
       <c r="AN68" s="57" t="n">
-        <v>3</v>
+        <v>11.1</v>
       </c>
       <c r="AO68" s="57" t="n"/>
       <c r="AP68" s="57" t="n"/>
@@ -12406,7 +12419,7 @@
         <v>5</v>
       </c>
       <c r="E69" s="56">
-        <f t="array" ref="E69">ROUND('Towers'!$C$9*POWER('Tuning'!$B$12,D69),0)</f>
+        <f t="array" ref="E69">ROUND('Towers'!$C$9*POWER('Towers'!$S$9,D69),0)</f>
         <v/>
       </c>
       <c r="F69" s="56">
@@ -12465,7 +12478,7 @@
       <c r="AL69" s="57" t="n"/>
       <c r="AM69" s="57" t="n"/>
       <c r="AN69" s="57" t="n">
-        <v>4</v>
+        <v>17.9</v>
       </c>
       <c r="AO69" s="57" t="n">
         <v>5</v>
@@ -12498,7 +12511,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="56">
-        <f t="array" ref="E70">ROUND('Towers'!$C$9*POWER('Tuning'!$B$12,D70),0)</f>
+        <f t="array" ref="E70">ROUND('Towers'!$C$9*POWER('Towers'!$S$9,D70),0)</f>
         <v/>
       </c>
       <c r="F70" s="56">
@@ -12563,7 +12576,7 @@
         <v>1</v>
       </c>
       <c r="AR70" s="57" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="AS70" s="57" t="n"/>
       <c r="AT70" s="57" t="n"/>
@@ -12588,7 +12601,7 @@
         <v>2</v>
       </c>
       <c r="E71" s="56">
-        <f t="array" ref="E71">ROUND('Towers'!$C$9*POWER('Tuning'!$B$12,D71),0)</f>
+        <f t="array" ref="E71">ROUND('Towers'!$C$9*POWER('Towers'!$S$9,D71),0)</f>
         <v/>
       </c>
       <c r="F71" s="56">
@@ -12653,7 +12666,7 @@
         <v>2</v>
       </c>
       <c r="AR71" s="57" t="n">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="AS71" s="57" t="n"/>
       <c r="AT71" s="57" t="n"/>
@@ -12678,7 +12691,7 @@
         <v>3</v>
       </c>
       <c r="E72" s="56">
-        <f t="array" ref="E72">ROUND('Towers'!$C$9*POWER('Tuning'!$B$12,D72),0)</f>
+        <f t="array" ref="E72">ROUND('Towers'!$C$9*POWER('Towers'!$S$9,D72),0)</f>
         <v/>
       </c>
       <c r="F72" s="56">
@@ -12743,7 +12756,7 @@
         <v>2</v>
       </c>
       <c r="AR72" s="57" t="n">
-        <v>120</v>
+        <v>515</v>
       </c>
       <c r="AS72" s="57" t="n"/>
       <c r="AT72" s="57" t="n"/>
@@ -12768,7 +12781,7 @@
         <v>4</v>
       </c>
       <c r="E73" s="56">
-        <f t="array" ref="E73">ROUND('Towers'!$C$9*POWER('Tuning'!$B$12,D73),0)</f>
+        <f t="array" ref="E73">ROUND('Towers'!$C$9*POWER('Towers'!$S$9,D73),0)</f>
         <v/>
       </c>
       <c r="F73" s="56">
@@ -12833,7 +12846,7 @@
         <v>3</v>
       </c>
       <c r="AR73" s="57" t="n">
-        <v>120</v>
+        <v>615</v>
       </c>
       <c r="AS73" s="57" t="n"/>
       <c r="AT73" s="57" t="n"/>
@@ -12858,7 +12871,7 @@
         <v>5</v>
       </c>
       <c r="E74" s="56">
-        <f t="array" ref="E74">ROUND('Towers'!$C$9*POWER('Tuning'!$B$12,D74),0)</f>
+        <f t="array" ref="E74">ROUND('Towers'!$C$9*POWER('Towers'!$S$9,D74),0)</f>
         <v/>
       </c>
       <c r="F74" s="56">
@@ -12923,7 +12936,7 @@
         <v>4</v>
       </c>
       <c r="AR74" s="57" t="n">
-        <v>250</v>
+        <v>790</v>
       </c>
       <c r="AS74" s="57" t="n"/>
       <c r="AT74" s="57" t="n"/>
@@ -12948,7 +12961,7 @@
         <v>1</v>
       </c>
       <c r="E75" s="56">
-        <f t="array" ref="E75">ROUND('Towers'!$C$9*POWER('Tuning'!$B$12,D75),0)</f>
+        <f t="array" ref="E75">ROUND('Towers'!$C$9*POWER('Towers'!$S$9,D75),0)</f>
         <v/>
       </c>
       <c r="F75" s="56">
@@ -13036,7 +13049,7 @@
         <v>2</v>
       </c>
       <c r="E76" s="56">
-        <f t="array" ref="E76">ROUND('Towers'!$C$9*POWER('Tuning'!$B$12,D76),0)</f>
+        <f t="array" ref="E76">ROUND('Towers'!$C$9*POWER('Towers'!$S$9,D76),0)</f>
         <v/>
       </c>
       <c r="F76" s="56">
@@ -13124,7 +13137,7 @@
         <v>3</v>
       </c>
       <c r="E77" s="56">
-        <f t="array" ref="E77">ROUND('Towers'!$C$9*POWER('Tuning'!$B$12,D77),0)</f>
+        <f t="array" ref="E77">ROUND('Towers'!$C$9*POWER('Towers'!$S$9,D77),0)</f>
         <v/>
       </c>
       <c r="F77" s="56">
@@ -13214,7 +13227,7 @@
         <v>4</v>
       </c>
       <c r="E78" s="56">
-        <f t="array" ref="E78">ROUND('Towers'!$C$9*POWER('Tuning'!$B$12,D78),0)</f>
+        <f t="array" ref="E78">ROUND('Towers'!$C$9*POWER('Towers'!$S$9,D78),0)</f>
         <v/>
       </c>
       <c r="F78" s="56">
@@ -13306,7 +13319,7 @@
         <v>5</v>
       </c>
       <c r="E79" s="56">
-        <f t="array" ref="E79">ROUND('Towers'!$C$9*POWER('Tuning'!$B$12,D79),0)</f>
+        <f t="array" ref="E79">ROUND('Towers'!$C$9*POWER('Towers'!$S$9,D79),0)</f>
         <v/>
       </c>
       <c r="F79" s="56">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -6139,7 +6139,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
         <is>
@@ -23779,7 +23778,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="60" t="n">
         <v>0</v>
@@ -23847,7 +23846,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E12" s="60" t="n">
         <v>0</v>
@@ -23915,7 +23914,7 @@
         <v>16</v>
       </c>
       <c r="D13" s="60" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E13" s="60" t="n">
         <v>0</v>
@@ -23924,7 +23923,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="60" t="n">
         <v>0</v>
@@ -23983,16 +23982,16 @@
         <v>17</v>
       </c>
       <c r="D14" s="60" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E14" s="60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="60" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" s="60" t="n">
         <v>0</v>
@@ -24051,10 +24050,10 @@
         <v>16</v>
       </c>
       <c r="D15" s="76" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E15" s="76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F15" s="76" t="n">
         <v>0</v>
@@ -24119,10 +24118,10 @@
         <v>17</v>
       </c>
       <c r="D16" s="60" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F16" s="60" t="n">
         <v>0</v>
@@ -24462,10 +24461,10 @@
         <v>22</v>
       </c>
       <c r="E21" s="60" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F21" s="60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="60" t="n">
         <v>7</v>
@@ -24530,10 +24529,10 @@
         <v>23</v>
       </c>
       <c r="E22" s="60" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F22" s="60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G22" s="60" t="n">
         <v>7</v>
@@ -24598,10 +24597,10 @@
         <v>24</v>
       </c>
       <c r="E23" s="60" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F23" s="60" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G23" s="60" t="n">
         <v>8</v>
@@ -24666,10 +24665,10 @@
         <v>25</v>
       </c>
       <c r="E24" s="60" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F24" s="60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G24" s="60" t="n">
         <v>8</v>
@@ -25414,16 +25413,16 @@
         <v>26</v>
       </c>
       <c r="E35" s="76" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F35" s="76" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G35" s="76" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H35" s="76" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I35" s="76" t="n">
         <v>0</v>
@@ -25482,16 +25481,16 @@
         <v>26</v>
       </c>
       <c r="E36" s="60" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F36" s="60" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G36" s="60" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H36" s="60" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I36" s="60" t="n">
         <v>0</v>
@@ -25550,16 +25549,16 @@
         <v>26</v>
       </c>
       <c r="E37" s="60" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F37" s="60" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G37" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H37" s="60" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I37" s="60" t="n">
         <v>0</v>
@@ -25618,16 +25617,16 @@
         <v>26</v>
       </c>
       <c r="E38" s="60" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F38" s="60" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G38" s="60" t="n">
         <v>18</v>
       </c>
       <c r="H38" s="60" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I38" s="60" t="n">
         <v>0</v>
@@ -25689,13 +25688,13 @@
         <v>31</v>
       </c>
       <c r="F39" s="60" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G39" s="60" t="n">
         <v>18</v>
       </c>
       <c r="H39" s="60" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I39" s="60" t="n">
         <v>0</v>
@@ -25831,7 +25830,7 @@
         <v>18</v>
       </c>
       <c r="H41" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I41" s="60" t="n">
         <v>0</v>
@@ -25899,7 +25898,7 @@
         <v>18</v>
       </c>
       <c r="H42" s="60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I42" s="60" t="n">
         <v>0</v>
@@ -25967,7 +25966,7 @@
         <v>18</v>
       </c>
       <c r="H43" s="60" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I43" s="60" t="n">
         <v>0</v>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -17,6 +17,8 @@
     <sheet name="Rounds" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Difficulty" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Balance Check" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Daily Haul" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Bounties" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -4214,13 +4216,1196 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="90" min="1" max="1"/>
+    <col width="9" customWidth="1" style="90" min="2" max="2"/>
+    <col width="40" customWidth="1" style="90" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>DAILY HAUL — the log-in calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>One claim per UTC day, by hand on the Hunt Board; after the last day it loops. The exporter fails unless every day is below the Easy clear reward and the week is at most two Easy clears (DECISIONS #64, #71).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="47" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="47" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="47" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="47" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" s="47" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" s="47" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="C11" s="47" t="inlineStr">
+        <is>
+          <t>Big Haul</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" style="90" min="1" max="1"/>
+    <col width="9" customWidth="1" style="90" min="2" max="2"/>
+    <col width="9" customWidth="1" style="90" min="3" max="3"/>
+    <col width="12" customWidth="1" style="90" min="4" max="4"/>
+    <col width="10" customWidth="1" style="90" min="5" max="5"/>
+    <col width="9" customWidth="1" style="90" min="6" max="6"/>
+    <col width="9" customWidth="1" style="90" min="7" max="7"/>
+    <col width="18" customWidth="1" style="90" min="8" max="8"/>
+    <col width="36" customWidth="1" style="90" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>BOUNTIES — the daily and weekly pools</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Each day and week the Hunt Board shows one bounty per slot (Tuning, REWARDS). Slot is never shown. Target: a dino key (pop), a difficulty key = that one or harder (clear), or a round (reachRound: reach that round Count times; blank = reach round Count). {n} in Text is Count. Ids are saved in profiles: never rename one. Counts and Amber: DECISIONS #65, #71, #75.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>D_COMPY_SWEEP</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D5" s="43" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="E5" s="43" t="inlineStr">
+        <is>
+          <t>HUSK</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>150</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" s="43" t="inlineStr">
+        <is>
+          <t>Compy Sweep</t>
+        </is>
+      </c>
+      <c r="I5" s="43" t="inlineStr">
+        <is>
+          <t>Pop {n} Compies</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>D_RAPTOR_CULL</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>BRUTE</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" s="43" t="inlineStr">
+        <is>
+          <t>Raptor Cull</t>
+        </is>
+      </c>
+      <c r="I6" s="43" t="inlineStr">
+        <is>
+          <t>Pop {n} Raptors</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>D_BUSY_DAY</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>popTotal</t>
+        </is>
+      </c>
+      <c r="E7" s="43" t="n"/>
+      <c r="F7" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" s="43" t="inlineStr">
+        <is>
+          <t>Busy Day</t>
+        </is>
+      </c>
+      <c r="I7" s="43" t="inlineStr">
+        <is>
+          <t>Pop {n} dinos of any kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>D_GEAR_CHECK</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>ability</t>
+        </is>
+      </c>
+      <c r="E8" s="43" t="n"/>
+      <c r="F8" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" s="43" t="inlineStr">
+        <is>
+          <t>Gear Check</t>
+        </is>
+      </c>
+      <c r="I8" s="43" t="inlineStr">
+        <is>
+          <t>Use your ability {n} times</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>D_PITCH_CAMP</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="n"/>
+      <c r="F9" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" s="43" t="inlineStr">
+        <is>
+          <t>Pitch Camp</t>
+        </is>
+      </c>
+      <c r="I9" s="43" t="inlineStr">
+        <is>
+          <t>Build {n} towers</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>D_HEADBUTT_HUNT</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="E10" s="43" t="inlineStr">
+        <is>
+          <t>SHIELD</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="H10" s="43" t="inlineStr">
+        <is>
+          <t>Headbutt Hunt</t>
+        </is>
+      </c>
+      <c r="I10" s="43" t="inlineStr">
+        <is>
+          <t>Pop {n} Pachycephalosaurs</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>D_SHELL_CRACKER</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>ARMOR</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" s="43" t="inlineStr">
+        <is>
+          <t>Shell Cracker</t>
+        </is>
+      </c>
+      <c r="I11" s="43" t="inlineStr">
+        <is>
+          <t>Pop {n} Ankylosaurs</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>D_CLEAR_SKIES</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>LLAMA</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="H12" s="43" t="inlineStr">
+        <is>
+          <t>Clear Skies</t>
+        </is>
+      </c>
+      <c r="I12" s="43" t="inlineStr">
+        <is>
+          <t>Pop {n} Pteranodons</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>D_DEEP_TRAIL_15</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
+        <is>
+          <t>reachRound</t>
+        </is>
+      </c>
+      <c r="E13" s="43" t="n"/>
+      <c r="F13" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="H13" s="43" t="inlineStr">
+        <is>
+          <t>Deep Trail</t>
+        </is>
+      </c>
+      <c r="I13" s="43" t="inlineStr">
+        <is>
+          <t>Reach round {n}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>D_SHARPEN_UP</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="inlineStr">
+        <is>
+          <t>upgrade</t>
+        </is>
+      </c>
+      <c r="E14" s="43" t="n"/>
+      <c r="F14" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="H14" s="43" t="inlineStr">
+        <is>
+          <t>Sharpen Up</t>
+        </is>
+      </c>
+      <c r="I14" s="43" t="inlineStr">
+        <is>
+          <t>Upgrade towers {n} times</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>D_RUN_THEM_DOWN</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D15" s="43" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="E15" s="43" t="inlineStr">
+        <is>
+          <t>STORM</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" s="43" t="inlineStr">
+        <is>
+          <t>Run Them Down</t>
+        </is>
+      </c>
+      <c r="I15" s="43" t="inlineStr">
+        <is>
+          <t>Pop {n} Gallimimus</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>D_DEEP_TRAIL_25</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="inlineStr">
+        <is>
+          <t>reachRound</t>
+        </is>
+      </c>
+      <c r="E16" s="43" t="n"/>
+      <c r="F16" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" s="43" t="inlineStr">
+        <is>
+          <t>Deep Trail</t>
+        </is>
+      </c>
+      <c r="I16" s="43" t="inlineStr">
+        <is>
+          <t>Reach round {n}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>D_PATCH_JOB</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="E17" s="43" t="n"/>
+      <c r="F17" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" s="43" t="inlineStr">
+        <is>
+          <t>Patch Job</t>
+        </is>
+      </c>
+      <c r="I17" s="43" t="inlineStr">
+        <is>
+          <t>Repair {n} trampled towers</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>D_CLEAN_SWEEP</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D18" s="43" t="inlineStr">
+        <is>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="E18" s="43" t="n"/>
+      <c r="F18" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" s="43" t="inlineStr">
+        <is>
+          <t>Clean Sweep</t>
+        </is>
+      </c>
+      <c r="I18" s="43" t="inlineStr">
+        <is>
+          <t>Clear any track</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>W_STAMPEDE</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="inlineStr">
+        <is>
+          <t>popTotal</t>
+        </is>
+      </c>
+      <c r="E19" s="43" t="n"/>
+      <c r="F19" s="27" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="H19" s="43" t="inlineStr">
+        <is>
+          <t>Stampede</t>
+        </is>
+      </c>
+      <c r="I19" s="43" t="inlineStr">
+        <is>
+          <t>Pop {n} dinos of any kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>W_GEAR_CHECK</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D20" s="43" t="inlineStr">
+        <is>
+          <t>ability</t>
+        </is>
+      </c>
+      <c r="E20" s="43" t="n"/>
+      <c r="F20" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="H20" s="43" t="inlineStr">
+        <is>
+          <t>Gear Check</t>
+        </is>
+      </c>
+      <c r="I20" s="43" t="inlineStr">
+        <is>
+          <t>Use your ability {n} times</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>W_DEEP_TRAIL_2</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D21" s="43" t="inlineStr">
+        <is>
+          <t>reachRound</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="n">
+        <v>31</v>
+      </c>
+      <c r="F21" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="H21" s="43" t="inlineStr">
+        <is>
+          <t>Deep Trail</t>
+        </is>
+      </c>
+      <c r="I21" s="43" t="inlineStr">
+        <is>
+          <t>Reach round 31 {n} times</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>W_CLEAN_SWEEP</t>
+        </is>
+      </c>
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C22" s="43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D22" s="43" t="inlineStr">
+        <is>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="E22" s="43" t="n"/>
+      <c r="F22" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="H22" s="43" t="inlineStr">
+        <is>
+          <t>Clean Sweep</t>
+        </is>
+      </c>
+      <c r="I22" s="43" t="inlineStr">
+        <is>
+          <t>Clear any track {n} times</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>W_ROUGH_COUNTRY</t>
+        </is>
+      </c>
+      <c r="B23" s="43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D23" s="43" t="inlineStr">
+        <is>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="E23" s="43" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="H23" s="43" t="inlineStr">
+        <is>
+          <t>Rough Country</t>
+        </is>
+      </c>
+      <c r="I23" s="43" t="inlineStr">
+        <is>
+          <t>Clear a track on Normal or harder</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>W_HORN_BREAKER</t>
+        </is>
+      </c>
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D24" s="43" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="E24" s="43" t="inlineStr">
+        <is>
+          <t>ZEP</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="H24" s="43" t="inlineStr">
+        <is>
+          <t>Horn Breaker</t>
+        </is>
+      </c>
+      <c r="I24" s="43" t="inlineStr">
+        <is>
+          <t>Pop {n} Triceratops</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>W_PATCH_JOB</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C25" s="43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D25" s="43" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="E25" s="43" t="n"/>
+      <c r="F25" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="G25" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="H25" s="43" t="inlineStr">
+        <is>
+          <t>Patch Job</t>
+        </is>
+      </c>
+      <c r="I25" s="43" t="inlineStr">
+        <is>
+          <t>Repair {n} trampled towers</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>W_BADLANDS</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C26" s="43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D26" s="43" t="inlineStr">
+        <is>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="E26" s="43" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="H26" s="43" t="inlineStr">
+        <is>
+          <t>Badlands</t>
+        </is>
+      </c>
+      <c r="I26" s="43" t="inlineStr">
+        <is>
+          <t>Clear a track on Hard or harder</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>W_TYRANTS_END</t>
+        </is>
+      </c>
+      <c r="B27" s="43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C27" s="43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D27" s="43" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="E27" s="43" t="inlineStr">
+        <is>
+          <t>BARGE</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="H27" s="43" t="inlineStr">
+        <is>
+          <t>Tyrant's End</t>
+        </is>
+      </c>
+      <c r="I27" s="43" t="inlineStr">
+        <is>
+          <t>Pop a T-Rex</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>W_DEEP_TRAIL_4</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C28" s="43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D28" s="43" t="inlineStr">
+        <is>
+          <t>reachRound</t>
+        </is>
+      </c>
+      <c r="E28" s="27" t="n">
+        <v>31</v>
+      </c>
+      <c r="F28" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="H28" s="43" t="inlineStr">
+        <is>
+          <t>Deep Trail</t>
+        </is>
+      </c>
+      <c r="I28" s="43" t="inlineStr">
+        <is>
+          <t>Reach round 31 {n} times</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -5478,6 +6663,158 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>REWARDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="26" t="inlineStr">
+        <is>
+          <t>Daily bounties</t>
+        </is>
+      </c>
+      <c r="B79" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" s="28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D79" s="29" t="inlineStr">
+        <is>
+          <t>Daily bounties on the Hunt Board. Slots fill in the order easy, medium, hard, so 3 = one of each (DECISIONS #65).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="26" t="inlineStr">
+        <is>
+          <t>Weekly bounties</t>
+        </is>
+      </c>
+      <c r="B80" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" s="28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D80" s="29" t="inlineStr">
+        <is>
+          <t>Weekly bounties on the Hunt Board, filled the same way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="26" t="inlineStr">
+        <is>
+          <t>Daily swaps</t>
+        </is>
+      </c>
+      <c r="B81" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D81" s="29" t="inlineStr">
+        <is>
+          <t>Free swaps a day, only on an unfinished bounty; the new one comes from the same slot (DECISIONS #67).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="26" t="inlineStr">
+        <is>
+          <t>Weekly swaps</t>
+        </is>
+      </c>
+      <c r="B82" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D82" s="29" t="inlineStr">
+        <is>
+          <t>Free swaps a week on the weekly bounties.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="26" t="inlineStr">
+        <is>
+          <t>Haul resets after missed days</t>
+        </is>
+      </c>
+      <c r="B83" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="28" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="D83" s="29" t="inlineStr">
+        <is>
+          <t>0 = never: a missed day only pauses the Daily Haul. 1 = miss one day and it starts again at day 1 (DECISIONS #64).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="26" t="inlineStr">
+        <is>
+          <t>Daily reset hour UTC</t>
+        </is>
+      </c>
+      <c r="B84" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="28" t="inlineStr">
+        <is>
+          <t>hour</t>
+        </is>
+      </c>
+      <c r="D84" s="29" t="inlineStr">
+        <is>
+          <t>The hour (0-23, UTC) a new day starts for the Daily Haul and the daily bounties (DECISIONS #68).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="26" t="inlineStr">
+        <is>
+          <t>Weekly reset day</t>
+        </is>
+      </c>
+      <c r="B85" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="28" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="D85" s="29" t="inlineStr">
+        <is>
+          <t>The day the weekly bounties reset, at the daily reset hour: 1 = Monday ... 7 = Sunday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -5405,7 +5405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -6663,7 +6663,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
@@ -6811,10 +6810,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -27303,7 +27298,7 @@
         <v>18</v>
       </c>
       <c r="H43" s="60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I43" s="60" t="n">
         <v>0</v>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -4367,6 +4367,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -5224,7 +5225,7 @@
       </c>
       <c r="I24" s="43" t="inlineStr">
         <is>
-          <t>Pop {n} Triceratops</t>
+          <t>Pop {n} Triceratops (team pops count)</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5350,7 @@
       </c>
       <c r="I27" s="43" t="inlineStr">
         <is>
-          <t>Pop a T-Rex</t>
+          <t>Pop a T-Rex (team pops count)</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -4367,7 +4367,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -4454,7 +4453,7 @@
       </c>
       <c r="I5" s="43" t="inlineStr">
         <is>
-          <t>Pop {n} Compies</t>
+          <t>Take down {n} Compies</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4496,7 @@
       </c>
       <c r="I6" s="43" t="inlineStr">
         <is>
-          <t>Pop {n} Raptors</t>
+          <t>Take down {n} Raptors</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4535,7 @@
       </c>
       <c r="I7" s="43" t="inlineStr">
         <is>
-          <t>Pop {n} dinos of any kind</t>
+          <t>Take down {n} dinos of any kind</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4656,7 @@
       </c>
       <c r="I10" s="43" t="inlineStr">
         <is>
-          <t>Pop {n} Pachycephalosaurs</t>
+          <t>Take down {n} Pachycephalosaurs</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4699,7 @@
       </c>
       <c r="I11" s="43" t="inlineStr">
         <is>
-          <t>Pop {n} Ankylosaurs</t>
+          <t>Take down {n} Ankylosaurs</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4742,7 @@
       </c>
       <c r="I12" s="43" t="inlineStr">
         <is>
-          <t>Pop {n} Pteranodons</t>
+          <t>Take down {n} Pteranodons</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4863,7 @@
       </c>
       <c r="I15" s="43" t="inlineStr">
         <is>
-          <t>Pop {n} Gallimimus</t>
+          <t>Take down {n} Gallimimus</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4897,7 @@
       </c>
       <c r="H16" s="43" t="inlineStr">
         <is>
-          <t>Deep Trail</t>
+          <t>Deeper Trail</t>
         </is>
       </c>
       <c r="I16" s="43" t="inlineStr">
@@ -5020,7 +5019,7 @@
       </c>
       <c r="I19" s="43" t="inlineStr">
         <is>
-          <t>Pop {n} dinos of any kind</t>
+          <t>Take down {n} dinos of any kind</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5094,7 @@
       </c>
       <c r="H21" s="43" t="inlineStr">
         <is>
-          <t>Deep Trail</t>
+          <t>Long Trail</t>
         </is>
       </c>
       <c r="I21" s="43" t="inlineStr">
@@ -5225,7 +5224,7 @@
       </c>
       <c r="I24" s="43" t="inlineStr">
         <is>
-          <t>Pop {n} Triceratops (team pops count)</t>
+          <t>Take down {n} Triceratops (team take-downs count)</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5349,7 @@
       </c>
       <c r="I27" s="43" t="inlineStr">
         <is>
-          <t>Pop a T-Rex (team pops count)</t>
+          <t>Take down a T-Rex (team take-downs count)</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5385,7 @@
       </c>
       <c r="H28" s="43" t="inlineStr">
         <is>
-          <t>Deep Trail</t>
+          <t>Longest Trail</t>
         </is>
       </c>
       <c r="I28" s="43" t="inlineStr">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -19,6 +19,7 @@
     <sheet name="Balance Check" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Daily Haul" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Bounties" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Mastery Perks" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -5399,13 +5400,310 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="90" min="1" max="1"/>
+    <col width="14" customWidth="1" style="90" min="2" max="2"/>
+    <col width="18" customWidth="1" style="90" min="3" max="3"/>
+    <col width="70" customWidth="1" style="90" min="4" max="4"/>
+    <col width="18" customWidth="1" style="90" min="5" max="5"/>
+    <col width="18" customWidth="1" style="90" min="6" max="6"/>
+    <col width="18" customWidth="1" style="90" min="7" max="7"/>
+    <col width="18" customWidth="1" style="90" min="8" max="8"/>
+    <col width="18" customWidth="1" style="90" min="9" max="9"/>
+    <col width="18" customWidth="1" style="90" min="10" max="10"/>
+    <col width="18" customWidth="1" style="90" min="11" max="11"/>
+    <col width="18" customWidth="1" style="90" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>MASTERY PERKS — a level-10 and a level-15 ability perk per hunter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>A hunter with mastery at or above the level has the perk (15 has both). Values are added to the hero's base ability value (Heroes sheet) before path multipliers. Blank = 0. Worth % = 100 x (seconds / base + radius / base + power / base + extra marks x extra mark power) + burn % per s x burn seconds: level 15 must be worth more than level 10, both at most Tuning 'Mastery perk worth cap'. Abilities only: no stun time, no gun damage (DECISIONS #97-#99).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Hero key</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Mastery level</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Ability seconds +</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Ability radius +</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>Ability power +</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>Extra marks</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>Extra mark power x</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>Extra mark reach</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>Strike burn % per s</t>
+        </is>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t>Strike burn (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>PISTOL</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>Lingering Dart</t>
+        </is>
+      </c>
+      <c r="D5" s="43" t="inlineStr">
+        <is>
+          <t>Tracking Dart lasts 2s longer</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>PISTOL</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>Split Dart</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>Tracking Dart also marks the nearest dino within 10 studs at 40% strength</t>
+        </is>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J6" s="27" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>RIFLE</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>Carrying Voice</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>Rally Cry reaches 5 studs further</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>RIFLE</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>Long Rally</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>Rally Cry lasts 3s longer</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>SHOTGUN</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>Wide Flare</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>Flare Strike is 1.5 studs wider</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>SHOTGUN</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>Smoulder</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
+          <t>Flare Strike leaves burning ground for 3s (12% of the strike each second)</t>
+        </is>
+      </c>
+      <c r="K10" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="L10" s="27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>MEDIC</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>Long Reach</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>Triage Kit reaches 4 studs further</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>MEDIC</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>Full Kit</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>Triage Kit heals 10 more HP</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -6810,6 +7108,143 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
+    <row r="87">
+      <c r="A87" s="31" t="inlineStr">
+        <is>
+          <t>HERO XP</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="26" t="inlineStr">
+        <is>
+          <t>XP per level</t>
+        </is>
+      </c>
+      <c r="B88" s="27" t="n">
+        <v>500</v>
+      </c>
+      <c r="C88" s="28" t="inlineStr">
+        <is>
+          <t>XP</t>
+        </is>
+      </c>
+      <c r="D88" s="29" t="inlineStr">
+        <is>
+          <t>XP for one hero level: level = 1 + XP / this, rounded down. Must be a whole multiple of Rounds per level, so a cleared round is worth a whole Round XP (DECISIONS #100).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="26" t="inlineStr">
+        <is>
+          <t>XP per pop</t>
+        </is>
+      </c>
+      <c r="B89" s="27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C89" s="28" t="inlineStr">
+        <is>
+          <t>XP</t>
+        </is>
+      </c>
+      <c r="D89" s="29" t="inlineStr">
+        <is>
+          <t>Pop XP for each take-down credited to the hunter (gun, towers, fire). Pending until the round is cleared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="26" t="inlineStr">
+        <is>
+          <t>Pop XP cap per round</t>
+        </is>
+      </c>
+      <c r="B90" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="C90" s="28" t="inlineStr">
+        <is>
+          <t>XP</t>
+        </is>
+      </c>
+      <c r="D90" s="29" t="inlineStr">
+        <is>
+          <t>The most pop XP one round can bank. 0 = the old every-5-rounds curve exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="26" t="inlineStr">
+        <is>
+          <t>Team pop share</t>
+        </is>
+      </c>
+      <c r="B91" s="27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C91" s="28" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D91" s="29" t="inlineStr">
+        <is>
+          <t>Share of teammates' take-downs that counts toward your pop XP (DECISIONS #102). 0 = own only, 1 = fully shared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="26" t="inlineStr">
+        <is>
+          <t>Hero level lead cap</t>
+        </is>
+      </c>
+      <c r="B92" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" s="28" t="inlineStr">
+        <is>
+          <t>levels</t>
+        </is>
+      </c>
+      <c r="D92" s="29" t="inlineStr">
+        <is>
+          <t>A hunter is never more than this many levels above the round level (DECISIONS #101). The export fails if the seeds alone would beat it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" s="31" t="inlineStr">
+        <is>
+          <t>MASTERY PERKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="26" t="inlineStr">
+        <is>
+          <t>Mastery perk worth cap</t>
+        </is>
+      </c>
+      <c r="B95" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="C95" s="28" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D95" s="29" t="inlineStr">
+        <is>
+          <t>The most a mastery perk may be worth, in % of one cast (Mastery Perks sheet, DECISIONS #99). Read by the exporter only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -22700,7 +23135,7 @@
     <row r="2" ht="13.65" customHeight="1" s="90">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Bought with Amber. Head starts and unlocks only — never damage multipliers.</t>
+          <t>Bought with Amber. Head starts and unlocks only — never gun damage multipliers.</t>
         </is>
       </c>
       <c r="B2" s="6" t="n"/>
@@ -23088,7 +23523,7 @@
       </c>
       <c r="E14" s="68" t="inlineStr">
         <is>
-          <t>Start every match with your first upgrade free (a second ability variant: coming later)</t>
+          <t>Start every match with your first upgrade free, plus your hunter's level-10 ability perk</t>
         </is>
       </c>
       <c r="F14" s="66" t="n">
@@ -23252,7 +23687,7 @@
       </c>
       <c r="E19" s="68" t="inlineStr">
         <is>
-          <t>Ability cooldown -30% (a secondary ability effect: coming later)</t>
+          <t>Ability cooldown -30%, plus your hunter's level-15 ability perk</t>
         </is>
       </c>
       <c r="F19" s="66" t="n">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -5680,7 +5680,7 @@
       </c>
       <c r="C12" s="43" t="inlineStr">
         <is>
-          <t>Full Kit</t>
+          <t>Stocked Kit</t>
         </is>
       </c>
       <c r="D12" s="43" t="inlineStr">
@@ -5703,7 +5703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -7108,7 +7108,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" s="31" t="inlineStr">
         <is>
@@ -7216,7 +7215,6 @@
         </is>
       </c>
     </row>
-    <row r="93"/>
     <row r="94">
       <c r="A94" s="31" t="inlineStr">
         <is>
@@ -7244,7 +7242,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -5510,7 +5510,7 @@
       </c>
       <c r="C5" s="43" t="inlineStr">
         <is>
-          <t>Lingering Dart</t>
+          <t>Sticky Dart</t>
         </is>
       </c>
       <c r="D5" s="43" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="C6" s="43" t="inlineStr">
         <is>
-          <t>Split Dart</t>
+          <t>Spare Dart</t>
         </is>
       </c>
       <c r="D6" s="43" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C7" s="43" t="inlineStr">
         <is>
-          <t>Carrying Voice</t>
+          <t>Hunting Horn</t>
         </is>
       </c>
       <c r="D7" s="43" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="D9" s="43" t="inlineStr">
         <is>
-          <t>Flare Strike is 1.5 studs wider</t>
+          <t>Flare Strike reaches 1.5 studs further</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="D10" s="43" t="inlineStr">
         <is>
-          <t>Flare Strike leaves burning ground for 3s (12% of the strike each second)</t>
+          <t>Flare Strike leaves burning ground for 3s (12% of the strike's damage each second)</t>
         </is>
       </c>
       <c r="K10" s="27" t="n">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="C11" s="43" t="inlineStr">
         <is>
-          <t>Long Reach</t>
+          <t>Far Reach</t>
         </is>
       </c>
       <c r="D11" s="43" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="E14" s="68" t="inlineStr">
         <is>
-          <t>Start every match with your first upgrade free, plus your hunter's level-10 ability perk</t>
+          <t>Start every match with your first upgrade free, plus this hero's mastery-10 ability perk</t>
         </is>
       </c>
       <c r="F14" s="66" t="n">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="E19" s="68" t="inlineStr">
         <is>
-          <t>Ability cooldown -30%, plus your hunter's level-15 ability perk</t>
+          <t>Ability cooldown -30%, plus this hero's mastery-15 ability perk</t>
         </is>
       </c>
       <c r="F19" s="66" t="n">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -10487,7 +10487,7 @@
       </c>
       <c r="M28" s="43" t="inlineStr">
         <is>
-          <t>Tactical Spotter</t>
+          <t>Game Spotter</t>
         </is>
       </c>
       <c r="N28" s="57" t="n"/>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="B30" s="43" t="inlineStr">
         <is>
-          <t>Siege</t>
+          <t>Big Bore</t>
         </is>
       </c>
       <c r="C30" s="43" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B31" s="43" t="inlineStr">
         <is>
-          <t>Siege</t>
+          <t>Big Bore</t>
         </is>
       </c>
       <c r="C31" s="43" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="M31" s="43" t="inlineStr">
         <is>
-          <t>Anti-Materiel</t>
+          <t>Bone Breaker</t>
         </is>
       </c>
       <c r="N31" s="57" t="n"/>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="B32" s="43" t="inlineStr">
         <is>
-          <t>Siege</t>
+          <t>Big Bore</t>
         </is>
       </c>
       <c r="C32" s="43" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B33" s="43" t="inlineStr">
         <is>
-          <t>Siege</t>
+          <t>Big Bore</t>
         </is>
       </c>
       <c r="C33" s="43" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="M33" s="43" t="inlineStr">
         <is>
-          <t>Siege Gun</t>
+          <t>Punt Gun</t>
         </is>
       </c>
       <c r="N33" s="57" t="n"/>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="B34" s="43" t="inlineStr">
         <is>
-          <t>Siege</t>
+          <t>Big Bore</t>
         </is>
       </c>
       <c r="C34" s="43" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="M54" s="43" t="inlineStr">
         <is>
-          <t>Hibernation</t>
+          <t>Deep Sleep</t>
         </is>
       </c>
       <c r="N54" s="57" t="n"/>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="M72" s="43" t="inlineStr">
         <is>
-          <t>Care Package</t>
+          <t>Chopper Drop</t>
         </is>
       </c>
       <c r="N72" s="57" t="n"/>
@@ -15019,7 +15019,7 @@
       </c>
       <c r="M78" s="43" t="inlineStr">
         <is>
-          <t>Forward Base</t>
+          <t>Forward Camp</t>
         </is>
       </c>
       <c r="N78" s="57" t="n"/>
@@ -15111,7 +15111,7 @@
       </c>
       <c r="M79" s="43" t="inlineStr">
         <is>
-          <t>Command Center</t>
+          <t>Base Camp</t>
         </is>
       </c>
       <c r="N79" s="57" t="n"/>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="C7" s="43" t="inlineStr">
         <is>
-          <t>Ordnance</t>
+          <t>Close range</t>
         </is>
       </c>
       <c r="D7" s="43" t="inlineStr">
@@ -20057,7 +20057,7 @@
       </c>
       <c r="B20" s="43" t="inlineStr">
         <is>
-          <t>Tactical</t>
+          <t>Stalker</t>
         </is>
       </c>
       <c r="C20" s="43" t="inlineStr">
@@ -20117,7 +20117,7 @@
       </c>
       <c r="B21" s="43" t="inlineStr">
         <is>
-          <t>Tactical</t>
+          <t>Stalker</t>
         </is>
       </c>
       <c r="C21" s="43" t="inlineStr">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="B22" s="43" t="inlineStr">
         <is>
-          <t>Tactical</t>
+          <t>Stalker</t>
         </is>
       </c>
       <c r="C22" s="43" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="B23" s="43" t="inlineStr">
         <is>
-          <t>Tactical</t>
+          <t>Stalker</t>
         </is>
       </c>
       <c r="C23" s="43" t="inlineStr">
@@ -20321,7 +20321,7 @@
       </c>
       <c r="B24" s="43" t="inlineStr">
         <is>
-          <t>Tactical</t>
+          <t>Stalker</t>
         </is>
       </c>
       <c r="C24" s="43" t="inlineStr">
@@ -21706,7 +21706,7 @@
       </c>
       <c r="E44" s="43" t="inlineStr">
         <is>
-          <t>Street Sweeper</t>
+          <t>Thicket Sweeper</t>
         </is>
       </c>
       <c r="F44" s="56">
@@ -21773,7 +21773,7 @@
       </c>
       <c r="B45" s="43" t="inlineStr">
         <is>
-          <t>Breacher</t>
+          <t>Point Blank</t>
         </is>
       </c>
       <c r="C45" s="43" t="inlineStr">
@@ -21833,7 +21833,7 @@
       </c>
       <c r="B46" s="43" t="inlineStr">
         <is>
-          <t>Breacher</t>
+          <t>Point Blank</t>
         </is>
       </c>
       <c r="C46" s="43" t="inlineStr">
@@ -21895,7 +21895,7 @@
       </c>
       <c r="B47" s="43" t="inlineStr">
         <is>
-          <t>Breacher</t>
+          <t>Point Blank</t>
         </is>
       </c>
       <c r="C47" s="43" t="inlineStr">
@@ -21959,7 +21959,7 @@
       </c>
       <c r="B48" s="43" t="inlineStr">
         <is>
-          <t>Breacher</t>
+          <t>Point Blank</t>
         </is>
       </c>
       <c r="C48" s="43" t="inlineStr">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="B49" s="43" t="inlineStr">
         <is>
-          <t>Breacher</t>
+          <t>Point Blank</t>
         </is>
       </c>
       <c r="C49" s="43" t="inlineStr">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -10114,7 +10114,7 @@
         <v/>
       </c>
       <c r="G24" s="57" t="n">
-        <v>6.41</v>
+        <v>8.84</v>
       </c>
       <c r="H24" s="57" t="n">
         <v>1</v>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -2218,7 +2218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="90" min="1" max="1"/>
@@ -2296,6 +2296,11 @@
           <t>Dino damage x</t>
         </is>
       </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>Starting cash</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="43" t="inlineStr">
@@ -2332,6 +2337,9 @@
       <c r="J5" s="27" t="n">
         <v>1</v>
       </c>
+      <c r="K5" s="27" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
@@ -2367,6 +2375,9 @@
       </c>
       <c r="J6" s="27" t="n">
         <v>1.25</v>
+      </c>
+      <c r="K6" s="27" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="7">
@@ -2400,6 +2411,9 @@
       <c r="J7" s="27" t="n">
         <v>1.6</v>
       </c>
+      <c r="K7" s="27" t="n">
+        <v>650</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
@@ -2435,6 +2449,9 @@
       </c>
       <c r="J8" s="27" t="n">
         <v>2.2</v>
+      </c>
+      <c r="K8" s="27" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="11">
@@ -5792,7 +5809,7 @@
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
-          <t>What players have before round 1.</t>
+          <t>Default: what players have before round 1 on Easy. Each level's own is Difficulty → Starting cash; the exporter checks Easy equals this.</t>
         </is>
       </c>
       <c r="E6" s="7" t="n"/>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -2412,7 +2412,7 @@
         <v>1.6</v>
       </c>
       <c r="K7" s="27" t="n">
-        <v>650</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -5720,7 +5720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -7232,14 +7232,14 @@
         </is>
       </c>
     </row>
-    <row r="94">
+    <row r="94" s="90">
       <c r="A94" s="31" t="inlineStr">
         <is>
           <t>MASTERY PERKS</t>
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" s="90">
       <c r="A95" s="26" t="inlineStr">
         <is>
           <t>Mastery perk worth cap</t>
@@ -7256,6 +7256,33 @@
       <c r="D95" s="29" t="inlineStr">
         <is>
           <t>The most a mastery perk may be worth, in % of one cast (Mastery Perks sheet, DECISIONS #99). Read by the exporter only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="31" t="inlineStr">
+        <is>
+          <t>BOSS THROWS</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="26" t="inlineStr">
+        <is>
+          <t>Boss ranged vs towers x</t>
+        </is>
+      </c>
+      <c r="B98" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C98" s="28" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D98" s="29" t="inlineStr">
+        <is>
+          <t>A Boss species' projectile damage to a tower is multiplied by this; hunters take full damage (they can dodge). DECISIONS #138, #154. 1 = off.</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -464,7 +464,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -758,6 +758,28 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -5720,7 +5742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -7283,6 +7305,54 @@
       <c r="D98" s="29" t="inlineStr">
         <is>
           <t>A Boss species' projectile damage to a tower is multiplied by this; hunters take full damage (they can dodge). DECISIONS #138, #154. 1 = off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99"/>
+    <row r="100">
+      <c r="A100" s="99" t="inlineStr">
+        <is>
+          <t>PIERCE-THROUGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="100" t="inlineStr">
+        <is>
+          <t>Break level step</t>
+        </is>
+      </c>
+      <c r="B101" s="101" t="n">
+        <v>3</v>
+      </c>
+      <c r="C101" s="102" t="inlineStr">
+        <is>
+          <t>levels</t>
+        </is>
+      </c>
+      <c r="D101" s="103" t="inlineStr">
+        <is>
+          <t>Raw-damage tiers (Size breaks 2+) break one more size per this many tower levels above 1: +1 at level 4, +2 at level 7. Heroes never. DECISIONS #126.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="100" t="inlineStr">
+        <is>
+          <t>Max size breaks</t>
+        </is>
+      </c>
+      <c r="B102" s="101" t="n">
+        <v>4</v>
+      </c>
+      <c r="C102" s="102" t="inlineStr">
+        <is>
+          <t>sizes</t>
+        </is>
+      </c>
+      <c r="D102" s="103" t="inlineStr">
+        <is>
+          <t>The most sizes one hit may drop (pierce-through cap). 1 = off everywhere. DECISIONS #126.</t>
         </is>
       </c>
     </row>
@@ -7984,7 +8054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI109"/>
+  <dimension ref="A1:BJ109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -8429,6 +8499,11 @@
           <t>Last stand</t>
         </is>
       </c>
+      <c r="BJ4" s="104" t="inlineStr">
+        <is>
+          <t>Size breaks</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -9669,6 +9744,9 @@
       <c r="AR18" s="57" t="n"/>
       <c r="AS18" s="57" t="n"/>
       <c r="AT18" s="57" t="n"/>
+      <c r="BJ18" s="105" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19" ht="13.65" customHeight="1" s="90">
       <c r="A19" s="43" t="inlineStr">
@@ -9765,6 +9843,9 @@
       <c r="AR19" s="57" t="n"/>
       <c r="AS19" s="57" t="n"/>
       <c r="AT19" s="57" t="n"/>
+      <c r="BJ19" s="105" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20" ht="13.65" customHeight="1" s="90">
       <c r="A20" s="43" t="inlineStr">
@@ -10129,6 +10210,9 @@
       <c r="AR23" s="57" t="n"/>
       <c r="AS23" s="57" t="n"/>
       <c r="AT23" s="57" t="n"/>
+      <c r="BJ23" s="105" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24" ht="13.65" customHeight="1" s="90">
       <c r="A24" s="43" t="inlineStr">
@@ -10221,6 +10305,9 @@
       <c r="AR24" s="57" t="n"/>
       <c r="AS24" s="57" t="n"/>
       <c r="AT24" s="57" t="n"/>
+      <c r="BJ24" s="105" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="25" ht="13.65" customHeight="1" s="90">
       <c r="A25" s="43" t="inlineStr">
@@ -10833,6 +10920,9 @@
       <c r="AR31" s="57" t="n"/>
       <c r="AS31" s="57" t="n"/>
       <c r="AT31" s="57" t="n"/>
+      <c r="BJ31" s="105" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32" ht="13.65" customHeight="1" s="90">
       <c r="A32" s="43" t="inlineStr">
@@ -10923,6 +11013,9 @@
       <c r="AR32" s="57" t="n"/>
       <c r="AS32" s="57" t="n"/>
       <c r="AT32" s="57" t="n"/>
+      <c r="BJ32" s="105" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="33" ht="13.65" customHeight="1" s="90">
       <c r="A33" s="43" t="inlineStr">
@@ -11013,6 +11106,9 @@
       <c r="AR33" s="57" t="n"/>
       <c r="AS33" s="57" t="n"/>
       <c r="AT33" s="57" t="n"/>
+      <c r="BJ33" s="105" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="34" ht="13.65" customHeight="1" s="90">
       <c r="A34" s="43" t="inlineStr">
@@ -11107,6 +11203,9 @@
       <c r="AR34" s="57" t="n"/>
       <c r="AS34" s="57" t="n"/>
       <c r="AT34" s="57" t="n"/>
+      <c r="BJ34" s="105" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35" ht="13.65" customHeight="1" s="90">
       <c r="A35" s="43" t="inlineStr">
@@ -18843,7 +18942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR64"/>
+  <dimension ref="A1:AS64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="90" min="1" max="1"/>
@@ -18895,6 +18994,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -19114,6 +19214,11 @@
       <c r="AR4" s="21" t="inlineStr">
         <is>
           <t>Jaw lock spread (studs)</t>
+        </is>
+      </c>
+      <c r="AS4" s="104" t="inlineStr">
+        <is>
+          <t>Size breaks</t>
         </is>
       </c>
     </row>
@@ -23948,7 +24053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="81" min="1" max="1"/>
@@ -24150,6 +24255,11 @@
           <t>Impact radius (studs)</t>
         </is>
       </c>
+      <c r="Y4" s="104" t="inlineStr">
+        <is>
+          <t>Break resist</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="65" t="inlineStr">
@@ -24241,6 +24351,9 @@
       <c r="X5" s="60" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" s="106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="13.65" customHeight="1" s="90">
       <c r="A6" s="65" t="inlineStr">
@@ -24328,6 +24441,9 @@
       <c r="X6" s="60" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" s="106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="13.65" customHeight="1" s="90">
       <c r="A7" s="65" t="inlineStr">
@@ -24423,6 +24539,9 @@
       <c r="X7" s="60" t="n">
         <v>3</v>
       </c>
+      <c r="Y7" s="106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="13.65" customHeight="1" s="90">
       <c r="A8" s="65" t="inlineStr">
@@ -24518,6 +24637,9 @@
       <c r="X8" s="60" t="n">
         <v>3</v>
       </c>
+      <c r="Y8" s="106" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
       <c r="A9" s="65" t="inlineStr">
@@ -24612,6 +24734,9 @@
       </c>
       <c r="X9" s="60" t="n">
         <v>3</v>
+      </c>
+      <c r="Y9" s="106" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="13.65" customHeight="1" s="90">
@@ -24704,6 +24829,9 @@
       <c r="X10" s="60" t="n">
         <v>4</v>
       </c>
+      <c r="Y10" s="106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" ht="13.65" customHeight="1" s="90">
       <c r="A11" s="65" t="inlineStr">
@@ -24799,6 +24927,9 @@
       <c r="X11" s="60" t="n">
         <v>5</v>
       </c>
+      <c r="Y11" s="106" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" ht="13.65" customHeight="1" s="90">
       <c r="A12" s="65" t="inlineStr">
@@ -24893,6 +25024,9 @@
       </c>
       <c r="X12" s="60" t="n">
         <v>8</v>
+      </c>
+      <c r="Y12" s="106" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13" ht="13.55" customHeight="1" s="90">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -7308,7 +7308,6 @@
         </is>
       </c>
     </row>
-    <row r="99"/>
     <row r="100">
       <c r="A100" s="99" t="inlineStr">
         <is>
@@ -18994,7 +18993,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -23253,7 +23251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="81" min="1" max="1"/>
@@ -23265,6 +23263,10 @@
     <col width="14" customWidth="1" style="90" min="7" max="7"/>
     <col width="14" customWidth="1" style="90" min="8" max="8"/>
     <col width="14" customWidth="1" style="90" min="9" max="9"/>
+    <col width="14" customWidth="1" style="90" min="10" max="10"/>
+    <col width="14" customWidth="1" style="90" min="11" max="11"/>
+    <col width="14" customWidth="1" style="90" min="12" max="12"/>
+    <col width="14" customWidth="1" style="90" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.5" customHeight="1" s="90">
@@ -23342,6 +23344,26 @@
           <t>Crossover cap</t>
         </is>
       </c>
+      <c r="J4" s="104" t="inlineStr">
+        <is>
+          <t>Pick-up reach +</t>
+        </is>
+      </c>
+      <c r="K4" s="104" t="inlineStr">
+        <is>
+          <t>Heal per round +</t>
+        </is>
+      </c>
+      <c r="L4" s="104" t="inlineStr">
+        <is>
+          <t>Respawn x</t>
+        </is>
+      </c>
+      <c r="M4" s="104" t="inlineStr">
+        <is>
+          <t>Repair cost x</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="56" t="n">
@@ -23377,6 +23399,12 @@
       </c>
       <c r="I5" s="56" t="n">
         <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="13.65" customHeight="1" s="90">
@@ -23414,6 +23442,12 @@
       <c r="I6" s="56" t="n">
         <v>2</v>
       </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" ht="13.65" customHeight="1" s="90">
       <c r="A7" s="56" t="n">
@@ -23450,6 +23484,12 @@
       <c r="I7" s="56" t="n">
         <v>2</v>
       </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" ht="13.65" customHeight="1" s="90">
       <c r="A8" s="56" t="n">
@@ -23486,6 +23526,12 @@
       <c r="I8" s="56" t="n">
         <v>2</v>
       </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
       <c r="A9" s="66" t="n">
@@ -23522,6 +23568,12 @@
       <c r="I9" s="66" t="n">
         <v>2</v>
       </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" ht="13.65" customHeight="1" s="90">
       <c r="A10" s="56" t="n">
@@ -23539,7 +23591,11 @@
         <f>ROUND(C10/Tuning!$B$26,1)</f>
         <v/>
       </c>
-      <c r="E10" s="69" t="n"/>
+      <c r="E10" s="69" t="inlineStr">
+        <is>
+          <t>Long Arms I: pick up chests and med kits from 2 studs away</t>
+        </is>
+      </c>
       <c r="F10" s="56" t="n">
         <v>20</v>
       </c>
@@ -23553,6 +23609,15 @@
       </c>
       <c r="I10" s="56" t="n">
         <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="13.65" customHeight="1" s="90">
@@ -23571,7 +23636,11 @@
         <f>ROUND(C11/Tuning!$B$26,1)</f>
         <v/>
       </c>
-      <c r="E11" s="69" t="n"/>
+      <c r="E11" s="69" t="inlineStr">
+        <is>
+          <t>Field Dressing I: heal 5 more HP when a round is cleared</t>
+        </is>
+      </c>
       <c r="F11" s="56" t="n">
         <v>20</v>
       </c>
@@ -23585,6 +23654,18 @@
       </c>
       <c r="I11" s="56" t="n">
         <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="13.65" customHeight="1" s="90">
@@ -23603,7 +23684,11 @@
         <f>ROUND(C12/Tuning!$B$26,1)</f>
         <v/>
       </c>
-      <c r="E12" s="69" t="n"/>
+      <c r="E12" s="69" t="inlineStr">
+        <is>
+          <t>Quick Recovery I: respawn 10% sooner</t>
+        </is>
+      </c>
       <c r="F12" s="56" t="n">
         <v>20</v>
       </c>
@@ -23617,6 +23702,18 @@
       </c>
       <c r="I12" s="56" t="n">
         <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13" ht="13.65" customHeight="1" s="90">
@@ -23635,7 +23732,11 @@
         <f>ROUND(C13/Tuning!$B$26,1)</f>
         <v/>
       </c>
-      <c r="E13" s="69" t="n"/>
+      <c r="E13" s="69" t="inlineStr">
+        <is>
+          <t>Handyman I: repairs cost 5% less</t>
+        </is>
+      </c>
       <c r="F13" s="56" t="n">
         <v>20</v>
       </c>
@@ -23649,6 +23750,18 @@
       </c>
       <c r="I13" s="56" t="n">
         <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="14" ht="13.65" customHeight="1" s="90">
@@ -23686,6 +23799,18 @@
       <c r="I14" s="66" t="n">
         <v>2</v>
       </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="15" ht="13.65" customHeight="1" s="90">
       <c r="A15" s="56" t="n">
@@ -23703,7 +23828,11 @@
         <f>ROUND(C15/Tuning!$B$26,1)</f>
         <v/>
       </c>
-      <c r="E15" s="69" t="n"/>
+      <c r="E15" s="69" t="inlineStr">
+        <is>
+          <t>Long Arms II: pick up chests and med kits from 4 studs away</t>
+        </is>
+      </c>
       <c r="F15" s="56" t="n">
         <v>20</v>
       </c>
@@ -23717,6 +23846,18 @@
       </c>
       <c r="I15" s="56" t="n">
         <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="16" ht="13.65" customHeight="1" s="90">
@@ -23735,7 +23876,11 @@
         <f>ROUND(C16/Tuning!$B$26,1)</f>
         <v/>
       </c>
-      <c r="E16" s="69" t="n"/>
+      <c r="E16" s="69" t="inlineStr">
+        <is>
+          <t>Field Dressing II: heal 10 more HP when a round is cleared</t>
+        </is>
+      </c>
       <c r="F16" s="56" t="n">
         <v>20</v>
       </c>
@@ -23749,6 +23894,18 @@
       </c>
       <c r="I16" s="56" t="n">
         <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="17" ht="13.65" customHeight="1" s="90">
@@ -23767,7 +23924,11 @@
         <f>ROUND(C17/Tuning!$B$26,1)</f>
         <v/>
       </c>
-      <c r="E17" s="69" t="n"/>
+      <c r="E17" s="69" t="inlineStr">
+        <is>
+          <t>Quick Recovery II: respawn 20% sooner</t>
+        </is>
+      </c>
       <c r="F17" s="56" t="n">
         <v>20</v>
       </c>
@@ -23781,6 +23942,18 @@
       </c>
       <c r="I17" s="56" t="n">
         <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="18" ht="13.65" customHeight="1" s="90">
@@ -23799,7 +23972,11 @@
         <f>ROUND(C18/Tuning!$B$26,1)</f>
         <v/>
       </c>
-      <c r="E18" s="69" t="n"/>
+      <c r="E18" s="69" t="inlineStr">
+        <is>
+          <t>Handyman II: repairs cost 10% less</t>
+        </is>
+      </c>
       <c r="F18" s="56" t="n">
         <v>20</v>
       </c>
@@ -23813,6 +23990,18 @@
       </c>
       <c r="I18" s="56" t="n">
         <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="19" ht="13.65" customHeight="1" s="90">
@@ -23850,6 +24039,18 @@
       <c r="I19" s="66" t="n">
         <v>2</v>
       </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="20" ht="13.65" customHeight="1" s="90">
       <c r="A20" s="56" t="n">
@@ -23867,7 +24068,11 @@
         <f>ROUND(C20/Tuning!$B$26,1)</f>
         <v/>
       </c>
-      <c r="E20" s="69" t="n"/>
+      <c r="E20" s="69" t="inlineStr">
+        <is>
+          <t>Long Arms III: pick up chests and med kits from 6 studs away</t>
+        </is>
+      </c>
       <c r="F20" s="56" t="n">
         <v>20</v>
       </c>
@@ -23881,6 +24086,18 @@
       </c>
       <c r="I20" s="56" t="n">
         <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="21" ht="13.65" customHeight="1" s="90">
@@ -23899,7 +24116,11 @@
         <f>ROUND(C21/Tuning!$B$26,1)</f>
         <v/>
       </c>
-      <c r="E21" s="69" t="n"/>
+      <c r="E21" s="69" t="inlineStr">
+        <is>
+          <t>Field Dressing III: heal 15 more HP when a round is cleared</t>
+        </is>
+      </c>
       <c r="F21" s="56" t="n">
         <v>20</v>
       </c>
@@ -23913,6 +24134,18 @@
       </c>
       <c r="I21" s="56" t="n">
         <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>15</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="22" ht="13.65" customHeight="1" s="90">
@@ -23931,7 +24164,11 @@
         <f>ROUND(C22/Tuning!$B$26,1)</f>
         <v/>
       </c>
-      <c r="E22" s="69" t="n"/>
+      <c r="E22" s="69" t="inlineStr">
+        <is>
+          <t>Quick Recovery III: respawn 30% sooner</t>
+        </is>
+      </c>
       <c r="F22" s="56" t="n">
         <v>20</v>
       </c>
@@ -23945,6 +24182,18 @@
       </c>
       <c r="I22" s="56" t="n">
         <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>15</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="23" ht="13.65" customHeight="1" s="90">
@@ -23963,7 +24212,11 @@
         <f>ROUND(C23/Tuning!$B$26,1)</f>
         <v/>
       </c>
-      <c r="E23" s="69" t="n"/>
+      <c r="E23" s="69" t="inlineStr">
+        <is>
+          <t>Handyman III: repairs cost 15% less</t>
+        </is>
+      </c>
       <c r="F23" s="56" t="n">
         <v>20</v>
       </c>
@@ -23977,6 +24230,18 @@
       </c>
       <c r="I23" s="56" t="n">
         <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>15</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="24" ht="13.65" customHeight="1" s="90">
@@ -24013,6 +24278,18 @@
       </c>
       <c r="I24" s="66" t="n">
         <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>15</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="25" ht="13.55" customHeight="1" s="90">
@@ -24033,6 +24310,10 @@
       <c r="D26" s="16" t="n"/>
       <c r="E26" s="17" t="n"/>
     </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -2240,7 +2240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="90" min="1" max="1"/>
@@ -2323,6 +2323,16 @@
           <t>Starting cash</t>
         </is>
       </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t>Tower damage x</t>
+        </is>
+      </c>
+      <c r="M4" s="21" t="inlineStr">
+        <is>
+          <t>Hero damage x</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="43" t="inlineStr">
@@ -2362,6 +2372,12 @@
       <c r="K5" s="27" t="n">
         <v>450</v>
       </c>
+      <c r="L5" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
@@ -2400,6 +2416,12 @@
       </c>
       <c r="K6" s="27" t="n">
         <v>450</v>
+      </c>
+      <c r="L6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2436,6 +2458,12 @@
       <c r="K7" s="27" t="n">
         <v>850</v>
       </c>
+      <c r="L7" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
@@ -2474,6 +2502,12 @@
       </c>
       <c r="K8" s="27" t="n">
         <v>450</v>
+      </c>
+      <c r="L8" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
@@ -23251,7 +23285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="81" min="1" max="1"/>
@@ -23400,10 +23434,10 @@
       <c r="I5" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="L5" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23442,10 +23476,10 @@
       <c r="I6" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="L6" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23484,10 +23518,10 @@
       <c r="I7" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="L7" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23526,10 +23560,10 @@
       <c r="I8" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="L8" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23568,10 +23602,10 @@
       <c r="I9" s="66" t="n">
         <v>2</v>
       </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="L9" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23610,13 +23644,13 @@
       <c r="I10" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="L10" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23655,16 +23689,16 @@
       <c r="I11" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="L11" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23703,16 +23737,16 @@
       <c r="I12" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="81" t="n">
         <v>0.9</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23751,16 +23785,16 @@
       <c r="I13" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="81" t="n">
         <v>0.9</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="81" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -23799,16 +23833,16 @@
       <c r="I14" s="66" t="n">
         <v>2</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="81" t="n">
         <v>0.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="81" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -23847,16 +23881,16 @@
       <c r="I15" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="81" t="n">
         <v>0.9</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="81" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -23895,16 +23929,16 @@
       <c r="I16" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="81" t="n">
         <v>0.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="81" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -23943,16 +23977,16 @@
       <c r="I17" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="81" t="n">
         <v>0.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="81" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -23991,16 +24025,16 @@
       <c r="I18" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="81" t="n">
         <v>0.8</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="81" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -24039,16 +24073,16 @@
       <c r="I19" s="66" t="n">
         <v>2</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="81" t="n">
         <v>0.8</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="81" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -24087,16 +24121,16 @@
       <c r="I20" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="81" t="n">
         <v>0.8</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="81" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -24135,16 +24169,16 @@
       <c r="I21" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="81" t="n">
         <v>0.8</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="81" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -24183,16 +24217,16 @@
       <c r="I22" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="81" t="n">
         <v>0.7</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="81" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -24231,16 +24265,16 @@
       <c r="I23" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="81" t="n">
         <v>0.7</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" s="81" t="n">
         <v>0.85</v>
       </c>
     </row>
@@ -24279,16 +24313,16 @@
       <c r="I24" s="66" t="n">
         <v>3</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="81" t="n">
         <v>0.7</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24" s="81" t="n">
         <v>0.85</v>
       </c>
     </row>
@@ -24310,10 +24344,6 @@
       <c r="D26" s="16" t="n"/>
       <c r="E26" s="17" t="n"/>
     </row>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -18975,7 +18975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS64"/>
+  <dimension ref="A1:BA79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="90" min="1" max="1"/>
@@ -19016,7 +19016,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>HERO UPGRADES — 4 heroes x 3 paths x 5 tiers (HEROES.md)</t>
+          <t>HERO UPGRADES — 4 heroes x 3 paths x 6 tiers (HEROES.md)</t>
         </is>
       </c>
     </row>
@@ -19251,6 +19251,46 @@
       <c r="AS4" s="104" t="inlineStr">
         <is>
           <t>Size breaks</t>
+        </is>
+      </c>
+      <c r="AT4" s="104" t="inlineStr">
+        <is>
+          <t>Burn patch reach (studs)</t>
+        </is>
+      </c>
+      <c r="AU4" s="104" t="inlineStr">
+        <is>
+          <t>Staggered reload</t>
+        </is>
+      </c>
+      <c r="AV4" s="104" t="inlineStr">
+        <is>
+          <t>Ricochet reload (rounds)</t>
+        </is>
+      </c>
+      <c r="AW4" s="104" t="inlineStr">
+        <is>
+          <t>Burst recoil reset</t>
+        </is>
+      </c>
+      <c r="AX4" s="104" t="inlineStr">
+        <is>
+          <t>Spun-up belt</t>
+        </is>
+      </c>
+      <c r="AY4" s="104" t="inlineStr">
+        <is>
+          <t>Still spread x</t>
+        </is>
+      </c>
+      <c r="AZ4" s="104" t="inlineStr">
+        <is>
+          <t>Scoped spread x</t>
+        </is>
+      </c>
+      <c r="BA4" s="104" t="inlineStr">
+        <is>
+          <t>Ability charges</t>
         </is>
       </c>
     </row>
@@ -23274,6 +23314,914 @@
         <v>6</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="43" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="B65" s="43" t="inlineStr">
+        <is>
+          <t>Gunslinger</t>
+        </is>
+      </c>
+      <c r="C65" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D65" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E65" s="43" t="inlineStr">
+        <is>
+          <t>Hot Swap</t>
+        </is>
+      </c>
+      <c r="F65" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D65-1),0)</f>
+        <v/>
+      </c>
+      <c r="G65" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I65" s="57" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J65" s="57" t="n"/>
+      <c r="K65" s="57" t="n"/>
+      <c r="L65" s="57" t="n"/>
+      <c r="M65" s="57" t="n"/>
+      <c r="N65" s="57" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="O65" s="57" t="n"/>
+      <c r="P65" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q65" s="57" t="n"/>
+      <c r="R65" s="57" t="n"/>
+      <c r="S65" s="57" t="n"/>
+      <c r="T65" s="57" t="n"/>
+      <c r="U65" s="57" t="n"/>
+      <c r="V65" s="57" t="n"/>
+      <c r="W65" s="57" t="n"/>
+      <c r="X65" s="57" t="n"/>
+      <c r="Y65" s="57" t="n"/>
+      <c r="Z65" s="57" t="n"/>
+      <c r="AA65" s="57" t="n"/>
+      <c r="AB65" s="57" t="n"/>
+      <c r="AC65" s="57" t="n"/>
+      <c r="AD65" s="57" t="n"/>
+      <c r="AE65" s="57" t="n"/>
+      <c r="AF65" s="57" t="n"/>
+      <c r="AG65" s="57" t="n"/>
+      <c r="AH65" s="57" t="n"/>
+      <c r="AI65" s="57" t="n"/>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="43" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="B66" s="43" t="inlineStr">
+        <is>
+          <t>Marksman</t>
+        </is>
+      </c>
+      <c r="C66" s="43" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D66" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E66" s="43" t="inlineStr">
+        <is>
+          <t>Heart Shot</t>
+        </is>
+      </c>
+      <c r="F66" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D66-1),0)</f>
+        <v/>
+      </c>
+      <c r="G66" s="57" t="n"/>
+      <c r="H66" s="57" t="n"/>
+      <c r="I66" s="57" t="n"/>
+      <c r="J66" s="57" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K66" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L66" s="57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M66" s="57" t="n"/>
+      <c r="N66" s="57" t="n"/>
+      <c r="O66" s="57" t="n"/>
+      <c r="P66" s="57" t="n"/>
+      <c r="Q66" s="57" t="n"/>
+      <c r="R66" s="57" t="n"/>
+      <c r="S66" s="57" t="n"/>
+      <c r="T66" s="57" t="n"/>
+      <c r="U66" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V66" s="57" t="n"/>
+      <c r="W66" s="57" t="n"/>
+      <c r="X66" s="57" t="n"/>
+      <c r="Y66" s="57" t="n"/>
+      <c r="Z66" s="57" t="n"/>
+      <c r="AA66" s="57" t="n"/>
+      <c r="AB66" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC66" s="57" t="n"/>
+      <c r="AD66" s="57" t="n"/>
+      <c r="AE66" s="57" t="n"/>
+      <c r="AF66" s="57" t="n"/>
+      <c r="AG66" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AH66" s="57" t="n"/>
+      <c r="AI66" s="57" t="n"/>
+      <c r="AS66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="43" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="B67" s="43" t="inlineStr">
+        <is>
+          <t>Trick Shot</t>
+        </is>
+      </c>
+      <c r="C67" s="43" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="D67" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E67" s="43" t="inlineStr">
+        <is>
+          <t>Trick Reload</t>
+        </is>
+      </c>
+      <c r="F67" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D67-1),0)</f>
+        <v/>
+      </c>
+      <c r="G67" s="57" t="n"/>
+      <c r="H67" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I67" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J67" s="57" t="n"/>
+      <c r="K67" s="57" t="n"/>
+      <c r="L67" s="57" t="n"/>
+      <c r="M67" s="57" t="n"/>
+      <c r="N67" s="57" t="n"/>
+      <c r="O67" s="57" t="n"/>
+      <c r="P67" s="57" t="n"/>
+      <c r="Q67" s="57" t="n"/>
+      <c r="R67" s="57" t="n"/>
+      <c r="S67" s="57" t="n"/>
+      <c r="T67" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" s="57" t="n"/>
+      <c r="V67" s="57" t="n"/>
+      <c r="W67" s="57" t="n"/>
+      <c r="X67" s="57" t="n"/>
+      <c r="Y67" s="57" t="n"/>
+      <c r="Z67" s="57" t="n"/>
+      <c r="AA67" s="57" t="n"/>
+      <c r="AB67" s="57" t="n"/>
+      <c r="AC67" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD67" s="57" t="n"/>
+      <c r="AE67" s="57" t="n"/>
+      <c r="AF67" s="57" t="n"/>
+      <c r="AG67" s="57" t="n"/>
+      <c r="AH67" s="57" t="n"/>
+      <c r="AI67" s="57" t="n"/>
+      <c r="AV67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="43" t="inlineStr">
+        <is>
+          <t>Big Game Hunter</t>
+        </is>
+      </c>
+      <c r="B68" s="43" t="inlineStr">
+        <is>
+          <t>Stalker</t>
+        </is>
+      </c>
+      <c r="C68" s="43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D68" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E68" s="43" t="inlineStr">
+        <is>
+          <t>Five-Round Burst</t>
+        </is>
+      </c>
+      <c r="F68" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D68-1),0)</f>
+        <v/>
+      </c>
+      <c r="G68" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H68" s="57" t="n"/>
+      <c r="I68" s="57" t="n"/>
+      <c r="J68" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K68" s="57" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L68" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M68" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N68" s="57" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="O68" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="P68" s="57" t="n"/>
+      <c r="Q68" s="57" t="n"/>
+      <c r="R68" s="57" t="n"/>
+      <c r="S68" s="57" t="n"/>
+      <c r="T68" s="57" t="n"/>
+      <c r="U68" s="57" t="n"/>
+      <c r="V68" s="57" t="n"/>
+      <c r="W68" s="57" t="n"/>
+      <c r="X68" s="57" t="n"/>
+      <c r="Y68" s="57" t="n"/>
+      <c r="Z68" s="57" t="n"/>
+      <c r="AA68" s="57" t="n"/>
+      <c r="AB68" s="57" t="n"/>
+      <c r="AC68" s="57" t="n"/>
+      <c r="AD68" s="57" t="n"/>
+      <c r="AE68" s="57" t="n"/>
+      <c r="AF68" s="57" t="n"/>
+      <c r="AG68" s="57" t="n"/>
+      <c r="AH68" s="57" t="n"/>
+      <c r="AI68" s="57" t="n"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="43" t="inlineStr">
+        <is>
+          <t>Big Game Hunter</t>
+        </is>
+      </c>
+      <c r="B69" s="43" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C69" s="43" t="inlineStr">
+        <is>
+          <t>sustain</t>
+        </is>
+      </c>
+      <c r="D69" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E69" s="43" t="inlineStr">
+        <is>
+          <t>Endless Belt</t>
+        </is>
+      </c>
+      <c r="F69" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D69-1),0)</f>
+        <v/>
+      </c>
+      <c r="G69" s="57" t="n"/>
+      <c r="H69" s="57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I69" s="57" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J69" s="57" t="n"/>
+      <c r="K69" s="57" t="n"/>
+      <c r="L69" s="57" t="n"/>
+      <c r="M69" s="57" t="n"/>
+      <c r="N69" s="57" t="n"/>
+      <c r="O69" s="57" t="n"/>
+      <c r="P69" s="57" t="n"/>
+      <c r="Q69" s="57" t="n"/>
+      <c r="R69" s="57" t="n"/>
+      <c r="S69" s="57" t="n"/>
+      <c r="T69" s="57" t="n"/>
+      <c r="U69" s="57" t="n"/>
+      <c r="V69" s="57" t="n"/>
+      <c r="W69" s="57" t="n"/>
+      <c r="X69" s="57" t="n"/>
+      <c r="Y69" s="57" t="n"/>
+      <c r="Z69" s="57" t="n"/>
+      <c r="AA69" s="57" t="n"/>
+      <c r="AB69" s="57" t="n"/>
+      <c r="AC69" s="57" t="n"/>
+      <c r="AD69" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE69" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF69" s="57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG69" s="57" t="n"/>
+      <c r="AH69" s="57" t="n"/>
+      <c r="AI69" s="57" t="n"/>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="43" t="inlineStr">
+        <is>
+          <t>Big Game Hunter</t>
+        </is>
+      </c>
+      <c r="B70" s="43" t="inlineStr">
+        <is>
+          <t>Special Ammo</t>
+        </is>
+      </c>
+      <c r="C70" s="43" t="inlineStr">
+        <is>
+          <t>rounds</t>
+        </is>
+      </c>
+      <c r="D70" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E70" s="43" t="inlineStr">
+        <is>
+          <t>Powder Tips</t>
+        </is>
+      </c>
+      <c r="F70" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D70-1),0)</f>
+        <v/>
+      </c>
+      <c r="G70" s="57" t="n"/>
+      <c r="H70" s="57" t="n"/>
+      <c r="I70" s="57" t="n"/>
+      <c r="J70" s="57" t="n"/>
+      <c r="K70" s="57" t="n"/>
+      <c r="L70" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M70" s="57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N70" s="57" t="n"/>
+      <c r="O70" s="57" t="n"/>
+      <c r="P70" s="57" t="n"/>
+      <c r="Q70" s="57" t="n"/>
+      <c r="R70" s="57" t="n"/>
+      <c r="S70" s="57" t="n"/>
+      <c r="T70" s="57" t="n"/>
+      <c r="U70" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V70" s="57" t="n"/>
+      <c r="W70" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X70" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y70" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z70" s="57" t="n"/>
+      <c r="AA70" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB70" s="57" t="n"/>
+      <c r="AC70" s="57" t="n"/>
+      <c r="AD70" s="57" t="n"/>
+      <c r="AE70" s="57" t="n"/>
+      <c r="AF70" s="57" t="n"/>
+      <c r="AG70" s="57" t="n"/>
+      <c r="AH70" s="57" t="n"/>
+      <c r="AI70" s="57" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="43" t="inlineStr">
+        <is>
+          <t>Brush Beater</t>
+        </is>
+      </c>
+      <c r="B71" s="43" t="inlineStr">
+        <is>
+          <t>Slug</t>
+        </is>
+      </c>
+      <c r="C71" s="43" t="inlineStr">
+        <is>
+          <t>reach</t>
+        </is>
+      </c>
+      <c r="D71" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E71" s="43" t="inlineStr">
+        <is>
+          <t>Thunder Slug</t>
+        </is>
+      </c>
+      <c r="F71" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D71-1),0)</f>
+        <v/>
+      </c>
+      <c r="G71" s="57" t="n"/>
+      <c r="H71" s="57" t="n"/>
+      <c r="I71" s="57" t="n"/>
+      <c r="J71" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K71" s="57" t="n"/>
+      <c r="L71" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="M71" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" s="57" t="n"/>
+      <c r="O71" s="57" t="n"/>
+      <c r="P71" s="57" t="n"/>
+      <c r="Q71" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R71" s="57" t="n"/>
+      <c r="S71" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="T71" s="57" t="n"/>
+      <c r="U71" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V71" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W71" s="57" t="n"/>
+      <c r="X71" s="57" t="n"/>
+      <c r="Y71" s="57" t="n"/>
+      <c r="Z71" s="57" t="n"/>
+      <c r="AA71" s="57" t="n"/>
+      <c r="AB71" s="57" t="n"/>
+      <c r="AC71" s="57" t="n"/>
+      <c r="AD71" s="57" t="n"/>
+      <c r="AE71" s="57" t="n"/>
+      <c r="AF71" s="57" t="n"/>
+      <c r="AG71" s="57" t="n"/>
+      <c r="AH71" s="57" t="n"/>
+      <c r="AI71" s="57" t="n"/>
+      <c r="AS71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="43" t="inlineStr">
+        <is>
+          <t>Brush Beater</t>
+        </is>
+      </c>
+      <c r="B72" s="43" t="inlineStr">
+        <is>
+          <t>Buckshot</t>
+        </is>
+      </c>
+      <c r="C72" s="43" t="inlineStr">
+        <is>
+          <t>crowds</t>
+        </is>
+      </c>
+      <c r="D72" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E72" s="43" t="inlineStr">
+        <is>
+          <t>Wildfire Drum</t>
+        </is>
+      </c>
+      <c r="F72" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D72-1),0)</f>
+        <v/>
+      </c>
+      <c r="G72" s="57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H72" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="I72" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J72" s="57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K72" s="57" t="n"/>
+      <c r="L72" s="57" t="n"/>
+      <c r="M72" s="57" t="n"/>
+      <c r="N72" s="57" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="O72" s="57" t="n"/>
+      <c r="P72" s="57" t="n"/>
+      <c r="Q72" s="57" t="n">
+        <v>9</v>
+      </c>
+      <c r="R72" s="57" t="n"/>
+      <c r="S72" s="57" t="n"/>
+      <c r="T72" s="57" t="n"/>
+      <c r="U72" s="57" t="n"/>
+      <c r="V72" s="57" t="n"/>
+      <c r="W72" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X72" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="57" t="n"/>
+      <c r="Z72" s="57" t="n"/>
+      <c r="AA72" s="57" t="n"/>
+      <c r="AB72" s="57" t="n"/>
+      <c r="AC72" s="57" t="n"/>
+      <c r="AD72" s="57" t="n"/>
+      <c r="AE72" s="57" t="n"/>
+      <c r="AF72" s="57" t="n"/>
+      <c r="AG72" s="57" t="n"/>
+      <c r="AH72" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI72" s="57" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="43" t="inlineStr">
+        <is>
+          <t>Brush Beater</t>
+        </is>
+      </c>
+      <c r="B73" s="43" t="inlineStr">
+        <is>
+          <t>Point Blank</t>
+        </is>
+      </c>
+      <c r="C73" s="43" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="D73" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E73" s="43" t="inlineStr">
+        <is>
+          <t>Quad Barrel</t>
+        </is>
+      </c>
+      <c r="F73" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D73-1),0)</f>
+        <v/>
+      </c>
+      <c r="G73" s="57" t="n"/>
+      <c r="H73" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I73" s="57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J73" s="57" t="n"/>
+      <c r="K73" s="57" t="n"/>
+      <c r="L73" s="57" t="n"/>
+      <c r="M73" s="57" t="n"/>
+      <c r="N73" s="57" t="n"/>
+      <c r="O73" s="57" t="n"/>
+      <c r="P73" s="57" t="n"/>
+      <c r="Q73" s="57" t="n"/>
+      <c r="R73" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="S73" s="57" t="n"/>
+      <c r="T73" s="57" t="n"/>
+      <c r="U73" s="57" t="n"/>
+      <c r="V73" s="57" t="n"/>
+      <c r="W73" s="57" t="n"/>
+      <c r="X73" s="57" t="n"/>
+      <c r="Y73" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z73" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA73" s="57" t="n"/>
+      <c r="AB73" s="57" t="n"/>
+      <c r="AC73" s="57" t="n"/>
+      <c r="AD73" s="57" t="n"/>
+      <c r="AE73" s="57" t="n"/>
+      <c r="AF73" s="57" t="n"/>
+      <c r="AG73" s="57" t="n"/>
+      <c r="AH73" s="57" t="n"/>
+      <c r="AI73" s="57" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B74" s="43" t="inlineStr">
+        <is>
+          <t>Triage</t>
+        </is>
+      </c>
+      <c r="C74" s="43" t="inlineStr">
+        <is>
+          <t>ability</t>
+        </is>
+      </c>
+      <c r="D74" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E74" s="43" t="inlineStr">
+        <is>
+          <t>Rapid Response</t>
+        </is>
+      </c>
+      <c r="F74" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D74-1),0)</f>
+        <v/>
+      </c>
+      <c r="G74" s="57" t="n"/>
+      <c r="H74" s="57" t="n"/>
+      <c r="I74" s="57" t="n"/>
+      <c r="J74" s="57" t="n"/>
+      <c r="K74" s="57" t="n"/>
+      <c r="L74" s="57" t="n"/>
+      <c r="M74" s="57" t="n"/>
+      <c r="N74" s="57" t="n"/>
+      <c r="O74" s="57" t="n"/>
+      <c r="P74" s="57" t="n"/>
+      <c r="Q74" s="57" t="n"/>
+      <c r="R74" s="57" t="n"/>
+      <c r="S74" s="57" t="n"/>
+      <c r="T74" s="57" t="n"/>
+      <c r="U74" s="57" t="n"/>
+      <c r="V74" s="57" t="n"/>
+      <c r="W74" s="57" t="n"/>
+      <c r="X74" s="57" t="n"/>
+      <c r="Y74" s="57" t="n"/>
+      <c r="Z74" s="57" t="n"/>
+      <c r="AA74" s="57" t="n"/>
+      <c r="AB74" s="57" t="n"/>
+      <c r="AC74" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD74" s="57" t="n"/>
+      <c r="AE74" s="57" t="n"/>
+      <c r="AF74" s="57" t="n"/>
+      <c r="AG74" s="57" t="n"/>
+      <c r="AH74" s="57" t="n"/>
+      <c r="AI74" s="57" t="n"/>
+      <c r="AJ74" s="81" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK74" s="81" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL74" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM74" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="AN74" s="81" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B75" s="43" t="inlineStr">
+        <is>
+          <t>Lever Action</t>
+        </is>
+      </c>
+      <c r="C75" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D75" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" s="43" t="inlineStr">
+        <is>
+          <t>Tube Feed</t>
+        </is>
+      </c>
+      <c r="F75" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D75-1),0)</f>
+        <v/>
+      </c>
+      <c r="G75" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H75" s="57" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I75" s="57" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J75" s="57" t="n"/>
+      <c r="K75" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L75" s="57" t="n"/>
+      <c r="M75" s="57" t="n"/>
+      <c r="N75" s="57" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="O75" s="57" t="n"/>
+      <c r="P75" s="57" t="n"/>
+      <c r="Q75" s="57" t="n"/>
+      <c r="R75" s="57" t="n"/>
+      <c r="S75" s="57" t="n"/>
+      <c r="T75" s="57" t="n"/>
+      <c r="U75" s="57" t="n"/>
+      <c r="V75" s="57" t="n"/>
+      <c r="W75" s="57" t="n"/>
+      <c r="X75" s="57" t="n"/>
+      <c r="Y75" s="57" t="n"/>
+      <c r="Z75" s="57" t="n"/>
+      <c r="AA75" s="57" t="n"/>
+      <c r="AB75" s="57" t="n"/>
+      <c r="AC75" s="57" t="n"/>
+      <c r="AD75" s="57" t="n"/>
+      <c r="AE75" s="57" t="n"/>
+      <c r="AF75" s="57" t="n"/>
+      <c r="AG75" s="57" t="n"/>
+      <c r="AH75" s="57" t="n"/>
+      <c r="AI75" s="57" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B76" s="43" t="inlineStr">
+        <is>
+          <t>Muzzle</t>
+        </is>
+      </c>
+      <c r="C76" s="43" t="inlineStr">
+        <is>
+          <t>protective rounds</t>
+        </is>
+      </c>
+      <c r="D76" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E76" s="43" t="inlineStr">
+        <is>
+          <t>Nightcap</t>
+        </is>
+      </c>
+      <c r="F76" s="56">
+        <f>ROUND(Tuning!$B$21*POWER(Tuning!$B$22,D76-1),0)</f>
+        <v/>
+      </c>
+      <c r="G76" s="57" t="n"/>
+      <c r="H76" s="57" t="n"/>
+      <c r="I76" s="57" t="n"/>
+      <c r="J76" s="57" t="n"/>
+      <c r="K76" s="57" t="n"/>
+      <c r="L76" s="57" t="n"/>
+      <c r="M76" s="57" t="n"/>
+      <c r="N76" s="57" t="n"/>
+      <c r="O76" s="57" t="n"/>
+      <c r="P76" s="57" t="n"/>
+      <c r="Q76" s="57" t="n"/>
+      <c r="R76" s="57" t="n"/>
+      <c r="S76" s="57" t="n"/>
+      <c r="T76" s="57" t="n"/>
+      <c r="U76" s="57" t="n"/>
+      <c r="V76" s="57" t="n"/>
+      <c r="W76" s="57" t="n"/>
+      <c r="X76" s="57" t="n"/>
+      <c r="Y76" s="57" t="n"/>
+      <c r="Z76" s="57" t="n"/>
+      <c r="AA76" s="57" t="n"/>
+      <c r="AB76" s="57" t="n"/>
+      <c r="AC76" s="57" t="n"/>
+      <c r="AD76" s="57" t="n"/>
+      <c r="AE76" s="57" t="n"/>
+      <c r="AF76" s="57" t="n"/>
+      <c r="AG76" s="57" t="n"/>
+      <c r="AH76" s="57" t="n"/>
+      <c r="AI76" s="57" t="n"/>
+      <c r="AO76" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP76" s="81" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ76" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR76" s="81" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -2240,7 +2240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="90" min="1" max="1"/>
@@ -2267,6 +2267,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -2333,6 +2334,11 @@
           <t>Hero damage x</t>
         </is>
       </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t>Clear XP</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="43" t="inlineStr">
@@ -2378,6 +2384,9 @@
       <c r="M5" s="27" t="n">
         <v>1</v>
       </c>
+      <c r="N5" s="27" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
@@ -2422,6 +2431,9 @@
       </c>
       <c r="M6" s="27" t="n">
         <v>1</v>
+      </c>
+      <c r="N6" s="27" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -2464,6 +2476,9 @@
       <c r="M7" s="27" t="n">
         <v>1</v>
       </c>
+      <c r="N7" s="27" t="n">
+        <v>1500</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
@@ -2509,7 +2524,12 @@
       <c r="M8" s="27" t="n">
         <v>1.5</v>
       </c>
-    </row>
+      <c r="N8" s="27" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -5776,7 +5796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -7386,6 +7406,97 @@
       <c r="D102" s="103" t="inlineStr">
         <is>
           <t>The most sizes one hit may drop (pierce-through cap). 1 = off everywhere. DECISIONS #126.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="99" t="inlineStr">
+        <is>
+          <t>PLAYER LEVEL</t>
+        </is>
+      </c>
+      <c r="B104" s="105" t="n"/>
+      <c r="C104" s="105" t="n"/>
+      <c r="D104" s="105" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="100" t="inlineStr">
+        <is>
+          <t>Player XP base</t>
+        </is>
+      </c>
+      <c r="B105" s="101" t="n">
+        <v>500</v>
+      </c>
+      <c r="C105" s="102" t="inlineStr">
+        <is>
+          <t>XP</t>
+        </is>
+      </c>
+      <c r="D105" s="103" t="inlineStr">
+        <is>
+          <t>Player level 1 -&gt; 2 costs this much player XP (DECISIONS #120). Saved between matches; rewards are cosmetic only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="100" t="inlineStr">
+        <is>
+          <t>Player XP step</t>
+        </is>
+      </c>
+      <c r="B106" s="101" t="n">
+        <v>50</v>
+      </c>
+      <c r="C106" s="102" t="inlineStr">
+        <is>
+          <t>XP</t>
+        </is>
+      </c>
+      <c r="D106" s="103" t="inlineStr">
+        <is>
+          <t>Each player level costs this much more than the one before: level n -&gt; n+1 = base + step x (n-1) (DECISIONS #120).</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="100" t="inlineStr">
+        <is>
+          <t>Player XP per level max</t>
+        </is>
+      </c>
+      <c r="B107" s="101" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C107" s="102" t="inlineStr">
+        <is>
+          <t>XP</t>
+        </is>
+      </c>
+      <c r="D107" s="103" t="inlineStr">
+        <is>
+          <t>No player level costs more than this (reached at level 191 with the seeds); levels never end (DECISIONS #120).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="100" t="inlineStr">
+        <is>
+          <t>Solo take-down XP x</t>
+        </is>
+      </c>
+      <c r="B108" s="101" t="n">
+        <v>2</v>
+      </c>
+      <c r="C108" s="102" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D108" s="103" t="inlineStr">
+        <is>
+          <t>In solo, the take-down part of the match's hero XP counts this many times toward player XP only; co-op and the hunter level are unchanged (DECISIONS #124). 1 = off.</t>
         </is>
       </c>
     </row>
@@ -18975,7 +19086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA79"/>
+  <dimension ref="A1:BA76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="90" min="1" max="1"/>
@@ -23383,7 +23494,7 @@
       <c r="AG65" s="57" t="n"/>
       <c r="AH65" s="57" t="n"/>
       <c r="AI65" s="57" t="n"/>
-      <c r="AU65" t="inlineStr">
+      <c r="AU65" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -23462,10 +23573,10 @@
       </c>
       <c r="AH66" s="57" t="n"/>
       <c r="AI66" s="57" t="n"/>
-      <c r="AS66" t="n">
+      <c r="AS66" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="AZ66" t="n">
+      <c r="AZ66" s="81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23534,7 +23645,7 @@
       <c r="AG67" s="57" t="n"/>
       <c r="AH67" s="57" t="n"/>
       <c r="AI67" s="57" t="n"/>
-      <c r="AV67" t="n">
+      <c r="AV67" s="81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23611,7 +23722,7 @@
       <c r="AG68" s="57" t="n"/>
       <c r="AH68" s="57" t="n"/>
       <c r="AI68" s="57" t="n"/>
-      <c r="AW68" t="inlineStr">
+      <c r="AW68" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -23686,7 +23797,7 @@
       <c r="AG69" s="57" t="n"/>
       <c r="AH69" s="57" t="n"/>
       <c r="AI69" s="57" t="n"/>
-      <c r="AX69" t="inlineStr">
+      <c r="AX69" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -23841,10 +23952,10 @@
       <c r="AG71" s="57" t="n"/>
       <c r="AH71" s="57" t="n"/>
       <c r="AI71" s="57" t="n"/>
-      <c r="AS71" t="n">
+      <c r="AS71" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="AY71" t="n">
+      <c r="AY71" s="81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23927,7 +24038,7 @@
       <c r="AI72" s="57" t="n">
         <v>0.35</v>
       </c>
-      <c r="AT72" t="n">
+      <c r="AT72" s="81" t="n">
         <v>4</v>
       </c>
     </row>
@@ -24075,7 +24186,7 @@
       <c r="AN74" s="81" t="n">
         <v>8</v>
       </c>
-      <c r="BA74" t="n">
+      <c r="BA74" s="81" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24219,9 +24330,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -2267,7 +2267,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -2528,8 +2527,6 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -7409,7 +7406,6 @@
         </is>
       </c>
     </row>
-    <row r="103"/>
     <row r="104">
       <c r="A104" s="99" t="inlineStr">
         <is>
@@ -23601,7 +23597,7 @@
       </c>
       <c r="E67" s="43" t="inlineStr">
         <is>
-          <t>Trick Reload</t>
+          <t>Bounce Back</t>
         </is>
       </c>
       <c r="F67" s="56">
@@ -23670,7 +23666,7 @@
       </c>
       <c r="E68" s="43" t="inlineStr">
         <is>
-          <t>Five-Round Burst</t>
+          <t>Big Five</t>
         </is>
       </c>
       <c r="F68" s="56">
@@ -23824,7 +23820,7 @@
       </c>
       <c r="E70" s="43" t="inlineStr">
         <is>
-          <t>Powder Tips</t>
+          <t>Dynamite Rounds</t>
         </is>
       </c>
       <c r="F70" s="56">
@@ -24211,7 +24207,7 @@
       </c>
       <c r="E75" s="43" t="inlineStr">
         <is>
-          <t>Tube Feed</t>
+          <t>Bottomless Tube</t>
         </is>
       </c>
       <c r="F75" s="56">
@@ -24281,7 +24277,7 @@
       </c>
       <c r="E76" s="43" t="inlineStr">
         <is>
-          <t>Nightcap</t>
+          <t>Lights Out</t>
         </is>
       </c>
       <c r="F76" s="56">
@@ -24728,7 +24724,7 @@
       </c>
       <c r="E11" s="69" t="inlineStr">
         <is>
-          <t>Field Dressing I: heal 5 more HP when a round is cleared</t>
+          <t>First Aid I: heal 5 more HP when a round is cleared</t>
         </is>
       </c>
       <c r="F11" s="56" t="n">
@@ -24776,7 +24772,7 @@
       </c>
       <c r="E12" s="69" t="inlineStr">
         <is>
-          <t>Quick Recovery I: respawn 10% sooner</t>
+          <t>Back in Action I: respawn 10% sooner</t>
         </is>
       </c>
       <c r="F12" s="56" t="n">
@@ -24968,7 +24964,7 @@
       </c>
       <c r="E16" s="69" t="inlineStr">
         <is>
-          <t>Field Dressing II: heal 10 more HP when a round is cleared</t>
+          <t>First Aid II: heal 10 more HP when a round is cleared</t>
         </is>
       </c>
       <c r="F16" s="56" t="n">
@@ -25016,7 +25012,7 @@
       </c>
       <c r="E17" s="69" t="inlineStr">
         <is>
-          <t>Quick Recovery II: respawn 20% sooner</t>
+          <t>Back in Action II: respawn 20% sooner</t>
         </is>
       </c>
       <c r="F17" s="56" t="n">
@@ -25208,7 +25204,7 @@
       </c>
       <c r="E21" s="69" t="inlineStr">
         <is>
-          <t>Field Dressing III: heal 15 more HP when a round is cleared</t>
+          <t>First Aid III: heal 15 more HP when a round is cleared</t>
         </is>
       </c>
       <c r="F21" s="56" t="n">
@@ -25256,7 +25252,7 @@
       </c>
       <c r="E22" s="69" t="inlineStr">
         <is>
-          <t>Quick Recovery III: respawn 30% sooner</t>
+          <t>Back in Action III: respawn 30% sooner</t>
         </is>
       </c>
       <c r="F22" s="56" t="n">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Daily Haul" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Bounties" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Mastery Perks" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Cosmetics" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -464,7 +465,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -780,6 +781,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -5787,6 +5794,3525 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I118"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="90" min="1" max="1"/>
+    <col width="8" customWidth="1" style="90" min="2" max="2"/>
+    <col width="20" customWidth="1" style="90" min="3" max="3"/>
+    <col width="22" customWidth="1" style="90" min="4" max="4"/>
+    <col width="11" customWidth="1" style="90" min="5" max="5"/>
+    <col width="10" customWidth="1" style="90" min="6" max="6"/>
+    <col width="14" customWidth="1" style="90" min="7" max="7"/>
+    <col width="10" customWidth="1" style="90" min="8" max="8"/>
+    <col width="13" customWidth="1" style="90" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="107" t="inlineStr">
+        <is>
+          <t>COSMETICS — player level rewards (names are working names, Dino review T59)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="108" t="inlineStr">
+        <is>
+          <t>One row per reward. Levels 2-99 except multiples of 10: one common each (name colour, gun tint, tracer colour, crosshair colour, tower flag, leaderboard banner). Every 10 to 100: a rare (hunting hat, gun pattern, hit-marker, sprint trail) + a title. 150 and 200: an animated set (legendary) + a title. Nothing else up to 200. Past 200: the row with 'Repeat every' gives a title every N levels, forever ({n} in its name = the level). Cosmetic only: no gameplay effect. No gold: gold is mastery 20's alone (DECISIONS #121). Colour = #RRGGBB; Material = a Roblox material; Pattern: hat Brim/Cap/Crest, hit-marker Cross/Plus/Diamond/Star, set Pulse/Cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="104" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B4" s="104" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="C4" s="104" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="D4" s="104" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E4" s="104" t="inlineStr">
+        <is>
+          <t>Rarity</t>
+        </is>
+      </c>
+      <c r="F4" s="104" t="inlineStr">
+        <is>
+          <t>Colour</t>
+        </is>
+      </c>
+      <c r="G4" s="104" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="H4" s="104" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+      <c r="I4" s="104" t="inlineStr">
+        <is>
+          <t>Repeat every</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="81" t="inlineStr">
+        <is>
+          <t>NAME_FERN</t>
+        </is>
+      </c>
+      <c r="B5" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="81" t="inlineStr">
+        <is>
+          <t>Name colour</t>
+        </is>
+      </c>
+      <c r="D5" s="81" t="inlineStr">
+        <is>
+          <t>Fern Name</t>
+        </is>
+      </c>
+      <c r="E5" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="81" t="inlineStr">
+        <is>
+          <t>#4F7942</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="81" t="inlineStr">
+        <is>
+          <t>TINT_OCHRE</t>
+        </is>
+      </c>
+      <c r="B6" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="81" t="inlineStr">
+        <is>
+          <t>Gun tint</t>
+        </is>
+      </c>
+      <c r="D6" s="81" t="inlineStr">
+        <is>
+          <t>Ochre Tint</t>
+        </is>
+      </c>
+      <c r="E6" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F6" s="81" t="inlineStr">
+        <is>
+          <t>#CC7722</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="81" t="inlineStr">
+        <is>
+          <t>TRACER_ASH</t>
+        </is>
+      </c>
+      <c r="B7" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="81" t="inlineStr">
+        <is>
+          <t>Tracer colour</t>
+        </is>
+      </c>
+      <c r="D7" s="81" t="inlineStr">
+        <is>
+          <t>Ash Tracers</t>
+        </is>
+      </c>
+      <c r="E7" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F7" s="81" t="inlineStr">
+        <is>
+          <t>#B2B2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="81" t="inlineStr">
+        <is>
+          <t>SIGHT_SKY</t>
+        </is>
+      </c>
+      <c r="B8" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="81" t="inlineStr">
+        <is>
+          <t>Crosshair colour</t>
+        </is>
+      </c>
+      <c r="D8" s="81" t="inlineStr">
+        <is>
+          <t>Sky Sights</t>
+        </is>
+      </c>
+      <c r="E8" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F8" s="81" t="inlineStr">
+        <is>
+          <t>#78B4E6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="81" t="inlineStr">
+        <is>
+          <t>FLAG_ROSE</t>
+        </is>
+      </c>
+      <c r="B9" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="81" t="inlineStr">
+        <is>
+          <t>Tower flag</t>
+        </is>
+      </c>
+      <c r="D9" s="81" t="inlineStr">
+        <is>
+          <t>Rose Flag</t>
+        </is>
+      </c>
+      <c r="E9" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F9" s="81" t="inlineStr">
+        <is>
+          <t>#DC8296</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="81" t="inlineStr">
+        <is>
+          <t>BANNER_FERN</t>
+        </is>
+      </c>
+      <c r="B10" s="81" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="81" t="inlineStr">
+        <is>
+          <t>Leaderboard banner</t>
+        </is>
+      </c>
+      <c r="D10" s="81" t="inlineStr">
+        <is>
+          <t>Fern Banner</t>
+        </is>
+      </c>
+      <c r="E10" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F10" s="81" t="inlineStr">
+        <is>
+          <t>#4F7942</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="81" t="inlineStr">
+        <is>
+          <t>NAME_MOSS</t>
+        </is>
+      </c>
+      <c r="B11" s="81" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="81" t="inlineStr">
+        <is>
+          <t>Name colour</t>
+        </is>
+      </c>
+      <c r="D11" s="81" t="inlineStr">
+        <is>
+          <t>Moss Name</t>
+        </is>
+      </c>
+      <c r="E11" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F11" s="81" t="inlineStr">
+        <is>
+          <t>#8A9A5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="81" t="inlineStr">
+        <is>
+          <t>TINT_RUST</t>
+        </is>
+      </c>
+      <c r="B12" s="81" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" s="81" t="inlineStr">
+        <is>
+          <t>Gun tint</t>
+        </is>
+      </c>
+      <c r="D12" s="81" t="inlineStr">
+        <is>
+          <t>Rust Tint</t>
+        </is>
+      </c>
+      <c r="E12" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F12" s="81" t="inlineStr">
+        <is>
+          <t>#A04828</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="81" t="inlineStr">
+        <is>
+          <t>HAT_BUSH</t>
+        </is>
+      </c>
+      <c r="B13" s="81" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="81" t="inlineStr">
+        <is>
+          <t>Hunting hat</t>
+        </is>
+      </c>
+      <c r="D13" s="81" t="inlineStr">
+        <is>
+          <t>Bush Hat</t>
+        </is>
+      </c>
+      <c r="E13" s="81" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F13" s="81" t="inlineStr">
+        <is>
+          <t>#6E7846</t>
+        </is>
+      </c>
+      <c r="G13" s="81" t="inlineStr">
+        <is>
+          <t>Fabric</t>
+        </is>
+      </c>
+      <c r="H13" s="81" t="inlineStr">
+        <is>
+          <t>Brim</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="81" t="inlineStr">
+        <is>
+          <t>TITLE_10</t>
+        </is>
+      </c>
+      <c r="B14" s="81" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="81" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D14" s="81" t="inlineStr">
+        <is>
+          <t>Greenhorn</t>
+        </is>
+      </c>
+      <c r="E14" s="81" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="81" t="inlineStr">
+        <is>
+          <t>TRACER_SLATE</t>
+        </is>
+      </c>
+      <c r="B15" s="81" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="81" t="inlineStr">
+        <is>
+          <t>Tracer colour</t>
+        </is>
+      </c>
+      <c r="D15" s="81" t="inlineStr">
+        <is>
+          <t>Slate Tracers</t>
+        </is>
+      </c>
+      <c r="E15" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F15" s="81" t="inlineStr">
+        <is>
+          <t>#586373</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="81" t="inlineStr">
+        <is>
+          <t>SIGHT_DUSK</t>
+        </is>
+      </c>
+      <c r="B16" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" s="81" t="inlineStr">
+        <is>
+          <t>Crosshair colour</t>
+        </is>
+      </c>
+      <c r="D16" s="81" t="inlineStr">
+        <is>
+          <t>Dusk Sights</t>
+        </is>
+      </c>
+      <c r="E16" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F16" s="81" t="inlineStr">
+        <is>
+          <t>#62508C</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="81" t="inlineStr">
+        <is>
+          <t>FLAG_EMBER</t>
+        </is>
+      </c>
+      <c r="B17" s="81" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" s="81" t="inlineStr">
+        <is>
+          <t>Tower flag</t>
+        </is>
+      </c>
+      <c r="D17" s="81" t="inlineStr">
+        <is>
+          <t>Ember Flag</t>
+        </is>
+      </c>
+      <c r="E17" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F17" s="81" t="inlineStr">
+        <is>
+          <t>#E65A32</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="81" t="inlineStr">
+        <is>
+          <t>BANNER_MOSS</t>
+        </is>
+      </c>
+      <c r="B18" s="81" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" s="81" t="inlineStr">
+        <is>
+          <t>Leaderboard banner</t>
+        </is>
+      </c>
+      <c r="D18" s="81" t="inlineStr">
+        <is>
+          <t>Moss Banner</t>
+        </is>
+      </c>
+      <c r="E18" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F18" s="81" t="inlineStr">
+        <is>
+          <t>#8A9A5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="81" t="inlineStr">
+        <is>
+          <t>NAME_CLAY</t>
+        </is>
+      </c>
+      <c r="B19" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" s="81" t="inlineStr">
+        <is>
+          <t>Name colour</t>
+        </is>
+      </c>
+      <c r="D19" s="81" t="inlineStr">
+        <is>
+          <t>Clay Name</t>
+        </is>
+      </c>
+      <c r="E19" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F19" s="81" t="inlineStr">
+        <is>
+          <t>#B0684A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="81" t="inlineStr">
+        <is>
+          <t>TINT_BONE</t>
+        </is>
+      </c>
+      <c r="B20" s="81" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" s="81" t="inlineStr">
+        <is>
+          <t>Gun tint</t>
+        </is>
+      </c>
+      <c r="D20" s="81" t="inlineStr">
+        <is>
+          <t>Bone Tint</t>
+        </is>
+      </c>
+      <c r="E20" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F20" s="81" t="inlineStr">
+        <is>
+          <t>#E3DAC9</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="81" t="inlineStr">
+        <is>
+          <t>TRACER_TEAL</t>
+        </is>
+      </c>
+      <c r="B21" s="81" t="n">
+        <v>17</v>
+      </c>
+      <c r="C21" s="81" t="inlineStr">
+        <is>
+          <t>Tracer colour</t>
+        </is>
+      </c>
+      <c r="D21" s="81" t="inlineStr">
+        <is>
+          <t>Teal Tracers</t>
+        </is>
+      </c>
+      <c r="E21" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F21" s="81" t="inlineStr">
+        <is>
+          <t>#288080</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="81" t="inlineStr">
+        <is>
+          <t>SIGHT_PLUM</t>
+        </is>
+      </c>
+      <c r="B22" s="81" t="n">
+        <v>18</v>
+      </c>
+      <c r="C22" s="81" t="inlineStr">
+        <is>
+          <t>Crosshair colour</t>
+        </is>
+      </c>
+      <c r="D22" s="81" t="inlineStr">
+        <is>
+          <t>Plum Sights</t>
+        </is>
+      </c>
+      <c r="E22" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F22" s="81" t="inlineStr">
+        <is>
+          <t>#823C64</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="81" t="inlineStr">
+        <is>
+          <t>FLAG_SAND</t>
+        </is>
+      </c>
+      <c r="B23" s="81" t="n">
+        <v>19</v>
+      </c>
+      <c r="C23" s="81" t="inlineStr">
+        <is>
+          <t>Tower flag</t>
+        </is>
+      </c>
+      <c r="D23" s="81" t="inlineStr">
+        <is>
+          <t>Sand Flag</t>
+        </is>
+      </c>
+      <c r="E23" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F23" s="81" t="inlineStr">
+        <is>
+          <t>#C2B280</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="81" t="inlineStr">
+        <is>
+          <t>GUN_IRONWOOD</t>
+        </is>
+      </c>
+      <c r="B24" s="81" t="n">
+        <v>20</v>
+      </c>
+      <c r="C24" s="81" t="inlineStr">
+        <is>
+          <t>Gun pattern</t>
+        </is>
+      </c>
+      <c r="D24" s="81" t="inlineStr">
+        <is>
+          <t>Ironwood Stock</t>
+        </is>
+      </c>
+      <c r="E24" s="81" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F24" s="81" t="inlineStr">
+        <is>
+          <t>#785032</t>
+        </is>
+      </c>
+      <c r="G24" s="81" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="81" t="inlineStr">
+        <is>
+          <t>TITLE_20</t>
+        </is>
+      </c>
+      <c r="B25" s="81" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="81" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D25" s="81" t="inlineStr">
+        <is>
+          <t>Trailblazer</t>
+        </is>
+      </c>
+      <c r="E25" s="81" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="81" t="inlineStr">
+        <is>
+          <t>BANNER_CLAY</t>
+        </is>
+      </c>
+      <c r="B26" s="81" t="n">
+        <v>21</v>
+      </c>
+      <c r="C26" s="81" t="inlineStr">
+        <is>
+          <t>Leaderboard banner</t>
+        </is>
+      </c>
+      <c r="D26" s="81" t="inlineStr">
+        <is>
+          <t>Clay Banner</t>
+        </is>
+      </c>
+      <c r="E26" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F26" s="81" t="inlineStr">
+        <is>
+          <t>#B0684A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="81" t="inlineStr">
+        <is>
+          <t>NAME_OCHRE</t>
+        </is>
+      </c>
+      <c r="B27" s="81" t="n">
+        <v>22</v>
+      </c>
+      <c r="C27" s="81" t="inlineStr">
+        <is>
+          <t>Name colour</t>
+        </is>
+      </c>
+      <c r="D27" s="81" t="inlineStr">
+        <is>
+          <t>Ochre Name</t>
+        </is>
+      </c>
+      <c r="E27" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F27" s="81" t="inlineStr">
+        <is>
+          <t>#CC7722</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="81" t="inlineStr">
+        <is>
+          <t>TINT_ASH</t>
+        </is>
+      </c>
+      <c r="B28" s="81" t="n">
+        <v>23</v>
+      </c>
+      <c r="C28" s="81" t="inlineStr">
+        <is>
+          <t>Gun tint</t>
+        </is>
+      </c>
+      <c r="D28" s="81" t="inlineStr">
+        <is>
+          <t>Ash Tint</t>
+        </is>
+      </c>
+      <c r="E28" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F28" s="81" t="inlineStr">
+        <is>
+          <t>#B2B2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="81" t="inlineStr">
+        <is>
+          <t>TRACER_SKY</t>
+        </is>
+      </c>
+      <c r="B29" s="81" t="n">
+        <v>24</v>
+      </c>
+      <c r="C29" s="81" t="inlineStr">
+        <is>
+          <t>Tracer colour</t>
+        </is>
+      </c>
+      <c r="D29" s="81" t="inlineStr">
+        <is>
+          <t>Sky Tracers</t>
+        </is>
+      </c>
+      <c r="E29" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F29" s="81" t="inlineStr">
+        <is>
+          <t>#78B4E6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="81" t="inlineStr">
+        <is>
+          <t>SIGHT_ROSE</t>
+        </is>
+      </c>
+      <c r="B30" s="81" t="n">
+        <v>25</v>
+      </c>
+      <c r="C30" s="81" t="inlineStr">
+        <is>
+          <t>Crosshair colour</t>
+        </is>
+      </c>
+      <c r="D30" s="81" t="inlineStr">
+        <is>
+          <t>Rose Sights</t>
+        </is>
+      </c>
+      <c r="E30" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F30" s="81" t="inlineStr">
+        <is>
+          <t>#DC8296</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="81" t="inlineStr">
+        <is>
+          <t>FLAG_FERN</t>
+        </is>
+      </c>
+      <c r="B31" s="81" t="n">
+        <v>26</v>
+      </c>
+      <c r="C31" s="81" t="inlineStr">
+        <is>
+          <t>Tower flag</t>
+        </is>
+      </c>
+      <c r="D31" s="81" t="inlineStr">
+        <is>
+          <t>Fern Flag</t>
+        </is>
+      </c>
+      <c r="E31" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F31" s="81" t="inlineStr">
+        <is>
+          <t>#4F7942</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="81" t="inlineStr">
+        <is>
+          <t>BANNER_OCHRE</t>
+        </is>
+      </c>
+      <c r="B32" s="81" t="n">
+        <v>27</v>
+      </c>
+      <c r="C32" s="81" t="inlineStr">
+        <is>
+          <t>Leaderboard banner</t>
+        </is>
+      </c>
+      <c r="D32" s="81" t="inlineStr">
+        <is>
+          <t>Ochre Banner</t>
+        </is>
+      </c>
+      <c r="E32" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F32" s="81" t="inlineStr">
+        <is>
+          <t>#CC7722</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="81" t="inlineStr">
+        <is>
+          <t>NAME_RUST</t>
+        </is>
+      </c>
+      <c r="B33" s="81" t="n">
+        <v>28</v>
+      </c>
+      <c r="C33" s="81" t="inlineStr">
+        <is>
+          <t>Name colour</t>
+        </is>
+      </c>
+      <c r="D33" s="81" t="inlineStr">
+        <is>
+          <t>Rust Name</t>
+        </is>
+      </c>
+      <c r="E33" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F33" s="81" t="inlineStr">
+        <is>
+          <t>#A04828</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="81" t="inlineStr">
+        <is>
+          <t>TINT_SLATE</t>
+        </is>
+      </c>
+      <c r="B34" s="81" t="n">
+        <v>29</v>
+      </c>
+      <c r="C34" s="81" t="inlineStr">
+        <is>
+          <t>Gun tint</t>
+        </is>
+      </c>
+      <c r="D34" s="81" t="inlineStr">
+        <is>
+          <t>Slate Tint</t>
+        </is>
+      </c>
+      <c r="E34" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F34" s="81" t="inlineStr">
+        <is>
+          <t>#586373</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="81" t="inlineStr">
+        <is>
+          <t>MARK_TOOTH</t>
+        </is>
+      </c>
+      <c r="B35" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="C35" s="81" t="inlineStr">
+        <is>
+          <t>Hit-marker</t>
+        </is>
+      </c>
+      <c r="D35" s="81" t="inlineStr">
+        <is>
+          <t>Tooth Marker</t>
+        </is>
+      </c>
+      <c r="E35" s="81" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F35" s="81" t="inlineStr">
+        <is>
+          <t>#EBE1BE</t>
+        </is>
+      </c>
+      <c r="H35" s="81" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="81" t="inlineStr">
+        <is>
+          <t>TITLE_30</t>
+        </is>
+      </c>
+      <c r="B36" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="C36" s="81" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D36" s="81" t="inlineStr">
+        <is>
+          <t>Trapper</t>
+        </is>
+      </c>
+      <c r="E36" s="81" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="81" t="inlineStr">
+        <is>
+          <t>TRACER_DUSK</t>
+        </is>
+      </c>
+      <c r="B37" s="81" t="n">
+        <v>31</v>
+      </c>
+      <c r="C37" s="81" t="inlineStr">
+        <is>
+          <t>Tracer colour</t>
+        </is>
+      </c>
+      <c r="D37" s="81" t="inlineStr">
+        <is>
+          <t>Dusk Tracers</t>
+        </is>
+      </c>
+      <c r="E37" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F37" s="81" t="inlineStr">
+        <is>
+          <t>#62508C</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="81" t="inlineStr">
+        <is>
+          <t>SIGHT_EMBER</t>
+        </is>
+      </c>
+      <c r="B38" s="81" t="n">
+        <v>32</v>
+      </c>
+      <c r="C38" s="81" t="inlineStr">
+        <is>
+          <t>Crosshair colour</t>
+        </is>
+      </c>
+      <c r="D38" s="81" t="inlineStr">
+        <is>
+          <t>Ember Sights</t>
+        </is>
+      </c>
+      <c r="E38" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F38" s="81" t="inlineStr">
+        <is>
+          <t>#E65A32</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="81" t="inlineStr">
+        <is>
+          <t>FLAG_MOSS</t>
+        </is>
+      </c>
+      <c r="B39" s="81" t="n">
+        <v>33</v>
+      </c>
+      <c r="C39" s="81" t="inlineStr">
+        <is>
+          <t>Tower flag</t>
+        </is>
+      </c>
+      <c r="D39" s="81" t="inlineStr">
+        <is>
+          <t>Moss Flag</t>
+        </is>
+      </c>
+      <c r="E39" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F39" s="81" t="inlineStr">
+        <is>
+          <t>#8A9A5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="81" t="inlineStr">
+        <is>
+          <t>BANNER_RUST</t>
+        </is>
+      </c>
+      <c r="B40" s="81" t="n">
+        <v>34</v>
+      </c>
+      <c r="C40" s="81" t="inlineStr">
+        <is>
+          <t>Leaderboard banner</t>
+        </is>
+      </c>
+      <c r="D40" s="81" t="inlineStr">
+        <is>
+          <t>Rust Banner</t>
+        </is>
+      </c>
+      <c r="E40" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F40" s="81" t="inlineStr">
+        <is>
+          <t>#A04828</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="81" t="inlineStr">
+        <is>
+          <t>NAME_BONE</t>
+        </is>
+      </c>
+      <c r="B41" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="C41" s="81" t="inlineStr">
+        <is>
+          <t>Name colour</t>
+        </is>
+      </c>
+      <c r="D41" s="81" t="inlineStr">
+        <is>
+          <t>Bone Name</t>
+        </is>
+      </c>
+      <c r="E41" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F41" s="81" t="inlineStr">
+        <is>
+          <t>#E3DAC9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="81" t="inlineStr">
+        <is>
+          <t>TINT_TEAL</t>
+        </is>
+      </c>
+      <c r="B42" s="81" t="n">
+        <v>36</v>
+      </c>
+      <c r="C42" s="81" t="inlineStr">
+        <is>
+          <t>Gun tint</t>
+        </is>
+      </c>
+      <c r="D42" s="81" t="inlineStr">
+        <is>
+          <t>Teal Tint</t>
+        </is>
+      </c>
+      <c r="E42" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F42" s="81" t="inlineStr">
+        <is>
+          <t>#288080</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="81" t="inlineStr">
+        <is>
+          <t>TRACER_PLUM</t>
+        </is>
+      </c>
+      <c r="B43" s="81" t="n">
+        <v>37</v>
+      </c>
+      <c r="C43" s="81" t="inlineStr">
+        <is>
+          <t>Tracer colour</t>
+        </is>
+      </c>
+      <c r="D43" s="81" t="inlineStr">
+        <is>
+          <t>Plum Tracers</t>
+        </is>
+      </c>
+      <c r="E43" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F43" s="81" t="inlineStr">
+        <is>
+          <t>#823C64</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="81" t="inlineStr">
+        <is>
+          <t>SIGHT_SAND</t>
+        </is>
+      </c>
+      <c r="B44" s="81" t="n">
+        <v>38</v>
+      </c>
+      <c r="C44" s="81" t="inlineStr">
+        <is>
+          <t>Crosshair colour</t>
+        </is>
+      </c>
+      <c r="D44" s="81" t="inlineStr">
+        <is>
+          <t>Sand Sights</t>
+        </is>
+      </c>
+      <c r="E44" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F44" s="81" t="inlineStr">
+        <is>
+          <t>#C2B280</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="81" t="inlineStr">
+        <is>
+          <t>FLAG_CLAY</t>
+        </is>
+      </c>
+      <c r="B45" s="81" t="n">
+        <v>39</v>
+      </c>
+      <c r="C45" s="81" t="inlineStr">
+        <is>
+          <t>Tower flag</t>
+        </is>
+      </c>
+      <c r="D45" s="81" t="inlineStr">
+        <is>
+          <t>Clay Flag</t>
+        </is>
+      </c>
+      <c r="E45" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F45" s="81" t="inlineStr">
+        <is>
+          <t>#B0684A</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="81" t="inlineStr">
+        <is>
+          <t>TRAIL_DUST</t>
+        </is>
+      </c>
+      <c r="B46" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="C46" s="81" t="inlineStr">
+        <is>
+          <t>Sprint trail</t>
+        </is>
+      </c>
+      <c r="D46" s="81" t="inlineStr">
+        <is>
+          <t>Dust Trail</t>
+        </is>
+      </c>
+      <c r="E46" s="81" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F46" s="81" t="inlineStr">
+        <is>
+          <t>#C2A078</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="81" t="inlineStr">
+        <is>
+          <t>TITLE_40</t>
+        </is>
+      </c>
+      <c r="B47" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="C47" s="81" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D47" s="81" t="inlineStr">
+        <is>
+          <t>Ranger</t>
+        </is>
+      </c>
+      <c r="E47" s="81" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="81" t="inlineStr">
+        <is>
+          <t>BANNER_BONE</t>
+        </is>
+      </c>
+      <c r="B48" s="81" t="n">
+        <v>41</v>
+      </c>
+      <c r="C48" s="81" t="inlineStr">
+        <is>
+          <t>Leaderboard banner</t>
+        </is>
+      </c>
+      <c r="D48" s="81" t="inlineStr">
+        <is>
+          <t>Bone Banner</t>
+        </is>
+      </c>
+      <c r="E48" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F48" s="81" t="inlineStr">
+        <is>
+          <t>#E3DAC9</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="81" t="inlineStr">
+        <is>
+          <t>NAME_ASH</t>
+        </is>
+      </c>
+      <c r="B49" s="81" t="n">
+        <v>42</v>
+      </c>
+      <c r="C49" s="81" t="inlineStr">
+        <is>
+          <t>Name colour</t>
+        </is>
+      </c>
+      <c r="D49" s="81" t="inlineStr">
+        <is>
+          <t>Ash Name</t>
+        </is>
+      </c>
+      <c r="E49" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F49" s="81" t="inlineStr">
+        <is>
+          <t>#B2B2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="81" t="inlineStr">
+        <is>
+          <t>TINT_SKY</t>
+        </is>
+      </c>
+      <c r="B50" s="81" t="n">
+        <v>43</v>
+      </c>
+      <c r="C50" s="81" t="inlineStr">
+        <is>
+          <t>Gun tint</t>
+        </is>
+      </c>
+      <c r="D50" s="81" t="inlineStr">
+        <is>
+          <t>Sky Tint</t>
+        </is>
+      </c>
+      <c r="E50" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F50" s="81" t="inlineStr">
+        <is>
+          <t>#78B4E6</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="81" t="inlineStr">
+        <is>
+          <t>TRACER_ROSE</t>
+        </is>
+      </c>
+      <c r="B51" s="81" t="n">
+        <v>44</v>
+      </c>
+      <c r="C51" s="81" t="inlineStr">
+        <is>
+          <t>Tracer colour</t>
+        </is>
+      </c>
+      <c r="D51" s="81" t="inlineStr">
+        <is>
+          <t>Rose Tracers</t>
+        </is>
+      </c>
+      <c r="E51" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F51" s="81" t="inlineStr">
+        <is>
+          <t>#DC8296</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="81" t="inlineStr">
+        <is>
+          <t>SIGHT_FERN</t>
+        </is>
+      </c>
+      <c r="B52" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="C52" s="81" t="inlineStr">
+        <is>
+          <t>Crosshair colour</t>
+        </is>
+      </c>
+      <c r="D52" s="81" t="inlineStr">
+        <is>
+          <t>Fern Sights</t>
+        </is>
+      </c>
+      <c r="E52" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F52" s="81" t="inlineStr">
+        <is>
+          <t>#4F7942</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="81" t="inlineStr">
+        <is>
+          <t>FLAG_OCHRE</t>
+        </is>
+      </c>
+      <c r="B53" s="81" t="n">
+        <v>46</v>
+      </c>
+      <c r="C53" s="81" t="inlineStr">
+        <is>
+          <t>Tower flag</t>
+        </is>
+      </c>
+      <c r="D53" s="81" t="inlineStr">
+        <is>
+          <t>Ochre Flag</t>
+        </is>
+      </c>
+      <c r="E53" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F53" s="81" t="inlineStr">
+        <is>
+          <t>#CC7722</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="81" t="inlineStr">
+        <is>
+          <t>BANNER_ASH</t>
+        </is>
+      </c>
+      <c r="B54" s="81" t="n">
+        <v>47</v>
+      </c>
+      <c r="C54" s="81" t="inlineStr">
+        <is>
+          <t>Leaderboard banner</t>
+        </is>
+      </c>
+      <c r="D54" s="81" t="inlineStr">
+        <is>
+          <t>Ash Banner</t>
+        </is>
+      </c>
+      <c r="E54" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F54" s="81" t="inlineStr">
+        <is>
+          <t>#B2B2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="81" t="inlineStr">
+        <is>
+          <t>NAME_SLATE</t>
+        </is>
+      </c>
+      <c r="B55" s="81" t="n">
+        <v>48</v>
+      </c>
+      <c r="C55" s="81" t="inlineStr">
+        <is>
+          <t>Name colour</t>
+        </is>
+      </c>
+      <c r="D55" s="81" t="inlineStr">
+        <is>
+          <t>Slate Name</t>
+        </is>
+      </c>
+      <c r="E55" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F55" s="81" t="inlineStr">
+        <is>
+          <t>#586373</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="81" t="inlineStr">
+        <is>
+          <t>TINT_DUSK</t>
+        </is>
+      </c>
+      <c r="B56" s="81" t="n">
+        <v>49</v>
+      </c>
+      <c r="C56" s="81" t="inlineStr">
+        <is>
+          <t>Gun tint</t>
+        </is>
+      </c>
+      <c r="D56" s="81" t="inlineStr">
+        <is>
+          <t>Dusk Tint</t>
+        </is>
+      </c>
+      <c r="E56" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F56" s="81" t="inlineStr">
+        <is>
+          <t>#62508C</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="81" t="inlineStr">
+        <is>
+          <t>HAT_RANGER</t>
+        </is>
+      </c>
+      <c r="B57" s="81" t="n">
+        <v>50</v>
+      </c>
+      <c r="C57" s="81" t="inlineStr">
+        <is>
+          <t>Hunting hat</t>
+        </is>
+      </c>
+      <c r="D57" s="81" t="inlineStr">
+        <is>
+          <t>Ranger Cap</t>
+        </is>
+      </c>
+      <c r="E57" s="81" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F57" s="81" t="inlineStr">
+        <is>
+          <t>#963C32</t>
+        </is>
+      </c>
+      <c r="G57" s="81" t="inlineStr">
+        <is>
+          <t>Fabric</t>
+        </is>
+      </c>
+      <c r="H57" s="81" t="inlineStr">
+        <is>
+          <t>Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="81" t="inlineStr">
+        <is>
+          <t>TITLE_50</t>
+        </is>
+      </c>
+      <c r="B58" s="81" t="n">
+        <v>50</v>
+      </c>
+      <c r="C58" s="81" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D58" s="81" t="inlineStr">
+        <is>
+          <t>Trophy Hunter</t>
+        </is>
+      </c>
+      <c r="E58" s="81" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="81" t="inlineStr">
+        <is>
+          <t>TRACER_EMBER</t>
+        </is>
+      </c>
+      <c r="B59" s="81" t="n">
+        <v>51</v>
+      </c>
+      <c r="C59" s="81" t="inlineStr">
+        <is>
+          <t>Tracer colour</t>
+        </is>
+      </c>
+      <c r="D59" s="81" t="inlineStr">
+        <is>
+          <t>Ember Tracers</t>
+        </is>
+      </c>
+      <c r="E59" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F59" s="81" t="inlineStr">
+        <is>
+          <t>#E65A32</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="81" t="inlineStr">
+        <is>
+          <t>SIGHT_MOSS</t>
+        </is>
+      </c>
+      <c r="B60" s="81" t="n">
+        <v>52</v>
+      </c>
+      <c r="C60" s="81" t="inlineStr">
+        <is>
+          <t>Crosshair colour</t>
+        </is>
+      </c>
+      <c r="D60" s="81" t="inlineStr">
+        <is>
+          <t>Moss Sights</t>
+        </is>
+      </c>
+      <c r="E60" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F60" s="81" t="inlineStr">
+        <is>
+          <t>#8A9A5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="81" t="inlineStr">
+        <is>
+          <t>FLAG_RUST</t>
+        </is>
+      </c>
+      <c r="B61" s="81" t="n">
+        <v>53</v>
+      </c>
+      <c r="C61" s="81" t="inlineStr">
+        <is>
+          <t>Tower flag</t>
+        </is>
+      </c>
+      <c r="D61" s="81" t="inlineStr">
+        <is>
+          <t>Rust Flag</t>
+        </is>
+      </c>
+      <c r="E61" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F61" s="81" t="inlineStr">
+        <is>
+          <t>#A04828</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="81" t="inlineStr">
+        <is>
+          <t>BANNER_SLATE</t>
+        </is>
+      </c>
+      <c r="B62" s="81" t="n">
+        <v>54</v>
+      </c>
+      <c r="C62" s="81" t="inlineStr">
+        <is>
+          <t>Leaderboard banner</t>
+        </is>
+      </c>
+      <c r="D62" s="81" t="inlineStr">
+        <is>
+          <t>Slate Banner</t>
+        </is>
+      </c>
+      <c r="E62" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F62" s="81" t="inlineStr">
+        <is>
+          <t>#586373</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="81" t="inlineStr">
+        <is>
+          <t>NAME_TEAL</t>
+        </is>
+      </c>
+      <c r="B63" s="81" t="n">
+        <v>55</v>
+      </c>
+      <c r="C63" s="81" t="inlineStr">
+        <is>
+          <t>Name colour</t>
+        </is>
+      </c>
+      <c r="D63" s="81" t="inlineStr">
+        <is>
+          <t>Teal Name</t>
+        </is>
+      </c>
+      <c r="E63" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F63" s="81" t="inlineStr">
+        <is>
+          <t>#288080</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="81" t="inlineStr">
+        <is>
+          <t>TINT_PLUM</t>
+        </is>
+      </c>
+      <c r="B64" s="81" t="n">
+        <v>56</v>
+      </c>
+      <c r="C64" s="81" t="inlineStr">
+        <is>
+          <t>Gun tint</t>
+        </is>
+      </c>
+      <c r="D64" s="81" t="inlineStr">
+        <is>
+          <t>Plum Tint</t>
+        </is>
+      </c>
+      <c r="E64" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F64" s="81" t="inlineStr">
+        <is>
+          <t>#823C64</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="81" t="inlineStr">
+        <is>
+          <t>TRACER_SAND</t>
+        </is>
+      </c>
+      <c r="B65" s="81" t="n">
+        <v>57</v>
+      </c>
+      <c r="C65" s="81" t="inlineStr">
+        <is>
+          <t>Tracer colour</t>
+        </is>
+      </c>
+      <c r="D65" s="81" t="inlineStr">
+        <is>
+          <t>Sand Tracers</t>
+        </is>
+      </c>
+      <c r="E65" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F65" s="81" t="inlineStr">
+        <is>
+          <t>#C2B280</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="81" t="inlineStr">
+        <is>
+          <t>SIGHT_CLAY</t>
+        </is>
+      </c>
+      <c r="B66" s="81" t="n">
+        <v>58</v>
+      </c>
+      <c r="C66" s="81" t="inlineStr">
+        <is>
+          <t>Crosshair colour</t>
+        </is>
+      </c>
+      <c r="D66" s="81" t="inlineStr">
+        <is>
+          <t>Clay Sights</t>
+        </is>
+      </c>
+      <c r="E66" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F66" s="81" t="inlineStr">
+        <is>
+          <t>#B0684A</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="81" t="inlineStr">
+        <is>
+          <t>FLAG_BONE</t>
+        </is>
+      </c>
+      <c r="B67" s="81" t="n">
+        <v>59</v>
+      </c>
+      <c r="C67" s="81" t="inlineStr">
+        <is>
+          <t>Tower flag</t>
+        </is>
+      </c>
+      <c r="D67" s="81" t="inlineStr">
+        <is>
+          <t>Bone Flag</t>
+        </is>
+      </c>
+      <c r="E67" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F67" s="81" t="inlineStr">
+        <is>
+          <t>#E3DAC9</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="81" t="inlineStr">
+        <is>
+          <t>GUN_BONE</t>
+        </is>
+      </c>
+      <c r="B68" s="81" t="n">
+        <v>60</v>
+      </c>
+      <c r="C68" s="81" t="inlineStr">
+        <is>
+          <t>Gun pattern</t>
+        </is>
+      </c>
+      <c r="D68" s="81" t="inlineStr">
+        <is>
+          <t>Bone Inlay</t>
+        </is>
+      </c>
+      <c r="E68" s="81" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F68" s="81" t="inlineStr">
+        <is>
+          <t>#E6DECD</t>
+        </is>
+      </c>
+      <c r="G68" s="81" t="inlineStr">
+        <is>
+          <t>Marble</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="81" t="inlineStr">
+        <is>
+          <t>TITLE_60</t>
+        </is>
+      </c>
+      <c r="B69" s="81" t="n">
+        <v>60</v>
+      </c>
+      <c r="C69" s="81" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D69" s="81" t="inlineStr">
+        <is>
+          <t>Warden</t>
+        </is>
+      </c>
+      <c r="E69" s="81" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="81" t="inlineStr">
+        <is>
+          <t>BANNER_TEAL</t>
+        </is>
+      </c>
+      <c r="B70" s="81" t="n">
+        <v>61</v>
+      </c>
+      <c r="C70" s="81" t="inlineStr">
+        <is>
+          <t>Leaderboard banner</t>
+        </is>
+      </c>
+      <c r="D70" s="81" t="inlineStr">
+        <is>
+          <t>Teal Banner</t>
+        </is>
+      </c>
+      <c r="E70" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F70" s="81" t="inlineStr">
+        <is>
+          <t>#288080</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="81" t="inlineStr">
+        <is>
+          <t>NAME_SKY</t>
+        </is>
+      </c>
+      <c r="B71" s="81" t="n">
+        <v>62</v>
+      </c>
+      <c r="C71" s="81" t="inlineStr">
+        <is>
+          <t>Name colour</t>
+        </is>
+      </c>
+      <c r="D71" s="81" t="inlineStr">
+        <is>
+          <t>Sky Name</t>
+        </is>
+      </c>
+      <c r="E71" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F71" s="81" t="inlineStr">
+        <is>
+          <t>#78B4E6</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="81" t="inlineStr">
+        <is>
+          <t>TINT_ROSE</t>
+        </is>
+      </c>
+      <c r="B72" s="81" t="n">
+        <v>63</v>
+      </c>
+      <c r="C72" s="81" t="inlineStr">
+        <is>
+          <t>Gun tint</t>
+        </is>
+      </c>
+      <c r="D72" s="81" t="inlineStr">
+        <is>
+          <t>Rose Tint</t>
+        </is>
+      </c>
+      <c r="E72" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F72" s="81" t="inlineStr">
+        <is>
+          <t>#DC8296</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="81" t="inlineStr">
+        <is>
+          <t>TRACER_FERN</t>
+        </is>
+      </c>
+      <c r="B73" s="81" t="n">
+        <v>64</v>
+      </c>
+      <c r="C73" s="81" t="inlineStr">
+        <is>
+          <t>Tracer colour</t>
+        </is>
+      </c>
+      <c r="D73" s="81" t="inlineStr">
+        <is>
+          <t>Fern Tracers</t>
+        </is>
+      </c>
+      <c r="E73" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F73" s="81" t="inlineStr">
+        <is>
+          <t>#4F7942</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="81" t="inlineStr">
+        <is>
+          <t>SIGHT_OCHRE</t>
+        </is>
+      </c>
+      <c r="B74" s="81" t="n">
+        <v>65</v>
+      </c>
+      <c r="C74" s="81" t="inlineStr">
+        <is>
+          <t>Crosshair colour</t>
+        </is>
+      </c>
+      <c r="D74" s="81" t="inlineStr">
+        <is>
+          <t>Ochre Sights</t>
+        </is>
+      </c>
+      <c r="E74" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F74" s="81" t="inlineStr">
+        <is>
+          <t>#CC7722</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="81" t="inlineStr">
+        <is>
+          <t>FLAG_ASH</t>
+        </is>
+      </c>
+      <c r="B75" s="81" t="n">
+        <v>66</v>
+      </c>
+      <c r="C75" s="81" t="inlineStr">
+        <is>
+          <t>Tower flag</t>
+        </is>
+      </c>
+      <c r="D75" s="81" t="inlineStr">
+        <is>
+          <t>Ash Flag</t>
+        </is>
+      </c>
+      <c r="E75" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F75" s="81" t="inlineStr">
+        <is>
+          <t>#B2B2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="81" t="inlineStr">
+        <is>
+          <t>BANNER_SKY</t>
+        </is>
+      </c>
+      <c r="B76" s="81" t="n">
+        <v>67</v>
+      </c>
+      <c r="C76" s="81" t="inlineStr">
+        <is>
+          <t>Leaderboard banner</t>
+        </is>
+      </c>
+      <c r="D76" s="81" t="inlineStr">
+        <is>
+          <t>Sky Banner</t>
+        </is>
+      </c>
+      <c r="E76" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F76" s="81" t="inlineStr">
+        <is>
+          <t>#78B4E6</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="81" t="inlineStr">
+        <is>
+          <t>NAME_DUSK</t>
+        </is>
+      </c>
+      <c r="B77" s="81" t="n">
+        <v>68</v>
+      </c>
+      <c r="C77" s="81" t="inlineStr">
+        <is>
+          <t>Name colour</t>
+        </is>
+      </c>
+      <c r="D77" s="81" t="inlineStr">
+        <is>
+          <t>Dusk Name</t>
+        </is>
+      </c>
+      <c r="E77" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F77" s="81" t="inlineStr">
+        <is>
+          <t>#62508C</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="81" t="inlineStr">
+        <is>
+          <t>TINT_EMBER</t>
+        </is>
+      </c>
+      <c r="B78" s="81" t="n">
+        <v>69</v>
+      </c>
+      <c r="C78" s="81" t="inlineStr">
+        <is>
+          <t>Gun tint</t>
+        </is>
+      </c>
+      <c r="D78" s="81" t="inlineStr">
+        <is>
+          <t>Ember Tint</t>
+        </is>
+      </c>
+      <c r="E78" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F78" s="81" t="inlineStr">
+        <is>
+          <t>#E65A32</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="81" t="inlineStr">
+        <is>
+          <t>MARK_STAR</t>
+        </is>
+      </c>
+      <c r="B79" s="81" t="n">
+        <v>70</v>
+      </c>
+      <c r="C79" s="81" t="inlineStr">
+        <is>
+          <t>Hit-marker</t>
+        </is>
+      </c>
+      <c r="D79" s="81" t="inlineStr">
+        <is>
+          <t>Star Marker</t>
+        </is>
+      </c>
+      <c r="E79" s="81" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F79" s="81" t="inlineStr">
+        <is>
+          <t>#78C8F0</t>
+        </is>
+      </c>
+      <c r="H79" s="81" t="inlineStr">
+        <is>
+          <t>Star</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="81" t="inlineStr">
+        <is>
+          <t>TITLE_70</t>
+        </is>
+      </c>
+      <c r="B80" s="81" t="n">
+        <v>70</v>
+      </c>
+      <c r="C80" s="81" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D80" s="81" t="inlineStr">
+        <is>
+          <t>Pathfinder</t>
+        </is>
+      </c>
+      <c r="E80" s="81" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="81" t="inlineStr">
+        <is>
+          <t>TRACER_MOSS</t>
+        </is>
+      </c>
+      <c r="B81" s="81" t="n">
+        <v>71</v>
+      </c>
+      <c r="C81" s="81" t="inlineStr">
+        <is>
+          <t>Tracer colour</t>
+        </is>
+      </c>
+      <c r="D81" s="81" t="inlineStr">
+        <is>
+          <t>Moss Tracers</t>
+        </is>
+      </c>
+      <c r="E81" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F81" s="81" t="inlineStr">
+        <is>
+          <t>#8A9A5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="81" t="inlineStr">
+        <is>
+          <t>SIGHT_RUST</t>
+        </is>
+      </c>
+      <c r="B82" s="81" t="n">
+        <v>72</v>
+      </c>
+      <c r="C82" s="81" t="inlineStr">
+        <is>
+          <t>Crosshair colour</t>
+        </is>
+      </c>
+      <c r="D82" s="81" t="inlineStr">
+        <is>
+          <t>Rust Sights</t>
+        </is>
+      </c>
+      <c r="E82" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F82" s="81" t="inlineStr">
+        <is>
+          <t>#A04828</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="81" t="inlineStr">
+        <is>
+          <t>FLAG_SLATE</t>
+        </is>
+      </c>
+      <c r="B83" s="81" t="n">
+        <v>73</v>
+      </c>
+      <c r="C83" s="81" t="inlineStr">
+        <is>
+          <t>Tower flag</t>
+        </is>
+      </c>
+      <c r="D83" s="81" t="inlineStr">
+        <is>
+          <t>Slate Flag</t>
+        </is>
+      </c>
+      <c r="E83" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F83" s="81" t="inlineStr">
+        <is>
+          <t>#586373</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="81" t="inlineStr">
+        <is>
+          <t>BANNER_DUSK</t>
+        </is>
+      </c>
+      <c r="B84" s="81" t="n">
+        <v>74</v>
+      </c>
+      <c r="C84" s="81" t="inlineStr">
+        <is>
+          <t>Leaderboard banner</t>
+        </is>
+      </c>
+      <c r="D84" s="81" t="inlineStr">
+        <is>
+          <t>Dusk Banner</t>
+        </is>
+      </c>
+      <c r="E84" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F84" s="81" t="inlineStr">
+        <is>
+          <t>#62508C</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="81" t="inlineStr">
+        <is>
+          <t>NAME_PLUM</t>
+        </is>
+      </c>
+      <c r="B85" s="81" t="n">
+        <v>75</v>
+      </c>
+      <c r="C85" s="81" t="inlineStr">
+        <is>
+          <t>Name colour</t>
+        </is>
+      </c>
+      <c r="D85" s="81" t="inlineStr">
+        <is>
+          <t>Plum Name</t>
+        </is>
+      </c>
+      <c r="E85" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F85" s="81" t="inlineStr">
+        <is>
+          <t>#823C64</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="81" t="inlineStr">
+        <is>
+          <t>TINT_SAND</t>
+        </is>
+      </c>
+      <c r="B86" s="81" t="n">
+        <v>76</v>
+      </c>
+      <c r="C86" s="81" t="inlineStr">
+        <is>
+          <t>Gun tint</t>
+        </is>
+      </c>
+      <c r="D86" s="81" t="inlineStr">
+        <is>
+          <t>Sand Tint</t>
+        </is>
+      </c>
+      <c r="E86" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F86" s="81" t="inlineStr">
+        <is>
+          <t>#C2B280</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="81" t="inlineStr">
+        <is>
+          <t>TRACER_CLAY</t>
+        </is>
+      </c>
+      <c r="B87" s="81" t="n">
+        <v>77</v>
+      </c>
+      <c r="C87" s="81" t="inlineStr">
+        <is>
+          <t>Tracer colour</t>
+        </is>
+      </c>
+      <c r="D87" s="81" t="inlineStr">
+        <is>
+          <t>Clay Tracers</t>
+        </is>
+      </c>
+      <c r="E87" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F87" s="81" t="inlineStr">
+        <is>
+          <t>#B0684A</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="81" t="inlineStr">
+        <is>
+          <t>SIGHT_BONE</t>
+        </is>
+      </c>
+      <c r="B88" s="81" t="n">
+        <v>78</v>
+      </c>
+      <c r="C88" s="81" t="inlineStr">
+        <is>
+          <t>Crosshair colour</t>
+        </is>
+      </c>
+      <c r="D88" s="81" t="inlineStr">
+        <is>
+          <t>Bone Sights</t>
+        </is>
+      </c>
+      <c r="E88" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F88" s="81" t="inlineStr">
+        <is>
+          <t>#E3DAC9</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="81" t="inlineStr">
+        <is>
+          <t>FLAG_TEAL</t>
+        </is>
+      </c>
+      <c r="B89" s="81" t="n">
+        <v>79</v>
+      </c>
+      <c r="C89" s="81" t="inlineStr">
+        <is>
+          <t>Tower flag</t>
+        </is>
+      </c>
+      <c r="D89" s="81" t="inlineStr">
+        <is>
+          <t>Teal Flag</t>
+        </is>
+      </c>
+      <c r="E89" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F89" s="81" t="inlineStr">
+        <is>
+          <t>#288080</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="81" t="inlineStr">
+        <is>
+          <t>TRAIL_FERN</t>
+        </is>
+      </c>
+      <c r="B90" s="81" t="n">
+        <v>80</v>
+      </c>
+      <c r="C90" s="81" t="inlineStr">
+        <is>
+          <t>Sprint trail</t>
+        </is>
+      </c>
+      <c r="D90" s="81" t="inlineStr">
+        <is>
+          <t>Fern Trail</t>
+        </is>
+      </c>
+      <c r="E90" s="81" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F90" s="81" t="inlineStr">
+        <is>
+          <t>#64AA5A</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="81" t="inlineStr">
+        <is>
+          <t>TITLE_80</t>
+        </is>
+      </c>
+      <c r="B91" s="81" t="n">
+        <v>80</v>
+      </c>
+      <c r="C91" s="81" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D91" s="81" t="inlineStr">
+        <is>
+          <t>Raptor Bane</t>
+        </is>
+      </c>
+      <c r="E91" s="81" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="81" t="inlineStr">
+        <is>
+          <t>BANNER_PLUM</t>
+        </is>
+      </c>
+      <c r="B92" s="81" t="n">
+        <v>81</v>
+      </c>
+      <c r="C92" s="81" t="inlineStr">
+        <is>
+          <t>Leaderboard banner</t>
+        </is>
+      </c>
+      <c r="D92" s="81" t="inlineStr">
+        <is>
+          <t>Plum Banner</t>
+        </is>
+      </c>
+      <c r="E92" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F92" s="81" t="inlineStr">
+        <is>
+          <t>#823C64</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="81" t="inlineStr">
+        <is>
+          <t>NAME_ROSE</t>
+        </is>
+      </c>
+      <c r="B93" s="81" t="n">
+        <v>82</v>
+      </c>
+      <c r="C93" s="81" t="inlineStr">
+        <is>
+          <t>Name colour</t>
+        </is>
+      </c>
+      <c r="D93" s="81" t="inlineStr">
+        <is>
+          <t>Rose Name</t>
+        </is>
+      </c>
+      <c r="E93" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F93" s="81" t="inlineStr">
+        <is>
+          <t>#DC8296</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="81" t="inlineStr">
+        <is>
+          <t>TINT_FERN</t>
+        </is>
+      </c>
+      <c r="B94" s="81" t="n">
+        <v>83</v>
+      </c>
+      <c r="C94" s="81" t="inlineStr">
+        <is>
+          <t>Gun tint</t>
+        </is>
+      </c>
+      <c r="D94" s="81" t="inlineStr">
+        <is>
+          <t>Fern Tint</t>
+        </is>
+      </c>
+      <c r="E94" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F94" s="81" t="inlineStr">
+        <is>
+          <t>#4F7942</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="81" t="inlineStr">
+        <is>
+          <t>TRACER_OCHRE</t>
+        </is>
+      </c>
+      <c r="B95" s="81" t="n">
+        <v>84</v>
+      </c>
+      <c r="C95" s="81" t="inlineStr">
+        <is>
+          <t>Tracer colour</t>
+        </is>
+      </c>
+      <c r="D95" s="81" t="inlineStr">
+        <is>
+          <t>Ochre Tracers</t>
+        </is>
+      </c>
+      <c r="E95" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F95" s="81" t="inlineStr">
+        <is>
+          <t>#CC7722</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="81" t="inlineStr">
+        <is>
+          <t>SIGHT_ASH</t>
+        </is>
+      </c>
+      <c r="B96" s="81" t="n">
+        <v>85</v>
+      </c>
+      <c r="C96" s="81" t="inlineStr">
+        <is>
+          <t>Crosshair colour</t>
+        </is>
+      </c>
+      <c r="D96" s="81" t="inlineStr">
+        <is>
+          <t>Ash Sights</t>
+        </is>
+      </c>
+      <c r="E96" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F96" s="81" t="inlineStr">
+        <is>
+          <t>#B2B2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="81" t="inlineStr">
+        <is>
+          <t>FLAG_SKY</t>
+        </is>
+      </c>
+      <c r="B97" s="81" t="n">
+        <v>86</v>
+      </c>
+      <c r="C97" s="81" t="inlineStr">
+        <is>
+          <t>Tower flag</t>
+        </is>
+      </c>
+      <c r="D97" s="81" t="inlineStr">
+        <is>
+          <t>Sky Flag</t>
+        </is>
+      </c>
+      <c r="E97" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F97" s="81" t="inlineStr">
+        <is>
+          <t>#78B4E6</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="81" t="inlineStr">
+        <is>
+          <t>BANNER_ROSE</t>
+        </is>
+      </c>
+      <c r="B98" s="81" t="n">
+        <v>87</v>
+      </c>
+      <c r="C98" s="81" t="inlineStr">
+        <is>
+          <t>Leaderboard banner</t>
+        </is>
+      </c>
+      <c r="D98" s="81" t="inlineStr">
+        <is>
+          <t>Rose Banner</t>
+        </is>
+      </c>
+      <c r="E98" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F98" s="81" t="inlineStr">
+        <is>
+          <t>#DC8296</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="81" t="inlineStr">
+        <is>
+          <t>NAME_EMBER</t>
+        </is>
+      </c>
+      <c r="B99" s="81" t="n">
+        <v>88</v>
+      </c>
+      <c r="C99" s="81" t="inlineStr">
+        <is>
+          <t>Name colour</t>
+        </is>
+      </c>
+      <c r="D99" s="81" t="inlineStr">
+        <is>
+          <t>Ember Name</t>
+        </is>
+      </c>
+      <c r="E99" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F99" s="81" t="inlineStr">
+        <is>
+          <t>#E65A32</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="81" t="inlineStr">
+        <is>
+          <t>TINT_MOSS</t>
+        </is>
+      </c>
+      <c r="B100" s="81" t="n">
+        <v>89</v>
+      </c>
+      <c r="C100" s="81" t="inlineStr">
+        <is>
+          <t>Gun tint</t>
+        </is>
+      </c>
+      <c r="D100" s="81" t="inlineStr">
+        <is>
+          <t>Moss Tint</t>
+        </is>
+      </c>
+      <c r="E100" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F100" s="81" t="inlineStr">
+        <is>
+          <t>#8A9A5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="81" t="inlineStr">
+        <is>
+          <t>HAT_CREST</t>
+        </is>
+      </c>
+      <c r="B101" s="81" t="n">
+        <v>90</v>
+      </c>
+      <c r="C101" s="81" t="inlineStr">
+        <is>
+          <t>Hunting hat</t>
+        </is>
+      </c>
+      <c r="D101" s="81" t="inlineStr">
+        <is>
+          <t>Crest Helm</t>
+        </is>
+      </c>
+      <c r="E101" s="81" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F101" s="81" t="inlineStr">
+        <is>
+          <t>#6E737D</t>
+        </is>
+      </c>
+      <c r="G101" s="81" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="H101" s="81" t="inlineStr">
+        <is>
+          <t>Crest</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="81" t="inlineStr">
+        <is>
+          <t>TITLE_90</t>
+        </is>
+      </c>
+      <c r="B102" s="81" t="n">
+        <v>90</v>
+      </c>
+      <c r="C102" s="81" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D102" s="81" t="inlineStr">
+        <is>
+          <t>Rex Wrangler</t>
+        </is>
+      </c>
+      <c r="E102" s="81" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="81" t="inlineStr">
+        <is>
+          <t>TRACER_RUST</t>
+        </is>
+      </c>
+      <c r="B103" s="81" t="n">
+        <v>91</v>
+      </c>
+      <c r="C103" s="81" t="inlineStr">
+        <is>
+          <t>Tracer colour</t>
+        </is>
+      </c>
+      <c r="D103" s="81" t="inlineStr">
+        <is>
+          <t>Rust Tracers</t>
+        </is>
+      </c>
+      <c r="E103" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F103" s="81" t="inlineStr">
+        <is>
+          <t>#A04828</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="81" t="inlineStr">
+        <is>
+          <t>SIGHT_SLATE</t>
+        </is>
+      </c>
+      <c r="B104" s="81" t="n">
+        <v>92</v>
+      </c>
+      <c r="C104" s="81" t="inlineStr">
+        <is>
+          <t>Crosshair colour</t>
+        </is>
+      </c>
+      <c r="D104" s="81" t="inlineStr">
+        <is>
+          <t>Slate Sights</t>
+        </is>
+      </c>
+      <c r="E104" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F104" s="81" t="inlineStr">
+        <is>
+          <t>#586373</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="81" t="inlineStr">
+        <is>
+          <t>FLAG_DUSK</t>
+        </is>
+      </c>
+      <c r="B105" s="81" t="n">
+        <v>93</v>
+      </c>
+      <c r="C105" s="81" t="inlineStr">
+        <is>
+          <t>Tower flag</t>
+        </is>
+      </c>
+      <c r="D105" s="81" t="inlineStr">
+        <is>
+          <t>Dusk Flag</t>
+        </is>
+      </c>
+      <c r="E105" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F105" s="81" t="inlineStr">
+        <is>
+          <t>#62508C</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="81" t="inlineStr">
+        <is>
+          <t>BANNER_EMBER</t>
+        </is>
+      </c>
+      <c r="B106" s="81" t="n">
+        <v>94</v>
+      </c>
+      <c r="C106" s="81" t="inlineStr">
+        <is>
+          <t>Leaderboard banner</t>
+        </is>
+      </c>
+      <c r="D106" s="81" t="inlineStr">
+        <is>
+          <t>Ember Banner</t>
+        </is>
+      </c>
+      <c r="E106" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F106" s="81" t="inlineStr">
+        <is>
+          <t>#E65A32</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="81" t="inlineStr">
+        <is>
+          <t>NAME_SAND</t>
+        </is>
+      </c>
+      <c r="B107" s="81" t="n">
+        <v>95</v>
+      </c>
+      <c r="C107" s="81" t="inlineStr">
+        <is>
+          <t>Name colour</t>
+        </is>
+      </c>
+      <c r="D107" s="81" t="inlineStr">
+        <is>
+          <t>Sand Name</t>
+        </is>
+      </c>
+      <c r="E107" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F107" s="81" t="inlineStr">
+        <is>
+          <t>#C2B280</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="81" t="inlineStr">
+        <is>
+          <t>TINT_CLAY</t>
+        </is>
+      </c>
+      <c r="B108" s="81" t="n">
+        <v>96</v>
+      </c>
+      <c r="C108" s="81" t="inlineStr">
+        <is>
+          <t>Gun tint</t>
+        </is>
+      </c>
+      <c r="D108" s="81" t="inlineStr">
+        <is>
+          <t>Clay Tint</t>
+        </is>
+      </c>
+      <c r="E108" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F108" s="81" t="inlineStr">
+        <is>
+          <t>#B0684A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="81" t="inlineStr">
+        <is>
+          <t>TRACER_BONE</t>
+        </is>
+      </c>
+      <c r="B109" s="81" t="n">
+        <v>97</v>
+      </c>
+      <c r="C109" s="81" t="inlineStr">
+        <is>
+          <t>Tracer colour</t>
+        </is>
+      </c>
+      <c r="D109" s="81" t="inlineStr">
+        <is>
+          <t>Bone Tracers</t>
+        </is>
+      </c>
+      <c r="E109" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F109" s="81" t="inlineStr">
+        <is>
+          <t>#E3DAC9</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="81" t="inlineStr">
+        <is>
+          <t>SIGHT_TEAL</t>
+        </is>
+      </c>
+      <c r="B110" s="81" t="n">
+        <v>98</v>
+      </c>
+      <c r="C110" s="81" t="inlineStr">
+        <is>
+          <t>Crosshair colour</t>
+        </is>
+      </c>
+      <c r="D110" s="81" t="inlineStr">
+        <is>
+          <t>Teal Sights</t>
+        </is>
+      </c>
+      <c r="E110" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F110" s="81" t="inlineStr">
+        <is>
+          <t>#288080</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="81" t="inlineStr">
+        <is>
+          <t>FLAG_PLUM</t>
+        </is>
+      </c>
+      <c r="B111" s="81" t="n">
+        <v>99</v>
+      </c>
+      <c r="C111" s="81" t="inlineStr">
+        <is>
+          <t>Tower flag</t>
+        </is>
+      </c>
+      <c r="D111" s="81" t="inlineStr">
+        <is>
+          <t>Plum Flag</t>
+        </is>
+      </c>
+      <c r="E111" s="81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F111" s="81" t="inlineStr">
+        <is>
+          <t>#823C64</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="81" t="inlineStr">
+        <is>
+          <t>GUN_SCALE</t>
+        </is>
+      </c>
+      <c r="B112" s="81" t="n">
+        <v>100</v>
+      </c>
+      <c r="C112" s="81" t="inlineStr">
+        <is>
+          <t>Gun pattern</t>
+        </is>
+      </c>
+      <c r="D112" s="81" t="inlineStr">
+        <is>
+          <t>Raptor Scale</t>
+        </is>
+      </c>
+      <c r="E112" s="81" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F112" s="81" t="inlineStr">
+        <is>
+          <t>#3C6E5A</t>
+        </is>
+      </c>
+      <c r="G112" s="81" t="inlineStr">
+        <is>
+          <t>Slate</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="81" t="inlineStr">
+        <is>
+          <t>TITLE_100</t>
+        </is>
+      </c>
+      <c r="B113" s="81" t="n">
+        <v>100</v>
+      </c>
+      <c r="C113" s="81" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D113" s="81" t="inlineStr">
+        <is>
+          <t>Apex Hunter</t>
+        </is>
+      </c>
+      <c r="E113" s="81" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="81" t="inlineStr">
+        <is>
+          <t>SET_TARPIT</t>
+        </is>
+      </c>
+      <c r="B114" s="81" t="n">
+        <v>150</v>
+      </c>
+      <c r="C114" s="81" t="inlineStr">
+        <is>
+          <t>Animated set</t>
+        </is>
+      </c>
+      <c r="D114" s="81" t="inlineStr">
+        <is>
+          <t>Tar Pit Set</t>
+        </is>
+      </c>
+      <c r="E114" s="81" t="inlineStr">
+        <is>
+          <t>legendary</t>
+        </is>
+      </c>
+      <c r="F114" s="81" t="inlineStr">
+        <is>
+          <t>#281E32</t>
+        </is>
+      </c>
+      <c r="G114" s="81" t="inlineStr">
+        <is>
+          <t>Foil</t>
+        </is>
+      </c>
+      <c r="H114" s="81" t="inlineStr">
+        <is>
+          <t>Pulse</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="81" t="inlineStr">
+        <is>
+          <t>TITLE_150</t>
+        </is>
+      </c>
+      <c r="B115" s="81" t="n">
+        <v>150</v>
+      </c>
+      <c r="C115" s="81" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D115" s="81" t="inlineStr">
+        <is>
+          <t>Fossil Legend</t>
+        </is>
+      </c>
+      <c r="E115" s="81" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="81" t="inlineStr">
+        <is>
+          <t>SET_METEOR</t>
+        </is>
+      </c>
+      <c r="B116" s="81" t="n">
+        <v>200</v>
+      </c>
+      <c r="C116" s="81" t="inlineStr">
+        <is>
+          <t>Animated set</t>
+        </is>
+      </c>
+      <c r="D116" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Set</t>
+        </is>
+      </c>
+      <c r="E116" s="81" t="inlineStr">
+        <is>
+          <t>legendary</t>
+        </is>
+      </c>
+      <c r="F116" s="81" t="inlineStr">
+        <is>
+          <t>#FF6E28</t>
+        </is>
+      </c>
+      <c r="G116" s="81" t="inlineStr">
+        <is>
+          <t>Glass</t>
+        </is>
+      </c>
+      <c r="H116" s="81" t="inlineStr">
+        <is>
+          <t>Cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="81" t="inlineStr">
+        <is>
+          <t>TITLE_200</t>
+        </is>
+      </c>
+      <c r="B117" s="81" t="n">
+        <v>200</v>
+      </c>
+      <c r="C117" s="81" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D117" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Hunter</t>
+        </is>
+      </c>
+      <c r="E117" s="81" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="81" t="inlineStr">
+        <is>
+          <t>TITLE_ELDER</t>
+        </is>
+      </c>
+      <c r="B118" s="81" t="n">
+        <v>250</v>
+      </c>
+      <c r="C118" s="81" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D118" s="81" t="inlineStr">
+        <is>
+          <t>Elder Hunter {n}</t>
+        </is>
+      </c>
+      <c r="E118" s="81" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I118" s="81" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9319,7 +9319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -11022,6 +11022,280 @@
         </is>
       </c>
     </row>
+    <row r="109"/>
+    <row r="110">
+      <c r="A110" s="99" t="inlineStr">
+        <is>
+          <t>STORM COIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="100" t="inlineStr">
+        <is>
+          <t>Coil arcs</t>
+        </is>
+      </c>
+      <c r="B111" s="101" t="n">
+        <v>4</v>
+      </c>
+      <c r="C111" s="102" t="inlineStr">
+        <is>
+          <t>arcs after the first hit (Copper Wire raises it)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="100" t="inlineStr">
+        <is>
+          <t>Coil arc reach</t>
+        </is>
+      </c>
+      <c r="B112" s="101" t="n">
+        <v>10</v>
+      </c>
+      <c r="C112" s="102" t="inlineStr">
+        <is>
+          <t>studs from one dino to the next</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="100" t="inlineStr">
+        <is>
+          <t>Coil arc falloff</t>
+        </is>
+      </c>
+      <c r="B113" s="101" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C113" s="102" t="inlineStr">
+        <is>
+          <t>each arc x this of the last</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="100" t="inlineStr">
+        <is>
+          <t>Power Grid range per coil</t>
+        </is>
+      </c>
+      <c r="B114" s="101" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C114" s="102" t="inlineStr">
+        <is>
+          <t>range x (1 + this x (n - 1)), DECISIONS #151</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="100" t="inlineStr">
+        <is>
+          <t>Power Grid damage base</t>
+        </is>
+      </c>
+      <c r="B115" s="101" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C115" s="102" t="inlineStr">
+        <is>
+          <t>damage x (base + per coil x n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="100" t="inlineStr">
+        <is>
+          <t>Power Grid damage per coil</t>
+        </is>
+      </c>
+      <c r="B116" s="101" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="100" t="inlineStr">
+        <is>
+          <t>Power Grid coil cap</t>
+        </is>
+      </c>
+      <c r="B117" s="101" t="n">
+        <v>6</v>
+      </c>
+      <c r="C117" s="102" t="inlineStr">
+        <is>
+          <t>n counted up to this</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="100" t="inlineStr">
+        <is>
+          <t>Power Grid every</t>
+        </is>
+      </c>
+      <c r="B118" s="101" t="n">
+        <v>6</v>
+      </c>
+      <c r="C118" s="102" t="inlineStr">
+        <is>
+          <t>s, one shared grid strike</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="100" t="inlineStr">
+        <is>
+          <t>Judgement Bolt every</t>
+        </is>
+      </c>
+      <c r="B119" s="101" t="n">
+        <v>10</v>
+      </c>
+      <c r="C119" s="102" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="100" t="inlineStr">
+        <is>
+          <t>Judgement Bolt x</t>
+        </is>
+      </c>
+      <c r="B120" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="C120" s="102" t="inlineStr">
+        <is>
+          <t>x the coil damage, biggest dino in range</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="100" t="inlineStr">
+        <is>
+          <t>Judgement Bolt breaks</t>
+        </is>
+      </c>
+      <c r="B121" s="101" t="n">
+        <v>3</v>
+      </c>
+      <c r="C121" s="102" t="inlineStr">
+        <is>
+          <t>sizes (pierce-through)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="100" t="inlineStr">
+        <is>
+          <t>Judgement Bolt stun</t>
+        </is>
+      </c>
+      <c r="B122" s="101" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C122" s="102" t="inlineStr">
+        <is>
+          <t>s, bosses too</t>
+        </is>
+      </c>
+    </row>
+    <row r="123"/>
+    <row r="124">
+      <c r="A124" s="99" t="inlineStr">
+        <is>
+          <t>FALCON ROOST</t>
+        </is>
+      </c>
+      <c r="C124" s="102" t="inlineStr">
+        <is>
+          <t>levers land with PLAN T65</t>
+        </is>
+      </c>
+    </row>
+    <row r="125"/>
+    <row r="126">
+      <c r="A126" s="99" t="inlineStr">
+        <is>
+          <t>TAR PIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="100" t="inlineStr">
+        <is>
+          <t>Eruption every</t>
+        </is>
+      </c>
+      <c r="B127" s="101" t="n">
+        <v>10</v>
+      </c>
+      <c r="C127" s="102" t="inlineStr">
+        <is>
+          <t>s, DECISIONS #150</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="100" t="inlineStr">
+        <is>
+          <t>Eruption sizes</t>
+        </is>
+      </c>
+      <c r="B128" s="101" t="n">
+        <v>2</v>
+      </c>
+      <c r="C128" s="102" t="inlineStr">
+        <is>
+          <t>sizes dropped outright, Break resist ignored</t>
+        </is>
+      </c>
+    </row>
+    <row r="129"/>
+    <row r="130">
+      <c r="A130" s="99" t="inlineStr">
+        <is>
+          <t>HARPOON BALLISTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="100" t="inlineStr">
+        <is>
+          <t>Tow Line every</t>
+        </is>
+      </c>
+      <c r="B131" s="101" t="n">
+        <v>15</v>
+      </c>
+      <c r="C131" s="102" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="100" t="inlineStr">
+        <is>
+          <t>Tow Line pull</t>
+        </is>
+      </c>
+      <c r="B132" s="101" t="n">
+        <v>10</v>
+      </c>
+      <c r="C132" s="102" t="inlineStr">
+        <is>
+          <t>studs back along the track (bosses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133"/>
+    <row r="134"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -11042,7 +11316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -11210,6 +11484,16 @@
           <t>Upgrade cost growth</t>
         </is>
       </c>
+      <c r="T4" s="21" t="inlineStr">
+        <is>
+          <t>Untouchable</t>
+        </is>
+      </c>
+      <c r="U4" s="21" t="inlineStr">
+        <is>
+          <t>On track</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -11698,6 +11982,290 @@
         <is>
           <t>Cash needed to buy 1 DPS at tier 0. Balance Check uses this.</t>
         </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>Chain lightning: crowds and air</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="n">
+        <v>550</v>
+      </c>
+      <c r="D15" s="91" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="92">
+        <f>D15*E15*F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="I15" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="47" t="inlineStr">
+        <is>
+          <t>Each strike arcs from dino to dino (falloff per arc, breaks 1). Short own range. TOWERS_NEXT.md.</t>
+        </is>
+      </c>
+      <c r="L15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="O15" s="43" t="inlineStr">
+        <is>
+          <t>COIL</t>
+        </is>
+      </c>
+      <c r="P15" s="27" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>Birds of prey: huge radius, can't be damaged</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="n">
+        <v>400</v>
+      </c>
+      <c r="D16" s="91" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="92">
+        <f>D16*E16*F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="I16" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="47" t="inlineStr">
+        <is>
+          <t>Falcons fly out, dive and return. No HP: dinos ignore it, never repaired (DECISIONS #148).</t>
+        </is>
+      </c>
+      <c r="L16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="27" t="n">
+        <v>200</v>
+      </c>
+      <c r="O16" s="43" t="inlineStr">
+        <is>
+          <t>FALCON</t>
+        </is>
+      </c>
+      <c r="P16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>Tar on the track: slows and sinks, can't be damaged</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>450</v>
+      </c>
+      <c r="D17" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="92">
+        <f>D17*E17*F17</f>
+        <v/>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" s="46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="47" t="inlineStr">
+        <is>
+          <t>Placed ON the track (DECISIONS #152); Range = the pool's length of track. No HP (#148).</t>
+        </is>
+      </c>
+      <c r="L17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="N17" s="27" t="n">
+        <v>250</v>
+      </c>
+      <c r="O17" s="43" t="inlineStr">
+        <is>
+          <t>TARPIT</t>
+        </is>
+      </c>
+      <c r="P17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U17" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>The heaviest single hit: pierce-through</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="n">
+        <v>600</v>
+      </c>
+      <c r="D18" s="91" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="92">
+        <f>D18*E18*F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>24</v>
+      </c>
+      <c r="I18" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="47" t="inlineStr">
+        <is>
+          <t>One heavy bolt every 2.5 s; its Spearhead path breaks several sizes (pierce-through).</t>
+        </is>
+      </c>
+      <c r="L18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="O18" s="43" t="inlineStr">
+        <is>
+          <t>BALLISTA</t>
+        </is>
+      </c>
+      <c r="P18" s="27" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="27" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11720,7 +12288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ109"/>
+  <dimension ref="A1:BJ169"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -11758,7 +12326,7 @@
     <row r="1" ht="18.5" customHeight="1" s="90">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>TOWER UPGRADES — 7 towers x 3 paths x 5 tiers</t>
+          <t>TOWER UPGRADES — 11 towers x 3 paths x 5 tiers</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -22000,6 +22568,3186 @@
       <c r="BI109" s="57" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B110" s="43" t="inlineStr">
+        <is>
+          <t>Arc</t>
+        </is>
+      </c>
+      <c r="C110" s="43" t="inlineStr">
+        <is>
+          <t>more arcs, reach</t>
+        </is>
+      </c>
+      <c r="D110" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="56">
+        <f>ROUND('Towers'!$C$15*POWER('Tuning'!$B$12,D110),0)</f>
+        <v/>
+      </c>
+      <c r="F110" s="56">
+        <f>'Towers'!$C$15+E110</f>
+        <v/>
+      </c>
+      <c r="G110" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" s="92">
+        <f>'Towers'!$G$15*G110*H110*I110</f>
+        <v/>
+      </c>
+      <c r="K110" s="92">
+        <f>IF(J110=0,0,F110/J110)</f>
+        <v/>
+      </c>
+      <c r="L110" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M110" s="43" t="inlineStr">
+        <is>
+          <t>Copper Wire</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B111" s="43" t="inlineStr">
+        <is>
+          <t>Arc</t>
+        </is>
+      </c>
+      <c r="C111" s="43" t="inlineStr">
+        <is>
+          <t>more arcs, reach</t>
+        </is>
+      </c>
+      <c r="D111" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" s="56">
+        <f>ROUND('Towers'!$C$15*POWER('Tuning'!$B$12,D111),0)</f>
+        <v/>
+      </c>
+      <c r="F111" s="56">
+        <f>F110+E111</f>
+        <v/>
+      </c>
+      <c r="G111" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="92">
+        <f>'Towers'!$G$15*G111*H111*I111</f>
+        <v/>
+      </c>
+      <c r="K111" s="92">
+        <f>IF(J111=0,0,F111/J111)</f>
+        <v/>
+      </c>
+      <c r="L111" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M111" s="43" t="inlineStr">
+        <is>
+          <t>Long Arc</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B112" s="43" t="inlineStr">
+        <is>
+          <t>Arc</t>
+        </is>
+      </c>
+      <c r="C112" s="43" t="inlineStr">
+        <is>
+          <t>more arcs, reach</t>
+        </is>
+      </c>
+      <c r="D112" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" s="56">
+        <f>ROUND('Towers'!$C$15*POWER('Tuning'!$B$12,D112),0)</f>
+        <v/>
+      </c>
+      <c r="F112" s="56">
+        <f>F111+E112</f>
+        <v/>
+      </c>
+      <c r="G112" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" s="92">
+        <f>'Towers'!$G$15*G112*H112*I112</f>
+        <v/>
+      </c>
+      <c r="K112" s="92">
+        <f>IF(J112=0,0,F112/J112)</f>
+        <v/>
+      </c>
+      <c r="L112" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" s="43" t="inlineStr">
+        <is>
+          <t>Fork Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B113" s="43" t="inlineStr">
+        <is>
+          <t>Arc</t>
+        </is>
+      </c>
+      <c r="C113" s="43" t="inlineStr">
+        <is>
+          <t>more arcs, reach</t>
+        </is>
+      </c>
+      <c r="D113" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E113" s="56">
+        <f>ROUND('Towers'!$C$15*POWER('Tuning'!$B$12,D113),0)</f>
+        <v/>
+      </c>
+      <c r="F113" s="56">
+        <f>F112+E113</f>
+        <v/>
+      </c>
+      <c r="G113" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" s="92">
+        <f>'Towers'!$G$15*G113*H113*I113</f>
+        <v/>
+      </c>
+      <c r="K113" s="92">
+        <f>IF(J113=0,0,F113/J113)</f>
+        <v/>
+      </c>
+      <c r="L113" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" s="43" t="inlineStr">
+        <is>
+          <t>Jump Spark</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B114" s="43" t="inlineStr">
+        <is>
+          <t>Arc</t>
+        </is>
+      </c>
+      <c r="C114" s="43" t="inlineStr">
+        <is>
+          <t>more arcs, reach</t>
+        </is>
+      </c>
+      <c r="D114" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E114" s="56">
+        <f>ROUND('Towers'!$C$15*POWER('Tuning'!$B$12,D114),0)</f>
+        <v/>
+      </c>
+      <c r="F114" s="56">
+        <f>F113+E114</f>
+        <v/>
+      </c>
+      <c r="G114" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" s="92">
+        <f>'Towers'!$G$15*G114*H114*I114</f>
+        <v/>
+      </c>
+      <c r="K114" s="92">
+        <f>IF(J114=0,0,F114/J114)</f>
+        <v/>
+      </c>
+      <c r="L114" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" s="43" t="inlineStr">
+        <is>
+          <t>Power Grid</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B115" s="43" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="C115" s="43" t="inlineStr">
+        <is>
+          <t>power, armour, stun</t>
+        </is>
+      </c>
+      <c r="D115" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="56">
+        <f>ROUND('Towers'!$C$15*POWER('Tuning'!$B$12,D115),0)</f>
+        <v/>
+      </c>
+      <c r="F115" s="56">
+        <f>'Towers'!$C$15+E115</f>
+        <v/>
+      </c>
+      <c r="G115" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" s="92">
+        <f>'Towers'!$G$15*G115*H115*I115</f>
+        <v/>
+      </c>
+      <c r="K115" s="92">
+        <f>IF(J115=0,0,F115/J115)</f>
+        <v/>
+      </c>
+      <c r="L115" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" s="43" t="inlineStr">
+        <is>
+          <t>Battery Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B116" s="43" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="C116" s="43" t="inlineStr">
+        <is>
+          <t>power, armour, stun</t>
+        </is>
+      </c>
+      <c r="D116" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E116" s="56">
+        <f>ROUND('Towers'!$C$15*POWER('Tuning'!$B$12,D116),0)</f>
+        <v/>
+      </c>
+      <c r="F116" s="56">
+        <f>F115+E116</f>
+        <v/>
+      </c>
+      <c r="G116" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" s="92">
+        <f>'Towers'!$G$15*G116*H116*I116</f>
+        <v/>
+      </c>
+      <c r="K116" s="92">
+        <f>IF(J116=0,0,F116/J116)</f>
+        <v/>
+      </c>
+      <c r="L116" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" s="43" t="inlineStr">
+        <is>
+          <t>Static Shock</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B117" s="43" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="C117" s="43" t="inlineStr">
+        <is>
+          <t>power, armour, stun</t>
+        </is>
+      </c>
+      <c r="D117" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E117" s="56">
+        <f>ROUND('Towers'!$C$15*POWER('Tuning'!$B$12,D117),0)</f>
+        <v/>
+      </c>
+      <c r="F117" s="56">
+        <f>F116+E117</f>
+        <v/>
+      </c>
+      <c r="G117" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" s="92">
+        <f>'Towers'!$G$15*G117*H117*I117</f>
+        <v/>
+      </c>
+      <c r="K117" s="92">
+        <f>IF(J117=0,0,F117/J117)</f>
+        <v/>
+      </c>
+      <c r="L117" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" s="43" t="inlineStr">
+        <is>
+          <t>Thunderclap</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B118" s="43" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="C118" s="43" t="inlineStr">
+        <is>
+          <t>power, armour, stun</t>
+        </is>
+      </c>
+      <c r="D118" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E118" s="56">
+        <f>ROUND('Towers'!$C$15*POWER('Tuning'!$B$12,D118),0)</f>
+        <v/>
+      </c>
+      <c r="F118" s="56">
+        <f>F117+E118</f>
+        <v/>
+      </c>
+      <c r="G118" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" s="92">
+        <f>'Towers'!$G$15*G118*H118*I118</f>
+        <v/>
+      </c>
+      <c r="K118" s="92">
+        <f>IF(J118=0,0,F118/J118)</f>
+        <v/>
+      </c>
+      <c r="L118" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" s="43" t="inlineStr">
+        <is>
+          <t>High Voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B119" s="43" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="C119" s="43" t="inlineStr">
+        <is>
+          <t>power, armour, stun</t>
+        </is>
+      </c>
+      <c r="D119" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E119" s="56">
+        <f>ROUND('Towers'!$C$15*POWER('Tuning'!$B$12,D119),0)</f>
+        <v/>
+      </c>
+      <c r="F119" s="56">
+        <f>F118+E119</f>
+        <v/>
+      </c>
+      <c r="G119" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I119" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" s="92">
+        <f>'Towers'!$G$15*G119*H119*I119</f>
+        <v/>
+      </c>
+      <c r="K119" s="92">
+        <f>IF(J119=0,0,F119/J119)</f>
+        <v/>
+      </c>
+      <c r="L119" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" s="43" t="inlineStr">
+        <is>
+          <t>Judgement Bolt</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B120" s="43" t="inlineStr">
+        <is>
+          <t>Lightning Rod</t>
+        </is>
+      </c>
+      <c r="C120" s="43" t="inlineStr">
+        <is>
+          <t>support, defence</t>
+        </is>
+      </c>
+      <c r="D120" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="56">
+        <f>ROUND('Towers'!$C$15*POWER('Tuning'!$B$12,D120),0)</f>
+        <v/>
+      </c>
+      <c r="F120" s="56">
+        <f>'Towers'!$C$15+E120</f>
+        <v/>
+      </c>
+      <c r="G120" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" s="92">
+        <f>'Towers'!$G$15*G120*H120*I120</f>
+        <v/>
+      </c>
+      <c r="K120" s="92">
+        <f>IF(J120=0,0,F120/J120)</f>
+        <v/>
+      </c>
+      <c r="L120" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" s="43" t="inlineStr">
+        <is>
+          <t>Tall Mast</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B121" s="43" t="inlineStr">
+        <is>
+          <t>Lightning Rod</t>
+        </is>
+      </c>
+      <c r="C121" s="43" t="inlineStr">
+        <is>
+          <t>support, defence</t>
+        </is>
+      </c>
+      <c r="D121" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" s="56">
+        <f>ROUND('Towers'!$C$15*POWER('Tuning'!$B$12,D121),0)</f>
+        <v/>
+      </c>
+      <c r="F121" s="56">
+        <f>F120+E121</f>
+        <v/>
+      </c>
+      <c r="G121" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="92">
+        <f>'Towers'!$G$15*G121*H121*I121</f>
+        <v/>
+      </c>
+      <c r="K121" s="92">
+        <f>IF(J121=0,0,F121/J121)</f>
+        <v/>
+      </c>
+      <c r="L121" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M121" s="43" t="inlineStr">
+        <is>
+          <t>Charged Air</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B122" s="43" t="inlineStr">
+        <is>
+          <t>Lightning Rod</t>
+        </is>
+      </c>
+      <c r="C122" s="43" t="inlineStr">
+        <is>
+          <t>support, defence</t>
+        </is>
+      </c>
+      <c r="D122" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" s="56">
+        <f>ROUND('Towers'!$C$15*POWER('Tuning'!$B$12,D122),0)</f>
+        <v/>
+      </c>
+      <c r="F122" s="56">
+        <f>F121+E122</f>
+        <v/>
+      </c>
+      <c r="G122" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" s="92">
+        <f>'Towers'!$G$15*G122*H122*I122</f>
+        <v/>
+      </c>
+      <c r="K122" s="92">
+        <f>IF(J122=0,0,F122/J122)</f>
+        <v/>
+      </c>
+      <c r="L122" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" s="43" t="inlineStr">
+        <is>
+          <t>Grounding Spike</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B123" s="43" t="inlineStr">
+        <is>
+          <t>Lightning Rod</t>
+        </is>
+      </c>
+      <c r="C123" s="43" t="inlineStr">
+        <is>
+          <t>support, defence</t>
+        </is>
+      </c>
+      <c r="D123" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E123" s="56">
+        <f>ROUND('Towers'!$C$15*POWER('Tuning'!$B$12,D123),0)</f>
+        <v/>
+      </c>
+      <c r="F123" s="56">
+        <f>F122+E123</f>
+        <v/>
+      </c>
+      <c r="G123" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" s="92">
+        <f>'Towers'!$G$15*G123*H123*I123</f>
+        <v/>
+      </c>
+      <c r="K123" s="92">
+        <f>IF(J123=0,0,F123/J123)</f>
+        <v/>
+      </c>
+      <c r="L123" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M123" s="43" t="inlineStr">
+        <is>
+          <t>Storm Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B124" s="43" t="inlineStr">
+        <is>
+          <t>Lightning Rod</t>
+        </is>
+      </c>
+      <c r="C124" s="43" t="inlineStr">
+        <is>
+          <t>support, defence</t>
+        </is>
+      </c>
+      <c r="D124" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E124" s="56">
+        <f>ROUND('Towers'!$C$15*POWER('Tuning'!$B$12,D124),0)</f>
+        <v/>
+      </c>
+      <c r="F124" s="56">
+        <f>F123+E124</f>
+        <v/>
+      </c>
+      <c r="G124" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" s="92">
+        <f>'Towers'!$G$15*G124*H124*I124</f>
+        <v/>
+      </c>
+      <c r="K124" s="92">
+        <f>IF(J124=0,0,F124/J124)</f>
+        <v/>
+      </c>
+      <c r="L124" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" s="43" t="inlineStr">
+        <is>
+          <t>Lightning Rodeo</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B125" s="43" t="inlineStr">
+        <is>
+          <t>Talons</t>
+        </is>
+      </c>
+      <c r="C125" s="43" t="inlineStr">
+        <is>
+          <t>raw damage, pierce-through</t>
+        </is>
+      </c>
+      <c r="D125" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="56">
+        <f>ROUND('Towers'!$C$16*POWER('Tuning'!$B$12,D125),0)</f>
+        <v/>
+      </c>
+      <c r="F125" s="56">
+        <f>'Towers'!$C$16+E125</f>
+        <v/>
+      </c>
+      <c r="G125" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" s="92">
+        <f>'Towers'!$G$16*G125*H125*I125</f>
+        <v/>
+      </c>
+      <c r="K125" s="92">
+        <f>IF(J125=0,0,F125/J125)</f>
+        <v/>
+      </c>
+      <c r="L125" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" s="43" t="inlineStr">
+        <is>
+          <t>Sharp Talons</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B126" s="43" t="inlineStr">
+        <is>
+          <t>Talons</t>
+        </is>
+      </c>
+      <c r="C126" s="43" t="inlineStr">
+        <is>
+          <t>raw damage, pierce-through</t>
+        </is>
+      </c>
+      <c r="D126" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E126" s="56">
+        <f>ROUND('Towers'!$C$16*POWER('Tuning'!$B$12,D126),0)</f>
+        <v/>
+      </c>
+      <c r="F126" s="56">
+        <f>F125+E126</f>
+        <v/>
+      </c>
+      <c r="G126" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" s="92">
+        <f>'Towers'!$G$16*G126*H126*I126</f>
+        <v/>
+      </c>
+      <c r="K126" s="92">
+        <f>IF(J126=0,0,F126/J126)</f>
+        <v/>
+      </c>
+      <c r="L126" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M126" s="43" t="inlineStr">
+        <is>
+          <t>Hooked Beak</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B127" s="43" t="inlineStr">
+        <is>
+          <t>Talons</t>
+        </is>
+      </c>
+      <c r="C127" s="43" t="inlineStr">
+        <is>
+          <t>raw damage, pierce-through</t>
+        </is>
+      </c>
+      <c r="D127" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E127" s="56">
+        <f>ROUND('Towers'!$C$16*POWER('Tuning'!$B$12,D127),0)</f>
+        <v/>
+      </c>
+      <c r="F127" s="56">
+        <f>F126+E127</f>
+        <v/>
+      </c>
+      <c r="G127" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" s="92">
+        <f>'Towers'!$G$16*G127*H127*I127</f>
+        <v/>
+      </c>
+      <c r="K127" s="92">
+        <f>IF(J127=0,0,F127/J127)</f>
+        <v/>
+      </c>
+      <c r="L127" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M127" s="43" t="inlineStr">
+        <is>
+          <t>Power Dive</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B128" s="43" t="inlineStr">
+        <is>
+          <t>Talons</t>
+        </is>
+      </c>
+      <c r="C128" s="43" t="inlineStr">
+        <is>
+          <t>raw damage, pierce-through</t>
+        </is>
+      </c>
+      <c r="D128" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E128" s="56">
+        <f>ROUND('Towers'!$C$16*POWER('Tuning'!$B$12,D128),0)</f>
+        <v/>
+      </c>
+      <c r="F128" s="56">
+        <f>F127+E128</f>
+        <v/>
+      </c>
+      <c r="G128" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" s="92">
+        <f>'Towers'!$G$16*G128*H128*I128</f>
+        <v/>
+      </c>
+      <c r="K128" s="92">
+        <f>IF(J128=0,0,F128/J128)</f>
+        <v/>
+      </c>
+      <c r="L128" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" s="43" t="inlineStr">
+        <is>
+          <t>Iron Talons</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B129" s="43" t="inlineStr">
+        <is>
+          <t>Talons</t>
+        </is>
+      </c>
+      <c r="C129" s="43" t="inlineStr">
+        <is>
+          <t>raw damage, pierce-through</t>
+        </is>
+      </c>
+      <c r="D129" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E129" s="56">
+        <f>ROUND('Towers'!$C$16*POWER('Tuning'!$B$12,D129),0)</f>
+        <v/>
+      </c>
+      <c r="F129" s="56">
+        <f>F128+E129</f>
+        <v/>
+      </c>
+      <c r="G129" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" s="92">
+        <f>'Towers'!$G$16*G129*H129*I129</f>
+        <v/>
+      </c>
+      <c r="K129" s="92">
+        <f>IF(J129=0,0,F129/J129)</f>
+        <v/>
+      </c>
+      <c r="L129" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" s="43" t="inlineStr">
+        <is>
+          <t>Eagle of the Peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B130" s="43" t="inlineStr">
+        <is>
+          <t>Flock</t>
+        </is>
+      </c>
+      <c r="C130" s="43" t="inlineStr">
+        <is>
+          <t>more birds</t>
+        </is>
+      </c>
+      <c r="D130" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="56">
+        <f>ROUND('Towers'!$C$16*POWER('Tuning'!$B$12,D130),0)</f>
+        <v/>
+      </c>
+      <c r="F130" s="56">
+        <f>'Towers'!$C$16+E130</f>
+        <v/>
+      </c>
+      <c r="G130" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J130" s="92">
+        <f>'Towers'!$G$16*G130*H130*I130</f>
+        <v/>
+      </c>
+      <c r="K130" s="92">
+        <f>IF(J130=0,0,F130/J130)</f>
+        <v/>
+      </c>
+      <c r="L130" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" s="43" t="inlineStr">
+        <is>
+          <t>Second Pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B131" s="43" t="inlineStr">
+        <is>
+          <t>Flock</t>
+        </is>
+      </c>
+      <c r="C131" s="43" t="inlineStr">
+        <is>
+          <t>more birds</t>
+        </is>
+      </c>
+      <c r="D131" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E131" s="56">
+        <f>ROUND('Towers'!$C$16*POWER('Tuning'!$B$12,D131),0)</f>
+        <v/>
+      </c>
+      <c r="F131" s="56">
+        <f>F130+E131</f>
+        <v/>
+      </c>
+      <c r="G131" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" s="92">
+        <f>'Towers'!$G$16*G131*H131*I131</f>
+        <v/>
+      </c>
+      <c r="K131" s="92">
+        <f>IF(J131=0,0,F131/J131)</f>
+        <v/>
+      </c>
+      <c r="L131" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" s="43" t="inlineStr">
+        <is>
+          <t>Quick Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B132" s="43" t="inlineStr">
+        <is>
+          <t>Flock</t>
+        </is>
+      </c>
+      <c r="C132" s="43" t="inlineStr">
+        <is>
+          <t>more birds</t>
+        </is>
+      </c>
+      <c r="D132" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E132" s="56">
+        <f>ROUND('Towers'!$C$16*POWER('Tuning'!$B$12,D132),0)</f>
+        <v/>
+      </c>
+      <c r="F132" s="56">
+        <f>F131+E132</f>
+        <v/>
+      </c>
+      <c r="G132" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" s="92">
+        <f>'Towers'!$G$16*G132*H132*I132</f>
+        <v/>
+      </c>
+      <c r="K132" s="92">
+        <f>IF(J132=0,0,F132/J132)</f>
+        <v/>
+      </c>
+      <c r="L132" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M132" s="43" t="inlineStr">
+        <is>
+          <t>Flock of Six</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B133" s="43" t="inlineStr">
+        <is>
+          <t>Flock</t>
+        </is>
+      </c>
+      <c r="C133" s="43" t="inlineStr">
+        <is>
+          <t>more birds</t>
+        </is>
+      </c>
+      <c r="D133" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E133" s="56">
+        <f>ROUND('Towers'!$C$16*POWER('Tuning'!$B$12,D133),0)</f>
+        <v/>
+      </c>
+      <c r="F133" s="56">
+        <f>F132+E133</f>
+        <v/>
+      </c>
+      <c r="G133" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J133" s="92">
+        <f>'Towers'!$G$16*G133*H133*I133</f>
+        <v/>
+      </c>
+      <c r="K133" s="92">
+        <f>IF(J133=0,0,F133/J133)</f>
+        <v/>
+      </c>
+      <c r="L133" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" s="43" t="inlineStr">
+        <is>
+          <t>Wide Circle</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B134" s="43" t="inlineStr">
+        <is>
+          <t>Flock</t>
+        </is>
+      </c>
+      <c r="C134" s="43" t="inlineStr">
+        <is>
+          <t>more birds</t>
+        </is>
+      </c>
+      <c r="D134" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E134" s="56">
+        <f>ROUND('Towers'!$C$16*POWER('Tuning'!$B$12,D134),0)</f>
+        <v/>
+      </c>
+      <c r="F134" s="56">
+        <f>F133+E134</f>
+        <v/>
+      </c>
+      <c r="G134" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" s="92">
+        <f>'Towers'!$G$16*G134*H134*I134</f>
+        <v/>
+      </c>
+      <c r="K134" s="92">
+        <f>IF(J134=0,0,F134/J134)</f>
+        <v/>
+      </c>
+      <c r="L134" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" s="43" t="inlineStr">
+        <is>
+          <t>Murmuration</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B135" s="43" t="inlineStr">
+        <is>
+          <t>Falconer</t>
+        </is>
+      </c>
+      <c r="C135" s="43" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D135" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" s="56">
+        <f>ROUND('Towers'!$C$16*POWER('Tuning'!$B$12,D135),0)</f>
+        <v/>
+      </c>
+      <c r="F135" s="56">
+        <f>'Towers'!$C$16+E135</f>
+        <v/>
+      </c>
+      <c r="G135" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J135" s="92">
+        <f>'Towers'!$G$16*G135*H135*I135</f>
+        <v/>
+      </c>
+      <c r="K135" s="92">
+        <f>IF(J135=0,0,F135/J135)</f>
+        <v/>
+      </c>
+      <c r="L135" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" s="43" t="inlineStr">
+        <is>
+          <t>Long Leash</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B136" s="43" t="inlineStr">
+        <is>
+          <t>Falconer</t>
+        </is>
+      </c>
+      <c r="C136" s="43" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D136" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" s="56">
+        <f>ROUND('Towers'!$C$16*POWER('Tuning'!$B$12,D136),0)</f>
+        <v/>
+      </c>
+      <c r="F136" s="56">
+        <f>F135+E136</f>
+        <v/>
+      </c>
+      <c r="G136" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I136" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" s="92">
+        <f>'Towers'!$G$16*G136*H136*I136</f>
+        <v/>
+      </c>
+      <c r="K136" s="92">
+        <f>IF(J136=0,0,F136/J136)</f>
+        <v/>
+      </c>
+      <c r="L136" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Bells</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B137" s="43" t="inlineStr">
+        <is>
+          <t>Falconer</t>
+        </is>
+      </c>
+      <c r="C137" s="43" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D137" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E137" s="56">
+        <f>ROUND('Towers'!$C$16*POWER('Tuning'!$B$12,D137),0)</f>
+        <v/>
+      </c>
+      <c r="F137" s="56">
+        <f>F136+E137</f>
+        <v/>
+      </c>
+      <c r="G137" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" s="92">
+        <f>'Towers'!$G$16*G137*H137*I137</f>
+        <v/>
+      </c>
+      <c r="K137" s="92">
+        <f>IF(J137=0,0,F137/J137)</f>
+        <v/>
+      </c>
+      <c r="L137" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" s="43" t="inlineStr">
+        <is>
+          <t>Hooded Scout</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B138" s="43" t="inlineStr">
+        <is>
+          <t>Falconer</t>
+        </is>
+      </c>
+      <c r="C138" s="43" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D138" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E138" s="56">
+        <f>ROUND('Towers'!$C$16*POWER('Tuning'!$B$12,D138),0)</f>
+        <v/>
+      </c>
+      <c r="F138" s="56">
+        <f>F137+E138</f>
+        <v/>
+      </c>
+      <c r="G138" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" s="92">
+        <f>'Towers'!$G$16*G138*H138*I138</f>
+        <v/>
+      </c>
+      <c r="K138" s="92">
+        <f>IF(J138=0,0,F138/J138)</f>
+        <v/>
+      </c>
+      <c r="L138" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" s="43" t="inlineStr">
+        <is>
+          <t>Lure</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B139" s="43" t="inlineStr">
+        <is>
+          <t>Falconer</t>
+        </is>
+      </c>
+      <c r="C139" s="43" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D139" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E139" s="56">
+        <f>ROUND('Towers'!$C$16*POWER('Tuning'!$B$12,D139),0)</f>
+        <v/>
+      </c>
+      <c r="F139" s="56">
+        <f>F138+E139</f>
+        <v/>
+      </c>
+      <c r="G139" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" s="92">
+        <f>'Towers'!$G$16*G139*H139*I139</f>
+        <v/>
+      </c>
+      <c r="K139" s="92">
+        <f>IF(J139=0,0,F139/J139)</f>
+        <v/>
+      </c>
+      <c r="L139" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M139" s="43" t="inlineStr">
+        <is>
+          <t>Hunting Party</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B140" s="43" t="inlineStr">
+        <is>
+          <t>Deep Tar</t>
+        </is>
+      </c>
+      <c r="C140" s="43" t="inlineStr">
+        <is>
+          <t>slow and sink</t>
+        </is>
+      </c>
+      <c r="D140" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" s="56">
+        <f>ROUND('Towers'!$C$17*POWER('Tuning'!$B$12,D140),0)</f>
+        <v/>
+      </c>
+      <c r="F140" s="56">
+        <f>'Towers'!$C$17+E140</f>
+        <v/>
+      </c>
+      <c r="G140" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" s="92">
+        <f>'Towers'!$G$17*G140*H140*I140</f>
+        <v/>
+      </c>
+      <c r="K140" s="92">
+        <f>IF(J140=0,0,F140/J140)</f>
+        <v/>
+      </c>
+      <c r="L140" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" s="43" t="inlineStr">
+        <is>
+          <t>Thick Tar</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B141" s="43" t="inlineStr">
+        <is>
+          <t>Deep Tar</t>
+        </is>
+      </c>
+      <c r="C141" s="43" t="inlineStr">
+        <is>
+          <t>slow and sink</t>
+        </is>
+      </c>
+      <c r="D141" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E141" s="56">
+        <f>ROUND('Towers'!$C$17*POWER('Tuning'!$B$12,D141),0)</f>
+        <v/>
+      </c>
+      <c r="F141" s="56">
+        <f>F140+E141</f>
+        <v/>
+      </c>
+      <c r="G141" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" s="92">
+        <f>'Towers'!$G$17*G141*H141*I141</f>
+        <v/>
+      </c>
+      <c r="K141" s="92">
+        <f>IF(J141=0,0,F141/J141)</f>
+        <v/>
+      </c>
+      <c r="L141" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" s="43" t="inlineStr">
+        <is>
+          <t>Wide Pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B142" s="43" t="inlineStr">
+        <is>
+          <t>Deep Tar</t>
+        </is>
+      </c>
+      <c r="C142" s="43" t="inlineStr">
+        <is>
+          <t>slow and sink</t>
+        </is>
+      </c>
+      <c r="D142" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E142" s="56">
+        <f>ROUND('Towers'!$C$17*POWER('Tuning'!$B$12,D142),0)</f>
+        <v/>
+      </c>
+      <c r="F142" s="56">
+        <f>F141+E142</f>
+        <v/>
+      </c>
+      <c r="G142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" s="92">
+        <f>'Towers'!$G$17*G142*H142*I142</f>
+        <v/>
+      </c>
+      <c r="K142" s="92">
+        <f>IF(J142=0,0,F142/J142)</f>
+        <v/>
+      </c>
+      <c r="L142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" s="43" t="inlineStr">
+        <is>
+          <t>Fast Sink</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B143" s="43" t="inlineStr">
+        <is>
+          <t>Deep Tar</t>
+        </is>
+      </c>
+      <c r="C143" s="43" t="inlineStr">
+        <is>
+          <t>slow and sink</t>
+        </is>
+      </c>
+      <c r="D143" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E143" s="56">
+        <f>ROUND('Towers'!$C$17*POWER('Tuning'!$B$12,D143),0)</f>
+        <v/>
+      </c>
+      <c r="F143" s="56">
+        <f>F142+E143</f>
+        <v/>
+      </c>
+      <c r="G143" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" s="92">
+        <f>'Towers'!$G$17*G143*H143*I143</f>
+        <v/>
+      </c>
+      <c r="K143" s="92">
+        <f>IF(J143=0,0,F143/J143)</f>
+        <v/>
+      </c>
+      <c r="L143" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" s="43" t="inlineStr">
+        <is>
+          <t>Clinging Tar</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B144" s="43" t="inlineStr">
+        <is>
+          <t>Deep Tar</t>
+        </is>
+      </c>
+      <c r="C144" s="43" t="inlineStr">
+        <is>
+          <t>slow and sink</t>
+        </is>
+      </c>
+      <c r="D144" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E144" s="56">
+        <f>ROUND('Towers'!$C$17*POWER('Tuning'!$B$12,D144),0)</f>
+        <v/>
+      </c>
+      <c r="F144" s="56">
+        <f>F143+E144</f>
+        <v/>
+      </c>
+      <c r="G144" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" s="92">
+        <f>'Towers'!$G$17*G144*H144*I144</f>
+        <v/>
+      </c>
+      <c r="K144" s="92">
+        <f>IF(J144=0,0,F144/J144)</f>
+        <v/>
+      </c>
+      <c r="L144" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" s="43" t="inlineStr">
+        <is>
+          <t>Tar Lake</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B145" s="43" t="inlineStr">
+        <is>
+          <t>Bubbling</t>
+        </is>
+      </c>
+      <c r="C145" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D145" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" s="56">
+        <f>ROUND('Towers'!$C$17*POWER('Tuning'!$B$12,D145),0)</f>
+        <v/>
+      </c>
+      <c r="F145" s="56">
+        <f>'Towers'!$C$17+E145</f>
+        <v/>
+      </c>
+      <c r="G145" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" s="92">
+        <f>'Towers'!$G$17*G145*H145*I145</f>
+        <v/>
+      </c>
+      <c r="K145" s="92">
+        <f>IF(J145=0,0,F145/J145)</f>
+        <v/>
+      </c>
+      <c r="L145" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" s="43" t="inlineStr">
+        <is>
+          <t>Warm Tar</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B146" s="43" t="inlineStr">
+        <is>
+          <t>Bubbling</t>
+        </is>
+      </c>
+      <c r="C146" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D146" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E146" s="56">
+        <f>ROUND('Towers'!$C$17*POWER('Tuning'!$B$12,D146),0)</f>
+        <v/>
+      </c>
+      <c r="F146" s="56">
+        <f>F145+E146</f>
+        <v/>
+      </c>
+      <c r="G146" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" s="92">
+        <f>'Towers'!$G$17*G146*H146*I146</f>
+        <v/>
+      </c>
+      <c r="K146" s="92">
+        <f>IF(J146=0,0,F146/J146)</f>
+        <v/>
+      </c>
+      <c r="L146" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" s="43" t="inlineStr">
+        <is>
+          <t>Simmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B147" s="43" t="inlineStr">
+        <is>
+          <t>Bubbling</t>
+        </is>
+      </c>
+      <c r="C147" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D147" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E147" s="56">
+        <f>ROUND('Towers'!$C$17*POWER('Tuning'!$B$12,D147),0)</f>
+        <v/>
+      </c>
+      <c r="F147" s="56">
+        <f>F146+E147</f>
+        <v/>
+      </c>
+      <c r="G147" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" s="92">
+        <f>'Towers'!$G$17*G147*H147*I147</f>
+        <v/>
+      </c>
+      <c r="K147" s="92">
+        <f>IF(J147=0,0,F147/J147)</f>
+        <v/>
+      </c>
+      <c r="L147" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" s="43" t="inlineStr">
+        <is>
+          <t>Boiling Pit</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B148" s="43" t="inlineStr">
+        <is>
+          <t>Bubbling</t>
+        </is>
+      </c>
+      <c r="C148" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D148" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E148" s="56">
+        <f>ROUND('Towers'!$C$17*POWER('Tuning'!$B$12,D148),0)</f>
+        <v/>
+      </c>
+      <c r="F148" s="56">
+        <f>F147+E148</f>
+        <v/>
+      </c>
+      <c r="G148" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" s="92">
+        <f>'Towers'!$G$17*G148*H148*I148</f>
+        <v/>
+      </c>
+      <c r="K148" s="92">
+        <f>IF(J148=0,0,F148/J148)</f>
+        <v/>
+      </c>
+      <c r="L148" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" s="43" t="inlineStr">
+        <is>
+          <t>Tar Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B149" s="43" t="inlineStr">
+        <is>
+          <t>Bubbling</t>
+        </is>
+      </c>
+      <c r="C149" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D149" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E149" s="56">
+        <f>ROUND('Towers'!$C$17*POWER('Tuning'!$B$12,D149),0)</f>
+        <v/>
+      </c>
+      <c r="F149" s="56">
+        <f>F148+E149</f>
+        <v/>
+      </c>
+      <c r="G149" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" s="92">
+        <f>'Towers'!$G$17*G149*H149*I149</f>
+        <v/>
+      </c>
+      <c r="K149" s="92">
+        <f>IF(J149=0,0,F149/J149)</f>
+        <v/>
+      </c>
+      <c r="L149" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" s="43" t="inlineStr">
+        <is>
+          <t>Eruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B150" s="43" t="inlineStr">
+        <is>
+          <t>Dig Site</t>
+        </is>
+      </c>
+      <c r="C150" s="43" t="inlineStr">
+        <is>
+          <t>cash and support</t>
+        </is>
+      </c>
+      <c r="D150" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" s="56">
+        <f>ROUND('Towers'!$C$17*POWER('Tuning'!$B$12,D150),0)</f>
+        <v/>
+      </c>
+      <c r="F150" s="56">
+        <f>'Towers'!$C$17+E150</f>
+        <v/>
+      </c>
+      <c r="G150" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" s="92">
+        <f>'Towers'!$G$17*G150*H150*I150</f>
+        <v/>
+      </c>
+      <c r="K150" s="92">
+        <f>IF(J150=0,0,F150/J150)</f>
+        <v/>
+      </c>
+      <c r="L150" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" s="43" t="inlineStr">
+        <is>
+          <t>Pick and Shovel</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B151" s="43" t="inlineStr">
+        <is>
+          <t>Dig Site</t>
+        </is>
+      </c>
+      <c r="C151" s="43" t="inlineStr">
+        <is>
+          <t>cash and support</t>
+        </is>
+      </c>
+      <c r="D151" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" s="56">
+        <f>ROUND('Towers'!$C$17*POWER('Tuning'!$B$12,D151),0)</f>
+        <v/>
+      </c>
+      <c r="F151" s="56">
+        <f>F150+E151</f>
+        <v/>
+      </c>
+      <c r="G151" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" s="92">
+        <f>'Towers'!$G$17*G151*H151*I151</f>
+        <v/>
+      </c>
+      <c r="K151" s="92">
+        <f>IF(J151=0,0,F151/J151)</f>
+        <v/>
+      </c>
+      <c r="L151" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" s="43" t="inlineStr">
+        <is>
+          <t>Fossil Hunter</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B152" s="43" t="inlineStr">
+        <is>
+          <t>Dig Site</t>
+        </is>
+      </c>
+      <c r="C152" s="43" t="inlineStr">
+        <is>
+          <t>cash and support</t>
+        </is>
+      </c>
+      <c r="D152" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E152" s="56">
+        <f>ROUND('Towers'!$C$17*POWER('Tuning'!$B$12,D152),0)</f>
+        <v/>
+      </c>
+      <c r="F152" s="56">
+        <f>F151+E152</f>
+        <v/>
+      </c>
+      <c r="G152" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I152" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" s="92">
+        <f>'Towers'!$G$17*G152*H152*I152</f>
+        <v/>
+      </c>
+      <c r="K152" s="92">
+        <f>IF(J152=0,0,F152/J152)</f>
+        <v/>
+      </c>
+      <c r="L152" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" s="43" t="inlineStr">
+        <is>
+          <t>Lucky Finds</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B153" s="43" t="inlineStr">
+        <is>
+          <t>Dig Site</t>
+        </is>
+      </c>
+      <c r="C153" s="43" t="inlineStr">
+        <is>
+          <t>cash and support</t>
+        </is>
+      </c>
+      <c r="D153" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E153" s="56">
+        <f>ROUND('Towers'!$C$17*POWER('Tuning'!$B$12,D153),0)</f>
+        <v/>
+      </c>
+      <c r="F153" s="56">
+        <f>F152+E153</f>
+        <v/>
+      </c>
+      <c r="G153" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I153" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="92">
+        <f>'Towers'!$G$17*G153*H153*I153</f>
+        <v/>
+      </c>
+      <c r="K153" s="92">
+        <f>IF(J153=0,0,F153/J153)</f>
+        <v/>
+      </c>
+      <c r="L153" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" s="43" t="inlineStr">
+        <is>
+          <t>Tar Tracks</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="43" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B154" s="43" t="inlineStr">
+        <is>
+          <t>Dig Site</t>
+        </is>
+      </c>
+      <c r="C154" s="43" t="inlineStr">
+        <is>
+          <t>cash and support</t>
+        </is>
+      </c>
+      <c r="D154" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E154" s="56">
+        <f>ROUND('Towers'!$C$17*POWER('Tuning'!$B$12,D154),0)</f>
+        <v/>
+      </c>
+      <c r="F154" s="56">
+        <f>F153+E154</f>
+        <v/>
+      </c>
+      <c r="G154" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" s="92">
+        <f>'Towers'!$G$17*G154*H154*I154</f>
+        <v/>
+      </c>
+      <c r="K154" s="92">
+        <f>IF(J154=0,0,F154/J154)</f>
+        <v/>
+      </c>
+      <c r="L154" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" s="43" t="inlineStr">
+        <is>
+          <t>Tar Totem</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B155" s="43" t="inlineStr">
+        <is>
+          <t>Spearhead</t>
+        </is>
+      </c>
+      <c r="C155" s="43" t="inlineStr">
+        <is>
+          <t>raw damage, breaks</t>
+        </is>
+      </c>
+      <c r="D155" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" s="56">
+        <f>ROUND('Towers'!$C$18*POWER('Tuning'!$B$12,D155),0)</f>
+        <v/>
+      </c>
+      <c r="F155" s="56">
+        <f>'Towers'!$C$18+E155</f>
+        <v/>
+      </c>
+      <c r="G155" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" s="92">
+        <f>'Towers'!$G$18*G155*H155*I155</f>
+        <v/>
+      </c>
+      <c r="K155" s="92">
+        <f>IF(J155=0,0,F155/J155)</f>
+        <v/>
+      </c>
+      <c r="L155" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" s="43" t="inlineStr">
+        <is>
+          <t>Steel Head</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B156" s="43" t="inlineStr">
+        <is>
+          <t>Spearhead</t>
+        </is>
+      </c>
+      <c r="C156" s="43" t="inlineStr">
+        <is>
+          <t>raw damage, breaks</t>
+        </is>
+      </c>
+      <c r="D156" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E156" s="56">
+        <f>ROUND('Towers'!$C$18*POWER('Tuning'!$B$12,D156),0)</f>
+        <v/>
+      </c>
+      <c r="F156" s="56">
+        <f>F155+E156</f>
+        <v/>
+      </c>
+      <c r="G156" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I156" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" s="92">
+        <f>'Towers'!$G$18*G156*H156*I156</f>
+        <v/>
+      </c>
+      <c r="K156" s="92">
+        <f>IF(J156=0,0,F156/J156)</f>
+        <v/>
+      </c>
+      <c r="L156" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" s="43" t="inlineStr">
+        <is>
+          <t>Saw Tip</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B157" s="43" t="inlineStr">
+        <is>
+          <t>Spearhead</t>
+        </is>
+      </c>
+      <c r="C157" s="43" t="inlineStr">
+        <is>
+          <t>raw damage, breaks</t>
+        </is>
+      </c>
+      <c r="D157" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E157" s="56">
+        <f>ROUND('Towers'!$C$18*POWER('Tuning'!$B$12,D157),0)</f>
+        <v/>
+      </c>
+      <c r="F157" s="56">
+        <f>F156+E157</f>
+        <v/>
+      </c>
+      <c r="G157" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I157" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J157" s="92">
+        <f>'Towers'!$G$18*G157*H157*I157</f>
+        <v/>
+      </c>
+      <c r="K157" s="92">
+        <f>IF(J157=0,0,F157/J157)</f>
+        <v/>
+      </c>
+      <c r="L157" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M157" s="43" t="inlineStr">
+        <is>
+          <t>Crusher Bolt</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B158" s="43" t="inlineStr">
+        <is>
+          <t>Spearhead</t>
+        </is>
+      </c>
+      <c r="C158" s="43" t="inlineStr">
+        <is>
+          <t>raw damage, breaks</t>
+        </is>
+      </c>
+      <c r="D158" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E158" s="56">
+        <f>ROUND('Towers'!$C$18*POWER('Tuning'!$B$12,D158),0)</f>
+        <v/>
+      </c>
+      <c r="F158" s="56">
+        <f>F157+E158</f>
+        <v/>
+      </c>
+      <c r="G158" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I158" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J158" s="92">
+        <f>'Towers'!$G$18*G158*H158*I158</f>
+        <v/>
+      </c>
+      <c r="K158" s="92">
+        <f>IF(J158=0,0,F158/J158)</f>
+        <v/>
+      </c>
+      <c r="L158" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" s="43" t="inlineStr">
+        <is>
+          <t>Great Harpoon</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B159" s="43" t="inlineStr">
+        <is>
+          <t>Spearhead</t>
+        </is>
+      </c>
+      <c r="C159" s="43" t="inlineStr">
+        <is>
+          <t>raw damage, breaks</t>
+        </is>
+      </c>
+      <c r="D159" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E159" s="56">
+        <f>ROUND('Towers'!$C$18*POWER('Tuning'!$B$12,D159),0)</f>
+        <v/>
+      </c>
+      <c r="F159" s="56">
+        <f>F158+E159</f>
+        <v/>
+      </c>
+      <c r="G159" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I159" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J159" s="92">
+        <f>'Towers'!$G$18*G159*H159*I159</f>
+        <v/>
+      </c>
+      <c r="K159" s="92">
+        <f>IF(J159=0,0,F159/J159)</f>
+        <v/>
+      </c>
+      <c r="L159" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M159" s="43" t="inlineStr">
+        <is>
+          <t>Skewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B160" s="43" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="C160" s="43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D160" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" s="56">
+        <f>ROUND('Towers'!$C$18*POWER('Tuning'!$B$12,D160),0)</f>
+        <v/>
+      </c>
+      <c r="F160" s="56">
+        <f>'Towers'!$C$18+E160</f>
+        <v/>
+      </c>
+      <c r="G160" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" s="92">
+        <f>'Towers'!$G$18*G160*H160*I160</f>
+        <v/>
+      </c>
+      <c r="K160" s="92">
+        <f>IF(J160=0,0,F160/J160)</f>
+        <v/>
+      </c>
+      <c r="L160" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" s="43" t="inlineStr">
+        <is>
+          <t>Rope Line</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B161" s="43" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="C161" s="43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D161" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E161" s="56">
+        <f>ROUND('Towers'!$C$18*POWER('Tuning'!$B$12,D161),0)</f>
+        <v/>
+      </c>
+      <c r="F161" s="56">
+        <f>F160+E161</f>
+        <v/>
+      </c>
+      <c r="G161" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I161" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" s="92">
+        <f>'Towers'!$G$18*G161*H161*I161</f>
+        <v/>
+      </c>
+      <c r="K161" s="92">
+        <f>IF(J161=0,0,F161/J161)</f>
+        <v/>
+      </c>
+      <c r="L161" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" s="43" t="inlineStr">
+        <is>
+          <t>Winch</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B162" s="43" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="C162" s="43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D162" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E162" s="56">
+        <f>ROUND('Towers'!$C$18*POWER('Tuning'!$B$12,D162),0)</f>
+        <v/>
+      </c>
+      <c r="F162" s="56">
+        <f>F161+E162</f>
+        <v/>
+      </c>
+      <c r="G162" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I162" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" s="92">
+        <f>'Towers'!$G$18*G162*H162*I162</f>
+        <v/>
+      </c>
+      <c r="K162" s="92">
+        <f>IF(J162=0,0,F162/J162)</f>
+        <v/>
+      </c>
+      <c r="L162" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" s="43" t="inlineStr">
+        <is>
+          <t>Pin Down</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B163" s="43" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="C163" s="43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D163" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E163" s="56">
+        <f>ROUND('Towers'!$C$18*POWER('Tuning'!$B$12,D163),0)</f>
+        <v/>
+      </c>
+      <c r="F163" s="56">
+        <f>F162+E163</f>
+        <v/>
+      </c>
+      <c r="G163" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I163" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" s="92">
+        <f>'Towers'!$G$18*G163*H163*I163</f>
+        <v/>
+      </c>
+      <c r="K163" s="92">
+        <f>IF(J163=0,0,F163/J163)</f>
+        <v/>
+      </c>
+      <c r="L163" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M163" s="43" t="inlineStr">
+        <is>
+          <t>Reel In</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B164" s="43" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="C164" s="43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D164" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E164" s="56">
+        <f>ROUND('Towers'!$C$18*POWER('Tuning'!$B$12,D164),0)</f>
+        <v/>
+      </c>
+      <c r="F164" s="56">
+        <f>F163+E164</f>
+        <v/>
+      </c>
+      <c r="G164" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H164" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I164" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" s="92">
+        <f>'Towers'!$G$18*G164*H164*I164</f>
+        <v/>
+      </c>
+      <c r="K164" s="92">
+        <f>IF(J164=0,0,F164/J164)</f>
+        <v/>
+      </c>
+      <c r="L164" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" s="43" t="inlineStr">
+        <is>
+          <t>Tow Line</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B165" s="43" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="C165" s="43" t="inlineStr">
+        <is>
+          <t>more bolts</t>
+        </is>
+      </c>
+      <c r="D165" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" s="56">
+        <f>ROUND('Towers'!$C$18*POWER('Tuning'!$B$12,D165),0)</f>
+        <v/>
+      </c>
+      <c r="F165" s="56">
+        <f>'Towers'!$C$18+E165</f>
+        <v/>
+      </c>
+      <c r="G165" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" s="92">
+        <f>'Towers'!$G$18*G165*H165*I165</f>
+        <v/>
+      </c>
+      <c r="K165" s="92">
+        <f>IF(J165=0,0,F165/J165)</f>
+        <v/>
+      </c>
+      <c r="L165" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M165" s="43" t="inlineStr">
+        <is>
+          <t>Twin Bolts</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B166" s="43" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="C166" s="43" t="inlineStr">
+        <is>
+          <t>more bolts</t>
+        </is>
+      </c>
+      <c r="D166" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E166" s="56">
+        <f>ROUND('Towers'!$C$18*POWER('Tuning'!$B$12,D166),0)</f>
+        <v/>
+      </c>
+      <c r="F166" s="56">
+        <f>F165+E166</f>
+        <v/>
+      </c>
+      <c r="G166" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I166" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J166" s="92">
+        <f>'Towers'!$G$18*G166*H166*I166</f>
+        <v/>
+      </c>
+      <c r="K166" s="92">
+        <f>IF(J166=0,0,F166/J166)</f>
+        <v/>
+      </c>
+      <c r="L166" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" s="43" t="inlineStr">
+        <is>
+          <t>Fast Crank</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B167" s="43" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="C167" s="43" t="inlineStr">
+        <is>
+          <t>more bolts</t>
+        </is>
+      </c>
+      <c r="D167" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E167" s="56">
+        <f>ROUND('Towers'!$C$18*POWER('Tuning'!$B$12,D167),0)</f>
+        <v/>
+      </c>
+      <c r="F167" s="56">
+        <f>F166+E167</f>
+        <v/>
+      </c>
+      <c r="G167" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" s="92">
+        <f>'Towers'!$G$18*G167*H167*I167</f>
+        <v/>
+      </c>
+      <c r="K167" s="92">
+        <f>IF(J167=0,0,F167/J167)</f>
+        <v/>
+      </c>
+      <c r="L167" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" s="43" t="inlineStr">
+        <is>
+          <t>Spread Volley</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B168" s="43" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="C168" s="43" t="inlineStr">
+        <is>
+          <t>more bolts</t>
+        </is>
+      </c>
+      <c r="D168" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E168" s="56">
+        <f>ROUND('Towers'!$C$18*POWER('Tuning'!$B$12,D168),0)</f>
+        <v/>
+      </c>
+      <c r="F168" s="56">
+        <f>F167+E168</f>
+        <v/>
+      </c>
+      <c r="G168" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I168" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" s="92">
+        <f>'Towers'!$G$18*G168*H168*I168</f>
+        <v/>
+      </c>
+      <c r="K168" s="92">
+        <f>IF(J168=0,0,F168/J168)</f>
+        <v/>
+      </c>
+      <c r="L168" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" s="43" t="inlineStr">
+        <is>
+          <t>Steam Crank</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="43" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B169" s="43" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="C169" s="43" t="inlineStr">
+        <is>
+          <t>more bolts</t>
+        </is>
+      </c>
+      <c r="D169" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E169" s="56">
+        <f>ROUND('Towers'!$C$18*POWER('Tuning'!$B$12,D169),0)</f>
+        <v/>
+      </c>
+      <c r="F169" s="56">
+        <f>F168+E169</f>
+        <v/>
+      </c>
+      <c r="G169" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I169" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J169" s="92">
+        <f>'Towers'!$G$18*G169*H169*I169</f>
+        <v/>
+      </c>
+      <c r="K169" s="92">
+        <f>IF(J169=0,0,F169/J169)</f>
+        <v/>
+      </c>
+      <c r="L169" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" s="43" t="inlineStr">
+        <is>
+          <t>Chain Harpoons</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9319,7 +9319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -11022,7 +11022,6 @@
         </is>
       </c>
     </row>
-    <row r="109"/>
     <row r="110">
       <c r="A110" s="99" t="inlineStr">
         <is>
@@ -11205,7 +11204,6 @@
         </is>
       </c>
     </row>
-    <row r="123"/>
     <row r="124">
       <c r="A124" s="99" t="inlineStr">
         <is>
@@ -11218,7 +11216,6 @@
         </is>
       </c>
     </row>
-    <row r="125"/>
     <row r="126">
       <c r="A126" s="99" t="inlineStr">
         <is>
@@ -11256,7 +11253,6 @@
         </is>
       </c>
     </row>
-    <row r="129"/>
     <row r="130">
       <c r="A130" s="99" t="inlineStr">
         <is>
@@ -11294,8 +11290,6 @@
         </is>
       </c>
     </row>
-    <row r="133"/>
-    <row r="134"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -11316,7 +11310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -11494,6 +11488,11 @@
           <t>On track</t>
         </is>
       </c>
+      <c r="V4" s="21" t="inlineStr">
+        <is>
+          <t>Chains</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -11984,7 +11983,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
         <is>
@@ -12050,6 +12048,11 @@
       </c>
       <c r="R15" s="27" t="n">
         <v>0</v>
+      </c>
+      <c r="V15" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -12288,7 +12291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ169"/>
+  <dimension ref="A1:BS169"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -12736,6 +12739,51 @@
       <c r="BJ4" s="104" t="inlineStr">
         <is>
           <t>Size breaks</t>
+        </is>
+      </c>
+      <c r="BK4" s="104" t="inlineStr">
+        <is>
+          <t>Arcs</t>
+        </is>
+      </c>
+      <c r="BL4" s="104" t="inlineStr">
+        <is>
+          <t>Arc reach</t>
+        </is>
+      </c>
+      <c r="BM4" s="104" t="inlineStr">
+        <is>
+          <t>Arc forks</t>
+        </is>
+      </c>
+      <c r="BN4" s="104" t="inlineStr">
+        <is>
+          <t>Arc jumps</t>
+        </is>
+      </c>
+      <c r="BO4" s="104" t="inlineStr">
+        <is>
+          <t>Power grid</t>
+        </is>
+      </c>
+      <c r="BP4" s="104" t="inlineStr">
+        <is>
+          <t>Static %</t>
+        </is>
+      </c>
+      <c r="BQ4" s="104" t="inlineStr">
+        <is>
+          <t>Judgement bolt</t>
+        </is>
+      </c>
+      <c r="BR4" s="104" t="inlineStr">
+        <is>
+          <t>Grounding every (s)</t>
+        </is>
+      </c>
+      <c r="BS4" s="104" t="inlineStr">
+        <is>
+          <t>Aura arc %</t>
         </is>
       </c>
     </row>
@@ -22599,7 +22647,7 @@
         <v/>
       </c>
       <c r="G110" s="57" t="n">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="H110" s="57" t="n">
         <v>1</v>
@@ -22623,6 +22671,9 @@
           <t>Copper Wire</t>
         </is>
       </c>
+      <c r="BK110" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="43" t="inlineStr">
@@ -22652,7 +22703,7 @@
         <v/>
       </c>
       <c r="G111" s="57" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="H111" s="57" t="n">
         <v>1</v>
@@ -22676,6 +22727,12 @@
           <t>Long Arc</t>
         </is>
       </c>
+      <c r="BK111" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL111" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="43" t="inlineStr">
@@ -22705,7 +22762,7 @@
         <v/>
       </c>
       <c r="G112" s="57" t="n">
-        <v>1</v>
+        <v>3.05</v>
       </c>
       <c r="H112" s="57" t="n">
         <v>1</v>
@@ -22729,6 +22786,15 @@
           <t>Fork Lightning</t>
         </is>
       </c>
+      <c r="BK112" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL112" t="n">
+        <v>15</v>
+      </c>
+      <c r="BM112" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="43" t="inlineStr">
@@ -22758,7 +22824,7 @@
         <v/>
       </c>
       <c r="G113" s="57" t="n">
-        <v>1</v>
+        <v>4.42</v>
       </c>
       <c r="H113" s="57" t="n">
         <v>1</v>
@@ -22782,6 +22848,20 @@
           <t>Jump Spark</t>
         </is>
       </c>
+      <c r="BK113" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL113" t="n">
+        <v>15</v>
+      </c>
+      <c r="BM113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN113" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="43" t="inlineStr">
@@ -22811,7 +22891,7 @@
         <v/>
       </c>
       <c r="G114" s="57" t="n">
-        <v>1</v>
+        <v>6.41</v>
       </c>
       <c r="H114" s="57" t="n">
         <v>1</v>
@@ -22835,6 +22915,25 @@
           <t>Power Grid</t>
         </is>
       </c>
+      <c r="BK114" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>15</v>
+      </c>
+      <c r="BM114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN114" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO114" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="43" t="inlineStr">
@@ -22864,7 +22963,7 @@
         <v/>
       </c>
       <c r="G115" s="57" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H115" s="57" t="n">
         <v>1</v>
@@ -22917,7 +23016,7 @@
         <v/>
       </c>
       <c r="G116" s="57" t="n">
-        <v>1</v>
+        <v>2.47</v>
       </c>
       <c r="H116" s="57" t="n">
         <v>1</v>
@@ -22941,6 +23040,9 @@
           <t>Static Shock</t>
         </is>
       </c>
+      <c r="BP116" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="43" t="inlineStr">
@@ -22970,7 +23072,7 @@
         <v/>
       </c>
       <c r="G117" s="57" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="H117" s="57" t="n">
         <v>1</v>
@@ -22994,6 +23096,12 @@
           <t>Thunderclap</t>
         </is>
       </c>
+      <c r="U117" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="43" t="inlineStr">
@@ -23023,7 +23131,7 @@
         <v/>
       </c>
       <c r="G118" s="57" t="n">
-        <v>1</v>
+        <v>6.58</v>
       </c>
       <c r="H118" s="57" t="n">
         <v>1</v>
@@ -23047,6 +23155,17 @@
           <t>High Voltage</t>
         </is>
       </c>
+      <c r="N118" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U118" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="43" t="inlineStr">
@@ -23076,7 +23195,7 @@
         <v/>
       </c>
       <c r="G119" s="57" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="H119" s="57" t="n">
         <v>1</v>
@@ -23100,6 +23219,22 @@
           <t>Judgement Bolt</t>
         </is>
       </c>
+      <c r="N119" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U119" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ119" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="43" t="inlineStr">
@@ -23129,7 +23264,7 @@
         <v/>
       </c>
       <c r="G120" s="57" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H120" s="57" t="n">
         <v>1</v>
@@ -23146,7 +23281,7 @@
         <v/>
       </c>
       <c r="L120" s="57" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="M120" s="43" t="inlineStr">
         <is>
@@ -23182,7 +23317,7 @@
         <v/>
       </c>
       <c r="G121" s="57" t="n">
-        <v>1</v>
+        <v>1.69</v>
       </c>
       <c r="H121" s="57" t="n">
         <v>1</v>
@@ -23199,12 +23334,15 @@
         <v/>
       </c>
       <c r="L121" s="57" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="M121" s="43" t="inlineStr">
         <is>
           <t>Charged Air</t>
         </is>
+      </c>
+      <c r="AB121" s="57" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="122">
@@ -23235,7 +23373,7 @@
         <v/>
       </c>
       <c r="G122" s="57" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="H122" s="57" t="n">
         <v>1</v>
@@ -23252,12 +23390,18 @@
         <v/>
       </c>
       <c r="L122" s="57" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="M122" s="43" t="inlineStr">
         <is>
           <t>Grounding Spike</t>
         </is>
+      </c>
+      <c r="AB122" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="123">
@@ -23288,7 +23432,7 @@
         <v/>
       </c>
       <c r="G123" s="57" t="n">
-        <v>1</v>
+        <v>2.86</v>
       </c>
       <c r="H123" s="57" t="n">
         <v>1</v>
@@ -23305,12 +23449,21 @@
         <v/>
       </c>
       <c r="L123" s="57" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="M123" s="43" t="inlineStr">
         <is>
           <t>Storm Warning</t>
         </is>
+      </c>
+      <c r="AB123" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC123" s="57" t="n">
+        <v>15</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="124">
@@ -23341,7 +23494,7 @@
         <v/>
       </c>
       <c r="G124" s="57" t="n">
-        <v>1</v>
+        <v>3.71</v>
       </c>
       <c r="H124" s="57" t="n">
         <v>1</v>
@@ -23358,12 +23511,24 @@
         <v/>
       </c>
       <c r="L124" s="57" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="M124" s="43" t="inlineStr">
         <is>
           <t>Lightning Rodeo</t>
         </is>
+      </c>
+      <c r="AB124" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC124" s="57" t="n">
+        <v>15</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="125">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -6501,7 +6501,7 @@
       </c>
       <c r="D25" s="81" t="inlineStr">
         <is>
-          <t>Trailblazer</t>
+          <t>Trapper</t>
         </is>
       </c>
       <c r="E25" s="81" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D36" s="81" t="inlineStr">
         <is>
-          <t>Trapper</t>
+          <t>Trailblazer</t>
         </is>
       </c>
       <c r="E36" s="81" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="D58" s="81" t="inlineStr">
         <is>
-          <t>Trophy Hunter</t>
+          <t>Veteran Hunter</t>
         </is>
       </c>
       <c r="E58" s="81" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="D69" s="81" t="inlineStr">
         <is>
-          <t>Warden</t>
+          <t>Game Warden</t>
         </is>
       </c>
       <c r="E69" s="81" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="D79" s="81" t="inlineStr">
         <is>
-          <t>Star Marker</t>
+          <t>Claw Marker</t>
         </is>
       </c>
       <c r="E79" s="81" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="D90" s="81" t="inlineStr">
         <is>
-          <t>Fern Trail</t>
+          <t>Footprint Trail</t>
         </is>
       </c>
       <c r="E90" s="81" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="D113" s="81" t="inlineStr">
         <is>
-          <t>Apex Hunter</t>
+          <t>Master Hunter</t>
         </is>
       </c>
       <c r="E113" s="81" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="D114" s="81" t="inlineStr">
         <is>
-          <t>Tar Pit Set</t>
+          <t>Volcano Set</t>
         </is>
       </c>
       <c r="E114" s="81" t="inlineStr">
@@ -22671,7 +22671,7 @@
           <t>Copper Wire</t>
         </is>
       </c>
-      <c r="BK110" t="n">
+      <c r="BK110" s="81" t="n">
         <v>6</v>
       </c>
     </row>
@@ -22727,10 +22727,10 @@
           <t>Long Arc</t>
         </is>
       </c>
-      <c r="BK111" t="n">
+      <c r="BK111" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="BL111" t="n">
+      <c r="BL111" s="81" t="n">
         <v>15</v>
       </c>
     </row>
@@ -22786,13 +22786,13 @@
           <t>Fork Lightning</t>
         </is>
       </c>
-      <c r="BK112" t="n">
+      <c r="BK112" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="BL112" t="n">
+      <c r="BL112" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="BM112" t="n">
+      <c r="BM112" s="81" t="n">
         <v>2</v>
       </c>
     </row>
@@ -22848,13 +22848,13 @@
           <t>Jump Spark</t>
         </is>
       </c>
-      <c r="BK113" t="n">
+      <c r="BK113" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="BL113" t="n">
+      <c r="BL113" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="BM113" t="n">
+      <c r="BM113" s="81" t="n">
         <v>2</v>
       </c>
       <c r="BN113" s="46" t="inlineStr">
@@ -22915,13 +22915,13 @@
           <t>Power Grid</t>
         </is>
       </c>
-      <c r="BK114" t="n">
+      <c r="BK114" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="BL114" t="n">
+      <c r="BL114" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="BM114" t="n">
+      <c r="BM114" s="81" t="n">
         <v>2</v>
       </c>
       <c r="BN114" s="46" t="inlineStr">
@@ -23040,7 +23040,7 @@
           <t>Static Shock</t>
         </is>
       </c>
-      <c r="BP116" t="n">
+      <c r="BP116" s="81" t="n">
         <v>10</v>
       </c>
     </row>
@@ -23099,7 +23099,7 @@
       <c r="U117" s="57" t="n">
         <v>0.4</v>
       </c>
-      <c r="BP117" t="n">
+      <c r="BP117" s="81" t="n">
         <v>10</v>
       </c>
     </row>
@@ -23163,7 +23163,7 @@
       <c r="U118" s="57" t="n">
         <v>0.4</v>
       </c>
-      <c r="BP118" t="n">
+      <c r="BP118" s="81" t="n">
         <v>10</v>
       </c>
     </row>
@@ -23227,7 +23227,7 @@
       <c r="U119" s="57" t="n">
         <v>0.4</v>
       </c>
-      <c r="BP119" t="n">
+      <c r="BP119" s="81" t="n">
         <v>10</v>
       </c>
       <c r="BQ119" s="46" t="inlineStr">
@@ -23400,7 +23400,7 @@
       <c r="AB122" s="57" t="n">
         <v>10</v>
       </c>
-      <c r="BR122" t="n">
+      <c r="BR122" s="81" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23462,7 +23462,7 @@
       <c r="AC123" s="57" t="n">
         <v>15</v>
       </c>
-      <c r="BR123" t="n">
+      <c r="BR123" s="81" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23524,10 +23524,10 @@
       <c r="AC124" s="57" t="n">
         <v>15</v>
       </c>
-      <c r="BR124" t="n">
+      <c r="BR124" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="BS124" t="n">
+      <c r="BS124" s="81" t="n">
         <v>50</v>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9319,7 +9319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E132"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -11210,81 +11210,122 @@
           <t>FALCON ROOST</t>
         </is>
       </c>
-      <c r="C124" s="102" t="inlineStr">
-        <is>
-          <t>levers land with PLAN T65</t>
+      <c r="C124" s="102" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="81" t="inlineStr">
+        <is>
+          <t>Falcon speed</t>
+        </is>
+      </c>
+      <c r="B125" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="C125" s="81" t="inlineStr">
+        <is>
+          <t>studs/s a bird flies out and back (travel time)</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="99" t="inlineStr">
+      <c r="A126" s="81" t="inlineStr">
+        <is>
+          <t>Eagle dive x</t>
+        </is>
+      </c>
+      <c r="B126" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="C126" s="81" t="inlineStr">
+        <is>
+          <t>x the roost's damage, Eagle of the Peak's one bird</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="81" t="inlineStr">
+        <is>
+          <t>Falcon Bells mark</t>
+        </is>
+      </c>
+      <c r="B127" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="C127" s="81" t="inlineStr">
+        <is>
+          <t>s a struck dino stays marked (Falcon Bells)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="99" t="inlineStr">
         <is>
           <t>TAR PIT</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="100" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="100" t="inlineStr">
         <is>
           <t>Eruption every</t>
         </is>
       </c>
-      <c r="B127" s="101" t="n">
+      <c r="B130" s="101" t="n">
         <v>10</v>
       </c>
-      <c r="C127" s="102" t="inlineStr">
+      <c r="C130" s="102" t="inlineStr">
         <is>
           <t>s, DECISIONS #150</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="100" t="inlineStr">
-        <is>
-          <t>Eruption sizes</t>
-        </is>
-      </c>
-      <c r="B128" s="101" t="n">
-        <v>2</v>
-      </c>
-      <c r="C128" s="102" t="inlineStr">
-        <is>
-          <t>sizes dropped outright, Break resist ignored</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="99" t="inlineStr">
-        <is>
-          <t>HARPOON BALLISTA</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="100" t="inlineStr">
         <is>
+          <t>Eruption sizes</t>
+        </is>
+      </c>
+      <c r="B131" s="101" t="n">
+        <v>2</v>
+      </c>
+      <c r="C131" s="102" t="inlineStr">
+        <is>
+          <t>sizes dropped outright, Break resist ignored</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="99" t="inlineStr">
+        <is>
+          <t>HARPOON BALLISTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="100" t="inlineStr">
+        <is>
           <t>Tow Line every</t>
         </is>
       </c>
-      <c r="B131" s="101" t="n">
+      <c r="B134" s="101" t="n">
         <v>15</v>
       </c>
-      <c r="C131" s="102" t="inlineStr">
+      <c r="C134" s="102" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="100" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="100" t="inlineStr">
         <is>
           <t>Tow Line pull</t>
         </is>
       </c>
-      <c r="B132" s="101" t="n">
+      <c r="B135" s="101" t="n">
         <v>10</v>
       </c>
-      <c r="C132" s="102" t="inlineStr">
+      <c r="C135" s="102" t="inlineStr">
         <is>
           <t>studs back along the track (bosses)</t>
         </is>
@@ -11310,7 +11351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -11493,6 +11534,11 @@
           <t>Chains</t>
         </is>
       </c>
+      <c r="W4" s="81" t="inlineStr">
+        <is>
+          <t>Birds</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -12125,6 +12171,9 @@
         <is>
           <t>Yes</t>
         </is>
+      </c>
+      <c r="W16" s="81" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -12291,7 +12340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS169"/>
+  <dimension ref="A1:BY169"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -12784,6 +12833,36 @@
       <c r="BS4" s="104" t="inlineStr">
         <is>
           <t>Aura arc %</t>
+        </is>
+      </c>
+      <c r="BT4" s="81" t="inlineStr">
+        <is>
+          <t>Birds</t>
+        </is>
+      </c>
+      <c r="BU4" s="81" t="inlineStr">
+        <is>
+          <t>First dive x</t>
+        </is>
+      </c>
+      <c r="BV4" s="81" t="inlineStr">
+        <is>
+          <t>Eagle</t>
+        </is>
+      </c>
+      <c r="BW4" s="81" t="inlineStr">
+        <is>
+          <t>Murmuration</t>
+        </is>
+      </c>
+      <c r="BX4" s="81" t="inlineStr">
+        <is>
+          <t>Boss mark %</t>
+        </is>
+      </c>
+      <c r="BY4" s="81" t="inlineStr">
+        <is>
+          <t>Dive aura rate %</t>
         </is>
       </c>
     </row>
@@ -23559,7 +23638,7 @@
         <v/>
       </c>
       <c r="G125" s="57" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="H125" s="57" t="n">
         <v>1</v>
@@ -23612,7 +23691,7 @@
         <v/>
       </c>
       <c r="G126" s="57" t="n">
-        <v>1</v>
+        <v>3.61</v>
       </c>
       <c r="H126" s="57" t="n">
         <v>1</v>
@@ -23665,7 +23744,7 @@
         <v/>
       </c>
       <c r="G127" s="57" t="n">
-        <v>1</v>
+        <v>6.86</v>
       </c>
       <c r="H127" s="57" t="n">
         <v>1</v>
@@ -23689,6 +23768,12 @@
           <t>Power Dive</t>
         </is>
       </c>
+      <c r="BJ127" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU127" s="81" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="43" t="inlineStr">
@@ -23718,7 +23803,7 @@
         <v/>
       </c>
       <c r="G128" s="57" t="n">
-        <v>1</v>
+        <v>13.03</v>
       </c>
       <c r="H128" s="57" t="n">
         <v>1</v>
@@ -23742,6 +23827,17 @@
           <t>Iron Talons</t>
         </is>
       </c>
+      <c r="N128" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BJ128" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU128" s="81" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="43" t="inlineStr">
@@ -23771,7 +23867,7 @@
         <v/>
       </c>
       <c r="G129" s="57" t="n">
-        <v>1</v>
+        <v>13.03</v>
       </c>
       <c r="H129" s="57" t="n">
         <v>1</v>
@@ -23795,6 +23891,25 @@
           <t>Eagle of the Peak</t>
         </is>
       </c>
+      <c r="N129" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U129" s="81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BJ129" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU129" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BV129" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="43" t="inlineStr">
@@ -23827,7 +23942,7 @@
         <v>1</v>
       </c>
       <c r="H130" s="57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I130" s="57" t="n">
         <v>1</v>
@@ -23848,6 +23963,9 @@
           <t>Second Pair</t>
         </is>
       </c>
+      <c r="BT130" s="81" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="43" t="inlineStr">
@@ -23877,10 +23995,10 @@
         <v/>
       </c>
       <c r="G131" s="57" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H131" s="57" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="I131" s="57" t="n">
         <v>1</v>
@@ -23901,6 +24019,9 @@
           <t>Quick Return</t>
         </is>
       </c>
+      <c r="BT131" s="81" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="43" t="inlineStr">
@@ -23930,10 +24051,10 @@
         <v/>
       </c>
       <c r="G132" s="57" t="n">
-        <v>1</v>
+        <v>1.85</v>
       </c>
       <c r="H132" s="57" t="n">
-        <v>1</v>
+        <v>3.75</v>
       </c>
       <c r="I132" s="57" t="n">
         <v>1</v>
@@ -23954,6 +24075,9 @@
           <t>Flock of Six</t>
         </is>
       </c>
+      <c r="BT132" s="81" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="43" t="inlineStr">
@@ -23983,10 +24107,10 @@
         <v/>
       </c>
       <c r="G133" s="57" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="H133" s="57" t="n">
-        <v>1</v>
+        <v>3.75</v>
       </c>
       <c r="I133" s="57" t="n">
         <v>1</v>
@@ -24000,12 +24124,15 @@
         <v/>
       </c>
       <c r="L133" s="57" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M133" s="43" t="inlineStr">
         <is>
           <t>Wide Circle</t>
         </is>
+      </c>
+      <c r="BT133" s="81" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="134">
@@ -24036,10 +24163,10 @@
         <v/>
       </c>
       <c r="G134" s="57" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="H134" s="57" t="n">
-        <v>1</v>
+        <v>3.75</v>
       </c>
       <c r="I134" s="57" t="n">
         <v>1</v>
@@ -24053,11 +24180,19 @@
         <v/>
       </c>
       <c r="L134" s="57" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M134" s="43" t="inlineStr">
         <is>
           <t>Murmuration</t>
+        </is>
+      </c>
+      <c r="BT134" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="BW134" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -24089,7 +24224,7 @@
         <v/>
       </c>
       <c r="G135" s="57" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H135" s="57" t="n">
         <v>1</v>
@@ -24106,7 +24241,7 @@
         <v/>
       </c>
       <c r="L135" s="57" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M135" s="43" t="inlineStr">
         <is>
@@ -24142,7 +24277,7 @@
         <v/>
       </c>
       <c r="G136" s="57" t="n">
-        <v>1</v>
+        <v>1.69</v>
       </c>
       <c r="H136" s="57" t="n">
         <v>1</v>
@@ -24159,12 +24294,15 @@
         <v/>
       </c>
       <c r="L136" s="57" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M136" s="43" t="inlineStr">
         <is>
           <t>Falcon Bells</t>
         </is>
+      </c>
+      <c r="T136" s="81" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="137">
@@ -24195,7 +24333,7 @@
         <v/>
       </c>
       <c r="G137" s="57" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="H137" s="57" t="n">
         <v>1</v>
@@ -24212,12 +24350,18 @@
         <v/>
       </c>
       <c r="L137" s="57" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M137" s="43" t="inlineStr">
         <is>
           <t>Hooded Scout</t>
         </is>
+      </c>
+      <c r="T137" s="81" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX137" s="81" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="138">
@@ -24248,7 +24392,7 @@
         <v/>
       </c>
       <c r="G138" s="57" t="n">
-        <v>1</v>
+        <v>2.86</v>
       </c>
       <c r="H138" s="57" t="n">
         <v>1</v>
@@ -24265,12 +24409,21 @@
         <v/>
       </c>
       <c r="L138" s="57" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M138" s="43" t="inlineStr">
         <is>
           <t>Lure</t>
         </is>
+      </c>
+      <c r="T138" s="81" t="n">
+        <v>10</v>
+      </c>
+      <c r="W138" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX138" s="81" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="139">
@@ -24301,7 +24454,7 @@
         <v/>
       </c>
       <c r="G139" s="57" t="n">
-        <v>1</v>
+        <v>3.71</v>
       </c>
       <c r="H139" s="57" t="n">
         <v>1</v>
@@ -24318,12 +24471,24 @@
         <v/>
       </c>
       <c r="L139" s="57" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M139" s="43" t="inlineStr">
         <is>
           <t>Hunting Party</t>
         </is>
+      </c>
+      <c r="T139" s="81" t="n">
+        <v>10</v>
+      </c>
+      <c r="W139" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX139" s="81" t="n">
+        <v>25</v>
+      </c>
+      <c r="BY139" s="81" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="140">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9319,7 +9319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E135"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -11328,6 +11328,21 @@
       <c r="C135" s="102" t="inlineStr">
         <is>
           <t>studs back along the track (bosses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="100" t="inlineStr">
+        <is>
+          <t>Bolt width</t>
+        </is>
+      </c>
+      <c r="B136" s="101" t="n">
+        <v>3</v>
+      </c>
+      <c r="C136" s="102" t="inlineStr">
+        <is>
+          <t>studs from a bolt's line (Skewer) or a chain (Chain Harpoons) that still counts as hit</t>
         </is>
       </c>
     </row>
@@ -11351,7 +11366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -11539,6 +11554,11 @@
           <t>Birds</t>
         </is>
       </c>
+      <c r="X4" s="81" t="inlineStr">
+        <is>
+          <t>Harpoons</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -12318,6 +12338,11 @@
       </c>
       <c r="R18" s="27" t="n">
         <v>0</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -12340,7 +12365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY169"/>
+  <dimension ref="A1:CB169"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -12863,6 +12888,21 @@
       <c r="BY4" s="81" t="inlineStr">
         <is>
           <t>Dive aura rate %</t>
+        </is>
+      </c>
+      <c r="BZ4" s="81" t="inlineStr">
+        <is>
+          <t>Skewer</t>
+        </is>
+      </c>
+      <c r="CA4" s="81" t="inlineStr">
+        <is>
+          <t>Tow line</t>
+        </is>
+      </c>
+      <c r="CB4" s="81" t="inlineStr">
+        <is>
+          <t>Chain harpoons</t>
         </is>
       </c>
     </row>
@@ -25314,7 +25354,7 @@
         <v/>
       </c>
       <c r="G155" s="57" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="H155" s="57" t="n">
         <v>1</v>
@@ -25367,7 +25407,7 @@
         <v/>
       </c>
       <c r="G156" s="57" t="n">
-        <v>1</v>
+        <v>3.61</v>
       </c>
       <c r="H156" s="57" t="n">
         <v>1</v>
@@ -25420,7 +25460,7 @@
         <v/>
       </c>
       <c r="G157" s="57" t="n">
-        <v>1</v>
+        <v>6.86</v>
       </c>
       <c r="H157" s="57" t="n">
         <v>1</v>
@@ -25444,6 +25484,9 @@
           <t>Crusher Bolt</t>
         </is>
       </c>
+      <c r="BJ157" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="43" t="inlineStr">
@@ -25473,7 +25516,7 @@
         <v/>
       </c>
       <c r="G158" s="57" t="n">
-        <v>1</v>
+        <v>13.03</v>
       </c>
       <c r="H158" s="57" t="n">
         <v>1</v>
@@ -25497,6 +25540,14 @@
           <t>Great Harpoon</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BJ158" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="43" t="inlineStr">
@@ -25526,10 +25577,10 @@
         <v/>
       </c>
       <c r="G159" s="57" t="n">
-        <v>1</v>
+        <v>24.76</v>
       </c>
       <c r="H159" s="57" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="I159" s="57" t="n">
         <v>1</v>
@@ -25550,6 +25601,19 @@
           <t>Skewer</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BJ159" t="n">
+        <v>3</v>
+      </c>
+      <c r="BZ159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="43" t="inlineStr">
@@ -25579,7 +25643,7 @@
         <v/>
       </c>
       <c r="G160" s="57" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H160" s="57" t="n">
         <v>1</v>
@@ -25596,7 +25660,7 @@
         <v/>
       </c>
       <c r="L160" s="57" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M160" s="43" t="inlineStr">
         <is>
@@ -25632,7 +25696,7 @@
         <v/>
       </c>
       <c r="G161" s="57" t="n">
-        <v>1</v>
+        <v>1.69</v>
       </c>
       <c r="H161" s="57" t="n">
         <v>1</v>
@@ -25649,7 +25713,7 @@
         <v/>
       </c>
       <c r="L161" s="57" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M161" s="43" t="inlineStr">
         <is>
@@ -25685,7 +25749,7 @@
         <v/>
       </c>
       <c r="G162" s="57" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="H162" s="57" t="n">
         <v>1</v>
@@ -25702,12 +25766,15 @@
         <v/>
       </c>
       <c r="L162" s="57" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M162" s="43" t="inlineStr">
         <is>
           <t>Pin Down</t>
         </is>
+      </c>
+      <c r="U162" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -25738,7 +25805,7 @@
         <v/>
       </c>
       <c r="G163" s="57" t="n">
-        <v>1</v>
+        <v>2.86</v>
       </c>
       <c r="H163" s="57" t="n">
         <v>1</v>
@@ -25755,12 +25822,18 @@
         <v/>
       </c>
       <c r="L163" s="57" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M163" s="43" t="inlineStr">
         <is>
           <t>Reel In</t>
         </is>
+      </c>
+      <c r="U163" t="n">
+        <v>1</v>
+      </c>
+      <c r="W163" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="164">
@@ -25791,7 +25864,7 @@
         <v/>
       </c>
       <c r="G164" s="57" t="n">
-        <v>1</v>
+        <v>3.71</v>
       </c>
       <c r="H164" s="57" t="n">
         <v>1</v>
@@ -25808,11 +25881,22 @@
         <v/>
       </c>
       <c r="L164" s="57" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M164" s="43" t="inlineStr">
         <is>
           <t>Tow Line</t>
+        </is>
+      </c>
+      <c r="U164" t="n">
+        <v>1</v>
+      </c>
+      <c r="W164" t="n">
+        <v>6</v>
+      </c>
+      <c r="CA164" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -25868,6 +25952,9 @@
           <t>Twin Bolts</t>
         </is>
       </c>
+      <c r="Q165" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="43" t="inlineStr">
@@ -25900,7 +25987,7 @@
         <v>1</v>
       </c>
       <c r="H166" s="57" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="I166" s="57" t="n">
         <v>1</v>
@@ -25921,6 +26008,9 @@
           <t>Fast Crank</t>
         </is>
       </c>
+      <c r="Q166" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="43" t="inlineStr">
@@ -25950,10 +26040,10 @@
         <v/>
       </c>
       <c r="G167" s="57" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H167" s="57" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="I167" s="57" t="n">
         <v>1</v>
@@ -25974,6 +26064,9 @@
           <t>Spread Volley</t>
         </is>
       </c>
+      <c r="Q167" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="43" t="inlineStr">
@@ -26003,10 +26096,10 @@
         <v/>
       </c>
       <c r="G168" s="57" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H168" s="57" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="I168" s="57" t="n">
         <v>1</v>
@@ -26027,6 +26120,9 @@
           <t>Steam Crank</t>
         </is>
       </c>
+      <c r="Q168" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="43" t="inlineStr">
@@ -26056,10 +26152,10 @@
         <v/>
       </c>
       <c r="G169" s="57" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="H169" s="57" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="I169" s="57" t="n">
         <v>1</v>
@@ -26078,6 +26174,14 @@
       <c r="M169" s="43" t="inlineStr">
         <is>
           <t>Chain Harpoons</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>4</v>
+      </c>
+      <c r="CB169" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9319,7 +9319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E139"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -11294,53 +11294,103 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="100" t="inlineStr">
+        <is>
+          <t>Tar sink seconds</t>
+        </is>
+      </c>
+      <c r="B132" s="101" t="n">
+        <v>3</v>
+      </c>
+      <c r="C132" s="102" t="inlineStr">
+        <is>
+          <t>s a last-size dino stays in the tar before it sinks (Fast Sink lowers it)</t>
+        </is>
+      </c>
+    </row>
     <row r="133">
-      <c r="A133" s="99" t="inlineStr">
-        <is>
-          <t>HARPOON BALLISTA</t>
+      <c r="A133" s="100" t="inlineStr">
+        <is>
+          <t>Tar Tracks length</t>
+        </is>
+      </c>
+      <c r="B133" s="101" t="n">
+        <v>12</v>
+      </c>
+      <c r="C133" s="102" t="inlineStr">
+        <is>
+          <t>studs of track past the pool that Tar Tracks' footprints cover</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="100" t="inlineStr">
         <is>
+          <t>Tar Tracks seconds</t>
+        </is>
+      </c>
+      <c r="B134" s="101" t="n">
+        <v>3</v>
+      </c>
+      <c r="C134" s="102" t="inlineStr">
+        <is>
+          <t>s the footprints stay after a dino walks out</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="100" t="n"/>
+      <c r="B135" s="101" t="n"/>
+      <c r="C135" s="102" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="99" t="inlineStr">
+        <is>
+          <t>HARPOON BALLISTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="100" t="inlineStr">
+        <is>
           <t>Tow Line every</t>
         </is>
       </c>
-      <c r="B134" s="101" t="n">
+      <c r="B137" s="101" t="n">
         <v>15</v>
       </c>
-      <c r="C134" s="102" t="inlineStr">
+      <c r="C137" s="102" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="100" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="100" t="inlineStr">
         <is>
           <t>Tow Line pull</t>
         </is>
       </c>
-      <c r="B135" s="101" t="n">
+      <c r="B138" s="101" t="n">
         <v>10</v>
       </c>
-      <c r="C135" s="102" t="inlineStr">
+      <c r="C138" s="102" t="inlineStr">
         <is>
           <t>studs back along the track (bosses)</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="100" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="100" t="inlineStr">
         <is>
           <t>Bolt width</t>
         </is>
       </c>
-      <c r="B136" s="101" t="n">
+      <c r="B139" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="C136" s="102" t="inlineStr">
+      <c r="C139" s="102" t="inlineStr">
         <is>
           <t>studs from a bolt's line (Skewer) or a chain (Chain Harpoons) that still counts as hit</t>
         </is>
@@ -12339,7 +12389,7 @@
       <c r="R18" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X18" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -12365,7 +12415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB169"/>
+  <dimension ref="A1:CH169"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -12903,6 +12953,36 @@
       <c r="CB4" s="81" t="inlineStr">
         <is>
           <t>Chain harpoons</t>
+        </is>
+      </c>
+      <c r="CC4" s="81" t="inlineStr">
+        <is>
+          <t>Sink seconds</t>
+        </is>
+      </c>
+      <c r="CD4" s="81" t="inlineStr">
+        <is>
+          <t>Sink cash</t>
+        </is>
+      </c>
+      <c r="CE4" s="81" t="inlineStr">
+        <is>
+          <t>Sink chest cash</t>
+        </is>
+      </c>
+      <c r="CF4" s="81" t="inlineStr">
+        <is>
+          <t>Eruption</t>
+        </is>
+      </c>
+      <c r="CG4" s="81" t="inlineStr">
+        <is>
+          <t>Tracks slow %</t>
+        </is>
+      </c>
+      <c r="CH4" s="81" t="inlineStr">
+        <is>
+          <t>Aura vs slowed %</t>
         </is>
       </c>
     </row>
@@ -24583,6 +24663,9 @@
           <t>Thick Tar</t>
         </is>
       </c>
+      <c r="AE140" s="81" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="43" t="inlineStr">
@@ -24629,12 +24712,15 @@
         <v/>
       </c>
       <c r="L141" s="57" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M141" s="43" t="inlineStr">
         <is>
           <t>Wide Pool</t>
         </is>
+      </c>
+      <c r="AE141" s="81" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="142">
@@ -24682,12 +24768,18 @@
         <v/>
       </c>
       <c r="L142" s="57" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M142" s="43" t="inlineStr">
         <is>
           <t>Fast Sink</t>
         </is>
+      </c>
+      <c r="AE142" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="CC142" s="81" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="143">
@@ -24735,12 +24827,21 @@
         <v/>
       </c>
       <c r="L143" s="57" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M143" s="43" t="inlineStr">
         <is>
           <t>Clinging Tar</t>
         </is>
+      </c>
+      <c r="AE143" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF143" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC143" s="81" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="144">
@@ -24788,12 +24889,21 @@
         <v/>
       </c>
       <c r="L144" s="57" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="M144" s="43" t="inlineStr">
         <is>
           <t>Tar Lake</t>
         </is>
+      </c>
+      <c r="AE144" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF144" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC144" s="81" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="145">
@@ -24848,6 +24958,9 @@
           <t>Warm Tar</t>
         </is>
       </c>
+      <c r="X145" s="81" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="43" t="inlineStr">
@@ -24901,6 +25014,9 @@
           <t>Simmer</t>
         </is>
       </c>
+      <c r="X146" s="81" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="43" t="inlineStr">
@@ -24954,6 +25070,9 @@
           <t>Boiling Pit</t>
         </is>
       </c>
+      <c r="X147" s="81" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="43" t="inlineStr">
@@ -25007,6 +25126,12 @@
           <t>Tar Fire</t>
         </is>
       </c>
+      <c r="X148" s="81" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y148" s="81" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="43" t="inlineStr">
@@ -25060,6 +25185,17 @@
           <t>Eruption</t>
         </is>
       </c>
+      <c r="X149" s="81" t="n">
+        <v>150</v>
+      </c>
+      <c r="Y149" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF149" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="43" t="inlineStr">
@@ -25113,6 +25249,9 @@
           <t>Pick and Shovel</t>
         </is>
       </c>
+      <c r="CD150" s="81" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="43" t="inlineStr">
@@ -25166,6 +25305,9 @@
           <t>Fossil Hunter</t>
         </is>
       </c>
+      <c r="CD151" s="81" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="43" t="inlineStr">
@@ -25219,6 +25361,12 @@
           <t>Lucky Finds</t>
         </is>
       </c>
+      <c r="CD152" s="81" t="n">
+        <v>25</v>
+      </c>
+      <c r="CE152" s="81" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="43" t="inlineStr">
@@ -25272,6 +25420,15 @@
           <t>Tar Tracks</t>
         </is>
       </c>
+      <c r="CD153" s="81" t="n">
+        <v>25</v>
+      </c>
+      <c r="CE153" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="CG153" s="81" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="43" t="inlineStr">
@@ -25325,6 +25482,18 @@
           <t>Tar Totem</t>
         </is>
       </c>
+      <c r="CD154" s="81" t="n">
+        <v>25</v>
+      </c>
+      <c r="CE154" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="CG154" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="CH154" s="81" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="43" t="inlineStr">
@@ -25484,7 +25653,7 @@
           <t>Crusher Bolt</t>
         </is>
       </c>
-      <c r="BJ157" t="n">
+      <c r="BJ157" s="81" t="n">
         <v>2</v>
       </c>
     </row>
@@ -25540,12 +25709,12 @@
           <t>Great Harpoon</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr">
+      <c r="N158" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="BJ158" t="n">
+      <c r="BJ158" s="81" t="n">
         <v>3</v>
       </c>
     </row>
@@ -25601,15 +25770,15 @@
           <t>Skewer</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr">
+      <c r="N159" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="BJ159" t="n">
+      <c r="BJ159" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="BZ159" t="inlineStr">
+      <c r="BZ159" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -25773,7 +25942,7 @@
           <t>Pin Down</t>
         </is>
       </c>
-      <c r="U162" t="n">
+      <c r="U162" s="81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25829,10 +25998,10 @@
           <t>Reel In</t>
         </is>
       </c>
-      <c r="U163" t="n">
-        <v>1</v>
-      </c>
-      <c r="W163" t="n">
+      <c r="U163" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="W163" s="81" t="n">
         <v>6</v>
       </c>
     </row>
@@ -25888,13 +26057,13 @@
           <t>Tow Line</t>
         </is>
       </c>
-      <c r="U164" t="n">
-        <v>1</v>
-      </c>
-      <c r="W164" t="n">
+      <c r="U164" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="W164" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="CA164" t="inlineStr">
+      <c r="CA164" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -25952,7 +26121,7 @@
           <t>Twin Bolts</t>
         </is>
       </c>
-      <c r="Q165" t="n">
+      <c r="Q165" s="81" t="n">
         <v>2</v>
       </c>
     </row>
@@ -26008,7 +26177,7 @@
           <t>Fast Crank</t>
         </is>
       </c>
-      <c r="Q166" t="n">
+      <c r="Q166" s="81" t="n">
         <v>2</v>
       </c>
     </row>
@@ -26064,7 +26233,7 @@
           <t>Spread Volley</t>
         </is>
       </c>
-      <c r="Q167" t="n">
+      <c r="Q167" s="81" t="n">
         <v>3</v>
       </c>
     </row>
@@ -26120,7 +26289,7 @@
           <t>Steam Crank</t>
         </is>
       </c>
-      <c r="Q168" t="n">
+      <c r="Q168" s="81" t="n">
         <v>3</v>
       </c>
     </row>
@@ -26176,10 +26345,10 @@
           <t>Chain Harpoons</t>
         </is>
       </c>
-      <c r="Q169" t="n">
+      <c r="Q169" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="CB169" t="inlineStr">
+      <c r="CB169" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="B130" s="101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C130" s="102" t="inlineStr">
         <is>
@@ -12111,10 +12111,10 @@
         </is>
       </c>
       <c r="C15" s="27" t="n">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="D15" s="91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>1</v>
@@ -12335,13 +12335,13 @@
         </is>
       </c>
       <c r="C18" s="27" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="D18" s="91" t="n">
         <v>12</v>
       </c>
       <c r="E18" s="30" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>1</v>
@@ -23987,7 +23987,7 @@
         <v/>
       </c>
       <c r="G129" s="57" t="n">
-        <v>13.03</v>
+        <v>12</v>
       </c>
       <c r="H129" s="57" t="n">
         <v>1</v>
@@ -24283,7 +24283,7 @@
         <v/>
       </c>
       <c r="G134" s="57" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="H134" s="57" t="n">
         <v>3.75</v>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="B130" s="101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C130" s="102" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         </is>
       </c>
       <c r="B132" s="101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C132" s="102" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="B16" s="43" t="inlineStr">
         <is>
-          <t>Birds of prey: huge radius, can't be damaged</t>
+          <t>Birds of prey: huge range, can't be damaged</t>
         </is>
       </c>
       <c r="C16" s="27" t="n">
@@ -23743,7 +23743,7 @@
       </c>
       <c r="C125" s="43" t="inlineStr">
         <is>
-          <t>raw damage, pierce-through</t>
+          <t>raw damage, pierces armour</t>
         </is>
       </c>
       <c r="D125" s="56" t="n">
@@ -23796,7 +23796,7 @@
       </c>
       <c r="C126" s="43" t="inlineStr">
         <is>
-          <t>raw damage, pierce-through</t>
+          <t>raw damage, pierces armour</t>
         </is>
       </c>
       <c r="D126" s="56" t="n">
@@ -23849,7 +23849,7 @@
       </c>
       <c r="C127" s="43" t="inlineStr">
         <is>
-          <t>raw damage, pierce-through</t>
+          <t>raw damage, pierces armour</t>
         </is>
       </c>
       <c r="D127" s="56" t="n">
@@ -23908,7 +23908,7 @@
       </c>
       <c r="C128" s="43" t="inlineStr">
         <is>
-          <t>raw damage, pierce-through</t>
+          <t>raw damage, pierces armour</t>
         </is>
       </c>
       <c r="D128" s="56" t="n">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="C129" s="43" t="inlineStr">
         <is>
-          <t>raw damage, pierce-through</t>
+          <t>raw damage, pierces armour</t>
         </is>
       </c>
       <c r="D129" s="56" t="n">
@@ -24779,7 +24779,7 @@
         <v>35</v>
       </c>
       <c r="CC142" s="81" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="143">
@@ -24841,7 +24841,7 @@
         <v>3</v>
       </c>
       <c r="CC143" s="81" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144">
@@ -24903,7 +24903,7 @@
         <v>3</v>
       </c>
       <c r="CC144" s="81" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
@@ -25186,7 +25186,7 @@
         </is>
       </c>
       <c r="X149" s="81" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="Y149" s="81" t="n">
         <v>2</v>
@@ -25250,7 +25250,7 @@
         </is>
       </c>
       <c r="CD150" s="81" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -25306,7 +25306,7 @@
         </is>
       </c>
       <c r="CD151" s="81" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152">
@@ -25362,10 +25362,10 @@
         </is>
       </c>
       <c r="CD152" s="81" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="CE152" s="81" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="153">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -21,6 +21,7 @@
     <sheet name="Bounties" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Mastery Perks" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Cosmetics" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Arenas" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -9313,13 +9314,189 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="90" min="1" max="1"/>
+    <col width="24" customWidth="1" style="90" min="2" max="2"/>
+    <col width="10" customWidth="1" style="90" min="3" max="3"/>
+    <col width="20" customWidth="1" style="90" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ARENAS — ranked Trophy gates (names are placeholders until the Dino review, T74)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>One row per arena, lowest first. Floor = the Trophies that reach it; you never drop below the floor of the best arena you've reached, and never below 0 (DECISIONS #218). Floors run up from 0. Reward = a Cosmetics Id unlocked the first time you reach it, or blank (cosmetic or title only, never power). Keys are saved in profiles: never rename one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Floor</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ARENA_1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Arena 1</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ARENA_2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arena 2</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ARENA_3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Arena 3</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ARENA_4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arena 4</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ARENA_5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Arena 5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ARENA_6</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Arena 6</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ARENA_7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Arena 7</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ARENA_8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Arena 8</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E139"/>
+  <dimension ref="A1:E170"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -11396,6 +11573,435 @@
         </is>
       </c>
     </row>
+    <row r="140"/>
+    <row r="141">
+      <c r="A141" s="99" t="inlineStr">
+        <is>
+          <t>BATTLE MODES</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="100" t="inlineStr">
+        <is>
+          <t>Battle build time</t>
+        </is>
+      </c>
+      <c r="B142" s="101" t="n">
+        <v>30</v>
+      </c>
+      <c r="C142" s="102" t="inlineStr">
+        <is>
+          <t>s, the one build phase before the rounds (no per-side Start; DECISIONS #210)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="100" t="inlineStr">
+        <is>
+          <t>Battle round time</t>
+        </is>
+      </c>
+      <c r="B143" s="101" t="n">
+        <v>60</v>
+      </c>
+      <c r="C143" s="102" t="inlineStr">
+        <is>
+          <t>s after a round starts, the next starts for every live side even if not all cleared (lockstep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="100" t="inlineStr">
+        <is>
+          <t>Battle side density</t>
+        </is>
+      </c>
+      <c r="B144" s="101" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C144" s="102" t="inlineStr">
+        <is>
+          <t>x dinos per side in Royale and 3-side Team, so every track fits the live cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="100" t="inlineStr">
+        <is>
+          <t>PvP tower damage</t>
+        </is>
+      </c>
+      <c r="B145" s="101" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C145" s="102" t="inlineStr">
+        <is>
+          <t>x a hunter's damage on an enemy side's tower (0 &lt; x &lt;= 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="100" t="inlineStr">
+        <is>
+          <t>PvP hunter damage</t>
+        </is>
+      </c>
+      <c r="B146" s="101" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C146" s="102" t="inlineStr">
+        <is>
+          <t>x a hunter's damage on an enemy hunter (0 &lt; x &lt;= 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="100" t="inlineStr">
+        <is>
+          <t>Spawn shield</t>
+        </is>
+      </c>
+      <c r="B147" s="101" t="n">
+        <v>3</v>
+      </c>
+      <c r="C147" s="102" t="inlineStr">
+        <is>
+          <t>s of no damage after a battle respawn</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="100" t="inlineStr">
+        <is>
+          <t>Overtime HP step</t>
+        </is>
+      </c>
+      <c r="B148" s="101" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C148" s="102" t="inlineStr">
+        <is>
+          <t>x dino HP per Team overtime repeat after the last round, compounding</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="100" t="inlineStr">
+        <is>
+          <t>Survivor bonus</t>
+        </is>
+      </c>
+      <c r="B149" s="101" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C149" s="102" t="inlineStr">
+        <is>
+          <t>x Bones added for the last Royale hunter alive</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="100" t="inlineStr">
+        <is>
+          <t>Raid bones</t>
+        </is>
+      </c>
+      <c r="B150" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="C150" s="102" t="inlineStr">
+        <is>
+          <t>Bones for knocking out an enemy tower</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="100" t="inlineStr">
+        <is>
+          <t>Team min players</t>
+        </is>
+      </c>
+      <c r="B151" s="101" t="n">
+        <v>2</v>
+      </c>
+      <c r="C151" s="102" t="inlineStr">
+        <is>
+          <t>players for a Team Battle (1v1 allowed); 3 sides need 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="100" t="inlineStr">
+        <is>
+          <t>Royale min players</t>
+        </is>
+      </c>
+      <c r="B152" s="101" t="n">
+        <v>3</v>
+      </c>
+      <c r="C152" s="102" t="inlineStr">
+        <is>
+          <t>players for a competitive Royale (72/23/5 needs 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="100" t="inlineStr">
+        <is>
+          <t>Battle max players</t>
+        </is>
+      </c>
+      <c r="B153" s="101" t="n">
+        <v>10</v>
+      </c>
+      <c r="C153" s="102" t="inlineStr">
+        <is>
+          <t>players in one battle (Royale: one side each)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="100" t="inlineStr">
+        <is>
+          <t>Competitive buy-in</t>
+        </is>
+      </c>
+      <c r="B154" s="101" t="n">
+        <v>15</v>
+      </c>
+      <c r="C154" s="102" t="inlineStr">
+        <is>
+          <t>Amber each player stakes (exporter: 10-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="100" t="inlineStr">
+        <is>
+          <t>Team win payout</t>
+        </is>
+      </c>
+      <c r="B155" s="101" t="n">
+        <v>50</v>
+      </c>
+      <c r="C155" s="102" t="inlineStr">
+        <is>
+          <t>Amber, casual Team Battle, each winner (competitive adds the pot share)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="100" t="inlineStr">
+        <is>
+          <t>Team loss payout</t>
+        </is>
+      </c>
+      <c r="B156" s="101" t="n">
+        <v>5</v>
+      </c>
+      <c r="C156" s="102" t="inlineStr">
+        <is>
+          <t>Amber, casual Team Battle, each loser</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="100" t="inlineStr">
+        <is>
+          <t>Royale 1st payout</t>
+        </is>
+      </c>
+      <c r="B157" s="101" t="n">
+        <v>60</v>
+      </c>
+      <c r="C157" s="102" t="inlineStr">
+        <is>
+          <t>Amber, casual Royale 1st (competitive adds the pot share)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="100" t="inlineStr">
+        <is>
+          <t>Royale 2nd payout</t>
+        </is>
+      </c>
+      <c r="B158" s="101" t="n">
+        <v>30</v>
+      </c>
+      <c r="C158" s="102" t="inlineStr">
+        <is>
+          <t>Amber, casual Royale 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="100" t="inlineStr">
+        <is>
+          <t>Royale 3rd payout</t>
+        </is>
+      </c>
+      <c r="B159" s="101" t="n">
+        <v>10</v>
+      </c>
+      <c r="C159" s="102" t="inlineStr">
+        <is>
+          <t>Amber, casual Royale 3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="100" t="inlineStr">
+        <is>
+          <t>Royale rest payout</t>
+        </is>
+      </c>
+      <c r="B160" s="101" t="n">
+        <v>5</v>
+      </c>
+      <c r="C160" s="102" t="inlineStr">
+        <is>
+          <t>Amber, casual Royale 4th and below</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="100" t="inlineStr">
+        <is>
+          <t>Royale pot 1st</t>
+        </is>
+      </c>
+      <c r="B161" s="101" t="n">
+        <v>72</v>
+      </c>
+      <c r="C161" s="102" t="inlineStr">
+        <is>
+          <t>% of the competitive pot, rounded down (the three add to 100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="100" t="inlineStr">
+        <is>
+          <t>Royale pot 2nd</t>
+        </is>
+      </c>
+      <c r="B162" s="101" t="n">
+        <v>23</v>
+      </c>
+      <c r="C162" s="102" t="inlineStr">
+        <is>
+          <t>% of the pot, rounded down</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="100" t="inlineStr">
+        <is>
+          <t>Royale pot 3rd</t>
+        </is>
+      </c>
+      <c r="B163" s="101" t="n">
+        <v>5</v>
+      </c>
+      <c r="C163" s="102" t="inlineStr">
+        <is>
+          <t>% of the pot, rounded down; unused shares go to 1st</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="100" t="inlineStr">
+        <is>
+          <t>Team win trophies</t>
+        </is>
+      </c>
+      <c r="B164" s="101" t="n">
+        <v>30</v>
+      </c>
+      <c r="C164" s="102" t="inlineStr">
+        <is>
+          <t>Trophies each winner gains (competitive only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="100" t="inlineStr">
+        <is>
+          <t>Team loss trophies</t>
+        </is>
+      </c>
+      <c r="B165" s="101" t="n">
+        <v>-30</v>
+      </c>
+      <c r="C165" s="102" t="inlineStr">
+        <is>
+          <t>Trophies each loser gains (negative = lost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="100" t="inlineStr">
+        <is>
+          <t>Royale 1st trophies</t>
+        </is>
+      </c>
+      <c r="B166" s="101" t="n">
+        <v>30</v>
+      </c>
+      <c r="C166" s="102" t="inlineStr">
+        <is>
+          <t>Trophies 1st gains; the rest of the top third less, the middle 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="100" t="inlineStr">
+        <is>
+          <t>Royale last trophies</t>
+        </is>
+      </c>
+      <c r="B167" s="101" t="n">
+        <v>-20</v>
+      </c>
+      <c r="C167" s="102" t="inlineStr">
+        <is>
+          <t>Trophies last gains (negative = lost); the rest of the bottom third less</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="100" t="inlineStr">
+        <is>
+          <t>Competitive edge max</t>
+        </is>
+      </c>
+      <c r="B168" s="101" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C168" s="102" t="inlineStr">
+        <is>
+          <t>x most a maxed hunter's perks may add over mastery 0 (PvP parity bar, T84)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="100" t="inlineStr">
+        <is>
+          <t>Perk parity band</t>
+        </is>
+      </c>
+      <c r="B169" s="101" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C169" s="102" t="inlineStr">
+        <is>
+          <t>x every hero's perks within this of each other at mastery 10/15/20 (T84)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9366,122 +9366,122 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="81" t="inlineStr">
         <is>
           <t>ARENA_1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="81" t="inlineStr">
         <is>
           <t>Arena 1</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="81" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>ARENA_2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="81" t="inlineStr">
         <is>
           <t>Arena 2</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="81" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="81" t="inlineStr">
         <is>
           <t>ARENA_3</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="81" t="inlineStr">
         <is>
           <t>Arena 3</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="81" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="81" t="inlineStr">
         <is>
           <t>ARENA_4</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="81" t="inlineStr">
         <is>
           <t>Arena 4</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="81" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>ARENA_5</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="81" t="inlineStr">
         <is>
           <t>Arena 5</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="81" t="n">
         <v>1500</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="81" t="inlineStr">
         <is>
           <t>ARENA_6</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="81" t="inlineStr">
         <is>
           <t>Arena 6</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="81" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="81" t="inlineStr">
         <is>
           <t>ARENA_7</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="81" t="inlineStr">
         <is>
           <t>Arena 7</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="81" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="81" t="inlineStr">
         <is>
           <t>ARENA_8</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="81" t="inlineStr">
         <is>
           <t>Arena 8</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="81" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -11573,7 +11573,6 @@
         </is>
       </c>
     </row>
-    <row r="140"/>
     <row r="141">
       <c r="A141" s="99" t="inlineStr">
         <is>
@@ -12001,7 +12000,21 @@
         </is>
       </c>
     </row>
-    <row r="170"/>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Battle round break</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>5</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>s after the last living side clears a round before the next starts (battles only; the round time still caps it, DECISIONS #232)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9332,7 +9332,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>ARENAS — ranked Trophy gates (names are placeholders until the Dino review, T74)</t>
+          <t>ARENAS — ranked Trophy gates (names: Dino review Round 16, DECISIONS #229; PLAN T81)</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="B5" s="81" t="inlineStr">
         <is>
-          <t>Arena 1</t>
+          <t>Fern Gully</t>
         </is>
       </c>
       <c r="C5" s="81" t="n">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="B6" s="81" t="inlineStr">
         <is>
-          <t>Arena 2</t>
+          <t>Raptor Ridge</t>
         </is>
       </c>
       <c r="C6" s="81" t="n">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="B7" s="81" t="inlineStr">
         <is>
-          <t>Arena 3</t>
+          <t>Muddy Springs</t>
         </is>
       </c>
       <c r="C7" s="81" t="n">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="B8" s="81" t="inlineStr">
         <is>
-          <t>Arena 4</t>
+          <t>Horn Canyon</t>
         </is>
       </c>
       <c r="C8" s="81" t="n">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="B9" s="81" t="inlineStr">
         <is>
-          <t>Arena 5</t>
+          <t>Volcano Rim</t>
         </is>
       </c>
       <c r="C9" s="81" t="n">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="B10" s="81" t="inlineStr">
         <is>
-          <t>Arena 6</t>
+          <t>Sky Cliffs</t>
         </is>
       </c>
       <c r="C10" s="81" t="n">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="B11" s="81" t="inlineStr">
         <is>
-          <t>Arena 7</t>
+          <t>Misty Jungle</t>
         </is>
       </c>
       <c r="C11" s="81" t="n">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="B12" s="81" t="inlineStr">
         <is>
-          <t>Arena 8</t>
+          <t>Rex Kingdom</t>
         </is>
       </c>
       <c r="C12" s="81" t="n">
@@ -12001,15 +12001,15 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
+      <c r="A170" s="81" t="inlineStr">
         <is>
           <t>Battle round break</t>
         </is>
       </c>
-      <c r="B170" t="n">
+      <c r="B170" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="C170" s="81" t="inlineStr">
         <is>
           <t>s after the last living side clears a round before the next starts (battles only; the round time still caps it, DECISIONS #232)</t>
         </is>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -5665,11 +5665,11 @@
       </c>
       <c r="D7" s="43" t="inlineStr">
         <is>
-          <t>Rally Cry reaches 5 studs further</t>
+          <t>Rally Cry reaches 6 studs further</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -5688,11 +5688,11 @@
       </c>
       <c r="D8" s="43" t="inlineStr">
         <is>
-          <t>Rally Cry lasts 3s longer</t>
+          <t>Rally Cry lasts 3.5s longer</t>
         </is>
       </c>
       <c r="E8" s="27" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9">
@@ -5711,11 +5711,11 @@
       </c>
       <c r="D9" s="43" t="inlineStr">
         <is>
-          <t>Flare Strike reaches 1.5 studs further</t>
+          <t>Flare Strike reaches 2.5 studs further</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -5760,11 +5760,11 @@
       </c>
       <c r="D11" s="43" t="inlineStr">
         <is>
-          <t>Triage Kit reaches 4 studs further</t>
+          <t>Triage Kit reaches 5 studs further</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -5783,11 +5783,11 @@
       </c>
       <c r="D12" s="43" t="inlineStr">
         <is>
-          <t>Triage Kit heals 10 more HP</t>
+          <t>Triage Kit heals 14 more HP</t>
         </is>
       </c>
       <c r="G12" s="27" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9496,7 +9496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E170"/>
+  <dimension ref="A1:E171"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -12012,6 +12012,21 @@
       <c r="C170" s="81" t="inlineStr">
         <is>
           <t>s after the last living side clears a round before the next starts (battles only; the round time still caps it, DECISIONS #232)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="81" t="inlineStr">
+        <is>
+          <t>Battle results time</t>
+        </is>
+      </c>
+      <c r="B171" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="C171" s="81" t="inlineStr">
+        <is>
+          <t>s the battle results card shows before everyone returns home (battles only; co-op keeps Results time, DECISIONS #236)</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -17626,7 +17626,7 @@
         <v/>
       </c>
       <c r="G49" s="57" t="n">
-        <v>24.76</v>
+        <v>34</v>
       </c>
       <c r="H49" s="57" t="n">
         <v>1</v>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -11602,11 +11602,11 @@
         </is>
       </c>
       <c r="B143" s="101" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="C143" s="102" t="inlineStr">
         <is>
-          <t>s after a round starts, the next starts for every live side even if not all cleared (lockstep)</t>
+          <t>s after a round starts, the next starts for every live side even if not all cleared (lockstep; ≥ the longest Normal round, 119 s)</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9496,7 +9496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E171"/>
+  <dimension ref="A1:E182"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -11602,11 +11602,11 @@
         </is>
       </c>
       <c r="B143" s="101" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="C143" s="102" t="inlineStr">
         <is>
-          <t>s after a round starts, the next starts for every live side even if not all cleared (lockstep; ≥ the longest Normal round, 119 s)</t>
+          <t>s after a round starts, the next starts for every live side even if not all cleared (lockstep; ≥ the longest paced Normal and Chaos round, 56 s; DECISIONS #251)</t>
         </is>
       </c>
     </row>
@@ -12027,6 +12027,171 @@
       <c r="C171" s="81" t="inlineStr">
         <is>
           <t>s the battle results card shows before everyone returns home (battles only; co-op keeps Results time, DECISIONS #236)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="81" t="inlineStr">
+        <is>
+          <t>Round pace</t>
+        </is>
+      </c>
+      <c r="B172" s="81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C172" s="81" t="inlineStr">
+        <is>
+          <t>x every round's spawn gap; dino HP x the pace factor (pace·S + W) / (S + W), S = enemies x spawn gap, W = Track walk seconds / difficulty speed; every mode (DECISIONS #250)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="81" t="inlineStr">
+        <is>
+          <t>Track walk seconds</t>
+        </is>
+      </c>
+      <c r="B173" s="81" t="n">
+        <v>14</v>
+      </c>
+      <c r="C173" s="81" t="inlineStr">
+        <is>
+          <t>s, the Rounds sheet's round length = enemies x spawn gap + this; W in the pace factor and the models (DECISIONS #250)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="81" t="inlineStr">
+        <is>
+          <t>Casual round step</t>
+        </is>
+      </c>
+      <c r="B174" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="C174" s="81" t="inlineStr">
+        <is>
+          <t>casual battles play every 3rd round, ending at the last: 1, 4, 7 … 40 (DECISIONS #251)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="81" t="inlineStr">
+        <is>
+          <t>Ranked round step</t>
+        </is>
+      </c>
+      <c r="B175" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="C175" s="81" t="inlineStr">
+        <is>
+          <t>Ranked battles play every 2nd round: 2, 4 … 40 (DECISIONS #251)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="81" t="inlineStr">
+        <is>
+          <t>Casual match cap</t>
+        </is>
+      </c>
+      <c r="B176" s="81" t="n">
+        <v>900</v>
+      </c>
+      <c r="C176" s="81" t="inlineStr">
+        <is>
+          <t>s from Building: casual battles end here at the latest, the tie-break chain ranks everyone standing (DECISIONS #252)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="81" t="inlineStr">
+        <is>
+          <t>Ranked match cap</t>
+        </is>
+      </c>
+      <c r="B177" s="81" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C177" s="81" t="inlineStr">
+        <is>
+          <t>s from Building, Final Stampede included (DECISIONS #252)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="81" t="inlineStr">
+        <is>
+          <t>Clock warning</t>
+        </is>
+      </c>
+      <c r="B178" s="81" t="n">
+        <v>60</v>
+      </c>
+      <c r="C178" s="81" t="inlineStr">
+        <is>
+          <t>s before the match cap: a warning banner (DECISIONS #252)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="81" t="inlineStr">
+        <is>
+          <t>Late join cash x</t>
+        </is>
+      </c>
+      <c r="B179" s="81" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C179" s="81" t="inlineStr">
+        <is>
+          <t>x one more hunter's expected income for the rounds before the join; at least Starting cash per extra player (DECISIONS #254)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="81" t="inlineStr">
+        <is>
+          <t>Late join last round</t>
+        </is>
+      </c>
+      <c r="B180" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="C180" s="81" t="inlineStr">
+        <is>
+          <t>casual battles seat joiners until the end of this round (DECISIONS #254)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="81" t="inlineStr">
+        <is>
+          <t>Bone Rush spare plots</t>
+        </is>
+      </c>
+      <c r="B181" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="C181" s="81" t="inlineStr">
+        <is>
+          <t>extra Bone Rush plots for late joiners, within Battle max players (DECISIONS #254)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="81" t="inlineStr">
+        <is>
+          <t>Co-op length max</t>
+        </is>
+      </c>
+      <c r="B182" s="81" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C182" s="81" t="inlineStr">
+        <is>
+          <t>s, model bar only (value.py --pacing: Normal solo, 40 rounds with breaks); not a game clock (DECISIONS #250)</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9496,7 +9496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E182"/>
+  <dimension ref="A1:E184"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="C172" s="81" t="inlineStr">
         <is>
-          <t>x every round's spawn gap; dino HP x the pace factor (pace·S + W) / (S + W), S = enemies x spawn gap, W = Track walk seconds / difficulty speed; every mode (DECISIONS #250)</t>
+          <t>x every species' count per round (half up, min 1; bosses kept), spawn gaps unchanged; dino HP x (unpaced round EHP x the pace factor (pace·S + W) / (S + W)) / paced round EHP, kill cash x the count ratio; S = enemies x spawn gap, W = Track walk seconds / difficulty speed; every mode (DECISIONS #250, #258)</t>
         </is>
       </c>
     </row>
@@ -12192,6 +12192,36 @@
       <c r="C182" s="81" t="inlineStr">
         <is>
           <t>s, model bar only (value.py --pacing: Normal solo, 40 rounds with breaks); not a game clock (DECISIONS #250)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="81" t="inlineStr">
+        <is>
+          <t>Battle crowd x</t>
+        </is>
+      </c>
+      <c r="B183" s="81" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C183" s="81" t="inlineStr">
+        <is>
+          <t>x every battle round's dino counts on top of Round pace (bosses kept); HP and kill cash scaled so round EHP and cash are unchanged; keeps peak live dinos under Max concurrent enemies (DECISIONS #258)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="81" t="inlineStr">
+        <is>
+          <t>Ability tempo</t>
+        </is>
+      </c>
+      <c r="B184" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="C184" s="81" t="inlineStr">
+        <is>
+          <t>hero ability cooldowns / this (on top of mastery), Field Hospital heal rate x this: paced rounds are shorter (DECISIONS #259); 1 to 1 / Round pace</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -12202,7 +12202,7 @@
         </is>
       </c>
       <c r="B183" s="81" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="C183" s="81" t="inlineStr">
         <is>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -466,7 +466,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -788,6 +788,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -9496,7 +9499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E184"/>
+  <dimension ref="A1:E185"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -12222,6 +12225,21 @@
       <c r="C184" s="81" t="inlineStr">
         <is>
           <t>hero ability cooldowns / this (on top of mastery), Field Hospital heal rate x this: paced rounds are shorter (DECISIONS #259); 1 to 1 / Round pace</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="109" t="inlineStr">
+        <is>
+          <t>Battle Fence drain</t>
+        </is>
+      </c>
+      <c r="B185" s="109" t="n">
+        <v>4</v>
+      </c>
+      <c r="C185" s="109" t="inlineStr">
+        <is>
+          <t>Fence per second, per side: battles only; a leak adds its cost to the side's pending loss, which comes off the Fence at most this fast and is applied in full before any match-end ranking (DECISIONS #267); co-op unchanged</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -13262,7 +13262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH169"/>
+  <dimension ref="A1:CJ170"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -13336,7 +13336,7 @@
     <row r="2" ht="13.65" customHeight="1" s="90">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Multipliers are blue because they define each path's character. Costs are formulas off Tuning. Range x multiplies the tower's base range (range-focus paths only). Name is the tier's in-game name (full design: UPGRADES.md). Columns from 'Pierces armour' on are ability values, cumulative per tier; blank = none.</t>
+          <t>Multipliers are blue because they define each path's character. Costs are formulas off Tuning. Range x multiplies the tower's base range (range-focus paths only). Name is the tier's in-game name (full design: UPGRADES.md). Columns from 'Pierces armour' on are ability values, cumulative per tier; blank = none. A/B/C (PLAN Phase 9, DECISIONS #275): tiers 1-3 rows are cumulative; a tier-4 or tier-5 row is one option (Option A/B/C, Blurb = its card line, max 60 chars) and holds ONLY ITS OWN STEP over the tier below (x columns multiply, amounts take the higher, flags add, overrides replace; blank = no change). The exporter composes every build. New options are appended at the bottom.</t>
         </is>
       </c>
       <c r="B2" s="6" t="n"/>
@@ -13830,6 +13830,16 @@
       <c r="CH4" s="81" t="inlineStr">
         <is>
           <t>Aura vs slowed %</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>Blurb</t>
         </is>
       </c>
     </row>
@@ -14121,10 +14131,10 @@
         <v/>
       </c>
       <c r="G8" s="57" t="n">
-        <v>2.86</v>
+        <v>1.3</v>
       </c>
       <c r="H8" s="57" t="n">
-        <v>1.75</v>
+        <v>1.151315789474</v>
       </c>
       <c r="I8" s="57" t="n">
         <v>1</v>
@@ -14138,7 +14148,7 @@
         <v/>
       </c>
       <c r="L8" s="57" t="n">
-        <v>1.75</v>
+        <v>1.166666666667</v>
       </c>
       <c r="M8" s="43" t="inlineStr">
         <is>
@@ -14159,9 +14169,7 @@
       <c r="Y8" s="57" t="n"/>
       <c r="Z8" s="57" t="n"/>
       <c r="AA8" s="57" t="n"/>
-      <c r="AB8" s="57" t="n">
-        <v>10</v>
-      </c>
+      <c r="AB8" s="57" t="n"/>
       <c r="AC8" s="57" t="n"/>
       <c r="AD8" s="57" t="n"/>
       <c r="AE8" s="57" t="n"/>
@@ -14180,6 +14188,11 @@
       <c r="AR8" s="57" t="n"/>
       <c r="AS8" s="57" t="n"/>
       <c r="AT8" s="57" t="n"/>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="13.65" customHeight="1" s="90">
       <c r="A9" s="43" t="inlineStr">
@@ -14209,10 +14222,10 @@
         <v/>
       </c>
       <c r="G9" s="57" t="n">
-        <v>3.71</v>
+        <v>1.297202797203</v>
       </c>
       <c r="H9" s="57" t="n">
-        <v>2.01</v>
+        <v>1.148571428571</v>
       </c>
       <c r="I9" s="57" t="n">
         <v>1</v>
@@ -14226,7 +14239,7 @@
         <v/>
       </c>
       <c r="L9" s="57" t="n">
-        <v>2</v>
+        <v>1.142857142857</v>
       </c>
       <c r="M9" s="43" t="inlineStr">
         <is>
@@ -14247,9 +14260,7 @@
       <c r="Y9" s="57" t="n"/>
       <c r="Z9" s="57" t="n"/>
       <c r="AA9" s="57" t="n"/>
-      <c r="AB9" s="57" t="n">
-        <v>10</v>
-      </c>
+      <c r="AB9" s="57" t="n"/>
       <c r="AC9" s="57" t="n">
         <v>20</v>
       </c>
@@ -14274,6 +14285,11 @@
       <c r="AR9" s="57" t="n"/>
       <c r="AS9" s="57" t="n"/>
       <c r="AT9" s="57" t="n"/>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="13.65" customHeight="1" s="90">
       <c r="A10" s="43" t="inlineStr">
@@ -14563,10 +14579,10 @@
         <v/>
       </c>
       <c r="G13" s="57" t="n">
-        <v>3.32</v>
+        <v>1.349593495935</v>
       </c>
       <c r="H13" s="57" t="n">
-        <v>4.07</v>
+        <v>1.423076923077</v>
       </c>
       <c r="I13" s="57" t="n">
         <v>1</v>
@@ -14590,9 +14606,7 @@
       <c r="N13" s="57" t="n"/>
       <c r="O13" s="57" t="n"/>
       <c r="P13" s="57" t="n"/>
-      <c r="Q13" s="57" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q13" s="57" t="n"/>
       <c r="R13" s="57" t="n"/>
       <c r="S13" s="57" t="n"/>
       <c r="T13" s="57" t="n"/>
@@ -14622,6 +14636,11 @@
       <c r="AR13" s="57" t="n"/>
       <c r="AS13" s="57" t="n"/>
       <c r="AT13" s="57" t="n"/>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="13.65" customHeight="1" s="90">
       <c r="A14" s="43" t="inlineStr">
@@ -14651,10 +14670,10 @@
         <v/>
       </c>
       <c r="G14" s="57" t="n">
-        <v>4.48</v>
+        <v>1.349397590361</v>
       </c>
       <c r="H14" s="57" t="n">
-        <v>5.77</v>
+        <v>1.41769041769</v>
       </c>
       <c r="I14" s="57" t="n">
         <v>1</v>
@@ -14710,6 +14729,11 @@
       <c r="AR14" s="57" t="n"/>
       <c r="AS14" s="57" t="n"/>
       <c r="AT14" s="57" t="n"/>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="13.65" customHeight="1" s="90">
       <c r="A15" s="43" t="inlineStr">
@@ -15007,7 +15031,7 @@
         <v/>
       </c>
       <c r="G18" s="57" t="n">
-        <v>13.03</v>
+        <v>1.899416909621</v>
       </c>
       <c r="H18" s="57" t="n">
         <v>1</v>
@@ -15031,13 +15055,9 @@
           <t>Railshot</t>
         </is>
       </c>
-      <c r="N18" s="46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="N18" s="46" t="n"/>
       <c r="O18" s="57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P18" s="57" t="n"/>
       <c r="Q18" s="57" t="n"/>
@@ -15075,6 +15095,11 @@
       <c r="BJ18" s="105" t="n">
         <v>2</v>
       </c>
+      <c r="CI18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="13.65" customHeight="1" s="90">
       <c r="A19" s="43" t="inlineStr">
@@ -15104,7 +15129,7 @@
         <v/>
       </c>
       <c r="G19" s="57" t="n">
-        <v>24.76</v>
+        <v>1.900230237913</v>
       </c>
       <c r="H19" s="57" t="n">
         <v>1</v>
@@ -15128,21 +15153,15 @@
           <t>Hide Buster</t>
         </is>
       </c>
-      <c r="N19" s="46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="N19" s="46" t="n"/>
       <c r="O19" s="57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P19" s="57" t="n">
         <v>4</v>
       </c>
       <c r="Q19" s="57" t="n"/>
-      <c r="R19" s="57" t="n">
-        <v>3</v>
-      </c>
+      <c r="R19" s="57" t="n"/>
       <c r="S19" s="57" t="n"/>
       <c r="T19" s="57" t="n"/>
       <c r="U19" s="57" t="n"/>
@@ -15171,8 +15190,11 @@
       <c r="AR19" s="57" t="n"/>
       <c r="AS19" s="57" t="n"/>
       <c r="AT19" s="57" t="n"/>
-      <c r="BJ19" s="105" t="n">
-        <v>2</v>
+      <c r="BJ19" s="105" t="n"/>
+      <c r="CI19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="13.65" customHeight="1" s="90">
@@ -15475,13 +15497,13 @@
         <v/>
       </c>
       <c r="G23" s="57" t="n">
-        <v>4.42</v>
+        <v>1.449180327869</v>
       </c>
       <c r="H23" s="57" t="n">
         <v>1</v>
       </c>
       <c r="I23" s="57" t="n">
-        <v>3.04</v>
+        <v>1.321739130435</v>
       </c>
       <c r="J23" s="92">
         <f t="array" ref="J23">'Towers'!$G$6*G23*H23*I23</f>
@@ -15499,11 +15521,7 @@
           <t>Tungsten Core</t>
         </is>
       </c>
-      <c r="N23" s="46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="N23" s="46" t="n"/>
       <c r="O23" s="57" t="n"/>
       <c r="P23" s="57" t="n"/>
       <c r="Q23" s="57" t="n"/>
@@ -15541,6 +15559,11 @@
       <c r="BJ23" s="105" t="n">
         <v>2</v>
       </c>
+      <c r="CI23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="13.65" customHeight="1" s="90">
       <c r="A24" s="43" t="inlineStr">
@@ -15570,13 +15593,13 @@
         <v/>
       </c>
       <c r="G24" s="57" t="n">
-        <v>8.84</v>
+        <v>2</v>
       </c>
       <c r="H24" s="57" t="n">
         <v>1</v>
       </c>
       <c r="I24" s="57" t="n">
-        <v>4.01</v>
+        <v>1.319078947368</v>
       </c>
       <c r="J24" s="92">
         <f t="array" ref="J24">'Towers'!$G$6*G24*H24*I24</f>
@@ -15594,11 +15617,7 @@
           <t>Linebreaker</t>
         </is>
       </c>
-      <c r="N24" s="46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="N24" s="46" t="n"/>
       <c r="O24" s="57" t="n"/>
       <c r="P24" s="57" t="n"/>
       <c r="Q24" s="57" t="n"/>
@@ -15635,6 +15654,11 @@
       <c r="AT24" s="57" t="n"/>
       <c r="BJ24" s="105" t="n">
         <v>3</v>
+      </c>
+      <c r="CI24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="13.65" customHeight="1" s="90">
@@ -15925,10 +15949,10 @@
         <v/>
       </c>
       <c r="G28" s="57" t="n">
-        <v>3.32</v>
+        <v>1.349593495935</v>
       </c>
       <c r="H28" s="57" t="n">
-        <v>4.07</v>
+        <v>1.423076923077</v>
       </c>
       <c r="I28" s="57" t="n">
         <v>1</v>
@@ -15984,6 +16008,11 @@
       <c r="AR28" s="57" t="n"/>
       <c r="AS28" s="57" t="n"/>
       <c r="AT28" s="57" t="n"/>
+      <c r="CI28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="13.65" customHeight="1" s="90">
       <c r="A29" s="43" t="inlineStr">
@@ -16013,10 +16042,10 @@
         <v/>
       </c>
       <c r="G29" s="57" t="n">
-        <v>4.48</v>
+        <v>1.349397590361</v>
       </c>
       <c r="H29" s="57" t="n">
-        <v>5.77</v>
+        <v>1.41769041769</v>
       </c>
       <c r="I29" s="57" t="n">
         <v>1</v>
@@ -16074,6 +16103,11 @@
       <c r="AR29" s="57" t="n"/>
       <c r="AS29" s="57" t="n"/>
       <c r="AT29" s="57" t="n"/>
+      <c r="CI29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="13.65" customHeight="1" s="90">
       <c r="A30" s="43" t="inlineStr">
@@ -16373,7 +16407,7 @@
         <v/>
       </c>
       <c r="G33" s="57" t="n">
-        <v>13.03</v>
+        <v>1.899416909621</v>
       </c>
       <c r="H33" s="57" t="n">
         <v>1</v>
@@ -16400,7 +16434,7 @@
       <c r="N33" s="57" t="n"/>
       <c r="O33" s="57" t="n"/>
       <c r="P33" s="57" t="n">
-        <v>5</v>
+        <v>1.666666666667</v>
       </c>
       <c r="Q33" s="57" t="n"/>
       <c r="R33" s="57" t="n"/>
@@ -16437,6 +16471,11 @@
       <c r="BJ33" s="105" t="n">
         <v>3</v>
       </c>
+      <c r="CI33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="13.65" customHeight="1" s="90">
       <c r="A34" s="43" t="inlineStr">
@@ -16466,7 +16505,7 @@
         <v/>
       </c>
       <c r="G34" s="57" t="n">
-        <v>24.76</v>
+        <v>1.900230237913</v>
       </c>
       <c r="H34" s="57" t="n">
         <v>1</v>
@@ -16493,7 +16532,7 @@
       <c r="N34" s="57" t="n"/>
       <c r="O34" s="57" t="n"/>
       <c r="P34" s="57" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="57" t="n"/>
       <c r="R34" s="57" t="n"/>
@@ -16533,6 +16572,11 @@
       <c r="AT34" s="57" t="n"/>
       <c r="BJ34" s="105" t="n">
         <v>4</v>
+      </c>
+      <c r="CI34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="13.65" customHeight="1" s="90">
@@ -16831,13 +16875,13 @@
         <v/>
       </c>
       <c r="G38" s="57" t="n">
-        <v>4.42</v>
+        <v>1.449180327869</v>
       </c>
       <c r="H38" s="57" t="n">
         <v>1</v>
       </c>
       <c r="I38" s="57" t="n">
-        <v>3.04</v>
+        <v>1.321739130435</v>
       </c>
       <c r="J38" s="92">
         <f t="array" ref="J38">'Towers'!$G$7*G38*H38*I38</f>
@@ -16861,7 +16905,7 @@
       <c r="Q38" s="57" t="n"/>
       <c r="R38" s="57" t="n"/>
       <c r="S38" s="57" t="n">
-        <v>1.6</v>
+        <v>1.066666666667</v>
       </c>
       <c r="T38" s="57" t="n"/>
       <c r="U38" s="57" t="n"/>
@@ -16894,6 +16938,11 @@
       <c r="AR38" s="57" t="n"/>
       <c r="AS38" s="57" t="n"/>
       <c r="AT38" s="57" t="n"/>
+      <c r="CI38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="13.65" customHeight="1" s="90">
       <c r="A39" s="43" t="inlineStr">
@@ -16923,13 +16972,13 @@
         <v/>
       </c>
       <c r="G39" s="57" t="n">
-        <v>6.41</v>
+        <v>1.450226244344</v>
       </c>
       <c r="H39" s="57" t="n">
         <v>1</v>
       </c>
       <c r="I39" s="57" t="n">
-        <v>4.01</v>
+        <v>1.319078947368</v>
       </c>
       <c r="J39" s="92">
         <f t="array" ref="J39">'Towers'!$G$7*G39*H39*I39</f>
@@ -16953,7 +17002,7 @@
       <c r="Q39" s="57" t="n"/>
       <c r="R39" s="57" t="n"/>
       <c r="S39" s="57" t="n">
-        <v>1.8</v>
+        <v>1.125</v>
       </c>
       <c r="T39" s="57" t="n"/>
       <c r="U39" s="57" t="n"/>
@@ -16986,6 +17035,11 @@
       <c r="AR39" s="57" t="n"/>
       <c r="AS39" s="57" t="n"/>
       <c r="AT39" s="57" t="n"/>
+      <c r="CI39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="13.65" customHeight="1" s="90">
       <c r="A40" s="43" t="inlineStr">
@@ -17285,13 +17339,13 @@
         <v/>
       </c>
       <c r="G43" s="57" t="n">
-        <v>4.42</v>
+        <v>1.449180327869</v>
       </c>
       <c r="H43" s="57" t="n">
         <v>1</v>
       </c>
       <c r="I43" s="57" t="n">
-        <v>3.04</v>
+        <v>1.321739130435</v>
       </c>
       <c r="J43" s="92">
         <f t="array" ref="J43">'Towers'!$G$7*G43*H43*I43</f>
@@ -17324,9 +17378,7 @@
       <c r="Z43" s="57" t="n">
         <v>4</v>
       </c>
-      <c r="AA43" s="57" t="n">
-        <v>2</v>
-      </c>
+      <c r="AA43" s="57" t="n"/>
       <c r="AB43" s="57" t="n"/>
       <c r="AC43" s="57" t="n"/>
       <c r="AD43" s="57" t="n"/>
@@ -17346,6 +17398,11 @@
       <c r="AR43" s="57" t="n"/>
       <c r="AS43" s="57" t="n"/>
       <c r="AT43" s="57" t="n"/>
+      <c r="CI43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="13.65" customHeight="1" s="90">
       <c r="A44" s="43" t="inlineStr">
@@ -17375,13 +17432,13 @@
         <v/>
       </c>
       <c r="G44" s="57" t="n">
-        <v>6.41</v>
+        <v>1.450226244344</v>
       </c>
       <c r="H44" s="57" t="n">
         <v>1</v>
       </c>
       <c r="I44" s="57" t="n">
-        <v>4.01</v>
+        <v>1.319078947368</v>
       </c>
       <c r="J44" s="92">
         <f t="array" ref="J44">'Towers'!$G$7*G44*H44*I44</f>
@@ -17414,9 +17471,7 @@
       <c r="Z44" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AA44" s="57" t="n">
-        <v>2</v>
-      </c>
+      <c r="AA44" s="57" t="n"/>
       <c r="AB44" s="57" t="n"/>
       <c r="AC44" s="57" t="n"/>
       <c r="AD44" s="57" t="n"/>
@@ -17436,6 +17491,11 @@
       <c r="AR44" s="57" t="n"/>
       <c r="AS44" s="57" t="n"/>
       <c r="AT44" s="57" t="n"/>
+      <c r="CI44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="13.65" customHeight="1" s="90">
       <c r="A45" s="43" t="inlineStr">
@@ -17743,7 +17803,7 @@
         <v/>
       </c>
       <c r="G48" s="57" t="n">
-        <v>13.03</v>
+        <v>1.899416909621</v>
       </c>
       <c r="H48" s="57" t="n">
         <v>1</v>
@@ -17767,22 +17827,16 @@
           <t>Earthshaker</t>
         </is>
       </c>
-      <c r="N48" s="46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="N48" s="46" t="n"/>
       <c r="O48" s="57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P48" s="57" t="n"/>
       <c r="Q48" s="57" t="n"/>
       <c r="R48" s="57" t="n"/>
       <c r="S48" s="57" t="n"/>
       <c r="T48" s="57" t="n"/>
-      <c r="U48" s="57" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="U48" s="57" t="n"/>
       <c r="V48" s="57" t="n"/>
       <c r="W48" s="57" t="n">
         <v>6</v>
@@ -17810,6 +17864,11 @@
       <c r="AR48" s="57" t="n"/>
       <c r="AS48" s="57" t="n"/>
       <c r="AT48" s="57" t="n"/>
+      <c r="CI48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="13.65" customHeight="1" s="90">
       <c r="A49" s="43" t="inlineStr">
@@ -17839,7 +17898,7 @@
         <v/>
       </c>
       <c r="G49" s="57" t="n">
-        <v>34</v>
+        <v>2.609363008442</v>
       </c>
       <c r="H49" s="57" t="n">
         <v>1</v>
@@ -17863,13 +17922,9 @@
           <t>Tectonic Slam</t>
         </is>
       </c>
-      <c r="N49" s="46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="N49" s="46" t="n"/>
       <c r="O49" s="57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P49" s="57" t="n"/>
       <c r="Q49" s="57" t="n"/>
@@ -17880,9 +17935,7 @@
         <v>1</v>
       </c>
       <c r="V49" s="57" t="n"/>
-      <c r="W49" s="57" t="n">
-        <v>6</v>
-      </c>
+      <c r="W49" s="57" t="n"/>
       <c r="X49" s="57" t="n"/>
       <c r="Y49" s="57" t="n"/>
       <c r="Z49" s="57" t="n"/>
@@ -17906,6 +17959,11 @@
       <c r="AR49" s="57" t="n"/>
       <c r="AS49" s="57" t="n"/>
       <c r="AT49" s="57" t="n"/>
+      <c r="CI49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="13.65" customHeight="1" s="90">
       <c r="A50" s="43" t="inlineStr">
@@ -18201,10 +18259,10 @@
         <v/>
       </c>
       <c r="G53" s="57" t="n">
-        <v>2.86</v>
+        <v>1.3</v>
       </c>
       <c r="H53" s="57" t="n">
-        <v>1.75</v>
+        <v>1.151315789474</v>
       </c>
       <c r="I53" s="57" t="n">
         <v>1</v>
@@ -18218,7 +18276,7 @@
         <v/>
       </c>
       <c r="L53" s="57" t="n">
-        <v>1.75</v>
+        <v>1.166666666667</v>
       </c>
       <c r="M53" s="43" t="inlineStr">
         <is>
@@ -18245,9 +18303,7 @@
       <c r="AE53" s="57" t="n">
         <v>70</v>
       </c>
-      <c r="AF53" s="57" t="n">
-        <v>2</v>
-      </c>
+      <c r="AF53" s="57" t="n"/>
       <c r="AG53" s="57" t="n"/>
       <c r="AH53" s="57" t="n"/>
       <c r="AI53" s="57" t="n"/>
@@ -18262,6 +18318,11 @@
       <c r="AR53" s="57" t="n"/>
       <c r="AS53" s="57" t="n"/>
       <c r="AT53" s="57" t="n"/>
+      <c r="CI53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="13.65" customHeight="1" s="90">
       <c r="A54" s="43" t="inlineStr">
@@ -18291,10 +18352,10 @@
         <v/>
       </c>
       <c r="G54" s="57" t="n">
-        <v>3.71</v>
+        <v>1.297202797203</v>
       </c>
       <c r="H54" s="57" t="n">
-        <v>2.01</v>
+        <v>1.148571428571</v>
       </c>
       <c r="I54" s="57" t="n">
         <v>1</v>
@@ -18308,7 +18369,7 @@
         <v/>
       </c>
       <c r="L54" s="57" t="n">
-        <v>2</v>
+        <v>1.142857142857</v>
       </c>
       <c r="M54" s="43" t="inlineStr">
         <is>
@@ -18356,6 +18417,11 @@
       <c r="AR54" s="57" t="n"/>
       <c r="AS54" s="57" t="n"/>
       <c r="AT54" s="57" t="n"/>
+      <c r="CI54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="13.65" customHeight="1" s="90">
       <c r="A55" s="43" t="inlineStr">
@@ -18657,10 +18723,10 @@
         <v/>
       </c>
       <c r="G58" s="57" t="n">
-        <v>3.32</v>
+        <v>1.349593495935</v>
       </c>
       <c r="H58" s="57" t="n">
-        <v>4.07</v>
+        <v>1.423076923077</v>
       </c>
       <c r="I58" s="57" t="n">
         <v>1</v>
@@ -18704,9 +18770,7 @@
       <c r="AH58" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AI58" s="57" t="n">
-        <v>1</v>
-      </c>
+      <c r="AI58" s="57" t="n"/>
       <c r="AJ58" s="57" t="n">
         <v>3</v>
       </c>
@@ -18720,6 +18784,11 @@
       <c r="AR58" s="57" t="n"/>
       <c r="AS58" s="57" t="n"/>
       <c r="AT58" s="57" t="n"/>
+      <c r="CI58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="13.65" customHeight="1" s="90">
       <c r="A59" s="43" t="inlineStr">
@@ -18749,10 +18818,10 @@
         <v/>
       </c>
       <c r="G59" s="57" t="n">
-        <v>4.48</v>
+        <v>1.349397590361</v>
       </c>
       <c r="H59" s="57" t="n">
-        <v>5.77</v>
+        <v>1.41769041769</v>
       </c>
       <c r="I59" s="57" t="n">
         <v>1</v>
@@ -18793,9 +18862,7 @@
       <c r="AE59" s="57" t="n"/>
       <c r="AF59" s="57" t="n"/>
       <c r="AG59" s="57" t="n"/>
-      <c r="AH59" s="57" t="n">
-        <v>5</v>
-      </c>
+      <c r="AH59" s="57" t="n"/>
       <c r="AI59" s="57" t="n">
         <v>2</v>
       </c>
@@ -18816,6 +18883,11 @@
       <c r="AR59" s="57" t="n"/>
       <c r="AS59" s="57" t="n"/>
       <c r="AT59" s="57" t="n"/>
+      <c r="CI59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="13.65" customHeight="1" s="90">
       <c r="A60" s="43" t="inlineStr">
@@ -19119,7 +19191,7 @@
         <v/>
       </c>
       <c r="G63" s="57" t="n">
-        <v>13.03</v>
+        <v>1.899416909621</v>
       </c>
       <c r="H63" s="57" t="n">
         <v>1</v>
@@ -19157,9 +19229,7 @@
       <c r="Y63" s="57" t="n"/>
       <c r="Z63" s="57" t="n"/>
       <c r="AA63" s="57" t="n"/>
-      <c r="AB63" s="57" t="n">
-        <v>10</v>
-      </c>
+      <c r="AB63" s="57" t="n"/>
       <c r="AC63" s="57" t="n"/>
       <c r="AD63" s="57" t="n"/>
       <c r="AE63" s="57" t="n"/>
@@ -19172,11 +19242,7 @@
       <c r="AL63" s="57" t="n">
         <v>50</v>
       </c>
-      <c r="AM63" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="AM63" s="57" t="n"/>
       <c r="AN63" s="57" t="n"/>
       <c r="AO63" s="57" t="n"/>
       <c r="AP63" s="57" t="n"/>
@@ -19184,6 +19250,11 @@
       <c r="AR63" s="57" t="n"/>
       <c r="AS63" s="57" t="n"/>
       <c r="AT63" s="57" t="n"/>
+      <c r="CI63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="13.65" customHeight="1" s="90">
       <c r="A64" s="43" t="inlineStr">
@@ -19213,7 +19284,7 @@
         <v/>
       </c>
       <c r="G64" s="57" t="n">
-        <v>24.76</v>
+        <v>1.900230237913</v>
       </c>
       <c r="H64" s="57" t="n">
         <v>1</v>
@@ -19251,9 +19322,7 @@
       <c r="Y64" s="57" t="n"/>
       <c r="Z64" s="57" t="n"/>
       <c r="AA64" s="57" t="n"/>
-      <c r="AB64" s="57" t="n">
-        <v>10</v>
-      </c>
+      <c r="AB64" s="57" t="n"/>
       <c r="AC64" s="57" t="n">
         <v>20</v>
       </c>
@@ -19268,11 +19337,7 @@
       <c r="AL64" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="AM64" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="AM64" s="57" t="n"/>
       <c r="AN64" s="57" t="n"/>
       <c r="AO64" s="57" t="n"/>
       <c r="AP64" s="57" t="n"/>
@@ -19280,6 +19345,11 @@
       <c r="AR64" s="57" t="n"/>
       <c r="AS64" s="57" t="n"/>
       <c r="AT64" s="57" t="n"/>
+      <c r="CI64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="13.65" customHeight="1" s="90">
       <c r="A65" s="43" t="inlineStr">
@@ -19624,7 +19694,7 @@
       <c r="AL68" s="57" t="n"/>
       <c r="AM68" s="57" t="n"/>
       <c r="AN68" s="57" t="n">
-        <v>11.1</v>
+        <v>1.681818181818</v>
       </c>
       <c r="AO68" s="57" t="n"/>
       <c r="AP68" s="57" t="n"/>
@@ -19632,6 +19702,11 @@
       <c r="AR68" s="57" t="n"/>
       <c r="AS68" s="57" t="n"/>
       <c r="AT68" s="57" t="n"/>
+      <c r="CI68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="13.65" customHeight="1" s="90">
       <c r="A69" s="43" t="inlineStr">
@@ -19712,7 +19787,7 @@
       <c r="AL69" s="57" t="n"/>
       <c r="AM69" s="57" t="n"/>
       <c r="AN69" s="57" t="n">
-        <v>17.9</v>
+        <v>1.612612612613</v>
       </c>
       <c r="AO69" s="57" t="n">
         <v>5</v>
@@ -19724,6 +19799,11 @@
       <c r="AR69" s="57" t="n"/>
       <c r="AS69" s="57" t="n"/>
       <c r="AT69" s="57" t="n"/>
+      <c r="CI69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="13.65" customHeight="1" s="90">
       <c r="A70" s="43" t="inlineStr">
@@ -20084,6 +20164,11 @@
       </c>
       <c r="AS73" s="57" t="n"/>
       <c r="AT73" s="57" t="n"/>
+      <c r="CI73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="13.65" customHeight="1" s="90">
       <c r="A74" s="43" t="inlineStr">
@@ -20174,6 +20259,11 @@
       </c>
       <c r="AS74" s="57" t="n"/>
       <c r="AT74" s="57" t="n"/>
+      <c r="CI74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="13.65" customHeight="1" s="90">
       <c r="A75" s="43" t="inlineStr">
@@ -20526,11 +20616,12 @@
       <c r="AP78" s="57" t="n"/>
       <c r="AQ78" s="57" t="n"/>
       <c r="AR78" s="57" t="n"/>
-      <c r="AS78" s="57" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT78" s="57" t="n">
-        <v>0.9</v>
+      <c r="AS78" s="57" t="n"/>
+      <c r="AT78" s="57" t="n"/>
+      <c r="CI78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="13.65" customHeight="1" s="90">
@@ -20599,9 +20690,7 @@
       <c r="Y79" s="57" t="n"/>
       <c r="Z79" s="57" t="n"/>
       <c r="AA79" s="57" t="n"/>
-      <c r="AB79" s="57" t="n">
-        <v>10</v>
-      </c>
+      <c r="AB79" s="57" t="n"/>
       <c r="AC79" s="57" t="n"/>
       <c r="AD79" s="57" t="n"/>
       <c r="AE79" s="57" t="n"/>
@@ -20623,6 +20712,11 @@
       </c>
       <c r="AT79" s="57" t="n">
         <v>1</v>
+      </c>
+      <c r="CI79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -21008,6 +21102,11 @@
       <c r="AY83" s="57" t="n"/>
       <c r="AZ83" s="57" t="n"/>
       <c r="BA83" s="57" t="n"/>
+      <c r="CI83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="43" t="inlineStr">
@@ -21097,9 +21196,7 @@
       <c r="AU84" s="57" t="n">
         <v>45</v>
       </c>
-      <c r="AV84" s="57" t="n">
-        <v>5</v>
-      </c>
+      <c r="AV84" s="57" t="n"/>
       <c r="AW84" s="57" t="n">
         <v>0.5</v>
       </c>
@@ -21107,6 +21204,11 @@
       <c r="AY84" s="57" t="n"/>
       <c r="AZ84" s="57" t="n"/>
       <c r="BA84" s="57" t="n"/>
+      <c r="CI84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="43" t="inlineStr">
@@ -21473,11 +21575,7 @@
       <c r="AC88" s="57" t="n">
         <v>20</v>
       </c>
-      <c r="AD88" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="AD88" s="57" t="n"/>
       <c r="AE88" s="57" t="n"/>
       <c r="AF88" s="57" t="n"/>
       <c r="AG88" s="57" t="n"/>
@@ -21501,6 +21599,11 @@
       <c r="AY88" s="57" t="n"/>
       <c r="AZ88" s="57" t="n"/>
       <c r="BA88" s="57" t="n"/>
+      <c r="CI88" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="43" t="inlineStr">
@@ -21574,11 +21677,7 @@
       <c r="AC89" s="57" t="n">
         <v>30</v>
       </c>
-      <c r="AD89" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="AD89" s="57" t="n"/>
       <c r="AE89" s="57" t="n"/>
       <c r="AF89" s="57" t="n"/>
       <c r="AG89" s="57" t="n"/>
@@ -21602,6 +21701,11 @@
       <c r="AY89" s="57" t="n"/>
       <c r="AZ89" s="57" t="n"/>
       <c r="BA89" s="57" t="n"/>
+      <c r="CI89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="43" t="inlineStr">
@@ -21933,7 +22037,7 @@
         </is>
       </c>
       <c r="L93" s="57" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="M93" s="43" t="inlineStr">
         <is>
@@ -21977,15 +22081,20 @@
       <c r="AV93" s="57" t="n"/>
       <c r="AW93" s="57" t="n"/>
       <c r="AX93" s="57" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AY93" s="57" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AZ93" s="57" t="n">
         <v>0.7</v>
       </c>
       <c r="BA93" s="57" t="n"/>
+      <c r="CI93" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="43" t="inlineStr">
@@ -22032,7 +22141,7 @@
         </is>
       </c>
       <c r="L94" s="57" t="n">
-        <v>1.5</v>
+        <v>1.153846153846</v>
       </c>
       <c r="M94" s="43" t="inlineStr">
         <is>
@@ -22076,16 +22185,21 @@
       <c r="AV94" s="57" t="n"/>
       <c r="AW94" s="57" t="n"/>
       <c r="AX94" s="57" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AY94" s="57" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AZ94" s="57" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="BA94" s="57" t="n">
         <v>20</v>
+      </c>
+      <c r="CI94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -22496,21 +22610,20 @@
       <c r="AZ98" s="57" t="n"/>
       <c r="BA98" s="57" t="n"/>
       <c r="BB98" s="57" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC98" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BD98" s="57" t="n">
-        <v>0.5</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="BC98" s="57" t="n"/>
+      <c r="BD98" s="57" t="n"/>
       <c r="BE98" s="57" t="n"/>
       <c r="BF98" s="57" t="n"/>
       <c r="BG98" s="57" t="n"/>
       <c r="BH98" s="57" t="n"/>
       <c r="BI98" s="57" t="n"/>
+      <c r="CI98" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="43" t="inlineStr">
@@ -22605,13 +22718,9 @@
       <c r="AZ99" s="57" t="n"/>
       <c r="BA99" s="57" t="n"/>
       <c r="BB99" s="57" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC99" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="BC99" s="57" t="n"/>
       <c r="BD99" s="57" t="n">
         <v>1</v>
       </c>
@@ -22620,6 +22729,11 @@
       <c r="BG99" s="57" t="n"/>
       <c r="BH99" s="57" t="n"/>
       <c r="BI99" s="57" t="n"/>
+      <c r="CI99" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="43" t="inlineStr">
@@ -22973,7 +23087,7 @@
         </is>
       </c>
       <c r="L103" s="57" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="M103" s="43" t="inlineStr">
         <is>
@@ -23032,6 +23146,11 @@
       <c r="BG103" s="57" t="n"/>
       <c r="BH103" s="57" t="n"/>
       <c r="BI103" s="57" t="n"/>
+      <c r="CI103" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="43" t="inlineStr">
@@ -23078,7 +23197,7 @@
         </is>
       </c>
       <c r="L104" s="57" t="n">
-        <v>1.8</v>
+        <v>1.285714285714</v>
       </c>
       <c r="M104" s="43" t="inlineStr">
         <is>
@@ -23128,9 +23247,7 @@
       <c r="BB104" s="57" t="n"/>
       <c r="BC104" s="57" t="n"/>
       <c r="BD104" s="57" t="n"/>
-      <c r="BE104" s="57" t="n">
-        <v>3</v>
-      </c>
+      <c r="BE104" s="57" t="n"/>
       <c r="BF104" s="57" t="n">
         <v>50</v>
       </c>
@@ -23139,6 +23256,11 @@
       </c>
       <c r="BH104" s="57" t="n"/>
       <c r="BI104" s="57" t="n"/>
+      <c r="CI104" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="43" t="inlineStr">
@@ -23517,9 +23639,7 @@
       <c r="Y108" s="57" t="n"/>
       <c r="Z108" s="57" t="n"/>
       <c r="AA108" s="57" t="n"/>
-      <c r="AB108" s="57" t="n">
-        <v>10</v>
-      </c>
+      <c r="AB108" s="57" t="n"/>
       <c r="AC108" s="57" t="n"/>
       <c r="AD108" s="57" t="n"/>
       <c r="AE108" s="57" t="n"/>
@@ -23555,6 +23675,11 @@
         <v>35</v>
       </c>
       <c r="BI108" s="57" t="n"/>
+      <c r="CI108" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="43" t="inlineStr">
@@ -23622,9 +23747,7 @@
       <c r="Y109" s="57" t="n"/>
       <c r="Z109" s="57" t="n"/>
       <c r="AA109" s="57" t="n"/>
-      <c r="AB109" s="57" t="n">
-        <v>10</v>
-      </c>
+      <c r="AB109" s="57" t="n"/>
       <c r="AC109" s="57" t="n"/>
       <c r="AD109" s="57" t="n"/>
       <c r="AE109" s="57" t="n"/>
@@ -23664,6 +23787,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="CI109" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="43" t="inlineStr">
@@ -23870,7 +23998,7 @@
         <v/>
       </c>
       <c r="G113" s="57" t="n">
-        <v>4.42</v>
+        <v>1.449180327869</v>
       </c>
       <c r="H113" s="57" t="n">
         <v>1</v>
@@ -23879,7 +24007,7 @@
         <v>1</v>
       </c>
       <c r="J113" s="92">
-        <f>'Towers'!$G$15*G113*H113*I113</f>
+        <f>J112*G113*H113*I113</f>
         <v/>
       </c>
       <c r="K113" s="92">
@@ -23894,18 +24022,17 @@
           <t>Jump Spark</t>
         </is>
       </c>
-      <c r="BK113" s="81" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL113" s="81" t="n">
-        <v>15</v>
-      </c>
-      <c r="BM113" s="81" t="n">
-        <v>2</v>
-      </c>
+      <c r="BK113" s="81" t="n"/>
+      <c r="BL113" s="81" t="n"/>
+      <c r="BM113" s="81" t="n"/>
       <c r="BN113" s="46" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="CI113" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -23937,7 +24064,7 @@
         <v/>
       </c>
       <c r="G114" s="57" t="n">
-        <v>6.41</v>
+        <v>1.450226244344</v>
       </c>
       <c r="H114" s="57" t="n">
         <v>1</v>
@@ -23946,7 +24073,7 @@
         <v>1</v>
       </c>
       <c r="J114" s="92">
-        <f>'Towers'!$G$15*G114*H114*I114</f>
+        <f>J113*G114*H114*I114</f>
         <v/>
       </c>
       <c r="K114" s="92">
@@ -23961,23 +24088,18 @@
           <t>Power Grid</t>
         </is>
       </c>
-      <c r="BK114" s="81" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL114" s="81" t="n">
-        <v>15</v>
-      </c>
-      <c r="BM114" s="81" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN114" s="46" t="inlineStr">
+      <c r="BK114" s="81" t="n"/>
+      <c r="BL114" s="81" t="n"/>
+      <c r="BM114" s="81" t="n"/>
+      <c r="BN114" s="46" t="n"/>
+      <c r="BO114" s="46" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="BO114" s="46" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="CI114" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -24177,7 +24299,7 @@
         <v/>
       </c>
       <c r="G118" s="57" t="n">
-        <v>6.58</v>
+        <v>1.4</v>
       </c>
       <c r="H118" s="57" t="n">
         <v>1</v>
@@ -24186,7 +24308,7 @@
         <v>1</v>
       </c>
       <c r="J118" s="92">
-        <f>'Towers'!$G$15*G118*H118*I118</f>
+        <f>J117*G118*H118*I118</f>
         <v/>
       </c>
       <c r="K118" s="92">
@@ -24206,11 +24328,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="U118" s="57" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BP118" s="81" t="n">
-        <v>10</v>
+      <c r="U118" s="57" t="n"/>
+      <c r="BP118" s="81" t="n"/>
+      <c r="CI118" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -24241,7 +24364,7 @@
         <v/>
       </c>
       <c r="G119" s="57" t="n">
-        <v>12.5</v>
+        <v>1.899696048632</v>
       </c>
       <c r="H119" s="57" t="n">
         <v>1</v>
@@ -24250,7 +24373,7 @@
         <v>1</v>
       </c>
       <c r="J119" s="92">
-        <f>'Towers'!$G$15*G119*H119*I119</f>
+        <f>J118*G119*H119*I119</f>
         <v/>
       </c>
       <c r="K119" s="92">
@@ -24265,20 +24388,17 @@
           <t>Judgement Bolt</t>
         </is>
       </c>
-      <c r="N119" s="46" t="inlineStr">
+      <c r="N119" s="46" t="n"/>
+      <c r="U119" s="57" t="n"/>
+      <c r="BP119" s="81" t="n"/>
+      <c r="BQ119" s="46" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="U119" s="57" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BP119" s="81" t="n">
-        <v>10</v>
-      </c>
-      <c r="BQ119" s="46" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="CI119" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -24478,7 +24598,7 @@
         <v/>
       </c>
       <c r="G123" s="57" t="n">
-        <v>2.86</v>
+        <v>1.3</v>
       </c>
       <c r="H123" s="57" t="n">
         <v>1</v>
@@ -24487,7 +24607,7 @@
         <v>1</v>
       </c>
       <c r="J123" s="92">
-        <f>'Towers'!$G$15*G123*H123*I123</f>
+        <f>J122*G123*H123*I123</f>
         <v/>
       </c>
       <c r="K123" s="92">
@@ -24495,21 +24615,22 @@
         <v/>
       </c>
       <c r="L123" s="57" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M123" s="43" t="inlineStr">
         <is>
           <t>Storm Warning</t>
         </is>
       </c>
-      <c r="AB123" s="57" t="n">
-        <v>10</v>
-      </c>
+      <c r="AB123" s="57" t="n"/>
       <c r="AC123" s="57" t="n">
         <v>15</v>
       </c>
-      <c r="BR123" s="81" t="n">
-        <v>4</v>
+      <c r="BR123" s="81" t="n"/>
+      <c r="CI123" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -24540,7 +24661,7 @@
         <v/>
       </c>
       <c r="G124" s="57" t="n">
-        <v>3.71</v>
+        <v>1.297202797203</v>
       </c>
       <c r="H124" s="57" t="n">
         <v>1</v>
@@ -24549,7 +24670,7 @@
         <v>1</v>
       </c>
       <c r="J124" s="92">
-        <f>'Towers'!$G$15*G124*H124*I124</f>
+        <f>J123*G124*H124*I124</f>
         <v/>
       </c>
       <c r="K124" s="92">
@@ -24557,25 +24678,24 @@
         <v/>
       </c>
       <c r="L124" s="57" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M124" s="43" t="inlineStr">
         <is>
           <t>Lightning Rodeo</t>
         </is>
       </c>
-      <c r="AB124" s="57" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC124" s="57" t="n">
-        <v>15</v>
-      </c>
-      <c r="BR124" s="81" t="n">
-        <v>4</v>
-      </c>
+      <c r="AB124" s="57" t="n"/>
+      <c r="AC124" s="57" t="n"/>
+      <c r="BR124" s="81" t="n"/>
       <c r="BS124" s="81" t="n">
         <v>50</v>
       </c>
+      <c r="CI124" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="43" t="inlineStr">
@@ -24770,7 +24890,7 @@
         <v/>
       </c>
       <c r="G128" s="57" t="n">
-        <v>13.03</v>
+        <v>1.899416909621</v>
       </c>
       <c r="H128" s="57" t="n">
         <v>1</v>
@@ -24779,7 +24899,7 @@
         <v>1</v>
       </c>
       <c r="J128" s="92">
-        <f>'Towers'!$G$16*G128*H128*I128</f>
+        <f>J127*G128*H128*I128</f>
         <v/>
       </c>
       <c r="K128" s="92">
@@ -24802,8 +24922,11 @@
       <c r="BJ128" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="BU128" s="81" t="n">
-        <v>3</v>
+      <c r="BU128" s="81" t="n"/>
+      <c r="CI128" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -24834,7 +24957,7 @@
         <v/>
       </c>
       <c r="G129" s="57" t="n">
-        <v>12</v>
+        <v>0.9209516500379999</v>
       </c>
       <c r="H129" s="57" t="n">
         <v>1</v>
@@ -24843,7 +24966,7 @@
         <v>1</v>
       </c>
       <c r="J129" s="92">
-        <f>'Towers'!$G$16*G129*H129*I129</f>
+        <f>J128*G129*H129*I129</f>
         <v/>
       </c>
       <c r="K129" s="92">
@@ -24858,23 +24981,20 @@
           <t>Eagle of the Peak</t>
         </is>
       </c>
-      <c r="N129" s="81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="N129" s="81" t="n"/>
       <c r="U129" s="81" t="n">
         <v>0.5</v>
       </c>
-      <c r="BJ129" s="81" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU129" s="81" t="n">
-        <v>3</v>
-      </c>
+      <c r="BJ129" s="81" t="n"/>
+      <c r="BU129" s="81" t="n"/>
       <c r="BV129" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="CI129" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -25074,16 +25194,16 @@
         <v/>
       </c>
       <c r="G133" s="57" t="n">
-        <v>5.2</v>
+        <v>2.810810810811</v>
       </c>
       <c r="H133" s="57" t="n">
-        <v>3.75</v>
+        <v>1</v>
       </c>
       <c r="I133" s="57" t="n">
         <v>1</v>
       </c>
       <c r="J133" s="92">
-        <f>'Towers'!$G$16*G133*H133*I133</f>
+        <f>J132*G133*H133*I133</f>
         <v/>
       </c>
       <c r="K133" s="92">
@@ -25098,8 +25218,11 @@
           <t>Wide Circle</t>
         </is>
       </c>
-      <c r="BT133" s="81" t="n">
-        <v>6</v>
+      <c r="BT133" s="81" t="n"/>
+      <c r="CI133" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -25130,16 +25253,16 @@
         <v/>
       </c>
       <c r="G134" s="57" t="n">
-        <v>4.4</v>
+        <v>0.846153846154</v>
       </c>
       <c r="H134" s="57" t="n">
-        <v>3.75</v>
+        <v>1</v>
       </c>
       <c r="I134" s="57" t="n">
         <v>1</v>
       </c>
       <c r="J134" s="92">
-        <f>'Towers'!$G$16*G134*H134*I134</f>
+        <f>J133*G134*H134*I134</f>
         <v/>
       </c>
       <c r="K134" s="92">
@@ -25147,7 +25270,7 @@
         <v/>
       </c>
       <c r="L134" s="57" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M134" s="43" t="inlineStr">
         <is>
@@ -25162,6 +25285,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="CI134" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="43" t="inlineStr">
@@ -25359,7 +25487,7 @@
         <v/>
       </c>
       <c r="G138" s="57" t="n">
-        <v>2.86</v>
+        <v>1.3</v>
       </c>
       <c r="H138" s="57" t="n">
         <v>1</v>
@@ -25368,7 +25496,7 @@
         <v>1</v>
       </c>
       <c r="J138" s="92">
-        <f>'Towers'!$G$16*G138*H138*I138</f>
+        <f>J137*G138*H138*I138</f>
         <v/>
       </c>
       <c r="K138" s="92">
@@ -25376,21 +25504,22 @@
         <v/>
       </c>
       <c r="L138" s="57" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M138" s="43" t="inlineStr">
         <is>
           <t>Lure</t>
         </is>
       </c>
-      <c r="T138" s="81" t="n">
-        <v>10</v>
-      </c>
+      <c r="T138" s="81" t="n"/>
       <c r="W138" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="BX138" s="81" t="n">
-        <v>25</v>
+      <c r="BX138" s="81" t="n"/>
+      <c r="CI138" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -25421,7 +25550,7 @@
         <v/>
       </c>
       <c r="G139" s="57" t="n">
-        <v>3.71</v>
+        <v>1.297202797203</v>
       </c>
       <c r="H139" s="57" t="n">
         <v>1</v>
@@ -25430,7 +25559,7 @@
         <v>1</v>
       </c>
       <c r="J139" s="92">
-        <f>'Towers'!$G$16*G139*H139*I139</f>
+        <f>J138*G139*H139*I139</f>
         <v/>
       </c>
       <c r="K139" s="92">
@@ -25438,25 +25567,24 @@
         <v/>
       </c>
       <c r="L139" s="57" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M139" s="43" t="inlineStr">
         <is>
           <t>Hunting Party</t>
         </is>
       </c>
-      <c r="T139" s="81" t="n">
-        <v>10</v>
-      </c>
-      <c r="W139" s="81" t="n">
-        <v>2</v>
-      </c>
-      <c r="BX139" s="81" t="n">
-        <v>25</v>
-      </c>
+      <c r="T139" s="81" t="n"/>
+      <c r="W139" s="81" t="n"/>
+      <c r="BX139" s="81" t="n"/>
       <c r="BY139" s="81" t="n">
         <v>15</v>
       </c>
+      <c r="CI139" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="43" t="inlineStr">
@@ -25666,7 +25794,7 @@
         <v>1</v>
       </c>
       <c r="J143" s="92">
-        <f>'Towers'!$G$17*G143*H143*I143</f>
+        <f>J142*G143*H143*I143</f>
         <v/>
       </c>
       <c r="K143" s="92">
@@ -25674,21 +25802,22 @@
         <v/>
       </c>
       <c r="L143" s="57" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M143" s="43" t="inlineStr">
         <is>
           <t>Clinging Tar</t>
         </is>
       </c>
-      <c r="AE143" s="81" t="n">
-        <v>35</v>
-      </c>
+      <c r="AE143" s="81" t="n"/>
       <c r="AF143" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="CC143" s="81" t="n">
-        <v>0.5</v>
+      <c r="CC143" s="81" t="n"/>
+      <c r="CI143" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -25728,7 +25857,7 @@
         <v>1</v>
       </c>
       <c r="J144" s="92">
-        <f>'Towers'!$G$17*G144*H144*I144</f>
+        <f>J143*G144*H144*I144</f>
         <v/>
       </c>
       <c r="K144" s="92">
@@ -25736,21 +25865,20 @@
         <v/>
       </c>
       <c r="L144" s="57" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="M144" s="43" t="inlineStr">
         <is>
           <t>Tar Lake</t>
         </is>
       </c>
-      <c r="AE144" s="81" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF144" s="81" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC144" s="81" t="n">
-        <v>0.5</v>
+      <c r="AE144" s="81" t="n"/>
+      <c r="AF144" s="81" t="n"/>
+      <c r="CC144" s="81" t="n"/>
+      <c r="CI144" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -25958,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="J148" s="92">
-        <f>'Towers'!$G$17*G148*H148*I148</f>
+        <f>J147*G148*H148*I148</f>
         <v/>
       </c>
       <c r="K148" s="92">
@@ -25973,12 +26101,15 @@
           <t>Tar Fire</t>
         </is>
       </c>
-      <c r="X148" s="81" t="n">
-        <v>80</v>
-      </c>
+      <c r="X148" s="81" t="n"/>
       <c r="Y148" s="81" t="n">
         <v>2</v>
       </c>
+      <c r="CI148" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="43" t="inlineStr">
@@ -26017,7 +26148,7 @@
         <v>1</v>
       </c>
       <c r="J149" s="92">
-        <f>'Towers'!$G$17*G149*H149*I149</f>
+        <f>J148*G149*H149*I149</f>
         <v/>
       </c>
       <c r="K149" s="92">
@@ -26032,15 +26163,16 @@
           <t>Eruption</t>
         </is>
       </c>
-      <c r="X149" s="81" t="n">
-        <v>80</v>
-      </c>
-      <c r="Y149" s="81" t="n">
-        <v>2</v>
-      </c>
+      <c r="X149" s="81" t="n"/>
+      <c r="Y149" s="81" t="n"/>
       <c r="CF149" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="CI149" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -26252,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="J153" s="92">
-        <f>'Towers'!$G$17*G153*H153*I153</f>
+        <f>J152*G153*H153*I153</f>
         <v/>
       </c>
       <c r="K153" s="92">
@@ -26276,6 +26408,11 @@
       <c r="CG153" s="81" t="n">
         <v>15</v>
       </c>
+      <c r="CI153" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="43" t="inlineStr">
@@ -26314,7 +26451,7 @@
         <v>1</v>
       </c>
       <c r="J154" s="92">
-        <f>'Towers'!$G$17*G154*H154*I154</f>
+        <f>J153*G154*H154*I154</f>
         <v/>
       </c>
       <c r="K154" s="92">
@@ -26329,18 +26466,17 @@
           <t>Tar Totem</t>
         </is>
       </c>
-      <c r="CD154" s="81" t="n">
-        <v>25</v>
-      </c>
-      <c r="CE154" s="81" t="n">
-        <v>40</v>
-      </c>
-      <c r="CG154" s="81" t="n">
-        <v>15</v>
-      </c>
+      <c r="CD154" s="81" t="n"/>
+      <c r="CE154" s="81" t="n"/>
+      <c r="CG154" s="81" t="n"/>
       <c r="CH154" s="81" t="n">
         <v>15</v>
       </c>
+      <c r="CI154" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="43" t="inlineStr">
@@ -26532,7 +26668,7 @@
         <v/>
       </c>
       <c r="G158" s="57" t="n">
-        <v>13.03</v>
+        <v>1.899416909621</v>
       </c>
       <c r="H158" s="57" t="n">
         <v>1</v>
@@ -26541,7 +26677,7 @@
         <v>1</v>
       </c>
       <c r="J158" s="92">
-        <f>'Towers'!$G$18*G158*H158*I158</f>
+        <f>J157*G158*H158*I158</f>
         <v/>
       </c>
       <c r="K158" s="92">
@@ -26564,6 +26700,11 @@
       <c r="BJ158" s="81" t="n">
         <v>3</v>
       </c>
+      <c r="CI158" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="43" t="inlineStr">
@@ -26593,7 +26734,7 @@
         <v/>
       </c>
       <c r="G159" s="57" t="n">
-        <v>24.76</v>
+        <v>1.900230237913</v>
       </c>
       <c r="H159" s="57" t="n">
         <v>1.15</v>
@@ -26602,7 +26743,7 @@
         <v>1</v>
       </c>
       <c r="J159" s="92">
-        <f>'Towers'!$G$18*G159*H159*I159</f>
+        <f>J158*G159*H159*I159</f>
         <v/>
       </c>
       <c r="K159" s="92">
@@ -26617,17 +26758,16 @@
           <t>Skewer</t>
         </is>
       </c>
-      <c r="N159" s="81" t="inlineStr">
+      <c r="N159" s="81" t="n"/>
+      <c r="BJ159" s="81" t="n"/>
+      <c r="BZ159" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="BJ159" s="81" t="n">
-        <v>3</v>
-      </c>
-      <c r="BZ159" s="81" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="CI159" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -26821,7 +26961,7 @@
         <v/>
       </c>
       <c r="G163" s="57" t="n">
-        <v>2.86</v>
+        <v>1.3</v>
       </c>
       <c r="H163" s="57" t="n">
         <v>1</v>
@@ -26830,7 +26970,7 @@
         <v>1</v>
       </c>
       <c r="J163" s="92">
-        <f>'Towers'!$G$18*G163*H163*I163</f>
+        <f>J162*G163*H163*I163</f>
         <v/>
       </c>
       <c r="K163" s="92">
@@ -26838,19 +26978,22 @@
         <v/>
       </c>
       <c r="L163" s="57" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M163" s="43" t="inlineStr">
         <is>
           <t>Reel In</t>
         </is>
       </c>
-      <c r="U163" s="81" t="n">
-        <v>1</v>
-      </c>
+      <c r="U163" s="81" t="n"/>
       <c r="W163" s="81" t="n">
         <v>6</v>
       </c>
+      <c r="CI163" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="43" t="inlineStr">
@@ -26880,7 +27023,7 @@
         <v/>
       </c>
       <c r="G164" s="57" t="n">
-        <v>3.71</v>
+        <v>1.297202797203</v>
       </c>
       <c r="H164" s="57" t="n">
         <v>1</v>
@@ -26889,7 +27032,7 @@
         <v>1</v>
       </c>
       <c r="J164" s="92">
-        <f>'Towers'!$G$18*G164*H164*I164</f>
+        <f>J163*G164*H164*I164</f>
         <v/>
       </c>
       <c r="K164" s="92">
@@ -26897,22 +27040,23 @@
         <v/>
       </c>
       <c r="L164" s="57" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M164" s="43" t="inlineStr">
         <is>
           <t>Tow Line</t>
         </is>
       </c>
-      <c r="U164" s="81" t="n">
-        <v>1</v>
-      </c>
-      <c r="W164" s="81" t="n">
-        <v>6</v>
-      </c>
+      <c r="U164" s="81" t="n"/>
+      <c r="W164" s="81" t="n"/>
       <c r="CA164" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="CI164" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -27112,16 +27256,16 @@
         <v/>
       </c>
       <c r="G168" s="57" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="H168" s="57" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="I168" s="57" t="n">
         <v>1</v>
       </c>
       <c r="J168" s="92">
-        <f>'Towers'!$G$18*G168*H168*I168</f>
+        <f>J167*G168*H168*I168</f>
         <v/>
       </c>
       <c r="K168" s="92">
@@ -27136,8 +27280,11 @@
           <t>Steam Crank</t>
         </is>
       </c>
-      <c r="Q168" s="81" t="n">
-        <v>3</v>
+      <c r="Q168" s="81" t="n"/>
+      <c r="CI168" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -27168,16 +27315,16 @@
         <v/>
       </c>
       <c r="G169" s="57" t="n">
-        <v>1.6</v>
+        <v>1.333333333333</v>
       </c>
       <c r="H169" s="57" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="I169" s="57" t="n">
         <v>1</v>
       </c>
       <c r="J169" s="92">
-        <f>'Towers'!$G$18*G169*H169*I169</f>
+        <f>J168*G169*H169*I169</f>
         <v/>
       </c>
       <c r="K169" s="92">
@@ -27200,7 +27347,13 @@
           <t>Yes</t>
         </is>
       </c>
-    </row>
+      <c r="CI169" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="170"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -27806,7 +27959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA76"/>
+  <dimension ref="A1:BC77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="90" min="1" max="1"/>
@@ -27854,10 +28007,11 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Effect columns are cumulative per tier (like Tower Upgrades); blank = no change. x columns multiply the hero's base; Fire mode / Guns / Pellets / Pierce / Bounces override it. Crossover rule as towers: two paths, one past tier 2. Damage is per shot: pellets share the hero's base damage x its base pellet count, so more pellets spread the same damage wider and a slug concentrates it. Ignite: an enemy hit burns for Ignite (s), then takes one tick of Ignite tick x the whole shot's damage. The fire passes to the enemy's split children, so a Brute shot down to Husks sees them burn out together.</t>
-        </is>
-      </c>
-    </row>
+          <t>Effect columns are cumulative per tier (like Tower Upgrades); blank = no change. x columns multiply the hero's base; Fire mode / Guns / Pellets / Pierce / Bounces override it. Crossover rule as towers: two paths, one past tier 2. Damage is per shot: pellets share the hero's base damage x its base pellet count, so more pellets spread the same damage wider and a slug concentrates it. Ignite: an enemy hit burns for Ignite (s), then takes one tick of Ignite tick x the whole shot's damage. The fire passes to the enemy's split children, so a Brute shot down to Husks sees them burn out together. A/B/C (PLAN Phase 9, DECISIONS #275): tiers 1-3 rows are cumulative; a tier-4 or tier-5 row is one option (Option A/B/C, Blurb = its card line, max 60 chars) and holds ONLY ITS OWN STEP over the tier below; so does tier 6 (no option) (x columns multiply, amounts take the higher, flags add, overrides replace; blank = no change). The exporter composes every build. New options are appended at the bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -28122,6 +28276,16 @@
       <c r="BA4" s="104" t="inlineStr">
         <is>
           <t>Ability charges</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>Blurb</t>
         </is>
       </c>
     </row>
@@ -28342,11 +28506,11 @@
         <v/>
       </c>
       <c r="G8" s="57" t="n">
-        <v>1.6</v>
+        <v>1.230769230769</v>
       </c>
       <c r="H8" s="57" t="n"/>
       <c r="I8" s="57" t="n">
-        <v>0.8</v>
+        <v>0.941176470588</v>
       </c>
       <c r="J8" s="57" t="n"/>
       <c r="K8" s="57" t="n"/>
@@ -28354,9 +28518,7 @@
       <c r="M8" s="57" t="n"/>
       <c r="N8" s="57" t="n"/>
       <c r="O8" s="57" t="n"/>
-      <c r="P8" s="57" t="n">
-        <v>2</v>
-      </c>
+      <c r="P8" s="57" t="n"/>
       <c r="Q8" s="57" t="n"/>
       <c r="R8" s="57" t="n"/>
       <c r="S8" s="57" t="n"/>
@@ -28376,6 +28538,11 @@
       <c r="AG8" s="57" t="n"/>
       <c r="AH8" s="57" t="n"/>
       <c r="AI8" s="57" t="n"/>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="43" t="inlineStr">
@@ -28406,13 +28573,13 @@
         <v/>
       </c>
       <c r="G9" s="57" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="H9" s="57" t="n">
         <v>1.5</v>
       </c>
       <c r="I9" s="57" t="n">
-        <v>0.7</v>
+        <v>0.875</v>
       </c>
       <c r="J9" s="57" t="n"/>
       <c r="K9" s="57" t="n"/>
@@ -28424,9 +28591,7 @@
         </is>
       </c>
       <c r="O9" s="57" t="n"/>
-      <c r="P9" s="57" t="n">
-        <v>2</v>
-      </c>
+      <c r="P9" s="57" t="n"/>
       <c r="Q9" s="57" t="n"/>
       <c r="R9" s="57" t="n"/>
       <c r="S9" s="57" t="n"/>
@@ -28446,6 +28611,11 @@
       <c r="AG9" s="57" t="n"/>
       <c r="AH9" s="57" t="n"/>
       <c r="AI9" s="57" t="n"/>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="43" t="inlineStr">
@@ -28669,13 +28839,13 @@
       <c r="H13" s="57" t="n"/>
       <c r="I13" s="57" t="n"/>
       <c r="J13" s="57" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="K13" s="57" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L13" s="57" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="M13" s="57" t="n"/>
       <c r="N13" s="57" t="n"/>
@@ -28701,13 +28871,14 @@
       <c r="AD13" s="57" t="n"/>
       <c r="AE13" s="57" t="n"/>
       <c r="AF13" s="57" t="n"/>
-      <c r="AG13" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="AG13" s="57" t="n"/>
       <c r="AH13" s="57" t="n"/>
       <c r="AI13" s="57" t="n"/>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="43" t="inlineStr">
@@ -28741,13 +28912,13 @@
       <c r="H14" s="57" t="n"/>
       <c r="I14" s="57" t="n"/>
       <c r="J14" s="57" t="n">
-        <v>0.25</v>
+        <v>0.833333333333</v>
       </c>
       <c r="K14" s="57" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="L14" s="57" t="n">
-        <v>1.8</v>
+        <v>1.125</v>
       </c>
       <c r="M14" s="57" t="n"/>
       <c r="N14" s="57" t="n"/>
@@ -28757,11 +28928,7 @@
       <c r="R14" s="57" t="n"/>
       <c r="S14" s="57" t="n"/>
       <c r="T14" s="57" t="n"/>
-      <c r="U14" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="U14" s="57" t="n"/>
       <c r="V14" s="57" t="n"/>
       <c r="W14" s="57" t="n"/>
       <c r="X14" s="57" t="n"/>
@@ -28775,13 +28942,14 @@
       <c r="AD14" s="57" t="n"/>
       <c r="AE14" s="57" t="n"/>
       <c r="AF14" s="57" t="n"/>
-      <c r="AG14" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="AG14" s="57" t="n"/>
       <c r="AH14" s="57" t="n"/>
       <c r="AI14" s="57" t="n"/>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
@@ -28999,10 +29167,10 @@
       </c>
       <c r="G18" s="57" t="n"/>
       <c r="H18" s="57" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="I18" s="57" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J18" s="57" t="n"/>
       <c r="K18" s="57" t="n"/>
@@ -29014,9 +29182,7 @@
       <c r="Q18" s="57" t="n"/>
       <c r="R18" s="57" t="n"/>
       <c r="S18" s="57" t="n"/>
-      <c r="T18" s="57" t="n">
-        <v>1</v>
-      </c>
+      <c r="T18" s="57" t="n"/>
       <c r="U18" s="57" t="n"/>
       <c r="V18" s="57" t="n"/>
       <c r="W18" s="57" t="n"/>
@@ -29034,6 +29200,11 @@
       <c r="AG18" s="57" t="n"/>
       <c r="AH18" s="57" t="n"/>
       <c r="AI18" s="57" t="n"/>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="43" t="inlineStr">
@@ -29065,10 +29236,10 @@
       </c>
       <c r="G19" s="57" t="n"/>
       <c r="H19" s="57" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="I19" s="57" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J19" s="57" t="n"/>
       <c r="K19" s="57" t="n"/>
@@ -29092,7 +29263,7 @@
       <c r="AA19" s="57" t="n"/>
       <c r="AB19" s="57" t="n"/>
       <c r="AC19" s="57" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AD19" s="57" t="n"/>
       <c r="AE19" s="57" t="n"/>
@@ -29100,6 +29271,11 @@
       <c r="AG19" s="57" t="n"/>
       <c r="AH19" s="57" t="n"/>
       <c r="AI19" s="57" t="n"/>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="43" t="inlineStr">
@@ -29322,28 +29498,22 @@
         <v/>
       </c>
       <c r="G23" s="57" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="H23" s="57" t="n"/>
       <c r="I23" s="57" t="n"/>
       <c r="J23" s="57" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K23" s="57" t="n">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
       <c r="L23" s="57" t="n">
         <v>1.3</v>
       </c>
       <c r="M23" s="57" t="n"/>
-      <c r="N23" s="57" t="inlineStr">
-        <is>
-          <t>burst</t>
-        </is>
-      </c>
-      <c r="O23" s="57" t="n">
-        <v>3</v>
-      </c>
+      <c r="N23" s="57" t="n"/>
+      <c r="O23" s="57" t="n"/>
       <c r="P23" s="57" t="n"/>
       <c r="Q23" s="57" t="n"/>
       <c r="R23" s="57" t="n"/>
@@ -29364,6 +29534,11 @@
       <c r="AG23" s="57" t="n"/>
       <c r="AH23" s="57" t="n"/>
       <c r="AI23" s="57" t="n"/>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="43" t="inlineStr">
@@ -29394,27 +29569,23 @@
         <v/>
       </c>
       <c r="G24" s="57" t="n">
-        <v>1.5</v>
+        <v>1.071428571429</v>
       </c>
       <c r="H24" s="57" t="n"/>
       <c r="I24" s="57" t="n"/>
       <c r="J24" s="57" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K24" s="57" t="n">
-        <v>0.25</v>
+        <v>0.833333333333</v>
       </c>
       <c r="L24" s="57" t="n">
-        <v>1.5</v>
+        <v>1.153846153846</v>
       </c>
       <c r="M24" s="57" t="n">
         <v>1.3</v>
       </c>
-      <c r="N24" s="57" t="inlineStr">
-        <is>
-          <t>burst</t>
-        </is>
-      </c>
+      <c r="N24" s="57" t="n"/>
       <c r="O24" s="57" t="n">
         <v>4</v>
       </c>
@@ -29438,6 +29609,11 @@
       <c r="AG24" s="57" t="n"/>
       <c r="AH24" s="57" t="n"/>
       <c r="AI24" s="57" t="n"/>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="43" t="inlineStr">
@@ -29657,10 +29833,10 @@
       </c>
       <c r="G28" s="57" t="n"/>
       <c r="H28" s="57" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="I28" s="57" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="J28" s="57" t="n"/>
       <c r="K28" s="57" t="n"/>
@@ -29682,11 +29858,7 @@
       <c r="AA28" s="57" t="n"/>
       <c r="AB28" s="57" t="n"/>
       <c r="AC28" s="57" t="n"/>
-      <c r="AD28" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="AD28" s="57" t="n"/>
       <c r="AE28" s="57" t="n">
         <v>0.3</v>
       </c>
@@ -29694,6 +29866,11 @@
       <c r="AG28" s="57" t="n"/>
       <c r="AH28" s="57" t="n"/>
       <c r="AI28" s="57" t="n"/>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="43" t="inlineStr">
@@ -29725,10 +29902,10 @@
       </c>
       <c r="G29" s="57" t="n"/>
       <c r="H29" s="57" t="n">
-        <v>2.2</v>
+        <v>1.294117647059</v>
       </c>
       <c r="I29" s="57" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="J29" s="57" t="n"/>
       <c r="K29" s="57" t="n"/>
@@ -29750,13 +29927,9 @@
       <c r="AA29" s="57" t="n"/>
       <c r="AB29" s="57" t="n"/>
       <c r="AC29" s="57" t="n"/>
-      <c r="AD29" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="AD29" s="57" t="n"/>
       <c r="AE29" s="57" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AF29" s="57" t="n">
         <v>2.5</v>
@@ -29764,6 +29937,11 @@
       <c r="AG29" s="57" t="n"/>
       <c r="AH29" s="57" t="n"/>
       <c r="AI29" s="57" t="n"/>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="43" t="inlineStr">
@@ -30003,23 +30181,13 @@
       <c r="R33" s="57" t="n"/>
       <c r="S33" s="57" t="n"/>
       <c r="T33" s="57" t="n"/>
-      <c r="U33" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="U33" s="57" t="n"/>
       <c r="V33" s="57" t="n"/>
-      <c r="W33" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="X33" s="57" t="n">
-        <v>2</v>
-      </c>
+      <c r="W33" s="57" t="n"/>
+      <c r="X33" s="57" t="n"/>
       <c r="Y33" s="57" t="n"/>
       <c r="Z33" s="57" t="n"/>
-      <c r="AA33" s="57" t="n">
-        <v>10</v>
-      </c>
+      <c r="AA33" s="57" t="n"/>
       <c r="AB33" s="57" t="n"/>
       <c r="AC33" s="57" t="n"/>
       <c r="AD33" s="57" t="n"/>
@@ -30028,6 +30196,11 @@
       <c r="AG33" s="57" t="n"/>
       <c r="AH33" s="57" t="n"/>
       <c r="AI33" s="57" t="n"/>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="43" t="inlineStr">
@@ -30063,10 +30236,10 @@
       <c r="J34" s="57" t="n"/>
       <c r="K34" s="57" t="n"/>
       <c r="L34" s="57" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M34" s="57" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="N34" s="57" t="n"/>
       <c r="O34" s="57" t="n"/>
@@ -30075,25 +30248,15 @@
       <c r="R34" s="57" t="n"/>
       <c r="S34" s="57" t="n"/>
       <c r="T34" s="57" t="n"/>
-      <c r="U34" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="U34" s="57" t="n"/>
       <c r="V34" s="57" t="n"/>
-      <c r="W34" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="X34" s="57" t="n">
-        <v>2</v>
-      </c>
+      <c r="W34" s="57" t="n"/>
+      <c r="X34" s="57" t="n"/>
       <c r="Y34" s="57" t="n">
         <v>4</v>
       </c>
       <c r="Z34" s="57" t="n"/>
-      <c r="AA34" s="57" t="n">
-        <v>10</v>
-      </c>
+      <c r="AA34" s="57" t="n"/>
       <c r="AB34" s="57" t="n"/>
       <c r="AC34" s="57" t="n"/>
       <c r="AD34" s="57" t="n"/>
@@ -30102,6 +30265,11 @@
       <c r="AG34" s="57" t="n"/>
       <c r="AH34" s="57" t="n"/>
       <c r="AI34" s="57" t="n"/>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="43" t="inlineStr">
@@ -30351,36 +30519,26 @@
       <c r="H38" s="57" t="n"/>
       <c r="I38" s="57" t="n"/>
       <c r="J38" s="57" t="n">
-        <v>0.08</v>
+        <v>0.8</v>
       </c>
       <c r="K38" s="57" t="n"/>
       <c r="L38" s="57" t="n">
-        <v>2.6</v>
+        <v>1.181818181818</v>
       </c>
       <c r="M38" s="57" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="N38" s="57" t="n"/>
       <c r="O38" s="57" t="n"/>
       <c r="P38" s="57" t="n"/>
-      <c r="Q38" s="57" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q38" s="57" t="n"/>
       <c r="R38" s="57" t="n"/>
       <c r="S38" s="57" t="n">
         <v>3</v>
       </c>
       <c r="T38" s="57" t="n"/>
-      <c r="U38" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V38" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="U38" s="57" t="n"/>
+      <c r="V38" s="57" t="n"/>
       <c r="W38" s="57" t="n"/>
       <c r="X38" s="57" t="n"/>
       <c r="Y38" s="57" t="n"/>
@@ -30394,6 +30552,11 @@
       <c r="AG38" s="57" t="n"/>
       <c r="AH38" s="57" t="n"/>
       <c r="AI38" s="57" t="n"/>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="43" t="inlineStr">
@@ -30427,36 +30590,26 @@
       <c r="H39" s="57" t="n"/>
       <c r="I39" s="57" t="n"/>
       <c r="J39" s="57" t="n">
-        <v>0.05</v>
+        <v>0.625</v>
       </c>
       <c r="K39" s="57" t="n"/>
       <c r="L39" s="57" t="n">
-        <v>3</v>
+        <v>1.153846153846</v>
       </c>
       <c r="M39" s="57" t="n">
-        <v>1</v>
+        <v>1.492537313433</v>
       </c>
       <c r="N39" s="57" t="n"/>
       <c r="O39" s="57" t="n"/>
       <c r="P39" s="57" t="n"/>
-      <c r="Q39" s="57" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q39" s="57" t="n"/>
       <c r="R39" s="57" t="n"/>
       <c r="S39" s="57" t="n">
         <v>6</v>
       </c>
       <c r="T39" s="57" t="n"/>
-      <c r="U39" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V39" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="U39" s="57" t="n"/>
+      <c r="V39" s="57" t="n"/>
       <c r="W39" s="57" t="n"/>
       <c r="X39" s="57" t="n"/>
       <c r="Y39" s="57" t="n"/>
@@ -30470,6 +30623,11 @@
       <c r="AG39" s="57" t="n"/>
       <c r="AH39" s="57" t="n"/>
       <c r="AI39" s="57" t="n"/>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="43" t="inlineStr">
@@ -30699,7 +30857,7 @@
         <v>0.8</v>
       </c>
       <c r="J43" s="57" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K43" s="57" t="n"/>
       <c r="L43" s="57" t="n"/>
@@ -30707,20 +30865,14 @@
       <c r="N43" s="57" t="n"/>
       <c r="O43" s="57" t="n"/>
       <c r="P43" s="57" t="n"/>
-      <c r="Q43" s="57" t="n">
-        <v>9</v>
-      </c>
+      <c r="Q43" s="57" t="n"/>
       <c r="R43" s="57" t="n"/>
       <c r="S43" s="57" t="n"/>
       <c r="T43" s="57" t="n"/>
       <c r="U43" s="57" t="n"/>
       <c r="V43" s="57" t="n"/>
-      <c r="W43" s="57" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X43" s="57" t="n">
-        <v>3</v>
-      </c>
+      <c r="W43" s="57" t="n"/>
+      <c r="X43" s="57" t="n"/>
       <c r="Y43" s="57" t="n"/>
       <c r="Z43" s="57" t="n"/>
       <c r="AA43" s="57" t="n"/>
@@ -30730,11 +30882,12 @@
       <c r="AE43" s="57" t="n"/>
       <c r="AF43" s="57" t="n"/>
       <c r="AG43" s="57" t="n"/>
-      <c r="AH43" s="57" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI43" s="57" t="n">
-        <v>0.35</v>
+      <c r="AH43" s="57" t="n"/>
+      <c r="AI43" s="57" t="n"/>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -30766,16 +30919,16 @@
         <v/>
       </c>
       <c r="G44" s="57" t="n">
-        <v>2.2</v>
+        <v>1.375</v>
       </c>
       <c r="H44" s="57" t="n">
         <v>2</v>
       </c>
       <c r="I44" s="57" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J44" s="57" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K44" s="57" t="n"/>
       <c r="L44" s="57" t="n"/>
@@ -30787,20 +30940,14 @@
       </c>
       <c r="O44" s="57" t="n"/>
       <c r="P44" s="57" t="n"/>
-      <c r="Q44" s="57" t="n">
-        <v>9</v>
-      </c>
+      <c r="Q44" s="57" t="n"/>
       <c r="R44" s="57" t="n"/>
       <c r="S44" s="57" t="n"/>
       <c r="T44" s="57" t="n"/>
       <c r="U44" s="57" t="n"/>
       <c r="V44" s="57" t="n"/>
-      <c r="W44" s="57" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X44" s="57" t="n">
-        <v>3</v>
-      </c>
+      <c r="W44" s="57" t="n"/>
+      <c r="X44" s="57" t="n"/>
       <c r="Y44" s="57" t="n"/>
       <c r="Z44" s="57" t="n"/>
       <c r="AA44" s="57" t="n"/>
@@ -30810,11 +30957,12 @@
       <c r="AE44" s="57" t="n"/>
       <c r="AF44" s="57" t="n"/>
       <c r="AG44" s="57" t="n"/>
-      <c r="AH44" s="57" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI44" s="57" t="n">
-        <v>0.35</v>
+      <c r="AH44" s="57" t="n"/>
+      <c r="AI44" s="57" t="n"/>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -31033,10 +31181,10 @@
       </c>
       <c r="G48" s="57" t="n"/>
       <c r="H48" s="57" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I48" s="57" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J48" s="57" t="n"/>
       <c r="K48" s="57" t="n"/>
@@ -31046,9 +31194,7 @@
       <c r="O48" s="57" t="n"/>
       <c r="P48" s="57" t="n"/>
       <c r="Q48" s="57" t="n"/>
-      <c r="R48" s="57" t="n">
-        <v>2</v>
-      </c>
+      <c r="R48" s="57" t="n"/>
       <c r="S48" s="57" t="n"/>
       <c r="T48" s="57" t="n"/>
       <c r="U48" s="57" t="n"/>
@@ -31068,6 +31214,11 @@
       <c r="AG48" s="57" t="n"/>
       <c r="AH48" s="57" t="n"/>
       <c r="AI48" s="57" t="n"/>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="43" t="inlineStr">
@@ -31099,10 +31250,10 @@
       </c>
       <c r="G49" s="57" t="n"/>
       <c r="H49" s="57" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I49" s="57" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J49" s="57" t="n"/>
       <c r="K49" s="57" t="n"/>
@@ -31112,9 +31263,7 @@
       <c r="O49" s="57" t="n"/>
       <c r="P49" s="57" t="n"/>
       <c r="Q49" s="57" t="n"/>
-      <c r="R49" s="57" t="n">
-        <v>2</v>
-      </c>
+      <c r="R49" s="57" t="n"/>
       <c r="S49" s="57" t="n"/>
       <c r="T49" s="57" t="n"/>
       <c r="U49" s="57" t="n"/>
@@ -31124,9 +31273,7 @@
       <c r="Y49" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="Z49" s="57" t="n">
-        <v>4</v>
-      </c>
+      <c r="Z49" s="57" t="n"/>
       <c r="AA49" s="57" t="n"/>
       <c r="AB49" s="57" t="n"/>
       <c r="AC49" s="57" t="n"/>
@@ -31136,6 +31283,11 @@
       <c r="AG49" s="57" t="n"/>
       <c r="AH49" s="57" t="n"/>
       <c r="AI49" s="57" t="n"/>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="43" t="inlineStr">
@@ -31380,7 +31532,7 @@
       <c r="AA53" s="57" t="n"/>
       <c r="AB53" s="57" t="n"/>
       <c r="AC53" s="57" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD53" s="57" t="n"/>
       <c r="AE53" s="57" t="n"/>
@@ -31389,14 +31541,15 @@
       <c r="AH53" s="57" t="n"/>
       <c r="AI53" s="57" t="n"/>
       <c r="AJ53" s="81" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AK53" s="81" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL53" s="81" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AL53" s="81" t="n"/>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -31451,7 +31604,7 @@
       <c r="AA54" s="57" t="n"/>
       <c r="AB54" s="57" t="n"/>
       <c r="AC54" s="57" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD54" s="57" t="n"/>
       <c r="AE54" s="57" t="n"/>
@@ -31460,21 +31613,22 @@
       <c r="AH54" s="57" t="n"/>
       <c r="AI54" s="57" t="n"/>
       <c r="AJ54" s="81" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AK54" s="81" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL54" s="81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AL54" s="81" t="n"/>
       <c r="AM54" s="81" t="n">
         <v>30</v>
       </c>
       <c r="AN54" s="81" t="n">
         <v>8</v>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -31700,13 +31854,13 @@
         <v/>
       </c>
       <c r="G58" s="57" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="H58" s="57" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I58" s="57" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J58" s="57" t="n"/>
       <c r="K58" s="57" t="n">
@@ -31714,14 +31868,8 @@
       </c>
       <c r="L58" s="57" t="n"/>
       <c r="M58" s="57" t="n"/>
-      <c r="N58" s="57" t="inlineStr">
-        <is>
-          <t>burst</t>
-        </is>
-      </c>
-      <c r="O58" s="57" t="n">
-        <v>2</v>
-      </c>
+      <c r="N58" s="57" t="n"/>
+      <c r="O58" s="57" t="n"/>
       <c r="P58" s="57" t="n"/>
       <c r="Q58" s="57" t="n"/>
       <c r="R58" s="57" t="n"/>
@@ -31742,6 +31890,11 @@
       <c r="AG58" s="57" t="n"/>
       <c r="AH58" s="57" t="n"/>
       <c r="AI58" s="57" t="n"/>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="43" t="inlineStr">
@@ -31772,17 +31925,17 @@
         <v/>
       </c>
       <c r="G59" s="57" t="n">
-        <v>1.6</v>
+        <v>1.333333333333</v>
       </c>
       <c r="H59" s="57" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I59" s="57" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J59" s="57" t="n"/>
       <c r="K59" s="57" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L59" s="57" t="n"/>
       <c r="M59" s="57" t="n"/>
@@ -31791,7 +31944,9 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="O59" s="57" t="n"/>
+      <c r="O59" s="57" t="n">
+        <v>0</v>
+      </c>
       <c r="P59" s="57" t="n"/>
       <c r="Q59" s="57" t="n"/>
       <c r="R59" s="57" t="n"/>
@@ -31812,6 +31967,11 @@
       <c r="AG59" s="57" t="n"/>
       <c r="AH59" s="57" t="n"/>
       <c r="AI59" s="57" t="n"/>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="43" t="inlineStr">
@@ -32065,14 +32225,15 @@
       <c r="AG63" s="57" t="n"/>
       <c r="AH63" s="57" t="n"/>
       <c r="AI63" s="57" t="n"/>
-      <c r="AO63" s="81" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP63" s="81" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="AO63" s="81" t="n"/>
+      <c r="AP63" s="81" t="n"/>
       <c r="AQ63" s="81" t="n">
         <v>3</v>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -32132,18 +32293,17 @@
       <c r="AG64" s="57" t="n"/>
       <c r="AH64" s="57" t="n"/>
       <c r="AI64" s="57" t="n"/>
-      <c r="AO64" s="81" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP64" s="81" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ64" s="81" t="n">
-        <v>3</v>
-      </c>
+      <c r="AO64" s="81" t="n"/>
+      <c r="AP64" s="81" t="n"/>
+      <c r="AQ64" s="81" t="n"/>
       <c r="AR64" s="81" t="n">
         <v>6</v>
       </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="43" t="inlineStr">
@@ -32174,27 +32334,21 @@
         <v/>
       </c>
       <c r="G65" s="57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H65" s="57" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I65" s="57" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J65" s="57" t="n"/>
       <c r="K65" s="57" t="n"/>
       <c r="L65" s="57" t="n"/>
       <c r="M65" s="57" t="n"/>
-      <c r="N65" s="57" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
+      <c r="N65" s="57" t="n"/>
       <c r="O65" s="57" t="n"/>
-      <c r="P65" s="57" t="n">
-        <v>2</v>
-      </c>
+      <c r="P65" s="57" t="n"/>
       <c r="Q65" s="57" t="n"/>
       <c r="R65" s="57" t="n"/>
       <c r="S65" s="57" t="n"/>
@@ -32252,13 +32406,13 @@
       <c r="H66" s="57" t="n"/>
       <c r="I66" s="57" t="n"/>
       <c r="J66" s="57" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="K66" s="57" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="L66" s="57" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="M66" s="57" t="n"/>
       <c r="N66" s="57" t="n"/>
@@ -32268,11 +32422,7 @@
       <c r="R66" s="57" t="n"/>
       <c r="S66" s="57" t="n"/>
       <c r="T66" s="57" t="n"/>
-      <c r="U66" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="U66" s="57" t="n"/>
       <c r="V66" s="57" t="n"/>
       <c r="W66" s="57" t="n"/>
       <c r="X66" s="57" t="n"/>
@@ -32280,17 +32430,13 @@
       <c r="Z66" s="57" t="n"/>
       <c r="AA66" s="57" t="n"/>
       <c r="AB66" s="57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC66" s="57" t="n"/>
       <c r="AD66" s="57" t="n"/>
       <c r="AE66" s="57" t="n"/>
       <c r="AF66" s="57" t="n"/>
-      <c r="AG66" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="AG66" s="57" t="n"/>
       <c r="AH66" s="57" t="n"/>
       <c r="AI66" s="57" t="n"/>
       <c r="AS66" s="81" t="n">
@@ -32330,10 +32476,10 @@
       </c>
       <c r="G67" s="57" t="n"/>
       <c r="H67" s="57" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="I67" s="57" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J67" s="57" t="n"/>
       <c r="K67" s="57" t="n"/>
@@ -32345,9 +32491,7 @@
       <c r="Q67" s="57" t="n"/>
       <c r="R67" s="57" t="n"/>
       <c r="S67" s="57" t="n"/>
-      <c r="T67" s="57" t="n">
-        <v>4</v>
-      </c>
+      <c r="T67" s="57" t="n"/>
       <c r="U67" s="57" t="n"/>
       <c r="V67" s="57" t="n"/>
       <c r="W67" s="57" t="n"/>
@@ -32357,7 +32501,7 @@
       <c r="AA67" s="57" t="n"/>
       <c r="AB67" s="57" t="n"/>
       <c r="AC67" s="57" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AD67" s="57" t="n"/>
       <c r="AE67" s="57" t="n"/>
@@ -32398,27 +32542,23 @@
         <v/>
       </c>
       <c r="G68" s="57" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H68" s="57" t="n"/>
       <c r="I68" s="57" t="n"/>
       <c r="J68" s="57" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="K68" s="57" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L68" s="57" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M68" s="57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N68" s="57" t="inlineStr">
-        <is>
-          <t>burst</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N68" s="57" t="n"/>
       <c r="O68" s="57" t="n">
         <v>5</v>
       </c>
@@ -32478,10 +32618,10 @@
       </c>
       <c r="G69" s="57" t="n"/>
       <c r="H69" s="57" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="I69" s="57" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="J69" s="57" t="n"/>
       <c r="K69" s="57" t="n"/>
@@ -32503,16 +32643,12 @@
       <c r="AA69" s="57" t="n"/>
       <c r="AB69" s="57" t="n"/>
       <c r="AC69" s="57" t="n"/>
-      <c r="AD69" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="AD69" s="57" t="n"/>
       <c r="AE69" s="57" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AF69" s="57" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="AG69" s="57" t="n"/>
       <c r="AH69" s="57" t="n"/>
@@ -32557,10 +32693,10 @@
       <c r="J70" s="57" t="n"/>
       <c r="K70" s="57" t="n"/>
       <c r="L70" s="57" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M70" s="57" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="N70" s="57" t="n"/>
       <c r="O70" s="57" t="n"/>
@@ -32569,25 +32705,15 @@
       <c r="R70" s="57" t="n"/>
       <c r="S70" s="57" t="n"/>
       <c r="T70" s="57" t="n"/>
-      <c r="U70" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="U70" s="57" t="n"/>
       <c r="V70" s="57" t="n"/>
-      <c r="W70" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="X70" s="57" t="n">
-        <v>2</v>
-      </c>
+      <c r="W70" s="57" t="n"/>
+      <c r="X70" s="57" t="n"/>
       <c r="Y70" s="57" t="n">
         <v>6</v>
       </c>
       <c r="Z70" s="57" t="n"/>
-      <c r="AA70" s="57" t="n">
-        <v>10</v>
-      </c>
+      <c r="AA70" s="57" t="n"/>
       <c r="AB70" s="57" t="n"/>
       <c r="AC70" s="57" t="n"/>
       <c r="AD70" s="57" t="n"/>
@@ -32629,11 +32755,11 @@
       <c r="H71" s="57" t="n"/>
       <c r="I71" s="57" t="n"/>
       <c r="J71" s="57" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="K71" s="57" t="n"/>
       <c r="L71" s="57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M71" s="57" t="n">
         <v>1</v>
@@ -32641,24 +32767,12 @@
       <c r="N71" s="57" t="n"/>
       <c r="O71" s="57" t="n"/>
       <c r="P71" s="57" t="n"/>
-      <c r="Q71" s="57" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q71" s="57" t="n"/>
       <c r="R71" s="57" t="n"/>
-      <c r="S71" s="57" t="n">
-        <v>6</v>
-      </c>
+      <c r="S71" s="57" t="n"/>
       <c r="T71" s="57" t="n"/>
-      <c r="U71" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V71" s="57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="U71" s="57" t="n"/>
+      <c r="V71" s="57" t="n"/>
       <c r="W71" s="57" t="n"/>
       <c r="X71" s="57" t="n"/>
       <c r="Y71" s="57" t="n"/>
@@ -32708,41 +32822,31 @@
         <v/>
       </c>
       <c r="G72" s="57" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="H72" s="57" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="I72" s="57" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J72" s="57" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K72" s="57" t="n"/>
       <c r="L72" s="57" t="n"/>
       <c r="M72" s="57" t="n"/>
-      <c r="N72" s="57" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
+      <c r="N72" s="57" t="n"/>
       <c r="O72" s="57" t="n"/>
       <c r="P72" s="57" t="n"/>
-      <c r="Q72" s="57" t="n">
-        <v>9</v>
-      </c>
+      <c r="Q72" s="57" t="n"/>
       <c r="R72" s="57" t="n"/>
       <c r="S72" s="57" t="n"/>
       <c r="T72" s="57" t="n"/>
       <c r="U72" s="57" t="n"/>
       <c r="V72" s="57" t="n"/>
-      <c r="W72" s="57" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X72" s="57" t="n">
-        <v>3</v>
-      </c>
+      <c r="W72" s="57" t="n"/>
+      <c r="X72" s="57" t="n"/>
       <c r="Y72" s="57" t="n"/>
       <c r="Z72" s="57" t="n"/>
       <c r="AA72" s="57" t="n"/>
@@ -32752,12 +32856,8 @@
       <c r="AE72" s="57" t="n"/>
       <c r="AF72" s="57" t="n"/>
       <c r="AG72" s="57" t="n"/>
-      <c r="AH72" s="57" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI72" s="57" t="n">
-        <v>0.35</v>
-      </c>
+      <c r="AH72" s="57" t="n"/>
+      <c r="AI72" s="57" t="n"/>
       <c r="AT72" s="81" t="n">
         <v>4</v>
       </c>
@@ -32792,10 +32892,10 @@
       </c>
       <c r="G73" s="57" t="n"/>
       <c r="H73" s="57" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I73" s="57" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="J73" s="57" t="n"/>
       <c r="K73" s="57" t="n"/>
@@ -32814,12 +32914,8 @@
       <c r="V73" s="57" t="n"/>
       <c r="W73" s="57" t="n"/>
       <c r="X73" s="57" t="n"/>
-      <c r="Y73" s="57" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z73" s="57" t="n">
-        <v>4</v>
-      </c>
+      <c r="Y73" s="57" t="n"/>
+      <c r="Z73" s="57" t="n"/>
       <c r="AA73" s="57" t="n"/>
       <c r="AB73" s="57" t="n"/>
       <c r="AC73" s="57" t="n"/>
@@ -32881,7 +32977,7 @@
       <c r="AA74" s="57" t="n"/>
       <c r="AB74" s="57" t="n"/>
       <c r="AC74" s="57" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD74" s="57" t="n"/>
       <c r="AE74" s="57" t="n"/>
@@ -32890,22 +32986,14 @@
       <c r="AH74" s="57" t="n"/>
       <c r="AI74" s="57" t="n"/>
       <c r="AJ74" s="81" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AK74" s="81" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL74" s="81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AM74" s="81" t="n">
-        <v>30</v>
-      </c>
-      <c r="AN74" s="81" t="n">
-        <v>8</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AL74" s="81" t="n"/>
+      <c r="AM74" s="81" t="n"/>
+      <c r="AN74" s="81" t="n"/>
       <c r="BA74" s="81" t="n">
         <v>2</v>
       </c>
@@ -32939,25 +33027,21 @@
         <v/>
       </c>
       <c r="G75" s="57" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="H75" s="57" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="I75" s="57" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="J75" s="57" t="n"/>
       <c r="K75" s="57" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L75" s="57" t="n"/>
       <c r="M75" s="57" t="n"/>
-      <c r="N75" s="57" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
+      <c r="N75" s="57" t="n"/>
       <c r="O75" s="57" t="n"/>
       <c r="P75" s="57" t="n"/>
       <c r="Q75" s="57" t="n"/>
@@ -33037,12 +33121,8 @@
       <c r="AG76" s="57" t="n"/>
       <c r="AH76" s="57" t="n"/>
       <c r="AI76" s="57" t="n"/>
-      <c r="AO76" s="81" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP76" s="81" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="AO76" s="81" t="n"/>
+      <c r="AP76" s="81" t="n"/>
       <c r="AQ76" s="81" t="n">
         <v>4</v>
       </c>
@@ -33050,6 +33130,7 @@
         <v>9</v>
       </c>
     </row>
+    <row r="77"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -13262,7 +13262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ170"/>
+  <dimension ref="A1:CJ169"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -13832,12 +13832,12 @@
           <t>Aura vs slowed %</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CI4" s="81" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CJ4" s="81" t="inlineStr">
         <is>
           <t>Blurb</t>
         </is>
@@ -14188,9 +14188,14 @@
       <c r="AR8" s="57" t="n"/>
       <c r="AS8" s="57" t="n"/>
       <c r="AT8" s="57" t="n"/>
-      <c r="CI8" t="inlineStr">
+      <c r="CI8" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>Sees further, and shoots faster and harder</t>
         </is>
       </c>
     </row>
@@ -14285,9 +14290,14 @@
       <c r="AR9" s="57" t="n"/>
       <c r="AS9" s="57" t="n"/>
       <c r="AT9" s="57" t="n"/>
-      <c r="CI9" t="inlineStr">
+      <c r="CI9" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>Towers in range hit harder and can hurt armour</t>
         </is>
       </c>
     </row>
@@ -14636,9 +14646,14 @@
       <c r="AR13" s="57" t="n"/>
       <c r="AS13" s="57" t="n"/>
       <c r="AT13" s="57" t="n"/>
-      <c r="CI13" t="inlineStr">
+      <c r="CI13" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>Fires much faster and hits harder</t>
         </is>
       </c>
     </row>
@@ -14729,9 +14744,14 @@
       <c r="AR14" s="57" t="n"/>
       <c r="AS14" s="57" t="n"/>
       <c r="AT14" s="57" t="n"/>
-      <c r="CI14" t="inlineStr">
+      <c r="CI14" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ14" t="inlineStr">
+        <is>
+          <t>The fastest fire in the game</t>
         </is>
       </c>
     </row>
@@ -15095,9 +15115,14 @@
       <c r="BJ18" s="105" t="n">
         <v>2</v>
       </c>
-      <c r="CI18" t="inlineStr">
+      <c r="CI18" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ18" t="inlineStr">
+        <is>
+          <t>Each bullet goes through 3 dinos</t>
         </is>
       </c>
     </row>
@@ -15191,9 +15216,14 @@
       <c r="AS19" s="57" t="n"/>
       <c r="AT19" s="57" t="n"/>
       <c r="BJ19" s="105" t="n"/>
-      <c r="CI19" t="inlineStr">
+      <c r="CI19" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ19" t="inlineStr">
+        <is>
+          <t>Hits armoured dinos and bosses 4 times as hard</t>
         </is>
       </c>
     </row>
@@ -15559,9 +15589,14 @@
       <c r="BJ23" s="105" t="n">
         <v>2</v>
       </c>
-      <c r="CI23" t="inlineStr">
+      <c r="CI23" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ23" t="inlineStr">
+        <is>
+          <t>Shots go through more dinos, shrinking each 2 sizes</t>
         </is>
       </c>
     </row>
@@ -15655,9 +15690,14 @@
       <c r="BJ24" s="105" t="n">
         <v>3</v>
       </c>
-      <c r="CI24" t="inlineStr">
+      <c r="CI24" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ24" t="inlineStr">
+        <is>
+          <t>Each shot hits 10 dinos in a line, double damage</t>
         </is>
       </c>
     </row>
@@ -16008,9 +16048,14 @@
       <c r="AR28" s="57" t="n"/>
       <c r="AS28" s="57" t="n"/>
       <c r="AT28" s="57" t="n"/>
-      <c r="CI28" t="inlineStr">
+      <c r="CI28" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ28" t="inlineStr">
+        <is>
+          <t>Fires faster, and its mark hits harder</t>
         </is>
       </c>
     </row>
@@ -16103,9 +16148,14 @@
       <c r="AR29" s="57" t="n"/>
       <c r="AS29" s="57" t="n"/>
       <c r="AT29" s="57" t="n"/>
-      <c r="CI29" t="inlineStr">
+      <c r="CI29" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ29" t="inlineStr">
+        <is>
+          <t>A bigger mark, and towers in range shoot faster</t>
         </is>
       </c>
     </row>
@@ -16471,9 +16521,14 @@
       <c r="BJ33" s="105" t="n">
         <v>3</v>
       </c>
-      <c r="CI33" t="inlineStr">
+      <c r="CI33" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ33" t="inlineStr">
+        <is>
+          <t>Huge shots that stun and shrink a dino 3 sizes</t>
         </is>
       </c>
     </row>
@@ -16573,9 +16628,14 @@
       <c r="BJ34" s="105" t="n">
         <v>4</v>
       </c>
-      <c r="CI34" t="inlineStr">
+      <c r="CI34" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ34" t="inlineStr">
+        <is>
+          <t>10 times damage to bosses, and stuns them</t>
         </is>
       </c>
     </row>
@@ -16938,9 +16998,14 @@
       <c r="AR38" s="57" t="n"/>
       <c r="AS38" s="57" t="n"/>
       <c r="AT38" s="57" t="n"/>
-      <c r="CI38" t="inlineStr">
+      <c r="CI38" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ38" t="inlineStr">
+        <is>
+          <t>Bigger blasts that leave dinos burning</t>
         </is>
       </c>
     </row>
@@ -17035,9 +17100,14 @@
       <c r="AR39" s="57" t="n"/>
       <c r="AS39" s="57" t="n"/>
       <c r="AT39" s="57" t="n"/>
-      <c r="CI39" t="inlineStr">
+      <c r="CI39" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ39" t="inlineStr">
+        <is>
+          <t>Leaves a long burning stretch of track</t>
         </is>
       </c>
     </row>
@@ -17398,9 +17468,14 @@
       <c r="AR43" s="57" t="n"/>
       <c r="AS43" s="57" t="n"/>
       <c r="AT43" s="57" t="n"/>
-      <c r="CI43" t="inlineStr">
+      <c r="CI43" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ43" t="inlineStr">
+        <is>
+          <t>More bomblets and harder blasts</t>
         </is>
       </c>
     </row>
@@ -17491,9 +17566,14 @@
       <c r="AR44" s="57" t="n"/>
       <c r="AS44" s="57" t="n"/>
       <c r="AT44" s="57" t="n"/>
-      <c r="CI44" t="inlineStr">
+      <c r="CI44" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ44" t="inlineStr">
+        <is>
+          <t>Even more bomblets rain down</t>
         </is>
       </c>
     </row>
@@ -17864,9 +17944,14 @@
       <c r="AR48" s="57" t="n"/>
       <c r="AS48" s="57" t="n"/>
       <c r="AT48" s="57" t="n"/>
-      <c r="CI48" t="inlineStr">
+      <c r="CI48" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ48" t="inlineStr">
+        <is>
+          <t>Hits much harder and knocks dinos further back</t>
         </is>
       </c>
     </row>
@@ -17959,9 +18044,14 @@
       <c r="AR49" s="57" t="n"/>
       <c r="AS49" s="57" t="n"/>
       <c r="AT49" s="57" t="n"/>
-      <c r="CI49" t="inlineStr">
+      <c r="CI49" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ49" t="inlineStr">
+        <is>
+          <t>Stuns every dino it hits for a second</t>
         </is>
       </c>
     </row>
@@ -18318,9 +18408,14 @@
       <c r="AR53" s="57" t="n"/>
       <c r="AS53" s="57" t="n"/>
       <c r="AT53" s="57" t="n"/>
-      <c r="CI53" t="inlineStr">
+      <c r="CI53" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ53" t="inlineStr">
+        <is>
+          <t>A much stronger slow over a wider area</t>
         </is>
       </c>
     </row>
@@ -18417,9 +18512,14 @@
       <c r="AR54" s="57" t="n"/>
       <c r="AS54" s="57" t="n"/>
       <c r="AT54" s="57" t="n"/>
-      <c r="CI54" t="inlineStr">
+      <c r="CI54" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ54" t="inlineStr">
+        <is>
+          <t>Its slow works on bosses too</t>
         </is>
       </c>
     </row>
@@ -18784,9 +18884,14 @@
       <c r="AR58" s="57" t="n"/>
       <c r="AS58" s="57" t="n"/>
       <c r="AT58" s="57" t="n"/>
-      <c r="CI58" t="inlineStr">
+      <c r="CI58" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ58" t="inlineStr">
+        <is>
+          <t>Knockouts come sooner and hurt more</t>
         </is>
       </c>
     </row>
@@ -18883,9 +18988,14 @@
       <c r="AR59" s="57" t="n"/>
       <c r="AS59" s="57" t="n"/>
       <c r="AT59" s="57" t="n"/>
-      <c r="CI59" t="inlineStr">
+      <c r="CI59" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ59" t="inlineStr">
+        <is>
+          <t>A long knockout that even holds bosses</t>
         </is>
       </c>
     </row>
@@ -19250,9 +19360,14 @@
       <c r="AR63" s="57" t="n"/>
       <c r="AS63" s="57" t="n"/>
       <c r="AT63" s="57" t="n"/>
-      <c r="CI63" t="inlineStr">
+      <c r="CI63" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ63" t="inlineStr">
+        <is>
+          <t>Sedated dinos take even more damage</t>
         </is>
       </c>
     </row>
@@ -19345,9 +19460,14 @@
       <c r="AR64" s="57" t="n"/>
       <c r="AS64" s="57" t="n"/>
       <c r="AT64" s="57" t="n"/>
-      <c r="CI64" t="inlineStr">
+      <c r="CI64" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ64" t="inlineStr">
+        <is>
+          <t>Dinos take much more damage; towers in range hit harder</t>
         </is>
       </c>
     </row>
@@ -19702,9 +19822,14 @@
       <c r="AR68" s="57" t="n"/>
       <c r="AS68" s="57" t="n"/>
       <c r="AT68" s="57" t="n"/>
-      <c r="CI68" t="inlineStr">
+      <c r="CI68" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ68" t="inlineStr">
+        <is>
+          <t>Pays a lot more cash every round</t>
         </is>
       </c>
     </row>
@@ -19799,9 +19924,14 @@
       <c r="AR69" s="57" t="n"/>
       <c r="AS69" s="57" t="n"/>
       <c r="AT69" s="57" t="n"/>
-      <c r="CI69" t="inlineStr">
+      <c r="CI69" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ69" t="inlineStr">
+        <is>
+          <t>Earns interest on your banked cash</t>
         </is>
       </c>
     </row>
@@ -20164,9 +20294,14 @@
       </c>
       <c r="AS73" s="57" t="n"/>
       <c r="AT73" s="57" t="n"/>
-      <c r="CI73" t="inlineStr">
+      <c r="CI73" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ73" t="inlineStr">
+        <is>
+          <t>More chests land each round, worth more</t>
         </is>
       </c>
     </row>
@@ -20259,9 +20394,14 @@
       </c>
       <c r="AS74" s="57" t="n"/>
       <c r="AT74" s="57" t="n"/>
-      <c r="CI74" t="inlineStr">
+      <c r="CI74" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ74" t="inlineStr">
+        <is>
+          <t>The richest chests, and more of them</t>
         </is>
       </c>
     </row>
@@ -20618,9 +20758,14 @@
       <c r="AR78" s="57" t="n"/>
       <c r="AS78" s="57" t="n"/>
       <c r="AT78" s="57" t="n"/>
-      <c r="CI78" t="inlineStr">
+      <c r="CI78" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ78" t="inlineStr">
+        <is>
+          <t>Towers in range shoot faster</t>
         </is>
       </c>
     </row>
@@ -20713,9 +20858,14 @@
       <c r="AT79" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="CI79" t="inlineStr">
+      <c r="CI79" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ79" t="inlineStr">
+        <is>
+          <t>Towers in range cost less and sell for full price</t>
         </is>
       </c>
     </row>
@@ -21102,9 +21252,14 @@
       <c r="AY83" s="57" t="n"/>
       <c r="AZ83" s="57" t="n"/>
       <c r="BA83" s="57" t="n"/>
-      <c r="CI83" t="inlineStr">
+      <c r="CI83" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ83" t="inlineStr">
+        <is>
+          <t>Tougher armour, and biters take more damage back</t>
         </is>
       </c>
     </row>
@@ -21204,9 +21359,14 @@
       <c r="AY84" s="57" t="n"/>
       <c r="AZ84" s="57" t="n"/>
       <c r="BA84" s="57" t="n"/>
-      <c r="CI84" t="inlineStr">
+      <c r="CI84" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ84" t="inlineStr">
+        <is>
+          <t>The best armour; biting dinos get stunned (not bosses)</t>
         </is>
       </c>
     </row>
@@ -21599,9 +21759,14 @@
       <c r="AY88" s="57" t="n"/>
       <c r="AZ88" s="57" t="n"/>
       <c r="BA88" s="57" t="n"/>
-      <c r="CI88" t="inlineStr">
+      <c r="CI88" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ88" t="inlineStr">
+        <is>
+          <t>Towers in range hit harder and shoot faster</t>
         </is>
       </c>
     </row>
@@ -21701,9 +21866,14 @@
       <c r="AY89" s="57" t="n"/>
       <c r="AZ89" s="57" t="n"/>
       <c r="BA89" s="57" t="n"/>
-      <c r="CI89" t="inlineStr">
+      <c r="CI89" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ89" t="inlineStr">
+        <is>
+          <t>Towers in range hit much harder and faster</t>
         </is>
       </c>
     </row>
@@ -22090,9 +22260,14 @@
         <v>0.7</v>
       </c>
       <c r="BA93" s="57" t="n"/>
-      <c r="CI93" t="inlineStr">
+      <c r="CI93" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ93" t="inlineStr">
+        <is>
+          <t>Hunters in range shoot straighter</t>
         </is>
       </c>
     </row>
@@ -22196,9 +22371,14 @@
       <c r="BA94" s="57" t="n">
         <v>20</v>
       </c>
-      <c r="CI94" t="inlineStr">
+      <c r="CI94" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ94" t="inlineStr">
+        <is>
+          <t>Wider reach, and hunters in range fire faster</t>
         </is>
       </c>
     </row>
@@ -22619,9 +22799,14 @@
       <c r="BG98" s="57" t="n"/>
       <c r="BH98" s="57" t="n"/>
       <c r="BI98" s="57" t="n"/>
-      <c r="CI98" t="inlineStr">
+      <c r="CI98" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ98" t="inlineStr">
+        <is>
+          <t>Heals towers and hunters even faster</t>
         </is>
       </c>
     </row>
@@ -22729,9 +22914,14 @@
       <c r="BG99" s="57" t="n"/>
       <c r="BH99" s="57" t="n"/>
       <c r="BI99" s="57" t="n"/>
-      <c r="CI99" t="inlineStr">
+      <c r="CI99" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ99" t="inlineStr">
+        <is>
+          <t>The fastest heals; trampled towers revive at full speed</t>
         </is>
       </c>
     </row>
@@ -23146,9 +23336,14 @@
       <c r="BG103" s="57" t="n"/>
       <c r="BH103" s="57" t="n"/>
       <c r="BI103" s="57" t="n"/>
-      <c r="CI103" t="inlineStr">
+      <c r="CI103" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ103" t="inlineStr">
+        <is>
+          <t>Three med kits a round, and each heals more</t>
         </is>
       </c>
     </row>
@@ -23256,9 +23451,14 @@
       </c>
       <c r="BH104" s="57" t="n"/>
       <c r="BI104" s="57" t="n"/>
-      <c r="CI104" t="inlineStr">
+      <c r="CI104" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ104" t="inlineStr">
+        <is>
+          <t>Bigger kits and reach; downed hunters return sooner</t>
         </is>
       </c>
     </row>
@@ -23675,9 +23875,14 @@
         <v>35</v>
       </c>
       <c r="BI108" s="57" t="n"/>
-      <c r="CI108" t="inlineStr">
+      <c r="CI108" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ108" t="inlineStr">
+        <is>
+          <t>Towers in range get much more health</t>
         </is>
       </c>
     </row>
@@ -23787,9 +23992,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="CI109" t="inlineStr">
+      <c r="CI109" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ109" t="inlineStr">
+        <is>
+          <t>More health; once a round, saves a tower from trampling</t>
         </is>
       </c>
     </row>
@@ -24030,9 +24240,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="CI113" t="inlineStr">
+      <c r="CI113" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ113" t="inlineStr">
+        <is>
+          <t>Arcs can jump from one coil's range to another's</t>
         </is>
       </c>
     </row>
@@ -24097,9 +24312,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="CI114" t="inlineStr">
+      <c r="CI114" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ114" t="inlineStr">
+        <is>
+          <t>Strikes every dino near every coil; more coils, more power</t>
         </is>
       </c>
     </row>
@@ -24330,9 +24550,14 @@
       </c>
       <c r="U118" s="57" t="n"/>
       <c r="BP118" s="81" t="n"/>
-      <c r="CI118" t="inlineStr">
+      <c r="CI118" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ118" t="inlineStr">
+        <is>
+          <t>Hurts armoured dinos, and hits harder</t>
         </is>
       </c>
     </row>
@@ -24396,9 +24621,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="CI119" t="inlineStr">
+      <c r="CI119" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ119" t="inlineStr">
+        <is>
+          <t>A huge bolt shrinks the biggest dino 3 sizes</t>
         </is>
       </c>
     </row>
@@ -24627,9 +24857,14 @@
         <v>15</v>
       </c>
       <c r="BR123" s="81" t="n"/>
-      <c r="CI123" t="inlineStr">
+      <c r="CI123" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ123" t="inlineStr">
+        <is>
+          <t>Towers in range hit harder</t>
         </is>
       </c>
     </row>
@@ -24691,9 +24926,14 @@
       <c r="BS124" s="81" t="n">
         <v>50</v>
       </c>
-      <c r="CI124" t="inlineStr">
+      <c r="CI124" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ124" t="inlineStr">
+        <is>
+          <t>Towers in range chain their shots to one more dino</t>
         </is>
       </c>
     </row>
@@ -24923,9 +25163,14 @@
         <v>3</v>
       </c>
       <c r="BU128" s="81" t="n"/>
-      <c r="CI128" t="inlineStr">
+      <c r="CI128" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ128" t="inlineStr">
+        <is>
+          <t>Hurts armoured dinos; dives shrink a dino 3 sizes</t>
         </is>
       </c>
     </row>
@@ -24992,9 +25237,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="CI129" t="inlineStr">
+      <c r="CI129" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ129" t="inlineStr">
+        <is>
+          <t>One giant eagle dives, stuns and shrinks a dino 3 sizes</t>
         </is>
       </c>
     </row>
@@ -25219,9 +25469,14 @@
         </is>
       </c>
       <c r="BT133" s="81" t="n"/>
-      <c r="CI133" t="inlineStr">
+      <c r="CI133" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ133" t="inlineStr">
+        <is>
+          <t>The birds hunt much further out</t>
         </is>
       </c>
     </row>
@@ -25285,9 +25540,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="CI134" t="inlineStr">
+      <c r="CI134" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ134" t="inlineStr">
+        <is>
+          <t>A swarm of small birds pecks every dino in range</t>
         </is>
       </c>
     </row>
@@ -25516,9 +25776,14 @@
         <v>2</v>
       </c>
       <c r="BX138" s="81" t="n"/>
-      <c r="CI138" t="inlineStr">
+      <c r="CI138" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ138" t="inlineStr">
+        <is>
+          <t>Struck dinos get pulled back (not bosses)</t>
         </is>
       </c>
     </row>
@@ -25580,9 +25845,14 @@
       <c r="BY139" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="CI139" t="inlineStr">
+      <c r="CI139" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ139" t="inlineStr">
+        <is>
+          <t>Towers in range shoot faster while a bird dives</t>
         </is>
       </c>
     </row>
@@ -25814,9 +26084,14 @@
         <v>3</v>
       </c>
       <c r="CC143" s="81" t="n"/>
-      <c r="CI143" t="inlineStr">
+      <c r="CI143" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ143" t="inlineStr">
+        <is>
+          <t>Dinos stay slowed for a while after they leave</t>
         </is>
       </c>
     </row>
@@ -25875,9 +26150,14 @@
       <c r="AE144" s="81" t="n"/>
       <c r="AF144" s="81" t="n"/>
       <c r="CC144" s="81" t="n"/>
-      <c r="CI144" t="inlineStr">
+      <c r="CI144" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ144" t="inlineStr">
+        <is>
+          <t>The pool covers three times as much track</t>
         </is>
       </c>
     </row>
@@ -26105,9 +26385,14 @@
       <c r="Y148" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="CI148" t="inlineStr">
+      <c r="CI148" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ148" t="inlineStr">
+        <is>
+          <t>Dinos walk out of the tar still burning</t>
         </is>
       </c>
     </row>
@@ -26170,9 +26455,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="CI149" t="inlineStr">
+      <c r="CI149" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ149" t="inlineStr">
+        <is>
+          <t>A geyser shrinks every dino in the pool 2 sizes</t>
         </is>
       </c>
     </row>
@@ -26408,9 +26698,14 @@
       <c r="CG153" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="CI153" t="inlineStr">
+      <c r="CI153" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ153" t="inlineStr">
+        <is>
+          <t>Dinos leaving the tar leave a slowing trail</t>
         </is>
       </c>
     </row>
@@ -26472,9 +26767,14 @@
       <c r="CH154" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="CI154" t="inlineStr">
+      <c r="CI154" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ154" t="inlineStr">
+        <is>
+          <t>Towers in range hit slowed dinos harder</t>
         </is>
       </c>
     </row>
@@ -26700,9 +27000,14 @@
       <c r="BJ158" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="CI158" t="inlineStr">
+      <c r="CI158" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ158" t="inlineStr">
+        <is>
+          <t>Pierces armour and shrinks a dino 3 sizes</t>
         </is>
       </c>
     </row>
@@ -26765,9 +27070,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="CI159" t="inlineStr">
+      <c r="CI159" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ159" t="inlineStr">
+        <is>
+          <t>The bolt flies on through every dino in its line</t>
         </is>
       </c>
     </row>
@@ -26989,9 +27299,14 @@
       <c r="W163" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="CI163" t="inlineStr">
+      <c r="CI163" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ163" t="inlineStr">
+        <is>
+          <t>Drags the hit dino back along the track (not bosses)</t>
         </is>
       </c>
     </row>
@@ -27054,9 +27369,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="CI164" t="inlineStr">
+      <c r="CI164" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ164" t="inlineStr">
+        <is>
+          <t>Every 15 seconds, pulls a boss back along the track</t>
         </is>
       </c>
     </row>
@@ -27281,9 +27601,14 @@
         </is>
       </c>
       <c r="Q168" s="81" t="n"/>
-      <c r="CI168" t="inlineStr">
+      <c r="CI168" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="CJ168" t="inlineStr">
+        <is>
+          <t>Fires twice as fast</t>
         </is>
       </c>
     </row>
@@ -27347,13 +27672,17 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="CI169" t="inlineStr">
+      <c r="CI169" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="170"/>
+      <c r="CJ169" t="inlineStr">
+        <is>
+          <t>Chained bolt pairs hit every dino between them</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -27959,7 +28288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC77"/>
+  <dimension ref="A1:BC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="90" min="1" max="1"/>
@@ -28011,7 +28340,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -28278,12 +28606,12 @@
           <t>Ability charges</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BB4" s="81" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BC4" s="81" t="inlineStr">
         <is>
           <t>Blurb</t>
         </is>
@@ -28538,9 +28866,14 @@
       <c r="AG8" s="57" t="n"/>
       <c r="AH8" s="57" t="n"/>
       <c r="AI8" s="57" t="n"/>
-      <c r="BB8" t="inlineStr">
+      <c r="BB8" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>Fires faster and reloads quicker</t>
         </is>
       </c>
     </row>
@@ -28611,9 +28944,14 @@
       <c r="AG9" s="57" t="n"/>
       <c r="AH9" s="57" t="n"/>
       <c r="AI9" s="57" t="n"/>
-      <c r="BB9" t="inlineStr">
+      <c r="BB9" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>Both guns go full-auto</t>
         </is>
       </c>
     </row>
@@ -28874,9 +29212,14 @@
       <c r="AG13" s="57" t="n"/>
       <c r="AH13" s="57" t="n"/>
       <c r="AI13" s="57" t="n"/>
-      <c r="BB13" t="inlineStr">
+      <c r="BB13" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>Shots pierce armour</t>
         </is>
       </c>
     </row>
@@ -28945,9 +29288,14 @@
       <c r="AG14" s="57" t="n"/>
       <c r="AH14" s="57" t="n"/>
       <c r="AI14" s="57" t="n"/>
-      <c r="BB14" t="inlineStr">
+      <c r="BB14" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>Triple damage to marked dinos</t>
         </is>
       </c>
     </row>
@@ -29200,9 +29548,14 @@
       <c r="AG18" s="57" t="n"/>
       <c r="AH18" s="57" t="n"/>
       <c r="AI18" s="57" t="n"/>
-      <c r="BB18" t="inlineStr">
+      <c r="BB18" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>Your Tracking Dart is ready again sooner</t>
         </is>
       </c>
     </row>
@@ -29271,9 +29624,14 @@
       <c r="AG19" s="57" t="n"/>
       <c r="AH19" s="57" t="n"/>
       <c r="AI19" s="57" t="n"/>
-      <c r="BB19" t="inlineStr">
+      <c r="BB19" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>Shots bounce 4 times</t>
         </is>
       </c>
     </row>
@@ -29534,9 +29892,14 @@
       <c r="AG23" s="57" t="n"/>
       <c r="AH23" s="57" t="n"/>
       <c r="AI23" s="57" t="n"/>
-      <c r="BB23" t="inlineStr">
+      <c r="BB23" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>Less kick and longer reach</t>
         </is>
       </c>
     </row>
@@ -29609,9 +29972,14 @@
       <c r="AG24" s="57" t="n"/>
       <c r="AH24" s="57" t="n"/>
       <c r="AI24" s="57" t="n"/>
-      <c r="BB24" t="inlineStr">
+      <c r="BB24" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>4-round bursts with a much tighter grouping</t>
         </is>
       </c>
     </row>
@@ -29866,9 +30234,14 @@
       <c r="AG28" s="57" t="n"/>
       <c r="AH28" s="57" t="n"/>
       <c r="AI28" s="57" t="n"/>
-      <c r="BB28" t="inlineStr">
+      <c r="BB28" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>Much less kick while you stand still</t>
         </is>
       </c>
     </row>
@@ -29937,9 +30310,14 @@
       <c r="AG29" s="57" t="n"/>
       <c r="AH29" s="57" t="n"/>
       <c r="AI29" s="57" t="n"/>
-      <c r="BB29" t="inlineStr">
+      <c r="BB29" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>Fire rate climbs while you hold the trigger</t>
         </is>
       </c>
     </row>
@@ -30196,9 +30574,14 @@
       <c r="AG33" s="57" t="n"/>
       <c r="AH33" s="57" t="n"/>
       <c r="AI33" s="57" t="n"/>
-      <c r="BB33" t="inlineStr">
+      <c r="BB33" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>Hits harder and reaches further</t>
         </is>
       </c>
     </row>
@@ -30265,9 +30648,14 @@
       <c r="AG34" s="57" t="n"/>
       <c r="AH34" s="57" t="n"/>
       <c r="AI34" s="57" t="n"/>
-      <c r="BB34" t="inlineStr">
+      <c r="BB34" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>Shots burst with a small splash</t>
         </is>
       </c>
     </row>
@@ -30552,9 +30940,14 @@
       <c r="AG38" s="57" t="n"/>
       <c r="AH38" s="57" t="n"/>
       <c r="AI38" s="57" t="n"/>
-      <c r="BB38" t="inlineStr">
+      <c r="BB38" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>Tighter, longer slugs that go through 3 dinos</t>
         </is>
       </c>
     </row>
@@ -30623,9 +31016,14 @@
       <c r="AG39" s="57" t="n"/>
       <c r="AH39" s="57" t="n"/>
       <c r="AI39" s="57" t="n"/>
-      <c r="BB39" t="inlineStr">
+      <c r="BB39" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>Slugs go through 6 dinos</t>
         </is>
       </c>
     </row>
@@ -30884,9 +31282,14 @@
       <c r="AG43" s="57" t="n"/>
       <c r="AH43" s="57" t="n"/>
       <c r="AI43" s="57" t="n"/>
-      <c r="BB43" t="inlineStr">
+      <c r="BB43" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>Fires faster and reloads quicker</t>
         </is>
       </c>
     </row>
@@ -30959,9 +31362,14 @@
       <c r="AG44" s="57" t="n"/>
       <c r="AH44" s="57" t="n"/>
       <c r="AI44" s="57" t="n"/>
-      <c r="BB44" t="inlineStr">
+      <c r="BB44" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>A full-auto drum</t>
         </is>
       </c>
     </row>
@@ -31214,9 +31622,14 @@
       <c r="AG48" s="57" t="n"/>
       <c r="AH48" s="57" t="n"/>
       <c r="AI48" s="57" t="n"/>
-      <c r="BB48" t="inlineStr">
+      <c r="BB48" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>Blasts knock dinos back</t>
         </is>
       </c>
     </row>
@@ -31283,9 +31696,14 @@
       <c r="AG49" s="57" t="n"/>
       <c r="AH49" s="57" t="n"/>
       <c r="AI49" s="57" t="n"/>
-      <c r="BB49" t="inlineStr">
+      <c r="BB49" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>Shells explode on impact</t>
         </is>
       </c>
     </row>
@@ -31547,9 +31965,14 @@
         <v>1.5</v>
       </c>
       <c r="AL53" s="81" t="n"/>
-      <c r="BB53" t="inlineStr">
+      <c r="BB53" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>Your Triage Kit heals a wider area</t>
         </is>
       </c>
     </row>
@@ -31625,9 +32048,14 @@
       <c r="AN54" s="81" t="n">
         <v>8</v>
       </c>
-      <c r="BB54" t="inlineStr">
+      <c r="BB54" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>Everyone you heal takes less damage for a while</t>
         </is>
       </c>
     </row>
@@ -31890,9 +32318,14 @@
       <c r="AG58" s="57" t="n"/>
       <c r="AH58" s="57" t="n"/>
       <c r="AI58" s="57" t="n"/>
-      <c r="BB58" t="inlineStr">
+      <c r="BB58" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>Half the kick</t>
         </is>
       </c>
     </row>
@@ -31967,9 +32400,14 @@
       <c r="AG59" s="57" t="n"/>
       <c r="AH59" s="57" t="n"/>
       <c r="AI59" s="57" t="n"/>
-      <c r="BB59" t="inlineStr">
+      <c r="BB59" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>Goes full auto</t>
         </is>
       </c>
     </row>
@@ -32230,9 +32668,14 @@
       <c r="AQ63" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="BB63" t="inlineStr">
+      <c r="BB63" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>Jaw Lock keeps a dino's jaws shut for longer</t>
         </is>
       </c>
     </row>
@@ -32299,9 +32742,14 @@
       <c r="AR64" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="BB64" t="inlineStr">
+      <c r="BB64" s="81" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>Jaw Lock spreads to nearby dinos</t>
         </is>
       </c>
     </row>
@@ -33130,7 +33578,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -13262,7 +13262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ169"/>
+  <dimension ref="A1:CK169"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -13842,6 +13842,11 @@
           <t>Blurb</t>
         </is>
       </c>
+      <c r="CK4" s="109" t="inlineStr">
+        <is>
+          <t>PvP effect</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -14193,7 +14198,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CJ8" s="81" t="inlineStr">
         <is>
           <t>Sees further, and shoots faster and harder</t>
         </is>
@@ -14295,7 +14300,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CJ9" s="81" t="inlineStr">
         <is>
           <t>Towers in range hit harder and can hurt armour</t>
         </is>
@@ -14651,7 +14656,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ13" t="inlineStr">
+      <c r="CJ13" s="81" t="inlineStr">
         <is>
           <t>Fires much faster and hits harder</t>
         </is>
@@ -14749,7 +14754,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ14" t="inlineStr">
+      <c r="CJ14" s="81" t="inlineStr">
         <is>
           <t>The fastest fire in the game</t>
         </is>
@@ -15120,7 +15125,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ18" t="inlineStr">
+      <c r="CJ18" s="81" t="inlineStr">
         <is>
           <t>Each bullet goes through 3 dinos</t>
         </is>
@@ -15221,7 +15226,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ19" t="inlineStr">
+      <c r="CJ19" s="81" t="inlineStr">
         <is>
           <t>Hits armoured dinos and bosses 4 times as hard</t>
         </is>
@@ -15594,7 +15599,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ23" t="inlineStr">
+      <c r="CJ23" s="81" t="inlineStr">
         <is>
           <t>Shots go through more dinos, shrinking each 2 sizes</t>
         </is>
@@ -15695,7 +15700,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ24" t="inlineStr">
+      <c r="CJ24" s="81" t="inlineStr">
         <is>
           <t>Each shot hits 10 dinos in a line, double damage</t>
         </is>
@@ -16053,7 +16058,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ28" t="inlineStr">
+      <c r="CJ28" s="81" t="inlineStr">
         <is>
           <t>Fires faster, and its mark hits harder</t>
         </is>
@@ -16153,7 +16158,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ29" t="inlineStr">
+      <c r="CJ29" s="81" t="inlineStr">
         <is>
           <t>A bigger mark, and towers in range shoot faster</t>
         </is>
@@ -16526,7 +16531,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ33" t="inlineStr">
+      <c r="CJ33" s="81" t="inlineStr">
         <is>
           <t>Huge shots that stun and shrink a dino 3 sizes</t>
         </is>
@@ -16633,7 +16638,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ34" t="inlineStr">
+      <c r="CJ34" s="81" t="inlineStr">
         <is>
           <t>10 times damage to bosses, and stuns them</t>
         </is>
@@ -17003,7 +17008,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ38" t="inlineStr">
+      <c r="CJ38" s="81" t="inlineStr">
         <is>
           <t>Bigger blasts that leave dinos burning</t>
         </is>
@@ -17105,7 +17110,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ39" t="inlineStr">
+      <c r="CJ39" s="81" t="inlineStr">
         <is>
           <t>Leaves a long burning stretch of track</t>
         </is>
@@ -17473,7 +17478,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ43" t="inlineStr">
+      <c r="CJ43" s="81" t="inlineStr">
         <is>
           <t>More bomblets and harder blasts</t>
         </is>
@@ -17571,7 +17576,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ44" t="inlineStr">
+      <c r="CJ44" s="81" t="inlineStr">
         <is>
           <t>Even more bomblets rain down</t>
         </is>
@@ -17949,7 +17954,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ48" t="inlineStr">
+      <c r="CJ48" s="81" t="inlineStr">
         <is>
           <t>Hits much harder and knocks dinos further back</t>
         </is>
@@ -18049,7 +18054,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ49" t="inlineStr">
+      <c r="CJ49" s="81" t="inlineStr">
         <is>
           <t>Stuns every dino it hits for a second</t>
         </is>
@@ -18413,7 +18418,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ53" t="inlineStr">
+      <c r="CJ53" s="81" t="inlineStr">
         <is>
           <t>A much stronger slow over a wider area</t>
         </is>
@@ -18517,7 +18522,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ54" t="inlineStr">
+      <c r="CJ54" s="81" t="inlineStr">
         <is>
           <t>Its slow works on bosses too</t>
         </is>
@@ -18889,7 +18894,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ58" t="inlineStr">
+      <c r="CJ58" s="81" t="inlineStr">
         <is>
           <t>Knockouts come sooner and hurt more</t>
         </is>
@@ -18993,7 +18998,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ59" t="inlineStr">
+      <c r="CJ59" s="81" t="inlineStr">
         <is>
           <t>A long knockout that even holds bosses</t>
         </is>
@@ -19365,7 +19370,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ63" t="inlineStr">
+      <c r="CJ63" s="81" t="inlineStr">
         <is>
           <t>Sedated dinos take even more damage</t>
         </is>
@@ -19465,7 +19470,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ64" t="inlineStr">
+      <c r="CJ64" s="81" t="inlineStr">
         <is>
           <t>Dinos take much more damage; towers in range hit harder</t>
         </is>
@@ -19827,7 +19832,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ68" t="inlineStr">
+      <c r="CJ68" s="81" t="inlineStr">
         <is>
           <t>Pays a lot more cash every round</t>
         </is>
@@ -19929,7 +19934,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ69" t="inlineStr">
+      <c r="CJ69" s="81" t="inlineStr">
         <is>
           <t>Earns interest on your banked cash</t>
         </is>
@@ -20299,7 +20304,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ73" t="inlineStr">
+      <c r="CJ73" s="81" t="inlineStr">
         <is>
           <t>More chests land each round, worth more</t>
         </is>
@@ -20399,7 +20404,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ74" t="inlineStr">
+      <c r="CJ74" s="81" t="inlineStr">
         <is>
           <t>The richest chests, and more of them</t>
         </is>
@@ -20763,7 +20768,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ78" t="inlineStr">
+      <c r="CJ78" s="81" t="inlineStr">
         <is>
           <t>Towers in range shoot faster</t>
         </is>
@@ -20863,7 +20868,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ79" t="inlineStr">
+      <c r="CJ79" s="81" t="inlineStr">
         <is>
           <t>Towers in range cost less and sell for full price</t>
         </is>
@@ -21257,7 +21262,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ83" t="inlineStr">
+      <c r="CJ83" s="81" t="inlineStr">
         <is>
           <t>Tougher armour, and biters take more damage back</t>
         </is>
@@ -21364,7 +21369,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ84" t="inlineStr">
+      <c r="CJ84" s="81" t="inlineStr">
         <is>
           <t>The best armour; biting dinos get stunned (not bosses)</t>
         </is>
@@ -21764,7 +21769,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ88" t="inlineStr">
+      <c r="CJ88" s="81" t="inlineStr">
         <is>
           <t>Towers in range hit harder and shoot faster</t>
         </is>
@@ -21871,7 +21876,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ89" t="inlineStr">
+      <c r="CJ89" s="81" t="inlineStr">
         <is>
           <t>Towers in range hit much harder and faster</t>
         </is>
@@ -22265,7 +22270,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ93" t="inlineStr">
+      <c r="CJ93" s="81" t="inlineStr">
         <is>
           <t>Hunters in range shoot straighter</t>
         </is>
@@ -22376,7 +22381,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ94" t="inlineStr">
+      <c r="CJ94" s="81" t="inlineStr">
         <is>
           <t>Wider reach, and hunters in range fire faster</t>
         </is>
@@ -22804,7 +22809,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ98" t="inlineStr">
+      <c r="CJ98" s="81" t="inlineStr">
         <is>
           <t>Heals towers and hunters even faster</t>
         </is>
@@ -22919,7 +22924,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ99" t="inlineStr">
+      <c r="CJ99" s="81" t="inlineStr">
         <is>
           <t>The fastest heals; trampled towers revive at full speed</t>
         </is>
@@ -23341,7 +23346,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ103" t="inlineStr">
+      <c r="CJ103" s="81" t="inlineStr">
         <is>
           <t>Three med kits a round, and each heals more</t>
         </is>
@@ -23456,7 +23461,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ104" t="inlineStr">
+      <c r="CJ104" s="81" t="inlineStr">
         <is>
           <t>Bigger kits and reach; downed hunters return sooner</t>
         </is>
@@ -23880,7 +23885,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ108" t="inlineStr">
+      <c r="CJ108" s="81" t="inlineStr">
         <is>
           <t>Towers in range get much more health</t>
         </is>
@@ -23997,7 +24002,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ109" t="inlineStr">
+      <c r="CJ109" s="81" t="inlineStr">
         <is>
           <t>More health; once a round, saves a tower from trampling</t>
         </is>
@@ -24245,7 +24250,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ113" t="inlineStr">
+      <c r="CJ113" s="81" t="inlineStr">
         <is>
           <t>Arcs can jump from one coil's range to another's</t>
         </is>
@@ -24317,7 +24322,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ114" t="inlineStr">
+      <c r="CJ114" s="81" t="inlineStr">
         <is>
           <t>Strikes every dino near every coil; more coils, more power</t>
         </is>
@@ -24555,7 +24560,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ118" t="inlineStr">
+      <c r="CJ118" s="81" t="inlineStr">
         <is>
           <t>Hurts armoured dinos, and hits harder</t>
         </is>
@@ -24626,7 +24631,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ119" t="inlineStr">
+      <c r="CJ119" s="81" t="inlineStr">
         <is>
           <t>A huge bolt shrinks the biggest dino 3 sizes</t>
         </is>
@@ -24862,7 +24867,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ123" t="inlineStr">
+      <c r="CJ123" s="81" t="inlineStr">
         <is>
           <t>Towers in range hit harder</t>
         </is>
@@ -24931,7 +24936,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ124" t="inlineStr">
+      <c r="CJ124" s="81" t="inlineStr">
         <is>
           <t>Towers in range chain their shots to one more dino</t>
         </is>
@@ -25168,7 +25173,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ128" t="inlineStr">
+      <c r="CJ128" s="81" t="inlineStr">
         <is>
           <t>Hurts armoured dinos; dives shrink a dino 3 sizes</t>
         </is>
@@ -25242,7 +25247,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ129" t="inlineStr">
+      <c r="CJ129" s="81" t="inlineStr">
         <is>
           <t>One giant eagle dives, stuns and shrinks a dino 3 sizes</t>
         </is>
@@ -25474,7 +25479,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ133" t="inlineStr">
+      <c r="CJ133" s="81" t="inlineStr">
         <is>
           <t>The birds hunt much further out</t>
         </is>
@@ -25545,7 +25550,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ134" t="inlineStr">
+      <c r="CJ134" s="81" t="inlineStr">
         <is>
           <t>A swarm of small birds pecks every dino in range</t>
         </is>
@@ -25781,7 +25786,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ138" t="inlineStr">
+      <c r="CJ138" s="81" t="inlineStr">
         <is>
           <t>Struck dinos get pulled back (not bosses)</t>
         </is>
@@ -25850,7 +25855,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ139" t="inlineStr">
+      <c r="CJ139" s="81" t="inlineStr">
         <is>
           <t>Towers in range shoot faster while a bird dives</t>
         </is>
@@ -26089,7 +26094,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ143" t="inlineStr">
+      <c r="CJ143" s="81" t="inlineStr">
         <is>
           <t>Dinos stay slowed for a while after they leave</t>
         </is>
@@ -26155,7 +26160,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ144" t="inlineStr">
+      <c r="CJ144" s="81" t="inlineStr">
         <is>
           <t>The pool covers three times as much track</t>
         </is>
@@ -26390,7 +26395,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ148" t="inlineStr">
+      <c r="CJ148" s="81" t="inlineStr">
         <is>
           <t>Dinos walk out of the tar still burning</t>
         </is>
@@ -26460,7 +26465,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ149" t="inlineStr">
+      <c r="CJ149" s="81" t="inlineStr">
         <is>
           <t>A geyser shrinks every dino in the pool 2 sizes</t>
         </is>
@@ -26703,7 +26708,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ153" t="inlineStr">
+      <c r="CJ153" s="81" t="inlineStr">
         <is>
           <t>Dinos leaving the tar leave a slowing trail</t>
         </is>
@@ -26772,7 +26777,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ154" t="inlineStr">
+      <c r="CJ154" s="81" t="inlineStr">
         <is>
           <t>Towers in range hit slowed dinos harder</t>
         </is>
@@ -27005,7 +27010,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ158" t="inlineStr">
+      <c r="CJ158" s="81" t="inlineStr">
         <is>
           <t>Pierces armour and shrinks a dino 3 sizes</t>
         </is>
@@ -27075,7 +27080,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ159" t="inlineStr">
+      <c r="CJ159" s="81" t="inlineStr">
         <is>
           <t>The bolt flies on through every dino in its line</t>
         </is>
@@ -27304,7 +27309,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ163" t="inlineStr">
+      <c r="CJ163" s="81" t="inlineStr">
         <is>
           <t>Drags the hit dino back along the track (not bosses)</t>
         </is>
@@ -27374,7 +27379,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ164" t="inlineStr">
+      <c r="CJ164" s="81" t="inlineStr">
         <is>
           <t>Every 15 seconds, pulls a boss back along the track</t>
         </is>
@@ -27606,7 +27611,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ168" t="inlineStr">
+      <c r="CJ168" s="81" t="inlineStr">
         <is>
           <t>Fires twice as fast</t>
         </is>
@@ -27677,7 +27682,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="CJ169" t="inlineStr">
+      <c r="CJ169" s="81" t="inlineStr">
         <is>
           <t>Chained bolt pairs hit every dino between them</t>
         </is>
@@ -28871,7 +28876,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BC8" s="81" t="inlineStr">
         <is>
           <t>Fires faster and reloads quicker</t>
         </is>
@@ -28949,7 +28954,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BC9" s="81" t="inlineStr">
         <is>
           <t>Both guns go full-auto</t>
         </is>
@@ -29217,7 +29222,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC13" t="inlineStr">
+      <c r="BC13" s="81" t="inlineStr">
         <is>
           <t>Shots pierce armour</t>
         </is>
@@ -29293,7 +29298,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC14" t="inlineStr">
+      <c r="BC14" s="81" t="inlineStr">
         <is>
           <t>Triple damage to marked dinos</t>
         </is>
@@ -29553,7 +29558,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC18" t="inlineStr">
+      <c r="BC18" s="81" t="inlineStr">
         <is>
           <t>Your Tracking Dart is ready again sooner</t>
         </is>
@@ -29629,7 +29634,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC19" t="inlineStr">
+      <c r="BC19" s="81" t="inlineStr">
         <is>
           <t>Shots bounce 4 times</t>
         </is>
@@ -29897,7 +29902,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC23" t="inlineStr">
+      <c r="BC23" s="81" t="inlineStr">
         <is>
           <t>Less kick and longer reach</t>
         </is>
@@ -29977,7 +29982,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC24" t="inlineStr">
+      <c r="BC24" s="81" t="inlineStr">
         <is>
           <t>4-round bursts with a much tighter grouping</t>
         </is>
@@ -30239,7 +30244,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC28" t="inlineStr">
+      <c r="BC28" s="81" t="inlineStr">
         <is>
           <t>Much less kick while you stand still</t>
         </is>
@@ -30315,7 +30320,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC29" t="inlineStr">
+      <c r="BC29" s="81" t="inlineStr">
         <is>
           <t>Fire rate climbs while you hold the trigger</t>
         </is>
@@ -30579,7 +30584,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC33" t="inlineStr">
+      <c r="BC33" s="81" t="inlineStr">
         <is>
           <t>Hits harder and reaches further</t>
         </is>
@@ -30653,7 +30658,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC34" t="inlineStr">
+      <c r="BC34" s="81" t="inlineStr">
         <is>
           <t>Shots burst with a small splash</t>
         </is>
@@ -30945,7 +30950,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC38" t="inlineStr">
+      <c r="BC38" s="81" t="inlineStr">
         <is>
           <t>Tighter, longer slugs that go through 3 dinos</t>
         </is>
@@ -31021,7 +31026,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC39" t="inlineStr">
+      <c r="BC39" s="81" t="inlineStr">
         <is>
           <t>Slugs go through 6 dinos</t>
         </is>
@@ -31287,7 +31292,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC43" t="inlineStr">
+      <c r="BC43" s="81" t="inlineStr">
         <is>
           <t>Fires faster and reloads quicker</t>
         </is>
@@ -31367,7 +31372,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC44" t="inlineStr">
+      <c r="BC44" s="81" t="inlineStr">
         <is>
           <t>A full-auto drum</t>
         </is>
@@ -31627,7 +31632,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC48" t="inlineStr">
+      <c r="BC48" s="81" t="inlineStr">
         <is>
           <t>Blasts knock dinos back</t>
         </is>
@@ -31701,7 +31706,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC49" t="inlineStr">
+      <c r="BC49" s="81" t="inlineStr">
         <is>
           <t>Shells explode on impact</t>
         </is>
@@ -31970,7 +31975,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC53" t="inlineStr">
+      <c r="BC53" s="81" t="inlineStr">
         <is>
           <t>Your Triage Kit heals a wider area</t>
         </is>
@@ -32053,7 +32058,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC54" t="inlineStr">
+      <c r="BC54" s="81" t="inlineStr">
         <is>
           <t>Everyone you heal takes less damage for a while</t>
         </is>
@@ -32323,7 +32328,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC58" t="inlineStr">
+      <c r="BC58" s="81" t="inlineStr">
         <is>
           <t>Half the kick</t>
         </is>
@@ -32405,7 +32410,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC59" t="inlineStr">
+      <c r="BC59" s="81" t="inlineStr">
         <is>
           <t>Goes full auto</t>
         </is>
@@ -32673,7 +32678,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC63" t="inlineStr">
+      <c r="BC63" s="81" t="inlineStr">
         <is>
           <t>Jaw Lock keeps a dino's jaws shut for longer</t>
         </is>
@@ -32747,7 +32752,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="BC64" t="inlineStr">
+      <c r="BC64" s="81" t="inlineStr">
         <is>
           <t>Jaw Lock spreads to nearby dinos</t>
         </is>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9499,7 +9499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E185"/>
+  <dimension ref="A1:E186"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -12240,6 +12240,21 @@
       <c r="C185" s="109" t="inlineStr">
         <is>
           <t>Fence per second, per side: battles only; a leak adds its cost to the side's pending loss, which comes off the Fence at most this fast and is applied in full before any match-end ranking (DECISIONS #267); co-op unchanged</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="109" t="inlineStr">
+        <is>
+          <t>Strip (s)</t>
+        </is>
+      </c>
+      <c r="B186" s="109" t="n">
+        <v>3</v>
+      </c>
+      <c r="C186" s="109" t="inlineStr">
+        <is>
+          <t>s a dino hit by a Strips armour shot stays unarmoured (Blind, Perch, Mortar options; PLAN 9c, #290)</t>
         </is>
       </c>
     </row>
@@ -13262,7 +13277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK169"/>
+  <dimension ref="A1:CK205"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -27685,6 +27700,3373 @@
       <c r="CJ169" s="81" t="inlineStr">
         <is>
           <t>Chained bolt pairs hit every dino between them</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="43" t="inlineStr">
+        <is>
+          <t>Hunting Blind</t>
+        </is>
+      </c>
+      <c r="B170" s="43" t="inlineStr">
+        <is>
+          <t>Lookout</t>
+        </is>
+      </c>
+      <c r="C170" s="43" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="D170" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E170" s="56">
+        <f>E8</f>
+        <v/>
+      </c>
+      <c r="F170" s="56">
+        <f>F8</f>
+        <v/>
+      </c>
+      <c r="G170" s="57" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H170" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J170" s="92" t="n"/>
+      <c r="K170" s="92" t="n"/>
+      <c r="L170" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" s="43" t="inlineStr">
+        <is>
+          <t>Signal Mirror</t>
+        </is>
+      </c>
+      <c r="N170" s="57" t="n"/>
+      <c r="O170" s="57" t="n"/>
+      <c r="P170" s="57" t="n"/>
+      <c r="Q170" s="57" t="n"/>
+      <c r="R170" s="57" t="n"/>
+      <c r="S170" s="57" t="n"/>
+      <c r="T170" s="57" t="n"/>
+      <c r="U170" s="57" t="n"/>
+      <c r="V170" s="57" t="n"/>
+      <c r="W170" s="57" t="n"/>
+      <c r="X170" s="57" t="n"/>
+      <c r="Y170" s="57" t="n"/>
+      <c r="Z170" s="57" t="n"/>
+      <c r="AA170" s="57" t="n"/>
+      <c r="AB170" s="57" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC170" s="57" t="n"/>
+      <c r="AD170" s="57" t="n"/>
+      <c r="AE170" s="57" t="n"/>
+      <c r="AF170" s="57" t="n"/>
+      <c r="AG170" s="57" t="n"/>
+      <c r="AH170" s="57" t="n"/>
+      <c r="AI170" s="57" t="n"/>
+      <c r="AJ170" s="57" t="n"/>
+      <c r="AK170" s="57" t="n"/>
+      <c r="AL170" s="57" t="n"/>
+      <c r="AM170" s="57" t="n"/>
+      <c r="AN170" s="57" t="n"/>
+      <c r="AO170" s="57" t="n"/>
+      <c r="AP170" s="57" t="n"/>
+      <c r="AQ170" s="57" t="n"/>
+      <c r="AR170" s="57" t="n"/>
+      <c r="AS170" s="57" t="n"/>
+      <c r="AT170" s="57" t="n"/>
+      <c r="CI170" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ170" s="81" t="inlineStr">
+        <is>
+          <t>Towers in range fire 18% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="43" t="inlineStr">
+        <is>
+          <t>Hunting Blind</t>
+        </is>
+      </c>
+      <c r="B171" s="43" t="inlineStr">
+        <is>
+          <t>Lookout</t>
+        </is>
+      </c>
+      <c r="C171" s="43" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="D171" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E171" s="56">
+        <f>E8</f>
+        <v/>
+      </c>
+      <c r="F171" s="56">
+        <f>F8</f>
+        <v/>
+      </c>
+      <c r="G171" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H171" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J171" s="92" t="n"/>
+      <c r="K171" s="92" t="n"/>
+      <c r="L171" s="57" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M171" s="43" t="inlineStr">
+        <is>
+          <t>Spotter's Call</t>
+        </is>
+      </c>
+      <c r="N171" s="57" t="n"/>
+      <c r="O171" s="57" t="n"/>
+      <c r="P171" s="57" t="n"/>
+      <c r="Q171" s="57" t="n"/>
+      <c r="R171" s="57" t="n"/>
+      <c r="S171" s="57" t="n"/>
+      <c r="T171" s="57" t="n">
+        <v>15</v>
+      </c>
+      <c r="U171" s="57" t="n"/>
+      <c r="V171" s="57" t="n"/>
+      <c r="W171" s="57" t="n"/>
+      <c r="X171" s="57" t="n"/>
+      <c r="Y171" s="57" t="n"/>
+      <c r="Z171" s="57" t="n"/>
+      <c r="AA171" s="57" t="n"/>
+      <c r="AB171" s="57" t="n"/>
+      <c r="AC171" s="57" t="n"/>
+      <c r="AD171" s="57" t="n"/>
+      <c r="AE171" s="57" t="n"/>
+      <c r="AF171" s="57" t="n"/>
+      <c r="AG171" s="57" t="n"/>
+      <c r="AH171" s="57" t="n"/>
+      <c r="AI171" s="57" t="n"/>
+      <c r="AJ171" s="57" t="n"/>
+      <c r="AK171" s="57" t="n"/>
+      <c r="AL171" s="57" t="n"/>
+      <c r="AM171" s="57" t="n"/>
+      <c r="AN171" s="57" t="n"/>
+      <c r="AO171" s="57" t="n"/>
+      <c r="AP171" s="57" t="n"/>
+      <c r="AQ171" s="57" t="n"/>
+      <c r="AR171" s="57" t="n"/>
+      <c r="AS171" s="57" t="n"/>
+      <c r="AT171" s="57" t="n"/>
+      <c r="CI171" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ171" s="81" t="inlineStr">
+        <is>
+          <t>Its target takes +15% from every tower</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="43" t="inlineStr">
+        <is>
+          <t>Hunting Blind</t>
+        </is>
+      </c>
+      <c r="B172" s="43" t="inlineStr">
+        <is>
+          <t>Lookout</t>
+        </is>
+      </c>
+      <c r="C172" s="43" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="D172" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E172" s="56">
+        <f>E9</f>
+        <v/>
+      </c>
+      <c r="F172" s="56">
+        <f>F9</f>
+        <v/>
+      </c>
+      <c r="G172" s="57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H172" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I172" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J172" s="92" t="n"/>
+      <c r="K172" s="92" t="n"/>
+      <c r="L172" s="57" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M172" s="43" t="inlineStr">
+        <is>
+          <t>Beacon Fire</t>
+        </is>
+      </c>
+      <c r="N172" s="57" t="n"/>
+      <c r="O172" s="57" t="n"/>
+      <c r="P172" s="57" t="n"/>
+      <c r="Q172" s="57" t="n"/>
+      <c r="R172" s="57" t="n"/>
+      <c r="S172" s="57" t="n"/>
+      <c r="T172" s="57" t="n"/>
+      <c r="U172" s="57" t="n"/>
+      <c r="V172" s="57" t="n"/>
+      <c r="W172" s="57" t="n"/>
+      <c r="X172" s="57" t="n"/>
+      <c r="Y172" s="57" t="n"/>
+      <c r="Z172" s="57" t="n"/>
+      <c r="AA172" s="57" t="n"/>
+      <c r="AB172" s="57" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC172" s="57" t="n"/>
+      <c r="AD172" s="46" t="n"/>
+      <c r="AE172" s="57" t="n"/>
+      <c r="AF172" s="57" t="n"/>
+      <c r="AG172" s="57" t="n"/>
+      <c r="AH172" s="57" t="n"/>
+      <c r="AI172" s="57" t="n"/>
+      <c r="AJ172" s="57" t="n"/>
+      <c r="AK172" s="57" t="n"/>
+      <c r="AL172" s="57" t="n"/>
+      <c r="AM172" s="57" t="n"/>
+      <c r="AN172" s="57" t="n"/>
+      <c r="AO172" s="57" t="n"/>
+      <c r="AP172" s="57" t="n"/>
+      <c r="AQ172" s="57" t="n"/>
+      <c r="AR172" s="57" t="n"/>
+      <c r="AS172" s="57" t="n"/>
+      <c r="AT172" s="57" t="n"/>
+      <c r="CI172" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ172" s="81" t="inlineStr">
+        <is>
+          <t>Towers in range fire 35% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="43" t="inlineStr">
+        <is>
+          <t>Hunting Blind</t>
+        </is>
+      </c>
+      <c r="B173" s="43" t="inlineStr">
+        <is>
+          <t>Lookout</t>
+        </is>
+      </c>
+      <c r="C173" s="43" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="D173" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E173" s="56">
+        <f>E9</f>
+        <v/>
+      </c>
+      <c r="F173" s="56">
+        <f>F9</f>
+        <v/>
+      </c>
+      <c r="G173" s="57" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H173" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J173" s="92" t="n"/>
+      <c r="K173" s="92" t="n"/>
+      <c r="L173" s="57" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M173" s="43" t="inlineStr">
+        <is>
+          <t>Trophy Spotter</t>
+        </is>
+      </c>
+      <c r="N173" s="57" t="n"/>
+      <c r="O173" s="57" t="n"/>
+      <c r="P173" s="57" t="n"/>
+      <c r="Q173" s="57" t="n"/>
+      <c r="R173" s="57" t="n"/>
+      <c r="S173" s="57" t="n"/>
+      <c r="T173" s="57" t="n"/>
+      <c r="U173" s="57" t="n"/>
+      <c r="V173" s="57" t="n"/>
+      <c r="W173" s="57" t="n"/>
+      <c r="X173" s="57" t="n"/>
+      <c r="Y173" s="57" t="n"/>
+      <c r="Z173" s="57" t="n"/>
+      <c r="AA173" s="57" t="n"/>
+      <c r="AB173" s="57" t="n"/>
+      <c r="AC173" s="57" t="n"/>
+      <c r="AD173" s="46" t="n"/>
+      <c r="AE173" s="57" t="n"/>
+      <c r="AF173" s="57" t="n"/>
+      <c r="AG173" s="57" t="n"/>
+      <c r="AH173" s="57" t="n"/>
+      <c r="AI173" s="57" t="n"/>
+      <c r="AJ173" s="57" t="n"/>
+      <c r="AK173" s="57" t="n"/>
+      <c r="AL173" s="57" t="n"/>
+      <c r="AM173" s="57" t="n"/>
+      <c r="AN173" s="57" t="n"/>
+      <c r="AO173" s="57" t="n"/>
+      <c r="AP173" s="57" t="n"/>
+      <c r="AQ173" s="57" t="n"/>
+      <c r="AR173" s="57" t="n"/>
+      <c r="AS173" s="57" t="n"/>
+      <c r="AT173" s="57" t="n"/>
+      <c r="BX173" t="n">
+        <v>40</v>
+      </c>
+      <c r="CI173" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ173" s="81" t="inlineStr">
+        <is>
+          <t>Bosses in range take +40% from everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="43" t="inlineStr">
+        <is>
+          <t>Hunting Blind</t>
+        </is>
+      </c>
+      <c r="B174" s="43" t="inlineStr">
+        <is>
+          <t>Trigger Happy</t>
+        </is>
+      </c>
+      <c r="C174" s="43" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="D174" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E174" s="56">
+        <f>E13</f>
+        <v/>
+      </c>
+      <c r="F174" s="56">
+        <f>F13</f>
+        <v/>
+      </c>
+      <c r="G174" s="57" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H174" s="57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I174" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J174" s="92" t="n"/>
+      <c r="K174" s="92" t="n"/>
+      <c r="L174" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" s="43" t="inlineStr">
+        <is>
+          <t>Belt Feed</t>
+        </is>
+      </c>
+      <c r="N174" s="57" t="n"/>
+      <c r="O174" s="57" t="n"/>
+      <c r="P174" s="57" t="n"/>
+      <c r="Q174" s="57" t="n"/>
+      <c r="R174" s="57" t="n"/>
+      <c r="S174" s="57" t="n"/>
+      <c r="T174" s="57" t="n"/>
+      <c r="U174" s="57" t="n"/>
+      <c r="V174" s="57" t="n"/>
+      <c r="W174" s="57" t="n"/>
+      <c r="X174" s="57" t="n"/>
+      <c r="Y174" s="57" t="n"/>
+      <c r="Z174" s="57" t="n"/>
+      <c r="AA174" s="57" t="n"/>
+      <c r="AB174" s="57" t="n"/>
+      <c r="AC174" s="57" t="n"/>
+      <c r="AD174" s="57" t="n"/>
+      <c r="AE174" s="57" t="n"/>
+      <c r="AF174" s="57" t="n"/>
+      <c r="AG174" s="57" t="n"/>
+      <c r="AH174" s="57" t="n"/>
+      <c r="AI174" s="57" t="n"/>
+      <c r="AJ174" s="57" t="n"/>
+      <c r="AK174" s="57" t="n"/>
+      <c r="AL174" s="57" t="n"/>
+      <c r="AM174" s="57" t="n"/>
+      <c r="AN174" s="57" t="n"/>
+      <c r="AO174" s="57" t="n"/>
+      <c r="AP174" s="57" t="n"/>
+      <c r="AQ174" s="57" t="n"/>
+      <c r="AR174" s="57" t="n"/>
+      <c r="AS174" s="57" t="n"/>
+      <c r="AT174" s="57" t="n"/>
+      <c r="CI174" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ174" s="81" t="inlineStr">
+        <is>
+          <t>Never stops to reload: fires 45% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="43" t="inlineStr">
+        <is>
+          <t>Hunting Blind</t>
+        </is>
+      </c>
+      <c r="B175" s="43" t="inlineStr">
+        <is>
+          <t>Trigger Happy</t>
+        </is>
+      </c>
+      <c r="C175" s="43" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="D175" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E175" s="56">
+        <f>E13</f>
+        <v/>
+      </c>
+      <c r="F175" s="56">
+        <f>F13</f>
+        <v/>
+      </c>
+      <c r="G175" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H175" s="57" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I175" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" s="92" t="n"/>
+      <c r="K175" s="92" t="n"/>
+      <c r="L175" s="57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M175" s="43" t="inlineStr">
+        <is>
+          <t>Long Burst</t>
+        </is>
+      </c>
+      <c r="N175" s="57" t="n"/>
+      <c r="O175" s="57" t="n"/>
+      <c r="P175" s="57" t="n"/>
+      <c r="Q175" s="57" t="n"/>
+      <c r="R175" s="57" t="n"/>
+      <c r="S175" s="57" t="n"/>
+      <c r="T175" s="57" t="n"/>
+      <c r="U175" s="57" t="n"/>
+      <c r="V175" s="57" t="n"/>
+      <c r="W175" s="57" t="n"/>
+      <c r="X175" s="57" t="n"/>
+      <c r="Y175" s="57" t="n"/>
+      <c r="Z175" s="57" t="n"/>
+      <c r="AA175" s="57" t="n"/>
+      <c r="AB175" s="57" t="n"/>
+      <c r="AC175" s="57" t="n"/>
+      <c r="AD175" s="57" t="n"/>
+      <c r="AE175" s="57" t="n"/>
+      <c r="AF175" s="57" t="n"/>
+      <c r="AG175" s="57" t="n"/>
+      <c r="AH175" s="57" t="n"/>
+      <c r="AI175" s="57" t="n"/>
+      <c r="AJ175" s="57" t="n"/>
+      <c r="AK175" s="57" t="n"/>
+      <c r="AL175" s="57" t="n"/>
+      <c r="AM175" s="57" t="n"/>
+      <c r="AN175" s="57" t="n"/>
+      <c r="AO175" s="57" t="n"/>
+      <c r="AP175" s="57" t="n"/>
+      <c r="AQ175" s="57" t="n"/>
+      <c r="AR175" s="57" t="n"/>
+      <c r="AS175" s="57" t="n"/>
+      <c r="AT175" s="57" t="n"/>
+      <c r="CI175" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ175" s="81" t="inlineStr">
+        <is>
+          <t>Fires faster from further away</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="43" t="inlineStr">
+        <is>
+          <t>Hunting Blind</t>
+        </is>
+      </c>
+      <c r="B176" s="43" t="inlineStr">
+        <is>
+          <t>Trigger Happy</t>
+        </is>
+      </c>
+      <c r="C176" s="43" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="D176" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E176" s="56">
+        <f>E14</f>
+        <v/>
+      </c>
+      <c r="F176" s="56">
+        <f>F14</f>
+        <v/>
+      </c>
+      <c r="G176" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H176" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I176" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J176" s="92" t="n"/>
+      <c r="K176" s="92" t="n"/>
+      <c r="L176" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" s="43" t="inlineStr">
+        <is>
+          <t>Bullet Storm</t>
+        </is>
+      </c>
+      <c r="N176" s="57" t="n"/>
+      <c r="O176" s="57" t="n"/>
+      <c r="P176" s="57" t="n"/>
+      <c r="Q176" s="57" t="n"/>
+      <c r="R176" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="S176" s="57" t="n"/>
+      <c r="T176" s="57" t="n"/>
+      <c r="U176" s="57" t="n"/>
+      <c r="V176" s="57" t="n"/>
+      <c r="W176" s="57" t="n"/>
+      <c r="X176" s="57" t="n"/>
+      <c r="Y176" s="57" t="n"/>
+      <c r="Z176" s="57" t="n"/>
+      <c r="AA176" s="57" t="n"/>
+      <c r="AB176" s="57" t="n"/>
+      <c r="AC176" s="57" t="n"/>
+      <c r="AD176" s="57" t="n"/>
+      <c r="AE176" s="57" t="n"/>
+      <c r="AF176" s="57" t="n"/>
+      <c r="AG176" s="57" t="n"/>
+      <c r="AH176" s="57" t="n"/>
+      <c r="AI176" s="57" t="n"/>
+      <c r="AJ176" s="57" t="n"/>
+      <c r="AK176" s="57" t="n"/>
+      <c r="AL176" s="57" t="n"/>
+      <c r="AM176" s="57" t="n"/>
+      <c r="AN176" s="57" t="n"/>
+      <c r="AO176" s="57" t="n"/>
+      <c r="AP176" s="57" t="n"/>
+      <c r="AQ176" s="57" t="n"/>
+      <c r="AR176" s="57" t="n"/>
+      <c r="AS176" s="57" t="n"/>
+      <c r="AT176" s="57" t="n"/>
+      <c r="CI176" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ176" s="81" t="inlineStr">
+        <is>
+          <t>Lighter bullets go through 4 dinos</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="43" t="inlineStr">
+        <is>
+          <t>Hunting Blind</t>
+        </is>
+      </c>
+      <c r="B177" s="43" t="inlineStr">
+        <is>
+          <t>Trigger Happy</t>
+        </is>
+      </c>
+      <c r="C177" s="43" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="D177" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E177" s="56">
+        <f>E14</f>
+        <v/>
+      </c>
+      <c r="F177" s="56">
+        <f>F14</f>
+        <v/>
+      </c>
+      <c r="G177" s="57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H177" s="57" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I177" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" s="92" t="n"/>
+      <c r="K177" s="92" t="n"/>
+      <c r="L177" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" s="43" t="inlineStr">
+        <is>
+          <t>Shredder</t>
+        </is>
+      </c>
+      <c r="N177" s="57" t="n"/>
+      <c r="O177" s="57" t="n"/>
+      <c r="P177" s="57" t="n"/>
+      <c r="Q177" s="57" t="n"/>
+      <c r="R177" s="57" t="n"/>
+      <c r="S177" s="57" t="n"/>
+      <c r="T177" s="57" t="n"/>
+      <c r="U177" s="57" t="n"/>
+      <c r="V177" s="57" t="n"/>
+      <c r="W177" s="57" t="n"/>
+      <c r="X177" s="57" t="n"/>
+      <c r="Y177" s="57" t="n"/>
+      <c r="Z177" s="57" t="n"/>
+      <c r="AA177" s="57" t="n"/>
+      <c r="AB177" s="57" t="n"/>
+      <c r="AC177" s="57" t="n"/>
+      <c r="AD177" s="57" t="n"/>
+      <c r="AE177" s="57" t="n"/>
+      <c r="AF177" s="57" t="n"/>
+      <c r="AG177" s="57" t="n"/>
+      <c r="AH177" s="57" t="n"/>
+      <c r="AI177" s="57" t="n"/>
+      <c r="AJ177" s="57" t="n"/>
+      <c r="AK177" s="57" t="n"/>
+      <c r="AL177" s="57" t="n"/>
+      <c r="AM177" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AN177" s="57" t="n"/>
+      <c r="AO177" s="57" t="n"/>
+      <c r="AP177" s="57" t="n"/>
+      <c r="AQ177" s="57" t="n"/>
+      <c r="AR177" s="57" t="n"/>
+      <c r="AS177" s="57" t="n"/>
+      <c r="AT177" s="57" t="n"/>
+      <c r="CI177" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ177" s="81" t="inlineStr">
+        <is>
+          <t>The hail of bullets strips armour</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="43" t="inlineStr">
+        <is>
+          <t>Hunting Blind</t>
+        </is>
+      </c>
+      <c r="B178" s="43" t="inlineStr">
+        <is>
+          <t>Hardliner</t>
+        </is>
+      </c>
+      <c r="C178" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D178" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E178" s="56">
+        <f>E18</f>
+        <v/>
+      </c>
+      <c r="F178" s="56">
+        <f>F18</f>
+        <v/>
+      </c>
+      <c r="G178" s="57" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H178" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I178" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J178" s="92" t="n"/>
+      <c r="K178" s="92" t="n"/>
+      <c r="L178" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" s="43" t="inlineStr">
+        <is>
+          <t>Cracking Shot</t>
+        </is>
+      </c>
+      <c r="N178" s="46" t="n"/>
+      <c r="O178" s="57" t="n"/>
+      <c r="P178" s="57" t="n"/>
+      <c r="Q178" s="57" t="n"/>
+      <c r="R178" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="S178" s="57" t="n"/>
+      <c r="T178" s="57" t="n"/>
+      <c r="U178" s="57" t="n"/>
+      <c r="V178" s="57" t="n"/>
+      <c r="W178" s="57" t="n"/>
+      <c r="X178" s="57" t="n"/>
+      <c r="Y178" s="57" t="n"/>
+      <c r="Z178" s="57" t="n"/>
+      <c r="AA178" s="57" t="n"/>
+      <c r="AB178" s="57" t="n"/>
+      <c r="AC178" s="57" t="n"/>
+      <c r="AD178" s="57" t="n"/>
+      <c r="AE178" s="57" t="n"/>
+      <c r="AF178" s="57" t="n"/>
+      <c r="AG178" s="57" t="n"/>
+      <c r="AH178" s="57" t="n"/>
+      <c r="AI178" s="57" t="n"/>
+      <c r="AJ178" s="57" t="n"/>
+      <c r="AK178" s="57" t="n"/>
+      <c r="AL178" s="57" t="n"/>
+      <c r="AM178" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AN178" s="57" t="n"/>
+      <c r="AO178" s="57" t="n"/>
+      <c r="AP178" s="57" t="n"/>
+      <c r="AQ178" s="57" t="n"/>
+      <c r="AR178" s="57" t="n"/>
+      <c r="AS178" s="57" t="n"/>
+      <c r="AT178" s="57" t="n"/>
+      <c r="BJ178" s="105" t="n"/>
+      <c r="CI178" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ178" s="81" t="inlineStr">
+        <is>
+          <t>Goes through 2 dinos and strips their armour</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="43" t="inlineStr">
+        <is>
+          <t>Hunting Blind</t>
+        </is>
+      </c>
+      <c r="B179" s="43" t="inlineStr">
+        <is>
+          <t>Hardliner</t>
+        </is>
+      </c>
+      <c r="C179" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D179" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E179" s="56">
+        <f>E18</f>
+        <v/>
+      </c>
+      <c r="F179" s="56">
+        <f>F18</f>
+        <v/>
+      </c>
+      <c r="G179" s="57" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H179" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I179" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" s="92" t="n"/>
+      <c r="K179" s="92" t="n"/>
+      <c r="L179" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" s="43" t="inlineStr">
+        <is>
+          <t>Heavy Slug</t>
+        </is>
+      </c>
+      <c r="N179" s="46" t="n"/>
+      <c r="O179" s="57" t="n"/>
+      <c r="P179" s="57" t="n"/>
+      <c r="Q179" s="57" t="n"/>
+      <c r="R179" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="S179" s="57" t="n"/>
+      <c r="T179" s="57" t="n"/>
+      <c r="U179" s="57" t="n"/>
+      <c r="V179" s="57" t="n"/>
+      <c r="W179" s="57" t="n"/>
+      <c r="X179" s="57" t="n"/>
+      <c r="Y179" s="57" t="n"/>
+      <c r="Z179" s="57" t="n"/>
+      <c r="AA179" s="57" t="n"/>
+      <c r="AB179" s="57" t="n"/>
+      <c r="AC179" s="57" t="n"/>
+      <c r="AD179" s="57" t="n"/>
+      <c r="AE179" s="57" t="n"/>
+      <c r="AF179" s="57" t="n"/>
+      <c r="AG179" s="57" t="n"/>
+      <c r="AH179" s="57" t="n"/>
+      <c r="AI179" s="57" t="n"/>
+      <c r="AJ179" s="57" t="n"/>
+      <c r="AK179" s="57" t="n"/>
+      <c r="AL179" s="57" t="n"/>
+      <c r="AM179" s="57" t="n"/>
+      <c r="AN179" s="57" t="n"/>
+      <c r="AO179" s="57" t="n"/>
+      <c r="AP179" s="57" t="n"/>
+      <c r="AQ179" s="57" t="n"/>
+      <c r="AR179" s="57" t="n"/>
+      <c r="AS179" s="57" t="n"/>
+      <c r="AT179" s="57" t="n"/>
+      <c r="BJ179" s="105" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI179" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ179" s="81" t="inlineStr">
+        <is>
+          <t>Goes through 2 dinos, shrinking each 3 sizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="43" t="inlineStr">
+        <is>
+          <t>Hunting Blind</t>
+        </is>
+      </c>
+      <c r="B180" s="43" t="inlineStr">
+        <is>
+          <t>Hardliner</t>
+        </is>
+      </c>
+      <c r="C180" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D180" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E180" s="56">
+        <f>E19</f>
+        <v/>
+      </c>
+      <c r="F180" s="56">
+        <f>F19</f>
+        <v/>
+      </c>
+      <c r="G180" s="57" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H180" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I180" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J180" s="92" t="n"/>
+      <c r="K180" s="92" t="n"/>
+      <c r="L180" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" s="43" t="inlineStr">
+        <is>
+          <t>Jolt Rounds</t>
+        </is>
+      </c>
+      <c r="N180" s="46" t="n"/>
+      <c r="O180" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="P180" s="57" t="n"/>
+      <c r="Q180" s="57" t="n"/>
+      <c r="R180" s="57" t="n"/>
+      <c r="S180" s="57" t="n"/>
+      <c r="T180" s="57" t="n"/>
+      <c r="U180" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V180" s="57" t="n"/>
+      <c r="W180" s="57" t="n"/>
+      <c r="X180" s="57" t="n"/>
+      <c r="Y180" s="57" t="n"/>
+      <c r="Z180" s="57" t="n"/>
+      <c r="AA180" s="57" t="n"/>
+      <c r="AB180" s="57" t="n"/>
+      <c r="AC180" s="57" t="n"/>
+      <c r="AD180" s="57" t="n"/>
+      <c r="AE180" s="57" t="n"/>
+      <c r="AF180" s="57" t="n"/>
+      <c r="AG180" s="57" t="n"/>
+      <c r="AH180" s="57" t="n"/>
+      <c r="AI180" s="57" t="n"/>
+      <c r="AJ180" s="57" t="n"/>
+      <c r="AK180" s="57" t="n"/>
+      <c r="AL180" s="57" t="n"/>
+      <c r="AM180" s="57" t="n"/>
+      <c r="AN180" s="57" t="n"/>
+      <c r="AO180" s="57" t="n"/>
+      <c r="AP180" s="57" t="n"/>
+      <c r="AQ180" s="57" t="n"/>
+      <c r="AR180" s="57" t="n"/>
+      <c r="AS180" s="57" t="n"/>
+      <c r="AT180" s="57" t="n"/>
+      <c r="BJ180" s="105" t="n"/>
+      <c r="CI180" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ180" s="81" t="inlineStr">
+        <is>
+          <t>Hits jolt dinos still for a moment</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="43" t="inlineStr">
+        <is>
+          <t>Hunting Blind</t>
+        </is>
+      </c>
+      <c r="B181" s="43" t="inlineStr">
+        <is>
+          <t>Hardliner</t>
+        </is>
+      </c>
+      <c r="C181" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D181" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E181" s="56">
+        <f>E19</f>
+        <v/>
+      </c>
+      <c r="F181" s="56">
+        <f>F19</f>
+        <v/>
+      </c>
+      <c r="G181" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H181" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" s="92" t="n"/>
+      <c r="K181" s="92" t="n"/>
+      <c r="L181" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" s="43" t="inlineStr">
+        <is>
+          <t>Rail Lance</t>
+        </is>
+      </c>
+      <c r="N181" s="46" t="n"/>
+      <c r="O181" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P181" s="57" t="n"/>
+      <c r="Q181" s="57" t="n"/>
+      <c r="R181" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="S181" s="57" t="n"/>
+      <c r="T181" s="57" t="n"/>
+      <c r="U181" s="57" t="n"/>
+      <c r="V181" s="57" t="n"/>
+      <c r="W181" s="57" t="n"/>
+      <c r="X181" s="57" t="n"/>
+      <c r="Y181" s="57" t="n"/>
+      <c r="Z181" s="57" t="n"/>
+      <c r="AA181" s="57" t="n"/>
+      <c r="AB181" s="57" t="n"/>
+      <c r="AC181" s="57" t="n"/>
+      <c r="AD181" s="57" t="n"/>
+      <c r="AE181" s="57" t="n"/>
+      <c r="AF181" s="57" t="n"/>
+      <c r="AG181" s="57" t="n"/>
+      <c r="AH181" s="57" t="n"/>
+      <c r="AI181" s="57" t="n"/>
+      <c r="AJ181" s="57" t="n"/>
+      <c r="AK181" s="57" t="n"/>
+      <c r="AL181" s="57" t="n"/>
+      <c r="AM181" s="57" t="n"/>
+      <c r="AN181" s="57" t="n"/>
+      <c r="AO181" s="57" t="n"/>
+      <c r="AP181" s="57" t="n"/>
+      <c r="AQ181" s="57" t="n"/>
+      <c r="AR181" s="57" t="n"/>
+      <c r="AS181" s="57" t="n"/>
+      <c r="AT181" s="57" t="n"/>
+      <c r="BJ181" s="105" t="n"/>
+      <c r="CI181" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ181" s="81" t="inlineStr">
+        <is>
+          <t>Each bullet goes through 6 dinos</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="43" t="inlineStr">
+        <is>
+          <t>Longshot Perch</t>
+        </is>
+      </c>
+      <c r="B182" s="43" t="inlineStr">
+        <is>
+          <t>Deadeye</t>
+        </is>
+      </c>
+      <c r="C182" s="43" t="inlineStr">
+        <is>
+          <t>targets</t>
+        </is>
+      </c>
+      <c r="D182" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E182" s="56">
+        <f>E23</f>
+        <v/>
+      </c>
+      <c r="F182" s="56">
+        <f>F23</f>
+        <v/>
+      </c>
+      <c r="G182" s="57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H182" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I182" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J182" s="92" t="n"/>
+      <c r="K182" s="92" t="n"/>
+      <c r="L182" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" s="43" t="inlineStr">
+        <is>
+          <t>Wind Shear</t>
+        </is>
+      </c>
+      <c r="N182" s="46" t="n"/>
+      <c r="O182" s="57" t="n"/>
+      <c r="P182" s="57" t="n"/>
+      <c r="Q182" s="57" t="n"/>
+      <c r="R182" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="S182" s="57" t="n"/>
+      <c r="T182" s="57" t="n"/>
+      <c r="U182" s="57" t="n"/>
+      <c r="V182" s="57" t="n"/>
+      <c r="W182" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="X182" s="57" t="n"/>
+      <c r="Y182" s="57" t="n"/>
+      <c r="Z182" s="57" t="n"/>
+      <c r="AA182" s="57" t="n"/>
+      <c r="AB182" s="57" t="n"/>
+      <c r="AC182" s="57" t="n"/>
+      <c r="AD182" s="57" t="n"/>
+      <c r="AE182" s="57" t="n"/>
+      <c r="AF182" s="57" t="n"/>
+      <c r="AG182" s="57" t="n"/>
+      <c r="AH182" s="57" t="n"/>
+      <c r="AI182" s="57" t="n"/>
+      <c r="AJ182" s="57" t="n"/>
+      <c r="AK182" s="57" t="n"/>
+      <c r="AL182" s="57" t="n"/>
+      <c r="AM182" s="57" t="n"/>
+      <c r="AN182" s="57" t="n"/>
+      <c r="AO182" s="57" t="n"/>
+      <c r="AP182" s="57" t="n"/>
+      <c r="AQ182" s="57" t="n"/>
+      <c r="AR182" s="57" t="n"/>
+      <c r="AS182" s="57" t="n"/>
+      <c r="AT182" s="57" t="n"/>
+      <c r="BJ182" s="105" t="n"/>
+      <c r="CI182" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ182" s="81" t="inlineStr">
+        <is>
+          <t>Shots shove the whole line 3 studs back</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="43" t="inlineStr">
+        <is>
+          <t>Longshot Perch</t>
+        </is>
+      </c>
+      <c r="B183" s="43" t="inlineStr">
+        <is>
+          <t>Deadeye</t>
+        </is>
+      </c>
+      <c r="C183" s="43" t="inlineStr">
+        <is>
+          <t>targets</t>
+        </is>
+      </c>
+      <c r="D183" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E183" s="56">
+        <f>E23</f>
+        <v/>
+      </c>
+      <c r="F183" s="56">
+        <f>F23</f>
+        <v/>
+      </c>
+      <c r="G183" s="57" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H183" s="57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I183" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J183" s="92" t="n"/>
+      <c r="K183" s="92" t="n"/>
+      <c r="L183" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M183" s="43" t="inlineStr">
+        <is>
+          <t>Fast Bolt</t>
+        </is>
+      </c>
+      <c r="N183" s="46" t="n"/>
+      <c r="O183" s="57" t="n"/>
+      <c r="P183" s="57" t="n"/>
+      <c r="Q183" s="57" t="n"/>
+      <c r="R183" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="S183" s="57" t="n"/>
+      <c r="T183" s="57" t="n"/>
+      <c r="U183" s="57" t="n"/>
+      <c r="V183" s="57" t="n"/>
+      <c r="W183" s="57" t="n"/>
+      <c r="X183" s="57" t="n"/>
+      <c r="Y183" s="57" t="n"/>
+      <c r="Z183" s="57" t="n"/>
+      <c r="AA183" s="57" t="n"/>
+      <c r="AB183" s="57" t="n"/>
+      <c r="AC183" s="57" t="n"/>
+      <c r="AD183" s="57" t="n"/>
+      <c r="AE183" s="57" t="n"/>
+      <c r="AF183" s="57" t="n"/>
+      <c r="AG183" s="57" t="n"/>
+      <c r="AH183" s="57" t="n"/>
+      <c r="AI183" s="57" t="n"/>
+      <c r="AJ183" s="57" t="n"/>
+      <c r="AK183" s="57" t="n"/>
+      <c r="AL183" s="57" t="n"/>
+      <c r="AM183" s="57" t="n"/>
+      <c r="AN183" s="57" t="n"/>
+      <c r="AO183" s="57" t="n"/>
+      <c r="AP183" s="57" t="n"/>
+      <c r="AQ183" s="57" t="n"/>
+      <c r="AR183" s="57" t="n"/>
+      <c r="AS183" s="57" t="n"/>
+      <c r="AT183" s="57" t="n"/>
+      <c r="BJ183" s="105" t="n"/>
+      <c r="CI183" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ183" s="81" t="inlineStr">
+        <is>
+          <t>Fires much faster through 5 dinos</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="43" t="inlineStr">
+        <is>
+          <t>Longshot Perch</t>
+        </is>
+      </c>
+      <c r="B184" s="43" t="inlineStr">
+        <is>
+          <t>Deadeye</t>
+        </is>
+      </c>
+      <c r="C184" s="43" t="inlineStr">
+        <is>
+          <t>targets</t>
+        </is>
+      </c>
+      <c r="D184" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E184" s="56">
+        <f>E24</f>
+        <v/>
+      </c>
+      <c r="F184" s="56">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="G184" s="57" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H184" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I184" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J184" s="92" t="n"/>
+      <c r="K184" s="92" t="n"/>
+      <c r="L184" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" s="43" t="inlineStr">
+        <is>
+          <t>Piercing Gale</t>
+        </is>
+      </c>
+      <c r="N184" s="46" t="n"/>
+      <c r="O184" s="57" t="n"/>
+      <c r="P184" s="57" t="n"/>
+      <c r="Q184" s="57" t="n"/>
+      <c r="R184" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="S184" s="57" t="n"/>
+      <c r="T184" s="57" t="n"/>
+      <c r="U184" s="57" t="n"/>
+      <c r="V184" s="57" t="n"/>
+      <c r="W184" s="57" t="n"/>
+      <c r="X184" s="57" t="n"/>
+      <c r="Y184" s="57" t="n"/>
+      <c r="Z184" s="57" t="n"/>
+      <c r="AA184" s="57" t="n"/>
+      <c r="AB184" s="57" t="n"/>
+      <c r="AC184" s="57" t="n"/>
+      <c r="AD184" s="57" t="n"/>
+      <c r="AE184" s="57" t="n"/>
+      <c r="AF184" s="57" t="n"/>
+      <c r="AG184" s="57" t="n"/>
+      <c r="AH184" s="57" t="n"/>
+      <c r="AI184" s="57" t="n"/>
+      <c r="AJ184" s="57" t="n"/>
+      <c r="AK184" s="57" t="n"/>
+      <c r="AL184" s="57" t="n"/>
+      <c r="AM184" s="57" t="n"/>
+      <c r="AN184" s="57" t="n"/>
+      <c r="AO184" s="57" t="n"/>
+      <c r="AP184" s="57" t="n"/>
+      <c r="AQ184" s="57" t="n"/>
+      <c r="AR184" s="57" t="n"/>
+      <c r="AS184" s="57" t="n"/>
+      <c r="AT184" s="57" t="n"/>
+      <c r="BJ184" s="105" t="n"/>
+      <c r="CI184" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ184" s="81" t="inlineStr">
+        <is>
+          <t>Fast shots through 8 dinos</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="43" t="inlineStr">
+        <is>
+          <t>Longshot Perch</t>
+        </is>
+      </c>
+      <c r="B185" s="43" t="inlineStr">
+        <is>
+          <t>Deadeye</t>
+        </is>
+      </c>
+      <c r="C185" s="43" t="inlineStr">
+        <is>
+          <t>targets</t>
+        </is>
+      </c>
+      <c r="D185" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E185" s="56">
+        <f>E24</f>
+        <v/>
+      </c>
+      <c r="F185" s="56">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="G185" s="57" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H185" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I185" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J185" s="92" t="n"/>
+      <c r="K185" s="92" t="n"/>
+      <c r="L185" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" s="43" t="inlineStr">
+        <is>
+          <t>Shatterline</t>
+        </is>
+      </c>
+      <c r="N185" s="46" t="n"/>
+      <c r="O185" s="57" t="n"/>
+      <c r="P185" s="57" t="n"/>
+      <c r="Q185" s="57" t="n"/>
+      <c r="R185" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="S185" s="57" t="n"/>
+      <c r="T185" s="57" t="n"/>
+      <c r="U185" s="57" t="n"/>
+      <c r="V185" s="57" t="n"/>
+      <c r="W185" s="57" t="n"/>
+      <c r="X185" s="57" t="n"/>
+      <c r="Y185" s="57" t="n"/>
+      <c r="Z185" s="57" t="n"/>
+      <c r="AA185" s="57" t="n"/>
+      <c r="AB185" s="57" t="n"/>
+      <c r="AC185" s="57" t="n"/>
+      <c r="AD185" s="57" t="n"/>
+      <c r="AE185" s="57" t="n"/>
+      <c r="AF185" s="57" t="n"/>
+      <c r="AG185" s="57" t="n"/>
+      <c r="AH185" s="57" t="n"/>
+      <c r="AI185" s="57" t="n"/>
+      <c r="AJ185" s="57" t="n"/>
+      <c r="AK185" s="57" t="n"/>
+      <c r="AL185" s="57" t="n"/>
+      <c r="AM185" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AN185" s="57" t="n"/>
+      <c r="AO185" s="57" t="n"/>
+      <c r="AP185" s="57" t="n"/>
+      <c r="AQ185" s="57" t="n"/>
+      <c r="AR185" s="57" t="n"/>
+      <c r="AS185" s="57" t="n"/>
+      <c r="AT185" s="57" t="n"/>
+      <c r="BJ185" s="105" t="n"/>
+      <c r="CI185" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ185" s="81" t="inlineStr">
+        <is>
+          <t>Every dino in the line loses its armour</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="43" t="inlineStr">
+        <is>
+          <t>Longshot Perch</t>
+        </is>
+      </c>
+      <c r="B186" s="43" t="inlineStr">
+        <is>
+          <t>Spotter</t>
+        </is>
+      </c>
+      <c r="C186" s="43" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="D186" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E186" s="56">
+        <f>E28</f>
+        <v/>
+      </c>
+      <c r="F186" s="56">
+        <f>F28</f>
+        <v/>
+      </c>
+      <c r="G186" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H186" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I186" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J186" s="92" t="n"/>
+      <c r="K186" s="92" t="n"/>
+      <c r="L186" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M186" s="43" t="inlineStr">
+        <is>
+          <t>Painted Target</t>
+        </is>
+      </c>
+      <c r="N186" s="57" t="n"/>
+      <c r="O186" s="57" t="n"/>
+      <c r="P186" s="57" t="n"/>
+      <c r="Q186" s="57" t="n"/>
+      <c r="R186" s="57" t="n"/>
+      <c r="S186" s="57" t="n"/>
+      <c r="T186" s="57" t="n">
+        <v>30</v>
+      </c>
+      <c r="U186" s="57" t="n"/>
+      <c r="V186" s="57" t="n"/>
+      <c r="W186" s="57" t="n"/>
+      <c r="X186" s="57" t="n"/>
+      <c r="Y186" s="57" t="n"/>
+      <c r="Z186" s="57" t="n"/>
+      <c r="AA186" s="57" t="n"/>
+      <c r="AB186" s="57" t="n"/>
+      <c r="AC186" s="57" t="n"/>
+      <c r="AD186" s="57" t="n"/>
+      <c r="AE186" s="57" t="n"/>
+      <c r="AF186" s="57" t="n"/>
+      <c r="AG186" s="57" t="n"/>
+      <c r="AH186" s="57" t="n"/>
+      <c r="AI186" s="57" t="n"/>
+      <c r="AJ186" s="57" t="n"/>
+      <c r="AK186" s="57" t="n"/>
+      <c r="AL186" s="57" t="n"/>
+      <c r="AM186" s="57" t="n"/>
+      <c r="AN186" s="57" t="n"/>
+      <c r="AO186" s="57" t="n"/>
+      <c r="AP186" s="57" t="n"/>
+      <c r="AQ186" s="57" t="n"/>
+      <c r="AR186" s="57" t="n"/>
+      <c r="AS186" s="57" t="n"/>
+      <c r="AT186" s="57" t="n"/>
+      <c r="BX186" t="n">
+        <v>25</v>
+      </c>
+      <c r="CI186" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ186" s="81" t="inlineStr">
+        <is>
+          <t>Bosses in range take +25% too</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="43" t="inlineStr">
+        <is>
+          <t>Longshot Perch</t>
+        </is>
+      </c>
+      <c r="B187" s="43" t="inlineStr">
+        <is>
+          <t>Spotter</t>
+        </is>
+      </c>
+      <c r="C187" s="43" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="D187" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E187" s="56">
+        <f>E28</f>
+        <v/>
+      </c>
+      <c r="F187" s="56">
+        <f>F28</f>
+        <v/>
+      </c>
+      <c r="G187" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H187" s="57" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I187" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J187" s="92" t="n"/>
+      <c r="K187" s="92" t="n"/>
+      <c r="L187" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M187" s="43" t="inlineStr">
+        <is>
+          <t>Quick Spot</t>
+        </is>
+      </c>
+      <c r="N187" s="57" t="n"/>
+      <c r="O187" s="57" t="n"/>
+      <c r="P187" s="57" t="n"/>
+      <c r="Q187" s="57" t="n"/>
+      <c r="R187" s="57" t="n"/>
+      <c r="S187" s="57" t="n"/>
+      <c r="T187" s="57" t="n"/>
+      <c r="U187" s="57" t="n"/>
+      <c r="V187" s="57" t="n"/>
+      <c r="W187" s="57" t="n"/>
+      <c r="X187" s="57" t="n"/>
+      <c r="Y187" s="57" t="n"/>
+      <c r="Z187" s="57" t="n"/>
+      <c r="AA187" s="57" t="n"/>
+      <c r="AB187" s="57" t="n"/>
+      <c r="AC187" s="57" t="n"/>
+      <c r="AD187" s="57" t="n"/>
+      <c r="AE187" s="57" t="n"/>
+      <c r="AF187" s="57" t="n"/>
+      <c r="AG187" s="57" t="n"/>
+      <c r="AH187" s="57" t="n"/>
+      <c r="AI187" s="57" t="n"/>
+      <c r="AJ187" s="57" t="n"/>
+      <c r="AK187" s="57" t="n"/>
+      <c r="AL187" s="57" t="n"/>
+      <c r="AM187" s="57" t="n"/>
+      <c r="AN187" s="57" t="n"/>
+      <c r="AO187" s="57" t="n"/>
+      <c r="AP187" s="57" t="n"/>
+      <c r="AQ187" s="57" t="n"/>
+      <c r="AR187" s="57" t="n"/>
+      <c r="AS187" s="57" t="n"/>
+      <c r="AT187" s="57" t="n"/>
+      <c r="CI187" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ187" s="81" t="inlineStr">
+        <is>
+          <t>Fires much faster, marks more often</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="43" t="inlineStr">
+        <is>
+          <t>Longshot Perch</t>
+        </is>
+      </c>
+      <c r="B188" s="43" t="inlineStr">
+        <is>
+          <t>Spotter</t>
+        </is>
+      </c>
+      <c r="C188" s="43" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="D188" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E188" s="56">
+        <f>E29</f>
+        <v/>
+      </c>
+      <c r="F188" s="56">
+        <f>F29</f>
+        <v/>
+      </c>
+      <c r="G188" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H188" s="57" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I188" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J188" s="92" t="n"/>
+      <c r="K188" s="92" t="n"/>
+      <c r="L188" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" s="43" t="inlineStr">
+        <is>
+          <t>Spotter Network</t>
+        </is>
+      </c>
+      <c r="N188" s="57" t="n"/>
+      <c r="O188" s="57" t="n"/>
+      <c r="P188" s="57" t="n"/>
+      <c r="Q188" s="57" t="n"/>
+      <c r="R188" s="57" t="n"/>
+      <c r="S188" s="57" t="n"/>
+      <c r="T188" s="57" t="n">
+        <v>45</v>
+      </c>
+      <c r="U188" s="57" t="n"/>
+      <c r="V188" s="57" t="n"/>
+      <c r="W188" s="57" t="n"/>
+      <c r="X188" s="57" t="n"/>
+      <c r="Y188" s="57" t="n"/>
+      <c r="Z188" s="57" t="n"/>
+      <c r="AA188" s="57" t="n"/>
+      <c r="AB188" s="57" t="n"/>
+      <c r="AC188" s="57" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD188" s="57" t="n"/>
+      <c r="AE188" s="57" t="n"/>
+      <c r="AF188" s="57" t="n"/>
+      <c r="AG188" s="57" t="n"/>
+      <c r="AH188" s="57" t="n"/>
+      <c r="AI188" s="57" t="n"/>
+      <c r="AJ188" s="57" t="n"/>
+      <c r="AK188" s="57" t="n"/>
+      <c r="AL188" s="57" t="n"/>
+      <c r="AM188" s="57" t="n"/>
+      <c r="AN188" s="57" t="n"/>
+      <c r="AO188" s="57" t="n"/>
+      <c r="AP188" s="57" t="n"/>
+      <c r="AQ188" s="57" t="n"/>
+      <c r="AR188" s="57" t="n"/>
+      <c r="AS188" s="57" t="n"/>
+      <c r="AT188" s="57" t="n"/>
+      <c r="CI188" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ188" s="81" t="inlineStr">
+        <is>
+          <t>Towers in range hit 15% harder</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="43" t="inlineStr">
+        <is>
+          <t>Longshot Perch</t>
+        </is>
+      </c>
+      <c r="B189" s="43" t="inlineStr">
+        <is>
+          <t>Spotter</t>
+        </is>
+      </c>
+      <c r="C189" s="43" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="D189" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E189" s="56">
+        <f>E29</f>
+        <v/>
+      </c>
+      <c r="F189" s="56">
+        <f>F29</f>
+        <v/>
+      </c>
+      <c r="G189" s="57" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H189" s="57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I189" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J189" s="92" t="n"/>
+      <c r="K189" s="92" t="n"/>
+      <c r="L189" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" s="43" t="inlineStr">
+        <is>
+          <t>Kill Order</t>
+        </is>
+      </c>
+      <c r="N189" s="57" t="n"/>
+      <c r="O189" s="57" t="n"/>
+      <c r="P189" s="57" t="n"/>
+      <c r="Q189" s="57" t="n"/>
+      <c r="R189" s="57" t="n"/>
+      <c r="S189" s="57" t="n"/>
+      <c r="T189" s="57" t="n">
+        <v>50</v>
+      </c>
+      <c r="U189" s="57" t="n"/>
+      <c r="V189" s="57" t="n"/>
+      <c r="W189" s="57" t="n"/>
+      <c r="X189" s="57" t="n"/>
+      <c r="Y189" s="57" t="n"/>
+      <c r="Z189" s="57" t="n"/>
+      <c r="AA189" s="57" t="n"/>
+      <c r="AB189" s="57" t="n"/>
+      <c r="AC189" s="57" t="n"/>
+      <c r="AD189" s="57" t="n"/>
+      <c r="AE189" s="57" t="n"/>
+      <c r="AF189" s="57" t="n"/>
+      <c r="AG189" s="57" t="n"/>
+      <c r="AH189" s="57" t="n"/>
+      <c r="AI189" s="57" t="n"/>
+      <c r="AJ189" s="57" t="n"/>
+      <c r="AK189" s="57" t="n"/>
+      <c r="AL189" s="57" t="n"/>
+      <c r="AM189" s="57" t="n"/>
+      <c r="AN189" s="57" t="n"/>
+      <c r="AO189" s="57" t="n"/>
+      <c r="AP189" s="57" t="n"/>
+      <c r="AQ189" s="57" t="n"/>
+      <c r="AR189" s="57" t="n"/>
+      <c r="AS189" s="57" t="n"/>
+      <c r="AT189" s="57" t="n"/>
+      <c r="BX189" t="n">
+        <v>40</v>
+      </c>
+      <c r="CI189" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ189" s="81" t="inlineStr">
+        <is>
+          <t>Every boss in range takes +40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="43" t="inlineStr">
+        <is>
+          <t>Longshot Perch</t>
+        </is>
+      </c>
+      <c r="B190" s="43" t="inlineStr">
+        <is>
+          <t>Big Bore</t>
+        </is>
+      </c>
+      <c r="C190" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D190" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E190" s="56">
+        <f>E33</f>
+        <v/>
+      </c>
+      <c r="F190" s="56">
+        <f>F33</f>
+        <v/>
+      </c>
+      <c r="G190" s="57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H190" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I190" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J190" s="92" t="n"/>
+      <c r="K190" s="92" t="n"/>
+      <c r="L190" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M190" s="43" t="inlineStr">
+        <is>
+          <t>Elephant Gun</t>
+        </is>
+      </c>
+      <c r="N190" s="57" t="n"/>
+      <c r="O190" s="57" t="n"/>
+      <c r="P190" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q190" s="57" t="n"/>
+      <c r="R190" s="57" t="n"/>
+      <c r="S190" s="57" t="n"/>
+      <c r="T190" s="57" t="n"/>
+      <c r="U190" s="57" t="n"/>
+      <c r="V190" s="57" t="n"/>
+      <c r="W190" s="57" t="n"/>
+      <c r="X190" s="57" t="n"/>
+      <c r="Y190" s="57" t="n"/>
+      <c r="Z190" s="57" t="n"/>
+      <c r="AA190" s="57" t="n"/>
+      <c r="AB190" s="57" t="n"/>
+      <c r="AC190" s="57" t="n"/>
+      <c r="AD190" s="57" t="n"/>
+      <c r="AE190" s="57" t="n"/>
+      <c r="AF190" s="57" t="n"/>
+      <c r="AG190" s="57" t="n"/>
+      <c r="AH190" s="57" t="n"/>
+      <c r="AI190" s="57" t="n"/>
+      <c r="AJ190" s="57" t="n"/>
+      <c r="AK190" s="57" t="n"/>
+      <c r="AL190" s="57" t="n"/>
+      <c r="AM190" s="57" t="n"/>
+      <c r="AN190" s="57" t="n"/>
+      <c r="AO190" s="57" t="n"/>
+      <c r="AP190" s="57" t="n"/>
+      <c r="AQ190" s="57" t="n"/>
+      <c r="AR190" s="57" t="n"/>
+      <c r="AS190" s="57" t="n"/>
+      <c r="AT190" s="57" t="n"/>
+      <c r="BJ190" s="105" t="n"/>
+      <c r="CI190" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ190" s="81" t="inlineStr">
+        <is>
+          <t>Twice the damage against bosses</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="43" t="inlineStr">
+        <is>
+          <t>Longshot Perch</t>
+        </is>
+      </c>
+      <c r="B191" s="43" t="inlineStr">
+        <is>
+          <t>Big Bore</t>
+        </is>
+      </c>
+      <c r="C191" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D191" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E191" s="56">
+        <f>E33</f>
+        <v/>
+      </c>
+      <c r="F191" s="56">
+        <f>F33</f>
+        <v/>
+      </c>
+      <c r="G191" s="57" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H191" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I191" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J191" s="92" t="n"/>
+      <c r="K191" s="92" t="n"/>
+      <c r="L191" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" s="43" t="inlineStr">
+        <is>
+          <t>Knockdown Round</t>
+        </is>
+      </c>
+      <c r="N191" s="57" t="n"/>
+      <c r="O191" s="57" t="n"/>
+      <c r="P191" s="57" t="n"/>
+      <c r="Q191" s="57" t="n"/>
+      <c r="R191" s="57" t="n"/>
+      <c r="S191" s="57" t="n"/>
+      <c r="T191" s="57" t="n"/>
+      <c r="U191" s="57" t="n"/>
+      <c r="V191" s="57" t="n"/>
+      <c r="W191" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="X191" s="57" t="n"/>
+      <c r="Y191" s="57" t="n"/>
+      <c r="Z191" s="57" t="n"/>
+      <c r="AA191" s="57" t="n"/>
+      <c r="AB191" s="57" t="n"/>
+      <c r="AC191" s="57" t="n"/>
+      <c r="AD191" s="57" t="n"/>
+      <c r="AE191" s="57" t="n"/>
+      <c r="AF191" s="57" t="n"/>
+      <c r="AG191" s="57" t="n"/>
+      <c r="AH191" s="57" t="n"/>
+      <c r="AI191" s="57" t="n"/>
+      <c r="AJ191" s="57" t="n"/>
+      <c r="AK191" s="57" t="n"/>
+      <c r="AL191" s="57" t="n"/>
+      <c r="AM191" s="57" t="n"/>
+      <c r="AN191" s="57" t="n"/>
+      <c r="AO191" s="57" t="n"/>
+      <c r="AP191" s="57" t="n"/>
+      <c r="AQ191" s="57" t="n"/>
+      <c r="AR191" s="57" t="n"/>
+      <c r="AS191" s="57" t="n"/>
+      <c r="AT191" s="57" t="n"/>
+      <c r="BJ191" s="105" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI191" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ191" s="81" t="inlineStr">
+        <is>
+          <t>Knocks the hit dino 4 studs back</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="43" t="inlineStr">
+        <is>
+          <t>Longshot Perch</t>
+        </is>
+      </c>
+      <c r="B192" s="43" t="inlineStr">
+        <is>
+          <t>Big Bore</t>
+        </is>
+      </c>
+      <c r="C192" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D192" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E192" s="56">
+        <f>E34</f>
+        <v/>
+      </c>
+      <c r="F192" s="56">
+        <f>F34</f>
+        <v/>
+      </c>
+      <c r="G192" s="57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H192" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I192" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J192" s="92" t="n"/>
+      <c r="K192" s="92" t="n"/>
+      <c r="L192" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M192" s="43" t="inlineStr">
+        <is>
+          <t>Bone Splitter</t>
+        </is>
+      </c>
+      <c r="N192" s="57" t="n"/>
+      <c r="O192" s="57" t="n"/>
+      <c r="P192" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q192" s="57" t="n"/>
+      <c r="R192" s="57" t="n"/>
+      <c r="S192" s="57" t="n"/>
+      <c r="T192" s="57" t="n"/>
+      <c r="U192" s="57" t="n"/>
+      <c r="V192" s="46" t="n"/>
+      <c r="W192" s="57" t="n"/>
+      <c r="X192" s="57" t="n"/>
+      <c r="Y192" s="57" t="n"/>
+      <c r="Z192" s="57" t="n"/>
+      <c r="AA192" s="57" t="n"/>
+      <c r="AB192" s="57" t="n"/>
+      <c r="AC192" s="57" t="n"/>
+      <c r="AD192" s="57" t="n"/>
+      <c r="AE192" s="57" t="n"/>
+      <c r="AF192" s="57" t="n"/>
+      <c r="AG192" s="57" t="n"/>
+      <c r="AH192" s="57" t="n"/>
+      <c r="AI192" s="57" t="n"/>
+      <c r="AJ192" s="57" t="n"/>
+      <c r="AK192" s="57" t="n"/>
+      <c r="AL192" s="57" t="n"/>
+      <c r="AM192" s="57" t="n"/>
+      <c r="AN192" s="57" t="n"/>
+      <c r="AO192" s="57" t="n"/>
+      <c r="AP192" s="57" t="n"/>
+      <c r="AQ192" s="57" t="n"/>
+      <c r="AR192" s="57" t="n"/>
+      <c r="AS192" s="57" t="n"/>
+      <c r="AT192" s="57" t="n"/>
+      <c r="BJ192" s="105" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI192" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ192" s="81" t="inlineStr">
+        <is>
+          <t>Each shot shrinks a dino 5 sizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="43" t="inlineStr">
+        <is>
+          <t>Longshot Perch</t>
+        </is>
+      </c>
+      <c r="B193" s="43" t="inlineStr">
+        <is>
+          <t>Big Bore</t>
+        </is>
+      </c>
+      <c r="C193" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D193" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E193" s="56">
+        <f>E34</f>
+        <v/>
+      </c>
+      <c r="F193" s="56">
+        <f>F34</f>
+        <v/>
+      </c>
+      <c r="G193" s="57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H193" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I193" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J193" s="92" t="n"/>
+      <c r="K193" s="92" t="n"/>
+      <c r="L193" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M193" s="43" t="inlineStr">
+        <is>
+          <t>Hammer Shot</t>
+        </is>
+      </c>
+      <c r="N193" s="57" t="n"/>
+      <c r="O193" s="57" t="n"/>
+      <c r="P193" s="57" t="n"/>
+      <c r="Q193" s="57" t="n"/>
+      <c r="R193" s="57" t="n"/>
+      <c r="S193" s="57" t="n"/>
+      <c r="T193" s="57" t="n"/>
+      <c r="U193" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V193" s="46" t="n"/>
+      <c r="W193" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="X193" s="57" t="n"/>
+      <c r="Y193" s="57" t="n"/>
+      <c r="Z193" s="57" t="n"/>
+      <c r="AA193" s="57" t="n"/>
+      <c r="AB193" s="57" t="n"/>
+      <c r="AC193" s="57" t="n"/>
+      <c r="AD193" s="57" t="n"/>
+      <c r="AE193" s="57" t="n"/>
+      <c r="AF193" s="57" t="n"/>
+      <c r="AG193" s="57" t="n"/>
+      <c r="AH193" s="57" t="n"/>
+      <c r="AI193" s="57" t="n"/>
+      <c r="AJ193" s="57" t="n"/>
+      <c r="AK193" s="57" t="n"/>
+      <c r="AL193" s="57" t="n"/>
+      <c r="AM193" s="57" t="n"/>
+      <c r="AN193" s="57" t="n"/>
+      <c r="AO193" s="57" t="n"/>
+      <c r="AP193" s="57" t="n"/>
+      <c r="AQ193" s="57" t="n"/>
+      <c r="AR193" s="57" t="n"/>
+      <c r="AS193" s="57" t="n"/>
+      <c r="AT193" s="57" t="n"/>
+      <c r="BJ193" s="105" t="n"/>
+      <c r="CI193" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ193" s="81" t="inlineStr">
+        <is>
+          <t>Stuns 1.2 s and knocks 6 studs back</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="43" t="inlineStr">
+        <is>
+          <t>Mortar Pit</t>
+        </is>
+      </c>
+      <c r="B194" s="43" t="inlineStr">
+        <is>
+          <t>Blast</t>
+        </is>
+      </c>
+      <c r="C194" s="43" t="inlineStr">
+        <is>
+          <t>targets</t>
+        </is>
+      </c>
+      <c r="D194" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E194" s="56">
+        <f>E38</f>
+        <v/>
+      </c>
+      <c r="F194" s="56">
+        <f>F38</f>
+        <v/>
+      </c>
+      <c r="G194" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H194" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I194" s="57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J194" s="92" t="n"/>
+      <c r="K194" s="92" t="n"/>
+      <c r="L194" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" s="43" t="inlineStr">
+        <is>
+          <t>Big Shell</t>
+        </is>
+      </c>
+      <c r="N194" s="57" t="n"/>
+      <c r="O194" s="57" t="n"/>
+      <c r="P194" s="57" t="n"/>
+      <c r="Q194" s="57" t="n"/>
+      <c r="R194" s="57" t="n"/>
+      <c r="S194" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T194" s="57" t="n"/>
+      <c r="U194" s="57" t="n"/>
+      <c r="V194" s="57" t="n"/>
+      <c r="W194" s="57" t="n"/>
+      <c r="X194" s="57" t="n"/>
+      <c r="Y194" s="57" t="n"/>
+      <c r="Z194" s="57" t="n"/>
+      <c r="AA194" s="57" t="n"/>
+      <c r="AB194" s="57" t="n"/>
+      <c r="AC194" s="57" t="n"/>
+      <c r="AD194" s="57" t="n"/>
+      <c r="AE194" s="57" t="n"/>
+      <c r="AF194" s="57" t="n"/>
+      <c r="AG194" s="57" t="n"/>
+      <c r="AH194" s="57" t="n"/>
+      <c r="AI194" s="57" t="n"/>
+      <c r="AJ194" s="57" t="n"/>
+      <c r="AK194" s="57" t="n"/>
+      <c r="AL194" s="57" t="n"/>
+      <c r="AM194" s="57" t="n"/>
+      <c r="AN194" s="57" t="n"/>
+      <c r="AO194" s="57" t="n"/>
+      <c r="AP194" s="57" t="n"/>
+      <c r="AQ194" s="57" t="n"/>
+      <c r="AR194" s="57" t="n"/>
+      <c r="AS194" s="57" t="n"/>
+      <c r="AT194" s="57" t="n"/>
+      <c r="CI194" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ194" s="81" t="inlineStr">
+        <is>
+          <t>Much bigger blasts</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="43" t="inlineStr">
+        <is>
+          <t>Mortar Pit</t>
+        </is>
+      </c>
+      <c r="B195" s="43" t="inlineStr">
+        <is>
+          <t>Blast</t>
+        </is>
+      </c>
+      <c r="C195" s="43" t="inlineStr">
+        <is>
+          <t>targets</t>
+        </is>
+      </c>
+      <c r="D195" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E195" s="56">
+        <f>E38</f>
+        <v/>
+      </c>
+      <c r="F195" s="56">
+        <f>F38</f>
+        <v/>
+      </c>
+      <c r="G195" s="57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H195" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I195" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J195" s="92" t="n"/>
+      <c r="K195" s="92" t="n"/>
+      <c r="L195" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M195" s="43" t="inlineStr">
+        <is>
+          <t>White Phosphorus</t>
+        </is>
+      </c>
+      <c r="N195" s="57" t="n"/>
+      <c r="O195" s="57" t="n"/>
+      <c r="P195" s="57" t="n"/>
+      <c r="Q195" s="57" t="n"/>
+      <c r="R195" s="57" t="n"/>
+      <c r="S195" s="57" t="n"/>
+      <c r="T195" s="57" t="n"/>
+      <c r="U195" s="57" t="n"/>
+      <c r="V195" s="57" t="n"/>
+      <c r="W195" s="57" t="n"/>
+      <c r="X195" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y195" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z195" s="57" t="n"/>
+      <c r="AA195" s="57" t="n"/>
+      <c r="AB195" s="57" t="n"/>
+      <c r="AC195" s="57" t="n"/>
+      <c r="AD195" s="57" t="n"/>
+      <c r="AE195" s="57" t="n"/>
+      <c r="AF195" s="57" t="n"/>
+      <c r="AG195" s="57" t="n"/>
+      <c r="AH195" s="57" t="n"/>
+      <c r="AI195" s="57" t="n"/>
+      <c r="AJ195" s="57" t="n"/>
+      <c r="AK195" s="57" t="n"/>
+      <c r="AL195" s="57" t="n"/>
+      <c r="AM195" s="57" t="n"/>
+      <c r="AN195" s="57" t="n"/>
+      <c r="AO195" s="57" t="n"/>
+      <c r="AP195" s="57" t="n"/>
+      <c r="AQ195" s="57" t="n"/>
+      <c r="AR195" s="57" t="n"/>
+      <c r="AS195" s="57" t="n"/>
+      <c r="AT195" s="57" t="n"/>
+      <c r="CI195" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ195" s="81" t="inlineStr">
+        <is>
+          <t>A short, very hot burning patch</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="43" t="inlineStr">
+        <is>
+          <t>Mortar Pit</t>
+        </is>
+      </c>
+      <c r="B196" s="43" t="inlineStr">
+        <is>
+          <t>Blast</t>
+        </is>
+      </c>
+      <c r="C196" s="43" t="inlineStr">
+        <is>
+          <t>targets</t>
+        </is>
+      </c>
+      <c r="D196" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E196" s="56">
+        <f>E39</f>
+        <v/>
+      </c>
+      <c r="F196" s="56">
+        <f>F39</f>
+        <v/>
+      </c>
+      <c r="G196" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H196" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I196" s="57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J196" s="92" t="n"/>
+      <c r="K196" s="92" t="n"/>
+      <c r="L196" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M196" s="43" t="inlineStr">
+        <is>
+          <t>Blast Furnace</t>
+        </is>
+      </c>
+      <c r="N196" s="57" t="n"/>
+      <c r="O196" s="57" t="n"/>
+      <c r="P196" s="57" t="n"/>
+      <c r="Q196" s="57" t="n"/>
+      <c r="R196" s="57" t="n"/>
+      <c r="S196" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T196" s="57" t="n"/>
+      <c r="U196" s="57" t="n"/>
+      <c r="V196" s="57" t="n"/>
+      <c r="W196" s="57" t="n"/>
+      <c r="X196" s="57" t="n"/>
+      <c r="Y196" s="57" t="n"/>
+      <c r="Z196" s="57" t="n"/>
+      <c r="AA196" s="57" t="n"/>
+      <c r="AB196" s="57" t="n"/>
+      <c r="AC196" s="57" t="n"/>
+      <c r="AD196" s="57" t="n"/>
+      <c r="AE196" s="57" t="n"/>
+      <c r="AF196" s="57" t="n"/>
+      <c r="AG196" s="57" t="n"/>
+      <c r="AH196" s="57" t="n"/>
+      <c r="AI196" s="57" t="n"/>
+      <c r="AJ196" s="57" t="n"/>
+      <c r="AK196" s="57" t="n"/>
+      <c r="AL196" s="57" t="n"/>
+      <c r="AM196" s="57" t="n"/>
+      <c r="AN196" s="57" t="n"/>
+      <c r="AO196" s="57" t="n"/>
+      <c r="AP196" s="57" t="n"/>
+      <c r="AQ196" s="57" t="n"/>
+      <c r="AR196" s="57" t="n"/>
+      <c r="AS196" s="57" t="n"/>
+      <c r="AT196" s="57" t="n"/>
+      <c r="CI196" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ196" s="81" t="inlineStr">
+        <is>
+          <t>Huge blasts that hit harder</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="43" t="inlineStr">
+        <is>
+          <t>Mortar Pit</t>
+        </is>
+      </c>
+      <c r="B197" s="43" t="inlineStr">
+        <is>
+          <t>Blast</t>
+        </is>
+      </c>
+      <c r="C197" s="43" t="inlineStr">
+        <is>
+          <t>targets</t>
+        </is>
+      </c>
+      <c r="D197" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E197" s="56">
+        <f>E39</f>
+        <v/>
+      </c>
+      <c r="F197" s="56">
+        <f>F39</f>
+        <v/>
+      </c>
+      <c r="G197" s="57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H197" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J197" s="92" t="n"/>
+      <c r="K197" s="92" t="n"/>
+      <c r="L197" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" s="43" t="inlineStr">
+        <is>
+          <t>Inferno Shell</t>
+        </is>
+      </c>
+      <c r="N197" s="57" t="n"/>
+      <c r="O197" s="57" t="n"/>
+      <c r="P197" s="57" t="n"/>
+      <c r="Q197" s="57" t="n"/>
+      <c r="R197" s="57" t="n"/>
+      <c r="S197" s="57" t="n"/>
+      <c r="T197" s="57" t="n"/>
+      <c r="U197" s="57" t="n"/>
+      <c r="V197" s="57" t="n"/>
+      <c r="W197" s="57" t="n"/>
+      <c r="X197" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y197" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z197" s="57" t="n"/>
+      <c r="AA197" s="57" t="n"/>
+      <c r="AB197" s="57" t="n"/>
+      <c r="AC197" s="57" t="n"/>
+      <c r="AD197" s="57" t="n"/>
+      <c r="AE197" s="57" t="n"/>
+      <c r="AF197" s="57" t="n"/>
+      <c r="AG197" s="57" t="n"/>
+      <c r="AH197" s="57" t="n"/>
+      <c r="AI197" s="57" t="n"/>
+      <c r="AJ197" s="57" t="n"/>
+      <c r="AK197" s="57" t="n"/>
+      <c r="AL197" s="57" t="n"/>
+      <c r="AM197" s="57" t="n"/>
+      <c r="AN197" s="57" t="n"/>
+      <c r="AO197" s="57" t="n"/>
+      <c r="AP197" s="57" t="n"/>
+      <c r="AQ197" s="57" t="n"/>
+      <c r="AR197" s="57" t="n"/>
+      <c r="AS197" s="57" t="n"/>
+      <c r="AT197" s="57" t="n"/>
+      <c r="CI197" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ197" s="81" t="inlineStr">
+        <is>
+          <t>Patches burn twice as hot</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="43" t="inlineStr">
+        <is>
+          <t>Mortar Pit</t>
+        </is>
+      </c>
+      <c r="B198" s="43" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="C198" s="43" t="inlineStr">
+        <is>
+          <t>targets</t>
+        </is>
+      </c>
+      <c r="D198" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E198" s="56">
+        <f>E43</f>
+        <v/>
+      </c>
+      <c r="F198" s="56">
+        <f>F43</f>
+        <v/>
+      </c>
+      <c r="G198" s="57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H198" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I198" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J198" s="92" t="n"/>
+      <c r="K198" s="92" t="n"/>
+      <c r="L198" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M198" s="43" t="inlineStr">
+        <is>
+          <t>Fire Bomblets</t>
+        </is>
+      </c>
+      <c r="N198" s="57" t="n"/>
+      <c r="O198" s="57" t="n"/>
+      <c r="P198" s="57" t="n"/>
+      <c r="Q198" s="57" t="n"/>
+      <c r="R198" s="57" t="n"/>
+      <c r="S198" s="57" t="n"/>
+      <c r="T198" s="57" t="n"/>
+      <c r="U198" s="57" t="n"/>
+      <c r="V198" s="57" t="n"/>
+      <c r="W198" s="57" t="n"/>
+      <c r="X198" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y198" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z198" s="57" t="n"/>
+      <c r="AA198" s="57" t="n"/>
+      <c r="AB198" s="57" t="n"/>
+      <c r="AC198" s="57" t="n"/>
+      <c r="AD198" s="57" t="n"/>
+      <c r="AE198" s="57" t="n"/>
+      <c r="AF198" s="57" t="n"/>
+      <c r="AG198" s="57" t="n"/>
+      <c r="AH198" s="57" t="n"/>
+      <c r="AI198" s="57" t="n"/>
+      <c r="AJ198" s="57" t="n"/>
+      <c r="AK198" s="57" t="n"/>
+      <c r="AL198" s="57" t="n"/>
+      <c r="AM198" s="57" t="n"/>
+      <c r="AN198" s="57" t="n"/>
+      <c r="AO198" s="57" t="n"/>
+      <c r="AP198" s="57" t="n"/>
+      <c r="AQ198" s="57" t="n"/>
+      <c r="AR198" s="57" t="n"/>
+      <c r="AS198" s="57" t="n"/>
+      <c r="AT198" s="57" t="n"/>
+      <c r="CI198" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ198" s="81" t="inlineStr">
+        <is>
+          <t>Bomblets leave small fires</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="43" t="inlineStr">
+        <is>
+          <t>Mortar Pit</t>
+        </is>
+      </c>
+      <c r="B199" s="43" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="C199" s="43" t="inlineStr">
+        <is>
+          <t>targets</t>
+        </is>
+      </c>
+      <c r="D199" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E199" s="56">
+        <f>E43</f>
+        <v/>
+      </c>
+      <c r="F199" s="56">
+        <f>F43</f>
+        <v/>
+      </c>
+      <c r="G199" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H199" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I199" s="57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J199" s="92" t="n"/>
+      <c r="K199" s="92" t="n"/>
+      <c r="L199" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M199" s="43" t="inlineStr">
+        <is>
+          <t>Wide Scatter</t>
+        </is>
+      </c>
+      <c r="N199" s="57" t="n"/>
+      <c r="O199" s="57" t="n"/>
+      <c r="P199" s="57" t="n"/>
+      <c r="Q199" s="57" t="n"/>
+      <c r="R199" s="57" t="n"/>
+      <c r="S199" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T199" s="57" t="n"/>
+      <c r="U199" s="57" t="n"/>
+      <c r="V199" s="57" t="n"/>
+      <c r="W199" s="57" t="n"/>
+      <c r="X199" s="57" t="n"/>
+      <c r="Y199" s="57" t="n"/>
+      <c r="Z199" s="57" t="n"/>
+      <c r="AA199" s="57" t="n"/>
+      <c r="AB199" s="57" t="n"/>
+      <c r="AC199" s="57" t="n"/>
+      <c r="AD199" s="57" t="n"/>
+      <c r="AE199" s="57" t="n"/>
+      <c r="AF199" s="57" t="n"/>
+      <c r="AG199" s="57" t="n"/>
+      <c r="AH199" s="57" t="n"/>
+      <c r="AI199" s="57" t="n"/>
+      <c r="AJ199" s="57" t="n"/>
+      <c r="AK199" s="57" t="n"/>
+      <c r="AL199" s="57" t="n"/>
+      <c r="AM199" s="57" t="n"/>
+      <c r="AN199" s="57" t="n"/>
+      <c r="AO199" s="57" t="n"/>
+      <c r="AP199" s="57" t="n"/>
+      <c r="AQ199" s="57" t="n"/>
+      <c r="AR199" s="57" t="n"/>
+      <c r="AS199" s="57" t="n"/>
+      <c r="AT199" s="57" t="n"/>
+      <c r="CI199" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ199" s="81" t="inlineStr">
+        <is>
+          <t>Bomblets spread over a wider area</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="43" t="inlineStr">
+        <is>
+          <t>Mortar Pit</t>
+        </is>
+      </c>
+      <c r="B200" s="43" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="C200" s="43" t="inlineStr">
+        <is>
+          <t>targets</t>
+        </is>
+      </c>
+      <c r="D200" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E200" s="56">
+        <f>E44</f>
+        <v/>
+      </c>
+      <c r="F200" s="56">
+        <f>F44</f>
+        <v/>
+      </c>
+      <c r="G200" s="57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H200" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I200" s="57" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J200" s="92" t="n"/>
+      <c r="K200" s="92" t="n"/>
+      <c r="L200" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" s="43" t="inlineStr">
+        <is>
+          <t>Firecracker Rain</t>
+        </is>
+      </c>
+      <c r="N200" s="57" t="n"/>
+      <c r="O200" s="57" t="n"/>
+      <c r="P200" s="57" t="n"/>
+      <c r="Q200" s="57" t="n"/>
+      <c r="R200" s="57" t="n"/>
+      <c r="S200" s="57" t="n"/>
+      <c r="T200" s="57" t="n"/>
+      <c r="U200" s="57" t="n"/>
+      <c r="V200" s="57" t="n"/>
+      <c r="W200" s="57" t="n"/>
+      <c r="X200" s="57" t="n"/>
+      <c r="Y200" s="57" t="n"/>
+      <c r="Z200" s="57" t="n"/>
+      <c r="AA200" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB200" s="57" t="n"/>
+      <c r="AC200" s="57" t="n"/>
+      <c r="AD200" s="57" t="n"/>
+      <c r="AE200" s="57" t="n"/>
+      <c r="AF200" s="57" t="n"/>
+      <c r="AG200" s="57" t="n"/>
+      <c r="AH200" s="57" t="n"/>
+      <c r="AI200" s="57" t="n"/>
+      <c r="AJ200" s="57" t="n"/>
+      <c r="AK200" s="57" t="n"/>
+      <c r="AL200" s="57" t="n"/>
+      <c r="AM200" s="57" t="n"/>
+      <c r="AN200" s="57" t="n"/>
+      <c r="AO200" s="57" t="n"/>
+      <c r="AP200" s="57" t="n"/>
+      <c r="AQ200" s="57" t="n"/>
+      <c r="AR200" s="57" t="n"/>
+      <c r="AS200" s="57" t="n"/>
+      <c r="AT200" s="57" t="n"/>
+      <c r="CI200" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ200" s="81" t="inlineStr">
+        <is>
+          <t>Bomblets burst a third time</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="43" t="inlineStr">
+        <is>
+          <t>Mortar Pit</t>
+        </is>
+      </c>
+      <c r="B201" s="43" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="C201" s="43" t="inlineStr">
+        <is>
+          <t>targets</t>
+        </is>
+      </c>
+      <c r="D201" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E201" s="56">
+        <f>E44</f>
+        <v/>
+      </c>
+      <c r="F201" s="56">
+        <f>F44</f>
+        <v/>
+      </c>
+      <c r="G201" s="57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H201" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I201" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J201" s="92" t="n"/>
+      <c r="K201" s="92" t="n"/>
+      <c r="L201" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M201" s="43" t="inlineStr">
+        <is>
+          <t>Thumper Shells</t>
+        </is>
+      </c>
+      <c r="N201" s="57" t="n"/>
+      <c r="O201" s="57" t="n"/>
+      <c r="P201" s="57" t="n"/>
+      <c r="Q201" s="57" t="n"/>
+      <c r="R201" s="57" t="n"/>
+      <c r="S201" s="57" t="n"/>
+      <c r="T201" s="57" t="n"/>
+      <c r="U201" s="57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V201" s="57" t="n"/>
+      <c r="W201" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="X201" s="57" t="n"/>
+      <c r="Y201" s="57" t="n"/>
+      <c r="Z201" s="57" t="n"/>
+      <c r="AA201" s="57" t="n"/>
+      <c r="AB201" s="57" t="n"/>
+      <c r="AC201" s="57" t="n"/>
+      <c r="AD201" s="57" t="n"/>
+      <c r="AE201" s="57" t="n"/>
+      <c r="AF201" s="57" t="n"/>
+      <c r="AG201" s="57" t="n"/>
+      <c r="AH201" s="57" t="n"/>
+      <c r="AI201" s="57" t="n"/>
+      <c r="AJ201" s="57" t="n"/>
+      <c r="AK201" s="57" t="n"/>
+      <c r="AL201" s="57" t="n"/>
+      <c r="AM201" s="57" t="n"/>
+      <c r="AN201" s="57" t="n"/>
+      <c r="AO201" s="57" t="n"/>
+      <c r="AP201" s="57" t="n"/>
+      <c r="AQ201" s="57" t="n"/>
+      <c r="AR201" s="57" t="n"/>
+      <c r="AS201" s="57" t="n"/>
+      <c r="AT201" s="57" t="n"/>
+      <c r="CI201" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ201" s="81" t="inlineStr">
+        <is>
+          <t>Bomblets knock small dinos back</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="43" t="inlineStr">
+        <is>
+          <t>Mortar Pit</t>
+        </is>
+      </c>
+      <c r="B202" s="43" t="inlineStr">
+        <is>
+          <t>Concussive</t>
+        </is>
+      </c>
+      <c r="C202" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D202" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E202" s="56">
+        <f>E48</f>
+        <v/>
+      </c>
+      <c r="F202" s="56">
+        <f>F48</f>
+        <v/>
+      </c>
+      <c r="G202" s="57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H202" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I202" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J202" s="92" t="n"/>
+      <c r="K202" s="92" t="n"/>
+      <c r="L202" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M202" s="43" t="inlineStr">
+        <is>
+          <t>Aftershock</t>
+        </is>
+      </c>
+      <c r="N202" s="46" t="n"/>
+      <c r="O202" s="57" t="n"/>
+      <c r="P202" s="57" t="n"/>
+      <c r="Q202" s="57" t="n"/>
+      <c r="R202" s="57" t="n"/>
+      <c r="S202" s="57" t="n"/>
+      <c r="T202" s="57" t="n"/>
+      <c r="U202" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V202" s="57" t="n"/>
+      <c r="W202" s="57" t="n"/>
+      <c r="X202" s="57" t="n"/>
+      <c r="Y202" s="57" t="n"/>
+      <c r="Z202" s="57" t="n"/>
+      <c r="AA202" s="57" t="n"/>
+      <c r="AB202" s="57" t="n"/>
+      <c r="AC202" s="57" t="n"/>
+      <c r="AD202" s="57" t="n"/>
+      <c r="AE202" s="57" t="n"/>
+      <c r="AF202" s="57" t="n"/>
+      <c r="AG202" s="57" t="n"/>
+      <c r="AH202" s="57" t="n"/>
+      <c r="AI202" s="57" t="n"/>
+      <c r="AJ202" s="57" t="n"/>
+      <c r="AK202" s="57" t="n"/>
+      <c r="AL202" s="57" t="n"/>
+      <c r="AM202" s="57" t="n"/>
+      <c r="AN202" s="57" t="n"/>
+      <c r="AO202" s="57" t="n"/>
+      <c r="AP202" s="57" t="n"/>
+      <c r="AQ202" s="57" t="n"/>
+      <c r="AR202" s="57" t="n"/>
+      <c r="AS202" s="57" t="n"/>
+      <c r="AT202" s="57" t="n"/>
+      <c r="CI202" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ202" s="81" t="inlineStr">
+        <is>
+          <t>Stuns hit dinos for half a second</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="43" t="inlineStr">
+        <is>
+          <t>Mortar Pit</t>
+        </is>
+      </c>
+      <c r="B203" s="43" t="inlineStr">
+        <is>
+          <t>Concussive</t>
+        </is>
+      </c>
+      <c r="C203" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D203" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E203" s="56">
+        <f>E48</f>
+        <v/>
+      </c>
+      <c r="F203" s="56">
+        <f>F48</f>
+        <v/>
+      </c>
+      <c r="G203" s="57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H203" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I203" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J203" s="92" t="n"/>
+      <c r="K203" s="92" t="n"/>
+      <c r="L203" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" s="43" t="inlineStr">
+        <is>
+          <t>Armour Splitter</t>
+        </is>
+      </c>
+      <c r="N203" s="46" t="n"/>
+      <c r="O203" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P203" s="57" t="n"/>
+      <c r="Q203" s="57" t="n"/>
+      <c r="R203" s="57" t="n"/>
+      <c r="S203" s="57" t="n"/>
+      <c r="T203" s="57" t="n"/>
+      <c r="U203" s="57" t="n"/>
+      <c r="V203" s="57" t="n"/>
+      <c r="W203" s="57" t="n"/>
+      <c r="X203" s="57" t="n"/>
+      <c r="Y203" s="57" t="n"/>
+      <c r="Z203" s="57" t="n"/>
+      <c r="AA203" s="57" t="n"/>
+      <c r="AB203" s="57" t="n"/>
+      <c r="AC203" s="57" t="n"/>
+      <c r="AD203" s="57" t="n"/>
+      <c r="AE203" s="57" t="n"/>
+      <c r="AF203" s="57" t="n"/>
+      <c r="AG203" s="57" t="n"/>
+      <c r="AH203" s="57" t="n"/>
+      <c r="AI203" s="57" t="n"/>
+      <c r="AJ203" s="57" t="n"/>
+      <c r="AK203" s="57" t="n"/>
+      <c r="AL203" s="57" t="n"/>
+      <c r="AM203" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AN203" s="57" t="n"/>
+      <c r="AO203" s="57" t="n"/>
+      <c r="AP203" s="57" t="n"/>
+      <c r="AQ203" s="57" t="n"/>
+      <c r="AR203" s="57" t="n"/>
+      <c r="AS203" s="57" t="n"/>
+      <c r="AT203" s="57" t="n"/>
+      <c r="CI203" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ203" s="81" t="inlineStr">
+        <is>
+          <t>Hit dinos lose their armour</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="43" t="inlineStr">
+        <is>
+          <t>Mortar Pit</t>
+        </is>
+      </c>
+      <c r="B204" s="43" t="inlineStr">
+        <is>
+          <t>Concussive</t>
+        </is>
+      </c>
+      <c r="C204" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D204" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E204" s="56">
+        <f>E49</f>
+        <v/>
+      </c>
+      <c r="F204" s="56">
+        <f>F49</f>
+        <v/>
+      </c>
+      <c r="G204" s="57" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H204" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I204" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J204" s="92" t="n"/>
+      <c r="K204" s="92" t="n"/>
+      <c r="L204" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M204" s="43" t="inlineStr">
+        <is>
+          <t>Seismic Charge</t>
+        </is>
+      </c>
+      <c r="N204" s="46" t="n"/>
+      <c r="O204" s="57" t="n"/>
+      <c r="P204" s="57" t="n"/>
+      <c r="Q204" s="57" t="n"/>
+      <c r="R204" s="57" t="n"/>
+      <c r="S204" s="57" t="n"/>
+      <c r="T204" s="57" t="n"/>
+      <c r="U204" s="57" t="n"/>
+      <c r="V204" s="57" t="n"/>
+      <c r="W204" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="X204" s="57" t="n"/>
+      <c r="Y204" s="57" t="n"/>
+      <c r="Z204" s="57" t="n"/>
+      <c r="AA204" s="57" t="n"/>
+      <c r="AB204" s="57" t="n"/>
+      <c r="AC204" s="57" t="n"/>
+      <c r="AD204" s="57" t="n"/>
+      <c r="AE204" s="57" t="n"/>
+      <c r="AF204" s="57" t="n"/>
+      <c r="AG204" s="57" t="n"/>
+      <c r="AH204" s="57" t="n"/>
+      <c r="AI204" s="57" t="n"/>
+      <c r="AJ204" s="57" t="n"/>
+      <c r="AK204" s="57" t="n"/>
+      <c r="AL204" s="57" t="n"/>
+      <c r="AM204" s="57" t="n"/>
+      <c r="AN204" s="57" t="n"/>
+      <c r="AO204" s="57" t="n"/>
+      <c r="AP204" s="57" t="n"/>
+      <c r="AQ204" s="57" t="n"/>
+      <c r="AR204" s="57" t="n"/>
+      <c r="AS204" s="57" t="n"/>
+      <c r="AT204" s="57" t="n"/>
+      <c r="CI204" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ204" s="81" t="inlineStr">
+        <is>
+          <t>Throws dinos 10 studs back</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="43" t="inlineStr">
+        <is>
+          <t>Mortar Pit</t>
+        </is>
+      </c>
+      <c r="B205" s="43" t="inlineStr">
+        <is>
+          <t>Concussive</t>
+        </is>
+      </c>
+      <c r="C205" s="43" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D205" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E205" s="56">
+        <f>E49</f>
+        <v/>
+      </c>
+      <c r="F205" s="56">
+        <f>F49</f>
+        <v/>
+      </c>
+      <c r="G205" s="57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H205" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I205" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J205" s="92" t="n"/>
+      <c r="K205" s="92" t="n"/>
+      <c r="L205" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M205" s="43" t="inlineStr">
+        <is>
+          <t>Rockfall</t>
+        </is>
+      </c>
+      <c r="N205" s="46" t="n"/>
+      <c r="O205" s="57" t="n"/>
+      <c r="P205" s="57" t="n"/>
+      <c r="Q205" s="57" t="n"/>
+      <c r="R205" s="57" t="n"/>
+      <c r="S205" s="57" t="n"/>
+      <c r="T205" s="57" t="n"/>
+      <c r="U205" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V205" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W205" s="57" t="n"/>
+      <c r="X205" s="57" t="n"/>
+      <c r="Y205" s="57" t="n"/>
+      <c r="Z205" s="57" t="n"/>
+      <c r="AA205" s="57" t="n"/>
+      <c r="AB205" s="57" t="n"/>
+      <c r="AC205" s="57" t="n"/>
+      <c r="AD205" s="57" t="n"/>
+      <c r="AE205" s="57" t="n"/>
+      <c r="AF205" s="57" t="n"/>
+      <c r="AG205" s="57" t="n"/>
+      <c r="AH205" s="57" t="n"/>
+      <c r="AI205" s="57" t="n"/>
+      <c r="AJ205" s="57" t="n"/>
+      <c r="AK205" s="57" t="n"/>
+      <c r="AL205" s="57" t="n"/>
+      <c r="AM205" s="57" t="n"/>
+      <c r="AN205" s="57" t="n"/>
+      <c r="AO205" s="57" t="n"/>
+      <c r="AP205" s="57" t="n"/>
+      <c r="AQ205" s="57" t="n"/>
+      <c r="AR205" s="57" t="n"/>
+      <c r="AS205" s="57" t="n"/>
+      <c r="AT205" s="57" t="n"/>
+      <c r="CI205" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ205" s="81" t="inlineStr">
+        <is>
+          <t>A short stun that holds bosses too</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9499,7 +9499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E186"/>
+  <dimension ref="A1:E187"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -12255,6 +12255,21 @@
       <c r="C186" s="109" t="inlineStr">
         <is>
           <t>s a dino hit by a Strips armour shot stays unarmoured (Blind, Perch, Mortar options; PLAN 9c, #290)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Raider sting cooldown (s)</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>3</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>s before the same enemy hunter can be stung again by this side's Raider towers (Sleeper Darts, Barbed Wire; battles only; PLAN 9d, #294)</t>
         </is>
       </c>
     </row>
@@ -13277,7 +13292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK205"/>
+  <dimension ref="A1:CO229"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -13860,6 +13875,26 @@
       <c r="CK4" s="109" t="inlineStr">
         <is>
           <t>PvP effect</t>
+        </is>
+      </c>
+      <c r="CL4" s="81" t="inlineStr">
+        <is>
+          <t>Raider slow %</t>
+        </is>
+      </c>
+      <c r="CM4" s="81" t="inlineStr">
+        <is>
+          <t>Raider slow (s)</t>
+        </is>
+      </c>
+      <c r="CN4" s="81" t="inlineStr">
+        <is>
+          <t>Raider damage</t>
+        </is>
+      </c>
+      <c r="CO4" s="81" t="inlineStr">
+        <is>
+          <t>Bounty cash</t>
         </is>
       </c>
     </row>
@@ -28058,7 +28093,7 @@
       <c r="AR173" s="57" t="n"/>
       <c r="AS173" s="57" t="n"/>
       <c r="AT173" s="57" t="n"/>
-      <c r="BX173" t="n">
+      <c r="BX173" s="81" t="n">
         <v>40</v>
       </c>
       <c r="CI173" s="81" t="inlineStr">
@@ -29279,7 +29314,7 @@
       <c r="AR186" s="57" t="n"/>
       <c r="AS186" s="57" t="n"/>
       <c r="AT186" s="57" t="n"/>
-      <c r="BX186" t="n">
+      <c r="BX186" s="81" t="n">
         <v>25</v>
       </c>
       <c r="CI186" s="81" t="inlineStr">
@@ -29558,7 +29593,7 @@
       <c r="AR189" s="57" t="n"/>
       <c r="AS189" s="57" t="n"/>
       <c r="AT189" s="57" t="n"/>
-      <c r="BX189" t="n">
+      <c r="BX189" s="81" t="n">
         <v>40</v>
       </c>
       <c r="CI189" s="81" t="inlineStr">
@@ -31067,6 +31102,1475 @@
       <c r="CJ205" s="81" t="inlineStr">
         <is>
           <t>A short stun that holds bosses too</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="81" t="inlineStr">
+        <is>
+          <t>Tranq Station</t>
+        </is>
+      </c>
+      <c r="B206" s="81" t="inlineStr">
+        <is>
+          <t>Sedate</t>
+        </is>
+      </c>
+      <c r="C206" s="81" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="D206" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E206" s="81">
+        <f>E53</f>
+        <v/>
+      </c>
+      <c r="F206" s="81">
+        <f>F53</f>
+        <v/>
+      </c>
+      <c r="G206" s="81" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H206" s="81" t="n">
+        <v>1.15132</v>
+      </c>
+      <c r="I206" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L206" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M206" s="81" t="inlineStr">
+        <is>
+          <t>Drowsy Trail</t>
+        </is>
+      </c>
+      <c r="AE206" s="81" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF206" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI206" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ206" s="81" t="inlineStr">
+        <is>
+          <t>Dinos stay slowed 4 s after they leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="81" t="inlineStr">
+        <is>
+          <t>Tranq Station</t>
+        </is>
+      </c>
+      <c r="B207" s="81" t="inlineStr">
+        <is>
+          <t>Sedate</t>
+        </is>
+      </c>
+      <c r="C207" s="81" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="D207" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E207" s="81">
+        <f>E53</f>
+        <v/>
+      </c>
+      <c r="F207" s="81">
+        <f>F53</f>
+        <v/>
+      </c>
+      <c r="G207" s="81" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H207" s="81" t="n">
+        <v>1.15132</v>
+      </c>
+      <c r="I207" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L207" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M207" s="81" t="inlineStr">
+        <is>
+          <t>Sleeper Darts</t>
+        </is>
+      </c>
+      <c r="AE207" s="81" t="n">
+        <v>72</v>
+      </c>
+      <c r="CI207" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ207" s="81" t="inlineStr">
+        <is>
+          <t>Also slows raiders who shoot your towers</t>
+        </is>
+      </c>
+      <c r="CK207" s="81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CL207" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="CM207" s="81" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="81" t="inlineStr">
+        <is>
+          <t>Tranq Station</t>
+        </is>
+      </c>
+      <c r="B208" s="81" t="inlineStr">
+        <is>
+          <t>Sedate</t>
+        </is>
+      </c>
+      <c r="C208" s="81" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="D208" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E208" s="81">
+        <f>E54</f>
+        <v/>
+      </c>
+      <c r="F208" s="81">
+        <f>F54</f>
+        <v/>
+      </c>
+      <c r="G208" s="81" t="n">
+        <v>1.2972</v>
+      </c>
+      <c r="H208" s="81" t="n">
+        <v>1.14857</v>
+      </c>
+      <c r="I208" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L208" s="81" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M208" s="81" t="inlineStr">
+        <is>
+          <t>Fog Bank</t>
+        </is>
+      </c>
+      <c r="AE208" s="81" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF208" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI208" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ208" s="81" t="inlineStr">
+        <is>
+          <t>A huge sleepy cloud slows a much wider ring</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="81" t="inlineStr">
+        <is>
+          <t>Tranq Station</t>
+        </is>
+      </c>
+      <c r="B209" s="81" t="inlineStr">
+        <is>
+          <t>Sedate</t>
+        </is>
+      </c>
+      <c r="C209" s="81" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="D209" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E209" s="81">
+        <f>E54</f>
+        <v/>
+      </c>
+      <c r="F209" s="81">
+        <f>F54</f>
+        <v/>
+      </c>
+      <c r="G209" s="81" t="n">
+        <v>1.2972</v>
+      </c>
+      <c r="H209" s="81" t="n">
+        <v>1.14857</v>
+      </c>
+      <c r="I209" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L209" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" s="81" t="inlineStr">
+        <is>
+          <t>Long Nap</t>
+        </is>
+      </c>
+      <c r="AE209" s="81" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF209" s="81" t="n">
+        <v>7</v>
+      </c>
+      <c r="CI209" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ209" s="81" t="inlineStr">
+        <is>
+          <t>Dinos stay slowed 7 s after they leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="81" t="inlineStr">
+        <is>
+          <t>Tranq Station</t>
+        </is>
+      </c>
+      <c r="B210" s="81" t="inlineStr">
+        <is>
+          <t>Knockout</t>
+        </is>
+      </c>
+      <c r="C210" s="81" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="D210" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E210" s="81">
+        <f>E58</f>
+        <v/>
+      </c>
+      <c r="F210" s="81">
+        <f>F58</f>
+        <v/>
+      </c>
+      <c r="G210" s="81" t="n">
+        <v>1.34959</v>
+      </c>
+      <c r="H210" s="81" t="n">
+        <v>1.42308</v>
+      </c>
+      <c r="I210" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L210" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M210" s="81" t="inlineStr">
+        <is>
+          <t>Long Sleep</t>
+        </is>
+      </c>
+      <c r="AI210" s="81" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ210" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI210" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ210" s="81" t="inlineStr">
+        <is>
+          <t>Knockouts hold dinos 1.8 s instead of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="81" t="inlineStr">
+        <is>
+          <t>Tranq Station</t>
+        </is>
+      </c>
+      <c r="B211" s="81" t="inlineStr">
+        <is>
+          <t>Knockout</t>
+        </is>
+      </c>
+      <c r="C211" s="81" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="D211" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E211" s="81">
+        <f>E58</f>
+        <v/>
+      </c>
+      <c r="F211" s="81">
+        <f>F58</f>
+        <v/>
+      </c>
+      <c r="G211" s="81" t="n">
+        <v>1.34959</v>
+      </c>
+      <c r="H211" s="81" t="n">
+        <v>1.42308</v>
+      </c>
+      <c r="I211" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L211" s="81" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M211" s="81" t="inlineStr">
+        <is>
+          <t>Knockout Ring</t>
+        </is>
+      </c>
+      <c r="AH211" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ211" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI211" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ211" s="81" t="inlineStr">
+        <is>
+          <t>Knocks out dinos in a much wider ring</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="81" t="inlineStr">
+        <is>
+          <t>Tranq Station</t>
+        </is>
+      </c>
+      <c r="B212" s="81" t="inlineStr">
+        <is>
+          <t>Knockout</t>
+        </is>
+      </c>
+      <c r="C212" s="81" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="D212" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E212" s="81">
+        <f>E59</f>
+        <v/>
+      </c>
+      <c r="F212" s="81">
+        <f>F59</f>
+        <v/>
+      </c>
+      <c r="G212" s="81" t="n">
+        <v>1.3494</v>
+      </c>
+      <c r="H212" s="81" t="n">
+        <v>1.41769</v>
+      </c>
+      <c r="I212" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L212" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" s="81" t="inlineStr">
+        <is>
+          <t>Snooze Alarm</t>
+        </is>
+      </c>
+      <c r="AH212" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI212" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ212" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI212" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ212" s="81" t="inlineStr">
+        <is>
+          <t>Knocks out every dino in range every 4 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="81" t="inlineStr">
+        <is>
+          <t>Tranq Station</t>
+        </is>
+      </c>
+      <c r="B213" s="81" t="inlineStr">
+        <is>
+          <t>Knockout</t>
+        </is>
+      </c>
+      <c r="C213" s="81" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="D213" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E213" s="81">
+        <f>E59</f>
+        <v/>
+      </c>
+      <c r="F213" s="81">
+        <f>F59</f>
+        <v/>
+      </c>
+      <c r="G213" s="81" t="n">
+        <v>1.3494</v>
+      </c>
+      <c r="H213" s="81" t="n">
+        <v>1.41769</v>
+      </c>
+      <c r="I213" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L213" s="81" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M213" s="81" t="inlineStr">
+        <is>
+          <t>Sleep Wave</t>
+        </is>
+      </c>
+      <c r="AI213" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ213" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI213" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ213" s="81" t="inlineStr">
+        <is>
+          <t>A giant knockout ring</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="81" t="inlineStr">
+        <is>
+          <t>Tranq Station</t>
+        </is>
+      </c>
+      <c r="B214" s="81" t="inlineStr">
+        <is>
+          <t>Weak Spot</t>
+        </is>
+      </c>
+      <c r="C214" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D214" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E214" s="81">
+        <f>E63</f>
+        <v/>
+      </c>
+      <c r="F214" s="81">
+        <f>F63</f>
+        <v/>
+      </c>
+      <c r="G214" s="81" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H214" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I214" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L214" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" s="81" t="inlineStr">
+        <is>
+          <t>Pack Instinct</t>
+        </is>
+      </c>
+      <c r="AB214" s="81" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL214" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="CI214" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ214" s="81" t="inlineStr">
+        <is>
+          <t>Towers in range fire 20% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="81" t="inlineStr">
+        <is>
+          <t>Tranq Station</t>
+        </is>
+      </c>
+      <c r="B215" s="81" t="inlineStr">
+        <is>
+          <t>Weak Spot</t>
+        </is>
+      </c>
+      <c r="C215" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D215" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E215" s="81">
+        <f>E63</f>
+        <v/>
+      </c>
+      <c r="F215" s="81">
+        <f>F63</f>
+        <v/>
+      </c>
+      <c r="G215" s="81" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H215" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I215" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" s="81" t="inlineStr">
+        <is>
+          <t>Big Game Weakness</t>
+        </is>
+      </c>
+      <c r="AL215" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX215" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="CI215" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ215" s="81" t="inlineStr">
+        <is>
+          <t>Bosses in range take +40% from everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="81" t="inlineStr">
+        <is>
+          <t>Tranq Station</t>
+        </is>
+      </c>
+      <c r="B216" s="81" t="inlineStr">
+        <is>
+          <t>Weak Spot</t>
+        </is>
+      </c>
+      <c r="C216" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D216" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E216" s="81">
+        <f>E64</f>
+        <v/>
+      </c>
+      <c r="F216" s="81">
+        <f>F64</f>
+        <v/>
+      </c>
+      <c r="G216" s="81" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H216" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I216" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L216" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" s="81" t="inlineStr">
+        <is>
+          <t>Feeding Frenzy</t>
+        </is>
+      </c>
+      <c r="AB216" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AL216" s="81" t="n">
+        <v>60</v>
+      </c>
+      <c r="CI216" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ216" s="81" t="inlineStr">
+        <is>
+          <t>Towers in range fire 35% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="81" t="inlineStr">
+        <is>
+          <t>Tranq Station</t>
+        </is>
+      </c>
+      <c r="B217" s="81" t="inlineStr">
+        <is>
+          <t>Weak Spot</t>
+        </is>
+      </c>
+      <c r="C217" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D217" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E217" s="81">
+        <f>E64</f>
+        <v/>
+      </c>
+      <c r="F217" s="81">
+        <f>F64</f>
+        <v/>
+      </c>
+      <c r="G217" s="81" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H217" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I217" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L217" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" s="81" t="inlineStr">
+        <is>
+          <t>Killing Ground</t>
+        </is>
+      </c>
+      <c r="AL217" s="81" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX217" s="81" t="n">
+        <v>75</v>
+      </c>
+      <c r="CI217" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ217" s="81" t="inlineStr">
+        <is>
+          <t>Bosses in range take +75% from everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="81" t="inlineStr">
+        <is>
+          <t>Supply Camp</t>
+        </is>
+      </c>
+      <c r="B218" s="81" t="inlineStr">
+        <is>
+          <t>Yield</t>
+        </is>
+      </c>
+      <c r="C218" s="81" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D218" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E218" s="81">
+        <f>E68</f>
+        <v/>
+      </c>
+      <c r="F218" s="81">
+        <f>F68</f>
+        <v/>
+      </c>
+      <c r="G218" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H218" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I218" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L218" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M218" s="81" t="inlineStr">
+        <is>
+          <t>Savings Jar</t>
+        </is>
+      </c>
+      <c r="AN218" s="81" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO218" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP218" s="81" t="n">
+        <v>250</v>
+      </c>
+      <c r="CI218" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ218" s="81" t="inlineStr">
+        <is>
+          <t>Less income, but 3% interest on banked cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="81" t="inlineStr">
+        <is>
+          <t>Supply Camp</t>
+        </is>
+      </c>
+      <c r="B219" s="81" t="inlineStr">
+        <is>
+          <t>Yield</t>
+        </is>
+      </c>
+      <c r="C219" s="81" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D219" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E219" s="81">
+        <f>E68</f>
+        <v/>
+      </c>
+      <c r="F219" s="81">
+        <f>F68</f>
+        <v/>
+      </c>
+      <c r="G219" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H219" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L219" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M219" s="81" t="inlineStr">
+        <is>
+          <t>Bounty Board</t>
+        </is>
+      </c>
+      <c r="AN219" s="81" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CI219" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ219" s="81" t="inlineStr">
+        <is>
+          <t>+8 cash for each dino taken down in its range</t>
+        </is>
+      </c>
+      <c r="CO219" s="81" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="81" t="inlineStr">
+        <is>
+          <t>Supply Camp</t>
+        </is>
+      </c>
+      <c r="B220" s="81" t="inlineStr">
+        <is>
+          <t>Yield</t>
+        </is>
+      </c>
+      <c r="C220" s="81" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D220" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E220" s="81">
+        <f>E69</f>
+        <v/>
+      </c>
+      <c r="F220" s="81">
+        <f>F69</f>
+        <v/>
+      </c>
+      <c r="G220" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H220" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I220" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L220" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" s="81" t="inlineStr">
+        <is>
+          <t>Gold Reserve</t>
+        </is>
+      </c>
+      <c r="AN220" s="81" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO220" s="81" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP220" s="81" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CI220" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ220" s="81" t="inlineStr">
+        <is>
+          <t>Big interest: 8% on banked cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="81" t="inlineStr">
+        <is>
+          <t>Supply Camp</t>
+        </is>
+      </c>
+      <c r="B221" s="81" t="inlineStr">
+        <is>
+          <t>Yield</t>
+        </is>
+      </c>
+      <c r="C221" s="81" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D221" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E221" s="81">
+        <f>E69</f>
+        <v/>
+      </c>
+      <c r="F221" s="81">
+        <f>F69</f>
+        <v/>
+      </c>
+      <c r="G221" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L221" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M221" s="81" t="inlineStr">
+        <is>
+          <t>Bounty Hall</t>
+        </is>
+      </c>
+      <c r="AN221" s="81" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CI221" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ221" s="81" t="inlineStr">
+        <is>
+          <t>+25 cash for each dino taken down in its range</t>
+        </is>
+      </c>
+      <c r="CO221" s="81" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="81" t="inlineStr">
+        <is>
+          <t>Supply Camp</t>
+        </is>
+      </c>
+      <c r="B222" s="81" t="inlineStr">
+        <is>
+          <t>Airdrop</t>
+        </is>
+      </c>
+      <c r="C222" s="81" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D222" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E222" s="81">
+        <f>E73</f>
+        <v/>
+      </c>
+      <c r="F222" s="81">
+        <f>F73</f>
+        <v/>
+      </c>
+      <c r="G222" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H222" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I222" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L222" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M222" s="81" t="inlineStr">
+        <is>
+          <t>Heavy Crates</t>
+        </is>
+      </c>
+      <c r="AR222" s="81" t="n">
+        <v>790</v>
+      </c>
+      <c r="CI222" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ222" s="81" t="inlineStr">
+        <is>
+          <t>Two crates a round, worth more each</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="81" t="inlineStr">
+        <is>
+          <t>Supply Camp</t>
+        </is>
+      </c>
+      <c r="B223" s="81" t="inlineStr">
+        <is>
+          <t>Airdrop</t>
+        </is>
+      </c>
+      <c r="C223" s="81" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D223" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E223" s="81">
+        <f>E73</f>
+        <v/>
+      </c>
+      <c r="F223" s="81">
+        <f>F73</f>
+        <v/>
+      </c>
+      <c r="G223" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H223" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I223" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L223" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M223" s="81" t="inlineStr">
+        <is>
+          <t>Extra Drop</t>
+        </is>
+      </c>
+      <c r="AQ223" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI223" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ223" s="81" t="inlineStr">
+        <is>
+          <t>Four crates a round</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="81" t="inlineStr">
+        <is>
+          <t>Supply Camp</t>
+        </is>
+      </c>
+      <c r="B224" s="81" t="inlineStr">
+        <is>
+          <t>Airdrop</t>
+        </is>
+      </c>
+      <c r="C224" s="81" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D224" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E224" s="81">
+        <f>E74</f>
+        <v/>
+      </c>
+      <c r="F224" s="81">
+        <f>F74</f>
+        <v/>
+      </c>
+      <c r="G224" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H224" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I224" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L224" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M224" s="81" t="inlineStr">
+        <is>
+          <t>Supply Fleet</t>
+        </is>
+      </c>
+      <c r="AQ224" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR224" s="81" t="n">
+        <v>790</v>
+      </c>
+      <c r="CI224" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ224" s="81" t="inlineStr">
+        <is>
+          <t>Five crates a round</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="81" t="inlineStr">
+        <is>
+          <t>Supply Camp</t>
+        </is>
+      </c>
+      <c r="B225" s="81" t="inlineStr">
+        <is>
+          <t>Airdrop</t>
+        </is>
+      </c>
+      <c r="C225" s="81" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D225" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E225" s="81">
+        <f>E74</f>
+        <v/>
+      </c>
+      <c r="F225" s="81">
+        <f>F74</f>
+        <v/>
+      </c>
+      <c r="G225" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H225" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I225" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L225" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M225" s="81" t="inlineStr">
+        <is>
+          <t>Gold Crates</t>
+        </is>
+      </c>
+      <c r="AQ225" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR225" s="81" t="n">
+        <v>900</v>
+      </c>
+      <c r="CI225" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ225" s="81" t="inlineStr">
+        <is>
+          <t>Four crates a round, worth 900 each</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="81" t="inlineStr">
+        <is>
+          <t>Supply Camp</t>
+        </is>
+      </c>
+      <c r="B226" s="81" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="C226" s="81" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D226" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E226" s="81">
+        <f>E78</f>
+        <v/>
+      </c>
+      <c r="F226" s="81">
+        <f>F78</f>
+        <v/>
+      </c>
+      <c r="G226" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H226" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I226" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L226" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M226" s="81" t="inlineStr">
+        <is>
+          <t>Bulk Buyer</t>
+        </is>
+      </c>
+      <c r="AS226" s="81" t="n">
+        <v>18</v>
+      </c>
+      <c r="CI226" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ226" s="81" t="inlineStr">
+        <is>
+          <t>Upgrades in range cost 18% less</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="81" t="inlineStr">
+        <is>
+          <t>Supply Camp</t>
+        </is>
+      </c>
+      <c r="B227" s="81" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="C227" s="81" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D227" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E227" s="81">
+        <f>E78</f>
+        <v/>
+      </c>
+      <c r="F227" s="81">
+        <f>F78</f>
+        <v/>
+      </c>
+      <c r="G227" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H227" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I227" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L227" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M227" s="81" t="inlineStr">
+        <is>
+          <t>Scrap Dealer</t>
+        </is>
+      </c>
+      <c r="AT227" s="81" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="CI227" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ227" s="81" t="inlineStr">
+        <is>
+          <t>Towers in range sell for 97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="81" t="inlineStr">
+        <is>
+          <t>Supply Camp</t>
+        </is>
+      </c>
+      <c r="B228" s="81" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="C228" s="81" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D228" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E228" s="81">
+        <f>E79</f>
+        <v/>
+      </c>
+      <c r="F228" s="81">
+        <f>F79</f>
+        <v/>
+      </c>
+      <c r="G228" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H228" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I228" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L228" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M228" s="81" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="AS228" s="81" t="n">
+        <v>32</v>
+      </c>
+      <c r="CI228" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ228" s="81" t="inlineStr">
+        <is>
+          <t>Upgrades in range cost 32% less</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="81" t="inlineStr">
+        <is>
+          <t>Supply Camp</t>
+        </is>
+      </c>
+      <c r="B229" s="81" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="C229" s="81" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D229" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E229" s="81">
+        <f>E79</f>
+        <v/>
+      </c>
+      <c r="F229" s="81">
+        <f>F79</f>
+        <v/>
+      </c>
+      <c r="G229" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H229" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L229" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M229" s="81" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="AB229" s="81" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS229" s="81" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT229" s="81" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CI229" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ229" s="81" t="inlineStr">
+        <is>
+          <t>Towers in range fire 20% faster, cost 15% less</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -12259,15 +12259,15 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="81" t="inlineStr">
         <is>
           <t>Raider sting cooldown (s)</t>
         </is>
       </c>
-      <c r="B187" t="n">
+      <c r="B187" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="C187" t="inlineStr">
+      <c r="C187" s="81" t="inlineStr">
         <is>
           <t>s before the same enemy hunter can be stung again by this side's Raider towers (Sleeper Darts, Barbed Wire; battles only; PLAN 9d, #294)</t>
         </is>
@@ -13292,7 +13292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO229"/>
+  <dimension ref="A1:CQ253"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -13895,6 +13895,16 @@
       <c r="CO4" s="81" t="inlineStr">
         <is>
           <t>Bounty cash</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>Biter slow %</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>Biter slow (s)</t>
         </is>
       </c>
     </row>
@@ -32571,6 +32581,1454 @@
       <c r="CJ229" s="81" t="inlineStr">
         <is>
           <t>Towers in range fire 20% faster, cost 15% less</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>healing</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>4</v>
+      </c>
+      <c r="E230">
+        <f>E98</f>
+        <v/>
+      </c>
+      <c r="F230">
+        <f>F98</f>
+        <v/>
+      </c>
+      <c r="G230" t="n">
+        <v>1</v>
+      </c>
+      <c r="H230" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" t="n">
+        <v>1</v>
+      </c>
+      <c r="L230" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Quick Stitch</t>
+        </is>
+      </c>
+      <c r="BD230" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI230" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ230" t="inlineStr">
+        <is>
+          <t>Trampled towers stand up twice as fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>healing</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>4</v>
+      </c>
+      <c r="E231">
+        <f>E98</f>
+        <v/>
+      </c>
+      <c r="F231">
+        <f>F98</f>
+        <v/>
+      </c>
+      <c r="G231" t="n">
+        <v>1</v>
+      </c>
+      <c r="H231" t="n">
+        <v>1</v>
+      </c>
+      <c r="I231" t="n">
+        <v>1</v>
+      </c>
+      <c r="L231" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Big Tent</t>
+        </is>
+      </c>
+      <c r="CI231" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ231" t="inlineStr">
+        <is>
+          <t>Heals towers in a wider ring</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>healing</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>5</v>
+      </c>
+      <c r="E232">
+        <f>E99</f>
+        <v/>
+      </c>
+      <c r="F232">
+        <f>F99</f>
+        <v/>
+      </c>
+      <c r="G232" t="n">
+        <v>1</v>
+      </c>
+      <c r="H232" t="n">
+        <v>1</v>
+      </c>
+      <c r="I232" t="n">
+        <v>1</v>
+      </c>
+      <c r="L232" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>Field Ward</t>
+        </is>
+      </c>
+      <c r="BB232" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CI232" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ232" t="inlineStr">
+        <is>
+          <t>Heals a huge ring of towers</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>healing</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>5</v>
+      </c>
+      <c r="E233">
+        <f>E99</f>
+        <v/>
+      </c>
+      <c r="F233">
+        <f>F99</f>
+        <v/>
+      </c>
+      <c r="G233" t="n">
+        <v>1</v>
+      </c>
+      <c r="H233" t="n">
+        <v>1</v>
+      </c>
+      <c r="I233" t="n">
+        <v>1</v>
+      </c>
+      <c r="L233" t="n">
+        <v>1</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Rapid Recovery</t>
+        </is>
+      </c>
+      <c r="BB233" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BD233" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI233" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ233" t="inlineStr">
+        <is>
+          <t>Trampled towers jump back up 4x as fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Rescue</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>4</v>
+      </c>
+      <c r="E234">
+        <f>E103</f>
+        <v/>
+      </c>
+      <c r="F234">
+        <f>F103</f>
+        <v/>
+      </c>
+      <c r="G234" t="n">
+        <v>1</v>
+      </c>
+      <c r="H234" t="n">
+        <v>1</v>
+      </c>
+      <c r="I234" t="n">
+        <v>1</v>
+      </c>
+      <c r="L234" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Long Whistle</t>
+        </is>
+      </c>
+      <c r="BE234" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI234" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ234" t="inlineStr">
+        <is>
+          <t>Kits reach hunters in a much wider ring</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Rescue</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>4</v>
+      </c>
+      <c r="E235">
+        <f>E103</f>
+        <v/>
+      </c>
+      <c r="F235">
+        <f>F103</f>
+        <v/>
+      </c>
+      <c r="G235" t="n">
+        <v>1</v>
+      </c>
+      <c r="H235" t="n">
+        <v>1</v>
+      </c>
+      <c r="I235" t="n">
+        <v>1</v>
+      </c>
+      <c r="L235" t="n">
+        <v>1</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Kit Bags</t>
+        </is>
+      </c>
+      <c r="BE235" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI235" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ235" t="inlineStr">
+        <is>
+          <t>Four med kits land each round</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Rescue</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>5</v>
+      </c>
+      <c r="E236">
+        <f>E104</f>
+        <v/>
+      </c>
+      <c r="F236">
+        <f>F104</f>
+        <v/>
+      </c>
+      <c r="G236" t="n">
+        <v>1</v>
+      </c>
+      <c r="H236" t="n">
+        <v>1</v>
+      </c>
+      <c r="I236" t="n">
+        <v>1</v>
+      </c>
+      <c r="L236" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Pack Train</t>
+        </is>
+      </c>
+      <c r="BE236" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF236" t="n">
+        <v>50</v>
+      </c>
+      <c r="CI236" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ236" t="inlineStr">
+        <is>
+          <t>Five med kits a round, 50 each</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Rescue</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>5</v>
+      </c>
+      <c r="E237">
+        <f>E104</f>
+        <v/>
+      </c>
+      <c r="F237">
+        <f>F104</f>
+        <v/>
+      </c>
+      <c r="G237" t="n">
+        <v>1</v>
+      </c>
+      <c r="H237" t="n">
+        <v>1</v>
+      </c>
+      <c r="I237" t="n">
+        <v>1</v>
+      </c>
+      <c r="L237" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>Medevac</t>
+        </is>
+      </c>
+      <c r="BF237" t="n">
+        <v>45</v>
+      </c>
+      <c r="BG237" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CI237" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ237" t="inlineStr">
+        <is>
+          <t>Downed hunters come back 3x as fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Tonic</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>tougher towers</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>4</v>
+      </c>
+      <c r="E238">
+        <f>E108</f>
+        <v/>
+      </c>
+      <c r="F238">
+        <f>F108</f>
+        <v/>
+      </c>
+      <c r="G238" t="n">
+        <v>1</v>
+      </c>
+      <c r="H238" t="n">
+        <v>1</v>
+      </c>
+      <c r="I238" t="n">
+        <v>1</v>
+      </c>
+      <c r="L238" t="n">
+        <v>1</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Hot Coffee</t>
+        </is>
+      </c>
+      <c r="AB238" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH238" t="n">
+        <v>25</v>
+      </c>
+      <c r="CI238" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ238" t="inlineStr">
+        <is>
+          <t>Towers in range fire 18% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Tonic</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>tougher towers</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>4</v>
+      </c>
+      <c r="E239">
+        <f>E108</f>
+        <v/>
+      </c>
+      <c r="F239">
+        <f>F108</f>
+        <v/>
+      </c>
+      <c r="G239" t="n">
+        <v>1</v>
+      </c>
+      <c r="H239" t="n">
+        <v>1</v>
+      </c>
+      <c r="I239" t="n">
+        <v>1</v>
+      </c>
+      <c r="L239" t="n">
+        <v>1</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>Bitter Tonic</t>
+        </is>
+      </c>
+      <c r="BH239" t="n">
+        <v>25</v>
+      </c>
+      <c r="CI239" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ239" t="inlineStr">
+        <is>
+          <t>Dinos that bite towers in range get slowed</t>
+        </is>
+      </c>
+      <c r="CP239" t="n">
+        <v>25</v>
+      </c>
+      <c r="CQ239" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Tonic</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>tougher towers</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>5</v>
+      </c>
+      <c r="E240">
+        <f>E109</f>
+        <v/>
+      </c>
+      <c r="F240">
+        <f>F109</f>
+        <v/>
+      </c>
+      <c r="G240" t="n">
+        <v>1</v>
+      </c>
+      <c r="H240" t="n">
+        <v>1</v>
+      </c>
+      <c r="I240" t="n">
+        <v>1</v>
+      </c>
+      <c r="L240" t="n">
+        <v>1</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>Adrenaline</t>
+        </is>
+      </c>
+      <c r="AB240" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH240" t="n">
+        <v>40</v>
+      </c>
+      <c r="CI240" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ240" t="inlineStr">
+        <is>
+          <t>Towers in range fire 30% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Tonic</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>tougher towers</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>5</v>
+      </c>
+      <c r="E241">
+        <f>E109</f>
+        <v/>
+      </c>
+      <c r="F241">
+        <f>F109</f>
+        <v/>
+      </c>
+      <c r="G241" t="n">
+        <v>1</v>
+      </c>
+      <c r="H241" t="n">
+        <v>1</v>
+      </c>
+      <c r="I241" t="n">
+        <v>1</v>
+      </c>
+      <c r="L241" t="n">
+        <v>1</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Bitter Brew</t>
+        </is>
+      </c>
+      <c r="BH241" t="n">
+        <v>45</v>
+      </c>
+      <c r="CI241" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ241" t="inlineStr">
+        <is>
+          <t>Biters slowed 30% for 3 s; towers +45% HP</t>
+        </is>
+      </c>
+      <c r="CP241" t="n">
+        <v>30</v>
+      </c>
+      <c r="CQ241" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Plating</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>resistance</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>4</v>
+      </c>
+      <c r="E242">
+        <f>E83</f>
+        <v/>
+      </c>
+      <c r="F242">
+        <f>F83</f>
+        <v/>
+      </c>
+      <c r="G242" t="n">
+        <v>1</v>
+      </c>
+      <c r="H242" t="n">
+        <v>1</v>
+      </c>
+      <c r="I242" t="n">
+        <v>1</v>
+      </c>
+      <c r="L242" t="n">
+        <v>1</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Spiked Walls</t>
+        </is>
+      </c>
+      <c r="AU242" t="n">
+        <v>30</v>
+      </c>
+      <c r="AV242" t="n">
+        <v>10</v>
+      </c>
+      <c r="CI242" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ242" t="inlineStr">
+        <is>
+          <t>Dinos that bite take 10 damage back</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Plating</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>resistance</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>4</v>
+      </c>
+      <c r="E243">
+        <f>E83</f>
+        <v/>
+      </c>
+      <c r="F243">
+        <f>F83</f>
+        <v/>
+      </c>
+      <c r="G243" t="n">
+        <v>1</v>
+      </c>
+      <c r="H243" t="n">
+        <v>1</v>
+      </c>
+      <c r="I243" t="n">
+        <v>1</v>
+      </c>
+      <c r="L243" t="n">
+        <v>1</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Barbed Wire</t>
+        </is>
+      </c>
+      <c r="AU243" t="n">
+        <v>32</v>
+      </c>
+      <c r="CI243" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ243" t="inlineStr">
+        <is>
+          <t>Stings and slows raiders who shoot towers here</t>
+        </is>
+      </c>
+      <c r="CK243" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CL243" t="n">
+        <v>20</v>
+      </c>
+      <c r="CM243" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN243" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Plating</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>resistance</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>5</v>
+      </c>
+      <c r="E244">
+        <f>E84</f>
+        <v/>
+      </c>
+      <c r="F244">
+        <f>F84</f>
+        <v/>
+      </c>
+      <c r="G244" t="n">
+        <v>1</v>
+      </c>
+      <c r="H244" t="n">
+        <v>1</v>
+      </c>
+      <c r="I244" t="n">
+        <v>1</v>
+      </c>
+      <c r="L244" t="n">
+        <v>1</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>Iron Fortress</t>
+        </is>
+      </c>
+      <c r="AU244" t="n">
+        <v>55</v>
+      </c>
+      <c r="CI244" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ244" t="inlineStr">
+        <is>
+          <t>Towers in range take 55% less damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Plating</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>resistance</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>5</v>
+      </c>
+      <c r="E245">
+        <f>E84</f>
+        <v/>
+      </c>
+      <c r="F245">
+        <f>F84</f>
+        <v/>
+      </c>
+      <c r="G245" t="n">
+        <v>1</v>
+      </c>
+      <c r="H245" t="n">
+        <v>1</v>
+      </c>
+      <c r="I245" t="n">
+        <v>1</v>
+      </c>
+      <c r="L245" t="n">
+        <v>1</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Spike Fortress</t>
+        </is>
+      </c>
+      <c r="AU245" t="n">
+        <v>40</v>
+      </c>
+      <c r="AV245" t="n">
+        <v>18</v>
+      </c>
+      <c r="CI245" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ245" t="inlineStr">
+        <is>
+          <t>Biters take 18 damage back</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Gunsmith</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>4</v>
+      </c>
+      <c r="E246">
+        <f>E88</f>
+        <v/>
+      </c>
+      <c r="F246">
+        <f>F88</f>
+        <v/>
+      </c>
+      <c r="G246" t="n">
+        <v>1</v>
+      </c>
+      <c r="H246" t="n">
+        <v>1</v>
+      </c>
+      <c r="I246" t="n">
+        <v>1</v>
+      </c>
+      <c r="L246" t="n">
+        <v>1</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Rapid Feed</t>
+        </is>
+      </c>
+      <c r="AB246" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>15</v>
+      </c>
+      <c r="CI246" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ246" t="inlineStr">
+        <is>
+          <t>Towers in range fire 20% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Gunsmith</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>4</v>
+      </c>
+      <c r="E247">
+        <f>E88</f>
+        <v/>
+      </c>
+      <c r="F247">
+        <f>F88</f>
+        <v/>
+      </c>
+      <c r="G247" t="n">
+        <v>1</v>
+      </c>
+      <c r="H247" t="n">
+        <v>1</v>
+      </c>
+      <c r="I247" t="n">
+        <v>1</v>
+      </c>
+      <c r="L247" t="n">
+        <v>1</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Heavy Loads</t>
+        </is>
+      </c>
+      <c r="AB247" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>30</v>
+      </c>
+      <c r="CI247" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ247" t="inlineStr">
+        <is>
+          <t>Towers in range hit 30% harder</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Gunsmith</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>5</v>
+      </c>
+      <c r="E248">
+        <f>E89</f>
+        <v/>
+      </c>
+      <c r="F248">
+        <f>F89</f>
+        <v/>
+      </c>
+      <c r="G248" t="n">
+        <v>1</v>
+      </c>
+      <c r="H248" t="n">
+        <v>1</v>
+      </c>
+      <c r="I248" t="n">
+        <v>1</v>
+      </c>
+      <c r="L248" t="n">
+        <v>1</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>Machine Shop</t>
+        </is>
+      </c>
+      <c r="AB248" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>25</v>
+      </c>
+      <c r="CI248" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ248" t="inlineStr">
+        <is>
+          <t>Towers in range fire 30% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Gunsmith</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>5</v>
+      </c>
+      <c r="E249">
+        <f>E89</f>
+        <v/>
+      </c>
+      <c r="F249">
+        <f>F89</f>
+        <v/>
+      </c>
+      <c r="G249" t="n">
+        <v>1</v>
+      </c>
+      <c r="H249" t="n">
+        <v>1</v>
+      </c>
+      <c r="I249" t="n">
+        <v>1</v>
+      </c>
+      <c r="L249" t="n">
+        <v>1</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Magnum Loads</t>
+        </is>
+      </c>
+      <c r="AB249" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>40</v>
+      </c>
+      <c r="CI249" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ249" t="inlineStr">
+        <is>
+          <t>Towers in range hit 40% harder</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Outfitter</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>4</v>
+      </c>
+      <c r="E250">
+        <f>E93</f>
+        <v/>
+      </c>
+      <c r="F250">
+        <f>F93</f>
+        <v/>
+      </c>
+      <c r="G250" t="n">
+        <v>1</v>
+      </c>
+      <c r="H250" t="n">
+        <v>1</v>
+      </c>
+      <c r="I250" t="n">
+        <v>1</v>
+      </c>
+      <c r="L250" t="n">
+        <v>1</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Speed Loader</t>
+        </is>
+      </c>
+      <c r="AY250" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CI250" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ250" t="inlineStr">
+        <is>
+          <t>Hunters in range reload 30% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Outfitter</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>4</v>
+      </c>
+      <c r="E251">
+        <f>E93</f>
+        <v/>
+      </c>
+      <c r="F251">
+        <f>F93</f>
+        <v/>
+      </c>
+      <c r="G251" t="n">
+        <v>1</v>
+      </c>
+      <c r="H251" t="n">
+        <v>1</v>
+      </c>
+      <c r="I251" t="n">
+        <v>1</v>
+      </c>
+      <c r="L251" t="n">
+        <v>1</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>Gun Braces</t>
+        </is>
+      </c>
+      <c r="AX251" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CI251" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ251" t="inlineStr">
+        <is>
+          <t>Hunters in range have 30% less recoil</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Outfitter</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>5</v>
+      </c>
+      <c r="E252">
+        <f>E94</f>
+        <v/>
+      </c>
+      <c r="F252">
+        <f>F94</f>
+        <v/>
+      </c>
+      <c r="G252" t="n">
+        <v>1</v>
+      </c>
+      <c r="H252" t="n">
+        <v>1</v>
+      </c>
+      <c r="I252" t="n">
+        <v>1</v>
+      </c>
+      <c r="L252" t="n">
+        <v>1.15385</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>Gun Oil</t>
+        </is>
+      </c>
+      <c r="AY252" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CI252" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ252" t="inlineStr">
+        <is>
+          <t>Wider ring; hunters in it reload 20% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Armory</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Outfitter</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>hunters</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>5</v>
+      </c>
+      <c r="E253">
+        <f>E94</f>
+        <v/>
+      </c>
+      <c r="F253">
+        <f>F94</f>
+        <v/>
+      </c>
+      <c r="G253" t="n">
+        <v>1</v>
+      </c>
+      <c r="H253" t="n">
+        <v>1</v>
+      </c>
+      <c r="I253" t="n">
+        <v>1</v>
+      </c>
+      <c r="L253" t="n">
+        <v>1.15385</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>Steady Aim</t>
+        </is>
+      </c>
+      <c r="AZ253" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CI253" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ253" t="inlineStr">
+        <is>
+          <t>Wider ring; hunters in it aim 20% tighter</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9499,7 +9499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E187"/>
+  <dimension ref="A1:E188"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -12270,6 +12270,21 @@
       <c r="C187" s="81" t="inlineStr">
         <is>
           <t>s before the same enemy hunter can be stung again by this side's Raider towers (Sleeper Darts, Barbed Wire; battles only; PLAN 9d, #294)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="81" t="inlineStr">
+        <is>
+          <t>Chain stun cap (s)</t>
+        </is>
+      </c>
+      <c r="B188" s="81" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C188" s="81" t="inlineStr">
+        <is>
+          <t>s: an arc's stun on a Chain effects coil (Supercell, Superconductor) is capped at this; the first target keeps its full stun (PLAN 9e, #297)</t>
         </is>
       </c>
     </row>
@@ -13292,7 +13307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ253"/>
+  <dimension ref="A1:CU277"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -13897,14 +13912,34 @@
           <t>Bounty cash</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CP4" s="81" t="inlineStr">
         <is>
           <t>Biter slow %</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CQ4" s="81" t="inlineStr">
         <is>
           <t>Biter slow (s)</t>
+        </is>
+      </c>
+      <c r="CR4" s="81" t="inlineStr">
+        <is>
+          <t>Field strike every (s)</t>
+        </is>
+      </c>
+      <c r="CS4" s="81" t="inlineStr">
+        <is>
+          <t>Field strike x</t>
+        </is>
+      </c>
+      <c r="CT4" s="81" t="inlineStr">
+        <is>
+          <t>Chain effects</t>
+        </is>
+      </c>
+      <c r="CU4" s="81" t="inlineStr">
+        <is>
+          <t>Targets biggest</t>
         </is>
       </c>
     </row>
@@ -32585,1450 +32620,2916 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
+      <c r="A230" s="81" t="inlineStr">
         <is>
           <t>Field Hospital</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B230" s="81" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
+      <c r="C230" s="81" t="inlineStr">
         <is>
           <t>healing</t>
         </is>
       </c>
-      <c r="D230" t="n">
+      <c r="D230" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E230">
+      <c r="E230" s="81">
         <f>E98</f>
         <v/>
       </c>
-      <c r="F230">
+      <c r="F230" s="81">
         <f>F98</f>
         <v/>
       </c>
-      <c r="G230" t="n">
-        <v>1</v>
-      </c>
-      <c r="H230" t="n">
-        <v>1</v>
-      </c>
-      <c r="I230" t="n">
-        <v>1</v>
-      </c>
-      <c r="L230" t="n">
-        <v>1</v>
-      </c>
-      <c r="M230" t="inlineStr">
+      <c r="G230" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H230" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L230" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" s="81" t="inlineStr">
         <is>
           <t>Quick Stitch</t>
         </is>
       </c>
-      <c r="BD230" t="n">
-        <v>1</v>
-      </c>
-      <c r="CI230" t="inlineStr">
+      <c r="BD230" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI230" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ230" t="inlineStr">
+      <c r="CJ230" s="81" t="inlineStr">
         <is>
           <t>Trampled towers stand up twice as fast</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
+      <c r="A231" s="81" t="inlineStr">
         <is>
           <t>Field Hospital</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B231" s="81" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
+      <c r="C231" s="81" t="inlineStr">
         <is>
           <t>healing</t>
         </is>
       </c>
-      <c r="D231" t="n">
+      <c r="D231" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E231">
+      <c r="E231" s="81">
         <f>E98</f>
         <v/>
       </c>
-      <c r="F231">
+      <c r="F231" s="81">
         <f>F98</f>
         <v/>
       </c>
-      <c r="G231" t="n">
-        <v>1</v>
-      </c>
-      <c r="H231" t="n">
-        <v>1</v>
-      </c>
-      <c r="I231" t="n">
-        <v>1</v>
-      </c>
-      <c r="L231" t="n">
+      <c r="G231" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H231" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I231" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L231" s="81" t="n">
         <v>1.25</v>
       </c>
-      <c r="M231" t="inlineStr">
+      <c r="M231" s="81" t="inlineStr">
         <is>
           <t>Big Tent</t>
         </is>
       </c>
-      <c r="CI231" t="inlineStr">
+      <c r="CI231" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ231" t="inlineStr">
+      <c r="CJ231" s="81" t="inlineStr">
         <is>
           <t>Heals towers in a wider ring</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
+      <c r="A232" s="81" t="inlineStr">
         <is>
           <t>Field Hospital</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B232" s="81" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
+      <c r="C232" s="81" t="inlineStr">
         <is>
           <t>healing</t>
         </is>
       </c>
-      <c r="D232" t="n">
+      <c r="D232" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E232">
+      <c r="E232" s="81">
         <f>E99</f>
         <v/>
       </c>
-      <c r="F232">
+      <c r="F232" s="81">
         <f>F99</f>
         <v/>
       </c>
-      <c r="G232" t="n">
-        <v>1</v>
-      </c>
-      <c r="H232" t="n">
-        <v>1</v>
-      </c>
-      <c r="I232" t="n">
-        <v>1</v>
-      </c>
-      <c r="L232" t="n">
+      <c r="G232" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H232" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I232" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L232" s="81" t="n">
         <v>1.4</v>
       </c>
-      <c r="M232" t="inlineStr">
+      <c r="M232" s="81" t="inlineStr">
         <is>
           <t>Field Ward</t>
         </is>
       </c>
-      <c r="BB232" t="n">
+      <c r="BB232" s="81" t="n">
         <v>1.2</v>
       </c>
-      <c r="CI232" t="inlineStr">
+      <c r="CI232" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ232" t="inlineStr">
+      <c r="CJ232" s="81" t="inlineStr">
         <is>
           <t>Heals a huge ring of towers</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
+      <c r="A233" s="81" t="inlineStr">
         <is>
           <t>Field Hospital</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B233" s="81" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
+      <c r="C233" s="81" t="inlineStr">
         <is>
           <t>healing</t>
         </is>
       </c>
-      <c r="D233" t="n">
+      <c r="D233" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E233">
+      <c r="E233" s="81">
         <f>E99</f>
         <v/>
       </c>
-      <c r="F233">
+      <c r="F233" s="81">
         <f>F99</f>
         <v/>
       </c>
-      <c r="G233" t="n">
-        <v>1</v>
-      </c>
-      <c r="H233" t="n">
-        <v>1</v>
-      </c>
-      <c r="I233" t="n">
-        <v>1</v>
-      </c>
-      <c r="L233" t="n">
-        <v>1</v>
-      </c>
-      <c r="M233" t="inlineStr">
+      <c r="G233" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H233" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I233" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L233" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M233" s="81" t="inlineStr">
         <is>
           <t>Rapid Recovery</t>
         </is>
       </c>
-      <c r="BB233" t="n">
+      <c r="BB233" s="81" t="n">
         <v>1.25</v>
       </c>
-      <c r="BD233" t="n">
+      <c r="BD233" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="CI233" t="inlineStr">
+      <c r="CI233" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ233" t="inlineStr">
+      <c r="CJ233" s="81" t="inlineStr">
         <is>
           <t>Trampled towers jump back up 4x as fast</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
+      <c r="A234" s="81" t="inlineStr">
         <is>
           <t>Field Hospital</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B234" s="81" t="inlineStr">
         <is>
           <t>Rescue</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
+      <c r="C234" s="81" t="inlineStr">
         <is>
           <t>hunters</t>
         </is>
       </c>
-      <c r="D234" t="n">
+      <c r="D234" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E234">
+      <c r="E234" s="81">
         <f>E103</f>
         <v/>
       </c>
-      <c r="F234">
+      <c r="F234" s="81">
         <f>F103</f>
         <v/>
       </c>
-      <c r="G234" t="n">
-        <v>1</v>
-      </c>
-      <c r="H234" t="n">
-        <v>1</v>
-      </c>
-      <c r="I234" t="n">
-        <v>1</v>
-      </c>
-      <c r="L234" t="n">
+      <c r="G234" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H234" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I234" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L234" s="81" t="n">
         <v>1.3</v>
       </c>
-      <c r="M234" t="inlineStr">
+      <c r="M234" s="81" t="inlineStr">
         <is>
           <t>Long Whistle</t>
         </is>
       </c>
-      <c r="BE234" t="n">
+      <c r="BE234" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="CI234" t="inlineStr">
+      <c r="CI234" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ234" t="inlineStr">
+      <c r="CJ234" s="81" t="inlineStr">
         <is>
           <t>Kits reach hunters in a much wider ring</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
+      <c r="A235" s="81" t="inlineStr">
         <is>
           <t>Field Hospital</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B235" s="81" t="inlineStr">
         <is>
           <t>Rescue</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="C235" s="81" t="inlineStr">
         <is>
           <t>hunters</t>
         </is>
       </c>
-      <c r="D235" t="n">
+      <c r="D235" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E235">
+      <c r="E235" s="81">
         <f>E103</f>
         <v/>
       </c>
-      <c r="F235">
+      <c r="F235" s="81">
         <f>F103</f>
         <v/>
       </c>
-      <c r="G235" t="n">
-        <v>1</v>
-      </c>
-      <c r="H235" t="n">
-        <v>1</v>
-      </c>
-      <c r="I235" t="n">
-        <v>1</v>
-      </c>
-      <c r="L235" t="n">
-        <v>1</v>
-      </c>
-      <c r="M235" t="inlineStr">
+      <c r="G235" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H235" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I235" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L235" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M235" s="81" t="inlineStr">
         <is>
           <t>Kit Bags</t>
         </is>
       </c>
-      <c r="BE235" t="n">
+      <c r="BE235" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="CI235" t="inlineStr">
+      <c r="CI235" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ235" t="inlineStr">
+      <c r="CJ235" s="81" t="inlineStr">
         <is>
           <t>Four med kits land each round</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
+      <c r="A236" s="81" t="inlineStr">
         <is>
           <t>Field Hospital</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B236" s="81" t="inlineStr">
         <is>
           <t>Rescue</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
+      <c r="C236" s="81" t="inlineStr">
         <is>
           <t>hunters</t>
         </is>
       </c>
-      <c r="D236" t="n">
+      <c r="D236" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E236">
+      <c r="E236" s="81">
         <f>E104</f>
         <v/>
       </c>
-      <c r="F236">
+      <c r="F236" s="81">
         <f>F104</f>
         <v/>
       </c>
-      <c r="G236" t="n">
-        <v>1</v>
-      </c>
-      <c r="H236" t="n">
-        <v>1</v>
-      </c>
-      <c r="I236" t="n">
-        <v>1</v>
-      </c>
-      <c r="L236" t="n">
+      <c r="G236" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H236" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I236" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L236" s="81" t="n">
         <v>1.15</v>
       </c>
-      <c r="M236" t="inlineStr">
+      <c r="M236" s="81" t="inlineStr">
         <is>
           <t>Pack Train</t>
         </is>
       </c>
-      <c r="BE236" t="n">
+      <c r="BE236" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="BF236" t="n">
+      <c r="BF236" s="81" t="n">
         <v>50</v>
       </c>
-      <c r="CI236" t="inlineStr">
+      <c r="CI236" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ236" t="inlineStr">
+      <c r="CJ236" s="81" t="inlineStr">
         <is>
           <t>Five med kits a round, 50 each</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
+      <c r="A237" s="81" t="inlineStr">
         <is>
           <t>Field Hospital</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B237" s="81" t="inlineStr">
         <is>
           <t>Rescue</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
+      <c r="C237" s="81" t="inlineStr">
         <is>
           <t>hunters</t>
         </is>
       </c>
-      <c r="D237" t="n">
+      <c r="D237" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E237">
+      <c r="E237" s="81">
         <f>E104</f>
         <v/>
       </c>
-      <c r="F237">
+      <c r="F237" s="81">
         <f>F104</f>
         <v/>
       </c>
-      <c r="G237" t="n">
-        <v>1</v>
-      </c>
-      <c r="H237" t="n">
-        <v>1</v>
-      </c>
-      <c r="I237" t="n">
-        <v>1</v>
-      </c>
-      <c r="L237" t="n">
+      <c r="G237" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H237" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I237" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L237" s="81" t="n">
         <v>1.15</v>
       </c>
-      <c r="M237" t="inlineStr">
+      <c r="M237" s="81" t="inlineStr">
         <is>
           <t>Medevac</t>
         </is>
       </c>
-      <c r="BF237" t="n">
+      <c r="BF237" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="BG237" t="n">
+      <c r="BG237" s="81" t="n">
         <v>0.35</v>
       </c>
-      <c r="CI237" t="inlineStr">
+      <c r="CI237" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ237" t="inlineStr">
+      <c r="CJ237" s="81" t="inlineStr">
         <is>
           <t>Downed hunters come back 3x as fast</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
+      <c r="A238" s="81" t="inlineStr">
         <is>
           <t>Field Hospital</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B238" s="81" t="inlineStr">
         <is>
           <t>Tonic</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
+      <c r="C238" s="81" t="inlineStr">
         <is>
           <t>tougher towers</t>
         </is>
       </c>
-      <c r="D238" t="n">
+      <c r="D238" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E238">
+      <c r="E238" s="81">
         <f>E108</f>
         <v/>
       </c>
-      <c r="F238">
+      <c r="F238" s="81">
         <f>F108</f>
         <v/>
       </c>
-      <c r="G238" t="n">
-        <v>1</v>
-      </c>
-      <c r="H238" t="n">
-        <v>1</v>
-      </c>
-      <c r="I238" t="n">
-        <v>1</v>
-      </c>
-      <c r="L238" t="n">
-        <v>1</v>
-      </c>
-      <c r="M238" t="inlineStr">
+      <c r="G238" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H238" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I238" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L238" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M238" s="81" t="inlineStr">
         <is>
           <t>Hot Coffee</t>
         </is>
       </c>
-      <c r="AB238" t="n">
+      <c r="AB238" s="81" t="n">
         <v>18</v>
       </c>
-      <c r="BH238" t="n">
+      <c r="BH238" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="CI238" t="inlineStr">
+      <c r="CI238" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ238" t="inlineStr">
+      <c r="CJ238" s="81" t="inlineStr">
         <is>
           <t>Towers in range fire 18% faster</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
+      <c r="A239" s="81" t="inlineStr">
         <is>
           <t>Field Hospital</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B239" s="81" t="inlineStr">
         <is>
           <t>Tonic</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
+      <c r="C239" s="81" t="inlineStr">
         <is>
           <t>tougher towers</t>
         </is>
       </c>
-      <c r="D239" t="n">
+      <c r="D239" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E239">
+      <c r="E239" s="81">
         <f>E108</f>
         <v/>
       </c>
-      <c r="F239">
+      <c r="F239" s="81">
         <f>F108</f>
         <v/>
       </c>
-      <c r="G239" t="n">
-        <v>1</v>
-      </c>
-      <c r="H239" t="n">
-        <v>1</v>
-      </c>
-      <c r="I239" t="n">
-        <v>1</v>
-      </c>
-      <c r="L239" t="n">
-        <v>1</v>
-      </c>
-      <c r="M239" t="inlineStr">
+      <c r="G239" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H239" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I239" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L239" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M239" s="81" t="inlineStr">
         <is>
           <t>Bitter Tonic</t>
         </is>
       </c>
-      <c r="BH239" t="n">
+      <c r="BH239" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="CI239" t="inlineStr">
+      <c r="CI239" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ239" t="inlineStr">
+      <c r="CJ239" s="81" t="inlineStr">
         <is>
           <t>Dinos that bite towers in range get slowed</t>
         </is>
       </c>
-      <c r="CP239" t="n">
+      <c r="CP239" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="CQ239" t="n">
+      <c r="CQ239" s="81" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
+      <c r="A240" s="81" t="inlineStr">
         <is>
           <t>Field Hospital</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B240" s="81" t="inlineStr">
         <is>
           <t>Tonic</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
+      <c r="C240" s="81" t="inlineStr">
         <is>
           <t>tougher towers</t>
         </is>
       </c>
-      <c r="D240" t="n">
+      <c r="D240" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E240">
+      <c r="E240" s="81">
         <f>E109</f>
         <v/>
       </c>
-      <c r="F240">
+      <c r="F240" s="81">
         <f>F109</f>
         <v/>
       </c>
-      <c r="G240" t="n">
-        <v>1</v>
-      </c>
-      <c r="H240" t="n">
-        <v>1</v>
-      </c>
-      <c r="I240" t="n">
-        <v>1</v>
-      </c>
-      <c r="L240" t="n">
-        <v>1</v>
-      </c>
-      <c r="M240" t="inlineStr">
+      <c r="G240" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H240" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I240" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L240" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M240" s="81" t="inlineStr">
         <is>
           <t>Adrenaline</t>
         </is>
       </c>
-      <c r="AB240" t="n">
+      <c r="AB240" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="BH240" t="n">
+      <c r="BH240" s="81" t="n">
         <v>40</v>
       </c>
-      <c r="CI240" t="inlineStr">
+      <c r="CI240" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ240" t="inlineStr">
+      <c r="CJ240" s="81" t="inlineStr">
         <is>
           <t>Towers in range fire 30% faster</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
+      <c r="A241" s="81" t="inlineStr">
         <is>
           <t>Field Hospital</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B241" s="81" t="inlineStr">
         <is>
           <t>Tonic</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="C241" s="81" t="inlineStr">
         <is>
           <t>tougher towers</t>
         </is>
       </c>
-      <c r="D241" t="n">
+      <c r="D241" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E241">
+      <c r="E241" s="81">
         <f>E109</f>
         <v/>
       </c>
-      <c r="F241">
+      <c r="F241" s="81">
         <f>F109</f>
         <v/>
       </c>
-      <c r="G241" t="n">
-        <v>1</v>
-      </c>
-      <c r="H241" t="n">
-        <v>1</v>
-      </c>
-      <c r="I241" t="n">
-        <v>1</v>
-      </c>
-      <c r="L241" t="n">
-        <v>1</v>
-      </c>
-      <c r="M241" t="inlineStr">
+      <c r="G241" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H241" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I241" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L241" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M241" s="81" t="inlineStr">
         <is>
           <t>Bitter Brew</t>
         </is>
       </c>
-      <c r="BH241" t="n">
+      <c r="BH241" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="CI241" t="inlineStr">
+      <c r="CI241" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ241" t="inlineStr">
+      <c r="CJ241" s="81" t="inlineStr">
         <is>
           <t>Biters slowed 30% for 3 s; towers +45% HP</t>
         </is>
       </c>
-      <c r="CP241" t="n">
+      <c r="CP241" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="CQ241" t="n">
+      <c r="CQ241" s="81" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
+      <c r="A242" s="81" t="inlineStr">
         <is>
           <t>Armory</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B242" s="81" t="inlineStr">
         <is>
           <t>Plating</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
+      <c r="C242" s="81" t="inlineStr">
         <is>
           <t>resistance</t>
         </is>
       </c>
-      <c r="D242" t="n">
+      <c r="D242" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E242">
+      <c r="E242" s="81">
         <f>E83</f>
         <v/>
       </c>
-      <c r="F242">
+      <c r="F242" s="81">
         <f>F83</f>
         <v/>
       </c>
-      <c r="G242" t="n">
-        <v>1</v>
-      </c>
-      <c r="H242" t="n">
-        <v>1</v>
-      </c>
-      <c r="I242" t="n">
-        <v>1</v>
-      </c>
-      <c r="L242" t="n">
-        <v>1</v>
-      </c>
-      <c r="M242" t="inlineStr">
+      <c r="G242" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H242" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I242" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L242" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M242" s="81" t="inlineStr">
         <is>
           <t>Spiked Walls</t>
         </is>
       </c>
-      <c r="AU242" t="n">
+      <c r="AU242" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="AV242" t="n">
+      <c r="AV242" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="CI242" t="inlineStr">
+      <c r="CI242" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ242" t="inlineStr">
+      <c r="CJ242" s="81" t="inlineStr">
         <is>
           <t>Dinos that bite take 10 damage back</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
+      <c r="A243" s="81" t="inlineStr">
         <is>
           <t>Armory</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B243" s="81" t="inlineStr">
         <is>
           <t>Plating</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
+      <c r="C243" s="81" t="inlineStr">
         <is>
           <t>resistance</t>
         </is>
       </c>
-      <c r="D243" t="n">
+      <c r="D243" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E243">
+      <c r="E243" s="81">
         <f>E83</f>
         <v/>
       </c>
-      <c r="F243">
+      <c r="F243" s="81">
         <f>F83</f>
         <v/>
       </c>
-      <c r="G243" t="n">
-        <v>1</v>
-      </c>
-      <c r="H243" t="n">
-        <v>1</v>
-      </c>
-      <c r="I243" t="n">
-        <v>1</v>
-      </c>
-      <c r="L243" t="n">
-        <v>1</v>
-      </c>
-      <c r="M243" t="inlineStr">
+      <c r="G243" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H243" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I243" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L243" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M243" s="81" t="inlineStr">
         <is>
           <t>Barbed Wire</t>
         </is>
       </c>
-      <c r="AU243" t="n">
+      <c r="AU243" s="81" t="n">
         <v>32</v>
       </c>
-      <c r="CI243" t="inlineStr">
+      <c r="CI243" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ243" t="inlineStr">
+      <c r="CJ243" s="81" t="inlineStr">
         <is>
           <t>Stings and slows raiders who shoot towers here</t>
         </is>
       </c>
-      <c r="CK243" t="inlineStr">
+      <c r="CK243" s="81" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="CL243" t="n">
+      <c r="CL243" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="CM243" t="n">
+      <c r="CM243" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="CN243" t="n">
+      <c r="CN243" s="81" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="A244" s="81" t="inlineStr">
         <is>
           <t>Armory</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B244" s="81" t="inlineStr">
         <is>
           <t>Plating</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
+      <c r="C244" s="81" t="inlineStr">
         <is>
           <t>resistance</t>
         </is>
       </c>
-      <c r="D244" t="n">
+      <c r="D244" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E244">
+      <c r="E244" s="81">
         <f>E84</f>
         <v/>
       </c>
-      <c r="F244">
+      <c r="F244" s="81">
         <f>F84</f>
         <v/>
       </c>
-      <c r="G244" t="n">
-        <v>1</v>
-      </c>
-      <c r="H244" t="n">
-        <v>1</v>
-      </c>
-      <c r="I244" t="n">
-        <v>1</v>
-      </c>
-      <c r="L244" t="n">
-        <v>1</v>
-      </c>
-      <c r="M244" t="inlineStr">
+      <c r="G244" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H244" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I244" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L244" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M244" s="81" t="inlineStr">
         <is>
           <t>Iron Fortress</t>
         </is>
       </c>
-      <c r="AU244" t="n">
+      <c r="AU244" s="81" t="n">
         <v>55</v>
       </c>
-      <c r="CI244" t="inlineStr">
+      <c r="CI244" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ244" t="inlineStr">
+      <c r="CJ244" s="81" t="inlineStr">
         <is>
           <t>Towers in range take 55% less damage</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
+      <c r="A245" s="81" t="inlineStr">
         <is>
           <t>Armory</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B245" s="81" t="inlineStr">
         <is>
           <t>Plating</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="C245" s="81" t="inlineStr">
         <is>
           <t>resistance</t>
         </is>
       </c>
-      <c r="D245" t="n">
+      <c r="D245" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E245">
+      <c r="E245" s="81">
         <f>E84</f>
         <v/>
       </c>
-      <c r="F245">
+      <c r="F245" s="81">
         <f>F84</f>
         <v/>
       </c>
-      <c r="G245" t="n">
-        <v>1</v>
-      </c>
-      <c r="H245" t="n">
-        <v>1</v>
-      </c>
-      <c r="I245" t="n">
-        <v>1</v>
-      </c>
-      <c r="L245" t="n">
-        <v>1</v>
-      </c>
-      <c r="M245" t="inlineStr">
+      <c r="G245" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H245" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I245" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L245" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M245" s="81" t="inlineStr">
         <is>
           <t>Spike Fortress</t>
         </is>
       </c>
-      <c r="AU245" t="n">
+      <c r="AU245" s="81" t="n">
         <v>40</v>
       </c>
-      <c r="AV245" t="n">
+      <c r="AV245" s="81" t="n">
         <v>18</v>
       </c>
-      <c r="CI245" t="inlineStr">
+      <c r="CI245" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ245" t="inlineStr">
+      <c r="CJ245" s="81" t="inlineStr">
         <is>
           <t>Biters take 18 damage back</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
+      <c r="A246" s="81" t="inlineStr">
         <is>
           <t>Armory</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B246" s="81" t="inlineStr">
         <is>
           <t>Gunsmith</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
+      <c r="C246" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D246" t="n">
+      <c r="D246" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E246">
+      <c r="E246" s="81">
         <f>E88</f>
         <v/>
       </c>
-      <c r="F246">
+      <c r="F246" s="81">
         <f>F88</f>
         <v/>
       </c>
-      <c r="G246" t="n">
-        <v>1</v>
-      </c>
-      <c r="H246" t="n">
-        <v>1</v>
-      </c>
-      <c r="I246" t="n">
-        <v>1</v>
-      </c>
-      <c r="L246" t="n">
-        <v>1</v>
-      </c>
-      <c r="M246" t="inlineStr">
+      <c r="G246" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H246" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I246" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L246" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M246" s="81" t="inlineStr">
         <is>
           <t>Rapid Feed</t>
         </is>
       </c>
-      <c r="AB246" t="n">
+      <c r="AB246" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="AC246" t="n">
+      <c r="AC246" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="CI246" t="inlineStr">
+      <c r="CI246" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ246" t="inlineStr">
+      <c r="CJ246" s="81" t="inlineStr">
         <is>
           <t>Towers in range fire 20% faster</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
+      <c r="A247" s="81" t="inlineStr">
         <is>
           <t>Armory</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B247" s="81" t="inlineStr">
         <is>
           <t>Gunsmith</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="C247" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D247" t="n">
+      <c r="D247" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E247">
+      <c r="E247" s="81">
         <f>E88</f>
         <v/>
       </c>
-      <c r="F247">
+      <c r="F247" s="81">
         <f>F88</f>
         <v/>
       </c>
-      <c r="G247" t="n">
-        <v>1</v>
-      </c>
-      <c r="H247" t="n">
-        <v>1</v>
-      </c>
-      <c r="I247" t="n">
-        <v>1</v>
-      </c>
-      <c r="L247" t="n">
-        <v>1</v>
-      </c>
-      <c r="M247" t="inlineStr">
+      <c r="G247" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H247" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I247" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L247" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M247" s="81" t="inlineStr">
         <is>
           <t>Heavy Loads</t>
         </is>
       </c>
-      <c r="AB247" t="n">
+      <c r="AB247" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="AC247" t="n">
+      <c r="AC247" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="CI247" t="inlineStr">
+      <c r="CI247" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ247" t="inlineStr">
+      <c r="CJ247" s="81" t="inlineStr">
         <is>
           <t>Towers in range hit 30% harder</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
+      <c r="A248" s="81" t="inlineStr">
         <is>
           <t>Armory</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B248" s="81" t="inlineStr">
         <is>
           <t>Gunsmith</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
+      <c r="C248" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D248" t="n">
+      <c r="D248" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E248">
+      <c r="E248" s="81">
         <f>E89</f>
         <v/>
       </c>
-      <c r="F248">
+      <c r="F248" s="81">
         <f>F89</f>
         <v/>
       </c>
-      <c r="G248" t="n">
-        <v>1</v>
-      </c>
-      <c r="H248" t="n">
-        <v>1</v>
-      </c>
-      <c r="I248" t="n">
-        <v>1</v>
-      </c>
-      <c r="L248" t="n">
-        <v>1</v>
-      </c>
-      <c r="M248" t="inlineStr">
+      <c r="G248" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H248" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I248" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L248" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M248" s="81" t="inlineStr">
         <is>
           <t>Machine Shop</t>
         </is>
       </c>
-      <c r="AB248" t="n">
+      <c r="AB248" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="AC248" t="n">
+      <c r="AC248" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="CI248" t="inlineStr">
+      <c r="CI248" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ248" t="inlineStr">
+      <c r="CJ248" s="81" t="inlineStr">
         <is>
           <t>Towers in range fire 30% faster</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
+      <c r="A249" s="81" t="inlineStr">
         <is>
           <t>Armory</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B249" s="81" t="inlineStr">
         <is>
           <t>Gunsmith</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="C249" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D249" t="n">
+      <c r="D249" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E249">
+      <c r="E249" s="81">
         <f>E89</f>
         <v/>
       </c>
-      <c r="F249">
+      <c r="F249" s="81">
         <f>F89</f>
         <v/>
       </c>
-      <c r="G249" t="n">
-        <v>1</v>
-      </c>
-      <c r="H249" t="n">
-        <v>1</v>
-      </c>
-      <c r="I249" t="n">
-        <v>1</v>
-      </c>
-      <c r="L249" t="n">
-        <v>1</v>
-      </c>
-      <c r="M249" t="inlineStr">
+      <c r="G249" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H249" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I249" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L249" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M249" s="81" t="inlineStr">
         <is>
           <t>Magnum Loads</t>
         </is>
       </c>
-      <c r="AB249" t="n">
+      <c r="AB249" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="AC249" t="n">
+      <c r="AC249" s="81" t="n">
         <v>40</v>
       </c>
-      <c r="CI249" t="inlineStr">
+      <c r="CI249" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ249" t="inlineStr">
+      <c r="CJ249" s="81" t="inlineStr">
         <is>
           <t>Towers in range hit 40% harder</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
+      <c r="A250" s="81" t="inlineStr">
         <is>
           <t>Armory</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B250" s="81" t="inlineStr">
         <is>
           <t>Outfitter</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="C250" s="81" t="inlineStr">
         <is>
           <t>hunters</t>
         </is>
       </c>
-      <c r="D250" t="n">
+      <c r="D250" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E250">
+      <c r="E250" s="81">
         <f>E93</f>
         <v/>
       </c>
-      <c r="F250">
+      <c r="F250" s="81">
         <f>F93</f>
         <v/>
       </c>
-      <c r="G250" t="n">
-        <v>1</v>
-      </c>
-      <c r="H250" t="n">
-        <v>1</v>
-      </c>
-      <c r="I250" t="n">
-        <v>1</v>
-      </c>
-      <c r="L250" t="n">
-        <v>1</v>
-      </c>
-      <c r="M250" t="inlineStr">
+      <c r="G250" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H250" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I250" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L250" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M250" s="81" t="inlineStr">
         <is>
           <t>Speed Loader</t>
         </is>
       </c>
-      <c r="AY250" t="n">
+      <c r="AY250" s="81" t="n">
         <v>0.7</v>
       </c>
-      <c r="CI250" t="inlineStr">
+      <c r="CI250" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ250" t="inlineStr">
+      <c r="CJ250" s="81" t="inlineStr">
         <is>
           <t>Hunters in range reload 30% faster</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
+      <c r="A251" s="81" t="inlineStr">
         <is>
           <t>Armory</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B251" s="81" t="inlineStr">
         <is>
           <t>Outfitter</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
+      <c r="C251" s="81" t="inlineStr">
         <is>
           <t>hunters</t>
         </is>
       </c>
-      <c r="D251" t="n">
+      <c r="D251" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E251">
+      <c r="E251" s="81">
         <f>E93</f>
         <v/>
       </c>
-      <c r="F251">
+      <c r="F251" s="81">
         <f>F93</f>
         <v/>
       </c>
-      <c r="G251" t="n">
-        <v>1</v>
-      </c>
-      <c r="H251" t="n">
-        <v>1</v>
-      </c>
-      <c r="I251" t="n">
-        <v>1</v>
-      </c>
-      <c r="L251" t="n">
-        <v>1</v>
-      </c>
-      <c r="M251" t="inlineStr">
+      <c r="G251" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H251" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I251" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L251" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M251" s="81" t="inlineStr">
         <is>
           <t>Gun Braces</t>
         </is>
       </c>
-      <c r="AX251" t="n">
+      <c r="AX251" s="81" t="n">
         <v>0.7</v>
       </c>
-      <c r="CI251" t="inlineStr">
+      <c r="CI251" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ251" t="inlineStr">
+      <c r="CJ251" s="81" t="inlineStr">
         <is>
           <t>Hunters in range have 30% less recoil</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
+      <c r="A252" s="81" t="inlineStr">
         <is>
           <t>Armory</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B252" s="81" t="inlineStr">
         <is>
           <t>Outfitter</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
+      <c r="C252" s="81" t="inlineStr">
         <is>
           <t>hunters</t>
         </is>
       </c>
-      <c r="D252" t="n">
+      <c r="D252" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E252">
+      <c r="E252" s="81">
         <f>E94</f>
         <v/>
       </c>
-      <c r="F252">
+      <c r="F252" s="81">
         <f>F94</f>
         <v/>
       </c>
-      <c r="G252" t="n">
-        <v>1</v>
-      </c>
-      <c r="H252" t="n">
-        <v>1</v>
-      </c>
-      <c r="I252" t="n">
-        <v>1</v>
-      </c>
-      <c r="L252" t="n">
+      <c r="G252" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H252" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I252" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L252" s="81" t="n">
         <v>1.15385</v>
       </c>
-      <c r="M252" t="inlineStr">
+      <c r="M252" s="81" t="inlineStr">
         <is>
           <t>Gun Oil</t>
         </is>
       </c>
-      <c r="AY252" t="n">
+      <c r="AY252" s="81" t="n">
         <v>0.8</v>
       </c>
-      <c r="CI252" t="inlineStr">
+      <c r="CI252" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ252" t="inlineStr">
+      <c r="CJ252" s="81" t="inlineStr">
         <is>
           <t>Wider ring; hunters in it reload 20% faster</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
+      <c r="A253" s="81" t="inlineStr">
         <is>
           <t>Armory</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B253" s="81" t="inlineStr">
         <is>
           <t>Outfitter</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
+      <c r="C253" s="81" t="inlineStr">
         <is>
           <t>hunters</t>
         </is>
       </c>
-      <c r="D253" t="n">
+      <c r="D253" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E253">
+      <c r="E253" s="81">
         <f>E94</f>
         <v/>
       </c>
-      <c r="F253">
+      <c r="F253" s="81">
         <f>F94</f>
         <v/>
       </c>
-      <c r="G253" t="n">
-        <v>1</v>
-      </c>
-      <c r="H253" t="n">
-        <v>1</v>
-      </c>
-      <c r="I253" t="n">
-        <v>1</v>
-      </c>
-      <c r="L253" t="n">
+      <c r="G253" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H253" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I253" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L253" s="81" t="n">
         <v>1.15385</v>
       </c>
-      <c r="M253" t="inlineStr">
+      <c r="M253" s="81" t="inlineStr">
         <is>
           <t>Steady Aim</t>
         </is>
       </c>
-      <c r="AZ253" t="n">
+      <c r="AZ253" s="81" t="n">
         <v>0.8</v>
       </c>
-      <c r="CI253" t="inlineStr">
+      <c r="CI253" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ253" t="inlineStr">
+      <c r="CJ253" s="81" t="inlineStr">
         <is>
           <t>Wider ring; hunters in it aim 20% tighter</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B254" s="43" t="inlineStr">
+        <is>
+          <t>Arc</t>
+        </is>
+      </c>
+      <c r="C254" s="43" t="inlineStr">
+        <is>
+          <t>more arcs, reach</t>
+        </is>
+      </c>
+      <c r="D254" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E254" s="56">
+        <f>E113</f>
+        <v/>
+      </c>
+      <c r="F254" s="56">
+        <f>F113</f>
+        <v/>
+      </c>
+      <c r="G254" s="57" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H254" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I254" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L254" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M254" s="43" t="inlineStr">
+        <is>
+          <t>Branching Bolt</t>
+        </is>
+      </c>
+      <c r="BM254" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI254" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ254" s="81" t="inlineStr">
+        <is>
+          <t>Every arc forks three ways</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B255" s="43" t="inlineStr">
+        <is>
+          <t>Arc</t>
+        </is>
+      </c>
+      <c r="C255" s="43" t="inlineStr">
+        <is>
+          <t>more arcs, reach</t>
+        </is>
+      </c>
+      <c r="D255" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E255" s="56">
+        <f>E113</f>
+        <v/>
+      </c>
+      <c r="F255" s="56">
+        <f>F113</f>
+        <v/>
+      </c>
+      <c r="G255" s="57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H255" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I255" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L255" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M255" s="43" t="inlineStr">
+        <is>
+          <t>Chain Surge</t>
+        </is>
+      </c>
+      <c r="BK255" s="81" t="n">
+        <v>9</v>
+      </c>
+      <c r="CI255" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ255" s="81" t="inlineStr">
+        <is>
+          <t>Three more arcs on every strike</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B256" s="43" t="inlineStr">
+        <is>
+          <t>Arc</t>
+        </is>
+      </c>
+      <c r="C256" s="43" t="inlineStr">
+        <is>
+          <t>more arcs, reach</t>
+        </is>
+      </c>
+      <c r="D256" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E256" s="56">
+        <f>E114</f>
+        <v/>
+      </c>
+      <c r="F256" s="56">
+        <f>F114</f>
+        <v/>
+      </c>
+      <c r="G256" s="57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H256" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I256" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L256" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M256" s="43" t="inlineStr">
+        <is>
+          <t>Storm Front</t>
+        </is>
+      </c>
+      <c r="CI256" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ256" s="81" t="inlineStr">
+        <is>
+          <t>Every 8 s a strike hits every dino on the field</t>
+        </is>
+      </c>
+      <c r="CR256" s="81" t="n">
+        <v>8</v>
+      </c>
+      <c r="CS256" s="81" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B257" s="43" t="inlineStr">
+        <is>
+          <t>Arc</t>
+        </is>
+      </c>
+      <c r="C257" s="43" t="inlineStr">
+        <is>
+          <t>more arcs, reach</t>
+        </is>
+      </c>
+      <c r="D257" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E257" s="56">
+        <f>E114</f>
+        <v/>
+      </c>
+      <c r="F257" s="56">
+        <f>F114</f>
+        <v/>
+      </c>
+      <c r="G257" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H257" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I257" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L257" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M257" s="43" t="inlineStr">
+        <is>
+          <t>Supercell</t>
+        </is>
+      </c>
+      <c r="AE257" s="81" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF257" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK257" s="81" t="n">
+        <v>14</v>
+      </c>
+      <c r="CI257" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ257" s="81" t="inlineStr">
+        <is>
+          <t>A 14-arc chain that slows every dino it hits</t>
+        </is>
+      </c>
+      <c r="CT257" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B258" s="43" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="C258" s="43" t="inlineStr">
+        <is>
+          <t>power, armour, stun</t>
+        </is>
+      </c>
+      <c r="D258" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E258" s="56">
+        <f>E118</f>
+        <v/>
+      </c>
+      <c r="F258" s="56">
+        <f>F118</f>
+        <v/>
+      </c>
+      <c r="G258" s="57" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H258" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I258" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L258" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M258" s="43" t="inlineStr">
+        <is>
+          <t>Overcharge</t>
+        </is>
+      </c>
+      <c r="N258" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U258" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CI258" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ258" s="81" t="inlineStr">
+        <is>
+          <t>Stuns its first target for 0.8 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B259" s="43" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="C259" s="43" t="inlineStr">
+        <is>
+          <t>power, armour, stun</t>
+        </is>
+      </c>
+      <c r="D259" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E259" s="56">
+        <f>E118</f>
+        <v/>
+      </c>
+      <c r="F259" s="56">
+        <f>F118</f>
+        <v/>
+      </c>
+      <c r="G259" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H259" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I259" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L259" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M259" s="43" t="inlineStr">
+        <is>
+          <t>Static Storm</t>
+        </is>
+      </c>
+      <c r="N259" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BP259" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="CI259" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ259" s="81" t="inlineStr">
+        <is>
+          <t>Struck dinos take +30% from the next strike</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B260" s="43" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="C260" s="43" t="inlineStr">
+        <is>
+          <t>power, armour, stun</t>
+        </is>
+      </c>
+      <c r="D260" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E260" s="56">
+        <f>E119</f>
+        <v/>
+      </c>
+      <c r="F260" s="56">
+        <f>F119</f>
+        <v/>
+      </c>
+      <c r="G260" s="57" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H260" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I260" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L260" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M260" s="43" t="inlineStr">
+        <is>
+          <t>Superconductor</t>
+        </is>
+      </c>
+      <c r="N260" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CI260" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ260" s="81" t="inlineStr">
+        <is>
+          <t>Every dino in the chain is stunned for a moment</t>
+        </is>
+      </c>
+      <c r="CT260" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B261" s="43" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="C261" s="43" t="inlineStr">
+        <is>
+          <t>power, armour, stun</t>
+        </is>
+      </c>
+      <c r="D261" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E261" s="56">
+        <f>E119</f>
+        <v/>
+      </c>
+      <c r="F261" s="56">
+        <f>F119</f>
+        <v/>
+      </c>
+      <c r="G261" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="H261" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I261" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L261" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M261" s="43" t="inlineStr">
+        <is>
+          <t>Thunderstrike</t>
+        </is>
+      </c>
+      <c r="N261" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BJ261" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI261" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ261" s="81" t="inlineStr">
+        <is>
+          <t>Huge strikes that break 2 sizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B262" s="43" t="inlineStr">
+        <is>
+          <t>Lightning Rod</t>
+        </is>
+      </c>
+      <c r="C262" s="43" t="inlineStr">
+        <is>
+          <t>support, defence</t>
+        </is>
+      </c>
+      <c r="D262" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E262" s="56">
+        <f>E123</f>
+        <v/>
+      </c>
+      <c r="F262" s="56">
+        <f>F123</f>
+        <v/>
+      </c>
+      <c r="G262" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H262" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I262" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L262" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M262" s="43" t="inlineStr">
+        <is>
+          <t>Ground Wire</t>
+        </is>
+      </c>
+      <c r="BR262" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI262" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ262" s="81" t="inlineStr">
+        <is>
+          <t>Strikes down a dino throw every 2 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B263" s="43" t="inlineStr">
+        <is>
+          <t>Lightning Rod</t>
+        </is>
+      </c>
+      <c r="C263" s="43" t="inlineStr">
+        <is>
+          <t>support, defence</t>
+        </is>
+      </c>
+      <c r="D263" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E263" s="56">
+        <f>E123</f>
+        <v/>
+      </c>
+      <c r="F263" s="56">
+        <f>F123</f>
+        <v/>
+      </c>
+      <c r="G263" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H263" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I263" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L263" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M263" s="43" t="inlineStr">
+        <is>
+          <t>Rod Strike</t>
+        </is>
+      </c>
+      <c r="AB263" s="57" t="n">
+        <v>15</v>
+      </c>
+      <c r="CI263" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ263" s="81" t="inlineStr">
+        <is>
+          <t>Zaps raiders; towers in range fire 15% faster</t>
+        </is>
+      </c>
+      <c r="CK263" s="81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CL263" s="81" t="n">
+        <v>20</v>
+      </c>
+      <c r="CM263" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN263" s="81" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B264" s="43" t="inlineStr">
+        <is>
+          <t>Lightning Rod</t>
+        </is>
+      </c>
+      <c r="C264" s="43" t="inlineStr">
+        <is>
+          <t>support, defence</t>
+        </is>
+      </c>
+      <c r="D264" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E264" s="56">
+        <f>E124</f>
+        <v/>
+      </c>
+      <c r="F264" s="56">
+        <f>F124</f>
+        <v/>
+      </c>
+      <c r="G264" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H264" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I264" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L264" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M264" s="43" t="inlineStr">
+        <is>
+          <t>Lightning Shield</t>
+        </is>
+      </c>
+      <c r="AC264" s="57" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR264" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI264" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ264" s="81" t="inlineStr">
+        <is>
+          <t>Strikes down a throw at a tower every second</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="43" t="inlineStr">
+        <is>
+          <t>Storm Coil</t>
+        </is>
+      </c>
+      <c r="B265" s="43" t="inlineStr">
+        <is>
+          <t>Lightning Rod</t>
+        </is>
+      </c>
+      <c r="C265" s="43" t="inlineStr">
+        <is>
+          <t>support, defence</t>
+        </is>
+      </c>
+      <c r="D265" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E265" s="56">
+        <f>E124</f>
+        <v/>
+      </c>
+      <c r="F265" s="56">
+        <f>F124</f>
+        <v/>
+      </c>
+      <c r="G265" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H265" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I265" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L265" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M265" s="43" t="inlineStr">
+        <is>
+          <t>Thunder Drums</t>
+        </is>
+      </c>
+      <c r="AB265" s="57" t="n">
+        <v>25</v>
+      </c>
+      <c r="CI265" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ265" s="81" t="inlineStr">
+        <is>
+          <t>Towers in range fire 25% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B266" s="43" t="inlineStr">
+        <is>
+          <t>Talons</t>
+        </is>
+      </c>
+      <c r="C266" s="43" t="inlineStr">
+        <is>
+          <t>raw damage, pierces armour</t>
+        </is>
+      </c>
+      <c r="D266" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E266" s="56">
+        <f>E128</f>
+        <v/>
+      </c>
+      <c r="F266" s="56">
+        <f>F128</f>
+        <v/>
+      </c>
+      <c r="G266" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H266" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I266" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="L266" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M266" s="43" t="inlineStr">
+        <is>
+          <t>Raking Strike</t>
+        </is>
+      </c>
+      <c r="N266" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CI266" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ266" s="81" t="inlineStr">
+        <is>
+          <t>Each dive also slashes the dino beside it</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B267" s="43" t="inlineStr">
+        <is>
+          <t>Talons</t>
+        </is>
+      </c>
+      <c r="C267" s="43" t="inlineStr">
+        <is>
+          <t>raw damage, pierces armour</t>
+        </is>
+      </c>
+      <c r="D267" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E267" s="56">
+        <f>E128</f>
+        <v/>
+      </c>
+      <c r="F267" s="56">
+        <f>F128</f>
+        <v/>
+      </c>
+      <c r="G267" s="57" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H267" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I267" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L267" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M267" s="43" t="inlineStr">
+        <is>
+          <t>Stoop Strike</t>
+        </is>
+      </c>
+      <c r="N267" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU267" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="CI267" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ267" s="81" t="inlineStr">
+        <is>
+          <t>The first dive on a dino hits 6x</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B268" s="43" t="inlineStr">
+        <is>
+          <t>Talons</t>
+        </is>
+      </c>
+      <c r="C268" s="43" t="inlineStr">
+        <is>
+          <t>raw damage, pierces armour</t>
+        </is>
+      </c>
+      <c r="D268" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E268" s="56">
+        <f>E129</f>
+        <v/>
+      </c>
+      <c r="F268" s="56">
+        <f>F129</f>
+        <v/>
+      </c>
+      <c r="G268" s="57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H268" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I268" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L268" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M268" s="43" t="inlineStr">
+        <is>
+          <t>Harpy Strike</t>
+        </is>
+      </c>
+      <c r="P268" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ268" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI268" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ268" s="81" t="inlineStr">
+        <is>
+          <t>Dives break 4 sizes and hit bosses 2x</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B269" s="43" t="inlineStr">
+        <is>
+          <t>Talons</t>
+        </is>
+      </c>
+      <c r="C269" s="43" t="inlineStr">
+        <is>
+          <t>raw damage, pierces armour</t>
+        </is>
+      </c>
+      <c r="D269" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E269" s="56">
+        <f>E129</f>
+        <v/>
+      </c>
+      <c r="F269" s="56">
+        <f>F129</f>
+        <v/>
+      </c>
+      <c r="G269" s="57" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H269" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I269" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L269" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M269" s="43" t="inlineStr">
+        <is>
+          <t>Hide Ripper</t>
+        </is>
+      </c>
+      <c r="O269" s="81" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CI269" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ269" s="81" t="inlineStr">
+        <is>
+          <t>Talons shred armoured dinos</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B270" s="43" t="inlineStr">
+        <is>
+          <t>Flock</t>
+        </is>
+      </c>
+      <c r="C270" s="43" t="inlineStr">
+        <is>
+          <t>more birds</t>
+        </is>
+      </c>
+      <c r="D270" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E270" s="56">
+        <f>E133</f>
+        <v/>
+      </c>
+      <c r="F270" s="56">
+        <f>F133</f>
+        <v/>
+      </c>
+      <c r="G270" s="57" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H270" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I270" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L270" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M270" s="43" t="inlineStr">
+        <is>
+          <t>Swift Wings</t>
+        </is>
+      </c>
+      <c r="CI270" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ270" s="81" t="inlineStr">
+        <is>
+          <t>Birds fly back much faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B271" s="43" t="inlineStr">
+        <is>
+          <t>Flock</t>
+        </is>
+      </c>
+      <c r="C271" s="43" t="inlineStr">
+        <is>
+          <t>more birds</t>
+        </is>
+      </c>
+      <c r="D271" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E271" s="56">
+        <f>E133</f>
+        <v/>
+      </c>
+      <c r="F271" s="56">
+        <f>F133</f>
+        <v/>
+      </c>
+      <c r="G271" s="57" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H271" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I271" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L271" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M271" s="43" t="inlineStr">
+        <is>
+          <t>Second Flock</t>
+        </is>
+      </c>
+      <c r="BT271" s="81" t="n">
+        <v>7</v>
+      </c>
+      <c r="CI271" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ271" s="81" t="inlineStr">
+        <is>
+          <t>Seven bigger birds hunt at once</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B272" s="43" t="inlineStr">
+        <is>
+          <t>Flock</t>
+        </is>
+      </c>
+      <c r="C272" s="43" t="inlineStr">
+        <is>
+          <t>more birds</t>
+        </is>
+      </c>
+      <c r="D272" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E272" s="56">
+        <f>E134</f>
+        <v/>
+      </c>
+      <c r="F272" s="56">
+        <f>F134</f>
+        <v/>
+      </c>
+      <c r="G272" s="57" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H272" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I272" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L272" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="M272" s="43" t="inlineStr">
+        <is>
+          <t>Sky Hunters</t>
+        </is>
+      </c>
+      <c r="BT272" s="81" t="n">
+        <v>12</v>
+      </c>
+      <c r="CI272" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ272" s="81" t="inlineStr">
+        <is>
+          <t>Twelve birds hunt twice as far out</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B273" s="43" t="inlineStr">
+        <is>
+          <t>Flock</t>
+        </is>
+      </c>
+      <c r="C273" s="43" t="inlineStr">
+        <is>
+          <t>more birds</t>
+        </is>
+      </c>
+      <c r="D273" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E273" s="56">
+        <f>E134</f>
+        <v/>
+      </c>
+      <c r="F273" s="56">
+        <f>F134</f>
+        <v/>
+      </c>
+      <c r="G273" s="57" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H273" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I273" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L273" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M273" s="43" t="inlineStr">
+        <is>
+          <t>Strafing Run</t>
+        </is>
+      </c>
+      <c r="R273" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI273" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ273" s="81" t="inlineStr">
+        <is>
+          <t>Each dive cuts through 3 dinos in a line</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B274" s="43" t="inlineStr">
+        <is>
+          <t>Falconer</t>
+        </is>
+      </c>
+      <c r="C274" s="43" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D274" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E274" s="56">
+        <f>E138</f>
+        <v/>
+      </c>
+      <c r="F274" s="56">
+        <f>F138</f>
+        <v/>
+      </c>
+      <c r="G274" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H274" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I274" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L274" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M274" s="43" t="inlineStr">
+        <is>
+          <t>Loud Bells</t>
+        </is>
+      </c>
+      <c r="T274" s="81" t="n">
+        <v>25</v>
+      </c>
+      <c r="CI274" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ274" s="81" t="inlineStr">
+        <is>
+          <t>Struck dinos take +25% from every tower</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B275" s="43" t="inlineStr">
+        <is>
+          <t>Falconer</t>
+        </is>
+      </c>
+      <c r="C275" s="43" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D275" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E275" s="56">
+        <f>E138</f>
+        <v/>
+      </c>
+      <c r="F275" s="56">
+        <f>F138</f>
+        <v/>
+      </c>
+      <c r="G275" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H275" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I275" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L275" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M275" s="43" t="inlineStr">
+        <is>
+          <t>Guard Falcons</t>
+        </is>
+      </c>
+      <c r="BX275" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="CI275" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ275" s="81" t="inlineStr">
+        <is>
+          <t>Birds dive at raiders; bosses take +40%</t>
+        </is>
+      </c>
+      <c r="CK275" s="81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CL275" s="81" t="n">
+        <v>20</v>
+      </c>
+      <c r="CM275" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN275" s="81" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B276" s="43" t="inlineStr">
+        <is>
+          <t>Falconer</t>
+        </is>
+      </c>
+      <c r="C276" s="43" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D276" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E276" s="56">
+        <f>E139</f>
+        <v/>
+      </c>
+      <c r="F276" s="56">
+        <f>F139</f>
+        <v/>
+      </c>
+      <c r="G276" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H276" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I276" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L276" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M276" s="43" t="inlineStr">
+        <is>
+          <t>Royal Hood</t>
+        </is>
+      </c>
+      <c r="BX276" s="81" t="n">
+        <v>60</v>
+      </c>
+      <c r="CI276" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ276" s="81" t="inlineStr">
+        <is>
+          <t>Bosses in range take +60% from everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="43" t="inlineStr">
+        <is>
+          <t>Falcon Roost</t>
+        </is>
+      </c>
+      <c r="B277" s="43" t="inlineStr">
+        <is>
+          <t>Falconer</t>
+        </is>
+      </c>
+      <c r="C277" s="43" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D277" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E277" s="56">
+        <f>E139</f>
+        <v/>
+      </c>
+      <c r="F277" s="56">
+        <f>F139</f>
+        <v/>
+      </c>
+      <c r="G277" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H277" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I277" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L277" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M277" s="43" t="inlineStr">
+        <is>
+          <t>Bell Chorus</t>
+        </is>
+      </c>
+      <c r="T277" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="CI277" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ277" s="81" t="inlineStr">
+        <is>
+          <t>Struck dinos take +40% from every tower</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -13307,7 +13307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU277"/>
+  <dimension ref="A1:CU301"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -35530,6 +35530,1481 @@
       <c r="CJ277" s="81" t="inlineStr">
         <is>
           <t>Struck dinos take +40% from every tower</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Deep Tar</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>slow and sink</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>4</v>
+      </c>
+      <c r="E278">
+        <f>E143</f>
+        <v/>
+      </c>
+      <c r="F278">
+        <f>F143</f>
+        <v/>
+      </c>
+      <c r="G278" t="n">
+        <v>1</v>
+      </c>
+      <c r="H278" t="n">
+        <v>1</v>
+      </c>
+      <c r="I278" t="n">
+        <v>1</v>
+      </c>
+      <c r="L278" t="n">
+        <v>1</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>Thick Mire</t>
+        </is>
+      </c>
+      <c r="AE278" t="n">
+        <v>55</v>
+      </c>
+      <c r="CI278" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ278" t="inlineStr">
+        <is>
+          <t>Thicker tar: dinos wade much slower</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Deep Tar</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>slow and sink</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>4</v>
+      </c>
+      <c r="E279">
+        <f>E143</f>
+        <v/>
+      </c>
+      <c r="F279">
+        <f>F143</f>
+        <v/>
+      </c>
+      <c r="G279" t="n">
+        <v>1</v>
+      </c>
+      <c r="H279" t="n">
+        <v>1</v>
+      </c>
+      <c r="I279" t="n">
+        <v>1</v>
+      </c>
+      <c r="L279" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>Bog Boots</t>
+        </is>
+      </c>
+      <c r="AE279" t="n">
+        <v>45</v>
+      </c>
+      <c r="CI279" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ279" t="inlineStr">
+        <is>
+          <t>A longer pool that also slows raiders</t>
+        </is>
+      </c>
+      <c r="CK279" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CL279" t="n">
+        <v>30</v>
+      </c>
+      <c r="CM279" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Deep Tar</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>slow and sink</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>5</v>
+      </c>
+      <c r="E280">
+        <f>E144</f>
+        <v/>
+      </c>
+      <c r="F280">
+        <f>F144</f>
+        <v/>
+      </c>
+      <c r="G280" t="n">
+        <v>1</v>
+      </c>
+      <c r="H280" t="n">
+        <v>1</v>
+      </c>
+      <c r="I280" t="n">
+        <v>1</v>
+      </c>
+      <c r="L280" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>La Brea</t>
+        </is>
+      </c>
+      <c r="AE280" t="n">
+        <v>62</v>
+      </c>
+      <c r="AF280" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC280" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CI280" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ280" t="inlineStr">
+        <is>
+          <t>Smallest dinos sink at once; the rest crawl</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Deep Tar</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>slow and sink</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>5</v>
+      </c>
+      <c r="E281">
+        <f>E144</f>
+        <v/>
+      </c>
+      <c r="F281">
+        <f>F144</f>
+        <v/>
+      </c>
+      <c r="G281" t="n">
+        <v>1</v>
+      </c>
+      <c r="H281" t="n">
+        <v>1</v>
+      </c>
+      <c r="I281" t="n">
+        <v>1</v>
+      </c>
+      <c r="L281" t="n">
+        <v>1</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>Black Glue</t>
+        </is>
+      </c>
+      <c r="AE281" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF281" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI281" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ281" t="inlineStr">
+        <is>
+          <t>Dinos stay slowed 5 s after they climb out</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Bubbling</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>4</v>
+      </c>
+      <c r="E282">
+        <f>E148</f>
+        <v/>
+      </c>
+      <c r="F282">
+        <f>F148</f>
+        <v/>
+      </c>
+      <c r="G282" t="n">
+        <v>1</v>
+      </c>
+      <c r="H282" t="n">
+        <v>1</v>
+      </c>
+      <c r="I282" t="n">
+        <v>1</v>
+      </c>
+      <c r="L282" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>Boiling Splash</t>
+        </is>
+      </c>
+      <c r="CI282" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ282" t="inlineStr">
+        <is>
+          <t>A bigger pool of boiling tar</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Bubbling</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>4</v>
+      </c>
+      <c r="E283">
+        <f>E148</f>
+        <v/>
+      </c>
+      <c r="F283">
+        <f>F148</f>
+        <v/>
+      </c>
+      <c r="G283" t="n">
+        <v>1</v>
+      </c>
+      <c r="H283" t="n">
+        <v>1</v>
+      </c>
+      <c r="I283" t="n">
+        <v>1</v>
+      </c>
+      <c r="L283" t="n">
+        <v>1</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Pitch Coat</t>
+        </is>
+      </c>
+      <c r="X283" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM283" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CI283" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ283" t="inlineStr">
+        <is>
+          <t>Sticky tar strips armour; dinos leave burning</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Bubbling</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>5</v>
+      </c>
+      <c r="E284">
+        <f>E149</f>
+        <v/>
+      </c>
+      <c r="F284">
+        <f>F149</f>
+        <v/>
+      </c>
+      <c r="G284" t="n">
+        <v>1</v>
+      </c>
+      <c r="H284" t="n">
+        <v>1</v>
+      </c>
+      <c r="I284" t="n">
+        <v>1</v>
+      </c>
+      <c r="L284" t="n">
+        <v>1</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>Ever-Burn</t>
+        </is>
+      </c>
+      <c r="Y284" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CI284" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ284" t="inlineStr">
+        <is>
+          <t>Dinos keep burning 2.75 s after they leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Bubbling</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>5</v>
+      </c>
+      <c r="E285">
+        <f>E149</f>
+        <v/>
+      </c>
+      <c r="F285">
+        <f>F149</f>
+        <v/>
+      </c>
+      <c r="G285" t="n">
+        <v>1</v>
+      </c>
+      <c r="H285" t="n">
+        <v>1</v>
+      </c>
+      <c r="I285" t="n">
+        <v>1</v>
+      </c>
+      <c r="L285" t="n">
+        <v>1</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>Tar Inferno</t>
+        </is>
+      </c>
+      <c r="X285" t="n">
+        <v>120</v>
+      </c>
+      <c r="CI285" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ285" t="inlineStr">
+        <is>
+          <t>The tar boils 50% hotter</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Dig Site</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>cash and support</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>4</v>
+      </c>
+      <c r="E286">
+        <f>E153</f>
+        <v/>
+      </c>
+      <c r="F286">
+        <f>F153</f>
+        <v/>
+      </c>
+      <c r="G286" t="n">
+        <v>1</v>
+      </c>
+      <c r="H286" t="n">
+        <v>1</v>
+      </c>
+      <c r="I286" t="n">
+        <v>1</v>
+      </c>
+      <c r="L286" t="n">
+        <v>1</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>Bone Yard</t>
+        </is>
+      </c>
+      <c r="CD286" t="n">
+        <v>28</v>
+      </c>
+      <c r="CE286" t="n">
+        <v>36</v>
+      </c>
+      <c r="CI286" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ286" t="inlineStr">
+        <is>
+          <t>Every sunk dino pays more cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Dig Site</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>cash and support</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>4</v>
+      </c>
+      <c r="E287">
+        <f>E153</f>
+        <v/>
+      </c>
+      <c r="F287">
+        <f>F153</f>
+        <v/>
+      </c>
+      <c r="G287" t="n">
+        <v>1</v>
+      </c>
+      <c r="H287" t="n">
+        <v>1</v>
+      </c>
+      <c r="I287" t="n">
+        <v>1</v>
+      </c>
+      <c r="L287" t="n">
+        <v>1</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Fossil Finder</t>
+        </is>
+      </c>
+      <c r="CD287" t="n">
+        <v>15</v>
+      </c>
+      <c r="CE287" t="n">
+        <v>55</v>
+      </c>
+      <c r="CI287" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ287" t="inlineStr">
+        <is>
+          <t>Bigger chests where dinos go under</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Dig Site</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>cash and support</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>5</v>
+      </c>
+      <c r="E288">
+        <f>E154</f>
+        <v/>
+      </c>
+      <c r="F288">
+        <f>F154</f>
+        <v/>
+      </c>
+      <c r="G288" t="n">
+        <v>1</v>
+      </c>
+      <c r="H288" t="n">
+        <v>1</v>
+      </c>
+      <c r="I288" t="n">
+        <v>1</v>
+      </c>
+      <c r="L288" t="n">
+        <v>1</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Preserved Specimens</t>
+        </is>
+      </c>
+      <c r="CD288" t="n">
+        <v>36</v>
+      </c>
+      <c r="CE288" t="n">
+        <v>40</v>
+      </c>
+      <c r="CI288" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ288" t="inlineStr">
+        <is>
+          <t>Every sunk dino pays 36 cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Tar Pit</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Dig Site</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>cash and support</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>5</v>
+      </c>
+      <c r="E289">
+        <f>E154</f>
+        <v/>
+      </c>
+      <c r="F289">
+        <f>F154</f>
+        <v/>
+      </c>
+      <c r="G289" t="n">
+        <v>1</v>
+      </c>
+      <c r="H289" t="n">
+        <v>1</v>
+      </c>
+      <c r="I289" t="n">
+        <v>1</v>
+      </c>
+      <c r="L289" t="n">
+        <v>1</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>Amber Seep</t>
+        </is>
+      </c>
+      <c r="CD289" t="n">
+        <v>25</v>
+      </c>
+      <c r="CE289" t="n">
+        <v>60</v>
+      </c>
+      <c r="CI289" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ289" t="inlineStr">
+        <is>
+          <t>Chests where dinos sink are worth 60</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Spearhead</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>raw damage, breaks</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>4</v>
+      </c>
+      <c r="E290">
+        <f>E158</f>
+        <v/>
+      </c>
+      <c r="F290">
+        <f>F158</f>
+        <v/>
+      </c>
+      <c r="G290" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H290" t="n">
+        <v>1</v>
+      </c>
+      <c r="I290" t="n">
+        <v>1</v>
+      </c>
+      <c r="L290" t="n">
+        <v>1</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Serrated Head</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T290" t="n">
+        <v>20</v>
+      </c>
+      <c r="CI290" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ290" t="inlineStr">
+        <is>
+          <t>Hit dinos take +20% from every tower</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Spearhead</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>raw damage, breaks</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>4</v>
+      </c>
+      <c r="E291">
+        <f>E158</f>
+        <v/>
+      </c>
+      <c r="F291">
+        <f>F158</f>
+        <v/>
+      </c>
+      <c r="G291" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H291" t="n">
+        <v>1</v>
+      </c>
+      <c r="I291" t="n">
+        <v>1</v>
+      </c>
+      <c r="L291" t="n">
+        <v>1</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>Whale Lance</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P291" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CI291" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ291" t="inlineStr">
+        <is>
+          <t>Bolts hit bosses 40% harder</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Spearhead</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>raw damage, breaks</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>5</v>
+      </c>
+      <c r="E292">
+        <f>E159</f>
+        <v/>
+      </c>
+      <c r="F292">
+        <f>F159</f>
+        <v/>
+      </c>
+      <c r="G292" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H292" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I292" t="n">
+        <v>1</v>
+      </c>
+      <c r="L292" t="n">
+        <v>1</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>Leviathan Bolt</t>
+        </is>
+      </c>
+      <c r="P292" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ292" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI292" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ292" t="inlineStr">
+        <is>
+          <t>Bolts break 4 sizes and hit bosses 3x</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Spearhead</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>raw damage, breaks</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>5</v>
+      </c>
+      <c r="E293">
+        <f>E159</f>
+        <v/>
+      </c>
+      <c r="F293">
+        <f>F159</f>
+        <v/>
+      </c>
+      <c r="G293" t="n">
+        <v>3</v>
+      </c>
+      <c r="H293" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I293" t="n">
+        <v>1</v>
+      </c>
+      <c r="L293" t="n">
+        <v>1</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>Heartseeker</t>
+        </is>
+      </c>
+      <c r="BJ293" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI293" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ293" t="inlineStr">
+        <is>
+          <t>Always aims for the biggest dino in range</t>
+        </is>
+      </c>
+      <c r="CU293" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>4</v>
+      </c>
+      <c r="E294">
+        <f>E163</f>
+        <v/>
+      </c>
+      <c r="F294">
+        <f>F163</f>
+        <v/>
+      </c>
+      <c r="G294" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H294" t="n">
+        <v>1</v>
+      </c>
+      <c r="I294" t="n">
+        <v>1</v>
+      </c>
+      <c r="L294" t="n">
+        <v>1</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Tether</t>
+        </is>
+      </c>
+      <c r="U294" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI294" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ294" t="inlineStr">
+        <is>
+          <t>Pinned dinos stay held 2 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>4</v>
+      </c>
+      <c r="E295">
+        <f>E163</f>
+        <v/>
+      </c>
+      <c r="F295">
+        <f>F163</f>
+        <v/>
+      </c>
+      <c r="G295" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H295" t="n">
+        <v>1</v>
+      </c>
+      <c r="I295" t="n">
+        <v>1</v>
+      </c>
+      <c r="L295" t="n">
+        <v>1</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>Snag Line</t>
+        </is>
+      </c>
+      <c r="U295" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CI295" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ295" t="inlineStr">
+        <is>
+          <t>Harpoons raiders too; holds dinos 1.75 s</t>
+        </is>
+      </c>
+      <c r="CK295" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CL295" t="n">
+        <v>30</v>
+      </c>
+      <c r="CM295" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN295" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>5</v>
+      </c>
+      <c r="E296">
+        <f>E164</f>
+        <v/>
+      </c>
+      <c r="F296">
+        <f>F164</f>
+        <v/>
+      </c>
+      <c r="G296" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H296" t="n">
+        <v>1</v>
+      </c>
+      <c r="I296" t="n">
+        <v>1</v>
+      </c>
+      <c r="L296" t="n">
+        <v>1</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>Anchor Line</t>
+        </is>
+      </c>
+      <c r="AE296" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF296" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG296" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CI296" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ296" t="inlineStr">
+        <is>
+          <t>Bolts slow bosses too: 30% for 2 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Reel</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>5</v>
+      </c>
+      <c r="E297">
+        <f>E164</f>
+        <v/>
+      </c>
+      <c r="F297">
+        <f>F164</f>
+        <v/>
+      </c>
+      <c r="G297" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H297" t="n">
+        <v>1</v>
+      </c>
+      <c r="I297" t="n">
+        <v>1</v>
+      </c>
+      <c r="L297" t="n">
+        <v>1</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>Winch Haul</t>
+        </is>
+      </c>
+      <c r="W297" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="CI297" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ297" t="inlineStr">
+        <is>
+          <t>Drags hit dinos 7.5 studs back</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>more bolts</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>4</v>
+      </c>
+      <c r="E298">
+        <f>E168</f>
+        <v/>
+      </c>
+      <c r="F298">
+        <f>F168</f>
+        <v/>
+      </c>
+      <c r="G298" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H298" t="n">
+        <v>1</v>
+      </c>
+      <c r="I298" t="n">
+        <v>1</v>
+      </c>
+      <c r="L298" t="n">
+        <v>1</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>Wide Volley</t>
+        </is>
+      </c>
+      <c r="Q298" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI298" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ298" t="inlineStr">
+        <is>
+          <t>Five bolts per volley</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>more bolts</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>4</v>
+      </c>
+      <c r="E299">
+        <f>E168</f>
+        <v/>
+      </c>
+      <c r="F299">
+        <f>F168</f>
+        <v/>
+      </c>
+      <c r="G299" t="n">
+        <v>1</v>
+      </c>
+      <c r="H299" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I299" t="n">
+        <v>1</v>
+      </c>
+      <c r="L299" t="n">
+        <v>1</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>Fire Bolts</t>
+        </is>
+      </c>
+      <c r="X299" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI299" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ299" t="inlineStr">
+        <is>
+          <t>Bolts set dinos on fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>more bolts</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>5</v>
+      </c>
+      <c r="E300">
+        <f>E169</f>
+        <v/>
+      </c>
+      <c r="F300">
+        <f>F169</f>
+        <v/>
+      </c>
+      <c r="G300" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H300" t="n">
+        <v>1</v>
+      </c>
+      <c r="I300" t="n">
+        <v>1</v>
+      </c>
+      <c r="L300" t="n">
+        <v>1</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>Siege Battery</t>
+        </is>
+      </c>
+      <c r="Q300" t="n">
+        <v>6</v>
+      </c>
+      <c r="CI300" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ300" t="inlineStr">
+        <is>
+          <t>Six bolts per volley</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Harpoon Ballista</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>more bolts</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>5</v>
+      </c>
+      <c r="E301">
+        <f>E169</f>
+        <v/>
+      </c>
+      <c r="F301">
+        <f>F169</f>
+        <v/>
+      </c>
+      <c r="G301" t="n">
+        <v>2</v>
+      </c>
+      <c r="H301" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I301" t="n">
+        <v>1</v>
+      </c>
+      <c r="L301" t="n">
+        <v>1</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>Firestorm Volley</t>
+        </is>
+      </c>
+      <c r="X301" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y301" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI301" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ301" t="inlineStr">
+        <is>
+          <t>Faster volleys of burning bolts</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9499,7 +9499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E188"/>
+  <dimension ref="A1:E189"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C186" s="109" t="inlineStr">
         <is>
-          <t>s a dino hit by a Strips armour shot stays unarmoured (Blind, Perch, Mortar options; PLAN 9c, #290)</t>
+          <t>s a dino hit by a Strips armour shot stays unarmoured (Blind, Perch, Mortar options; PLAN 9c, #290); bosses half of it, as Jaw Lock (#307)</t>
         </is>
       </c>
     </row>
@@ -12285,6 +12285,21 @@
       <c r="C188" s="81" t="inlineStr">
         <is>
           <t>s: an arc's stun on a Chain effects coil (Supercell, Superconductor) is capped at this; the first target keeps its full stun (PLAN 9e, #297)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="81" t="inlineStr">
+        <is>
+          <t>Bomblet fires per shell</t>
+        </is>
+      </c>
+      <c r="B189" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="C189" s="81" t="inlineStr">
+        <is>
+          <t>fires a Fire Bomblets shell lights at most (first generation first, then the next); the rest of its bomblets still hit (Fire Bomblets, Firecracker Rain; PLAN T115b, #306)</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14093,7 @@
       </c>
       <c r="M6" s="43" t="inlineStr">
         <is>
-          <t>Long Barrel</t>
+          <t>Spyglass</t>
         </is>
       </c>
       <c r="N6" s="57" t="n"/>
@@ -28102,7 +28117,7 @@
       </c>
       <c r="M173" s="43" t="inlineStr">
         <is>
-          <t>Trophy Spotter</t>
+          <t>Alpha Spotter</t>
         </is>
       </c>
       <c r="N173" s="57" t="n"/>
@@ -28452,7 +28467,7 @@
         <v/>
       </c>
       <c r="G177" s="57" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="H177" s="57" t="n">
         <v>1.35</v>
@@ -28470,7 +28485,11 @@
           <t>Shredder</t>
         </is>
       </c>
-      <c r="N177" s="57" t="n"/>
+      <c r="N177" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O177" s="57" t="n"/>
       <c r="P177" s="57" t="n"/>
       <c r="Q177" s="57" t="n"/>
@@ -28514,7 +28533,7 @@
       </c>
       <c r="CJ177" s="81" t="inlineStr">
         <is>
-          <t>The hail of bullets strips armour</t>
+          <t>Bullets punch through armour and strip it</t>
         </is>
       </c>
     </row>
@@ -33876,7 +33895,7 @@
       </c>
       <c r="M250" s="81" t="inlineStr">
         <is>
-          <t>Speed Loader</t>
+          <t>Loading Bench</t>
         </is>
       </c>
       <c r="AY250" s="81" t="n">
@@ -35534,1475 +35553,1475 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
+      <c r="A278" s="81" t="inlineStr">
         <is>
           <t>Tar Pit</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
+      <c r="B278" s="81" t="inlineStr">
         <is>
           <t>Deep Tar</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
+      <c r="C278" s="81" t="inlineStr">
         <is>
           <t>slow and sink</t>
         </is>
       </c>
-      <c r="D278" t="n">
+      <c r="D278" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E278">
+      <c r="E278" s="81">
         <f>E143</f>
         <v/>
       </c>
-      <c r="F278">
+      <c r="F278" s="81">
         <f>F143</f>
         <v/>
       </c>
-      <c r="G278" t="n">
-        <v>1</v>
-      </c>
-      <c r="H278" t="n">
-        <v>1</v>
-      </c>
-      <c r="I278" t="n">
-        <v>1</v>
-      </c>
-      <c r="L278" t="n">
-        <v>1</v>
-      </c>
-      <c r="M278" t="inlineStr">
+      <c r="G278" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H278" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I278" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L278" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M278" s="81" t="inlineStr">
         <is>
           <t>Thick Mire</t>
         </is>
       </c>
-      <c r="AE278" t="n">
+      <c r="AE278" s="81" t="n">
         <v>55</v>
       </c>
-      <c r="CI278" t="inlineStr">
+      <c r="CI278" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ278" t="inlineStr">
+      <c r="CJ278" s="81" t="inlineStr">
         <is>
           <t>Thicker tar: dinos wade much slower</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
+      <c r="A279" s="81" t="inlineStr">
         <is>
           <t>Tar Pit</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
+      <c r="B279" s="81" t="inlineStr">
         <is>
           <t>Deep Tar</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
+      <c r="C279" s="81" t="inlineStr">
         <is>
           <t>slow and sink</t>
         </is>
       </c>
-      <c r="D279" t="n">
+      <c r="D279" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E279">
+      <c r="E279" s="81">
         <f>E143</f>
         <v/>
       </c>
-      <c r="F279">
+      <c r="F279" s="81">
         <f>F143</f>
         <v/>
       </c>
-      <c r="G279" t="n">
-        <v>1</v>
-      </c>
-      <c r="H279" t="n">
-        <v>1</v>
-      </c>
-      <c r="I279" t="n">
-        <v>1</v>
-      </c>
-      <c r="L279" t="n">
+      <c r="G279" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H279" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I279" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L279" s="81" t="n">
         <v>1.5</v>
       </c>
-      <c r="M279" t="inlineStr">
+      <c r="M279" s="81" t="inlineStr">
         <is>
           <t>Bog Boots</t>
         </is>
       </c>
-      <c r="AE279" t="n">
+      <c r="AE279" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="CI279" t="inlineStr">
+      <c r="CI279" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ279" t="inlineStr">
+      <c r="CJ279" s="81" t="inlineStr">
         <is>
           <t>A longer pool that also slows raiders</t>
         </is>
       </c>
-      <c r="CK279" t="inlineStr">
+      <c r="CK279" s="81" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="CL279" t="n">
+      <c r="CL279" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="CM279" t="n">
+      <c r="CM279" s="81" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr">
+      <c r="A280" s="81" t="inlineStr">
         <is>
           <t>Tar Pit</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
+      <c r="B280" s="81" t="inlineStr">
         <is>
           <t>Deep Tar</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
+      <c r="C280" s="81" t="inlineStr">
         <is>
           <t>slow and sink</t>
         </is>
       </c>
-      <c r="D280" t="n">
+      <c r="D280" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E280">
+      <c r="E280" s="81">
         <f>E144</f>
         <v/>
       </c>
-      <c r="F280">
+      <c r="F280" s="81">
         <f>F144</f>
         <v/>
       </c>
-      <c r="G280" t="n">
-        <v>1</v>
-      </c>
-      <c r="H280" t="n">
-        <v>1</v>
-      </c>
-      <c r="I280" t="n">
-        <v>1</v>
-      </c>
-      <c r="L280" t="n">
+      <c r="G280" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H280" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I280" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L280" s="81" t="n">
         <v>1.15</v>
       </c>
-      <c r="M280" t="inlineStr">
+      <c r="M280" s="81" t="inlineStr">
         <is>
           <t>La Brea</t>
         </is>
       </c>
-      <c r="AE280" t="n">
+      <c r="AE280" s="81" t="n">
         <v>62</v>
       </c>
-      <c r="AF280" t="n">
+      <c r="AF280" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="CC280" t="n">
+      <c r="CC280" s="81" t="n">
         <v>0.05</v>
       </c>
-      <c r="CI280" t="inlineStr">
+      <c r="CI280" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ280" t="inlineStr">
+      <c r="CJ280" s="81" t="inlineStr">
         <is>
           <t>Smallest dinos sink at once; the rest crawl</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr">
+      <c r="A281" s="81" t="inlineStr">
         <is>
           <t>Tar Pit</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
+      <c r="B281" s="81" t="inlineStr">
         <is>
           <t>Deep Tar</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
+      <c r="C281" s="81" t="inlineStr">
         <is>
           <t>slow and sink</t>
         </is>
       </c>
-      <c r="D281" t="n">
+      <c r="D281" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E281">
+      <c r="E281" s="81">
         <f>E144</f>
         <v/>
       </c>
-      <c r="F281">
+      <c r="F281" s="81">
         <f>F144</f>
         <v/>
       </c>
-      <c r="G281" t="n">
-        <v>1</v>
-      </c>
-      <c r="H281" t="n">
-        <v>1</v>
-      </c>
-      <c r="I281" t="n">
-        <v>1</v>
-      </c>
-      <c r="L281" t="n">
-        <v>1</v>
-      </c>
-      <c r="M281" t="inlineStr">
+      <c r="G281" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H281" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I281" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L281" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M281" s="81" t="inlineStr">
         <is>
           <t>Black Glue</t>
         </is>
       </c>
-      <c r="AE281" t="n">
+      <c r="AE281" s="81" t="n">
         <v>50</v>
       </c>
-      <c r="AF281" t="n">
+      <c r="AF281" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="CI281" t="inlineStr">
+      <c r="CI281" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ281" t="inlineStr">
+      <c r="CJ281" s="81" t="inlineStr">
         <is>
           <t>Dinos stay slowed 5 s after they climb out</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr">
+      <c r="A282" s="81" t="inlineStr">
         <is>
           <t>Tar Pit</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
+      <c r="B282" s="81" t="inlineStr">
         <is>
           <t>Bubbling</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
+      <c r="C282" s="81" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="D282" t="n">
+      <c r="D282" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E282">
+      <c r="E282" s="81">
         <f>E148</f>
         <v/>
       </c>
-      <c r="F282">
+      <c r="F282" s="81">
         <f>F148</f>
         <v/>
       </c>
-      <c r="G282" t="n">
-        <v>1</v>
-      </c>
-      <c r="H282" t="n">
-        <v>1</v>
-      </c>
-      <c r="I282" t="n">
-        <v>1</v>
-      </c>
-      <c r="L282" t="n">
+      <c r="G282" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H282" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I282" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L282" s="81" t="n">
         <v>1.3</v>
       </c>
-      <c r="M282" t="inlineStr">
+      <c r="M282" s="81" t="inlineStr">
         <is>
           <t>Boiling Splash</t>
         </is>
       </c>
-      <c r="CI282" t="inlineStr">
+      <c r="CI282" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ282" t="inlineStr">
+      <c r="CJ282" s="81" t="inlineStr">
         <is>
           <t>A bigger pool of boiling tar</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr">
+      <c r="A283" s="81" t="inlineStr">
         <is>
           <t>Tar Pit</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
+      <c r="B283" s="81" t="inlineStr">
         <is>
           <t>Bubbling</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
+      <c r="C283" s="81" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="D283" t="n">
+      <c r="D283" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E283">
+      <c r="E283" s="81">
         <f>E148</f>
         <v/>
       </c>
-      <c r="F283">
+      <c r="F283" s="81">
         <f>F148</f>
         <v/>
       </c>
-      <c r="G283" t="n">
-        <v>1</v>
-      </c>
-      <c r="H283" t="n">
-        <v>1</v>
-      </c>
-      <c r="I283" t="n">
-        <v>1</v>
-      </c>
-      <c r="L283" t="n">
-        <v>1</v>
-      </c>
-      <c r="M283" t="inlineStr">
+      <c r="G283" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H283" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I283" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L283" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M283" s="81" t="inlineStr">
         <is>
           <t>Pitch Coat</t>
         </is>
       </c>
-      <c r="X283" t="n">
+      <c r="X283" s="81" t="n">
         <v>85</v>
       </c>
-      <c r="Y283" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM283" t="inlineStr">
+      <c r="Y283" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM283" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="CI283" t="inlineStr">
+      <c r="CI283" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ283" t="inlineStr">
+      <c r="CJ283" s="81" t="inlineStr">
         <is>
           <t>Sticky tar strips armour; dinos leave burning</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
+      <c r="A284" s="81" t="inlineStr">
         <is>
           <t>Tar Pit</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
+      <c r="B284" s="81" t="inlineStr">
         <is>
           <t>Bubbling</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
+      <c r="C284" s="81" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="D284" t="n">
+      <c r="D284" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E284">
+      <c r="E284" s="81">
         <f>E149</f>
         <v/>
       </c>
-      <c r="F284">
+      <c r="F284" s="81">
         <f>F149</f>
         <v/>
       </c>
-      <c r="G284" t="n">
-        <v>1</v>
-      </c>
-      <c r="H284" t="n">
-        <v>1</v>
-      </c>
-      <c r="I284" t="n">
-        <v>1</v>
-      </c>
-      <c r="L284" t="n">
-        <v>1</v>
-      </c>
-      <c r="M284" t="inlineStr">
+      <c r="G284" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H284" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I284" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L284" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M284" s="81" t="inlineStr">
         <is>
           <t>Ever-Burn</t>
         </is>
       </c>
-      <c r="Y284" t="n">
+      <c r="Y284" s="81" t="n">
         <v>2.75</v>
       </c>
-      <c r="CI284" t="inlineStr">
+      <c r="CI284" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ284" t="inlineStr">
+      <c r="CJ284" s="81" t="inlineStr">
         <is>
           <t>Dinos keep burning 2.75 s after they leave</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr">
+      <c r="A285" s="81" t="inlineStr">
         <is>
           <t>Tar Pit</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
+      <c r="B285" s="81" t="inlineStr">
         <is>
           <t>Bubbling</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
+      <c r="C285" s="81" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="D285" t="n">
+      <c r="D285" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E285">
+      <c r="E285" s="81">
         <f>E149</f>
         <v/>
       </c>
-      <c r="F285">
+      <c r="F285" s="81">
         <f>F149</f>
         <v/>
       </c>
-      <c r="G285" t="n">
-        <v>1</v>
-      </c>
-      <c r="H285" t="n">
-        <v>1</v>
-      </c>
-      <c r="I285" t="n">
-        <v>1</v>
-      </c>
-      <c r="L285" t="n">
-        <v>1</v>
-      </c>
-      <c r="M285" t="inlineStr">
+      <c r="G285" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H285" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I285" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L285" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M285" s="81" t="inlineStr">
         <is>
           <t>Tar Inferno</t>
         </is>
       </c>
-      <c r="X285" t="n">
+      <c r="X285" s="81" t="n">
         <v>120</v>
       </c>
-      <c r="CI285" t="inlineStr">
+      <c r="CI285" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ285" t="inlineStr">
+      <c r="CJ285" s="81" t="inlineStr">
         <is>
           <t>The tar boils 50% hotter</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
+      <c r="A286" s="81" t="inlineStr">
         <is>
           <t>Tar Pit</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
+      <c r="B286" s="81" t="inlineStr">
         <is>
           <t>Dig Site</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
+      <c r="C286" s="81" t="inlineStr">
         <is>
           <t>cash and support</t>
         </is>
       </c>
-      <c r="D286" t="n">
+      <c r="D286" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E286">
+      <c r="E286" s="81">
         <f>E153</f>
         <v/>
       </c>
-      <c r="F286">
+      <c r="F286" s="81">
         <f>F153</f>
         <v/>
       </c>
-      <c r="G286" t="n">
-        <v>1</v>
-      </c>
-      <c r="H286" t="n">
-        <v>1</v>
-      </c>
-      <c r="I286" t="n">
-        <v>1</v>
-      </c>
-      <c r="L286" t="n">
-        <v>1</v>
-      </c>
-      <c r="M286" t="inlineStr">
+      <c r="G286" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H286" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I286" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L286" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M286" s="81" t="inlineStr">
         <is>
           <t>Bone Yard</t>
         </is>
       </c>
-      <c r="CD286" t="n">
+      <c r="CD286" s="81" t="n">
         <v>28</v>
       </c>
-      <c r="CE286" t="n">
+      <c r="CE286" s="81" t="n">
         <v>36</v>
       </c>
-      <c r="CI286" t="inlineStr">
+      <c r="CI286" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ286" t="inlineStr">
+      <c r="CJ286" s="81" t="inlineStr">
         <is>
           <t>Every sunk dino pays more cash</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr">
+      <c r="A287" s="81" t="inlineStr">
         <is>
           <t>Tar Pit</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
+      <c r="B287" s="81" t="inlineStr">
         <is>
           <t>Dig Site</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr">
+      <c r="C287" s="81" t="inlineStr">
         <is>
           <t>cash and support</t>
         </is>
       </c>
-      <c r="D287" t="n">
+      <c r="D287" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E287">
+      <c r="E287" s="81">
         <f>E153</f>
         <v/>
       </c>
-      <c r="F287">
+      <c r="F287" s="81">
         <f>F153</f>
         <v/>
       </c>
-      <c r="G287" t="n">
-        <v>1</v>
-      </c>
-      <c r="H287" t="n">
-        <v>1</v>
-      </c>
-      <c r="I287" t="n">
-        <v>1</v>
-      </c>
-      <c r="L287" t="n">
-        <v>1</v>
-      </c>
-      <c r="M287" t="inlineStr">
+      <c r="G287" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H287" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I287" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L287" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M287" s="81" t="inlineStr">
         <is>
           <t>Fossil Finder</t>
         </is>
       </c>
-      <c r="CD287" t="n">
+      <c r="CD287" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="CE287" t="n">
+      <c r="CE287" s="81" t="n">
         <v>55</v>
       </c>
-      <c r="CI287" t="inlineStr">
+      <c r="CI287" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ287" t="inlineStr">
+      <c r="CJ287" s="81" t="inlineStr">
         <is>
           <t>Bigger chests where dinos go under</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr">
+      <c r="A288" s="81" t="inlineStr">
         <is>
           <t>Tar Pit</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
+      <c r="B288" s="81" t="inlineStr">
         <is>
           <t>Dig Site</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
+      <c r="C288" s="81" t="inlineStr">
         <is>
           <t>cash and support</t>
         </is>
       </c>
-      <c r="D288" t="n">
+      <c r="D288" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E288">
+      <c r="E288" s="81">
         <f>E154</f>
         <v/>
       </c>
-      <c r="F288">
+      <c r="F288" s="81">
         <f>F154</f>
         <v/>
       </c>
-      <c r="G288" t="n">
-        <v>1</v>
-      </c>
-      <c r="H288" t="n">
-        <v>1</v>
-      </c>
-      <c r="I288" t="n">
-        <v>1</v>
-      </c>
-      <c r="L288" t="n">
-        <v>1</v>
-      </c>
-      <c r="M288" t="inlineStr">
+      <c r="G288" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H288" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I288" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L288" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M288" s="81" t="inlineStr">
         <is>
           <t>Preserved Specimens</t>
         </is>
       </c>
-      <c r="CD288" t="n">
+      <c r="CD288" s="81" t="n">
         <v>36</v>
       </c>
-      <c r="CE288" t="n">
+      <c r="CE288" s="81" t="n">
         <v>40</v>
       </c>
-      <c r="CI288" t="inlineStr">
+      <c r="CI288" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ288" t="inlineStr">
+      <c r="CJ288" s="81" t="inlineStr">
         <is>
           <t>Every sunk dino pays 36 cash</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr">
+      <c r="A289" s="81" t="inlineStr">
         <is>
           <t>Tar Pit</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
+      <c r="B289" s="81" t="inlineStr">
         <is>
           <t>Dig Site</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr">
+      <c r="C289" s="81" t="inlineStr">
         <is>
           <t>cash and support</t>
         </is>
       </c>
-      <c r="D289" t="n">
+      <c r="D289" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E289">
+      <c r="E289" s="81">
         <f>E154</f>
         <v/>
       </c>
-      <c r="F289">
+      <c r="F289" s="81">
         <f>F154</f>
         <v/>
       </c>
-      <c r="G289" t="n">
-        <v>1</v>
-      </c>
-      <c r="H289" t="n">
-        <v>1</v>
-      </c>
-      <c r="I289" t="n">
-        <v>1</v>
-      </c>
-      <c r="L289" t="n">
-        <v>1</v>
-      </c>
-      <c r="M289" t="inlineStr">
+      <c r="G289" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H289" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I289" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L289" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M289" s="81" t="inlineStr">
         <is>
           <t>Amber Seep</t>
         </is>
       </c>
-      <c r="CD289" t="n">
+      <c r="CD289" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="CE289" t="n">
+      <c r="CE289" s="81" t="n">
         <v>60</v>
       </c>
-      <c r="CI289" t="inlineStr">
+      <c r="CI289" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ289" t="inlineStr">
+      <c r="CJ289" s="81" t="inlineStr">
         <is>
           <t>Chests where dinos sink are worth 60</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr">
+      <c r="A290" s="81" t="inlineStr">
         <is>
           <t>Harpoon Ballista</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
+      <c r="B290" s="81" t="inlineStr">
         <is>
           <t>Spearhead</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr">
+      <c r="C290" s="81" t="inlineStr">
         <is>
           <t>raw damage, breaks</t>
         </is>
       </c>
-      <c r="D290" t="n">
+      <c r="D290" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E290">
+      <c r="E290" s="81">
         <f>E158</f>
         <v/>
       </c>
-      <c r="F290">
+      <c r="F290" s="81">
         <f>F158</f>
         <v/>
       </c>
-      <c r="G290" t="n">
+      <c r="G290" s="81" t="n">
         <v>1.7</v>
       </c>
-      <c r="H290" t="n">
-        <v>1</v>
-      </c>
-      <c r="I290" t="n">
-        <v>1</v>
-      </c>
-      <c r="L290" t="n">
-        <v>1</v>
-      </c>
-      <c r="M290" t="inlineStr">
+      <c r="H290" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I290" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L290" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M290" s="81" t="inlineStr">
         <is>
           <t>Serrated Head</t>
         </is>
       </c>
-      <c r="N290" t="inlineStr">
+      <c r="N290" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T290" t="n">
+      <c r="T290" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="CI290" t="inlineStr">
+      <c r="CI290" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ290" t="inlineStr">
+      <c r="CJ290" s="81" t="inlineStr">
         <is>
           <t>Hit dinos take +20% from every tower</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr">
+      <c r="A291" s="81" t="inlineStr">
         <is>
           <t>Harpoon Ballista</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
+      <c r="B291" s="81" t="inlineStr">
         <is>
           <t>Spearhead</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr">
+      <c r="C291" s="81" t="inlineStr">
         <is>
           <t>raw damage, breaks</t>
         </is>
       </c>
-      <c r="D291" t="n">
+      <c r="D291" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E291">
+      <c r="E291" s="81">
         <f>E158</f>
         <v/>
       </c>
-      <c r="F291">
+      <c r="F291" s="81">
         <f>F158</f>
         <v/>
       </c>
-      <c r="G291" t="n">
+      <c r="G291" s="81" t="n">
         <v>1.6</v>
       </c>
-      <c r="H291" t="n">
-        <v>1</v>
-      </c>
-      <c r="I291" t="n">
-        <v>1</v>
-      </c>
-      <c r="L291" t="n">
-        <v>1</v>
-      </c>
-      <c r="M291" t="inlineStr">
+      <c r="H291" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I291" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L291" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M291" s="81" t="inlineStr">
         <is>
           <t>Whale Lance</t>
         </is>
       </c>
-      <c r="N291" t="inlineStr">
+      <c r="N291" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P291" t="n">
+      <c r="P291" s="81" t="n">
         <v>1.4</v>
       </c>
-      <c r="CI291" t="inlineStr">
+      <c r="CI291" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ291" t="inlineStr">
+      <c r="CJ291" s="81" t="inlineStr">
         <is>
           <t>Bolts hit bosses 40% harder</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr">
+      <c r="A292" s="81" t="inlineStr">
         <is>
           <t>Harpoon Ballista</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
+      <c r="B292" s="81" t="inlineStr">
         <is>
           <t>Spearhead</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr">
+      <c r="C292" s="81" t="inlineStr">
         <is>
           <t>raw damage, breaks</t>
         </is>
       </c>
-      <c r="D292" t="n">
+      <c r="D292" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E292">
+      <c r="E292" s="81">
         <f>E159</f>
         <v/>
       </c>
-      <c r="F292">
+      <c r="F292" s="81">
         <f>F159</f>
         <v/>
       </c>
-      <c r="G292" t="n">
+      <c r="G292" s="81" t="n">
         <v>2.5</v>
       </c>
-      <c r="H292" t="n">
+      <c r="H292" s="81" t="n">
         <v>1.4</v>
       </c>
-      <c r="I292" t="n">
-        <v>1</v>
-      </c>
-      <c r="L292" t="n">
-        <v>1</v>
-      </c>
-      <c r="M292" t="inlineStr">
+      <c r="I292" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L292" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M292" s="81" t="inlineStr">
         <is>
           <t>Leviathan Bolt</t>
         </is>
       </c>
-      <c r="P292" t="n">
+      <c r="P292" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="BJ292" t="n">
+      <c r="BJ292" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="CI292" t="inlineStr">
+      <c r="CI292" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ292" t="inlineStr">
+      <c r="CJ292" s="81" t="inlineStr">
         <is>
           <t>Bolts break 4 sizes and hit bosses 3x</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr">
+      <c r="A293" s="81" t="inlineStr">
         <is>
           <t>Harpoon Ballista</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
+      <c r="B293" s="81" t="inlineStr">
         <is>
           <t>Spearhead</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr">
+      <c r="C293" s="81" t="inlineStr">
         <is>
           <t>raw damage, breaks</t>
         </is>
       </c>
-      <c r="D293" t="n">
+      <c r="D293" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E293">
+      <c r="E293" s="81">
         <f>E159</f>
         <v/>
       </c>
-      <c r="F293">
+      <c r="F293" s="81">
         <f>F159</f>
         <v/>
       </c>
-      <c r="G293" t="n">
+      <c r="G293" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="H293" t="n">
+      <c r="H293" s="81" t="n">
         <v>2.1</v>
       </c>
-      <c r="I293" t="n">
-        <v>1</v>
-      </c>
-      <c r="L293" t="n">
-        <v>1</v>
-      </c>
-      <c r="M293" t="inlineStr">
+      <c r="I293" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L293" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M293" s="81" t="inlineStr">
         <is>
           <t>Heartseeker</t>
         </is>
       </c>
-      <c r="BJ293" t="n">
+      <c r="BJ293" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="CI293" t="inlineStr">
+      <c r="CI293" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ293" t="inlineStr">
+      <c r="CJ293" s="81" t="inlineStr">
         <is>
           <t>Always aims for the biggest dino in range</t>
         </is>
       </c>
-      <c r="CU293" t="inlineStr">
+      <c r="CU293" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr">
+      <c r="A294" s="81" t="inlineStr">
         <is>
           <t>Harpoon Ballista</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
+      <c r="B294" s="81" t="inlineStr">
         <is>
           <t>Reel</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr">
+      <c r="C294" s="81" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="D294" t="n">
+      <c r="D294" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E294">
+      <c r="E294" s="81">
         <f>E163</f>
         <v/>
       </c>
-      <c r="F294">
+      <c r="F294" s="81">
         <f>F163</f>
         <v/>
       </c>
-      <c r="G294" t="n">
+      <c r="G294" s="81" t="n">
         <v>1.3</v>
       </c>
-      <c r="H294" t="n">
-        <v>1</v>
-      </c>
-      <c r="I294" t="n">
-        <v>1</v>
-      </c>
-      <c r="L294" t="n">
-        <v>1</v>
-      </c>
-      <c r="M294" t="inlineStr">
+      <c r="H294" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I294" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L294" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M294" s="81" t="inlineStr">
         <is>
           <t>Tether</t>
         </is>
       </c>
-      <c r="U294" t="n">
+      <c r="U294" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="CI294" t="inlineStr">
+      <c r="CI294" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ294" t="inlineStr">
+      <c r="CJ294" s="81" t="inlineStr">
         <is>
           <t>Pinned dinos stay held 2 s</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr">
+      <c r="A295" s="81" t="inlineStr">
         <is>
           <t>Harpoon Ballista</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
+      <c r="B295" s="81" t="inlineStr">
         <is>
           <t>Reel</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr">
+      <c r="C295" s="81" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="D295" t="n">
+      <c r="D295" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E295">
+      <c r="E295" s="81">
         <f>E163</f>
         <v/>
       </c>
-      <c r="F295">
+      <c r="F295" s="81">
         <f>F163</f>
         <v/>
       </c>
-      <c r="G295" t="n">
+      <c r="G295" s="81" t="n">
         <v>1.3</v>
       </c>
-      <c r="H295" t="n">
-        <v>1</v>
-      </c>
-      <c r="I295" t="n">
-        <v>1</v>
-      </c>
-      <c r="L295" t="n">
-        <v>1</v>
-      </c>
-      <c r="M295" t="inlineStr">
+      <c r="H295" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I295" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L295" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M295" s="81" t="inlineStr">
         <is>
           <t>Snag Line</t>
         </is>
       </c>
-      <c r="U295" t="n">
+      <c r="U295" s="81" t="n">
         <v>1.75</v>
       </c>
-      <c r="CI295" t="inlineStr">
+      <c r="CI295" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ295" t="inlineStr">
+      <c r="CJ295" s="81" t="inlineStr">
         <is>
           <t>Harpoons raiders too; holds dinos 1.75 s</t>
         </is>
       </c>
-      <c r="CK295" t="inlineStr">
+      <c r="CK295" s="81" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="CL295" t="n">
+      <c r="CL295" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="CM295" t="n">
+      <c r="CM295" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="CN295" t="n">
+      <c r="CN295" s="81" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr">
+      <c r="A296" s="81" t="inlineStr">
         <is>
           <t>Harpoon Ballista</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
+      <c r="B296" s="81" t="inlineStr">
         <is>
           <t>Reel</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr">
+      <c r="C296" s="81" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="D296" t="n">
+      <c r="D296" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E296">
+      <c r="E296" s="81">
         <f>E164</f>
         <v/>
       </c>
-      <c r="F296">
+      <c r="F296" s="81">
         <f>F164</f>
         <v/>
       </c>
-      <c r="G296" t="n">
+      <c r="G296" s="81" t="n">
         <v>1.3</v>
       </c>
-      <c r="H296" t="n">
-        <v>1</v>
-      </c>
-      <c r="I296" t="n">
-        <v>1</v>
-      </c>
-      <c r="L296" t="n">
-        <v>1</v>
-      </c>
-      <c r="M296" t="inlineStr">
+      <c r="H296" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I296" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L296" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M296" s="81" t="inlineStr">
         <is>
           <t>Anchor Line</t>
         </is>
       </c>
-      <c r="AE296" t="n">
+      <c r="AE296" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="AF296" t="n">
+      <c r="AF296" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="AG296" t="inlineStr">
+      <c r="AG296" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="CI296" t="inlineStr">
+      <c r="CI296" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ296" t="inlineStr">
+      <c r="CJ296" s="81" t="inlineStr">
         <is>
           <t>Bolts slow bosses too: 30% for 2 s</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr">
+      <c r="A297" s="81" t="inlineStr">
         <is>
           <t>Harpoon Ballista</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
+      <c r="B297" s="81" t="inlineStr">
         <is>
           <t>Reel</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr">
+      <c r="C297" s="81" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="D297" t="n">
+      <c r="D297" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E297">
+      <c r="E297" s="81">
         <f>E164</f>
         <v/>
       </c>
-      <c r="F297">
+      <c r="F297" s="81">
         <f>F164</f>
         <v/>
       </c>
-      <c r="G297" t="n">
+      <c r="G297" s="81" t="n">
         <v>1.3</v>
       </c>
-      <c r="H297" t="n">
-        <v>1</v>
-      </c>
-      <c r="I297" t="n">
-        <v>1</v>
-      </c>
-      <c r="L297" t="n">
-        <v>1</v>
-      </c>
-      <c r="M297" t="inlineStr">
+      <c r="H297" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I297" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L297" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M297" s="81" t="inlineStr">
         <is>
           <t>Winch Haul</t>
         </is>
       </c>
-      <c r="W297" t="n">
+      <c r="W297" s="81" t="n">
         <v>7.5</v>
       </c>
-      <c r="CI297" t="inlineStr">
+      <c r="CI297" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ297" t="inlineStr">
+      <c r="CJ297" s="81" t="inlineStr">
         <is>
           <t>Drags hit dinos 7.5 studs back</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr">
+      <c r="A298" s="81" t="inlineStr">
         <is>
           <t>Harpoon Ballista</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
+      <c r="B298" s="81" t="inlineStr">
         <is>
           <t>Volley</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr">
+      <c r="C298" s="81" t="inlineStr">
         <is>
           <t>more bolts</t>
         </is>
       </c>
-      <c r="D298" t="n">
+      <c r="D298" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E298">
+      <c r="E298" s="81">
         <f>E168</f>
         <v/>
       </c>
-      <c r="F298">
+      <c r="F298" s="81">
         <f>F168</f>
         <v/>
       </c>
-      <c r="G298" t="n">
+      <c r="G298" s="81" t="n">
         <v>1.15</v>
       </c>
-      <c r="H298" t="n">
-        <v>1</v>
-      </c>
-      <c r="I298" t="n">
-        <v>1</v>
-      </c>
-      <c r="L298" t="n">
-        <v>1</v>
-      </c>
-      <c r="M298" t="inlineStr">
+      <c r="H298" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I298" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L298" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M298" s="81" t="inlineStr">
         <is>
           <t>Wide Volley</t>
         </is>
       </c>
-      <c r="Q298" t="n">
+      <c r="Q298" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="CI298" t="inlineStr">
+      <c r="CI298" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ298" t="inlineStr">
+      <c r="CJ298" s="81" t="inlineStr">
         <is>
           <t>Five bolts per volley</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr">
+      <c r="A299" s="81" t="inlineStr">
         <is>
           <t>Harpoon Ballista</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
+      <c r="B299" s="81" t="inlineStr">
         <is>
           <t>Volley</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr">
+      <c r="C299" s="81" t="inlineStr">
         <is>
           <t>more bolts</t>
         </is>
       </c>
-      <c r="D299" t="n">
+      <c r="D299" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E299">
+      <c r="E299" s="81">
         <f>E168</f>
         <v/>
       </c>
-      <c r="F299">
+      <c r="F299" s="81">
         <f>F168</f>
         <v/>
       </c>
-      <c r="G299" t="n">
-        <v>1</v>
-      </c>
-      <c r="H299" t="n">
+      <c r="G299" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H299" s="81" t="n">
         <v>1.6</v>
       </c>
-      <c r="I299" t="n">
-        <v>1</v>
-      </c>
-      <c r="L299" t="n">
-        <v>1</v>
-      </c>
-      <c r="M299" t="inlineStr">
+      <c r="I299" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L299" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M299" s="81" t="inlineStr">
         <is>
           <t>Fire Bolts</t>
         </is>
       </c>
-      <c r="X299" t="n">
+      <c r="X299" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="Y299" t="n">
+      <c r="Y299" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="CI299" t="inlineStr">
+      <c r="CI299" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ299" t="inlineStr">
+      <c r="CJ299" s="81" t="inlineStr">
         <is>
           <t>Bolts set dinos on fire</t>
         </is>
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr">
+      <c r="A300" s="81" t="inlineStr">
         <is>
           <t>Harpoon Ballista</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B300" s="81" t="inlineStr">
         <is>
           <t>Volley</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
+      <c r="C300" s="81" t="inlineStr">
         <is>
           <t>more bolts</t>
         </is>
       </c>
-      <c r="D300" t="n">
+      <c r="D300" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E300">
+      <c r="E300" s="81">
         <f>E169</f>
         <v/>
       </c>
-      <c r="F300">
+      <c r="F300" s="81">
         <f>F169</f>
         <v/>
       </c>
-      <c r="G300" t="n">
+      <c r="G300" s="81" t="n">
         <v>2.4</v>
       </c>
-      <c r="H300" t="n">
-        <v>1</v>
-      </c>
-      <c r="I300" t="n">
-        <v>1</v>
-      </c>
-      <c r="L300" t="n">
-        <v>1</v>
-      </c>
-      <c r="M300" t="inlineStr">
+      <c r="H300" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I300" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L300" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M300" s="81" t="inlineStr">
         <is>
           <t>Siege Battery</t>
         </is>
       </c>
-      <c r="Q300" t="n">
+      <c r="Q300" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="CI300" t="inlineStr">
+      <c r="CI300" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ300" t="inlineStr">
+      <c r="CJ300" s="81" t="inlineStr">
         <is>
           <t>Six bolts per volley</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr">
+      <c r="A301" s="81" t="inlineStr">
         <is>
           <t>Harpoon Ballista</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B301" s="81" t="inlineStr">
         <is>
           <t>Volley</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
+      <c r="C301" s="81" t="inlineStr">
         <is>
           <t>more bolts</t>
         </is>
       </c>
-      <c r="D301" t="n">
+      <c r="D301" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E301">
+      <c r="E301" s="81">
         <f>E169</f>
         <v/>
       </c>
-      <c r="F301">
+      <c r="F301" s="81">
         <f>F169</f>
         <v/>
       </c>
-      <c r="G301" t="n">
+      <c r="G301" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="H301" t="n">
+      <c r="H301" s="81" t="n">
         <v>1.8</v>
       </c>
-      <c r="I301" t="n">
-        <v>1</v>
-      </c>
-      <c r="L301" t="n">
-        <v>1</v>
-      </c>
-      <c r="M301" t="inlineStr">
+      <c r="I301" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L301" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M301" s="81" t="inlineStr">
         <is>
           <t>Firestorm Volley</t>
         </is>
       </c>
-      <c r="X301" t="n">
+      <c r="X301" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="Y301" t="n">
+      <c r="Y301" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="CI301" t="inlineStr">
+      <c r="CI301" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ301" t="inlineStr">
+      <c r="CJ301" s="81" t="inlineStr">
         <is>
           <t>Faster volleys of burning bolts</t>
         </is>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -37632,7 +37632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC76"/>
+  <dimension ref="A1:CA88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="90" min="1" max="1"/>
@@ -42920,6 +42920,878 @@
       </c>
       <c r="AR76" s="81" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="43" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="B77" s="43" t="inlineStr">
+        <is>
+          <t>Gunslinger</t>
+        </is>
+      </c>
+      <c r="C77" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D77" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" s="43" t="inlineStr">
+        <is>
+          <t>Deep Cylinders</t>
+        </is>
+      </c>
+      <c r="F77" s="56">
+        <f>F8</f>
+        <v/>
+      </c>
+      <c r="G77" s="57" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H77" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I77" s="57" t="n"/>
+      <c r="J77" s="57" t="n"/>
+      <c r="K77" s="57" t="n"/>
+      <c r="L77" s="57" t="n"/>
+      <c r="M77" s="57" t="n"/>
+      <c r="N77" s="57" t="n"/>
+      <c r="O77" s="57" t="n"/>
+      <c r="P77" s="57" t="n"/>
+      <c r="Q77" s="57" t="n"/>
+      <c r="R77" s="57" t="n"/>
+      <c r="S77" s="57" t="n"/>
+      <c r="T77" s="57" t="n"/>
+      <c r="U77" s="57" t="n"/>
+      <c r="V77" s="57" t="n"/>
+      <c r="W77" s="57" t="n"/>
+      <c r="X77" s="57" t="n"/>
+      <c r="Y77" s="57" t="n"/>
+      <c r="Z77" s="57" t="n"/>
+      <c r="AA77" s="57" t="n"/>
+      <c r="AB77" s="57" t="n"/>
+      <c r="AC77" s="57" t="n"/>
+      <c r="AD77" s="57" t="n"/>
+      <c r="AE77" s="57" t="n"/>
+      <c r="AF77" s="57" t="n"/>
+      <c r="AG77" s="57" t="n"/>
+      <c r="AH77" s="57" t="n"/>
+      <c r="AI77" s="57" t="n"/>
+      <c r="BB77" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC77" s="81" t="inlineStr">
+        <is>
+          <t>Both guns hold 50% more and fire 15% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="43" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="B78" s="43" t="inlineStr">
+        <is>
+          <t>Gunslinger</t>
+        </is>
+      </c>
+      <c r="C78" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D78" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E78" s="43" t="inlineStr">
+        <is>
+          <t>Crossdraw</t>
+        </is>
+      </c>
+      <c r="F78" s="56">
+        <f>F8</f>
+        <v/>
+      </c>
+      <c r="G78" s="57" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H78" s="57" t="n"/>
+      <c r="I78" s="57" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J78" s="57" t="n"/>
+      <c r="K78" s="57" t="n"/>
+      <c r="L78" s="57" t="n"/>
+      <c r="M78" s="57" t="n"/>
+      <c r="N78" s="57" t="n"/>
+      <c r="O78" s="57" t="n"/>
+      <c r="P78" s="57" t="n"/>
+      <c r="Q78" s="57" t="n"/>
+      <c r="R78" s="57" t="n"/>
+      <c r="S78" s="57" t="n"/>
+      <c r="T78" s="57" t="n"/>
+      <c r="U78" s="57" t="n"/>
+      <c r="V78" s="57" t="n"/>
+      <c r="W78" s="57" t="n"/>
+      <c r="X78" s="57" t="n"/>
+      <c r="Y78" s="57" t="n"/>
+      <c r="Z78" s="57" t="n"/>
+      <c r="AA78" s="57" t="n"/>
+      <c r="AB78" s="57" t="n"/>
+      <c r="AC78" s="57" t="n"/>
+      <c r="AD78" s="57" t="n"/>
+      <c r="AE78" s="57" t="n"/>
+      <c r="AF78" s="57" t="n"/>
+      <c r="AG78" s="57" t="n"/>
+      <c r="AH78" s="57" t="n"/>
+      <c r="AI78" s="57" t="n"/>
+      <c r="BB78" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC78" s="81" t="inlineStr">
+        <is>
+          <t>Reload 35% faster, fire 15% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="43" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="B79" s="43" t="inlineStr">
+        <is>
+          <t>Gunslinger</t>
+        </is>
+      </c>
+      <c r="C79" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D79" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E79" s="43" t="inlineStr">
+        <is>
+          <t>Twin Burst</t>
+        </is>
+      </c>
+      <c r="F79" s="56">
+        <f>F9</f>
+        <v/>
+      </c>
+      <c r="G79" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H79" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I79" s="57" t="n"/>
+      <c r="J79" s="57" t="n"/>
+      <c r="K79" s="57" t="n"/>
+      <c r="L79" s="57" t="n"/>
+      <c r="M79" s="57" t="n"/>
+      <c r="N79" s="57" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="O79" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="P79" s="57" t="n"/>
+      <c r="Q79" s="57" t="n"/>
+      <c r="R79" s="57" t="n"/>
+      <c r="S79" s="57" t="n"/>
+      <c r="T79" s="57" t="n"/>
+      <c r="U79" s="57" t="n"/>
+      <c r="V79" s="57" t="n"/>
+      <c r="W79" s="57" t="n"/>
+      <c r="X79" s="57" t="n"/>
+      <c r="Y79" s="57" t="n"/>
+      <c r="Z79" s="57" t="n"/>
+      <c r="AA79" s="57" t="n"/>
+      <c r="AB79" s="57" t="n"/>
+      <c r="AC79" s="57" t="n"/>
+      <c r="AD79" s="57" t="n"/>
+      <c r="AE79" s="57" t="n"/>
+      <c r="AF79" s="57" t="n"/>
+      <c r="AG79" s="57" t="n"/>
+      <c r="AH79" s="57" t="n"/>
+      <c r="AI79" s="57" t="n"/>
+      <c r="BB79" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC79" s="81" t="inlineStr">
+        <is>
+          <t>Each click fires a 3-round burst, 30% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="43" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="B80" s="43" t="inlineStr">
+        <is>
+          <t>Gunslinger</t>
+        </is>
+      </c>
+      <c r="C80" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D80" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E80" s="43" t="inlineStr">
+        <is>
+          <t>Steady Pair</t>
+        </is>
+      </c>
+      <c r="F80" s="56">
+        <f>F9</f>
+        <v/>
+      </c>
+      <c r="G80" s="57" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H80" s="57" t="n"/>
+      <c r="I80" s="57" t="n"/>
+      <c r="J80" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K80" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L80" s="57" t="n"/>
+      <c r="M80" s="57" t="n"/>
+      <c r="N80" s="57" t="n"/>
+      <c r="O80" s="57" t="n"/>
+      <c r="P80" s="57" t="n"/>
+      <c r="Q80" s="57" t="n"/>
+      <c r="R80" s="57" t="n"/>
+      <c r="S80" s="57" t="n"/>
+      <c r="T80" s="57" t="n"/>
+      <c r="U80" s="57" t="n"/>
+      <c r="V80" s="57" t="n"/>
+      <c r="W80" s="57" t="n"/>
+      <c r="X80" s="57" t="n"/>
+      <c r="Y80" s="57" t="n"/>
+      <c r="Z80" s="57" t="n"/>
+      <c r="AA80" s="57" t="n"/>
+      <c r="AB80" s="57" t="n"/>
+      <c r="AC80" s="57" t="n"/>
+      <c r="AD80" s="57" t="n"/>
+      <c r="AE80" s="57" t="n"/>
+      <c r="AF80" s="57" t="n"/>
+      <c r="AG80" s="57" t="n"/>
+      <c r="AH80" s="57" t="n"/>
+      <c r="AI80" s="57" t="n"/>
+      <c r="BB80" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC80" s="81" t="inlineStr">
+        <is>
+          <t>Half the kick, tighter aim, 10% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="43" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="B81" s="43" t="inlineStr">
+        <is>
+          <t>Marksman</t>
+        </is>
+      </c>
+      <c r="C81" s="43" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D81" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" s="43" t="inlineStr">
+        <is>
+          <t>Quick Cock</t>
+        </is>
+      </c>
+      <c r="F81" s="56">
+        <f>F13</f>
+        <v/>
+      </c>
+      <c r="G81" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H81" s="57" t="n"/>
+      <c r="I81" s="57" t="n"/>
+      <c r="J81" s="57" t="n"/>
+      <c r="K81" s="57" t="n"/>
+      <c r="L81" s="57" t="n"/>
+      <c r="M81" s="57" t="n"/>
+      <c r="N81" s="57" t="n"/>
+      <c r="O81" s="57" t="n"/>
+      <c r="P81" s="57" t="n"/>
+      <c r="Q81" s="57" t="n"/>
+      <c r="R81" s="57" t="n"/>
+      <c r="S81" s="57" t="n"/>
+      <c r="T81" s="57" t="n"/>
+      <c r="U81" s="57" t="n"/>
+      <c r="V81" s="57" t="n"/>
+      <c r="W81" s="57" t="n"/>
+      <c r="X81" s="57" t="n"/>
+      <c r="Y81" s="57" t="n"/>
+      <c r="Z81" s="57" t="n"/>
+      <c r="AA81" s="57" t="n"/>
+      <c r="AB81" s="57" t="n"/>
+      <c r="AC81" s="57" t="n"/>
+      <c r="AD81" s="57" t="n"/>
+      <c r="AE81" s="57" t="n"/>
+      <c r="AF81" s="57" t="n"/>
+      <c r="AG81" s="57" t="n"/>
+      <c r="AH81" s="57" t="n"/>
+      <c r="AI81" s="57" t="n"/>
+      <c r="BB81" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC81" s="81" t="inlineStr">
+        <is>
+          <t>Fire 20% faster, scope and all</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="43" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="B82" s="43" t="inlineStr">
+        <is>
+          <t>Marksman</t>
+        </is>
+      </c>
+      <c r="C82" s="43" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D82" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E82" s="43" t="inlineStr">
+        <is>
+          <t>Breath Control</t>
+        </is>
+      </c>
+      <c r="F82" s="56">
+        <f>F13</f>
+        <v/>
+      </c>
+      <c r="G82" s="57" t="n"/>
+      <c r="H82" s="57" t="n"/>
+      <c r="I82" s="57" t="n"/>
+      <c r="J82" s="57" t="n"/>
+      <c r="K82" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L82" s="57" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M82" s="57" t="n"/>
+      <c r="N82" s="57" t="n"/>
+      <c r="O82" s="57" t="n"/>
+      <c r="P82" s="57" t="n"/>
+      <c r="Q82" s="57" t="n"/>
+      <c r="R82" s="57" t="n"/>
+      <c r="S82" s="57" t="n"/>
+      <c r="T82" s="57" t="n"/>
+      <c r="U82" s="57" t="n"/>
+      <c r="V82" s="57" t="n"/>
+      <c r="W82" s="57" t="n"/>
+      <c r="X82" s="57" t="n"/>
+      <c r="Y82" s="57" t="n"/>
+      <c r="Z82" s="57" t="n"/>
+      <c r="AA82" s="57" t="n"/>
+      <c r="AB82" s="57" t="n"/>
+      <c r="AC82" s="57" t="n"/>
+      <c r="AD82" s="57" t="n"/>
+      <c r="AE82" s="57" t="n"/>
+      <c r="AF82" s="57" t="n"/>
+      <c r="AG82" s="57" t="n"/>
+      <c r="AH82" s="57" t="n"/>
+      <c r="AI82" s="57" t="n"/>
+      <c r="BB82" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC82" s="81" t="inlineStr">
+        <is>
+          <t>Half the kick; the scope reaches 35% further</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="43" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="B83" s="43" t="inlineStr">
+        <is>
+          <t>Marksman</t>
+        </is>
+      </c>
+      <c r="C83" s="43" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D83" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E83" s="43" t="inlineStr">
+        <is>
+          <t>Quick Scope</t>
+        </is>
+      </c>
+      <c r="F83" s="56">
+        <f>F14</f>
+        <v/>
+      </c>
+      <c r="G83" s="57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H83" s="57" t="n"/>
+      <c r="I83" s="57" t="n"/>
+      <c r="J83" s="57" t="n"/>
+      <c r="K83" s="57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L83" s="57" t="n"/>
+      <c r="M83" s="57" t="n"/>
+      <c r="N83" s="57" t="n"/>
+      <c r="O83" s="57" t="n"/>
+      <c r="P83" s="57" t="n"/>
+      <c r="Q83" s="57" t="n"/>
+      <c r="R83" s="57" t="n"/>
+      <c r="S83" s="57" t="n"/>
+      <c r="T83" s="57" t="n"/>
+      <c r="U83" s="57" t="n"/>
+      <c r="V83" s="57" t="n"/>
+      <c r="W83" s="57" t="n"/>
+      <c r="X83" s="57" t="n"/>
+      <c r="Y83" s="57" t="n"/>
+      <c r="Z83" s="57" t="n"/>
+      <c r="AA83" s="57" t="n"/>
+      <c r="AB83" s="57" t="n"/>
+      <c r="AC83" s="57" t="n"/>
+      <c r="AD83" s="57" t="n"/>
+      <c r="AE83" s="57" t="n"/>
+      <c r="AF83" s="57" t="n"/>
+      <c r="AG83" s="57" t="n"/>
+      <c r="AH83" s="57" t="n"/>
+      <c r="AI83" s="57" t="n"/>
+      <c r="BB83" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC83" s="81" t="inlineStr">
+        <is>
+          <t>Fire 70% faster with 30% less kick</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="43" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="B84" s="43" t="inlineStr">
+        <is>
+          <t>Marksman</t>
+        </is>
+      </c>
+      <c r="C84" s="43" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D84" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E84" s="43" t="inlineStr">
+        <is>
+          <t>Hunter's Mark</t>
+        </is>
+      </c>
+      <c r="F84" s="56">
+        <f>F14</f>
+        <v/>
+      </c>
+      <c r="G84" s="57" t="n"/>
+      <c r="H84" s="57" t="n"/>
+      <c r="I84" s="57" t="n"/>
+      <c r="J84" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K84" s="57" t="n"/>
+      <c r="L84" s="57" t="n"/>
+      <c r="M84" s="57" t="n"/>
+      <c r="N84" s="57" t="n"/>
+      <c r="O84" s="57" t="n"/>
+      <c r="P84" s="57" t="n"/>
+      <c r="Q84" s="57" t="n"/>
+      <c r="R84" s="57" t="n"/>
+      <c r="S84" s="57" t="n"/>
+      <c r="T84" s="57" t="n"/>
+      <c r="U84" s="57" t="n"/>
+      <c r="V84" s="57" t="n"/>
+      <c r="W84" s="57" t="n"/>
+      <c r="X84" s="57" t="n"/>
+      <c r="Y84" s="57" t="n"/>
+      <c r="Z84" s="57" t="n"/>
+      <c r="AA84" s="57" t="n">
+        <v>35</v>
+      </c>
+      <c r="AB84" s="57" t="n"/>
+      <c r="AC84" s="57" t="n"/>
+      <c r="AD84" s="57" t="n"/>
+      <c r="AE84" s="57" t="n"/>
+      <c r="AF84" s="57" t="n"/>
+      <c r="AG84" s="57" t="n"/>
+      <c r="AH84" s="57" t="n"/>
+      <c r="AI84" s="57" t="n"/>
+      <c r="BB84" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC84" s="81" t="inlineStr">
+        <is>
+          <t>Hits mark dinos: +35% from everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="43" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="B85" s="43" t="inlineStr">
+        <is>
+          <t>Trick Shot</t>
+        </is>
+      </c>
+      <c r="C85" s="43" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="D85" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E85" s="43" t="inlineStr">
+        <is>
+          <t>Bank Shot</t>
+        </is>
+      </c>
+      <c r="F85" s="56">
+        <f>F18</f>
+        <v/>
+      </c>
+      <c r="G85" s="57" t="n"/>
+      <c r="H85" s="57" t="n"/>
+      <c r="I85" s="57" t="n"/>
+      <c r="J85" s="57" t="n"/>
+      <c r="K85" s="57" t="n"/>
+      <c r="L85" s="57" t="n"/>
+      <c r="M85" s="57" t="n"/>
+      <c r="N85" s="57" t="n"/>
+      <c r="O85" s="57" t="n"/>
+      <c r="P85" s="57" t="n"/>
+      <c r="Q85" s="57" t="n"/>
+      <c r="R85" s="57" t="n"/>
+      <c r="S85" s="57" t="n"/>
+      <c r="T85" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" s="57" t="n"/>
+      <c r="V85" s="57" t="n"/>
+      <c r="W85" s="57" t="n"/>
+      <c r="X85" s="57" t="n"/>
+      <c r="Y85" s="57" t="n"/>
+      <c r="Z85" s="57" t="n"/>
+      <c r="AA85" s="57" t="n"/>
+      <c r="AB85" s="57" t="n"/>
+      <c r="AC85" s="57" t="n"/>
+      <c r="AD85" s="57" t="n"/>
+      <c r="AE85" s="57" t="n"/>
+      <c r="AF85" s="57" t="n"/>
+      <c r="AG85" s="57" t="n"/>
+      <c r="AH85" s="57" t="n"/>
+      <c r="AI85" s="57" t="n"/>
+      <c r="BB85" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC85" s="81" t="inlineStr">
+        <is>
+          <t>Ricochets bounce twice</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="43" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="B86" s="43" t="inlineStr">
+        <is>
+          <t>Trick Shot</t>
+        </is>
+      </c>
+      <c r="C86" s="43" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="D86" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E86" s="43" t="inlineStr">
+        <is>
+          <t>Quick Fingers</t>
+        </is>
+      </c>
+      <c r="F86" s="56">
+        <f>F18</f>
+        <v/>
+      </c>
+      <c r="G86" s="57" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H86" s="57" t="n"/>
+      <c r="I86" s="57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J86" s="57" t="n"/>
+      <c r="K86" s="57" t="n"/>
+      <c r="L86" s="57" t="n"/>
+      <c r="M86" s="57" t="n"/>
+      <c r="N86" s="57" t="n"/>
+      <c r="O86" s="57" t="n"/>
+      <c r="P86" s="57" t="n"/>
+      <c r="Q86" s="57" t="n"/>
+      <c r="R86" s="57" t="n"/>
+      <c r="S86" s="57" t="n"/>
+      <c r="T86" s="57" t="n"/>
+      <c r="U86" s="57" t="n"/>
+      <c r="V86" s="57" t="n"/>
+      <c r="W86" s="57" t="n"/>
+      <c r="X86" s="57" t="n"/>
+      <c r="Y86" s="57" t="n"/>
+      <c r="Z86" s="57" t="n"/>
+      <c r="AA86" s="57" t="n"/>
+      <c r="AB86" s="57" t="n"/>
+      <c r="AC86" s="57" t="n"/>
+      <c r="AD86" s="57" t="n"/>
+      <c r="AE86" s="57" t="n"/>
+      <c r="AF86" s="57" t="n"/>
+      <c r="AG86" s="57" t="n"/>
+      <c r="AH86" s="57" t="n"/>
+      <c r="AI86" s="57" t="n"/>
+      <c r="BB86" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC86" s="81" t="inlineStr">
+        <is>
+          <t>Reload 30% faster, fire a bit faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="43" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="B87" s="43" t="inlineStr">
+        <is>
+          <t>Trick Shot</t>
+        </is>
+      </c>
+      <c r="C87" s="43" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="D87" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E87" s="43" t="inlineStr">
+        <is>
+          <t>Pinball</t>
+        </is>
+      </c>
+      <c r="F87" s="56">
+        <f>F19</f>
+        <v/>
+      </c>
+      <c r="G87" s="57" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H87" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I87" s="57" t="n"/>
+      <c r="J87" s="57" t="n"/>
+      <c r="K87" s="57" t="n"/>
+      <c r="L87" s="57" t="n"/>
+      <c r="M87" s="57" t="n"/>
+      <c r="N87" s="57" t="n"/>
+      <c r="O87" s="57" t="n"/>
+      <c r="P87" s="57" t="n"/>
+      <c r="Q87" s="57" t="n"/>
+      <c r="R87" s="57" t="n"/>
+      <c r="S87" s="57" t="n"/>
+      <c r="T87" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U87" s="57" t="n"/>
+      <c r="V87" s="57" t="n"/>
+      <c r="W87" s="57" t="n"/>
+      <c r="X87" s="57" t="n"/>
+      <c r="Y87" s="57" t="n"/>
+      <c r="Z87" s="57" t="n"/>
+      <c r="AA87" s="57" t="n"/>
+      <c r="AB87" s="57" t="n"/>
+      <c r="AC87" s="57" t="n"/>
+      <c r="AD87" s="57" t="n"/>
+      <c r="AE87" s="57" t="n"/>
+      <c r="AF87" s="57" t="n"/>
+      <c r="AG87" s="57" t="n"/>
+      <c r="AH87" s="57" t="n"/>
+      <c r="AI87" s="57" t="n"/>
+      <c r="BB87" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC87" s="81" t="inlineStr">
+        <is>
+          <t>3 bounces, a bigger cylinder, faster shots</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="43" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="B88" s="43" t="inlineStr">
+        <is>
+          <t>Trick Shot</t>
+        </is>
+      </c>
+      <c r="C88" s="43" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="D88" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E88" s="43" t="inlineStr">
+        <is>
+          <t>Dart Storm</t>
+        </is>
+      </c>
+      <c r="F88" s="56">
+        <f>F19</f>
+        <v/>
+      </c>
+      <c r="G88" s="57" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H88" s="57" t="n"/>
+      <c r="I88" s="57" t="n"/>
+      <c r="J88" s="57" t="n"/>
+      <c r="K88" s="57" t="n"/>
+      <c r="L88" s="57" t="n"/>
+      <c r="M88" s="57" t="n"/>
+      <c r="N88" s="57" t="n"/>
+      <c r="O88" s="57" t="n"/>
+      <c r="P88" s="57" t="n"/>
+      <c r="Q88" s="57" t="n"/>
+      <c r="R88" s="57" t="n"/>
+      <c r="S88" s="57" t="n"/>
+      <c r="T88" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U88" s="57" t="n"/>
+      <c r="V88" s="57" t="n"/>
+      <c r="W88" s="57" t="n"/>
+      <c r="X88" s="57" t="n"/>
+      <c r="Y88" s="57" t="n"/>
+      <c r="Z88" s="57" t="n"/>
+      <c r="AA88" s="57" t="n"/>
+      <c r="AB88" s="57" t="n"/>
+      <c r="AC88" s="57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD88" s="57" t="n"/>
+      <c r="AE88" s="57" t="n"/>
+      <c r="AF88" s="57" t="n"/>
+      <c r="AG88" s="57" t="n"/>
+      <c r="AH88" s="57" t="n"/>
+      <c r="AI88" s="57" t="n"/>
+      <c r="BB88" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC88" s="81" t="inlineStr">
+        <is>
+          <t>3 bounces, faster shots, Tracking Dart sooner</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -37632,7 +37632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA88"/>
+  <dimension ref="A1:CA100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="90" min="1" max="1"/>
@@ -43791,6 +43791,870 @@
       <c r="BC88" s="81" t="inlineStr">
         <is>
           <t>3 bounces, faster shots, Tracking Dart sooner</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="43" t="inlineStr">
+        <is>
+          <t>Big Game Hunter</t>
+        </is>
+      </c>
+      <c r="B89" s="43" t="inlineStr">
+        <is>
+          <t>Stalker</t>
+        </is>
+      </c>
+      <c r="C89" s="43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D89" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E89" s="43" t="inlineStr">
+        <is>
+          <t>Snap Bursts</t>
+        </is>
+      </c>
+      <c r="F89" s="56">
+        <f>F23</f>
+        <v/>
+      </c>
+      <c r="G89" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H89" s="57" t="n"/>
+      <c r="I89" s="57" t="n"/>
+      <c r="J89" s="57" t="n"/>
+      <c r="K89" s="57" t="n"/>
+      <c r="L89" s="57" t="n"/>
+      <c r="M89" s="57" t="n"/>
+      <c r="N89" s="57" t="n"/>
+      <c r="O89" s="57" t="n"/>
+      <c r="P89" s="57" t="n"/>
+      <c r="Q89" s="57" t="n"/>
+      <c r="R89" s="57" t="n"/>
+      <c r="S89" s="57" t="n"/>
+      <c r="T89" s="57" t="n"/>
+      <c r="U89" s="57" t="n"/>
+      <c r="V89" s="57" t="n"/>
+      <c r="W89" s="57" t="n"/>
+      <c r="X89" s="57" t="n"/>
+      <c r="Y89" s="57" t="n"/>
+      <c r="Z89" s="57" t="n"/>
+      <c r="AA89" s="57" t="n"/>
+      <c r="AB89" s="57" t="n"/>
+      <c r="AC89" s="57" t="n"/>
+      <c r="AD89" s="57" t="n"/>
+      <c r="AE89" s="57" t="n"/>
+      <c r="AF89" s="57" t="n"/>
+      <c r="AG89" s="57" t="n"/>
+      <c r="AH89" s="57" t="n"/>
+      <c r="AI89" s="57" t="n"/>
+      <c r="BB89" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC89" s="81" t="inlineStr">
+        <is>
+          <t>Bursts come 20% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="43" t="inlineStr">
+        <is>
+          <t>Big Game Hunter</t>
+        </is>
+      </c>
+      <c r="B90" s="43" t="inlineStr">
+        <is>
+          <t>Stalker</t>
+        </is>
+      </c>
+      <c r="C90" s="43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D90" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E90" s="43" t="inlineStr">
+        <is>
+          <t>Quick Mag</t>
+        </is>
+      </c>
+      <c r="F90" s="56">
+        <f>F23</f>
+        <v/>
+      </c>
+      <c r="G90" s="57" t="n"/>
+      <c r="H90" s="57" t="n"/>
+      <c r="I90" s="57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J90" s="57" t="n"/>
+      <c r="K90" s="57" t="n"/>
+      <c r="L90" s="57" t="n"/>
+      <c r="M90" s="57" t="n"/>
+      <c r="N90" s="57" t="n"/>
+      <c r="O90" s="57" t="n"/>
+      <c r="P90" s="57" t="n"/>
+      <c r="Q90" s="57" t="n"/>
+      <c r="R90" s="57" t="n"/>
+      <c r="S90" s="57" t="n"/>
+      <c r="T90" s="57" t="n"/>
+      <c r="U90" s="57" t="n"/>
+      <c r="V90" s="57" t="n"/>
+      <c r="W90" s="57" t="n"/>
+      <c r="X90" s="57" t="n"/>
+      <c r="Y90" s="57" t="n"/>
+      <c r="Z90" s="57" t="n"/>
+      <c r="AA90" s="57" t="n"/>
+      <c r="AB90" s="57" t="n"/>
+      <c r="AC90" s="57" t="n"/>
+      <c r="AD90" s="57" t="n"/>
+      <c r="AE90" s="57" t="n"/>
+      <c r="AF90" s="57" t="n"/>
+      <c r="AG90" s="57" t="n"/>
+      <c r="AH90" s="57" t="n"/>
+      <c r="AI90" s="57" t="n"/>
+      <c r="BB90" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC90" s="81" t="inlineStr">
+        <is>
+          <t>Reload 25% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="43" t="inlineStr">
+        <is>
+          <t>Big Game Hunter</t>
+        </is>
+      </c>
+      <c r="B91" s="43" t="inlineStr">
+        <is>
+          <t>Stalker</t>
+        </is>
+      </c>
+      <c r="C91" s="43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D91" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E91" s="43" t="inlineStr">
+        <is>
+          <t>Marking Burst</t>
+        </is>
+      </c>
+      <c r="F91" s="56">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="G91" s="57" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H91" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I91" s="57" t="n"/>
+      <c r="J91" s="57" t="n"/>
+      <c r="K91" s="57" t="n"/>
+      <c r="L91" s="57" t="n"/>
+      <c r="M91" s="57" t="n"/>
+      <c r="N91" s="57" t="n"/>
+      <c r="O91" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="P91" s="57" t="n"/>
+      <c r="Q91" s="57" t="n"/>
+      <c r="R91" s="57" t="n"/>
+      <c r="S91" s="57" t="n"/>
+      <c r="T91" s="57" t="n"/>
+      <c r="U91" s="57" t="n"/>
+      <c r="V91" s="57" t="n"/>
+      <c r="W91" s="57" t="n"/>
+      <c r="X91" s="57" t="n"/>
+      <c r="Y91" s="57" t="n"/>
+      <c r="Z91" s="57" t="n"/>
+      <c r="AA91" s="57" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB91" s="57" t="n"/>
+      <c r="AC91" s="57" t="n"/>
+      <c r="AD91" s="57" t="n"/>
+      <c r="AE91" s="57" t="n"/>
+      <c r="AF91" s="57" t="n"/>
+      <c r="AG91" s="57" t="n"/>
+      <c r="AH91" s="57" t="n"/>
+      <c r="AI91" s="57" t="n"/>
+      <c r="BB91" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC91" s="81" t="inlineStr">
+        <is>
+          <t>4-round bursts that mark: +25% from everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="43" t="inlineStr">
+        <is>
+          <t>Big Game Hunter</t>
+        </is>
+      </c>
+      <c r="B92" s="43" t="inlineStr">
+        <is>
+          <t>Stalker</t>
+        </is>
+      </c>
+      <c r="C92" s="43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D92" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E92" s="43" t="inlineStr">
+        <is>
+          <t>Rapid Volley</t>
+        </is>
+      </c>
+      <c r="F92" s="56">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="G92" s="57" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H92" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I92" s="57" t="n"/>
+      <c r="J92" s="57" t="n"/>
+      <c r="K92" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L92" s="57" t="n"/>
+      <c r="M92" s="57" t="n"/>
+      <c r="N92" s="57" t="n"/>
+      <c r="O92" s="57" t="n"/>
+      <c r="P92" s="57" t="n"/>
+      <c r="Q92" s="57" t="n"/>
+      <c r="R92" s="57" t="n"/>
+      <c r="S92" s="57" t="n"/>
+      <c r="T92" s="57" t="n"/>
+      <c r="U92" s="57" t="n"/>
+      <c r="V92" s="57" t="n"/>
+      <c r="W92" s="57" t="n"/>
+      <c r="X92" s="57" t="n"/>
+      <c r="Y92" s="57" t="n"/>
+      <c r="Z92" s="57" t="n"/>
+      <c r="AA92" s="57" t="n"/>
+      <c r="AB92" s="57" t="n"/>
+      <c r="AC92" s="57" t="n"/>
+      <c r="AD92" s="57" t="n"/>
+      <c r="AE92" s="57" t="n"/>
+      <c r="AF92" s="57" t="n"/>
+      <c r="AG92" s="57" t="n"/>
+      <c r="AH92" s="57" t="n"/>
+      <c r="AI92" s="57" t="n"/>
+      <c r="BB92" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC92" s="81" t="inlineStr">
+        <is>
+          <t>Bursts 35% faster, half the kick, bigger mag</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="43" t="inlineStr">
+        <is>
+          <t>Big Game Hunter</t>
+        </is>
+      </c>
+      <c r="B93" s="43" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C93" s="43" t="inlineStr">
+        <is>
+          <t>sustain</t>
+        </is>
+      </c>
+      <c r="D93" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E93" s="43" t="inlineStr">
+        <is>
+          <t>Steady Sling</t>
+        </is>
+      </c>
+      <c r="F93" s="56">
+        <f>F28</f>
+        <v/>
+      </c>
+      <c r="G93" s="57" t="n"/>
+      <c r="H93" s="57" t="n"/>
+      <c r="I93" s="57" t="n"/>
+      <c r="J93" s="57" t="n"/>
+      <c r="K93" s="57" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L93" s="57" t="n"/>
+      <c r="M93" s="57" t="n"/>
+      <c r="N93" s="57" t="n"/>
+      <c r="O93" s="57" t="n"/>
+      <c r="P93" s="57" t="n"/>
+      <c r="Q93" s="57" t="n"/>
+      <c r="R93" s="57" t="n"/>
+      <c r="S93" s="57" t="n"/>
+      <c r="T93" s="57" t="n"/>
+      <c r="U93" s="57" t="n"/>
+      <c r="V93" s="57" t="n"/>
+      <c r="W93" s="57" t="n"/>
+      <c r="X93" s="57" t="n"/>
+      <c r="Y93" s="57" t="n"/>
+      <c r="Z93" s="57" t="n"/>
+      <c r="AA93" s="57" t="n"/>
+      <c r="AB93" s="57" t="n"/>
+      <c r="AC93" s="57" t="n"/>
+      <c r="AD93" s="57" t="n"/>
+      <c r="AE93" s="57" t="n"/>
+      <c r="AF93" s="57" t="n"/>
+      <c r="AG93" s="57" t="n"/>
+      <c r="AH93" s="57" t="n"/>
+      <c r="AI93" s="57" t="n"/>
+      <c r="BB93" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC93" s="81" t="inlineStr">
+        <is>
+          <t>35% less kick, moving or not</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="43" t="inlineStr">
+        <is>
+          <t>Big Game Hunter</t>
+        </is>
+      </c>
+      <c r="B94" s="43" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C94" s="43" t="inlineStr">
+        <is>
+          <t>sustain</t>
+        </is>
+      </c>
+      <c r="D94" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E94" s="43" t="inlineStr">
+        <is>
+          <t>Quick Belt</t>
+        </is>
+      </c>
+      <c r="F94" s="56">
+        <f>F28</f>
+        <v/>
+      </c>
+      <c r="G94" s="57" t="n"/>
+      <c r="H94" s="57" t="n"/>
+      <c r="I94" s="57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J94" s="57" t="n"/>
+      <c r="K94" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L94" s="57" t="n"/>
+      <c r="M94" s="57" t="n"/>
+      <c r="N94" s="57" t="n"/>
+      <c r="O94" s="57" t="n"/>
+      <c r="P94" s="57" t="n"/>
+      <c r="Q94" s="57" t="n"/>
+      <c r="R94" s="57" t="n"/>
+      <c r="S94" s="57" t="n"/>
+      <c r="T94" s="57" t="n"/>
+      <c r="U94" s="57" t="n"/>
+      <c r="V94" s="57" t="n"/>
+      <c r="W94" s="57" t="n"/>
+      <c r="X94" s="57" t="n"/>
+      <c r="Y94" s="57" t="n"/>
+      <c r="Z94" s="57" t="n"/>
+      <c r="AA94" s="57" t="n"/>
+      <c r="AB94" s="57" t="n"/>
+      <c r="AC94" s="57" t="n"/>
+      <c r="AD94" s="57" t="n"/>
+      <c r="AE94" s="57" t="n"/>
+      <c r="AF94" s="57" t="n"/>
+      <c r="AG94" s="57" t="n"/>
+      <c r="AH94" s="57" t="n"/>
+      <c r="AI94" s="57" t="n"/>
+      <c r="BB94" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC94" s="81" t="inlineStr">
+        <is>
+          <t>Belt changes 30% faster; 20% less kick</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="43" t="inlineStr">
+        <is>
+          <t>Big Game Hunter</t>
+        </is>
+      </c>
+      <c r="B95" s="43" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C95" s="43" t="inlineStr">
+        <is>
+          <t>sustain</t>
+        </is>
+      </c>
+      <c r="D95" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E95" s="43" t="inlineStr">
+        <is>
+          <t>Hot Barrel</t>
+        </is>
+      </c>
+      <c r="F95" s="56">
+        <f>F29</f>
+        <v/>
+      </c>
+      <c r="G95" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H95" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I95" s="57" t="n"/>
+      <c r="J95" s="57" t="n"/>
+      <c r="K95" s="57" t="n"/>
+      <c r="L95" s="57" t="n"/>
+      <c r="M95" s="57" t="n"/>
+      <c r="N95" s="57" t="n"/>
+      <c r="O95" s="57" t="n"/>
+      <c r="P95" s="57" t="n"/>
+      <c r="Q95" s="57" t="n"/>
+      <c r="R95" s="57" t="n"/>
+      <c r="S95" s="57" t="n"/>
+      <c r="T95" s="57" t="n"/>
+      <c r="U95" s="57" t="n"/>
+      <c r="V95" s="57" t="n"/>
+      <c r="W95" s="57" t="n"/>
+      <c r="X95" s="57" t="n"/>
+      <c r="Y95" s="57" t="n"/>
+      <c r="Z95" s="57" t="n"/>
+      <c r="AA95" s="57" t="n"/>
+      <c r="AB95" s="57" t="n"/>
+      <c r="AC95" s="57" t="n"/>
+      <c r="AD95" s="57" t="n"/>
+      <c r="AE95" s="57" t="n"/>
+      <c r="AF95" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG95" s="57" t="n"/>
+      <c r="AH95" s="57" t="n"/>
+      <c r="AI95" s="57" t="n"/>
+      <c r="BB95" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC95" s="81" t="inlineStr">
+        <is>
+          <t>50% faster at once, spins up to +60% more</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="43" t="inlineStr">
+        <is>
+          <t>Big Game Hunter</t>
+        </is>
+      </c>
+      <c r="B96" s="43" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C96" s="43" t="inlineStr">
+        <is>
+          <t>sustain</t>
+        </is>
+      </c>
+      <c r="D96" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E96" s="43" t="inlineStr">
+        <is>
+          <t>War Drum</t>
+        </is>
+      </c>
+      <c r="F96" s="56">
+        <f>F29</f>
+        <v/>
+      </c>
+      <c r="G96" s="57" t="n"/>
+      <c r="H96" s="57" t="n"/>
+      <c r="I96" s="57" t="n"/>
+      <c r="J96" s="57" t="n"/>
+      <c r="K96" s="57" t="n"/>
+      <c r="L96" s="57" t="n"/>
+      <c r="M96" s="57" t="n"/>
+      <c r="N96" s="57" t="n"/>
+      <c r="O96" s="57" t="n"/>
+      <c r="P96" s="57" t="n"/>
+      <c r="Q96" s="57" t="n"/>
+      <c r="R96" s="57" t="n"/>
+      <c r="S96" s="57" t="n"/>
+      <c r="T96" s="57" t="n"/>
+      <c r="U96" s="57" t="n"/>
+      <c r="V96" s="57" t="n"/>
+      <c r="W96" s="57" t="n"/>
+      <c r="X96" s="57" t="n"/>
+      <c r="Y96" s="57" t="n"/>
+      <c r="Z96" s="57" t="n"/>
+      <c r="AA96" s="57" t="n"/>
+      <c r="AB96" s="57" t="n"/>
+      <c r="AC96" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD96" s="57" t="n"/>
+      <c r="AE96" s="57" t="n"/>
+      <c r="AF96" s="57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG96" s="57" t="n"/>
+      <c r="AH96" s="57" t="n"/>
+      <c r="AI96" s="57" t="n"/>
+      <c r="BB96" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC96" s="81" t="inlineStr">
+        <is>
+          <t>Rally Cry twice as often; spins up to +130%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="43" t="inlineStr">
+        <is>
+          <t>Big Game Hunter</t>
+        </is>
+      </c>
+      <c r="B97" s="43" t="inlineStr">
+        <is>
+          <t>Special Ammo</t>
+        </is>
+      </c>
+      <c r="C97" s="43" t="inlineStr">
+        <is>
+          <t>rounds</t>
+        </is>
+      </c>
+      <c r="D97" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E97" s="43" t="inlineStr">
+        <is>
+          <t>Phosphor Rounds</t>
+        </is>
+      </c>
+      <c r="F97" s="56">
+        <f>F33</f>
+        <v/>
+      </c>
+      <c r="G97" s="57" t="n"/>
+      <c r="H97" s="57" t="n"/>
+      <c r="I97" s="57" t="n"/>
+      <c r="J97" s="57" t="n"/>
+      <c r="K97" s="57" t="n"/>
+      <c r="L97" s="57" t="n"/>
+      <c r="M97" s="57" t="n"/>
+      <c r="N97" s="57" t="n"/>
+      <c r="O97" s="57" t="n"/>
+      <c r="P97" s="57" t="n"/>
+      <c r="Q97" s="57" t="n"/>
+      <c r="R97" s="57" t="n"/>
+      <c r="S97" s="57" t="n"/>
+      <c r="T97" s="57" t="n"/>
+      <c r="U97" s="57" t="n"/>
+      <c r="V97" s="57" t="n"/>
+      <c r="W97" s="57" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X97" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y97" s="57" t="n"/>
+      <c r="Z97" s="57" t="n"/>
+      <c r="AA97" s="57" t="n"/>
+      <c r="AB97" s="57" t="n"/>
+      <c r="AC97" s="57" t="n"/>
+      <c r="AD97" s="57" t="n"/>
+      <c r="AE97" s="57" t="n"/>
+      <c r="AF97" s="57" t="n"/>
+      <c r="AG97" s="57" t="n"/>
+      <c r="AH97" s="57" t="n"/>
+      <c r="AI97" s="57" t="n"/>
+      <c r="BB97" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC97" s="81" t="inlineStr">
+        <is>
+          <t>Fires burn 10% hotter and 50% longer</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="43" t="inlineStr">
+        <is>
+          <t>Big Game Hunter</t>
+        </is>
+      </c>
+      <c r="B98" s="43" t="inlineStr">
+        <is>
+          <t>Special Ammo</t>
+        </is>
+      </c>
+      <c r="C98" s="43" t="inlineStr">
+        <is>
+          <t>rounds</t>
+        </is>
+      </c>
+      <c r="D98" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E98" s="43" t="inlineStr">
+        <is>
+          <t>Bright Tracers</t>
+        </is>
+      </c>
+      <c r="F98" s="56">
+        <f>F33</f>
+        <v/>
+      </c>
+      <c r="G98" s="57" t="n"/>
+      <c r="H98" s="57" t="n"/>
+      <c r="I98" s="57" t="n"/>
+      <c r="J98" s="57" t="n"/>
+      <c r="K98" s="57" t="n"/>
+      <c r="L98" s="57" t="n"/>
+      <c r="M98" s="57" t="n"/>
+      <c r="N98" s="57" t="n"/>
+      <c r="O98" s="57" t="n"/>
+      <c r="P98" s="57" t="n"/>
+      <c r="Q98" s="57" t="n"/>
+      <c r="R98" s="57" t="n"/>
+      <c r="S98" s="57" t="n"/>
+      <c r="T98" s="57" t="n"/>
+      <c r="U98" s="57" t="n"/>
+      <c r="V98" s="57" t="n"/>
+      <c r="W98" s="57" t="n"/>
+      <c r="X98" s="57" t="n"/>
+      <c r="Y98" s="57" t="n"/>
+      <c r="Z98" s="57" t="n"/>
+      <c r="AA98" s="57" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB98" s="57" t="n"/>
+      <c r="AC98" s="57" t="n"/>
+      <c r="AD98" s="57" t="n"/>
+      <c r="AE98" s="57" t="n"/>
+      <c r="AF98" s="57" t="n"/>
+      <c r="AG98" s="57" t="n"/>
+      <c r="AH98" s="57" t="n"/>
+      <c r="AI98" s="57" t="n"/>
+      <c r="BB98" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC98" s="81" t="inlineStr">
+        <is>
+          <t>Hits mark dinos: +30% from everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="43" t="inlineStr">
+        <is>
+          <t>Big Game Hunter</t>
+        </is>
+      </c>
+      <c r="B99" s="43" t="inlineStr">
+        <is>
+          <t>Special Ammo</t>
+        </is>
+      </c>
+      <c r="C99" s="43" t="inlineStr">
+        <is>
+          <t>rounds</t>
+        </is>
+      </c>
+      <c r="D99" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E99" s="43" t="inlineStr">
+        <is>
+          <t>Fire Tips</t>
+        </is>
+      </c>
+      <c r="F99" s="56">
+        <f>F34</f>
+        <v/>
+      </c>
+      <c r="G99" s="57" t="n"/>
+      <c r="H99" s="57" t="n"/>
+      <c r="I99" s="57" t="n"/>
+      <c r="J99" s="57" t="n"/>
+      <c r="K99" s="57" t="n"/>
+      <c r="L99" s="57" t="n"/>
+      <c r="M99" s="57" t="n"/>
+      <c r="N99" s="57" t="n"/>
+      <c r="O99" s="57" t="n"/>
+      <c r="P99" s="57" t="n"/>
+      <c r="Q99" s="57" t="n"/>
+      <c r="R99" s="57" t="n"/>
+      <c r="S99" s="57" t="n"/>
+      <c r="T99" s="57" t="n"/>
+      <c r="U99" s="57" t="n"/>
+      <c r="V99" s="57" t="n"/>
+      <c r="W99" s="57" t="n"/>
+      <c r="X99" s="57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y99" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z99" s="57" t="n"/>
+      <c r="AA99" s="57" t="n"/>
+      <c r="AB99" s="57" t="n"/>
+      <c r="AC99" s="57" t="n"/>
+      <c r="AD99" s="57" t="n"/>
+      <c r="AE99" s="57" t="n"/>
+      <c r="AF99" s="57" t="n"/>
+      <c r="AG99" s="57" t="n"/>
+      <c r="AH99" s="57" t="n"/>
+      <c r="AI99" s="57" t="n"/>
+      <c r="BB99" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC99" s="81" t="inlineStr">
+        <is>
+          <t>Small blasts; dinos burn 25% longer</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="43" t="inlineStr">
+        <is>
+          <t>Big Game Hunter</t>
+        </is>
+      </c>
+      <c r="B100" s="43" t="inlineStr">
+        <is>
+          <t>Special Ammo</t>
+        </is>
+      </c>
+      <c r="C100" s="43" t="inlineStr">
+        <is>
+          <t>rounds</t>
+        </is>
+      </c>
+      <c r="D100" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E100" s="43" t="inlineStr">
+        <is>
+          <t>Flat Tips</t>
+        </is>
+      </c>
+      <c r="F100" s="56">
+        <f>F34</f>
+        <v/>
+      </c>
+      <c r="G100" s="57" t="n"/>
+      <c r="H100" s="57" t="n"/>
+      <c r="I100" s="57" t="n"/>
+      <c r="J100" s="57" t="n"/>
+      <c r="K100" s="57" t="n"/>
+      <c r="L100" s="57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M100" s="57" t="n"/>
+      <c r="N100" s="57" t="n"/>
+      <c r="O100" s="57" t="n"/>
+      <c r="P100" s="57" t="n"/>
+      <c r="Q100" s="57" t="n"/>
+      <c r="R100" s="57" t="n"/>
+      <c r="S100" s="57" t="n"/>
+      <c r="T100" s="57" t="n"/>
+      <c r="U100" s="57" t="n"/>
+      <c r="V100" s="57" t="n"/>
+      <c r="W100" s="57" t="n"/>
+      <c r="X100" s="57" t="n"/>
+      <c r="Y100" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z100" s="57" t="n"/>
+      <c r="AA100" s="57" t="n"/>
+      <c r="AB100" s="57" t="n"/>
+      <c r="AC100" s="57" t="n"/>
+      <c r="AD100" s="57" t="n"/>
+      <c r="AE100" s="57" t="n"/>
+      <c r="AF100" s="57" t="n"/>
+      <c r="AG100" s="57" t="n"/>
+      <c r="AH100" s="57" t="n"/>
+      <c r="AI100" s="57" t="n"/>
+      <c r="BB100" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC100" s="81" t="inlineStr">
+        <is>
+          <t>Small blasts; rounds fly 25% further</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -37632,7 +37632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA100"/>
+  <dimension ref="A1:CA112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="90" min="1" max="1"/>
@@ -44655,6 +44655,878 @@
       <c r="BC100" s="81" t="inlineStr">
         <is>
           <t>Small blasts; rounds fly 25% further</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="43" t="inlineStr">
+        <is>
+          <t>Brush Beater</t>
+        </is>
+      </c>
+      <c r="B101" s="43" t="inlineStr">
+        <is>
+          <t>Slug</t>
+        </is>
+      </c>
+      <c r="C101" s="43" t="inlineStr">
+        <is>
+          <t>reach</t>
+        </is>
+      </c>
+      <c r="D101" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E101" s="43" t="inlineStr">
+        <is>
+          <t>Quick Pump</t>
+        </is>
+      </c>
+      <c r="F101" s="56">
+        <f>F38</f>
+        <v/>
+      </c>
+      <c r="G101" s="57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H101" s="57" t="n"/>
+      <c r="I101" s="57" t="n"/>
+      <c r="J101" s="57" t="n"/>
+      <c r="K101" s="57" t="n"/>
+      <c r="L101" s="57" t="n"/>
+      <c r="M101" s="57" t="n"/>
+      <c r="N101" s="57" t="n"/>
+      <c r="O101" s="57" t="n"/>
+      <c r="P101" s="57" t="n"/>
+      <c r="Q101" s="57" t="n"/>
+      <c r="R101" s="57" t="n"/>
+      <c r="S101" s="57" t="n"/>
+      <c r="T101" s="57" t="n"/>
+      <c r="U101" s="57" t="n"/>
+      <c r="V101" s="57" t="n"/>
+      <c r="W101" s="57" t="n"/>
+      <c r="X101" s="57" t="n"/>
+      <c r="Y101" s="57" t="n"/>
+      <c r="Z101" s="57" t="n"/>
+      <c r="AA101" s="57" t="n"/>
+      <c r="AB101" s="57" t="n"/>
+      <c r="AC101" s="57" t="n"/>
+      <c r="AD101" s="57" t="n"/>
+      <c r="AE101" s="57" t="n"/>
+      <c r="AF101" s="57" t="n"/>
+      <c r="AG101" s="57" t="n"/>
+      <c r="AH101" s="57" t="n"/>
+      <c r="AI101" s="57" t="n"/>
+      <c r="BB101" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC101" s="81" t="inlineStr">
+        <is>
+          <t>Pump 25% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="43" t="inlineStr">
+        <is>
+          <t>Brush Beater</t>
+        </is>
+      </c>
+      <c r="B102" s="43" t="inlineStr">
+        <is>
+          <t>Slug</t>
+        </is>
+      </c>
+      <c r="C102" s="43" t="inlineStr">
+        <is>
+          <t>reach</t>
+        </is>
+      </c>
+      <c r="D102" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E102" s="43" t="inlineStr">
+        <is>
+          <t>Side Saddle</t>
+        </is>
+      </c>
+      <c r="F102" s="56">
+        <f>F38</f>
+        <v/>
+      </c>
+      <c r="G102" s="57" t="n"/>
+      <c r="H102" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I102" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J102" s="57" t="n"/>
+      <c r="K102" s="57" t="n"/>
+      <c r="L102" s="57" t="n"/>
+      <c r="M102" s="57" t="n"/>
+      <c r="N102" s="57" t="n"/>
+      <c r="O102" s="57" t="n"/>
+      <c r="P102" s="57" t="n"/>
+      <c r="Q102" s="57" t="n"/>
+      <c r="R102" s="57" t="n"/>
+      <c r="S102" s="57" t="n"/>
+      <c r="T102" s="57" t="n"/>
+      <c r="U102" s="57" t="n"/>
+      <c r="V102" s="57" t="n"/>
+      <c r="W102" s="57" t="n"/>
+      <c r="X102" s="57" t="n"/>
+      <c r="Y102" s="57" t="n"/>
+      <c r="Z102" s="57" t="n"/>
+      <c r="AA102" s="57" t="n"/>
+      <c r="AB102" s="57" t="n"/>
+      <c r="AC102" s="57" t="n"/>
+      <c r="AD102" s="57" t="n"/>
+      <c r="AE102" s="57" t="n"/>
+      <c r="AF102" s="57" t="n"/>
+      <c r="AG102" s="57" t="n"/>
+      <c r="AH102" s="57" t="n"/>
+      <c r="AI102" s="57" t="n"/>
+      <c r="BB102" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC102" s="81" t="inlineStr">
+        <is>
+          <t>Holds 50% more slugs, loads 20% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="43" t="inlineStr">
+        <is>
+          <t>Brush Beater</t>
+        </is>
+      </c>
+      <c r="B103" s="43" t="inlineStr">
+        <is>
+          <t>Slug</t>
+        </is>
+      </c>
+      <c r="C103" s="43" t="inlineStr">
+        <is>
+          <t>reach</t>
+        </is>
+      </c>
+      <c r="D103" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E103" s="43" t="inlineStr">
+        <is>
+          <t>Express Slug</t>
+        </is>
+      </c>
+      <c r="F103" s="56">
+        <f>F39</f>
+        <v/>
+      </c>
+      <c r="G103" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H103" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I103" s="57" t="n"/>
+      <c r="J103" s="57" t="n"/>
+      <c r="K103" s="57" t="n"/>
+      <c r="L103" s="57" t="n"/>
+      <c r="M103" s="57" t="n"/>
+      <c r="N103" s="57" t="n"/>
+      <c r="O103" s="57" t="n"/>
+      <c r="P103" s="57" t="n"/>
+      <c r="Q103" s="57" t="n"/>
+      <c r="R103" s="57" t="n"/>
+      <c r="S103" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="T103" s="57" t="n"/>
+      <c r="U103" s="57" t="n"/>
+      <c r="V103" s="57" t="n"/>
+      <c r="W103" s="57" t="n"/>
+      <c r="X103" s="57" t="n"/>
+      <c r="Y103" s="57" t="n"/>
+      <c r="Z103" s="57" t="n"/>
+      <c r="AA103" s="57" t="n"/>
+      <c r="AB103" s="57" t="n"/>
+      <c r="AC103" s="57" t="n"/>
+      <c r="AD103" s="57" t="n"/>
+      <c r="AE103" s="57" t="n"/>
+      <c r="AF103" s="57" t="n"/>
+      <c r="AG103" s="57" t="n"/>
+      <c r="AH103" s="57" t="n"/>
+      <c r="AI103" s="57" t="n"/>
+      <c r="BB103" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC103" s="81" t="inlineStr">
+        <is>
+          <t>Slugs through 6, 60% faster, bigger tube</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="43" t="inlineStr">
+        <is>
+          <t>Brush Beater</t>
+        </is>
+      </c>
+      <c r="B104" s="43" t="inlineStr">
+        <is>
+          <t>Slug</t>
+        </is>
+      </c>
+      <c r="C104" s="43" t="inlineStr">
+        <is>
+          <t>reach</t>
+        </is>
+      </c>
+      <c r="D104" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E104" s="43" t="inlineStr">
+        <is>
+          <t>Twin Slug</t>
+        </is>
+      </c>
+      <c r="F104" s="56">
+        <f>F39</f>
+        <v/>
+      </c>
+      <c r="G104" s="57" t="n"/>
+      <c r="H104" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I104" s="57" t="n"/>
+      <c r="J104" s="57" t="n"/>
+      <c r="K104" s="57" t="n"/>
+      <c r="L104" s="57" t="n"/>
+      <c r="M104" s="57" t="n"/>
+      <c r="N104" s="57" t="n"/>
+      <c r="O104" s="57" t="n"/>
+      <c r="P104" s="57" t="n"/>
+      <c r="Q104" s="57" t="n"/>
+      <c r="R104" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="S104" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="T104" s="57" t="n"/>
+      <c r="U104" s="57" t="n"/>
+      <c r="V104" s="57" t="n"/>
+      <c r="W104" s="57" t="n"/>
+      <c r="X104" s="57" t="n"/>
+      <c r="Y104" s="57" t="n"/>
+      <c r="Z104" s="57" t="n"/>
+      <c r="AA104" s="57" t="n"/>
+      <c r="AB104" s="57" t="n"/>
+      <c r="AC104" s="57" t="n"/>
+      <c r="AD104" s="57" t="n"/>
+      <c r="AE104" s="57" t="n"/>
+      <c r="AF104" s="57" t="n"/>
+      <c r="AG104" s="57" t="n"/>
+      <c r="AH104" s="57" t="n"/>
+      <c r="AI104" s="57" t="n"/>
+      <c r="BB104" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC104" s="81" t="inlineStr">
+        <is>
+          <t>Two slugs per pump, each through 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="43" t="inlineStr">
+        <is>
+          <t>Brush Beater</t>
+        </is>
+      </c>
+      <c r="B105" s="43" t="inlineStr">
+        <is>
+          <t>Buckshot</t>
+        </is>
+      </c>
+      <c r="C105" s="43" t="inlineStr">
+        <is>
+          <t>crowds</t>
+        </is>
+      </c>
+      <c r="D105" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E105" s="43" t="inlineStr">
+        <is>
+          <t>Hot Shells</t>
+        </is>
+      </c>
+      <c r="F105" s="56">
+        <f>F43</f>
+        <v/>
+      </c>
+      <c r="G105" s="57" t="n"/>
+      <c r="H105" s="57" t="n"/>
+      <c r="I105" s="57" t="n"/>
+      <c r="J105" s="57" t="n"/>
+      <c r="K105" s="57" t="n"/>
+      <c r="L105" s="57" t="n"/>
+      <c r="M105" s="57" t="n"/>
+      <c r="N105" s="57" t="n"/>
+      <c r="O105" s="57" t="n"/>
+      <c r="P105" s="57" t="n"/>
+      <c r="Q105" s="57" t="n"/>
+      <c r="R105" s="57" t="n"/>
+      <c r="S105" s="57" t="n"/>
+      <c r="T105" s="57" t="n"/>
+      <c r="U105" s="57" t="n"/>
+      <c r="V105" s="57" t="n"/>
+      <c r="W105" s="57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X105" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y105" s="57" t="n"/>
+      <c r="Z105" s="57" t="n"/>
+      <c r="AA105" s="57" t="n"/>
+      <c r="AB105" s="57" t="n"/>
+      <c r="AC105" s="57" t="n"/>
+      <c r="AD105" s="57" t="n"/>
+      <c r="AE105" s="57" t="n"/>
+      <c r="AF105" s="57" t="n"/>
+      <c r="AG105" s="57" t="n"/>
+      <c r="AH105" s="57" t="n"/>
+      <c r="AI105" s="57" t="n"/>
+      <c r="BB105" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC105" s="81" t="inlineStr">
+        <is>
+          <t>Fires burn more than twice as hot</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="43" t="inlineStr">
+        <is>
+          <t>Brush Beater</t>
+        </is>
+      </c>
+      <c r="B106" s="43" t="inlineStr">
+        <is>
+          <t>Buckshot</t>
+        </is>
+      </c>
+      <c r="C106" s="43" t="inlineStr">
+        <is>
+          <t>crowds</t>
+        </is>
+      </c>
+      <c r="D106" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E106" s="43" t="inlineStr">
+        <is>
+          <t>Shell Belt</t>
+        </is>
+      </c>
+      <c r="F106" s="56">
+        <f>F43</f>
+        <v/>
+      </c>
+      <c r="G106" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H106" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I106" s="57" t="n"/>
+      <c r="J106" s="57" t="n"/>
+      <c r="K106" s="57" t="n"/>
+      <c r="L106" s="57" t="n"/>
+      <c r="M106" s="57" t="n"/>
+      <c r="N106" s="57" t="n"/>
+      <c r="O106" s="57" t="n"/>
+      <c r="P106" s="57" t="n"/>
+      <c r="Q106" s="57" t="n"/>
+      <c r="R106" s="57" t="n"/>
+      <c r="S106" s="57" t="n"/>
+      <c r="T106" s="57" t="n"/>
+      <c r="U106" s="57" t="n"/>
+      <c r="V106" s="57" t="n"/>
+      <c r="W106" s="57" t="n"/>
+      <c r="X106" s="57" t="n"/>
+      <c r="Y106" s="57" t="n"/>
+      <c r="Z106" s="57" t="n"/>
+      <c r="AA106" s="57" t="n"/>
+      <c r="AB106" s="57" t="n"/>
+      <c r="AC106" s="57" t="n"/>
+      <c r="AD106" s="57" t="n"/>
+      <c r="AE106" s="57" t="n"/>
+      <c r="AF106" s="57" t="n"/>
+      <c r="AG106" s="57" t="n"/>
+      <c r="AH106" s="57" t="n"/>
+      <c r="AI106" s="57" t="n"/>
+      <c r="BB106" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC106" s="81" t="inlineStr">
+        <is>
+          <t>Pump 50% faster; holds 50% more</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="43" t="inlineStr">
+        <is>
+          <t>Brush Beater</t>
+        </is>
+      </c>
+      <c r="B107" s="43" t="inlineStr">
+        <is>
+          <t>Buckshot</t>
+        </is>
+      </c>
+      <c r="C107" s="43" t="inlineStr">
+        <is>
+          <t>crowds</t>
+        </is>
+      </c>
+      <c r="D107" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E107" s="43" t="inlineStr">
+        <is>
+          <t>Flame Choke</t>
+        </is>
+      </c>
+      <c r="F107" s="56">
+        <f>F44</f>
+        <v/>
+      </c>
+      <c r="G107" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H107" s="57" t="n"/>
+      <c r="I107" s="57" t="n"/>
+      <c r="J107" s="57" t="n"/>
+      <c r="K107" s="57" t="n"/>
+      <c r="L107" s="57" t="n"/>
+      <c r="M107" s="57" t="n"/>
+      <c r="N107" s="57" t="n"/>
+      <c r="O107" s="57" t="n"/>
+      <c r="P107" s="57" t="n"/>
+      <c r="Q107" s="57" t="n"/>
+      <c r="R107" s="57" t="n"/>
+      <c r="S107" s="57" t="n"/>
+      <c r="T107" s="57" t="n"/>
+      <c r="U107" s="57" t="n"/>
+      <c r="V107" s="57" t="n"/>
+      <c r="W107" s="57" t="n"/>
+      <c r="X107" s="57" t="n"/>
+      <c r="Y107" s="57" t="n"/>
+      <c r="Z107" s="57" t="n"/>
+      <c r="AA107" s="57" t="n"/>
+      <c r="AB107" s="57" t="n"/>
+      <c r="AC107" s="57" t="n"/>
+      <c r="AD107" s="57" t="n"/>
+      <c r="AE107" s="57" t="n"/>
+      <c r="AF107" s="57" t="n"/>
+      <c r="AG107" s="57" t="n"/>
+      <c r="AH107" s="57" t="n"/>
+      <c r="AI107" s="57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BB107" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC107" s="81" t="inlineStr">
+        <is>
+          <t>Dragon's Breath bursts for 70% of a shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="43" t="inlineStr">
+        <is>
+          <t>Brush Beater</t>
+        </is>
+      </c>
+      <c r="B108" s="43" t="inlineStr">
+        <is>
+          <t>Buckshot</t>
+        </is>
+      </c>
+      <c r="C108" s="43" t="inlineStr">
+        <is>
+          <t>crowds</t>
+        </is>
+      </c>
+      <c r="D108" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E108" s="43" t="inlineStr">
+        <is>
+          <t>Pump Storm</t>
+        </is>
+      </c>
+      <c r="F108" s="56">
+        <f>F44</f>
+        <v/>
+      </c>
+      <c r="G108" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H108" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I108" s="57" t="n"/>
+      <c r="J108" s="57" t="n"/>
+      <c r="K108" s="57" t="n"/>
+      <c r="L108" s="57" t="n"/>
+      <c r="M108" s="57" t="n"/>
+      <c r="N108" s="57" t="n"/>
+      <c r="O108" s="57" t="n"/>
+      <c r="P108" s="57" t="n"/>
+      <c r="Q108" s="57" t="n"/>
+      <c r="R108" s="57" t="n"/>
+      <c r="S108" s="57" t="n"/>
+      <c r="T108" s="57" t="n"/>
+      <c r="U108" s="57" t="n"/>
+      <c r="V108" s="57" t="n"/>
+      <c r="W108" s="57" t="n"/>
+      <c r="X108" s="57" t="n"/>
+      <c r="Y108" s="57" t="n"/>
+      <c r="Z108" s="57" t="n"/>
+      <c r="AA108" s="57" t="n"/>
+      <c r="AB108" s="57" t="n"/>
+      <c r="AC108" s="57" t="n"/>
+      <c r="AD108" s="57" t="n"/>
+      <c r="AE108" s="57" t="n"/>
+      <c r="AF108" s="57" t="n"/>
+      <c r="AG108" s="57" t="n"/>
+      <c r="AH108" s="57" t="n"/>
+      <c r="AI108" s="57" t="n"/>
+      <c r="BB108" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC108" s="81" t="inlineStr">
+        <is>
+          <t>Pump 50% faster, bigger tube</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="43" t="inlineStr">
+        <is>
+          <t>Brush Beater</t>
+        </is>
+      </c>
+      <c r="B109" s="43" t="inlineStr">
+        <is>
+          <t>Point Blank</t>
+        </is>
+      </c>
+      <c r="C109" s="43" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="D109" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E109" s="43" t="inlineStr">
+        <is>
+          <t>Quick Breech</t>
+        </is>
+      </c>
+      <c r="F109" s="56">
+        <f>F48</f>
+        <v/>
+      </c>
+      <c r="G109" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H109" s="57" t="n"/>
+      <c r="I109" s="57" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J109" s="57" t="n"/>
+      <c r="K109" s="57" t="n"/>
+      <c r="L109" s="57" t="n"/>
+      <c r="M109" s="57" t="n"/>
+      <c r="N109" s="57" t="n"/>
+      <c r="O109" s="57" t="n"/>
+      <c r="P109" s="57" t="n"/>
+      <c r="Q109" s="57" t="n"/>
+      <c r="R109" s="57" t="n"/>
+      <c r="S109" s="57" t="n"/>
+      <c r="T109" s="57" t="n"/>
+      <c r="U109" s="57" t="n"/>
+      <c r="V109" s="57" t="n"/>
+      <c r="W109" s="57" t="n"/>
+      <c r="X109" s="57" t="n"/>
+      <c r="Y109" s="57" t="n"/>
+      <c r="Z109" s="57" t="n"/>
+      <c r="AA109" s="57" t="n"/>
+      <c r="AB109" s="57" t="n"/>
+      <c r="AC109" s="57" t="n"/>
+      <c r="AD109" s="57" t="n"/>
+      <c r="AE109" s="57" t="n"/>
+      <c r="AF109" s="57" t="n"/>
+      <c r="AG109" s="57" t="n"/>
+      <c r="AH109" s="57" t="n"/>
+      <c r="AI109" s="57" t="n"/>
+      <c r="BB109" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC109" s="81" t="inlineStr">
+        <is>
+          <t>Reload 35% faster, fire 20% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="43" t="inlineStr">
+        <is>
+          <t>Brush Beater</t>
+        </is>
+      </c>
+      <c r="B110" s="43" t="inlineStr">
+        <is>
+          <t>Point Blank</t>
+        </is>
+      </c>
+      <c r="C110" s="43" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="D110" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E110" s="43" t="inlineStr">
+        <is>
+          <t>Bird Shot</t>
+        </is>
+      </c>
+      <c r="F110" s="56">
+        <f>F48</f>
+        <v/>
+      </c>
+      <c r="G110" s="57" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H110" s="57" t="n"/>
+      <c r="I110" s="57" t="n"/>
+      <c r="J110" s="57" t="n"/>
+      <c r="K110" s="57" t="n"/>
+      <c r="L110" s="57" t="n"/>
+      <c r="M110" s="57" t="n"/>
+      <c r="N110" s="57" t="n"/>
+      <c r="O110" s="57" t="n"/>
+      <c r="P110" s="57" t="n"/>
+      <c r="Q110" s="57" t="n"/>
+      <c r="R110" s="57" t="n"/>
+      <c r="S110" s="57" t="n"/>
+      <c r="T110" s="57" t="n"/>
+      <c r="U110" s="57" t="n"/>
+      <c r="V110" s="57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W110" s="57" t="n"/>
+      <c r="X110" s="57" t="n"/>
+      <c r="Y110" s="57" t="n"/>
+      <c r="Z110" s="57" t="n"/>
+      <c r="AA110" s="57" t="n"/>
+      <c r="AB110" s="57" t="n"/>
+      <c r="AC110" s="57" t="n"/>
+      <c r="AD110" s="57" t="n"/>
+      <c r="AE110" s="57" t="n"/>
+      <c r="AF110" s="57" t="n"/>
+      <c r="AG110" s="57" t="n"/>
+      <c r="AH110" s="57" t="n"/>
+      <c r="AI110" s="57" t="n"/>
+      <c r="BB110" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC110" s="81" t="inlineStr">
+        <is>
+          <t>Blasts hit flying dinos; fire 15% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="43" t="inlineStr">
+        <is>
+          <t>Brush Beater</t>
+        </is>
+      </c>
+      <c r="B111" s="43" t="inlineStr">
+        <is>
+          <t>Point Blank</t>
+        </is>
+      </c>
+      <c r="C111" s="43" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="D111" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E111" s="43" t="inlineStr">
+        <is>
+          <t>Breech Loader</t>
+        </is>
+      </c>
+      <c r="F111" s="56">
+        <f>F49</f>
+        <v/>
+      </c>
+      <c r="G111" s="57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H111" s="57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I111" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J111" s="57" t="n"/>
+      <c r="K111" s="57" t="n"/>
+      <c r="L111" s="57" t="n"/>
+      <c r="M111" s="57" t="n"/>
+      <c r="N111" s="57" t="n"/>
+      <c r="O111" s="57" t="n"/>
+      <c r="P111" s="57" t="n"/>
+      <c r="Q111" s="57" t="n"/>
+      <c r="R111" s="57" t="n"/>
+      <c r="S111" s="57" t="n"/>
+      <c r="T111" s="57" t="n"/>
+      <c r="U111" s="57" t="n"/>
+      <c r="V111" s="57" t="n"/>
+      <c r="W111" s="57" t="n"/>
+      <c r="X111" s="57" t="n"/>
+      <c r="Y111" s="57" t="n"/>
+      <c r="Z111" s="57" t="n"/>
+      <c r="AA111" s="57" t="n"/>
+      <c r="AB111" s="57" t="n"/>
+      <c r="AC111" s="57" t="n"/>
+      <c r="AD111" s="57" t="n"/>
+      <c r="AE111" s="57" t="n"/>
+      <c r="AF111" s="57" t="n"/>
+      <c r="AG111" s="57" t="n"/>
+      <c r="AH111" s="57" t="n"/>
+      <c r="AI111" s="57" t="n"/>
+      <c r="BB111" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC111" s="81" t="inlineStr">
+        <is>
+          <t>45% faster, bigger tube, quick reload</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="43" t="inlineStr">
+        <is>
+          <t>Brush Beater</t>
+        </is>
+      </c>
+      <c r="B112" s="43" t="inlineStr">
+        <is>
+          <t>Point Blank</t>
+        </is>
+      </c>
+      <c r="C112" s="43" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="D112" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E112" s="43" t="inlineStr">
+        <is>
+          <t>Slam Fire</t>
+        </is>
+      </c>
+      <c r="F112" s="56">
+        <f>F49</f>
+        <v/>
+      </c>
+      <c r="G112" s="57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H112" s="57" t="n"/>
+      <c r="I112" s="57" t="n"/>
+      <c r="J112" s="57" t="n"/>
+      <c r="K112" s="57" t="n"/>
+      <c r="L112" s="57" t="n"/>
+      <c r="M112" s="57" t="n"/>
+      <c r="N112" s="57" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="O112" s="57" t="n"/>
+      <c r="P112" s="57" t="n"/>
+      <c r="Q112" s="57" t="n"/>
+      <c r="R112" s="57" t="n"/>
+      <c r="S112" s="57" t="n"/>
+      <c r="T112" s="57" t="n"/>
+      <c r="U112" s="57" t="n"/>
+      <c r="V112" s="57" t="n"/>
+      <c r="W112" s="57" t="n"/>
+      <c r="X112" s="57" t="n"/>
+      <c r="Y112" s="57" t="n"/>
+      <c r="Z112" s="57" t="n"/>
+      <c r="AA112" s="57" t="n"/>
+      <c r="AB112" s="57" t="n"/>
+      <c r="AC112" s="57" t="n"/>
+      <c r="AD112" s="57" t="n"/>
+      <c r="AE112" s="57" t="n"/>
+      <c r="AF112" s="57" t="n"/>
+      <c r="AG112" s="57" t="n"/>
+      <c r="AH112" s="57" t="n"/>
+      <c r="AI112" s="57" t="n"/>
+      <c r="BB112" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC112" s="81" t="inlineStr">
+        <is>
+          <t>Hold to keep both barrels firing, 70% faster</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -37632,7 +37632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA112"/>
+  <dimension ref="A1:CC124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="90" min="1" max="1"/>
@@ -37668,6 +37668,9 @@
     <col width="11" customWidth="1" style="90" min="31" max="31"/>
     <col width="11" customWidth="1" style="90" min="32" max="32"/>
     <col width="11" customWidth="1" style="90" min="33" max="33"/>
+    <col width="13" customWidth="1" style="90" min="53" max="53"/>
+    <col width="13" customWidth="1" style="90" min="56" max="56"/>
+    <col width="13" customWidth="1" style="90" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37958,6 +37961,16 @@
       <c r="BC4" s="81" t="inlineStr">
         <is>
           <t>Blurb</t>
+        </is>
+      </c>
+      <c r="BD4" s="104" t="inlineStr">
+        <is>
+          <t>Heal regen HP/s</t>
+        </is>
+      </c>
+      <c r="BE4" s="104" t="inlineStr">
+        <is>
+          <t>Heal regen (s)</t>
         </is>
       </c>
     </row>
@@ -45527,6 +45540,895 @@
       <c r="BC112" s="81" t="inlineStr">
         <is>
           <t>Hold to keep both barrels firing, 70% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B113" s="43" t="inlineStr">
+        <is>
+          <t>Triage</t>
+        </is>
+      </c>
+      <c r="C113" s="43" t="inlineStr">
+        <is>
+          <t>ability</t>
+        </is>
+      </c>
+      <c r="D113" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E113" s="43" t="inlineStr">
+        <is>
+          <t>Thick Gauze</t>
+        </is>
+      </c>
+      <c r="F113" s="56">
+        <f>F53</f>
+        <v/>
+      </c>
+      <c r="G113" s="57" t="n"/>
+      <c r="H113" s="57" t="n"/>
+      <c r="I113" s="57" t="n"/>
+      <c r="J113" s="57" t="n"/>
+      <c r="K113" s="57" t="n"/>
+      <c r="L113" s="57" t="n"/>
+      <c r="M113" s="57" t="n"/>
+      <c r="N113" s="57" t="n"/>
+      <c r="O113" s="57" t="n"/>
+      <c r="P113" s="57" t="n"/>
+      <c r="Q113" s="57" t="n"/>
+      <c r="R113" s="57" t="n"/>
+      <c r="S113" s="57" t="n"/>
+      <c r="T113" s="57" t="n"/>
+      <c r="U113" s="57" t="n"/>
+      <c r="V113" s="57" t="n"/>
+      <c r="W113" s="57" t="n"/>
+      <c r="X113" s="57" t="n"/>
+      <c r="Y113" s="57" t="n"/>
+      <c r="Z113" s="57" t="n"/>
+      <c r="AA113" s="57" t="n"/>
+      <c r="AB113" s="57" t="n"/>
+      <c r="AC113" s="57" t="n"/>
+      <c r="AD113" s="57" t="n"/>
+      <c r="AE113" s="57" t="n"/>
+      <c r="AF113" s="57" t="n"/>
+      <c r="AG113" s="57" t="n"/>
+      <c r="AH113" s="57" t="n"/>
+      <c r="AI113" s="57" t="n"/>
+      <c r="AJ113" s="81" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK113" s="81" t="n"/>
+      <c r="AL113" s="81" t="n"/>
+      <c r="BB113" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC113" s="81" t="inlineStr">
+        <is>
+          <t>Triage Kit heals 55% more</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B114" s="43" t="inlineStr">
+        <is>
+          <t>Triage</t>
+        </is>
+      </c>
+      <c r="C114" s="43" t="inlineStr">
+        <is>
+          <t>ability</t>
+        </is>
+      </c>
+      <c r="D114" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E114" s="43" t="inlineStr">
+        <is>
+          <t>Quick Kit</t>
+        </is>
+      </c>
+      <c r="F114" s="56">
+        <f>F53</f>
+        <v/>
+      </c>
+      <c r="G114" s="57" t="n"/>
+      <c r="H114" s="57" t="n"/>
+      <c r="I114" s="57" t="n"/>
+      <c r="J114" s="57" t="n"/>
+      <c r="K114" s="57" t="n"/>
+      <c r="L114" s="57" t="n"/>
+      <c r="M114" s="57" t="n"/>
+      <c r="N114" s="57" t="n"/>
+      <c r="O114" s="57" t="n"/>
+      <c r="P114" s="57" t="n"/>
+      <c r="Q114" s="57" t="n"/>
+      <c r="R114" s="57" t="n"/>
+      <c r="S114" s="57" t="n"/>
+      <c r="T114" s="57" t="n"/>
+      <c r="U114" s="57" t="n"/>
+      <c r="V114" s="57" t="n"/>
+      <c r="W114" s="57" t="n"/>
+      <c r="X114" s="57" t="n"/>
+      <c r="Y114" s="57" t="n"/>
+      <c r="Z114" s="57" t="n"/>
+      <c r="AA114" s="57" t="n"/>
+      <c r="AB114" s="57" t="n"/>
+      <c r="AC114" s="57" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AD114" s="57" t="n"/>
+      <c r="AE114" s="57" t="n"/>
+      <c r="AF114" s="57" t="n"/>
+      <c r="AG114" s="57" t="n"/>
+      <c r="AH114" s="57" t="n"/>
+      <c r="AI114" s="57" t="n"/>
+      <c r="AJ114" s="81" t="n"/>
+      <c r="AK114" s="81" t="n"/>
+      <c r="AL114" s="81" t="n"/>
+      <c r="BB114" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC114" s="81" t="inlineStr">
+        <is>
+          <t>Triage Kit is ready a third sooner</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B115" s="43" t="inlineStr">
+        <is>
+          <t>Triage</t>
+        </is>
+      </c>
+      <c r="C115" s="43" t="inlineStr">
+        <is>
+          <t>ability</t>
+        </is>
+      </c>
+      <c r="D115" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E115" s="43" t="inlineStr">
+        <is>
+          <t>Mending Salve</t>
+        </is>
+      </c>
+      <c r="F115" s="56">
+        <f>F54</f>
+        <v/>
+      </c>
+      <c r="G115" s="57" t="n"/>
+      <c r="H115" s="57" t="n"/>
+      <c r="I115" s="57" t="n"/>
+      <c r="J115" s="57" t="n"/>
+      <c r="K115" s="57" t="n"/>
+      <c r="L115" s="57" t="n"/>
+      <c r="M115" s="57" t="n"/>
+      <c r="N115" s="57" t="n"/>
+      <c r="O115" s="57" t="n"/>
+      <c r="P115" s="57" t="n"/>
+      <c r="Q115" s="57" t="n"/>
+      <c r="R115" s="57" t="n"/>
+      <c r="S115" s="57" t="n"/>
+      <c r="T115" s="57" t="n"/>
+      <c r="U115" s="57" t="n"/>
+      <c r="V115" s="57" t="n"/>
+      <c r="W115" s="57" t="n"/>
+      <c r="X115" s="57" t="n"/>
+      <c r="Y115" s="57" t="n"/>
+      <c r="Z115" s="57" t="n"/>
+      <c r="AA115" s="57" t="n"/>
+      <c r="AB115" s="57" t="n"/>
+      <c r="AC115" s="57" t="n"/>
+      <c r="AD115" s="57" t="n"/>
+      <c r="AE115" s="57" t="n"/>
+      <c r="AF115" s="57" t="n"/>
+      <c r="AG115" s="57" t="n"/>
+      <c r="AH115" s="57" t="n"/>
+      <c r="AI115" s="57" t="n"/>
+      <c r="AJ115" s="81" t="n"/>
+      <c r="AK115" s="81" t="n"/>
+      <c r="AL115" s="81" t="n"/>
+      <c r="AM115" s="81" t="n"/>
+      <c r="AN115" s="81" t="n"/>
+      <c r="BB115" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC115" s="81" t="inlineStr">
+        <is>
+          <t>Everything healed regains 2 HP/s for 8 s</t>
+        </is>
+      </c>
+      <c r="BD115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B116" s="43" t="inlineStr">
+        <is>
+          <t>Triage</t>
+        </is>
+      </c>
+      <c r="C116" s="43" t="inlineStr">
+        <is>
+          <t>ability</t>
+        </is>
+      </c>
+      <c r="D116" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E116" s="43" t="inlineStr">
+        <is>
+          <t>Field Surgeon</t>
+        </is>
+      </c>
+      <c r="F116" s="56">
+        <f>F54</f>
+        <v/>
+      </c>
+      <c r="G116" s="57" t="n"/>
+      <c r="H116" s="57" t="n"/>
+      <c r="I116" s="57" t="n"/>
+      <c r="J116" s="57" t="n"/>
+      <c r="K116" s="57" t="n"/>
+      <c r="L116" s="57" t="n"/>
+      <c r="M116" s="57" t="n"/>
+      <c r="N116" s="57" t="n"/>
+      <c r="O116" s="57" t="n"/>
+      <c r="P116" s="57" t="n"/>
+      <c r="Q116" s="57" t="n"/>
+      <c r="R116" s="57" t="n"/>
+      <c r="S116" s="57" t="n"/>
+      <c r="T116" s="57" t="n"/>
+      <c r="U116" s="57" t="n"/>
+      <c r="V116" s="57" t="n"/>
+      <c r="W116" s="57" t="n"/>
+      <c r="X116" s="57" t="n"/>
+      <c r="Y116" s="57" t="n"/>
+      <c r="Z116" s="57" t="n"/>
+      <c r="AA116" s="57" t="n"/>
+      <c r="AB116" s="57" t="n"/>
+      <c r="AC116" s="57" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AD116" s="57" t="n"/>
+      <c r="AE116" s="57" t="n"/>
+      <c r="AF116" s="57" t="n"/>
+      <c r="AG116" s="57" t="n"/>
+      <c r="AH116" s="57" t="n"/>
+      <c r="AI116" s="57" t="n"/>
+      <c r="AJ116" s="81" t="n"/>
+      <c r="AK116" s="81" t="n"/>
+      <c r="AL116" s="81" t="n"/>
+      <c r="AM116" s="81" t="n"/>
+      <c r="AN116" s="81" t="n"/>
+      <c r="BB116" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC116" s="81" t="inlineStr">
+        <is>
+          <t>Triage Kit is ready 22% sooner</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B117" s="43" t="inlineStr">
+        <is>
+          <t>Lever Action</t>
+        </is>
+      </c>
+      <c r="C117" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D117" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E117" s="43" t="inlineStr">
+        <is>
+          <t>Long Tube</t>
+        </is>
+      </c>
+      <c r="F117" s="56">
+        <f>F58</f>
+        <v/>
+      </c>
+      <c r="G117" s="57" t="n"/>
+      <c r="H117" s="57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I117" s="57" t="n"/>
+      <c r="J117" s="57" t="n"/>
+      <c r="K117" s="57" t="n"/>
+      <c r="L117" s="57" t="n"/>
+      <c r="M117" s="57" t="n"/>
+      <c r="N117" s="57" t="n"/>
+      <c r="O117" s="57" t="n"/>
+      <c r="P117" s="57" t="n"/>
+      <c r="Q117" s="57" t="n"/>
+      <c r="R117" s="57" t="n"/>
+      <c r="S117" s="57" t="n"/>
+      <c r="T117" s="57" t="n"/>
+      <c r="U117" s="57" t="n"/>
+      <c r="V117" s="57" t="n"/>
+      <c r="W117" s="57" t="n"/>
+      <c r="X117" s="57" t="n"/>
+      <c r="Y117" s="57" t="n"/>
+      <c r="Z117" s="57" t="n"/>
+      <c r="AA117" s="57" t="n"/>
+      <c r="AB117" s="57" t="n"/>
+      <c r="AC117" s="57" t="n"/>
+      <c r="AD117" s="57" t="n"/>
+      <c r="AE117" s="57" t="n"/>
+      <c r="AF117" s="57" t="n"/>
+      <c r="AG117" s="57" t="n"/>
+      <c r="AH117" s="57" t="n"/>
+      <c r="AI117" s="57" t="n"/>
+      <c r="BB117" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC117" s="81" t="inlineStr">
+        <is>
+          <t>Holds 80% more rounds</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B118" s="43" t="inlineStr">
+        <is>
+          <t>Lever Action</t>
+        </is>
+      </c>
+      <c r="C118" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D118" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E118" s="43" t="inlineStr">
+        <is>
+          <t>Snap Lever</t>
+        </is>
+      </c>
+      <c r="F118" s="56">
+        <f>F58</f>
+        <v/>
+      </c>
+      <c r="G118" s="57" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H118" s="57" t="n"/>
+      <c r="I118" s="57" t="n"/>
+      <c r="J118" s="57" t="n"/>
+      <c r="K118" s="57" t="n"/>
+      <c r="L118" s="57" t="n"/>
+      <c r="M118" s="57" t="n"/>
+      <c r="N118" s="57" t="n"/>
+      <c r="O118" s="57" t="n"/>
+      <c r="P118" s="57" t="n"/>
+      <c r="Q118" s="57" t="n"/>
+      <c r="R118" s="57" t="n"/>
+      <c r="S118" s="57" t="n"/>
+      <c r="T118" s="57" t="n"/>
+      <c r="U118" s="57" t="n"/>
+      <c r="V118" s="57" t="n"/>
+      <c r="W118" s="57" t="n"/>
+      <c r="X118" s="57" t="n"/>
+      <c r="Y118" s="57" t="n"/>
+      <c r="Z118" s="57" t="n"/>
+      <c r="AA118" s="57" t="n"/>
+      <c r="AB118" s="57" t="n"/>
+      <c r="AC118" s="57" t="n"/>
+      <c r="AD118" s="57" t="n"/>
+      <c r="AE118" s="57" t="n"/>
+      <c r="AF118" s="57" t="n"/>
+      <c r="AG118" s="57" t="n"/>
+      <c r="AH118" s="57" t="n"/>
+      <c r="AI118" s="57" t="n"/>
+      <c r="BB118" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC118" s="81" t="inlineStr">
+        <is>
+          <t>Cycles 14% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B119" s="43" t="inlineStr">
+        <is>
+          <t>Lever Action</t>
+        </is>
+      </c>
+      <c r="C119" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D119" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E119" s="43" t="inlineStr">
+        <is>
+          <t>Triple Cycle</t>
+        </is>
+      </c>
+      <c r="F119" s="56">
+        <f>F59</f>
+        <v/>
+      </c>
+      <c r="G119" s="57" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H119" s="57" t="n"/>
+      <c r="I119" s="57" t="n"/>
+      <c r="J119" s="57" t="n"/>
+      <c r="K119" s="57" t="n"/>
+      <c r="L119" s="57" t="n"/>
+      <c r="M119" s="57" t="n"/>
+      <c r="N119" s="57" t="n"/>
+      <c r="O119" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="P119" s="57" t="n"/>
+      <c r="Q119" s="57" t="n"/>
+      <c r="R119" s="57" t="n"/>
+      <c r="S119" s="57" t="n"/>
+      <c r="T119" s="57" t="n"/>
+      <c r="U119" s="57" t="n"/>
+      <c r="V119" s="57" t="n"/>
+      <c r="W119" s="57" t="n"/>
+      <c r="X119" s="57" t="n"/>
+      <c r="Y119" s="57" t="n"/>
+      <c r="Z119" s="57" t="n"/>
+      <c r="AA119" s="57" t="n"/>
+      <c r="AB119" s="57" t="n"/>
+      <c r="AC119" s="57" t="n"/>
+      <c r="AD119" s="57" t="n"/>
+      <c r="AE119" s="57" t="n"/>
+      <c r="AF119" s="57" t="n"/>
+      <c r="AG119" s="57" t="n"/>
+      <c r="AH119" s="57" t="n"/>
+      <c r="AI119" s="57" t="n"/>
+      <c r="BB119" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC119" s="81" t="inlineStr">
+        <is>
+          <t>3-round bursts, cycling 33% faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B120" s="43" t="inlineStr">
+        <is>
+          <t>Lever Action</t>
+        </is>
+      </c>
+      <c r="C120" s="43" t="inlineStr">
+        <is>
+          <t>handling</t>
+        </is>
+      </c>
+      <c r="D120" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E120" s="43" t="inlineStr">
+        <is>
+          <t>Steady Lever</t>
+        </is>
+      </c>
+      <c r="F120" s="56">
+        <f>F59</f>
+        <v/>
+      </c>
+      <c r="G120" s="57" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H120" s="57" t="n"/>
+      <c r="I120" s="57" t="n"/>
+      <c r="J120" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K120" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L120" s="57" t="n"/>
+      <c r="M120" s="57" t="n"/>
+      <c r="N120" s="57" t="n"/>
+      <c r="O120" s="57" t="n"/>
+      <c r="P120" s="57" t="n"/>
+      <c r="Q120" s="57" t="n"/>
+      <c r="R120" s="57" t="n"/>
+      <c r="S120" s="57" t="n"/>
+      <c r="T120" s="57" t="n"/>
+      <c r="U120" s="57" t="n"/>
+      <c r="V120" s="57" t="n"/>
+      <c r="W120" s="57" t="n"/>
+      <c r="X120" s="57" t="n"/>
+      <c r="Y120" s="57" t="n"/>
+      <c r="Z120" s="57" t="n"/>
+      <c r="AA120" s="57" t="n"/>
+      <c r="AB120" s="57" t="n"/>
+      <c r="AC120" s="57" t="n"/>
+      <c r="AD120" s="57" t="n"/>
+      <c r="AE120" s="57" t="n"/>
+      <c r="AF120" s="57" t="n"/>
+      <c r="AG120" s="57" t="n"/>
+      <c r="AH120" s="57" t="n"/>
+      <c r="AI120" s="57" t="n"/>
+      <c r="BB120" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC120" s="81" t="inlineStr">
+        <is>
+          <t>10% faster, half the kick, tighter aim</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B121" s="43" t="inlineStr">
+        <is>
+          <t>Muzzle</t>
+        </is>
+      </c>
+      <c r="C121" s="43" t="inlineStr">
+        <is>
+          <t>protective rounds</t>
+        </is>
+      </c>
+      <c r="D121" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E121" s="43" t="inlineStr">
+        <is>
+          <t>Quick Dose</t>
+        </is>
+      </c>
+      <c r="F121" s="56">
+        <f>F63</f>
+        <v/>
+      </c>
+      <c r="G121" s="57" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H121" s="57" t="n"/>
+      <c r="I121" s="57" t="n"/>
+      <c r="J121" s="57" t="n"/>
+      <c r="K121" s="57" t="n"/>
+      <c r="L121" s="57" t="n"/>
+      <c r="M121" s="57" t="n"/>
+      <c r="N121" s="57" t="n"/>
+      <c r="O121" s="57" t="n"/>
+      <c r="P121" s="57" t="n"/>
+      <c r="Q121" s="57" t="n"/>
+      <c r="R121" s="57" t="n"/>
+      <c r="S121" s="57" t="n"/>
+      <c r="T121" s="57" t="n"/>
+      <c r="U121" s="57" t="n"/>
+      <c r="V121" s="57" t="n"/>
+      <c r="W121" s="57" t="n"/>
+      <c r="X121" s="57" t="n"/>
+      <c r="Y121" s="57" t="n"/>
+      <c r="Z121" s="57" t="n"/>
+      <c r="AA121" s="57" t="n"/>
+      <c r="AB121" s="57" t="n"/>
+      <c r="AC121" s="57" t="n"/>
+      <c r="AD121" s="57" t="n"/>
+      <c r="AE121" s="57" t="n"/>
+      <c r="AF121" s="57" t="n"/>
+      <c r="AG121" s="57" t="n"/>
+      <c r="AH121" s="57" t="n"/>
+      <c r="AI121" s="57" t="n"/>
+      <c r="AO121" s="81" t="n"/>
+      <c r="AP121" s="81" t="n"/>
+      <c r="AQ121" s="81" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB121" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC121" s="81" t="inlineStr">
+        <is>
+          <t>Fire 12% faster; jaws locked 2.6 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B122" s="43" t="inlineStr">
+        <is>
+          <t>Muzzle</t>
+        </is>
+      </c>
+      <c r="C122" s="43" t="inlineStr">
+        <is>
+          <t>protective rounds</t>
+        </is>
+      </c>
+      <c r="D122" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E122" s="43" t="inlineStr">
+        <is>
+          <t>Strap Toss</t>
+        </is>
+      </c>
+      <c r="F122" s="56">
+        <f>F63</f>
+        <v/>
+      </c>
+      <c r="G122" s="57" t="n"/>
+      <c r="H122" s="57" t="n"/>
+      <c r="I122" s="57" t="n"/>
+      <c r="J122" s="57" t="n"/>
+      <c r="K122" s="57" t="n"/>
+      <c r="L122" s="57" t="n"/>
+      <c r="M122" s="57" t="n"/>
+      <c r="N122" s="57" t="n"/>
+      <c r="O122" s="57" t="n"/>
+      <c r="P122" s="57" t="n"/>
+      <c r="Q122" s="57" t="n"/>
+      <c r="R122" s="57" t="n"/>
+      <c r="S122" s="57" t="n"/>
+      <c r="T122" s="57" t="n"/>
+      <c r="U122" s="57" t="n"/>
+      <c r="V122" s="57" t="n"/>
+      <c r="W122" s="57" t="n"/>
+      <c r="X122" s="57" t="n"/>
+      <c r="Y122" s="57" t="n"/>
+      <c r="Z122" s="57" t="n"/>
+      <c r="AA122" s="57" t="n"/>
+      <c r="AB122" s="57" t="n"/>
+      <c r="AC122" s="57" t="n"/>
+      <c r="AD122" s="57" t="n"/>
+      <c r="AE122" s="57" t="n"/>
+      <c r="AF122" s="57" t="n"/>
+      <c r="AG122" s="57" t="n"/>
+      <c r="AH122" s="57" t="n"/>
+      <c r="AI122" s="57" t="n"/>
+      <c r="AO122" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP122" s="81" t="n"/>
+      <c r="AQ122" s="81" t="n"/>
+      <c r="AR122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB122" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC122" s="81" t="inlineStr">
+        <is>
+          <t>Lock jumps 2 studs; hits slow dinos 40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B123" s="43" t="inlineStr">
+        <is>
+          <t>Muzzle</t>
+        </is>
+      </c>
+      <c r="C123" s="43" t="inlineStr">
+        <is>
+          <t>protective rounds</t>
+        </is>
+      </c>
+      <c r="D123" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E123" s="43" t="inlineStr">
+        <is>
+          <t>Heavy Lids</t>
+        </is>
+      </c>
+      <c r="F123" s="56">
+        <f>F64</f>
+        <v/>
+      </c>
+      <c r="G123" s="57" t="n"/>
+      <c r="H123" s="57" t="n"/>
+      <c r="I123" s="57" t="n"/>
+      <c r="J123" s="57" t="n"/>
+      <c r="K123" s="57" t="n"/>
+      <c r="L123" s="57" t="n"/>
+      <c r="M123" s="57" t="n"/>
+      <c r="N123" s="57" t="n"/>
+      <c r="O123" s="57" t="n"/>
+      <c r="P123" s="57" t="n"/>
+      <c r="Q123" s="57" t="n"/>
+      <c r="R123" s="57" t="n"/>
+      <c r="S123" s="57" t="n"/>
+      <c r="T123" s="57" t="n"/>
+      <c r="U123" s="57" t="n"/>
+      <c r="V123" s="57" t="n"/>
+      <c r="W123" s="57" t="n"/>
+      <c r="X123" s="57" t="n"/>
+      <c r="Y123" s="57" t="n"/>
+      <c r="Z123" s="57" t="n"/>
+      <c r="AA123" s="57" t="n"/>
+      <c r="AB123" s="57" t="n"/>
+      <c r="AC123" s="57" t="n"/>
+      <c r="AD123" s="57" t="n"/>
+      <c r="AE123" s="57" t="n"/>
+      <c r="AF123" s="57" t="n"/>
+      <c r="AG123" s="57" t="n"/>
+      <c r="AH123" s="57" t="n"/>
+      <c r="AI123" s="57" t="n"/>
+      <c r="AO123" s="81" t="n"/>
+      <c r="AP123" s="81" t="n"/>
+      <c r="AQ123" s="81" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR123" s="81" t="n"/>
+      <c r="BB123" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC123" s="81" t="inlineStr">
+        <is>
+          <t>Locked jaws stay shut 4.2 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="43" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="B124" s="43" t="inlineStr">
+        <is>
+          <t>Muzzle</t>
+        </is>
+      </c>
+      <c r="C124" s="43" t="inlineStr">
+        <is>
+          <t>protective rounds</t>
+        </is>
+      </c>
+      <c r="D124" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E124" s="43" t="inlineStr">
+        <is>
+          <t>Drowsy Cloud</t>
+        </is>
+      </c>
+      <c r="F124" s="56">
+        <f>F64</f>
+        <v/>
+      </c>
+      <c r="G124" s="57" t="n"/>
+      <c r="H124" s="57" t="n"/>
+      <c r="I124" s="57" t="n"/>
+      <c r="J124" s="57" t="n"/>
+      <c r="K124" s="57" t="n"/>
+      <c r="L124" s="57" t="n"/>
+      <c r="M124" s="57" t="n"/>
+      <c r="N124" s="57" t="n"/>
+      <c r="O124" s="57" t="n"/>
+      <c r="P124" s="57" t="n"/>
+      <c r="Q124" s="57" t="n"/>
+      <c r="R124" s="57" t="n"/>
+      <c r="S124" s="57" t="n"/>
+      <c r="T124" s="57" t="n"/>
+      <c r="U124" s="57" t="n"/>
+      <c r="V124" s="57" t="n"/>
+      <c r="W124" s="57" t="n"/>
+      <c r="X124" s="57" t="n"/>
+      <c r="Y124" s="57" t="n"/>
+      <c r="Z124" s="57" t="n"/>
+      <c r="AA124" s="57" t="n"/>
+      <c r="AB124" s="57" t="n"/>
+      <c r="AC124" s="57" t="n"/>
+      <c r="AD124" s="57" t="n"/>
+      <c r="AE124" s="57" t="n"/>
+      <c r="AF124" s="57" t="n"/>
+      <c r="AG124" s="57" t="n"/>
+      <c r="AH124" s="57" t="n"/>
+      <c r="AI124" s="57" t="n"/>
+      <c r="AO124" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP124" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ124" s="81" t="n"/>
+      <c r="AR124" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB124" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC124" s="81" t="inlineStr">
+        <is>
+          <t>Lock spreads 4 studs; hits slow 40% for 2 s</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9499,7 +9499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E189"/>
+  <dimension ref="A1:E190"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -12300,6 +12300,21 @@
       <c r="C189" s="81" t="inlineStr">
         <is>
           <t>fires a Fire Bomblets shell lights at most (first generation first, then the next); the rest of its bomblets still hit (Fire Bomblets, Firecracker Rain; PLAN T115b, #306)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Pool sting reach (studs)</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>12</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>studs: an on-track Raider tower (Bog Boots) stings a raider within this of the nearest point of its pool (its current length, Tar Lake included), not the whole pool; off-track Raider towers keep their range (PLAN T120b, #321)</t>
         </is>
       </c>
     </row>
@@ -37632,7 +37647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC124"/>
+  <dimension ref="A1:BF124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="90" min="1" max="1"/>
@@ -37973,6 +37988,11 @@
           <t>Heal regen (s)</t>
         </is>
       </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>One round per trigger</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="43" t="inlineStr">
@@ -44960,6 +44980,11 @@
           <t>Two slugs per pump, each through 4</t>
         </is>
       </c>
+      <c r="BF104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="43" t="inlineStr">
@@ -45173,7 +45198,7 @@
       </c>
       <c r="BC107" s="81" t="inlineStr">
         <is>
-          <t>Dragon's Breath bursts for 70% of a shot</t>
+          <t>Dragon's Breath bursts for 90% of a shot</t>
         </is>
       </c>
     </row>
@@ -45761,10 +45786,10 @@
           <t>Everything healed regains 2 HP/s for 8 s</t>
         </is>
       </c>
-      <c r="BD115" t="n">
+      <c r="BD115" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="BE115" t="n">
+      <c r="BE115" s="81" t="n">
         <v>8</v>
       </c>
     </row>
@@ -46266,7 +46291,7 @@
       </c>
       <c r="AP122" s="81" t="n"/>
       <c r="AQ122" s="81" t="n"/>
-      <c r="AR122" t="n">
+      <c r="AR122" s="81" t="n">
         <v>2</v>
       </c>
       <c r="BB122" s="81" t="inlineStr">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9499,7 +9499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E190"/>
+  <dimension ref="A1:E199"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -12304,17 +12304,130 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
+      <c r="A190" s="81" t="inlineStr">
         <is>
           <t>Pool sting reach (studs)</t>
         </is>
       </c>
-      <c r="B190" t="n">
+      <c r="B190" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="C190" t="inlineStr">
+      <c r="C190" s="81" t="inlineStr">
         <is>
           <t>studs: an on-track Raider tower (Bog Boots) stings a raider within this of the nearest point of its pool (its current length, Tar Lake included), not the whole pool; off-track Raider towers keep their range (PLAN T120b, #321)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191"/>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>4× TOWERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Boss hard stop x</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>x a 4x hard stop (entomb, walls, nets, holds) on a boss unless the option says otherwise; hard stops never stack, the longer remaining wins (PLAN 9g common rule 4, #316)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Small size</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>2</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>"small dinos" = a non-boss at its last this many sizes (#316)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Wall min bunch</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>6</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>dinos in an area that set off a once-a-round effect at once (Shared/AutoFire, #316)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Wall reach (studs)</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>10</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>studs of track around a point counted as one bunch (Shared/AutoFire: the densest bunch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Take-down mark radius</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>6</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>studs: a Take-down mark % take-down marks the dinos this near (Mark duration 3 s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Round seconds (model)</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>50</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>s a round lasts in the value.py 4x metrics (per-round effects and cash a round; #313)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Walker cap per side</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>24</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>walkers (raptors, later paratroopers, rangers) a side may have out; past it none spawn (Shared/Walker, #315)</t>
         </is>
       </c>
     </row>
@@ -37988,7 +38101,7 @@
           <t>Heal regen (s)</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BF4" s="81" t="inlineStr">
         <is>
           <t>One round per trigger</t>
         </is>
@@ -44980,7 +45093,7 @@
           <t>Two slugs per pump, each through 4</t>
         </is>
       </c>
-      <c r="BF104" t="inlineStr">
+      <c r="BF104" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -466,7 +466,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -793,6 +793,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9499,7 +9500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E199"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -12318,116 +12319,243 @@
         </is>
       </c>
     </row>
-    <row r="191"/>
     <row r="192">
-      <c r="A192" t="inlineStr">
+      <c r="A192" s="81" t="inlineStr">
         <is>
           <t>4× TOWERS</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
+      <c r="A193" s="81" t="inlineStr">
         <is>
           <t>Boss hard stop x</t>
         </is>
       </c>
-      <c r="B193" t="n">
+      <c r="B193" s="81" t="n">
         <v>0.5</v>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="C193" s="81" t="inlineStr">
         <is>
           <t>x a 4x hard stop (entomb, walls, nets, holds) on a boss unless the option says otherwise; hard stops never stack, the longer remaining wins (PLAN 9g common rule 4, #316)</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="81" t="inlineStr">
         <is>
           <t>Small size</t>
         </is>
       </c>
-      <c r="B194" t="n">
+      <c r="B194" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="C194" t="inlineStr">
+      <c r="C194" s="81" t="inlineStr">
         <is>
           <t>"small dinos" = a non-boss at its last this many sizes (#316)</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
+      <c r="A195" s="81" t="inlineStr">
         <is>
           <t>Wall min bunch</t>
         </is>
       </c>
-      <c r="B195" t="n">
+      <c r="B195" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C195" s="81" t="inlineStr">
         <is>
           <t>dinos in an area that set off a once-a-round effect at once (Shared/AutoFire, #316)</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
+      <c r="A196" s="81" t="inlineStr">
         <is>
           <t>Wall reach (studs)</t>
         </is>
       </c>
-      <c r="B196" t="n">
+      <c r="B196" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="C196" t="inlineStr">
+      <c r="C196" s="81" t="inlineStr">
         <is>
           <t>studs of track around a point counted as one bunch (Shared/AutoFire: the densest bunch)</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
+      <c r="A197" s="81" t="inlineStr">
         <is>
           <t>Take-down mark radius</t>
         </is>
       </c>
-      <c r="B197" t="n">
+      <c r="B197" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="C197" s="81" t="inlineStr">
         <is>
           <t>studs: a Take-down mark % take-down marks the dinos this near (Mark duration 3 s)</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
+      <c r="A198" s="81" t="inlineStr">
         <is>
           <t>Round seconds (model)</t>
         </is>
       </c>
-      <c r="B198" t="n">
+      <c r="B198" s="81" t="n">
         <v>50</v>
       </c>
-      <c r="C198" t="inlineStr">
+      <c r="C198" s="81" t="inlineStr">
         <is>
           <t>s a round lasts in the value.py 4x metrics (per-round effects and cash a round; #313)</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
+      <c r="A199" s="81" t="inlineStr">
         <is>
           <t>Walker cap per side</t>
         </is>
       </c>
-      <c r="B199" t="n">
+      <c r="B199" s="81" t="n">
         <v>24</v>
       </c>
-      <c r="C199" t="inlineStr">
+      <c r="C199" s="81" t="inlineStr">
         <is>
           <t>walkers (raptors, later paratroopers, rangers) a side may have out; past it none spawn (Shared/Walker, #315)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200"/>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>AMBER RESIN CANNON</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Resin hits to entomb</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>6</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>resin a full-HP dino needs before it is entombed (x Entomb hits x x its HP-left share, at least 1; Shared/Resin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Entomb base (s)</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>s an entomb holds when the build sets no Entomb (s) (a hard stop; bosses x Boss hard stop x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Resin hit slow %</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>20</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>% slower after each resin hit (not bosses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Resin hit slow (s)</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>1</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>s the resin-hit slow lasts</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Boss entomb every (s)</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>10</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>s: a boss is entombed at most once per this, per boss</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Spread reach (studs)</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>6</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>studs: Spreading Amber takes the nearest dinos this close</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Sticky bed reach (studs)</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>6</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>studs: Sticky Bed slows dinos this close to an entombed one</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Fossil Fuel cap %</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>30</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>% attack speed Fossil Fuel's stack reaches at most (per round)</t>
         </is>
       </c>
     </row>
@@ -12451,7 +12579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -12644,6 +12772,11 @@
           <t>Harpoons</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Resin</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -13425,6 +13558,78 @@
         <v>0</v>
       </c>
       <c r="X18" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Control: resin slows, entombs and fossilizes</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>800</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <f>D19*E19*F19</f>
+        <v/>
+      </c>
+      <c r="H19" t="n">
+        <v>18</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Resin globs: slows, entombs (hard stop), fossils. TOWERS_LATER.md.</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>500</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -13450,7 +13655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU301"/>
+  <dimension ref="A1:DM328"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -14083,6 +14288,96 @@
       <c r="CU4" s="81" t="inlineStr">
         <is>
           <t>Targets biggest</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>Entomb (s)</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>Entomb hits x</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>Entomb amp %</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>Entomb spread</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>Entomb slow %</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>Entomb all every (s)</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>Boss entomb (s)</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>Send back (studs)</t>
+        </is>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>Fossil below %</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>Fossil rate %</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>Bounty fossils x</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>Heart every (fossils)</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>Seal (s)</t>
+        </is>
+      </c>
+      <c r="DI4" t="inlineStr">
+        <is>
+          <t>Seal every (s)</t>
+        </is>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>Seal heal %</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>Reflect damage</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr">
+        <is>
+          <t>Wall (s)</t>
+        </is>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>Take-down mark %</t>
         </is>
       </c>
     </row>
@@ -37153,6 +37448,1658 @@
         <is>
           <t>Faster volleys of burning bolts</t>
         </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Entomb</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>1</v>
+      </c>
+      <c r="E302">
+        <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D302),0)</f>
+        <v/>
+      </c>
+      <c r="F302">
+        <f>'Towers'!$C$19+E302</f>
+        <v/>
+      </c>
+      <c r="G302" s="110" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H302" s="110" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I302" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J302">
+        <f>'Towers'!$G$19*G302*H302*I302</f>
+        <v/>
+      </c>
+      <c r="K302">
+        <f>IF(J302=0,0,F302/J302)</f>
+        <v/>
+      </c>
+      <c r="L302" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>Thick Resin</t>
+        </is>
+      </c>
+      <c r="CW302" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Entomb</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>2</v>
+      </c>
+      <c r="E303">
+        <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D303),0)</f>
+        <v/>
+      </c>
+      <c r="F303">
+        <f>F302+E303</f>
+        <v/>
+      </c>
+      <c r="G303" s="110" t="n">
+        <v>2</v>
+      </c>
+      <c r="H303" s="110" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I303" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J303">
+        <f>'Towers'!$G$19*G303*H303*I303</f>
+        <v/>
+      </c>
+      <c r="K303">
+        <f>IF(J303=0,0,F303/J303)</f>
+        <v/>
+      </c>
+      <c r="L303" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>Quick Set</t>
+        </is>
+      </c>
+      <c r="CW303" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Entomb</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>3</v>
+      </c>
+      <c r="E304">
+        <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D304),0)</f>
+        <v/>
+      </c>
+      <c r="F304">
+        <f>F303+E304</f>
+        <v/>
+      </c>
+      <c r="G304" s="110" t="n">
+        <v>3</v>
+      </c>
+      <c r="H304" s="110" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I304" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J304">
+        <f>'Towers'!$G$19*G304*H304*I304</f>
+        <v/>
+      </c>
+      <c r="K304">
+        <f>IF(J304=0,0,F304/J304)</f>
+        <v/>
+      </c>
+      <c r="L304" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>Amber Tomb</t>
+        </is>
+      </c>
+      <c r="CV304" t="n">
+        <v>2</v>
+      </c>
+      <c r="CW304" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Entomb</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>4</v>
+      </c>
+      <c r="E305">
+        <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D305),0)</f>
+        <v/>
+      </c>
+      <c r="F305">
+        <f>F304+E305</f>
+        <v/>
+      </c>
+      <c r="G305" s="110" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H305" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I305" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J305">
+        <f>J304*G305*H305*I305</f>
+        <v/>
+      </c>
+      <c r="K305">
+        <f>IF(J305=0,0,F305/J305)</f>
+        <v/>
+      </c>
+      <c r="L305" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>Hardened Amber</t>
+        </is>
+      </c>
+      <c r="CI305" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ305" t="inlineStr">
+        <is>
+          <t>Stuck dinos take +30% from everything</t>
+        </is>
+      </c>
+      <c r="CX305" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Entomb</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>5</v>
+      </c>
+      <c r="E306">
+        <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D306),0)</f>
+        <v/>
+      </c>
+      <c r="F306">
+        <f>F305+E306</f>
+        <v/>
+      </c>
+      <c r="G306" s="110" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H306" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I306" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J306">
+        <f>J305*G306*H306*I306</f>
+        <v/>
+      </c>
+      <c r="K306">
+        <f>IF(J306=0,0,F306/J306)</f>
+        <v/>
+      </c>
+      <c r="L306" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Amber Age</t>
+        </is>
+      </c>
+      <c r="CI306" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ306" t="inlineStr">
+        <is>
+          <t>Every 12 s, everything in range is stuck</t>
+        </is>
+      </c>
+      <c r="DA306" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Fossilize</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>1</v>
+      </c>
+      <c r="E307">
+        <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D307),0)</f>
+        <v/>
+      </c>
+      <c r="F307">
+        <f>'Towers'!$C$19+E307</f>
+        <v/>
+      </c>
+      <c r="G307" s="110" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H307" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I307" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J307">
+        <f>'Towers'!$G$19*G307*H307*I307</f>
+        <v/>
+      </c>
+      <c r="K307">
+        <f>IF(J307=0,0,F307/J307)</f>
+        <v/>
+      </c>
+      <c r="L307" s="110" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>Collector's Eye</t>
+        </is>
+      </c>
+      <c r="CD307" t="n">
+        <v>4</v>
+      </c>
+      <c r="DD307" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Fossilize</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>2</v>
+      </c>
+      <c r="E308">
+        <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D308),0)</f>
+        <v/>
+      </c>
+      <c r="F308">
+        <f>F307+E308</f>
+        <v/>
+      </c>
+      <c r="G308" s="110" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H308" s="110" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I308" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J308">
+        <f>'Towers'!$G$19*G308*H308*I308</f>
+        <v/>
+      </c>
+      <c r="K308">
+        <f>IF(J308=0,0,F308/J308)</f>
+        <v/>
+      </c>
+      <c r="L308" s="110" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>Rare Find</t>
+        </is>
+      </c>
+      <c r="CD308" t="n">
+        <v>10</v>
+      </c>
+      <c r="DD308" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Fossilize</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>3</v>
+      </c>
+      <c r="E309">
+        <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D309),0)</f>
+        <v/>
+      </c>
+      <c r="F309">
+        <f>F308+E309</f>
+        <v/>
+      </c>
+      <c r="G309" s="110" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H309" s="110" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I309" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J309">
+        <f>'Towers'!$G$19*G309*H309*I309</f>
+        <v/>
+      </c>
+      <c r="K309">
+        <f>IF(J309=0,0,F309/J309)</f>
+        <v/>
+      </c>
+      <c r="L309" s="110" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Fossil Record</t>
+        </is>
+      </c>
+      <c r="CD309" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW309" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DD309" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Fossilize</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>4</v>
+      </c>
+      <c r="E310">
+        <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D310),0)</f>
+        <v/>
+      </c>
+      <c r="F310">
+        <f>F309+E310</f>
+        <v/>
+      </c>
+      <c r="G310" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H310" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I310" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J310">
+        <f>J309*G310*H310*I310</f>
+        <v/>
+      </c>
+      <c r="K310">
+        <f>IF(J310=0,0,F310/J310)</f>
+        <v/>
+      </c>
+      <c r="L310" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>Museum Piece</t>
+        </is>
+      </c>
+      <c r="CD310" t="n">
+        <v>32</v>
+      </c>
+      <c r="CI310" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ310" t="inlineStr">
+        <is>
+          <t>Fossils pay double cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Fossilize</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>5</v>
+      </c>
+      <c r="E311">
+        <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D311),0)</f>
+        <v/>
+      </c>
+      <c r="F311">
+        <f>F310+E311</f>
+        <v/>
+      </c>
+      <c r="G311" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H311" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I311" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J311">
+        <f>J310*G311*H311*I311</f>
+        <v/>
+      </c>
+      <c r="K311">
+        <f>IF(J311=0,0,F311/J311)</f>
+        <v/>
+      </c>
+      <c r="L311" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>Fossil Fuel</t>
+        </is>
+      </c>
+      <c r="CI311" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ311" t="inlineStr">
+        <is>
+          <t>Each fossil speeds up nearby towers</t>
+        </is>
+      </c>
+      <c r="DD311" t="n">
+        <v>25</v>
+      </c>
+      <c r="DE311" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Resin Shell</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>1</v>
+      </c>
+      <c r="E312">
+        <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D312),0)</f>
+        <v/>
+      </c>
+      <c r="F312">
+        <f>'Towers'!$C$19+E312</f>
+        <v/>
+      </c>
+      <c r="G312" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H312" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I312" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J312">
+        <f>'Towers'!$G$19*G312*H312*I312</f>
+        <v/>
+      </c>
+      <c r="K312">
+        <f>IF(J312=0,0,F312/J312)</f>
+        <v/>
+      </c>
+      <c r="L312" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>Coat of Resin</t>
+        </is>
+      </c>
+      <c r="BH312" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Resin Shell</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>2</v>
+      </c>
+      <c r="E313">
+        <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D313),0)</f>
+        <v/>
+      </c>
+      <c r="F313">
+        <f>F312+E313</f>
+        <v/>
+      </c>
+      <c r="G313" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H313" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I313" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J313">
+        <f>'Towers'!$G$19*G313*H313*I313</f>
+        <v/>
+      </c>
+      <c r="K313">
+        <f>IF(J313=0,0,F313/J313)</f>
+        <v/>
+      </c>
+      <c r="L313" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>Sticky Armour</t>
+        </is>
+      </c>
+      <c r="AU313" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH313" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Resin Shell</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>3</v>
+      </c>
+      <c r="E314">
+        <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D314),0)</f>
+        <v/>
+      </c>
+      <c r="F314">
+        <f>F313+E314</f>
+        <v/>
+      </c>
+      <c r="G314" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H314" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I314" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J314">
+        <f>'Towers'!$G$19*G314*H314*I314</f>
+        <v/>
+      </c>
+      <c r="K314">
+        <f>IF(J314=0,0,F314/J314)</f>
+        <v/>
+      </c>
+      <c r="L314" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>Amber Shield</t>
+        </is>
+      </c>
+      <c r="AU314" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH314" t="n">
+        <v>15</v>
+      </c>
+      <c r="DH314" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Resin Shell</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>4</v>
+      </c>
+      <c r="E315">
+        <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D315),0)</f>
+        <v/>
+      </c>
+      <c r="F315">
+        <f>F314+E315</f>
+        <v/>
+      </c>
+      <c r="G315" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H315" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I315" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J315">
+        <f>J314*G315*H315*I315</f>
+        <v/>
+      </c>
+      <c r="K315">
+        <f>IF(J315=0,0,F315/J315)</f>
+        <v/>
+      </c>
+      <c r="L315" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>Self-Sealing</t>
+        </is>
+      </c>
+      <c r="CI315" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ315" t="inlineStr">
+        <is>
+          <t>Sealed towers heal 30% when the shell breaks</t>
+        </is>
+      </c>
+      <c r="DJ315" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Resin Shell</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>5</v>
+      </c>
+      <c r="E316">
+        <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D316),0)</f>
+        <v/>
+      </c>
+      <c r="F316">
+        <f>F315+E316</f>
+        <v/>
+      </c>
+      <c r="G316" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H316" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I316" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J316">
+        <f>J315*G316*H316*I316</f>
+        <v/>
+      </c>
+      <c r="K316">
+        <f>IF(J316=0,0,F316/J316)</f>
+        <v/>
+      </c>
+      <c r="L316" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Amber Fortress</t>
+        </is>
+      </c>
+      <c r="CI316" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ316" t="inlineStr">
+        <is>
+          <t>Nearby towers can't be knocked out (20 s each)</t>
+        </is>
+      </c>
+      <c r="DI316" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Entomb</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>4</v>
+      </c>
+      <c r="E317">
+        <f>E305</f>
+        <v/>
+      </c>
+      <c r="F317">
+        <f>F305</f>
+        <v/>
+      </c>
+      <c r="G317" s="110" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H317" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I317" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L317" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Spreading Amber</t>
+        </is>
+      </c>
+      <c r="CI317" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ317" t="inlineStr">
+        <is>
+          <t>The amber jumps to the next dino</t>
+        </is>
+      </c>
+      <c r="CY317" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Entomb</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>4</v>
+      </c>
+      <c r="E318">
+        <f>E305</f>
+        <v/>
+      </c>
+      <c r="F318">
+        <f>F305</f>
+        <v/>
+      </c>
+      <c r="G318" s="110" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H318" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I318" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L318" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Sticky Bed</t>
+        </is>
+      </c>
+      <c r="CI318" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ318" t="inlineStr">
+        <is>
+          <t>Dinos walking past a stuck one slow 30%</t>
+        </is>
+      </c>
+      <c r="CZ318" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Entomb</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>5</v>
+      </c>
+      <c r="E319">
+        <f>E306</f>
+        <v/>
+      </c>
+      <c r="F319">
+        <f>F306</f>
+        <v/>
+      </c>
+      <c r="G319" s="110" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H319" s="110" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I319" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L319" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>Living Amber</t>
+        </is>
+      </c>
+      <c r="CI319" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ319" t="inlineStr">
+        <is>
+          <t>Traps a boss 3 s; others stay stuck longer</t>
+        </is>
+      </c>
+      <c r="CV319" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DB319" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Entomb</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>5</v>
+      </c>
+      <c r="E320">
+        <f>E306</f>
+        <v/>
+      </c>
+      <c r="F320">
+        <f>F306</f>
+        <v/>
+      </c>
+      <c r="G320" s="110" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H320" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I320" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L320" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>Time Capsule</t>
+        </is>
+      </c>
+      <c r="CI320" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ320" t="inlineStr">
+        <is>
+          <t>Stuck dinos are sent 12 studs back</t>
+        </is>
+      </c>
+      <c r="DC320" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Fossilize</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>4</v>
+      </c>
+      <c r="E321">
+        <f>E310</f>
+        <v/>
+      </c>
+      <c r="F321">
+        <f>F310</f>
+        <v/>
+      </c>
+      <c r="G321" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H321" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I321" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L321" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>Dig Crew</t>
+        </is>
+      </c>
+      <c r="CE321" t="n">
+        <v>25</v>
+      </c>
+      <c r="CI321" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ321" t="inlineStr">
+        <is>
+          <t>A fossil drops a cash chest</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Fossilize</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>4</v>
+      </c>
+      <c r="E322">
+        <f>E310</f>
+        <v/>
+      </c>
+      <c r="F322">
+        <f>F310</f>
+        <v/>
+      </c>
+      <c r="G322" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H322" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I322" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L322" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>Bone Dust</t>
+        </is>
+      </c>
+      <c r="CI322" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ322" t="inlineStr">
+        <is>
+          <t>Fossils mark nearby dinos +15%</t>
+        </is>
+      </c>
+      <c r="DM322" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Fossilize</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>5</v>
+      </c>
+      <c r="E323">
+        <f>E311</f>
+        <v/>
+      </c>
+      <c r="F323">
+        <f>F311</f>
+        <v/>
+      </c>
+      <c r="G323" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H323" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I323" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L323" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Prize Fossils</t>
+        </is>
+      </c>
+      <c r="CI323" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ323" t="inlineStr">
+        <is>
+          <t>More fossils; each counts double for bounties</t>
+        </is>
+      </c>
+      <c r="DD323" t="n">
+        <v>30</v>
+      </c>
+      <c r="DF323" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Fossilize</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>5</v>
+      </c>
+      <c r="E324">
+        <f>E311</f>
+        <v/>
+      </c>
+      <c r="F324">
+        <f>F311</f>
+        <v/>
+      </c>
+      <c r="G324" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H324" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I324" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L324" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Amber Heart</t>
+        </is>
+      </c>
+      <c r="CI324" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ324" t="inlineStr">
+        <is>
+          <t>Every 15th fossil freezes your whole side 1 s</t>
+        </is>
+      </c>
+      <c r="DG324" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Resin Shell</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>4</v>
+      </c>
+      <c r="E325">
+        <f>E315</f>
+        <v/>
+      </c>
+      <c r="F325">
+        <f>F315</f>
+        <v/>
+      </c>
+      <c r="G325" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H325" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I325" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L325" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>Raider Glue</t>
+        </is>
+      </c>
+      <c r="CI325" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ325" t="inlineStr">
+        <is>
+          <t>Raiders and biters near your towers slow down</t>
+        </is>
+      </c>
+      <c r="CK325" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CL325" t="n">
+        <v>20</v>
+      </c>
+      <c r="CM325" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP325" t="n">
+        <v>25</v>
+      </c>
+      <c r="CQ325" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Resin Shell</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>4</v>
+      </c>
+      <c r="E326">
+        <f>E315</f>
+        <v/>
+      </c>
+      <c r="F326">
+        <f>F315</f>
+        <v/>
+      </c>
+      <c r="G326" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H326" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I326" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L326" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Sticky Thorns</t>
+        </is>
+      </c>
+      <c r="AV326" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI326" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ326" t="inlineStr">
+        <is>
+          <t>Biters get slowed and take 5 damage</t>
+        </is>
+      </c>
+      <c r="CP326" t="n">
+        <v>15</v>
+      </c>
+      <c r="CQ326" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Resin Shell</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>5</v>
+      </c>
+      <c r="E327">
+        <f>E316</f>
+        <v/>
+      </c>
+      <c r="F327">
+        <f>F316</f>
+        <v/>
+      </c>
+      <c r="G327" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H327" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I327" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L327" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>Resin Wall</t>
+        </is>
+      </c>
+      <c r="CI327" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ327" t="inlineStr">
+        <is>
+          <t>Once a round, an amber wall holds every dino 3 s</t>
+        </is>
+      </c>
+      <c r="DL327" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Amber Resin Cannon</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Resin Shell</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>5</v>
+      </c>
+      <c r="E328">
+        <f>E316</f>
+        <v/>
+      </c>
+      <c r="F328">
+        <f>F316</f>
+        <v/>
+      </c>
+      <c r="G328" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H328" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I328" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L328" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>Amber Mirror</t>
+        </is>
+      </c>
+      <c r="BR328" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI328" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ328" t="inlineStr">
+        <is>
+          <t>Throws at your towers bounce back</t>
+        </is>
+      </c>
+      <c r="DK328" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9500,7 +9500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:E228"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -12431,131 +12431,407 @@
         </is>
       </c>
     </row>
-    <row r="200"/>
     <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="A201" s="81" t="inlineStr">
         <is>
           <t>AMBER RESIN CANNON</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
+      <c r="A202" s="81" t="inlineStr">
         <is>
           <t>Resin hits to entomb</t>
         </is>
       </c>
-      <c r="B202" t="n">
+      <c r="B202" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="C202" s="81" t="inlineStr">
         <is>
           <t>resin a full-HP dino needs before it is entombed (x Entomb hits x x its HP-left share, at least 1; Shared/Resin)</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
+      <c r="A203" s="81" t="inlineStr">
         <is>
           <t>Entomb base (s)</t>
         </is>
       </c>
-      <c r="B203" t="n">
+      <c r="B203" s="81" t="n">
         <v>0.8</v>
       </c>
-      <c r="C203" t="inlineStr">
+      <c r="C203" s="81" t="inlineStr">
         <is>
           <t>s an entomb holds when the build sets no Entomb (s) (a hard stop; bosses x Boss hard stop x)</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
+      <c r="A204" s="81" t="inlineStr">
         <is>
           <t>Resin hit slow %</t>
         </is>
       </c>
-      <c r="B204" t="n">
+      <c r="B204" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="C204" t="inlineStr">
+      <c r="C204" s="81" t="inlineStr">
         <is>
           <t>% slower after each resin hit (not bosses)</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
+      <c r="A205" s="81" t="inlineStr">
         <is>
           <t>Resin hit slow (s)</t>
         </is>
       </c>
-      <c r="B205" t="n">
-        <v>1</v>
-      </c>
-      <c r="C205" t="inlineStr">
+      <c r="B205" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C205" s="81" t="inlineStr">
         <is>
           <t>s the resin-hit slow lasts</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
+      <c r="A206" s="81" t="inlineStr">
         <is>
           <t>Boss entomb every (s)</t>
         </is>
       </c>
-      <c r="B206" t="n">
+      <c r="B206" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="C206" s="81" t="inlineStr">
         <is>
           <t>s: a boss is entombed at most once per this, per boss</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
+      <c r="A207" s="81" t="inlineStr">
         <is>
           <t>Spread reach (studs)</t>
         </is>
       </c>
-      <c r="B207" t="n">
+      <c r="B207" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="C207" s="81" t="inlineStr">
         <is>
           <t>studs: Spreading Amber takes the nearest dinos this close</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
+      <c r="A208" s="81" t="inlineStr">
         <is>
           <t>Sticky bed reach (studs)</t>
         </is>
       </c>
-      <c r="B208" t="n">
+      <c r="B208" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C208" s="81" t="inlineStr">
         <is>
           <t>studs: Sticky Bed slows dinos this close to an entombed one</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
+      <c r="A209" s="81" t="inlineStr">
         <is>
           <t>Fossil Fuel cap %</t>
         </is>
       </c>
-      <c r="B209" t="n">
+      <c r="B209" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C209" s="81" t="inlineStr">
         <is>
           <t>% attack speed Fossil Fuel's stack reaches at most (per round)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>RAPTOR PEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Raptor HP</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>60</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>a raptor's HP (x Walker HP x x (1 + Tower HP per tier x tiers bought), as towers; Shared/Walker)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Raptor speed</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>30</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>studs/s a raptor runs along the track (home at x1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Raptor reach</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>4</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>studs: a raptor this close to its target pounces / bites</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Pounce hold (s)</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>s a pounce holds a non-boss when the build sets no Hold (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Retreat HP share</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>a raptor at or below this share of its HP runs home</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Raptor respawn (s)</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>8</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>s a raptor bitten to 0 HP is gone (x Walker respawn x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Pen heal (HP/s)</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>15</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>HP/s a raptor heals at home (it runs out again at 80 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Leash x</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>x range: a target further than this from the pen is let go</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Trample size</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>3</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>a dino with at least this many sizes left tramples a raptor in its path</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Trample share</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>x a raptor's max HP a trample takes (once per dino)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Dodge every (s)</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>3</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Clever Girls: a raptor ignores one bite per this many s</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Swarm raptors</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>10</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Raptor Swarm: small raptors that pour out once a round</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Swarm share</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>x a raptor's HP and bite for a Swarm raptor</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Swarm (s)</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>15</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>s the Swarm hunts anywhere on your side's track, then vanishes</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Charge knockback (studs)</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>6</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Raptor Charge: small dinos a charging raptor passes are knocked back this far (not bosses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Guard reach (studs)</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>10</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Guard Raptors: a dino this close to a guarded tower that bites or throws at it is attacked</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Roar reach (studs)</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>10</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Rex Tamer: small dinos this close to the alpha are stunned by its roar</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Hungry Alpha cap %</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>50</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Hungry Alpha: the most its take-down stack adds this round</t>
         </is>
       </c>
     </row>
@@ -12579,7 +12855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -12772,9 +13048,14 @@
           <t>Harpoons</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y4" s="81" t="inlineStr">
         <is>
           <t>Resin</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Walkers</t>
         </is>
       </c>
     </row>
@@ -13564,75 +13845,145 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="81" t="inlineStr">
         <is>
           <t>Control: resin slows, entombs and fossilizes</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="81" t="n">
         <v>800</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19">
+      <c r="E19" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="81">
         <f>D19*E19*F19</f>
         <v/>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="81" t="n">
         <v>18</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="81" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="81" t="inlineStr">
         <is>
           <t>Resin globs: slows, entombs (hard stop), fossils. TOWERS_LATER.md.</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="81" t="n">
         <v>500</v>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" s="81" t="inlineStr">
         <is>
           <t>RESIN</t>
         </is>
       </c>
-      <c r="P19" t="n">
+      <c r="P19" s="81" t="n">
         <v>150</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q19" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R19" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y19" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tamed raptors: they run out, bite and come back</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>850</v>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <f>D20*E20*F20</f>
+        <v/>
+      </c>
+      <c r="H20" t="n">
+        <v>22</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Tamed raptors sprint out, pounce, bite and come back; they can be bitten. TOWERS_LATER.md.</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>500</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>RAPTOR</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -13655,7 +14006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DM328"/>
+  <dimension ref="A1:EG355"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -14290,94 +14641,194 @@
           <t>Targets biggest</t>
         </is>
       </c>
-      <c r="CV4" t="inlineStr">
+      <c r="CV4" s="81" t="inlineStr">
         <is>
           <t>Entomb (s)</t>
         </is>
       </c>
-      <c r="CW4" t="inlineStr">
+      <c r="CW4" s="81" t="inlineStr">
         <is>
           <t>Entomb hits x</t>
         </is>
       </c>
-      <c r="CX4" t="inlineStr">
+      <c r="CX4" s="81" t="inlineStr">
         <is>
           <t>Entomb amp %</t>
         </is>
       </c>
-      <c r="CY4" t="inlineStr">
+      <c r="CY4" s="81" t="inlineStr">
         <is>
           <t>Entomb spread</t>
         </is>
       </c>
-      <c r="CZ4" t="inlineStr">
+      <c r="CZ4" s="81" t="inlineStr">
         <is>
           <t>Entomb slow %</t>
         </is>
       </c>
-      <c r="DA4" t="inlineStr">
+      <c r="DA4" s="81" t="inlineStr">
         <is>
           <t>Entomb all every (s)</t>
         </is>
       </c>
-      <c r="DB4" t="inlineStr">
+      <c r="DB4" s="81" t="inlineStr">
         <is>
           <t>Boss entomb (s)</t>
         </is>
       </c>
-      <c r="DC4" t="inlineStr">
+      <c r="DC4" s="81" t="inlineStr">
         <is>
           <t>Send back (studs)</t>
         </is>
       </c>
-      <c r="DD4" t="inlineStr">
+      <c r="DD4" s="81" t="inlineStr">
         <is>
           <t>Fossil below %</t>
         </is>
       </c>
-      <c r="DE4" t="inlineStr">
+      <c r="DE4" s="81" t="inlineStr">
         <is>
           <t>Fossil rate %</t>
         </is>
       </c>
-      <c r="DF4" t="inlineStr">
+      <c r="DF4" s="81" t="inlineStr">
         <is>
           <t>Bounty fossils x</t>
         </is>
       </c>
-      <c r="DG4" t="inlineStr">
+      <c r="DG4" s="81" t="inlineStr">
         <is>
           <t>Heart every (fossils)</t>
         </is>
       </c>
-      <c r="DH4" t="inlineStr">
+      <c r="DH4" s="81" t="inlineStr">
         <is>
           <t>Seal (s)</t>
         </is>
       </c>
-      <c r="DI4" t="inlineStr">
+      <c r="DI4" s="81" t="inlineStr">
         <is>
           <t>Seal every (s)</t>
         </is>
       </c>
-      <c r="DJ4" t="inlineStr">
+      <c r="DJ4" s="81" t="inlineStr">
         <is>
           <t>Seal heal %</t>
         </is>
       </c>
-      <c r="DK4" t="inlineStr">
+      <c r="DK4" s="81" t="inlineStr">
         <is>
           <t>Reflect damage</t>
         </is>
       </c>
-      <c r="DL4" t="inlineStr">
+      <c r="DL4" s="81" t="inlineStr">
         <is>
           <t>Wall (s)</t>
         </is>
       </c>
-      <c r="DM4" t="inlineStr">
+      <c r="DM4" s="81" t="inlineStr">
         <is>
           <t>Take-down mark %</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>Walkers</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>Walker HP x</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>Walker speed x</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>Walker resist %</t>
+        </is>
+      </c>
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>Walker respawn x</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>Hold (s)</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>Boss hold (s)</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>Flanking</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>Targets first</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>Hits air</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>Heals between rounds</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>Dodge</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>Swarm</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>Stun roar every (s)</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>Take-down stack %</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>Avenger x</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>Hunter damage %</t>
         </is>
       </c>
     </row>
@@ -37451,29 +37902,29 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr">
+      <c r="A302" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
+      <c r="B302" s="81" t="inlineStr">
         <is>
           <t>Entomb</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr">
+      <c r="C302" s="81" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="D302" t="n">
-        <v>1</v>
-      </c>
-      <c r="E302">
+      <c r="D302" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E302" s="81">
         <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D302),0)</f>
         <v/>
       </c>
-      <c r="F302">
+      <c r="F302" s="81">
         <f>'Towers'!$C$19+E302</f>
         <v/>
       </c>
@@ -37486,50 +37937,50 @@
       <c r="I302" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J302">
+      <c r="J302" s="81">
         <f>'Towers'!$G$19*G302*H302*I302</f>
         <v/>
       </c>
-      <c r="K302">
+      <c r="K302" s="81">
         <f>IF(J302=0,0,F302/J302)</f>
         <v/>
       </c>
       <c r="L302" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M302" t="inlineStr">
+      <c r="M302" s="81" t="inlineStr">
         <is>
           <t>Thick Resin</t>
         </is>
       </c>
-      <c r="CW302" t="n">
+      <c r="CW302" s="81" t="n">
         <v>0.85</v>
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr">
+      <c r="A303" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
+      <c r="B303" s="81" t="inlineStr">
         <is>
           <t>Entomb</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr">
+      <c r="C303" s="81" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="D303" t="n">
+      <c r="D303" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="E303">
+      <c r="E303" s="81">
         <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D303),0)</f>
         <v/>
       </c>
-      <c r="F303">
+      <c r="F303" s="81">
         <f>F302+E303</f>
         <v/>
       </c>
@@ -37542,50 +37993,50 @@
       <c r="I303" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J303">
+      <c r="J303" s="81">
         <f>'Towers'!$G$19*G303*H303*I303</f>
         <v/>
       </c>
-      <c r="K303">
+      <c r="K303" s="81">
         <f>IF(J303=0,0,F303/J303)</f>
         <v/>
       </c>
       <c r="L303" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M303" t="inlineStr">
+      <c r="M303" s="81" t="inlineStr">
         <is>
           <t>Quick Set</t>
         </is>
       </c>
-      <c r="CW303" t="n">
+      <c r="CW303" s="81" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="inlineStr">
+      <c r="A304" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
+      <c r="B304" s="81" t="inlineStr">
         <is>
           <t>Entomb</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr">
+      <c r="C304" s="81" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="D304" t="n">
+      <c r="D304" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="E304">
+      <c r="E304" s="81">
         <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D304),0)</f>
         <v/>
       </c>
-      <c r="F304">
+      <c r="F304" s="81">
         <f>F303+E304</f>
         <v/>
       </c>
@@ -37598,53 +38049,53 @@
       <c r="I304" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J304">
+      <c r="J304" s="81">
         <f>'Towers'!$G$19*G304*H304*I304</f>
         <v/>
       </c>
-      <c r="K304">
+      <c r="K304" s="81">
         <f>IF(J304=0,0,F304/J304)</f>
         <v/>
       </c>
       <c r="L304" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M304" t="inlineStr">
+      <c r="M304" s="81" t="inlineStr">
         <is>
           <t>Amber Tomb</t>
         </is>
       </c>
-      <c r="CV304" t="n">
+      <c r="CV304" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="CW304" t="n">
+      <c r="CW304" s="81" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr">
+      <c r="A305" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
+      <c r="B305" s="81" t="inlineStr">
         <is>
           <t>Entomb</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr">
+      <c r="C305" s="81" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="D305" t="n">
+      <c r="D305" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E305">
+      <c r="E305" s="81">
         <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D305),0)</f>
         <v/>
       </c>
-      <c r="F305">
+      <c r="F305" s="81">
         <f>F304+E305</f>
         <v/>
       </c>
@@ -37657,60 +38108,60 @@
       <c r="I305" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J305">
+      <c r="J305" s="81">
         <f>J304*G305*H305*I305</f>
         <v/>
       </c>
-      <c r="K305">
+      <c r="K305" s="81">
         <f>IF(J305=0,0,F305/J305)</f>
         <v/>
       </c>
       <c r="L305" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M305" t="inlineStr">
+      <c r="M305" s="81" t="inlineStr">
         <is>
           <t>Hardened Amber</t>
         </is>
       </c>
-      <c r="CI305" t="inlineStr">
+      <c r="CI305" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ305" t="inlineStr">
+      <c r="CJ305" s="81" t="inlineStr">
         <is>
           <t>Stuck dinos take +30% from everything</t>
         </is>
       </c>
-      <c r="CX305" t="n">
+      <c r="CX305" s="81" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr">
+      <c r="A306" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
+      <c r="B306" s="81" t="inlineStr">
         <is>
           <t>Entomb</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr">
+      <c r="C306" s="81" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="D306" t="n">
+      <c r="D306" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E306">
+      <c r="E306" s="81">
         <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D306),0)</f>
         <v/>
       </c>
-      <c r="F306">
+      <c r="F306" s="81">
         <f>F305+E306</f>
         <v/>
       </c>
@@ -37723,60 +38174,60 @@
       <c r="I306" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J306">
+      <c r="J306" s="81">
         <f>J305*G306*H306*I306</f>
         <v/>
       </c>
-      <c r="K306">
+      <c r="K306" s="81">
         <f>IF(J306=0,0,F306/J306)</f>
         <v/>
       </c>
       <c r="L306" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M306" t="inlineStr">
+      <c r="M306" s="81" t="inlineStr">
         <is>
           <t>Amber Age</t>
         </is>
       </c>
-      <c r="CI306" t="inlineStr">
+      <c r="CI306" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ306" t="inlineStr">
+      <c r="CJ306" s="81" t="inlineStr">
         <is>
           <t>Every 12 s, everything in range is stuck</t>
         </is>
       </c>
-      <c r="DA306" t="n">
+      <c r="DA306" s="81" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr">
+      <c r="A307" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
+      <c r="B307" s="81" t="inlineStr">
         <is>
           <t>Fossilize</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr">
+      <c r="C307" s="81" t="inlineStr">
         <is>
           <t>economy</t>
         </is>
       </c>
-      <c r="D307" t="n">
-        <v>1</v>
-      </c>
-      <c r="E307">
+      <c r="D307" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E307" s="81">
         <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D307),0)</f>
         <v/>
       </c>
-      <c r="F307">
+      <c r="F307" s="81">
         <f>'Towers'!$C$19+E307</f>
         <v/>
       </c>
@@ -37789,53 +38240,53 @@
       <c r="I307" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J307">
+      <c r="J307" s="81">
         <f>'Towers'!$G$19*G307*H307*I307</f>
         <v/>
       </c>
-      <c r="K307">
+      <c r="K307" s="81">
         <f>IF(J307=0,0,F307/J307)</f>
         <v/>
       </c>
       <c r="L307" s="110" t="n">
         <v>1.15</v>
       </c>
-      <c r="M307" t="inlineStr">
+      <c r="M307" s="81" t="inlineStr">
         <is>
           <t>Collector's Eye</t>
         </is>
       </c>
-      <c r="CD307" t="n">
+      <c r="CD307" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="DD307" t="n">
+      <c r="DD307" s="81" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr">
+      <c r="A308" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
+      <c r="B308" s="81" t="inlineStr">
         <is>
           <t>Fossilize</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr">
+      <c r="C308" s="81" t="inlineStr">
         <is>
           <t>economy</t>
         </is>
       </c>
-      <c r="D308" t="n">
+      <c r="D308" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="E308">
+      <c r="E308" s="81">
         <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D308),0)</f>
         <v/>
       </c>
-      <c r="F308">
+      <c r="F308" s="81">
         <f>F307+E308</f>
         <v/>
       </c>
@@ -37848,53 +38299,53 @@
       <c r="I308" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J308">
+      <c r="J308" s="81">
         <f>'Towers'!$G$19*G308*H308*I308</f>
         <v/>
       </c>
-      <c r="K308">
+      <c r="K308" s="81">
         <f>IF(J308=0,0,F308/J308)</f>
         <v/>
       </c>
       <c r="L308" s="110" t="n">
         <v>1.15</v>
       </c>
-      <c r="M308" t="inlineStr">
+      <c r="M308" s="81" t="inlineStr">
         <is>
           <t>Rare Find</t>
         </is>
       </c>
-      <c r="CD308" t="n">
+      <c r="CD308" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="DD308" t="n">
+      <c r="DD308" s="81" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr">
+      <c r="A309" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
+      <c r="B309" s="81" t="inlineStr">
         <is>
           <t>Fossilize</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr">
+      <c r="C309" s="81" t="inlineStr">
         <is>
           <t>economy</t>
         </is>
       </c>
-      <c r="D309" t="n">
+      <c r="D309" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="E309">
+      <c r="E309" s="81">
         <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D309),0)</f>
         <v/>
       </c>
-      <c r="F309">
+      <c r="F309" s="81">
         <f>F308+E309</f>
         <v/>
       </c>
@@ -37907,56 +38358,56 @@
       <c r="I309" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J309">
+      <c r="J309" s="81">
         <f>'Towers'!$G$19*G309*H309*I309</f>
         <v/>
       </c>
-      <c r="K309">
+      <c r="K309" s="81">
         <f>IF(J309=0,0,F309/J309)</f>
         <v/>
       </c>
       <c r="L309" s="110" t="n">
         <v>1.15</v>
       </c>
-      <c r="M309" t="inlineStr">
+      <c r="M309" s="81" t="inlineStr">
         <is>
           <t>Fossil Record</t>
         </is>
       </c>
-      <c r="CD309" t="n">
+      <c r="CD309" s="81" t="n">
         <v>16</v>
       </c>
-      <c r="CW309" t="n">
+      <c r="CW309" s="81" t="n">
         <v>0.7</v>
       </c>
-      <c r="DD309" t="n">
+      <c r="DD309" s="81" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="inlineStr">
+      <c r="A310" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
+      <c r="B310" s="81" t="inlineStr">
         <is>
           <t>Fossilize</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr">
+      <c r="C310" s="81" t="inlineStr">
         <is>
           <t>economy</t>
         </is>
       </c>
-      <c r="D310" t="n">
+      <c r="D310" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E310">
+      <c r="E310" s="81">
         <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D310),0)</f>
         <v/>
       </c>
-      <c r="F310">
+      <c r="F310" s="81">
         <f>F309+E310</f>
         <v/>
       </c>
@@ -37969,60 +38420,60 @@
       <c r="I310" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J310">
+      <c r="J310" s="81">
         <f>J309*G310*H310*I310</f>
         <v/>
       </c>
-      <c r="K310">
+      <c r="K310" s="81">
         <f>IF(J310=0,0,F310/J310)</f>
         <v/>
       </c>
       <c r="L310" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M310" t="inlineStr">
+      <c r="M310" s="81" t="inlineStr">
         <is>
           <t>Museum Piece</t>
         </is>
       </c>
-      <c r="CD310" t="n">
+      <c r="CD310" s="81" t="n">
         <v>32</v>
       </c>
-      <c r="CI310" t="inlineStr">
+      <c r="CI310" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ310" t="inlineStr">
+      <c r="CJ310" s="81" t="inlineStr">
         <is>
           <t>Fossils pay double cash</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr">
+      <c r="A311" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
+      <c r="B311" s="81" t="inlineStr">
         <is>
           <t>Fossilize</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr">
+      <c r="C311" s="81" t="inlineStr">
         <is>
           <t>economy</t>
         </is>
       </c>
-      <c r="D311" t="n">
+      <c r="D311" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E311">
+      <c r="E311" s="81">
         <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D311),0)</f>
         <v/>
       </c>
-      <c r="F311">
+      <c r="F311" s="81">
         <f>F310+E311</f>
         <v/>
       </c>
@@ -38035,63 +38486,63 @@
       <c r="I311" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J311">
+      <c r="J311" s="81">
         <f>J310*G311*H311*I311</f>
         <v/>
       </c>
-      <c r="K311">
+      <c r="K311" s="81">
         <f>IF(J311=0,0,F311/J311)</f>
         <v/>
       </c>
       <c r="L311" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M311" t="inlineStr">
+      <c r="M311" s="81" t="inlineStr">
         <is>
           <t>Fossil Fuel</t>
         </is>
       </c>
-      <c r="CI311" t="inlineStr">
+      <c r="CI311" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ311" t="inlineStr">
+      <c r="CJ311" s="81" t="inlineStr">
         <is>
           <t>Each fossil speeds up nearby towers</t>
         </is>
       </c>
-      <c r="DD311" t="n">
+      <c r="DD311" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="DE311" t="n">
+      <c r="DE311" s="81" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr">
+      <c r="A312" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
+      <c r="B312" s="81" t="inlineStr">
         <is>
           <t>Resin Shell</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr">
+      <c r="C312" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D312" t="n">
-        <v>1</v>
-      </c>
-      <c r="E312">
+      <c r="D312" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E312" s="81">
         <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D312),0)</f>
         <v/>
       </c>
-      <c r="F312">
+      <c r="F312" s="81">
         <f>'Towers'!$C$19+E312</f>
         <v/>
       </c>
@@ -38104,50 +38555,50 @@
       <c r="I312" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J312">
+      <c r="J312" s="81">
         <f>'Towers'!$G$19*G312*H312*I312</f>
         <v/>
       </c>
-      <c r="K312">
+      <c r="K312" s="81">
         <f>IF(J312=0,0,F312/J312)</f>
         <v/>
       </c>
       <c r="L312" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M312" t="inlineStr">
+      <c r="M312" s="81" t="inlineStr">
         <is>
           <t>Coat of Resin</t>
         </is>
       </c>
-      <c r="BH312" t="n">
+      <c r="BH312" s="81" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr">
+      <c r="A313" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
+      <c r="B313" s="81" t="inlineStr">
         <is>
           <t>Resin Shell</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr">
+      <c r="C313" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D313" t="n">
+      <c r="D313" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="E313">
+      <c r="E313" s="81">
         <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D313),0)</f>
         <v/>
       </c>
-      <c r="F313">
+      <c r="F313" s="81">
         <f>F312+E313</f>
         <v/>
       </c>
@@ -38160,53 +38611,53 @@
       <c r="I313" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J313">
+      <c r="J313" s="81">
         <f>'Towers'!$G$19*G313*H313*I313</f>
         <v/>
       </c>
-      <c r="K313">
+      <c r="K313" s="81">
         <f>IF(J313=0,0,F313/J313)</f>
         <v/>
       </c>
       <c r="L313" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M313" t="inlineStr">
+      <c r="M313" s="81" t="inlineStr">
         <is>
           <t>Sticky Armour</t>
         </is>
       </c>
-      <c r="AU313" t="n">
+      <c r="AU313" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="BH313" t="n">
+      <c r="BH313" s="81" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="inlineStr">
+      <c r="A314" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
+      <c r="B314" s="81" t="inlineStr">
         <is>
           <t>Resin Shell</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr">
+      <c r="C314" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D314" t="n">
+      <c r="D314" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="E314">
+      <c r="E314" s="81">
         <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D314),0)</f>
         <v/>
       </c>
-      <c r="F314">
+      <c r="F314" s="81">
         <f>F313+E314</f>
         <v/>
       </c>
@@ -38219,56 +38670,56 @@
       <c r="I314" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J314">
+      <c r="J314" s="81">
         <f>'Towers'!$G$19*G314*H314*I314</f>
         <v/>
       </c>
-      <c r="K314">
+      <c r="K314" s="81">
         <f>IF(J314=0,0,F314/J314)</f>
         <v/>
       </c>
       <c r="L314" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M314" t="inlineStr">
+      <c r="M314" s="81" t="inlineStr">
         <is>
           <t>Amber Shield</t>
         </is>
       </c>
-      <c r="AU314" t="n">
+      <c r="AU314" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="BH314" t="n">
+      <c r="BH314" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="DH314" t="n">
+      <c r="DH314" s="81" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr">
+      <c r="A315" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
+      <c r="B315" s="81" t="inlineStr">
         <is>
           <t>Resin Shell</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr">
+      <c r="C315" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D315" t="n">
+      <c r="D315" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E315">
+      <c r="E315" s="81">
         <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D315),0)</f>
         <v/>
       </c>
-      <c r="F315">
+      <c r="F315" s="81">
         <f>F314+E315</f>
         <v/>
       </c>
@@ -38281,60 +38732,60 @@
       <c r="I315" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J315">
+      <c r="J315" s="81">
         <f>J314*G315*H315*I315</f>
         <v/>
       </c>
-      <c r="K315">
+      <c r="K315" s="81">
         <f>IF(J315=0,0,F315/J315)</f>
         <v/>
       </c>
       <c r="L315" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M315" t="inlineStr">
+      <c r="M315" s="81" t="inlineStr">
         <is>
           <t>Self-Sealing</t>
         </is>
       </c>
-      <c r="CI315" t="inlineStr">
+      <c r="CI315" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ315" t="inlineStr">
+      <c r="CJ315" s="81" t="inlineStr">
         <is>
           <t>Sealed towers heal 30% when the shell breaks</t>
         </is>
       </c>
-      <c r="DJ315" t="n">
+      <c r="DJ315" s="81" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr">
+      <c r="A316" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
+      <c r="B316" s="81" t="inlineStr">
         <is>
           <t>Resin Shell</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr">
+      <c r="C316" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D316" t="n">
+      <c r="D316" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E316">
+      <c r="E316" s="81">
         <f>ROUND('Towers'!$C$19*POWER('Tuning'!$B$12,D316),0)</f>
         <v/>
       </c>
-      <c r="F316">
+      <c r="F316" s="81">
         <f>F315+E316</f>
         <v/>
       </c>
@@ -38347,60 +38798,60 @@
       <c r="I316" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J316">
+      <c r="J316" s="81">
         <f>J315*G316*H316*I316</f>
         <v/>
       </c>
-      <c r="K316">
+      <c r="K316" s="81">
         <f>IF(J316=0,0,F316/J316)</f>
         <v/>
       </c>
       <c r="L316" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M316" t="inlineStr">
+      <c r="M316" s="81" t="inlineStr">
         <is>
           <t>Amber Fortress</t>
         </is>
       </c>
-      <c r="CI316" t="inlineStr">
+      <c r="CI316" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ316" t="inlineStr">
+      <c r="CJ316" s="81" t="inlineStr">
         <is>
           <t>Nearby towers can't be knocked out (20 s each)</t>
         </is>
       </c>
-      <c r="DI316" t="n">
+      <c r="DI316" s="81" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="inlineStr">
+      <c r="A317" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
+      <c r="B317" s="81" t="inlineStr">
         <is>
           <t>Entomb</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr">
+      <c r="C317" s="81" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="D317" t="n">
+      <c r="D317" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E317">
+      <c r="E317" s="81">
         <f>E305</f>
         <v/>
       </c>
-      <c r="F317">
+      <c r="F317" s="81">
         <f>F305</f>
         <v/>
       </c>
@@ -38416,49 +38867,49 @@
       <c r="L317" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M317" t="inlineStr">
+      <c r="M317" s="81" t="inlineStr">
         <is>
           <t>Spreading Amber</t>
         </is>
       </c>
-      <c r="CI317" t="inlineStr">
+      <c r="CI317" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ317" t="inlineStr">
+      <c r="CJ317" s="81" t="inlineStr">
         <is>
           <t>The amber jumps to the next dino</t>
         </is>
       </c>
-      <c r="CY317" t="n">
+      <c r="CY317" s="81" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr">
+      <c r="A318" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
+      <c r="B318" s="81" t="inlineStr">
         <is>
           <t>Entomb</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr">
+      <c r="C318" s="81" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="D318" t="n">
+      <c r="D318" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E318">
+      <c r="E318" s="81">
         <f>E305</f>
         <v/>
       </c>
-      <c r="F318">
+      <c r="F318" s="81">
         <f>F305</f>
         <v/>
       </c>
@@ -38474,49 +38925,49 @@
       <c r="L318" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M318" t="inlineStr">
+      <c r="M318" s="81" t="inlineStr">
         <is>
           <t>Sticky Bed</t>
         </is>
       </c>
-      <c r="CI318" t="inlineStr">
+      <c r="CI318" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ318" t="inlineStr">
+      <c r="CJ318" s="81" t="inlineStr">
         <is>
           <t>Dinos walking past a stuck one slow 30%</t>
         </is>
       </c>
-      <c r="CZ318" t="n">
+      <c r="CZ318" s="81" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr">
+      <c r="A319" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
+      <c r="B319" s="81" t="inlineStr">
         <is>
           <t>Entomb</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
+      <c r="C319" s="81" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="D319" t="n">
+      <c r="D319" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E319">
+      <c r="E319" s="81">
         <f>E306</f>
         <v/>
       </c>
-      <c r="F319">
+      <c r="F319" s="81">
         <f>F306</f>
         <v/>
       </c>
@@ -38532,52 +38983,52 @@
       <c r="L319" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M319" t="inlineStr">
+      <c r="M319" s="81" t="inlineStr">
         <is>
           <t>Living Amber</t>
         </is>
       </c>
-      <c r="CI319" t="inlineStr">
+      <c r="CI319" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ319" t="inlineStr">
+      <c r="CJ319" s="81" t="inlineStr">
         <is>
           <t>Traps a boss 3 s; others stay stuck longer</t>
         </is>
       </c>
-      <c r="CV319" t="n">
+      <c r="CV319" s="81" t="n">
         <v>2.5</v>
       </c>
-      <c r="DB319" t="n">
+      <c r="DB319" s="81" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr">
+      <c r="A320" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
+      <c r="B320" s="81" t="inlineStr">
         <is>
           <t>Entomb</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr">
+      <c r="C320" s="81" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="D320" t="n">
+      <c r="D320" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E320">
+      <c r="E320" s="81">
         <f>E306</f>
         <v/>
       </c>
-      <c r="F320">
+      <c r="F320" s="81">
         <f>F306</f>
         <v/>
       </c>
@@ -38593,49 +39044,49 @@
       <c r="L320" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M320" t="inlineStr">
+      <c r="M320" s="81" t="inlineStr">
         <is>
           <t>Time Capsule</t>
         </is>
       </c>
-      <c r="CI320" t="inlineStr">
+      <c r="CI320" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ320" t="inlineStr">
+      <c r="CJ320" s="81" t="inlineStr">
         <is>
           <t>Stuck dinos are sent 12 studs back</t>
         </is>
       </c>
-      <c r="DC320" t="n">
+      <c r="DC320" s="81" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="inlineStr">
+      <c r="A321" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
+      <c r="B321" s="81" t="inlineStr">
         <is>
           <t>Fossilize</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr">
+      <c r="C321" s="81" t="inlineStr">
         <is>
           <t>economy</t>
         </is>
       </c>
-      <c r="D321" t="n">
+      <c r="D321" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E321">
+      <c r="E321" s="81">
         <f>E310</f>
         <v/>
       </c>
-      <c r="F321">
+      <c r="F321" s="81">
         <f>F310</f>
         <v/>
       </c>
@@ -38651,49 +39102,49 @@
       <c r="L321" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M321" t="inlineStr">
+      <c r="M321" s="81" t="inlineStr">
         <is>
           <t>Dig Crew</t>
         </is>
       </c>
-      <c r="CE321" t="n">
+      <c r="CE321" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="CI321" t="inlineStr">
+      <c r="CI321" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ321" t="inlineStr">
+      <c r="CJ321" s="81" t="inlineStr">
         <is>
           <t>A fossil drops a cash chest</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr">
+      <c r="A322" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
+      <c r="B322" s="81" t="inlineStr">
         <is>
           <t>Fossilize</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr">
+      <c r="C322" s="81" t="inlineStr">
         <is>
           <t>economy</t>
         </is>
       </c>
-      <c r="D322" t="n">
+      <c r="D322" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E322">
+      <c r="E322" s="81">
         <f>E310</f>
         <v/>
       </c>
-      <c r="F322">
+      <c r="F322" s="81">
         <f>F310</f>
         <v/>
       </c>
@@ -38709,49 +39160,49 @@
       <c r="L322" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M322" t="inlineStr">
+      <c r="M322" s="81" t="inlineStr">
         <is>
           <t>Bone Dust</t>
         </is>
       </c>
-      <c r="CI322" t="inlineStr">
+      <c r="CI322" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ322" t="inlineStr">
+      <c r="CJ322" s="81" t="inlineStr">
         <is>
           <t>Fossils mark nearby dinos +15%</t>
         </is>
       </c>
-      <c r="DM322" t="n">
+      <c r="DM322" s="81" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr">
+      <c r="A323" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
+      <c r="B323" s="81" t="inlineStr">
         <is>
           <t>Fossilize</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr">
+      <c r="C323" s="81" t="inlineStr">
         <is>
           <t>economy</t>
         </is>
       </c>
-      <c r="D323" t="n">
+      <c r="D323" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E323">
+      <c r="E323" s="81">
         <f>E311</f>
         <v/>
       </c>
-      <c r="F323">
+      <c r="F323" s="81">
         <f>F311</f>
         <v/>
       </c>
@@ -38767,52 +39218,52 @@
       <c r="L323" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M323" t="inlineStr">
+      <c r="M323" s="81" t="inlineStr">
         <is>
           <t>Prize Fossils</t>
         </is>
       </c>
-      <c r="CI323" t="inlineStr">
+      <c r="CI323" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ323" t="inlineStr">
+      <c r="CJ323" s="81" t="inlineStr">
         <is>
           <t>More fossils; each counts double for bounties</t>
         </is>
       </c>
-      <c r="DD323" t="n">
+      <c r="DD323" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="DF323" t="n">
+      <c r="DF323" s="81" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
+      <c r="A324" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
+      <c r="B324" s="81" t="inlineStr">
         <is>
           <t>Fossilize</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr">
+      <c r="C324" s="81" t="inlineStr">
         <is>
           <t>economy</t>
         </is>
       </c>
-      <c r="D324" t="n">
+      <c r="D324" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E324">
+      <c r="E324" s="81">
         <f>E311</f>
         <v/>
       </c>
-      <c r="F324">
+      <c r="F324" s="81">
         <f>F311</f>
         <v/>
       </c>
@@ -38828,49 +39279,49 @@
       <c r="L324" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M324" t="inlineStr">
+      <c r="M324" s="81" t="inlineStr">
         <is>
           <t>Amber Heart</t>
         </is>
       </c>
-      <c r="CI324" t="inlineStr">
+      <c r="CI324" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ324" t="inlineStr">
+      <c r="CJ324" s="81" t="inlineStr">
         <is>
           <t>Every 15th fossil freezes your whole side 1 s</t>
         </is>
       </c>
-      <c r="DG324" t="n">
+      <c r="DG324" s="81" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr">
+      <c r="A325" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
+      <c r="B325" s="81" t="inlineStr">
         <is>
           <t>Resin Shell</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
+      <c r="C325" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D325" t="n">
+      <c r="D325" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E325">
+      <c r="E325" s="81">
         <f>E315</f>
         <v/>
       </c>
-      <c r="F325">
+      <c r="F325" s="81">
         <f>F315</f>
         <v/>
       </c>
@@ -38886,63 +39337,63 @@
       <c r="L325" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M325" t="inlineStr">
+      <c r="M325" s="81" t="inlineStr">
         <is>
           <t>Raider Glue</t>
         </is>
       </c>
-      <c r="CI325" t="inlineStr">
+      <c r="CI325" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ325" t="inlineStr">
+      <c r="CJ325" s="81" t="inlineStr">
         <is>
           <t>Raiders and biters near your towers slow down</t>
         </is>
       </c>
-      <c r="CK325" t="inlineStr">
+      <c r="CK325" s="81" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="CL325" t="n">
+      <c r="CL325" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="CM325" t="n">
+      <c r="CM325" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="CP325" t="n">
+      <c r="CP325" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="CQ325" t="n">
+      <c r="CQ325" s="81" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="inlineStr">
+      <c r="A326" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
+      <c r="B326" s="81" t="inlineStr">
         <is>
           <t>Resin Shell</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr">
+      <c r="C326" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D326" t="n">
+      <c r="D326" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E326">
+      <c r="E326" s="81">
         <f>E315</f>
         <v/>
       </c>
-      <c r="F326">
+      <c r="F326" s="81">
         <f>F315</f>
         <v/>
       </c>
@@ -38958,55 +39409,55 @@
       <c r="L326" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M326" t="inlineStr">
+      <c r="M326" s="81" t="inlineStr">
         <is>
           <t>Sticky Thorns</t>
         </is>
       </c>
-      <c r="AV326" t="n">
+      <c r="AV326" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="CI326" t="inlineStr">
+      <c r="CI326" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ326" t="inlineStr">
+      <c r="CJ326" s="81" t="inlineStr">
         <is>
           <t>Biters get slowed and take 5 damage</t>
         </is>
       </c>
-      <c r="CP326" t="n">
+      <c r="CP326" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="CQ326" t="n">
+      <c r="CQ326" s="81" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="inlineStr">
+      <c r="A327" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
+      <c r="B327" s="81" t="inlineStr">
         <is>
           <t>Resin Shell</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr">
+      <c r="C327" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D327" t="n">
+      <c r="D327" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E327">
+      <c r="E327" s="81">
         <f>E316</f>
         <v/>
       </c>
-      <c r="F327">
+      <c r="F327" s="81">
         <f>F316</f>
         <v/>
       </c>
@@ -39022,49 +39473,49 @@
       <c r="L327" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M327" t="inlineStr">
+      <c r="M327" s="81" t="inlineStr">
         <is>
           <t>Resin Wall</t>
         </is>
       </c>
-      <c r="CI327" t="inlineStr">
+      <c r="CI327" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ327" t="inlineStr">
+      <c r="CJ327" s="81" t="inlineStr">
         <is>
           <t>Once a round, an amber wall holds every dino 3 s</t>
         </is>
       </c>
-      <c r="DL327" t="n">
+      <c r="DL327" s="81" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="inlineStr">
+      <c r="A328" s="81" t="inlineStr">
         <is>
           <t>Amber Resin Cannon</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
+      <c r="B328" s="81" t="inlineStr">
         <is>
           <t>Resin Shell</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr">
+      <c r="C328" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D328" t="n">
+      <c r="D328" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E328">
+      <c r="E328" s="81">
         <f>E316</f>
         <v/>
       </c>
-      <c r="F328">
+      <c r="F328" s="81">
         <f>F316</f>
         <v/>
       </c>
@@ -39080,26 +39531,1729 @@
       <c r="L328" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M328" t="inlineStr">
+      <c r="M328" s="81" t="inlineStr">
         <is>
           <t>Amber Mirror</t>
         </is>
       </c>
-      <c r="BR328" t="n">
-        <v>1</v>
-      </c>
-      <c r="CI328" t="inlineStr">
+      <c r="BR328" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI328" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ328" t="inlineStr">
+      <c r="CJ328" s="81" t="inlineStr">
         <is>
           <t>Throws at your towers bounce back</t>
         </is>
       </c>
-      <c r="DK328" t="n">
+      <c r="DK328" s="81" t="n">
         <v>60</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>pack damage</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>1</v>
+      </c>
+      <c r="E329">
+        <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D329),0)</f>
+        <v/>
+      </c>
+      <c r="F329">
+        <f>'Towers'!$C$20+E329</f>
+        <v/>
+      </c>
+      <c r="G329" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H329" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I329" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J329">
+        <f>'Towers'!$G$20*G329*H329*I329</f>
+        <v/>
+      </c>
+      <c r="K329">
+        <f>IF(J329=0,0,F329/J329)</f>
+        <v/>
+      </c>
+      <c r="L329" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>Second Raptor</t>
+        </is>
+      </c>
+      <c r="DN329" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>pack damage</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>2</v>
+      </c>
+      <c r="E330">
+        <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D330),0)</f>
+        <v/>
+      </c>
+      <c r="F330">
+        <f>F329+E330</f>
+        <v/>
+      </c>
+      <c r="G330" s="110" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H330" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I330" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J330">
+        <f>'Towers'!$G$20*G330*H330*I330</f>
+        <v/>
+      </c>
+      <c r="K330">
+        <f>IF(J330=0,0,F330/J330)</f>
+        <v/>
+      </c>
+      <c r="L330" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>Quick Whistle</t>
+        </is>
+      </c>
+      <c r="DN330" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP330" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DR330" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>pack damage</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>3</v>
+      </c>
+      <c r="E331">
+        <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D331),0)</f>
+        <v/>
+      </c>
+      <c r="F331">
+        <f>F330+E331</f>
+        <v/>
+      </c>
+      <c r="G331" s="110" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H331" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I331" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J331">
+        <f>'Towers'!$G$20*G331*H331*I331</f>
+        <v/>
+      </c>
+      <c r="K331">
+        <f>IF(J331=0,0,F331/J331)</f>
+        <v/>
+      </c>
+      <c r="L331" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Pack of Five</t>
+        </is>
+      </c>
+      <c r="DN331" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP331" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DR331" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>pack damage</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>4</v>
+      </c>
+      <c r="E332">
+        <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D332),0)</f>
+        <v/>
+      </c>
+      <c r="F332">
+        <f>F331+E332</f>
+        <v/>
+      </c>
+      <c r="G332" s="110" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H332" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I332" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J332">
+        <f>J331*G332*H332*I332</f>
+        <v/>
+      </c>
+      <c r="K332">
+        <f>IF(J332=0,0,F332/J332)</f>
+        <v/>
+      </c>
+      <c r="L332" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>Hide Rippers</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CI332" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ332" t="inlineStr">
+        <is>
+          <t>Raptors bite through armour</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>pack damage</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>5</v>
+      </c>
+      <c r="E333">
+        <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D333),0)</f>
+        <v/>
+      </c>
+      <c r="F333">
+        <f>F332+E333</f>
+        <v/>
+      </c>
+      <c r="G333" s="110" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H333" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I333" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J333">
+        <f>J332*G333*H333*I333</f>
+        <v/>
+      </c>
+      <c r="K333">
+        <f>IF(J333=0,0,F333/J333)</f>
+        <v/>
+      </c>
+      <c r="L333" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>Raptor Swarm</t>
+        </is>
+      </c>
+      <c r="CI333" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ333" t="inlineStr">
+        <is>
+          <t>10 small raptors flood the track once a round</t>
+        </is>
+      </c>
+      <c r="EA333" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>one big hunter</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>1</v>
+      </c>
+      <c r="E334">
+        <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D334),0)</f>
+        <v/>
+      </c>
+      <c r="F334">
+        <f>'Towers'!$C$20+E334</f>
+        <v/>
+      </c>
+      <c r="G334" s="110" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H334" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I334" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J334">
+        <f>'Towers'!$G$20*G334*H334*I334</f>
+        <v/>
+      </c>
+      <c r="K334">
+        <f>IF(J334=0,0,F334/J334)</f>
+        <v/>
+      </c>
+      <c r="L334" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>Sharp Claws</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>one big hunter</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>2</v>
+      </c>
+      <c r="E335">
+        <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D335),0)</f>
+        <v/>
+      </c>
+      <c r="F335">
+        <f>F334+E335</f>
+        <v/>
+      </c>
+      <c r="G335" s="110" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H335" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I335" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J335">
+        <f>'Towers'!$G$20*G335*H335*I335</f>
+        <v/>
+      </c>
+      <c r="K335">
+        <f>IF(J335=0,0,F335/J335)</f>
+        <v/>
+      </c>
+      <c r="L335" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>Thick Hide</t>
+        </is>
+      </c>
+      <c r="DO335" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DQ335" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>one big hunter</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>3</v>
+      </c>
+      <c r="E336">
+        <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D336),0)</f>
+        <v/>
+      </c>
+      <c r="F336">
+        <f>F335+E336</f>
+        <v/>
+      </c>
+      <c r="G336" s="110" t="n">
+        <v>7</v>
+      </c>
+      <c r="H336" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I336" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J336">
+        <f>'Towers'!$G$20*G336*H336*I336</f>
+        <v/>
+      </c>
+      <c r="K336">
+        <f>IF(J336=0,0,F336/J336)</f>
+        <v/>
+      </c>
+      <c r="L336" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>Alpha Raptor</t>
+        </is>
+      </c>
+      <c r="BJ336" t="n">
+        <v>2</v>
+      </c>
+      <c r="DO336" t="n">
+        <v>3</v>
+      </c>
+      <c r="DQ336" t="n">
+        <v>25</v>
+      </c>
+      <c r="DS336" t="n">
+        <v>1</v>
+      </c>
+      <c r="DZ336" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>one big hunter</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>4</v>
+      </c>
+      <c r="E337">
+        <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D337),0)</f>
+        <v/>
+      </c>
+      <c r="F337">
+        <f>F336+E337</f>
+        <v/>
+      </c>
+      <c r="G337" s="110" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H337" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I337" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J337">
+        <f>J336*G337*H337*I337</f>
+        <v/>
+      </c>
+      <c r="K337">
+        <f>IF(J337=0,0,F337/J337)</f>
+        <v/>
+      </c>
+      <c r="L337" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>Sickle Claw</t>
+        </is>
+      </c>
+      <c r="BJ337" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI337" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ337" t="inlineStr">
+        <is>
+          <t>×3 on its target, breaks 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>one big hunter</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>5</v>
+      </c>
+      <c r="E338">
+        <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D338),0)</f>
+        <v/>
+      </c>
+      <c r="F338">
+        <f>F337+E338</f>
+        <v/>
+      </c>
+      <c r="G338" s="110" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H338" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I338" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J338">
+        <f>J337*G338*H338*I338</f>
+        <v/>
+      </c>
+      <c r="K338">
+        <f>IF(J338=0,0,F338/J338)</f>
+        <v/>
+      </c>
+      <c r="L338" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>King of the Pack</t>
+        </is>
+      </c>
+      <c r="BJ338" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI338" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ338" t="inlineStr">
+        <is>
+          <t>A giant raptor, half damage taken</t>
+        </is>
+      </c>
+      <c r="DO338" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DQ338" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>1</v>
+      </c>
+      <c r="E339">
+        <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D339),0)</f>
+        <v/>
+      </c>
+      <c r="F339">
+        <f>'Towers'!$C$20+E339</f>
+        <v/>
+      </c>
+      <c r="G339" s="110" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H339" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I339" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J339">
+        <f>'Towers'!$G$20*G339*H339*I339</f>
+        <v/>
+      </c>
+      <c r="K339">
+        <f>IF(J339=0,0,F339/J339)</f>
+        <v/>
+      </c>
+      <c r="L339" s="110" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Tracking Nose</t>
+        </is>
+      </c>
+      <c r="DV339" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>2</v>
+      </c>
+      <c r="E340">
+        <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D340),0)</f>
+        <v/>
+      </c>
+      <c r="F340">
+        <f>F339+E340</f>
+        <v/>
+      </c>
+      <c r="G340" s="110" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H340" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I340" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J340">
+        <f>'Towers'!$G$20*G340*H340*I340</f>
+        <v/>
+      </c>
+      <c r="K340">
+        <f>IF(J340=0,0,F340/J340)</f>
+        <v/>
+      </c>
+      <c r="L340" s="110" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>Herding Call</t>
+        </is>
+      </c>
+      <c r="AE340" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF340" t="n">
+        <v>1</v>
+      </c>
+      <c r="DV340" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>3</v>
+      </c>
+      <c r="E341">
+        <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D341),0)</f>
+        <v/>
+      </c>
+      <c r="F341">
+        <f>F340+E341</f>
+        <v/>
+      </c>
+      <c r="G341" s="110" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H341" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I341" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J341">
+        <f>'Towers'!$G$20*G341*H341*I341</f>
+        <v/>
+      </c>
+      <c r="K341">
+        <f>IF(J341=0,0,F341/J341)</f>
+        <v/>
+      </c>
+      <c r="L341" s="110" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Pack Howl</t>
+        </is>
+      </c>
+      <c r="AE341" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF341" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY341" t="n">
+        <v>15</v>
+      </c>
+      <c r="DN341" t="n">
+        <v>2</v>
+      </c>
+      <c r="DV341" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>4</v>
+      </c>
+      <c r="E342">
+        <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D342),0)</f>
+        <v/>
+      </c>
+      <c r="F342">
+        <f>F341+E342</f>
+        <v/>
+      </c>
+      <c r="G342" s="110" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H342" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I342" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J342">
+        <f>J341*G342*H342*I342</f>
+        <v/>
+      </c>
+      <c r="K342">
+        <f>IF(J342=0,0,F342/J342)</f>
+        <v/>
+      </c>
+      <c r="L342" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>Treat Bag</t>
+        </is>
+      </c>
+      <c r="CI342" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ342" t="inlineStr">
+        <is>
+          <t>Raptors heal and return faster</t>
+        </is>
+      </c>
+      <c r="DR342" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DX342" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>5</v>
+      </c>
+      <c r="E343">
+        <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D343),0)</f>
+        <v/>
+      </c>
+      <c r="F343">
+        <f>F342+E343</f>
+        <v/>
+      </c>
+      <c r="G343" s="110" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H343" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I343" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J343">
+        <f>J342*G343*H343*I343</f>
+        <v/>
+      </c>
+      <c r="K343">
+        <f>IF(J343=0,0,F343/J343)</f>
+        <v/>
+      </c>
+      <c r="L343" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>Raptor Charge</t>
+        </is>
+      </c>
+      <c r="CI343" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ343" t="inlineStr">
+        <is>
+          <t>Every raptor charges the track once a round</t>
+        </is>
+      </c>
+      <c r="EB343" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>pack damage</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>4</v>
+      </c>
+      <c r="E344">
+        <f>E332</f>
+        <v/>
+      </c>
+      <c r="F344">
+        <f>F332</f>
+        <v/>
+      </c>
+      <c r="G344" s="110" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H344" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I344" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L344" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>Flanking</t>
+        </is>
+      </c>
+      <c r="CI344" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ344" t="inlineStr">
+        <is>
+          <t>Each raptor picks a different dino</t>
+        </is>
+      </c>
+      <c r="DU344" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>pack damage</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>4</v>
+      </c>
+      <c r="E345">
+        <f>E332</f>
+        <v/>
+      </c>
+      <c r="F345">
+        <f>F332</f>
+        <v/>
+      </c>
+      <c r="G345" s="110" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H345" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I345" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L345" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>Ambush</t>
+        </is>
+      </c>
+      <c r="BU345" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI345" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ345" t="inlineStr">
+        <is>
+          <t>Each raptor's first pounce hits double</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>pack damage</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>5</v>
+      </c>
+      <c r="E346">
+        <f>E333</f>
+        <v/>
+      </c>
+      <c r="F346">
+        <f>F333</f>
+        <v/>
+      </c>
+      <c r="G346" s="110" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H346" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I346" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L346" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>Clever Girls</t>
+        </is>
+      </c>
+      <c r="CI346" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ346" t="inlineStr">
+        <is>
+          <t>Raptors dodge bites and never get trampled</t>
+        </is>
+      </c>
+      <c r="DY346" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>pack damage</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>5</v>
+      </c>
+      <c r="E347">
+        <f>E333</f>
+        <v/>
+      </c>
+      <c r="F347">
+        <f>F333</f>
+        <v/>
+      </c>
+      <c r="G347" s="110" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H347" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I347" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L347" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>Sky Leap</t>
+        </is>
+      </c>
+      <c r="CI347" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ347" t="inlineStr">
+        <is>
+          <t>Raptors jump at low flyers</t>
+        </is>
+      </c>
+      <c r="DW347" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>one big hunter</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>4</v>
+      </c>
+      <c r="E348">
+        <f>E337</f>
+        <v/>
+      </c>
+      <c r="F348">
+        <f>F337</f>
+        <v/>
+      </c>
+      <c r="G348" s="110" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H348" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I348" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L348" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>Boss Hunter</t>
+        </is>
+      </c>
+      <c r="P348" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CI348" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ348" t="inlineStr">
+        <is>
+          <t>Can hold a boss for a moment</t>
+        </is>
+      </c>
+      <c r="DT348" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>one big hunter</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>4</v>
+      </c>
+      <c r="E349">
+        <f>E337</f>
+        <v/>
+      </c>
+      <c r="F349">
+        <f>F337</f>
+        <v/>
+      </c>
+      <c r="G349" s="110" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H349" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I349" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L349" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>Scent Trail</t>
+        </is>
+      </c>
+      <c r="T349" t="n">
+        <v>15</v>
+      </c>
+      <c r="CI349" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ349" t="inlineStr">
+        <is>
+          <t>Its target is marked +15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>one big hunter</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>5</v>
+      </c>
+      <c r="E350">
+        <f>E338</f>
+        <v/>
+      </c>
+      <c r="F350">
+        <f>F338</f>
+        <v/>
+      </c>
+      <c r="G350" s="110" t="n">
+        <v>2</v>
+      </c>
+      <c r="H350" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I350" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L350" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>Rex Tamer</t>
+        </is>
+      </c>
+      <c r="U350" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI350" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ350" t="inlineStr">
+        <is>
+          <t>A tamed T. rex whose roar stuns</t>
+        </is>
+      </c>
+      <c r="DO350" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="ED350" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>one big hunter</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>5</v>
+      </c>
+      <c r="E351">
+        <f>E338</f>
+        <v/>
+      </c>
+      <c r="F351">
+        <f>F338</f>
+        <v/>
+      </c>
+      <c r="G351" s="110" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H351" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I351" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L351" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>Hungry Alpha</t>
+        </is>
+      </c>
+      <c r="CI351" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ351" t="inlineStr">
+        <is>
+          <t>Stronger with every take-down</t>
+        </is>
+      </c>
+      <c r="EE351" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>4</v>
+      </c>
+      <c r="E352">
+        <f>E342</f>
+        <v/>
+      </c>
+      <c r="F352">
+        <f>F342</f>
+        <v/>
+      </c>
+      <c r="G352" s="110" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H352" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I352" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L352" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>Guard Raptors</t>
+        </is>
+      </c>
+      <c r="CI352" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ352" t="inlineStr">
+        <is>
+          <t>A raptor guards each tower</t>
+        </is>
+      </c>
+      <c r="EC352" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>4</v>
+      </c>
+      <c r="E353">
+        <f>E342</f>
+        <v/>
+      </c>
+      <c r="F353">
+        <f>F342</f>
+        <v/>
+      </c>
+      <c r="G353" s="110" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H353" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I353" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L353" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>Whistle Drill</t>
+        </is>
+      </c>
+      <c r="BY353" t="n">
+        <v>20</v>
+      </c>
+      <c r="CI353" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ353" t="inlineStr">
+        <is>
+          <t>Raptors run 30% faster</t>
+        </is>
+      </c>
+      <c r="DP353" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>5</v>
+      </c>
+      <c r="E354">
+        <f>E343</f>
+        <v/>
+      </c>
+      <c r="F354">
+        <f>F343</f>
+        <v/>
+      </c>
+      <c r="G354" s="110" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H354" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I354" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L354" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>Pack Bond</t>
+        </is>
+      </c>
+      <c r="CI354" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ354" t="inlineStr">
+        <is>
+          <t>Hunters nearby +20% with 3+ raptors out</t>
+        </is>
+      </c>
+      <c r="DN354" t="n">
+        <v>3</v>
+      </c>
+      <c r="EG354" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Raptor Pen</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>5</v>
+      </c>
+      <c r="E355">
+        <f>E343</f>
+        <v/>
+      </c>
+      <c r="F355">
+        <f>F343</f>
+        <v/>
+      </c>
+      <c r="G355" s="110" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H355" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I355" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L355" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>Raider Hounds</t>
+        </is>
+      </c>
+      <c r="BJ355" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI355" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ355" t="inlineStr">
+        <is>
+          <t>Raptors chase raiders (or the dino that hurt a tower)</t>
+        </is>
+      </c>
+      <c r="CK355" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CL355" t="n">
+        <v>20</v>
+      </c>
+      <c r="CM355" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN355" t="n">
+        <v>10</v>
+      </c>
+      <c r="EF355" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -12559,277 +12559,277 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
+      <c r="A210" s="81" t="inlineStr">
         <is>
           <t>RAPTOR PEN</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
+      <c r="A211" s="81" t="inlineStr">
         <is>
           <t>Raptor HP</t>
         </is>
       </c>
-      <c r="B211" t="n">
+      <c r="B211" s="81" t="n">
         <v>60</v>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="C211" s="81" t="inlineStr">
         <is>
           <t>a raptor's HP (x Walker HP x x (1 + Tower HP per tier x tiers bought), as towers; Shared/Walker)</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
+      <c r="A212" s="81" t="inlineStr">
         <is>
           <t>Raptor speed</t>
         </is>
       </c>
-      <c r="B212" t="n">
+      <c r="B212" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="C212" t="inlineStr">
+      <c r="C212" s="81" t="inlineStr">
         <is>
           <t>studs/s a raptor runs along the track (home at x1.5)</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
+      <c r="A213" s="81" t="inlineStr">
         <is>
           <t>Raptor reach</t>
         </is>
       </c>
-      <c r="B213" t="n">
+      <c r="B213" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="C213" t="inlineStr">
+      <c r="C213" s="81" t="inlineStr">
         <is>
           <t>studs: a raptor this close to its target pounces / bites</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
+      <c r="A214" s="81" t="inlineStr">
         <is>
           <t>Pounce hold (s)</t>
         </is>
       </c>
-      <c r="B214" t="n">
+      <c r="B214" s="81" t="n">
         <v>0.5</v>
       </c>
-      <c r="C214" t="inlineStr">
+      <c r="C214" s="81" t="inlineStr">
         <is>
           <t>s a pounce holds a non-boss when the build sets no Hold (s)</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
+      <c r="A215" s="81" t="inlineStr">
         <is>
           <t>Retreat HP share</t>
         </is>
       </c>
-      <c r="B215" t="n">
+      <c r="B215" s="81" t="n">
         <v>0.3</v>
       </c>
-      <c r="C215" t="inlineStr">
+      <c r="C215" s="81" t="inlineStr">
         <is>
           <t>a raptor at or below this share of its HP runs home</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
+      <c r="A216" s="81" t="inlineStr">
         <is>
           <t>Raptor respawn (s)</t>
         </is>
       </c>
-      <c r="B216" t="n">
+      <c r="B216" s="81" t="n">
         <v>8</v>
       </c>
-      <c r="C216" t="inlineStr">
+      <c r="C216" s="81" t="inlineStr">
         <is>
           <t>s a raptor bitten to 0 HP is gone (x Walker respawn x)</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
+      <c r="A217" s="81" t="inlineStr">
         <is>
           <t>Pen heal (HP/s)</t>
         </is>
       </c>
-      <c r="B217" t="n">
+      <c r="B217" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="C217" t="inlineStr">
+      <c r="C217" s="81" t="inlineStr">
         <is>
           <t>HP/s a raptor heals at home (it runs out again at 80 %)</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="A218" s="81" t="inlineStr">
         <is>
           <t>Leash x</t>
         </is>
       </c>
-      <c r="B218" t="n">
+      <c r="B218" s="81" t="n">
         <v>1.5</v>
       </c>
-      <c r="C218" t="inlineStr">
+      <c r="C218" s="81" t="inlineStr">
         <is>
           <t>x range: a target further than this from the pen is let go</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
+      <c r="A219" s="81" t="inlineStr">
         <is>
           <t>Trample size</t>
         </is>
       </c>
-      <c r="B219" t="n">
+      <c r="B219" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="C219" s="81" t="inlineStr">
         <is>
           <t>a dino with at least this many sizes left tramples a raptor in its path</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
+      <c r="A220" s="81" t="inlineStr">
         <is>
           <t>Trample share</t>
         </is>
       </c>
-      <c r="B220" t="n">
+      <c r="B220" s="81" t="n">
         <v>0.25</v>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="C220" s="81" t="inlineStr">
         <is>
           <t>x a raptor's max HP a trample takes (once per dino)</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
+      <c r="A221" s="81" t="inlineStr">
         <is>
           <t>Dodge every (s)</t>
         </is>
       </c>
-      <c r="B221" t="n">
+      <c r="B221" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C221" s="81" t="inlineStr">
         <is>
           <t>Clever Girls: a raptor ignores one bite per this many s</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
+      <c r="A222" s="81" t="inlineStr">
         <is>
           <t>Swarm raptors</t>
         </is>
       </c>
-      <c r="B222" t="n">
+      <c r="B222" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C222" s="81" t="inlineStr">
         <is>
           <t>Raptor Swarm: small raptors that pour out once a round</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
+      <c r="A223" s="81" t="inlineStr">
         <is>
           <t>Swarm share</t>
         </is>
       </c>
-      <c r="B223" t="n">
+      <c r="B223" s="81" t="n">
         <v>0.4</v>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C223" s="81" t="inlineStr">
         <is>
           <t>x a raptor's HP and bite for a Swarm raptor</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
+      <c r="A224" s="81" t="inlineStr">
         <is>
           <t>Swarm (s)</t>
         </is>
       </c>
-      <c r="B224" t="n">
+      <c r="B224" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="C224" t="inlineStr">
+      <c r="C224" s="81" t="inlineStr">
         <is>
           <t>s the Swarm hunts anywhere on your side's track, then vanishes</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
+      <c r="A225" s="81" t="inlineStr">
         <is>
           <t>Charge knockback (studs)</t>
         </is>
       </c>
-      <c r="B225" t="n">
+      <c r="B225" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="C225" t="inlineStr">
+      <c r="C225" s="81" t="inlineStr">
         <is>
           <t>Raptor Charge: small dinos a charging raptor passes are knocked back this far (not bosses)</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
+      <c r="A226" s="81" t="inlineStr">
         <is>
           <t>Guard reach (studs)</t>
         </is>
       </c>
-      <c r="B226" t="n">
+      <c r="B226" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="C226" s="81" t="inlineStr">
         <is>
           <t>Guard Raptors: a dino this close to a guarded tower that bites or throws at it is attacked</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
+      <c r="A227" s="81" t="inlineStr">
         <is>
           <t>Roar reach (studs)</t>
         </is>
       </c>
-      <c r="B227" t="n">
+      <c r="B227" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C227" s="81" t="inlineStr">
         <is>
           <t>Rex Tamer: small dinos this close to the alpha are stunned by its roar</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
+      <c r="A228" s="81" t="inlineStr">
         <is>
           <t>Hungry Alpha cap %</t>
         </is>
       </c>
-      <c r="B228" t="n">
+      <c r="B228" s="81" t="n">
         <v>50</v>
       </c>
-      <c r="C228" t="inlineStr">
+      <c r="C228" s="81" t="inlineStr">
         <is>
           <t>Hungry Alpha: the most its take-down stack adds this round</t>
         </is>
@@ -13053,7 +13053,7 @@
           <t>Resin</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z4" s="81" t="inlineStr">
         <is>
           <t>Walkers</t>
         </is>
@@ -13917,72 +13917,72 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="81" t="inlineStr">
         <is>
           <t>Tamed raptors: they run out, bite and come back</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>850</v>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="C20" s="81" t="n">
+        <v>600</v>
+      </c>
+      <c r="D20" s="81" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" s="81" t="n">
         <v>1.5</v>
       </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20">
+      <c r="F20" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="81">
         <f>D20*E20*F20</f>
         <v/>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="81" t="n">
         <v>22</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="81" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="81" t="inlineStr">
         <is>
           <t>Tamed raptors sprint out, pounce, bite and come back; they can be bitten. TOWERS_LATER.md.</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="81" t="n">
         <v>500</v>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="81" t="inlineStr">
         <is>
           <t>RAPTOR</t>
         </is>
       </c>
-      <c r="P20" t="n">
+      <c r="P20" s="81" t="n">
         <v>150</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R20" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="Z20" s="81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14731,102 +14731,102 @@
           <t>Take-down mark %</t>
         </is>
       </c>
-      <c r="DN4" t="inlineStr">
+      <c r="DN4" s="81" t="inlineStr">
         <is>
           <t>Walkers</t>
         </is>
       </c>
-      <c r="DO4" t="inlineStr">
+      <c r="DO4" s="81" t="inlineStr">
         <is>
           <t>Walker HP x</t>
         </is>
       </c>
-      <c r="DP4" t="inlineStr">
+      <c r="DP4" s="81" t="inlineStr">
         <is>
           <t>Walker speed x</t>
         </is>
       </c>
-      <c r="DQ4" t="inlineStr">
+      <c r="DQ4" s="81" t="inlineStr">
         <is>
           <t>Walker resist %</t>
         </is>
       </c>
-      <c r="DR4" t="inlineStr">
+      <c r="DR4" s="81" t="inlineStr">
         <is>
           <t>Walker respawn x</t>
         </is>
       </c>
-      <c r="DS4" t="inlineStr">
+      <c r="DS4" s="81" t="inlineStr">
         <is>
           <t>Hold (s)</t>
         </is>
       </c>
-      <c r="DT4" t="inlineStr">
+      <c r="DT4" s="81" t="inlineStr">
         <is>
           <t>Boss hold (s)</t>
         </is>
       </c>
-      <c r="DU4" t="inlineStr">
+      <c r="DU4" s="81" t="inlineStr">
         <is>
           <t>Flanking</t>
         </is>
       </c>
-      <c r="DV4" t="inlineStr">
+      <c r="DV4" s="81" t="inlineStr">
         <is>
           <t>Targets first</t>
         </is>
       </c>
-      <c r="DW4" t="inlineStr">
+      <c r="DW4" s="81" t="inlineStr">
         <is>
           <t>Hits air</t>
         </is>
       </c>
-      <c r="DX4" t="inlineStr">
+      <c r="DX4" s="81" t="inlineStr">
         <is>
           <t>Heals between rounds</t>
         </is>
       </c>
-      <c r="DY4" t="inlineStr">
+      <c r="DY4" s="81" t="inlineStr">
         <is>
           <t>Dodge</t>
         </is>
       </c>
-      <c r="DZ4" t="inlineStr">
+      <c r="DZ4" s="81" t="inlineStr">
         <is>
           <t>Alpha</t>
         </is>
       </c>
-      <c r="EA4" t="inlineStr">
+      <c r="EA4" s="81" t="inlineStr">
         <is>
           <t>Swarm</t>
         </is>
       </c>
-      <c r="EB4" t="inlineStr">
+      <c r="EB4" s="81" t="inlineStr">
         <is>
           <t>Charge</t>
         </is>
       </c>
-      <c r="EC4" t="inlineStr">
+      <c r="EC4" s="81" t="inlineStr">
         <is>
           <t>Guard</t>
         </is>
       </c>
-      <c r="ED4" t="inlineStr">
+      <c r="ED4" s="81" t="inlineStr">
         <is>
           <t>Stun roar every (s)</t>
         </is>
       </c>
-      <c r="EE4" t="inlineStr">
+      <c r="EE4" s="81" t="inlineStr">
         <is>
           <t>Take-down stack %</t>
         </is>
       </c>
-      <c r="EF4" t="inlineStr">
+      <c r="EF4" s="81" t="inlineStr">
         <is>
           <t>Avenger x</t>
         </is>
       </c>
-      <c r="EG4" t="inlineStr">
+      <c r="EG4" s="81" t="inlineStr">
         <is>
           <t>Hunter damage %</t>
         </is>
@@ -38257,7 +38257,7 @@
         </is>
       </c>
       <c r="CD307" s="81" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="DD307" s="81" t="n">
         <v>10</v>
@@ -38316,7 +38316,7 @@
         </is>
       </c>
       <c r="CD308" s="81" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="DD308" s="81" t="n">
         <v>12</v>
@@ -38375,7 +38375,7 @@
         </is>
       </c>
       <c r="CD309" s="81" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="CW309" s="81" t="n">
         <v>0.7</v>
@@ -39554,29 +39554,29 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="inlineStr">
+      <c r="A329" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
+      <c r="B329" s="81" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr">
+      <c r="C329" s="81" t="inlineStr">
         <is>
           <t>pack damage</t>
         </is>
       </c>
-      <c r="D329" t="n">
-        <v>1</v>
-      </c>
-      <c r="E329">
+      <c r="D329" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E329" s="81">
         <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D329),0)</f>
         <v/>
       </c>
-      <c r="F329">
+      <c r="F329" s="81">
         <f>'Towers'!$C$20+E329</f>
         <v/>
       </c>
@@ -39589,50 +39589,50 @@
       <c r="I329" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J329">
+      <c r="J329" s="81">
         <f>'Towers'!$G$20*G329*H329*I329</f>
         <v/>
       </c>
-      <c r="K329">
+      <c r="K329" s="81">
         <f>IF(J329=0,0,F329/J329)</f>
         <v/>
       </c>
       <c r="L329" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M329" t="inlineStr">
+      <c r="M329" s="81" t="inlineStr">
         <is>
           <t>Second Raptor</t>
         </is>
       </c>
-      <c r="DN329" t="n">
+      <c r="DN329" s="81" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr">
+      <c r="A330" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
+      <c r="B330" s="81" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr">
+      <c r="C330" s="81" t="inlineStr">
         <is>
           <t>pack damage</t>
         </is>
       </c>
-      <c r="D330" t="n">
+      <c r="D330" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="E330">
+      <c r="E330" s="81">
         <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D330),0)</f>
         <v/>
       </c>
-      <c r="F330">
+      <c r="F330" s="81">
         <f>F329+E330</f>
         <v/>
       </c>
@@ -39645,56 +39645,56 @@
       <c r="I330" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J330">
+      <c r="J330" s="81">
         <f>'Towers'!$G$20*G330*H330*I330</f>
         <v/>
       </c>
-      <c r="K330">
+      <c r="K330" s="81">
         <f>IF(J330=0,0,F330/J330)</f>
         <v/>
       </c>
       <c r="L330" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M330" t="inlineStr">
+      <c r="M330" s="81" t="inlineStr">
         <is>
           <t>Quick Whistle</t>
         </is>
       </c>
-      <c r="DN330" t="n">
+      <c r="DN330" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="DP330" t="n">
+      <c r="DP330" s="81" t="n">
         <v>1.3</v>
       </c>
-      <c r="DR330" t="n">
+      <c r="DR330" s="81" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="inlineStr">
+      <c r="A331" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
+      <c r="B331" s="81" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr">
+      <c r="C331" s="81" t="inlineStr">
         <is>
           <t>pack damage</t>
         </is>
       </c>
-      <c r="D331" t="n">
+      <c r="D331" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="E331">
+      <c r="E331" s="81">
         <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D331),0)</f>
         <v/>
       </c>
-      <c r="F331">
+      <c r="F331" s="81">
         <f>F330+E331</f>
         <v/>
       </c>
@@ -39707,56 +39707,56 @@
       <c r="I331" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J331">
+      <c r="J331" s="81">
         <f>'Towers'!$G$20*G331*H331*I331</f>
         <v/>
       </c>
-      <c r="K331">
+      <c r="K331" s="81">
         <f>IF(J331=0,0,F331/J331)</f>
         <v/>
       </c>
       <c r="L331" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M331" t="inlineStr">
+      <c r="M331" s="81" t="inlineStr">
         <is>
           <t>Pack of Five</t>
         </is>
       </c>
-      <c r="DN331" t="n">
+      <c r="DN331" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="DP331" t="n">
+      <c r="DP331" s="81" t="n">
         <v>1.3</v>
       </c>
-      <c r="DR331" t="n">
+      <c r="DR331" s="81" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="inlineStr">
+      <c r="A332" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
+      <c r="B332" s="81" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr">
+      <c r="C332" s="81" t="inlineStr">
         <is>
           <t>pack damage</t>
         </is>
       </c>
-      <c r="D332" t="n">
+      <c r="D332" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E332">
+      <c r="E332" s="81">
         <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D332),0)</f>
         <v/>
       </c>
-      <c r="F332">
+      <c r="F332" s="81">
         <f>F331+E332</f>
         <v/>
       </c>
@@ -39769,62 +39769,62 @@
       <c r="I332" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J332">
+      <c r="J332" s="81">
         <f>J331*G332*H332*I332</f>
         <v/>
       </c>
-      <c r="K332">
+      <c r="K332" s="81">
         <f>IF(J332=0,0,F332/J332)</f>
         <v/>
       </c>
       <c r="L332" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M332" t="inlineStr">
+      <c r="M332" s="81" t="inlineStr">
         <is>
           <t>Hide Rippers</t>
         </is>
       </c>
-      <c r="N332" t="inlineStr">
+      <c r="N332" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="CI332" t="inlineStr">
+      <c r="CI332" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ332" t="inlineStr">
+      <c r="CJ332" s="81" t="inlineStr">
         <is>
           <t>Raptors bite through armour</t>
         </is>
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr">
+      <c r="A333" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
+      <c r="B333" s="81" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr">
+      <c r="C333" s="81" t="inlineStr">
         <is>
           <t>pack damage</t>
         </is>
       </c>
-      <c r="D333" t="n">
+      <c r="D333" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E333">
+      <c r="E333" s="81">
         <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D333),0)</f>
         <v/>
       </c>
-      <c r="F333">
+      <c r="F333" s="81">
         <f>F332+E333</f>
         <v/>
       </c>
@@ -39837,62 +39837,62 @@
       <c r="I333" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J333">
+      <c r="J333" s="81">
         <f>J332*G333*H333*I333</f>
         <v/>
       </c>
-      <c r="K333">
+      <c r="K333" s="81">
         <f>IF(J333=0,0,F333/J333)</f>
         <v/>
       </c>
       <c r="L333" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M333" t="inlineStr">
+      <c r="M333" s="81" t="inlineStr">
         <is>
           <t>Raptor Swarm</t>
         </is>
       </c>
-      <c r="CI333" t="inlineStr">
+      <c r="CI333" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ333" t="inlineStr">
+      <c r="CJ333" s="81" t="inlineStr">
         <is>
           <t>10 small raptors flood the track once a round</t>
         </is>
       </c>
-      <c r="EA333" t="inlineStr">
+      <c r="EA333" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="inlineStr">
+      <c r="A334" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
+      <c r="B334" s="81" t="inlineStr">
         <is>
           <t>Alpha</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr">
+      <c r="C334" s="81" t="inlineStr">
         <is>
           <t>one big hunter</t>
         </is>
       </c>
-      <c r="D334" t="n">
-        <v>1</v>
-      </c>
-      <c r="E334">
+      <c r="D334" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E334" s="81">
         <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D334),0)</f>
         <v/>
       </c>
-      <c r="F334">
+      <c r="F334" s="81">
         <f>'Towers'!$C$20+E334</f>
         <v/>
       </c>
@@ -39905,47 +39905,47 @@
       <c r="I334" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J334">
+      <c r="J334" s="81">
         <f>'Towers'!$G$20*G334*H334*I334</f>
         <v/>
       </c>
-      <c r="K334">
+      <c r="K334" s="81">
         <f>IF(J334=0,0,F334/J334)</f>
         <v/>
       </c>
       <c r="L334" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M334" t="inlineStr">
+      <c r="M334" s="81" t="inlineStr">
         <is>
           <t>Sharp Claws</t>
         </is>
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="inlineStr">
+      <c r="A335" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
+      <c r="B335" s="81" t="inlineStr">
         <is>
           <t>Alpha</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr">
+      <c r="C335" s="81" t="inlineStr">
         <is>
           <t>one big hunter</t>
         </is>
       </c>
-      <c r="D335" t="n">
+      <c r="D335" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="E335">
+      <c r="E335" s="81">
         <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D335),0)</f>
         <v/>
       </c>
-      <c r="F335">
+      <c r="F335" s="81">
         <f>F334+E335</f>
         <v/>
       </c>
@@ -39958,53 +39958,53 @@
       <c r="I335" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J335">
+      <c r="J335" s="81">
         <f>'Towers'!$G$20*G335*H335*I335</f>
         <v/>
       </c>
-      <c r="K335">
+      <c r="K335" s="81">
         <f>IF(J335=0,0,F335/J335)</f>
         <v/>
       </c>
       <c r="L335" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M335" t="inlineStr">
+      <c r="M335" s="81" t="inlineStr">
         <is>
           <t>Thick Hide</t>
         </is>
       </c>
-      <c r="DO335" t="n">
+      <c r="DO335" s="81" t="n">
         <v>1.6</v>
       </c>
-      <c r="DQ335" t="n">
+      <c r="DQ335" s="81" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr">
+      <c r="A336" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
+      <c r="B336" s="81" t="inlineStr">
         <is>
           <t>Alpha</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr">
+      <c r="C336" s="81" t="inlineStr">
         <is>
           <t>one big hunter</t>
         </is>
       </c>
-      <c r="D336" t="n">
+      <c r="D336" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="E336">
+      <c r="E336" s="81">
         <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D336),0)</f>
         <v/>
       </c>
-      <c r="F336">
+      <c r="F336" s="81">
         <f>F335+E336</f>
         <v/>
       </c>
@@ -40017,64 +40017,64 @@
       <c r="I336" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J336">
+      <c r="J336" s="81">
         <f>'Towers'!$G$20*G336*H336*I336</f>
         <v/>
       </c>
-      <c r="K336">
+      <c r="K336" s="81">
         <f>IF(J336=0,0,F336/J336)</f>
         <v/>
       </c>
       <c r="L336" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M336" t="inlineStr">
+      <c r="M336" s="81" t="inlineStr">
         <is>
           <t>Alpha Raptor</t>
         </is>
       </c>
-      <c r="BJ336" t="n">
+      <c r="BJ336" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="DO336" t="n">
+      <c r="DO336" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="DQ336" t="n">
+      <c r="DQ336" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="DS336" t="n">
-        <v>1</v>
-      </c>
-      <c r="DZ336" t="inlineStr">
+      <c r="DS336" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="DZ336" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr">
+      <c r="A337" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
+      <c r="B337" s="81" t="inlineStr">
         <is>
           <t>Alpha</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr">
+      <c r="C337" s="81" t="inlineStr">
         <is>
           <t>one big hunter</t>
         </is>
       </c>
-      <c r="D337" t="n">
+      <c r="D337" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E337">
+      <c r="E337" s="81">
         <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D337),0)</f>
         <v/>
       </c>
-      <c r="F337">
+      <c r="F337" s="81">
         <f>F336+E337</f>
         <v/>
       </c>
@@ -40087,60 +40087,60 @@
       <c r="I337" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J337">
+      <c r="J337" s="81">
         <f>J336*G337*H337*I337</f>
         <v/>
       </c>
-      <c r="K337">
+      <c r="K337" s="81">
         <f>IF(J337=0,0,F337/J337)</f>
         <v/>
       </c>
       <c r="L337" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M337" t="inlineStr">
+      <c r="M337" s="81" t="inlineStr">
         <is>
           <t>Sickle Claw</t>
         </is>
       </c>
-      <c r="BJ337" t="n">
+      <c r="BJ337" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="CI337" t="inlineStr">
+      <c r="CI337" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ337" t="inlineStr">
+      <c r="CJ337" s="81" t="inlineStr">
         <is>
           <t>×3 on its target, breaks 3</t>
         </is>
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr">
+      <c r="A338" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr">
+      <c r="B338" s="81" t="inlineStr">
         <is>
           <t>Alpha</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr">
+      <c r="C338" s="81" t="inlineStr">
         <is>
           <t>one big hunter</t>
         </is>
       </c>
-      <c r="D338" t="n">
+      <c r="D338" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E338">
+      <c r="E338" s="81">
         <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D338),0)</f>
         <v/>
       </c>
-      <c r="F338">
+      <c r="F338" s="81">
         <f>F337+E338</f>
         <v/>
       </c>
@@ -40153,66 +40153,66 @@
       <c r="I338" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J338">
+      <c r="J338" s="81">
         <f>J337*G338*H338*I338</f>
         <v/>
       </c>
-      <c r="K338">
+      <c r="K338" s="81">
         <f>IF(J338=0,0,F338/J338)</f>
         <v/>
       </c>
       <c r="L338" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M338" t="inlineStr">
+      <c r="M338" s="81" t="inlineStr">
         <is>
           <t>King of the Pack</t>
         </is>
       </c>
-      <c r="BJ338" t="n">
+      <c r="BJ338" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="CI338" t="inlineStr">
+      <c r="CI338" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ338" t="inlineStr">
+      <c r="CJ338" s="81" t="inlineStr">
         <is>
           <t>A giant raptor, half damage taken</t>
         </is>
       </c>
-      <c r="DO338" t="n">
+      <c r="DO338" s="81" t="n">
         <v>1.5</v>
       </c>
-      <c r="DQ338" t="n">
+      <c r="DQ338" s="81" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="inlineStr">
+      <c r="A339" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
+      <c r="B339" s="81" t="inlineStr">
         <is>
           <t>Trainer</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr">
+      <c r="C339" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D339" t="n">
-        <v>1</v>
-      </c>
-      <c r="E339">
+      <c r="D339" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E339" s="81">
         <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D339),0)</f>
         <v/>
       </c>
-      <c r="F339">
+      <c r="F339" s="81">
         <f>'Towers'!$C$20+E339</f>
         <v/>
       </c>
@@ -40225,52 +40225,52 @@
       <c r="I339" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J339">
+      <c r="J339" s="81">
         <f>'Towers'!$G$20*G339*H339*I339</f>
         <v/>
       </c>
-      <c r="K339">
+      <c r="K339" s="81">
         <f>IF(J339=0,0,F339/J339)</f>
         <v/>
       </c>
       <c r="L339" s="110" t="n">
         <v>1.15</v>
       </c>
-      <c r="M339" t="inlineStr">
+      <c r="M339" s="81" t="inlineStr">
         <is>
           <t>Tracking Nose</t>
         </is>
       </c>
-      <c r="DV339" t="inlineStr">
+      <c r="DV339" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr">
+      <c r="A340" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
+      <c r="B340" s="81" t="inlineStr">
         <is>
           <t>Trainer</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr">
+      <c r="C340" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D340" t="n">
+      <c r="D340" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="E340">
+      <c r="E340" s="81">
         <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D340),0)</f>
         <v/>
       </c>
-      <c r="F340">
+      <c r="F340" s="81">
         <f>F339+E340</f>
         <v/>
       </c>
@@ -40283,58 +40283,58 @@
       <c r="I340" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J340">
+      <c r="J340" s="81">
         <f>'Towers'!$G$20*G340*H340*I340</f>
         <v/>
       </c>
-      <c r="K340">
+      <c r="K340" s="81">
         <f>IF(J340=0,0,F340/J340)</f>
         <v/>
       </c>
       <c r="L340" s="110" t="n">
         <v>1.15</v>
       </c>
-      <c r="M340" t="inlineStr">
+      <c r="M340" s="81" t="inlineStr">
         <is>
           <t>Herding Call</t>
         </is>
       </c>
-      <c r="AE340" t="n">
+      <c r="AE340" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="AF340" t="n">
-        <v>1</v>
-      </c>
-      <c r="DV340" t="inlineStr">
+      <c r="AF340" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="DV340" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr">
+      <c r="A341" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
+      <c r="B341" s="81" t="inlineStr">
         <is>
           <t>Trainer</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr">
+      <c r="C341" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D341" t="n">
+      <c r="D341" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="E341">
+      <c r="E341" s="81">
         <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D341),0)</f>
         <v/>
       </c>
-      <c r="F341">
+      <c r="F341" s="81">
         <f>F340+E341</f>
         <v/>
       </c>
@@ -40347,64 +40347,64 @@
       <c r="I341" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J341">
+      <c r="J341" s="81">
         <f>'Towers'!$G$20*G341*H341*I341</f>
         <v/>
       </c>
-      <c r="K341">
+      <c r="K341" s="81">
         <f>IF(J341=0,0,F341/J341)</f>
         <v/>
       </c>
       <c r="L341" s="110" t="n">
         <v>1.15</v>
       </c>
-      <c r="M341" t="inlineStr">
+      <c r="M341" s="81" t="inlineStr">
         <is>
           <t>Pack Howl</t>
         </is>
       </c>
-      <c r="AE341" t="n">
+      <c r="AE341" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="AF341" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY341" t="n">
+      <c r="AF341" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY341" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="DN341" t="n">
+      <c r="DN341" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="DV341" t="inlineStr">
+      <c r="DV341" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="inlineStr">
+      <c r="A342" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
+      <c r="B342" s="81" t="inlineStr">
         <is>
           <t>Trainer</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr">
+      <c r="C342" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D342" t="n">
+      <c r="D342" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E342">
+      <c r="E342" s="81">
         <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D342),0)</f>
         <v/>
       </c>
-      <c r="F342">
+      <c r="F342" s="81">
         <f>F341+E342</f>
         <v/>
       </c>
@@ -40417,65 +40417,65 @@
       <c r="I342" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J342">
+      <c r="J342" s="81">
         <f>J341*G342*H342*I342</f>
         <v/>
       </c>
-      <c r="K342">
+      <c r="K342" s="81">
         <f>IF(J342=0,0,F342/J342)</f>
         <v/>
       </c>
       <c r="L342" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M342" t="inlineStr">
+      <c r="M342" s="81" t="inlineStr">
         <is>
           <t>Treat Bag</t>
         </is>
       </c>
-      <c r="CI342" t="inlineStr">
+      <c r="CI342" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ342" t="inlineStr">
+      <c r="CJ342" s="81" t="inlineStr">
         <is>
           <t>Raptors heal and return faster</t>
         </is>
       </c>
-      <c r="DR342" t="n">
+      <c r="DR342" s="81" t="n">
         <v>0.5</v>
       </c>
-      <c r="DX342" t="inlineStr">
+      <c r="DX342" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr">
+      <c r="A343" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr">
+      <c r="B343" s="81" t="inlineStr">
         <is>
           <t>Trainer</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr">
+      <c r="C343" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D343" t="n">
+      <c r="D343" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E343">
+      <c r="E343" s="81">
         <f>ROUND('Towers'!$C$20*POWER('Tuning'!$B$12,D343),0)</f>
         <v/>
       </c>
-      <c r="F343">
+      <c r="F343" s="81">
         <f>F342+E343</f>
         <v/>
       </c>
@@ -40488,62 +40488,62 @@
       <c r="I343" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="J343">
+      <c r="J343" s="81">
         <f>J342*G343*H343*I343</f>
         <v/>
       </c>
-      <c r="K343">
+      <c r="K343" s="81">
         <f>IF(J343=0,0,F343/J343)</f>
         <v/>
       </c>
       <c r="L343" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M343" t="inlineStr">
+      <c r="M343" s="81" t="inlineStr">
         <is>
           <t>Raptor Charge</t>
         </is>
       </c>
-      <c r="CI343" t="inlineStr">
+      <c r="CI343" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ343" t="inlineStr">
+      <c r="CJ343" s="81" t="inlineStr">
         <is>
           <t>Every raptor charges the track once a round</t>
         </is>
       </c>
-      <c r="EB343" t="inlineStr">
+      <c r="EB343" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr">
+      <c r="A344" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
+      <c r="B344" s="81" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr">
+      <c r="C344" s="81" t="inlineStr">
         <is>
           <t>pack damage</t>
         </is>
       </c>
-      <c r="D344" t="n">
+      <c r="D344" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E344">
+      <c r="E344" s="81">
         <f>E332</f>
         <v/>
       </c>
-      <c r="F344">
+      <c r="F344" s="81">
         <f>F332</f>
         <v/>
       </c>
@@ -40559,51 +40559,51 @@
       <c r="L344" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M344" t="inlineStr">
+      <c r="M344" s="81" t="inlineStr">
         <is>
           <t>Flanking</t>
         </is>
       </c>
-      <c r="CI344" t="inlineStr">
+      <c r="CI344" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ344" t="inlineStr">
+      <c r="CJ344" s="81" t="inlineStr">
         <is>
           <t>Each raptor picks a different dino</t>
         </is>
       </c>
-      <c r="DU344" t="inlineStr">
+      <c r="DU344" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr">
+      <c r="A345" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
+      <c r="B345" s="81" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr">
+      <c r="C345" s="81" t="inlineStr">
         <is>
           <t>pack damage</t>
         </is>
       </c>
-      <c r="D345" t="n">
+      <c r="D345" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E345">
+      <c r="E345" s="81">
         <f>E332</f>
         <v/>
       </c>
-      <c r="F345">
+      <c r="F345" s="81">
         <f>F332</f>
         <v/>
       </c>
@@ -40619,49 +40619,49 @@
       <c r="L345" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M345" t="inlineStr">
+      <c r="M345" s="81" t="inlineStr">
         <is>
           <t>Ambush</t>
         </is>
       </c>
-      <c r="BU345" t="n">
+      <c r="BU345" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="CI345" t="inlineStr">
+      <c r="CI345" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ345" t="inlineStr">
+      <c r="CJ345" s="81" t="inlineStr">
         <is>
           <t>Each raptor's first pounce hits double</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
+      <c r="A346" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
+      <c r="B346" s="81" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr">
+      <c r="C346" s="81" t="inlineStr">
         <is>
           <t>pack damage</t>
         </is>
       </c>
-      <c r="D346" t="n">
+      <c r="D346" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E346">
+      <c r="E346" s="81">
         <f>E333</f>
         <v/>
       </c>
-      <c r="F346">
+      <c r="F346" s="81">
         <f>F333</f>
         <v/>
       </c>
@@ -40677,51 +40677,51 @@
       <c r="L346" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M346" t="inlineStr">
+      <c r="M346" s="81" t="inlineStr">
         <is>
           <t>Clever Girls</t>
         </is>
       </c>
-      <c r="CI346" t="inlineStr">
+      <c r="CI346" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ346" t="inlineStr">
+      <c r="CJ346" s="81" t="inlineStr">
         <is>
           <t>Raptors dodge bites and never get trampled</t>
         </is>
       </c>
-      <c r="DY346" t="inlineStr">
+      <c r="DY346" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr">
+      <c r="A347" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
+      <c r="B347" s="81" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr">
+      <c r="C347" s="81" t="inlineStr">
         <is>
           <t>pack damage</t>
         </is>
       </c>
-      <c r="D347" t="n">
+      <c r="D347" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E347">
+      <c r="E347" s="81">
         <f>E333</f>
         <v/>
       </c>
-      <c r="F347">
+      <c r="F347" s="81">
         <f>F333</f>
         <v/>
       </c>
@@ -40737,51 +40737,51 @@
       <c r="L347" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M347" t="inlineStr">
+      <c r="M347" s="81" t="inlineStr">
         <is>
           <t>Sky Leap</t>
         </is>
       </c>
-      <c r="CI347" t="inlineStr">
+      <c r="CI347" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ347" t="inlineStr">
+      <c r="CJ347" s="81" t="inlineStr">
         <is>
           <t>Raptors jump at low flyers</t>
         </is>
       </c>
-      <c r="DW347" t="inlineStr">
+      <c r="DW347" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr">
+      <c r="A348" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
+      <c r="B348" s="81" t="inlineStr">
         <is>
           <t>Alpha</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr">
+      <c r="C348" s="81" t="inlineStr">
         <is>
           <t>one big hunter</t>
         </is>
       </c>
-      <c r="D348" t="n">
+      <c r="D348" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E348">
+      <c r="E348" s="81">
         <f>E337</f>
         <v/>
       </c>
-      <c r="F348">
+      <c r="F348" s="81">
         <f>F337</f>
         <v/>
       </c>
@@ -40797,52 +40797,52 @@
       <c r="L348" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M348" t="inlineStr">
+      <c r="M348" s="81" t="inlineStr">
         <is>
           <t>Boss Hunter</t>
         </is>
       </c>
-      <c r="P348" t="n">
+      <c r="P348" s="81" t="n">
         <v>1.6</v>
       </c>
-      <c r="CI348" t="inlineStr">
+      <c r="CI348" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ348" t="inlineStr">
+      <c r="CJ348" s="81" t="inlineStr">
         <is>
           <t>Can hold a boss for a moment</t>
         </is>
       </c>
-      <c r="DT348" t="n">
+      <c r="DT348" s="81" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr">
+      <c r="A349" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
+      <c r="B349" s="81" t="inlineStr">
         <is>
           <t>Alpha</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr">
+      <c r="C349" s="81" t="inlineStr">
         <is>
           <t>one big hunter</t>
         </is>
       </c>
-      <c r="D349" t="n">
+      <c r="D349" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E349">
+      <c r="E349" s="81">
         <f>E337</f>
         <v/>
       </c>
-      <c r="F349">
+      <c r="F349" s="81">
         <f>F337</f>
         <v/>
       </c>
@@ -40858,49 +40858,49 @@
       <c r="L349" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M349" t="inlineStr">
+      <c r="M349" s="81" t="inlineStr">
         <is>
           <t>Scent Trail</t>
         </is>
       </c>
-      <c r="T349" t="n">
+      <c r="T349" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="CI349" t="inlineStr">
+      <c r="CI349" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ349" t="inlineStr">
+      <c r="CJ349" s="81" t="inlineStr">
         <is>
           <t>Its target is marked +15%</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
+      <c r="A350" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
+      <c r="B350" s="81" t="inlineStr">
         <is>
           <t>Alpha</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr">
+      <c r="C350" s="81" t="inlineStr">
         <is>
           <t>one big hunter</t>
         </is>
       </c>
-      <c r="D350" t="n">
+      <c r="D350" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E350">
+      <c r="E350" s="81">
         <f>E338</f>
         <v/>
       </c>
-      <c r="F350">
+      <c r="F350" s="81">
         <f>F338</f>
         <v/>
       </c>
@@ -40916,55 +40916,55 @@
       <c r="L350" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M350" t="inlineStr">
+      <c r="M350" s="81" t="inlineStr">
         <is>
           <t>Rex Tamer</t>
         </is>
       </c>
-      <c r="U350" t="n">
-        <v>1</v>
-      </c>
-      <c r="CI350" t="inlineStr">
+      <c r="U350" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI350" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ350" t="inlineStr">
+      <c r="CJ350" s="81" t="inlineStr">
         <is>
           <t>A tamed T. rex whose roar stuns</t>
         </is>
       </c>
-      <c r="DO350" t="n">
+      <c r="DO350" s="81" t="n">
         <v>1.4</v>
       </c>
-      <c r="ED350" t="n">
+      <c r="ED350" s="81" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
+      <c r="A351" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
+      <c r="B351" s="81" t="inlineStr">
         <is>
           <t>Alpha</t>
         </is>
       </c>
-      <c r="C351" t="inlineStr">
+      <c r="C351" s="81" t="inlineStr">
         <is>
           <t>one big hunter</t>
         </is>
       </c>
-      <c r="D351" t="n">
+      <c r="D351" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E351">
+      <c r="E351" s="81">
         <f>E338</f>
         <v/>
       </c>
-      <c r="F351">
+      <c r="F351" s="81">
         <f>F338</f>
         <v/>
       </c>
@@ -40980,49 +40980,49 @@
       <c r="L351" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M351" t="inlineStr">
+      <c r="M351" s="81" t="inlineStr">
         <is>
           <t>Hungry Alpha</t>
         </is>
       </c>
-      <c r="CI351" t="inlineStr">
+      <c r="CI351" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ351" t="inlineStr">
+      <c r="CJ351" s="81" t="inlineStr">
         <is>
           <t>Stronger with every take-down</t>
         </is>
       </c>
-      <c r="EE351" t="n">
+      <c r="EE351" s="81" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="inlineStr">
+      <c r="A352" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
+      <c r="B352" s="81" t="inlineStr">
         <is>
           <t>Trainer</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr">
+      <c r="C352" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D352" t="n">
+      <c r="D352" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E352">
+      <c r="E352" s="81">
         <f>E342</f>
         <v/>
       </c>
-      <c r="F352">
+      <c r="F352" s="81">
         <f>F342</f>
         <v/>
       </c>
@@ -41038,51 +41038,51 @@
       <c r="L352" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M352" t="inlineStr">
+      <c r="M352" s="81" t="inlineStr">
         <is>
           <t>Guard Raptors</t>
         </is>
       </c>
-      <c r="CI352" t="inlineStr">
+      <c r="CI352" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ352" t="inlineStr">
+      <c r="CJ352" s="81" t="inlineStr">
         <is>
           <t>A raptor guards each tower</t>
         </is>
       </c>
-      <c r="EC352" t="inlineStr">
+      <c r="EC352" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr">
+      <c r="A353" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
+      <c r="B353" s="81" t="inlineStr">
         <is>
           <t>Trainer</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr">
+      <c r="C353" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D353" t="n">
+      <c r="D353" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E353">
+      <c r="E353" s="81">
         <f>E342</f>
         <v/>
       </c>
-      <c r="F353">
+      <c r="F353" s="81">
         <f>F342</f>
         <v/>
       </c>
@@ -41098,52 +41098,52 @@
       <c r="L353" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M353" t="inlineStr">
+      <c r="M353" s="81" t="inlineStr">
         <is>
           <t>Whistle Drill</t>
         </is>
       </c>
-      <c r="BY353" t="n">
+      <c r="BY353" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="CI353" t="inlineStr">
+      <c r="CI353" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ353" t="inlineStr">
+      <c r="CJ353" s="81" t="inlineStr">
         <is>
           <t>Raptors run 30% faster</t>
         </is>
       </c>
-      <c r="DP353" t="n">
+      <c r="DP353" s="81" t="n">
         <v>1.3</v>
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="inlineStr">
+      <c r="A354" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
+      <c r="B354" s="81" t="inlineStr">
         <is>
           <t>Trainer</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr">
+      <c r="C354" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D354" t="n">
+      <c r="D354" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E354">
+      <c r="E354" s="81">
         <f>E343</f>
         <v/>
       </c>
-      <c r="F354">
+      <c r="F354" s="81">
         <f>F343</f>
         <v/>
       </c>
@@ -41159,52 +41159,52 @@
       <c r="L354" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M354" t="inlineStr">
+      <c r="M354" s="81" t="inlineStr">
         <is>
           <t>Pack Bond</t>
         </is>
       </c>
-      <c r="CI354" t="inlineStr">
+      <c r="CI354" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ354" t="inlineStr">
+      <c r="CJ354" s="81" t="inlineStr">
         <is>
           <t>Hunters nearby +20% with 3+ raptors out</t>
         </is>
       </c>
-      <c r="DN354" t="n">
+      <c r="DN354" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="EG354" t="n">
+      <c r="EG354" s="81" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="inlineStr">
+      <c r="A355" s="81" t="inlineStr">
         <is>
           <t>Raptor Pen</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr">
+      <c r="B355" s="81" t="inlineStr">
         <is>
           <t>Trainer</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr">
+      <c r="C355" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D355" t="n">
+      <c r="D355" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E355">
+      <c r="E355" s="81">
         <f>E343</f>
         <v/>
       </c>
-      <c r="F355">
+      <c r="F355" s="81">
         <f>F343</f>
         <v/>
       </c>
@@ -41220,39 +41220,39 @@
       <c r="L355" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="M355" t="inlineStr">
+      <c r="M355" s="81" t="inlineStr">
         <is>
           <t>Raider Hounds</t>
         </is>
       </c>
-      <c r="BJ355" t="n">
+      <c r="BJ355" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="CI355" t="inlineStr">
+      <c r="CI355" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ355" t="inlineStr">
+      <c r="CJ355" s="81" t="inlineStr">
         <is>
           <t>Raptors chase raiders (or the dino that hurt a tower)</t>
         </is>
       </c>
-      <c r="CK355" t="inlineStr">
+      <c r="CK355" s="81" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="CL355" t="n">
+      <c r="CL355" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="CM355" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN355" t="n">
+      <c r="CM355" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN355" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="EF355" t="n">
+      <c r="EF355" s="81" t="n">
         <v>2</v>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -13931,10 +13931,10 @@
         <v>600</v>
       </c>
       <c r="D20" s="81" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E20" s="81" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="F20" s="81" t="n">
         <v>1</v>
@@ -38437,7 +38437,7 @@
         </is>
       </c>
       <c r="CD310" s="81" t="n">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="CI310" s="81" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
       </c>
       <c r="CJ310" s="81" t="inlineStr">
         <is>
-          <t>Fossils pay double cash</t>
+          <t>Fossils pay 50% more cash</t>
         </is>
       </c>
     </row>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -40148,7 +40148,7 @@
         <v>1.9</v>
       </c>
       <c r="H338" s="110" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I338" s="110" t="n">
         <v>1</v>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9500,7 +9500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E228"/>
+  <dimension ref="A1:E242"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -10178,6 +10178,7 @@
       </c>
       <c r="E38" s="17" t="n"/>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="31" t="inlineStr">
         <is>
@@ -10248,6 +10249,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="31" t="inlineStr">
         <is>
@@ -10398,6 +10400,7 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
         <is>
@@ -10448,6 +10451,7 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="31" t="inlineStr">
         <is>
@@ -10518,6 +10522,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
@@ -10568,6 +10573,7 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
@@ -10758,6 +10764,7 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
@@ -10905,6 +10912,7 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" s="31" t="inlineStr">
         <is>
@@ -11012,6 +11020,7 @@
         </is>
       </c>
     </row>
+    <row r="93"/>
     <row r="94" s="90">
       <c r="A94" s="31" t="inlineStr">
         <is>
@@ -11039,6 +11048,7 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" s="31" t="inlineStr">
         <is>
@@ -11066,6 +11076,7 @@
         </is>
       </c>
     </row>
+    <row r="99"/>
     <row r="100">
       <c r="A100" s="99" t="inlineStr">
         <is>
@@ -11113,6 +11124,7 @@
         </is>
       </c>
     </row>
+    <row r="103"/>
     <row r="104">
       <c r="A104" s="99" t="inlineStr">
         <is>
@@ -11203,6 +11215,7 @@
         </is>
       </c>
     </row>
+    <row r="109"/>
     <row r="110">
       <c r="A110" s="99" t="inlineStr">
         <is>
@@ -11385,6 +11398,7 @@
         </is>
       </c>
     </row>
+    <row r="123"/>
     <row r="124">
       <c r="A124" s="99" t="inlineStr">
         <is>
@@ -11438,6 +11452,7 @@
         </is>
       </c>
     </row>
+    <row r="128"/>
     <row r="129">
       <c r="A129" s="99" t="inlineStr">
         <is>
@@ -11577,6 +11592,7 @@
         </is>
       </c>
     </row>
+    <row r="140"/>
     <row r="141">
       <c r="A141" s="99" t="inlineStr">
         <is>
@@ -12319,6 +12335,7 @@
         </is>
       </c>
     </row>
+    <row r="191"/>
     <row r="192">
       <c r="A192" s="81" t="inlineStr">
         <is>
@@ -12431,6 +12448,7 @@
         </is>
       </c>
     </row>
+    <row r="200"/>
     <row r="201">
       <c r="A201" s="81" t="inlineStr">
         <is>
@@ -12832,6 +12850,194 @@
       <c r="C228" s="81" t="inlineStr">
         <is>
           <t>Hungry Alpha: the most its take-down stack adds this round</t>
+        </is>
+      </c>
+    </row>
+    <row r="229"/>
+    <row r="230">
+      <c r="A230" s="81" t="inlineStr">
+        <is>
+          <t>BONE TOTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="81" t="inlineStr">
+        <is>
+          <t>Totem charge (Bones)</t>
+        </is>
+      </c>
+      <c r="B231" s="81" t="n">
+        <v>8</v>
+      </c>
+      <c r="C231" s="81" t="inlineStr">
+        <is>
+          <t>pops (a dino losing a size) inside a Bone Totem's range that fill it (x Charge needed x; Shared/Totem)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="81" t="inlineStr">
+        <is>
+          <t>Roar breaks</t>
+        </is>
+      </c>
+      <c r="B232" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="C232" s="81" t="inlineStr">
+        <is>
+          <t>sizes the Spirit Roar may drop on each dino it hits (a Size breaks tier raises it)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="81" t="inlineStr">
+        <is>
+          <t>Fear knockback (studs)</t>
+        </is>
+      </c>
+      <c r="B233" s="81" t="n">
+        <v>8</v>
+      </c>
+      <c r="C233" s="81" t="inlineStr">
+        <is>
+          <t>the most the roar knocks a small dino back (Fear: Knockback (studs); never a boss)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="81" t="inlineStr">
+        <is>
+          <t>Shatter strip (s)</t>
+        </is>
+      </c>
+      <c r="B234" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="C234" s="81" t="inlineStr">
+        <is>
+          <t>s a dino hit by a Shatter Roar stays unarmoured (bosses half, as Strip (s))</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="81" t="inlineStr">
+        <is>
+          <t>Skull x</t>
+        </is>
+      </c>
+      <c r="B235" s="81" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C235" s="81" t="inlineStr">
+        <is>
+          <t>x the roar's damage for each Skull Storm skull (one dino each, breaks 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="81" t="inlineStr">
+        <is>
+          <t>Spirit hunters</t>
+        </is>
+      </c>
+      <c r="B236" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="C236" s="81" t="inlineStr">
+        <is>
+          <t>ghost hunters a full Spirit Hunters totem calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="81" t="inlineStr">
+        <is>
+          <t>Spirit hunter damage</t>
+        </is>
+      </c>
+      <c r="B237" s="81" t="n">
+        <v>9</v>
+      </c>
+      <c r="C237" s="81" t="inlineStr">
+        <is>
+          <t>a ghost hunter's shot (x the team's level)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="81" t="inlineStr">
+        <is>
+          <t>Spirit hunter rate</t>
+        </is>
+      </c>
+      <c r="B238" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="C238" s="81" t="inlineStr">
+        <is>
+          <t>shots a second per ghost hunter</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="81" t="inlineStr">
+        <is>
+          <t>Spirit (s)</t>
+        </is>
+      </c>
+      <c r="B239" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="C239" s="81" t="inlineStr">
+        <is>
+          <t>s the ghost hunters stay</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="81" t="inlineStr">
+        <is>
+          <t>Full buff (s)</t>
+        </is>
+      </c>
+      <c r="B240" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="C240" s="81" t="inlineStr">
+        <is>
+          <t>s War Paint's hunter buff lasts after a full charge</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="81" t="inlineStr">
+        <is>
+          <t>Finisher %</t>
+        </is>
+      </c>
+      <c r="B241" s="81" t="n">
+        <v>25</v>
+      </c>
+      <c r="C241" s="81" t="inlineStr">
+        <is>
+          <t>Finishing Roar: a boss in range dropping below this % of its HP gets one free roar (once per boss)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="81" t="inlineStr">
+        <is>
+          <t>Treasure cash</t>
+        </is>
+      </c>
+      <c r="B242" s="81" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C242" s="81" t="inlineStr">
+        <is>
+          <t>Ancient Treasure: the first full charge of the match also drops a chest worth this</t>
         </is>
       </c>
     </row>
@@ -12855,7 +13061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -13986,6 +14192,74 @@
         <v>1</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B21" s="81" t="inlineStr">
+        <is>
+          <t>Bones charge it: a roar, buffs or cash</t>
+        </is>
+      </c>
+      <c r="C21" s="81" t="n">
+        <v>800</v>
+      </c>
+      <c r="D21" s="81" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="81">
+        <f>D21*E21*F21</f>
+        <v/>
+      </c>
+      <c r="H21" s="81" t="n">
+        <v>24</v>
+      </c>
+      <c r="I21" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J21" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="81" t="inlineStr">
+        <is>
+          <t>Bones taken near it charge it; full = Spirit Roar (area, breaks 2). Never adds Bones to any score. TOWERS_LATER.md.</t>
+        </is>
+      </c>
+      <c r="L21" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="81" t="n">
+        <v>450</v>
+      </c>
+      <c r="O21" s="81" t="inlineStr">
+        <is>
+          <t>TOTEM</t>
+        </is>
+      </c>
+      <c r="P21" s="81" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q21" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="81" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -14006,7 +14280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EG355"/>
+  <dimension ref="A1:FA382"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -14829,6 +15103,106 @@
       <c r="EG4" s="81" t="inlineStr">
         <is>
           <t>Hunter damage %</t>
+        </is>
+      </c>
+      <c r="EH4" s="81" t="inlineStr">
+        <is>
+          <t>Charge x</t>
+        </is>
+      </c>
+      <c r="EI4" s="81" t="inlineStr">
+        <is>
+          <t>Hunter charge x</t>
+        </is>
+      </c>
+      <c r="EJ4" s="81" t="inlineStr">
+        <is>
+          <t>Boss charge %</t>
+        </is>
+      </c>
+      <c r="EK4" s="81" t="inlineStr">
+        <is>
+          <t>Bounty charge x</t>
+        </is>
+      </c>
+      <c r="EL4" s="81" t="inlineStr">
+        <is>
+          <t>Charge needed x</t>
+        </is>
+      </c>
+      <c r="EM4" s="81" t="inlineStr">
+        <is>
+          <t>Roar echoes</t>
+        </is>
+      </c>
+      <c r="EN4" s="81" t="inlineStr">
+        <is>
+          <t>Roar whole track</t>
+        </is>
+      </c>
+      <c r="EO4" s="81" t="inlineStr">
+        <is>
+          <t>Skulls</t>
+        </is>
+      </c>
+      <c r="EP4" s="81" t="inlineStr">
+        <is>
+          <t>Full guard (s)</t>
+        </is>
+      </c>
+      <c r="EQ4" s="81" t="inlineStr">
+        <is>
+          <t>Spirit hunters</t>
+        </is>
+      </c>
+      <c r="ER4" s="81" t="inlineStr">
+        <is>
+          <t>Full cash</t>
+        </is>
+      </c>
+      <c r="ES4" s="81" t="inlineStr">
+        <is>
+          <t>Payday cash</t>
+        </is>
+      </c>
+      <c r="ET4" s="81" t="inlineStr">
+        <is>
+          <t>Treasure</t>
+        </is>
+      </c>
+      <c r="EU4" s="81" t="inlineStr">
+        <is>
+          <t>Charge aura damage %</t>
+        </is>
+      </c>
+      <c r="EV4" s="81" t="inlineStr">
+        <is>
+          <t>Hunter ability cooldown x</t>
+        </is>
+      </c>
+      <c r="EW4" s="81" t="inlineStr">
+        <is>
+          <t>Side aura half</t>
+        </is>
+      </c>
+      <c r="EX4" s="81" t="inlineStr">
+        <is>
+          <t>Bone cash</t>
+        </is>
+      </c>
+      <c r="EY4" s="81" t="inlineStr">
+        <is>
+          <t>Bank cash per charge</t>
+        </is>
+      </c>
+      <c r="EZ4" s="81" t="inlineStr">
+        <is>
+          <t>Finishing roar</t>
+        </is>
+      </c>
+      <c r="FA4" s="81" t="inlineStr">
+        <is>
+          <t>Aura range %</t>
         </is>
       </c>
     </row>
@@ -41254,6 +41628,1691 @@
       </c>
       <c r="EF355" s="81" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B356" s="81" t="inlineStr">
+        <is>
+          <t>Roar</t>
+        </is>
+      </c>
+      <c r="C356" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D356" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E356" s="81">
+        <f>ROUND('Towers'!$C$21*POWER('Tuning'!$B$12,D356),0)</f>
+        <v/>
+      </c>
+      <c r="F356" s="81">
+        <f>'Towers'!$C$21+E356</f>
+        <v/>
+      </c>
+      <c r="G356" s="110" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H356" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I356" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J356" s="81">
+        <f>'Towers'!$G$21*G356*H356*I356</f>
+        <v/>
+      </c>
+      <c r="K356" s="81">
+        <f>IF(J356=0,0,F356/J356)</f>
+        <v/>
+      </c>
+      <c r="L356" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M356" s="81" t="inlineStr">
+        <is>
+          <t>Louder Roar</t>
+        </is>
+      </c>
+      <c r="DN356" s="81" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B357" s="81" t="inlineStr">
+        <is>
+          <t>Roar</t>
+        </is>
+      </c>
+      <c r="C357" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D357" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E357" s="81">
+        <f>ROUND('Towers'!$C$21*POWER('Tuning'!$B$12,D357),0)</f>
+        <v/>
+      </c>
+      <c r="F357" s="81">
+        <f>F356+E357</f>
+        <v/>
+      </c>
+      <c r="G357" s="110" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H357" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I357" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J357" s="81">
+        <f>'Towers'!$G$21*G357*H357*I357</f>
+        <v/>
+      </c>
+      <c r="K357" s="81">
+        <f>IF(J357=0,0,F357/J357)</f>
+        <v/>
+      </c>
+      <c r="L357" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M357" s="81" t="inlineStr">
+        <is>
+          <t>Quick Charge</t>
+        </is>
+      </c>
+      <c r="DN357" s="81" t="n"/>
+      <c r="DP357" s="81" t="n"/>
+      <c r="DR357" s="81" t="n"/>
+      <c r="EL357" s="81" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B358" s="81" t="inlineStr">
+        <is>
+          <t>Roar</t>
+        </is>
+      </c>
+      <c r="C358" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D358" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E358" s="81">
+        <f>ROUND('Towers'!$C$21*POWER('Tuning'!$B$12,D358),0)</f>
+        <v/>
+      </c>
+      <c r="F358" s="81">
+        <f>F357+E358</f>
+        <v/>
+      </c>
+      <c r="G358" s="110" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H358" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I358" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J358" s="81">
+        <f>'Towers'!$G$21*G358*H358*I358</f>
+        <v/>
+      </c>
+      <c r="K358" s="81">
+        <f>IF(J358=0,0,F358/J358)</f>
+        <v/>
+      </c>
+      <c r="L358" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M358" s="81" t="inlineStr">
+        <is>
+          <t>Thunder Roar</t>
+        </is>
+      </c>
+      <c r="N358" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BJ358" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="DN358" s="81" t="n"/>
+      <c r="DP358" s="81" t="n"/>
+      <c r="DR358" s="81" t="n"/>
+      <c r="EL358" s="81" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B359" s="81" t="inlineStr">
+        <is>
+          <t>Roar</t>
+        </is>
+      </c>
+      <c r="C359" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D359" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E359" s="81">
+        <f>ROUND('Towers'!$C$21*POWER('Tuning'!$B$12,D359),0)</f>
+        <v/>
+      </c>
+      <c r="F359" s="81">
+        <f>F358+E359</f>
+        <v/>
+      </c>
+      <c r="G359" s="110" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H359" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I359" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J359" s="81">
+        <f>J358*G359*H359*I359</f>
+        <v/>
+      </c>
+      <c r="K359" s="81">
+        <f>IF(J359=0,0,F359/J359)</f>
+        <v/>
+      </c>
+      <c r="L359" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M359" s="81" t="inlineStr">
+        <is>
+          <t>Echo Roar</t>
+        </is>
+      </c>
+      <c r="N359" s="81" t="n"/>
+      <c r="CI359" s="81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ359" s="81" t="inlineStr">
+        <is>
+          <t>The roar hits twice</t>
+        </is>
+      </c>
+      <c r="EM359" s="81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B360" s="81" t="inlineStr">
+        <is>
+          <t>Roar</t>
+        </is>
+      </c>
+      <c r="C360" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D360" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E360" s="81">
+        <f>ROUND('Towers'!$C$21*POWER('Tuning'!$B$12,D360),0)</f>
+        <v/>
+      </c>
+      <c r="F360" s="81">
+        <f>F359+E360</f>
+        <v/>
+      </c>
+      <c r="G360" s="110" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H360" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I360" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J360" s="81">
+        <f>J359*G360*H360*I360</f>
+        <v/>
+      </c>
+      <c r="K360" s="81">
+        <f>IF(J360=0,0,F360/J360)</f>
+        <v/>
+      </c>
+      <c r="L360" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M360" s="81" t="inlineStr">
+        <is>
+          <t>Ancient Roar</t>
+        </is>
+      </c>
+      <c r="CI360" s="81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ360" s="81" t="inlineStr">
+        <is>
+          <t>The roar reaches your whole track</t>
+        </is>
+      </c>
+      <c r="EA360" s="81" t="n"/>
+      <c r="EN360" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B361" s="81" t="inlineStr">
+        <is>
+          <t>Ancestors</t>
+        </is>
+      </c>
+      <c r="C361" s="81" t="inlineStr">
+        <is>
+          <t>buffs</t>
+        </is>
+      </c>
+      <c r="D361" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E361" s="81">
+        <f>ROUND('Towers'!$C$21*POWER('Tuning'!$B$12,D361),0)</f>
+        <v/>
+      </c>
+      <c r="F361" s="81">
+        <f>'Towers'!$C$21+E361</f>
+        <v/>
+      </c>
+      <c r="G361" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H361" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I361" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J361" s="81">
+        <f>'Towers'!$G$21*G361*H361*I361</f>
+        <v/>
+      </c>
+      <c r="K361" s="81">
+        <f>IF(J361=0,0,F361/J361)</f>
+        <v/>
+      </c>
+      <c r="L361" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M361" s="81" t="inlineStr">
+        <is>
+          <t>Old Bones</t>
+        </is>
+      </c>
+      <c r="EU361" s="81" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B362" s="81" t="inlineStr">
+        <is>
+          <t>Ancestors</t>
+        </is>
+      </c>
+      <c r="C362" s="81" t="inlineStr">
+        <is>
+          <t>buffs</t>
+        </is>
+      </c>
+      <c r="D362" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E362" s="81">
+        <f>ROUND('Towers'!$C$21*POWER('Tuning'!$B$12,D362),0)</f>
+        <v/>
+      </c>
+      <c r="F362" s="81">
+        <f>F361+E362</f>
+        <v/>
+      </c>
+      <c r="G362" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H362" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I362" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J362" s="81">
+        <f>'Towers'!$G$21*G362*H362*I362</f>
+        <v/>
+      </c>
+      <c r="K362" s="81">
+        <f>IF(J362=0,0,F362/J362)</f>
+        <v/>
+      </c>
+      <c r="L362" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M362" s="81" t="inlineStr">
+        <is>
+          <t>Shared Charge</t>
+        </is>
+      </c>
+      <c r="DO362" s="81" t="n"/>
+      <c r="DQ362" s="81" t="n"/>
+      <c r="EI362" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="EU362" s="81" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B363" s="81" t="inlineStr">
+        <is>
+          <t>Ancestors</t>
+        </is>
+      </c>
+      <c r="C363" s="81" t="inlineStr">
+        <is>
+          <t>buffs</t>
+        </is>
+      </c>
+      <c r="D363" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E363" s="81">
+        <f>ROUND('Towers'!$C$21*POWER('Tuning'!$B$12,D363),0)</f>
+        <v/>
+      </c>
+      <c r="F363" s="81">
+        <f>F362+E363</f>
+        <v/>
+      </c>
+      <c r="G363" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H363" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I363" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J363" s="81">
+        <f>'Towers'!$G$21*G363*H363*I363</f>
+        <v/>
+      </c>
+      <c r="K363" s="81">
+        <f>IF(J363=0,0,F363/J363)</f>
+        <v/>
+      </c>
+      <c r="L363" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M363" s="81" t="inlineStr">
+        <is>
+          <t>Spirit Guard</t>
+        </is>
+      </c>
+      <c r="BJ363" s="81" t="n"/>
+      <c r="DO363" s="81" t="n"/>
+      <c r="DQ363" s="81" t="n"/>
+      <c r="DS363" s="81" t="n"/>
+      <c r="DZ363" s="81" t="n"/>
+      <c r="EI363" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="EP363" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="EU363" s="81" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B364" s="81" t="inlineStr">
+        <is>
+          <t>Ancestors</t>
+        </is>
+      </c>
+      <c r="C364" s="81" t="inlineStr">
+        <is>
+          <t>buffs</t>
+        </is>
+      </c>
+      <c r="D364" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E364" s="81">
+        <f>ROUND('Towers'!$C$21*POWER('Tuning'!$B$12,D364),0)</f>
+        <v/>
+      </c>
+      <c r="F364" s="81">
+        <f>F363+E364</f>
+        <v/>
+      </c>
+      <c r="G364" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H364" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I364" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J364" s="81">
+        <f>J363*G364*H364*I364</f>
+        <v/>
+      </c>
+      <c r="K364" s="81">
+        <f>IF(J364=0,0,F364/J364)</f>
+        <v/>
+      </c>
+      <c r="L364" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M364" s="81" t="inlineStr">
+        <is>
+          <t>War Paint</t>
+        </is>
+      </c>
+      <c r="BJ364" s="81" t="n"/>
+      <c r="CI364" s="81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ364" s="81" t="inlineStr">
+        <is>
+          <t>Hunters nearby +15% for 6 s when full</t>
+        </is>
+      </c>
+      <c r="EG364" s="81" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B365" s="81" t="inlineStr">
+        <is>
+          <t>Ancestors</t>
+        </is>
+      </c>
+      <c r="C365" s="81" t="inlineStr">
+        <is>
+          <t>buffs</t>
+        </is>
+      </c>
+      <c r="D365" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E365" s="81">
+        <f>ROUND('Towers'!$C$21*POWER('Tuning'!$B$12,D365),0)</f>
+        <v/>
+      </c>
+      <c r="F365" s="81">
+        <f>F364+E365</f>
+        <v/>
+      </c>
+      <c r="G365" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H365" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I365" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J365" s="81">
+        <f>J364*G365*H365*I365</f>
+        <v/>
+      </c>
+      <c r="K365" s="81">
+        <f>IF(J365=0,0,F365/J365)</f>
+        <v/>
+      </c>
+      <c r="L365" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M365" s="81" t="inlineStr">
+        <is>
+          <t>Spirit Hunters</t>
+        </is>
+      </c>
+      <c r="BJ365" s="81" t="n"/>
+      <c r="CI365" s="81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ365" s="81" t="inlineStr">
+        <is>
+          <t>3 ghost hunters fire for 6 s when full</t>
+        </is>
+      </c>
+      <c r="DO365" s="81" t="n"/>
+      <c r="DQ365" s="81" t="n"/>
+      <c r="EQ365" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B366" s="81" t="inlineStr">
+        <is>
+          <t>Bone Pile</t>
+        </is>
+      </c>
+      <c r="C366" s="81" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D366" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E366" s="81">
+        <f>ROUND('Towers'!$C$21*POWER('Tuning'!$B$12,D366),0)</f>
+        <v/>
+      </c>
+      <c r="F366" s="81">
+        <f>'Towers'!$C$21+E366</f>
+        <v/>
+      </c>
+      <c r="G366" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H366" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I366" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J366" s="81">
+        <f>'Towers'!$G$21*G366*H366*I366</f>
+        <v/>
+      </c>
+      <c r="K366" s="81">
+        <f>IF(J366=0,0,F366/J366)</f>
+        <v/>
+      </c>
+      <c r="L366" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M366" s="81" t="inlineStr">
+        <is>
+          <t>Bone Collector</t>
+        </is>
+      </c>
+      <c r="DV366" s="81" t="n"/>
+      <c r="EX366" s="81" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B367" s="81" t="inlineStr">
+        <is>
+          <t>Bone Pile</t>
+        </is>
+      </c>
+      <c r="C367" s="81" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D367" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E367" s="81">
+        <f>ROUND('Towers'!$C$21*POWER('Tuning'!$B$12,D367),0)</f>
+        <v/>
+      </c>
+      <c r="F367" s="81">
+        <f>F366+E367</f>
+        <v/>
+      </c>
+      <c r="G367" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H367" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I367" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J367" s="81">
+        <f>'Towers'!$G$21*G367*H367*I367</f>
+        <v/>
+      </c>
+      <c r="K367" s="81">
+        <f>IF(J367=0,0,F367/J367)</f>
+        <v/>
+      </c>
+      <c r="L367" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M367" s="81" t="inlineStr">
+        <is>
+          <t>Trade Post</t>
+        </is>
+      </c>
+      <c r="AE367" s="81" t="n"/>
+      <c r="AF367" s="81" t="n"/>
+      <c r="DV367" s="81" t="n"/>
+      <c r="EX367" s="81" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B368" s="81" t="inlineStr">
+        <is>
+          <t>Bone Pile</t>
+        </is>
+      </c>
+      <c r="C368" s="81" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D368" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E368" s="81">
+        <f>ROUND('Towers'!$C$21*POWER('Tuning'!$B$12,D368),0)</f>
+        <v/>
+      </c>
+      <c r="F368" s="81">
+        <f>F367+E368</f>
+        <v/>
+      </c>
+      <c r="G368" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H368" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I368" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J368" s="81">
+        <f>'Towers'!$G$21*G368*H368*I368</f>
+        <v/>
+      </c>
+      <c r="K368" s="81">
+        <f>IF(J368=0,0,F368/J368)</f>
+        <v/>
+      </c>
+      <c r="L368" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M368" s="81" t="inlineStr">
+        <is>
+          <t>Bone Market</t>
+        </is>
+      </c>
+      <c r="AE368" s="81" t="n"/>
+      <c r="AF368" s="81" t="n"/>
+      <c r="BY368" s="81" t="n"/>
+      <c r="DN368" s="81" t="n"/>
+      <c r="DV368" s="81" t="n"/>
+      <c r="ER368" s="81" t="n">
+        <v>400</v>
+      </c>
+      <c r="EX368" s="81" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B369" s="81" t="inlineStr">
+        <is>
+          <t>Bone Pile</t>
+        </is>
+      </c>
+      <c r="C369" s="81" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D369" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E369" s="81">
+        <f>ROUND('Towers'!$C$21*POWER('Tuning'!$B$12,D369),0)</f>
+        <v/>
+      </c>
+      <c r="F369" s="81">
+        <f>F368+E369</f>
+        <v/>
+      </c>
+      <c r="G369" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H369" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I369" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J369" s="81">
+        <f>J368*G369*H369*I369</f>
+        <v/>
+      </c>
+      <c r="K369" s="81">
+        <f>IF(J369=0,0,F369/J369)</f>
+        <v/>
+      </c>
+      <c r="L369" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M369" s="81" t="inlineStr">
+        <is>
+          <t>Rare Bones</t>
+        </is>
+      </c>
+      <c r="CI369" s="81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ369" s="81" t="inlineStr">
+        <is>
+          <t>Bosses fill half the charge</t>
+        </is>
+      </c>
+      <c r="DR369" s="81" t="n"/>
+      <c r="DX369" s="81" t="n"/>
+      <c r="EJ369" s="81" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B370" s="81" t="inlineStr">
+        <is>
+          <t>Bone Pile</t>
+        </is>
+      </c>
+      <c r="C370" s="81" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D370" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E370" s="81">
+        <f>ROUND('Towers'!$C$21*POWER('Tuning'!$B$12,D370),0)</f>
+        <v/>
+      </c>
+      <c r="F370" s="81">
+        <f>F369+E370</f>
+        <v/>
+      </c>
+      <c r="G370" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H370" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I370" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J370" s="81">
+        <f>J369*G370*H370*I370</f>
+        <v/>
+      </c>
+      <c r="K370" s="81">
+        <f>IF(J370=0,0,F370/J370)</f>
+        <v/>
+      </c>
+      <c r="L370" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M370" s="81" t="inlineStr">
+        <is>
+          <t>Camp Payday</t>
+        </is>
+      </c>
+      <c r="CI370" s="81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ370" s="81" t="inlineStr">
+        <is>
+          <t>Every hunter in your camp gets paid</t>
+        </is>
+      </c>
+      <c r="EB370" s="81" t="n"/>
+      <c r="ES370" s="81" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B371" s="81" t="inlineStr">
+        <is>
+          <t>Roar</t>
+        </is>
+      </c>
+      <c r="C371" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D371" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E371" s="81">
+        <f>E359</f>
+        <v/>
+      </c>
+      <c r="F371" s="81">
+        <f>F359</f>
+        <v/>
+      </c>
+      <c r="G371" s="110" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H371" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I371" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L371" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M371" s="81" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+      <c r="W371" s="81" t="n">
+        <v>8</v>
+      </c>
+      <c r="CI371" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ371" s="81" t="inlineStr">
+        <is>
+          <t>The roar scares small dinos 8 studs back</t>
+        </is>
+      </c>
+      <c r="DU371" s="81" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B372" s="81" t="inlineStr">
+        <is>
+          <t>Roar</t>
+        </is>
+      </c>
+      <c r="C372" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D372" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E372" s="81">
+        <f>E359</f>
+        <v/>
+      </c>
+      <c r="F372" s="81">
+        <f>F359</f>
+        <v/>
+      </c>
+      <c r="G372" s="110" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H372" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I372" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L372" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M372" s="81" t="inlineStr">
+        <is>
+          <t>Shatter Roar</t>
+        </is>
+      </c>
+      <c r="AM372" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BU372" s="81" t="n"/>
+      <c r="CI372" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ372" s="81" t="inlineStr">
+        <is>
+          <t>The roar strips armour for 4 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B373" s="81" t="inlineStr">
+        <is>
+          <t>Roar</t>
+        </is>
+      </c>
+      <c r="C373" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D373" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E373" s="81">
+        <f>E360</f>
+        <v/>
+      </c>
+      <c r="F373" s="81">
+        <f>F360</f>
+        <v/>
+      </c>
+      <c r="G373" s="110" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H373" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I373" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L373" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M373" s="81" t="inlineStr">
+        <is>
+          <t>Skull Storm</t>
+        </is>
+      </c>
+      <c r="CI373" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ373" s="81" t="inlineStr">
+        <is>
+          <t>8 flying skulls hunt dinos</t>
+        </is>
+      </c>
+      <c r="DY373" s="81" t="n"/>
+      <c r="EO373" s="81" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B374" s="81" t="inlineStr">
+        <is>
+          <t>Roar</t>
+        </is>
+      </c>
+      <c r="C374" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D374" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E374" s="81">
+        <f>E360</f>
+        <v/>
+      </c>
+      <c r="F374" s="81">
+        <f>F360</f>
+        <v/>
+      </c>
+      <c r="G374" s="110" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H374" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I374" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L374" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M374" s="81" t="inlineStr">
+        <is>
+          <t>Finishing Roar</t>
+        </is>
+      </c>
+      <c r="CI374" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ374" s="81" t="inlineStr">
+        <is>
+          <t>A free roar at a weak boss</t>
+        </is>
+      </c>
+      <c r="DW374" s="81" t="n"/>
+      <c r="EZ374" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B375" s="81" t="inlineStr">
+        <is>
+          <t>Ancestors</t>
+        </is>
+      </c>
+      <c r="C375" s="81" t="inlineStr">
+        <is>
+          <t>buffs</t>
+        </is>
+      </c>
+      <c r="D375" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E375" s="81">
+        <f>E364</f>
+        <v/>
+      </c>
+      <c r="F375" s="81">
+        <f>F364</f>
+        <v/>
+      </c>
+      <c r="G375" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H375" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I375" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L375" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M375" s="81" t="inlineStr">
+        <is>
+          <t>Bone Armour</t>
+        </is>
+      </c>
+      <c r="P375" s="81" t="n"/>
+      <c r="BH375" s="81" t="n">
+        <v>20</v>
+      </c>
+      <c r="CI375" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ375" s="81" t="inlineStr">
+        <is>
+          <t>Nearby towers get 20% more HP</t>
+        </is>
+      </c>
+      <c r="DT375" s="81" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B376" s="81" t="inlineStr">
+        <is>
+          <t>Ancestors</t>
+        </is>
+      </c>
+      <c r="C376" s="81" t="inlineStr">
+        <is>
+          <t>buffs</t>
+        </is>
+      </c>
+      <c r="D376" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E376" s="81">
+        <f>E364</f>
+        <v/>
+      </c>
+      <c r="F376" s="81">
+        <f>F364</f>
+        <v/>
+      </c>
+      <c r="G376" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H376" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I376" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L376" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M376" s="81" t="inlineStr">
+        <is>
+          <t>Ancestor's Eye</t>
+        </is>
+      </c>
+      <c r="T376" s="81" t="n"/>
+      <c r="CI376" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ376" s="81" t="inlineStr">
+        <is>
+          <t>Nearby towers see 10% further</t>
+        </is>
+      </c>
+      <c r="FA376" s="81" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B377" s="81" t="inlineStr">
+        <is>
+          <t>Ancestors</t>
+        </is>
+      </c>
+      <c r="C377" s="81" t="inlineStr">
+        <is>
+          <t>buffs</t>
+        </is>
+      </c>
+      <c r="D377" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E377" s="81">
+        <f>E365</f>
+        <v/>
+      </c>
+      <c r="F377" s="81">
+        <f>F365</f>
+        <v/>
+      </c>
+      <c r="G377" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H377" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I377" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L377" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M377" s="81" t="inlineStr">
+        <is>
+          <t>Totem Pole</t>
+        </is>
+      </c>
+      <c r="U377" s="81" t="n"/>
+      <c r="CI377" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ377" s="81" t="inlineStr">
+        <is>
+          <t>Buffs reach every tower, half strength</t>
+        </is>
+      </c>
+      <c r="DO377" s="81" t="n"/>
+      <c r="ED377" s="81" t="n"/>
+      <c r="EU377" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="EW377" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B378" s="81" t="inlineStr">
+        <is>
+          <t>Ancestors</t>
+        </is>
+      </c>
+      <c r="C378" s="81" t="inlineStr">
+        <is>
+          <t>buffs</t>
+        </is>
+      </c>
+      <c r="D378" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E378" s="81">
+        <f>E365</f>
+        <v/>
+      </c>
+      <c r="F378" s="81">
+        <f>F365</f>
+        <v/>
+      </c>
+      <c r="G378" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H378" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I378" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L378" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M378" s="81" t="inlineStr">
+        <is>
+          <t>Elder Wisdom</t>
+        </is>
+      </c>
+      <c r="CI378" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ378" s="81" t="inlineStr">
+        <is>
+          <t>Hero abilities nearby recharge 25% faster</t>
+        </is>
+      </c>
+      <c r="EE378" s="81" t="n"/>
+      <c r="EV378" s="81" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B379" s="81" t="inlineStr">
+        <is>
+          <t>Bone Pile</t>
+        </is>
+      </c>
+      <c r="C379" s="81" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D379" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E379" s="81">
+        <f>E369</f>
+        <v/>
+      </c>
+      <c r="F379" s="81">
+        <f>F369</f>
+        <v/>
+      </c>
+      <c r="G379" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H379" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I379" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L379" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M379" s="81" t="inlineStr">
+        <is>
+          <t>Bone Bank</t>
+        </is>
+      </c>
+      <c r="CI379" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ379" s="81" t="inlineStr">
+        <is>
+          <t>Leftover charge pays at round end</t>
+        </is>
+      </c>
+      <c r="EC379" s="81" t="n"/>
+      <c r="EY379" s="81" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B380" s="81" t="inlineStr">
+        <is>
+          <t>Bone Pile</t>
+        </is>
+      </c>
+      <c r="C380" s="81" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D380" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E380" s="81">
+        <f>E369</f>
+        <v/>
+      </c>
+      <c r="F380" s="81">
+        <f>F369</f>
+        <v/>
+      </c>
+      <c r="G380" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H380" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I380" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L380" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M380" s="81" t="inlineStr">
+        <is>
+          <t>Bone Bonus</t>
+        </is>
+      </c>
+      <c r="BY380" s="81" t="n"/>
+      <c r="CI380" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ380" s="81" t="inlineStr">
+        <is>
+          <t>Each full charge pays 40% more</t>
+        </is>
+      </c>
+      <c r="DP380" s="81" t="n"/>
+      <c r="ER380" s="81" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B381" s="81" t="inlineStr">
+        <is>
+          <t>Bone Pile</t>
+        </is>
+      </c>
+      <c r="C381" s="81" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D381" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E381" s="81">
+        <f>E370</f>
+        <v/>
+      </c>
+      <c r="F381" s="81">
+        <f>F370</f>
+        <v/>
+      </c>
+      <c r="G381" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H381" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I381" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L381" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M381" s="81" t="inlineStr">
+        <is>
+          <t>Bounty Wall</t>
+        </is>
+      </c>
+      <c r="CI381" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ381" s="81" t="inlineStr">
+        <is>
+          <t>Bones nearby charge 25% faster and count +25% for bounties</t>
+        </is>
+      </c>
+      <c r="DN381" s="81" t="n"/>
+      <c r="EG381" s="81" t="n"/>
+      <c r="EH381" s="81" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="EK381" s="81" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="81" t="inlineStr">
+        <is>
+          <t>Bone Totem</t>
+        </is>
+      </c>
+      <c r="B382" s="81" t="inlineStr">
+        <is>
+          <t>Bone Pile</t>
+        </is>
+      </c>
+      <c r="C382" s="81" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D382" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E382" s="81">
+        <f>E370</f>
+        <v/>
+      </c>
+      <c r="F382" s="81">
+        <f>F370</f>
+        <v/>
+      </c>
+      <c r="G382" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H382" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I382" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L382" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M382" s="81" t="inlineStr">
+        <is>
+          <t>Ancient Treasure</t>
+        </is>
+      </c>
+      <c r="BJ382" s="81" t="n"/>
+      <c r="CI382" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ382" s="81" t="inlineStr">
+        <is>
+          <t>One big treasure chest a match</t>
+        </is>
+      </c>
+      <c r="CK382" s="81" t="n"/>
+      <c r="CL382" s="81" t="n"/>
+      <c r="CM382" s="81" t="n"/>
+      <c r="CN382" s="81" t="n"/>
+      <c r="EF382" s="81" t="n"/>
+      <c r="ET382" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -10178,7 +10178,6 @@
       </c>
       <c r="E38" s="17" t="n"/>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="31" t="inlineStr">
         <is>
@@ -10249,7 +10248,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="31" t="inlineStr">
         <is>
@@ -10400,7 +10398,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
         <is>
@@ -10451,7 +10448,6 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="31" t="inlineStr">
         <is>
@@ -10522,7 +10518,6 @@
         </is>
       </c>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
@@ -10573,7 +10568,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
@@ -10764,7 +10758,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
@@ -10912,7 +10905,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" s="31" t="inlineStr">
         <is>
@@ -11020,7 +11012,6 @@
         </is>
       </c>
     </row>
-    <row r="93"/>
     <row r="94" s="90">
       <c r="A94" s="31" t="inlineStr">
         <is>
@@ -11048,7 +11039,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="31" t="inlineStr">
         <is>
@@ -11076,7 +11066,6 @@
         </is>
       </c>
     </row>
-    <row r="99"/>
     <row r="100">
       <c r="A100" s="99" t="inlineStr">
         <is>
@@ -11124,7 +11113,6 @@
         </is>
       </c>
     </row>
-    <row r="103"/>
     <row r="104">
       <c r="A104" s="99" t="inlineStr">
         <is>
@@ -11215,7 +11203,6 @@
         </is>
       </c>
     </row>
-    <row r="109"/>
     <row r="110">
       <c r="A110" s="99" t="inlineStr">
         <is>
@@ -11398,7 +11385,6 @@
         </is>
       </c>
     </row>
-    <row r="123"/>
     <row r="124">
       <c r="A124" s="99" t="inlineStr">
         <is>
@@ -11452,7 +11438,6 @@
         </is>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="A129" s="99" t="inlineStr">
         <is>
@@ -11592,7 +11577,6 @@
         </is>
       </c>
     </row>
-    <row r="140"/>
     <row r="141">
       <c r="A141" s="99" t="inlineStr">
         <is>
@@ -12335,7 +12319,6 @@
         </is>
       </c>
     </row>
-    <row r="191"/>
     <row r="192">
       <c r="A192" s="81" t="inlineStr">
         <is>
@@ -12448,7 +12431,6 @@
         </is>
       </c>
     </row>
-    <row r="200"/>
     <row r="201">
       <c r="A201" s="81" t="inlineStr">
         <is>
@@ -12853,7 +12835,6 @@
         </is>
       </c>
     </row>
-    <row r="229"/>
     <row r="230">
       <c r="A230" s="81" t="inlineStr">
         <is>
@@ -12868,7 +12849,7 @@
         </is>
       </c>
       <c r="B231" s="81" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C231" s="81" t="inlineStr">
         <is>
@@ -12958,7 +12939,7 @@
         </is>
       </c>
       <c r="B237" s="81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C237" s="81" t="inlineStr">
         <is>
@@ -14204,7 +14185,7 @@
         </is>
       </c>
       <c r="C21" s="81" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="D21" s="81" t="n">
         <v>60</v>
@@ -42322,7 +42303,7 @@
       </c>
       <c r="DV366" s="81" t="n"/>
       <c r="EX366" s="81" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="367">
@@ -42381,7 +42362,7 @@
       <c r="AF367" s="81" t="n"/>
       <c r="DV367" s="81" t="n"/>
       <c r="EX367" s="81" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="368">
@@ -42442,10 +42423,10 @@
       <c r="DN368" s="81" t="n"/>
       <c r="DV368" s="81" t="n"/>
       <c r="ER368" s="81" t="n">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="EX368" s="81" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="369">
@@ -43183,7 +43164,7 @@
       </c>
       <c r="DP380" s="81" t="n"/>
       <c r="ER380" s="81" t="n">
-        <v>560</v>
+        <v>168</v>
       </c>
     </row>
     <row r="381">

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9500,7 +9500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E242"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -13019,6 +13019,118 @@
       <c r="C242" s="81" t="inlineStr">
         <is>
           <t>Ancient Treasure: the first full charge of the match also drops a chest worth this</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>SPOTTER BLIMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Blimp speed (studs/s)</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>40</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>the blimp's flying speed along its side's track (x Blimp speed x); a lap = spawn end to exit end and back (Shared/Blimp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Paratrooper HP</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>80</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>a Paratroopers ranger's HP (the 9g walker, fight mode)</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Paratrooper damage</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>40</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>a paratrooper's shot (x the team's level)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Paratrooper rate</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>shots a second per paratrooper</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Paratrooper reach</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>14</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>studs: paratroopers hunt dinos within this of where they land</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Paratrooper speed</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>14</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>studs/s a paratrooper walks</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Hook max sizes</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>2</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Sky Hook takes only a non-boss dino with at most this many sizes left</t>
         </is>
       </c>
     </row>
@@ -13042,7 +13154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -14241,6 +14353,78 @@
       </c>
       <c r="Z21" s="81" t="n"/>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Flies your track: a door gun, a searchlight or cargo</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>600</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <f>D22*E22*F22</f>
+        <v/>
+      </c>
+      <c r="H22" t="n">
+        <v>14</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Its mooring mast is placed like any tower; the blimp flies your track there and back. Can't be damaged (#148).</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>400</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>BLIMP</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -14261,7 +14445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FA382"/>
+  <dimension ref="A1:FM409"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -15184,6 +15368,61 @@
       <c r="FA4" s="81" t="inlineStr">
         <is>
           <t>Aura range %</t>
+        </is>
+      </c>
+      <c r="FB4" t="inlineStr">
+        <is>
+          <t>Blimp speed x</t>
+        </is>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t>Lap chests</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr">
+        <is>
+          <t>Lap repairs</t>
+        </is>
+      </c>
+      <c r="FE4" t="inlineStr">
+        <is>
+          <t>Crate heal %</t>
+        </is>
+      </c>
+      <c r="FF4" t="inlineStr">
+        <is>
+          <t>Paratroopers</t>
+        </is>
+      </c>
+      <c r="FG4" t="inlineStr">
+        <is>
+          <t>Airlift</t>
+        </is>
+      </c>
+      <c r="FH4" t="inlineStr">
+        <is>
+          <t>Throw miss %</t>
+        </is>
+      </c>
+      <c r="FI4" t="inlineStr">
+        <is>
+          <t>Aura reach x</t>
+        </is>
+      </c>
+      <c r="FJ4" t="inlineStr">
+        <is>
+          <t>Dino outlines</t>
+        </is>
+      </c>
+      <c r="FK4" t="inlineStr">
+        <is>
+          <t>Bombing run</t>
+        </is>
+      </c>
+      <c r="FL4" t="inlineStr">
+        <is>
+          <t>Hook every (s)</t>
         </is>
       </c>
     </row>
@@ -43291,6 +43530,1671 @@
       <c r="CN382" s="81" t="n"/>
       <c r="EF382" s="81" t="n"/>
       <c r="ET382" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Door Gun</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>1</v>
+      </c>
+      <c r="E383">
+        <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D383),0)</f>
+        <v/>
+      </c>
+      <c r="F383">
+        <f>'Towers'!$C$22+E383</f>
+        <v/>
+      </c>
+      <c r="G383" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H383" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I383" t="n">
+        <v>1</v>
+      </c>
+      <c r="J383">
+        <f>'Towers'!$G$22*G383*H383*I383</f>
+        <v/>
+      </c>
+      <c r="K383">
+        <f>IF(J383=0,0,F383/J383)</f>
+        <v/>
+      </c>
+      <c r="L383" t="n">
+        <v>1</v>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>Belt Gun</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Door Gun</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>2</v>
+      </c>
+      <c r="E384">
+        <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D384),0)</f>
+        <v/>
+      </c>
+      <c r="F384">
+        <f>F383+E384</f>
+        <v/>
+      </c>
+      <c r="G384" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H384" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I384" t="n">
+        <v>1</v>
+      </c>
+      <c r="J384">
+        <f>'Towers'!$G$22*G384*H384*I384</f>
+        <v/>
+      </c>
+      <c r="K384">
+        <f>IF(J384=0,0,F384/J384)</f>
+        <v/>
+      </c>
+      <c r="L384" t="n">
+        <v>1</v>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Twin Mount</t>
+        </is>
+      </c>
+      <c r="Q384" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Door Gun</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>3</v>
+      </c>
+      <c r="E385">
+        <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D385),0)</f>
+        <v/>
+      </c>
+      <c r="F385">
+        <f>F384+E385</f>
+        <v/>
+      </c>
+      <c r="G385" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H385" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I385" t="n">
+        <v>1</v>
+      </c>
+      <c r="J385">
+        <f>'Towers'!$G$22*G385*H385*I385</f>
+        <v/>
+      </c>
+      <c r="K385">
+        <f>IF(J385=0,0,F385/J385)</f>
+        <v/>
+      </c>
+      <c r="L385" t="n">
+        <v>1</v>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Strafing Run</t>
+        </is>
+      </c>
+      <c r="Q385" t="n">
+        <v>2</v>
+      </c>
+      <c r="R385" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Door Gun</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>4</v>
+      </c>
+      <c r="E386">
+        <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D386),0)</f>
+        <v/>
+      </c>
+      <c r="F386">
+        <f>F385+E386</f>
+        <v/>
+      </c>
+      <c r="G386" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H386" t="n">
+        <v>1</v>
+      </c>
+      <c r="I386" t="n">
+        <v>1</v>
+      </c>
+      <c r="J386">
+        <f>J385*G386*H386*I386</f>
+        <v/>
+      </c>
+      <c r="K386">
+        <f>IF(J386=0,0,F386/J386)</f>
+        <v/>
+      </c>
+      <c r="L386" t="n">
+        <v>1</v>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Heavy Mount</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BJ386" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI386" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ386" t="inlineStr">
+        <is>
+          <t>Shoots through armour, breaks 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Door Gun</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>5</v>
+      </c>
+      <c r="E387">
+        <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D387),0)</f>
+        <v/>
+      </c>
+      <c r="F387">
+        <f>F386+E387</f>
+        <v/>
+      </c>
+      <c r="G387" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H387" t="n">
+        <v>1</v>
+      </c>
+      <c r="I387" t="n">
+        <v>1</v>
+      </c>
+      <c r="J387">
+        <f>J386*G387*H387*I387</f>
+        <v/>
+      </c>
+      <c r="K387">
+        <f>IF(J387=0,0,F387/J387)</f>
+        <v/>
+      </c>
+      <c r="L387" t="n">
+        <v>1</v>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>Gunship</t>
+        </is>
+      </c>
+      <c r="Q387" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z387" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA387" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI387" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ387" t="inlineStr">
+        <is>
+          <t>Faster, four guns and rockets</t>
+        </is>
+      </c>
+      <c r="FB387" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Searchlight</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>1</v>
+      </c>
+      <c r="E388">
+        <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D388),0)</f>
+        <v/>
+      </c>
+      <c r="F388">
+        <f>'Towers'!$C$22+E388</f>
+        <v/>
+      </c>
+      <c r="G388" t="n">
+        <v>1</v>
+      </c>
+      <c r="H388" t="n">
+        <v>1</v>
+      </c>
+      <c r="I388" t="n">
+        <v>1</v>
+      </c>
+      <c r="J388">
+        <f>'Towers'!$G$22*G388*H388*I388</f>
+        <v/>
+      </c>
+      <c r="K388">
+        <f>IF(J388=0,0,F388/J388)</f>
+        <v/>
+      </c>
+      <c r="L388" t="n">
+        <v>1</v>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>Spotlight</t>
+        </is>
+      </c>
+      <c r="AL388" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Searchlight</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>2</v>
+      </c>
+      <c r="E389">
+        <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D389),0)</f>
+        <v/>
+      </c>
+      <c r="F389">
+        <f>F388+E389</f>
+        <v/>
+      </c>
+      <c r="G389" t="n">
+        <v>1</v>
+      </c>
+      <c r="H389" t="n">
+        <v>1</v>
+      </c>
+      <c r="I389" t="n">
+        <v>1</v>
+      </c>
+      <c r="J389">
+        <f>'Towers'!$G$22*G389*H389*I389</f>
+        <v/>
+      </c>
+      <c r="K389">
+        <f>IF(J389=0,0,F389/J389)</f>
+        <v/>
+      </c>
+      <c r="L389" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>Wide Beam</t>
+        </is>
+      </c>
+      <c r="AL389" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Searchlight</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>3</v>
+      </c>
+      <c r="E390">
+        <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D390),0)</f>
+        <v/>
+      </c>
+      <c r="F390">
+        <f>F389+E390</f>
+        <v/>
+      </c>
+      <c r="G390" t="n">
+        <v>1</v>
+      </c>
+      <c r="H390" t="n">
+        <v>1</v>
+      </c>
+      <c r="I390" t="n">
+        <v>1</v>
+      </c>
+      <c r="J390">
+        <f>'Towers'!$G$22*G390*H390*I390</f>
+        <v/>
+      </c>
+      <c r="K390">
+        <f>IF(J390=0,0,F390/J390)</f>
+        <v/>
+      </c>
+      <c r="L390" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>Night Hunt</t>
+        </is>
+      </c>
+      <c r="AL390" t="n">
+        <v>10</v>
+      </c>
+      <c r="FA390" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Searchlight</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>4</v>
+      </c>
+      <c r="E391">
+        <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D391),0)</f>
+        <v/>
+      </c>
+      <c r="F391">
+        <f>F390+E391</f>
+        <v/>
+      </c>
+      <c r="G391" t="n">
+        <v>1</v>
+      </c>
+      <c r="H391" t="n">
+        <v>1</v>
+      </c>
+      <c r="I391" t="n">
+        <v>1</v>
+      </c>
+      <c r="J391">
+        <f>J390*G391*H391*I391</f>
+        <v/>
+      </c>
+      <c r="K391">
+        <f>IF(J391=0,0,F391/J391)</f>
+        <v/>
+      </c>
+      <c r="L391" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>Floodlights</t>
+        </is>
+      </c>
+      <c r="CI391" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ391" t="inlineStr">
+        <is>
+          <t>Lights a much wider circle</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Searchlight</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>5</v>
+      </c>
+      <c r="E392">
+        <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D392),0)</f>
+        <v/>
+      </c>
+      <c r="F392">
+        <f>F391+E392</f>
+        <v/>
+      </c>
+      <c r="G392" t="n">
+        <v>1</v>
+      </c>
+      <c r="H392" t="n">
+        <v>1</v>
+      </c>
+      <c r="I392" t="n">
+        <v>1</v>
+      </c>
+      <c r="J392">
+        <f>J391*G392*H392*I392</f>
+        <v/>
+      </c>
+      <c r="K392">
+        <f>IF(J392=0,0,F392/J392)</f>
+        <v/>
+      </c>
+      <c r="L392" t="n">
+        <v>1</v>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>All-Seeing Eye</t>
+        </is>
+      </c>
+      <c r="AL392" t="n">
+        <v>25</v>
+      </c>
+      <c r="CI392" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ392" t="inlineStr">
+        <is>
+          <t>Every dino under the blimp marked +25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>1</v>
+      </c>
+      <c r="E393">
+        <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D393),0)</f>
+        <v/>
+      </c>
+      <c r="F393">
+        <f>'Towers'!$C$22+E393</f>
+        <v/>
+      </c>
+      <c r="G393" t="n">
+        <v>1</v>
+      </c>
+      <c r="H393" t="n">
+        <v>1</v>
+      </c>
+      <c r="I393" t="n">
+        <v>1</v>
+      </c>
+      <c r="J393">
+        <f>'Towers'!$G$22*G393*H393*I393</f>
+        <v/>
+      </c>
+      <c r="K393">
+        <f>IF(J393=0,0,F393/J393)</f>
+        <v/>
+      </c>
+      <c r="L393" t="n">
+        <v>1</v>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>Supply Crates</t>
+        </is>
+      </c>
+      <c r="AQ393" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR393" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>2</v>
+      </c>
+      <c r="E394">
+        <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D394),0)</f>
+        <v/>
+      </c>
+      <c r="F394">
+        <f>F393+E394</f>
+        <v/>
+      </c>
+      <c r="G394" t="n">
+        <v>1</v>
+      </c>
+      <c r="H394" t="n">
+        <v>1</v>
+      </c>
+      <c r="I394" t="n">
+        <v>1</v>
+      </c>
+      <c r="J394">
+        <f>'Towers'!$G$22*G394*H394*I394</f>
+        <v/>
+      </c>
+      <c r="K394">
+        <f>IF(J394=0,0,F394/J394)</f>
+        <v/>
+      </c>
+      <c r="L394" t="n">
+        <v>1</v>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>Ammo Drop</t>
+        </is>
+      </c>
+      <c r="AQ394" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR394" t="n">
+        <v>550</v>
+      </c>
+      <c r="AY394" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>3</v>
+      </c>
+      <c r="E395">
+        <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D395),0)</f>
+        <v/>
+      </c>
+      <c r="F395">
+        <f>F394+E395</f>
+        <v/>
+      </c>
+      <c r="G395" t="n">
+        <v>1</v>
+      </c>
+      <c r="H395" t="n">
+        <v>1</v>
+      </c>
+      <c r="I395" t="n">
+        <v>1</v>
+      </c>
+      <c r="J395">
+        <f>'Towers'!$G$22*G395*H395*I395</f>
+        <v/>
+      </c>
+      <c r="K395">
+        <f>IF(J395=0,0,F395/J395)</f>
+        <v/>
+      </c>
+      <c r="L395" t="n">
+        <v>1</v>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>Med Drop</t>
+        </is>
+      </c>
+      <c r="AQ395" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR395" t="n">
+        <v>1550</v>
+      </c>
+      <c r="AY395" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BE395" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF395" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>4</v>
+      </c>
+      <c r="E396">
+        <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D396),0)</f>
+        <v/>
+      </c>
+      <c r="F396">
+        <f>F395+E396</f>
+        <v/>
+      </c>
+      <c r="G396" t="n">
+        <v>1</v>
+      </c>
+      <c r="H396" t="n">
+        <v>1</v>
+      </c>
+      <c r="I396" t="n">
+        <v>1</v>
+      </c>
+      <c r="J396">
+        <f>J395*G396*H396*I396</f>
+        <v/>
+      </c>
+      <c r="K396">
+        <f>IF(J396=0,0,F396/J396)</f>
+        <v/>
+      </c>
+      <c r="L396" t="n">
+        <v>1</v>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>Heavy Cargo</t>
+        </is>
+      </c>
+      <c r="AR396" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CI396" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ396" t="inlineStr">
+        <is>
+          <t>Bigger crates</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>5</v>
+      </c>
+      <c r="E397">
+        <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D397),0)</f>
+        <v/>
+      </c>
+      <c r="F397">
+        <f>F396+E397</f>
+        <v/>
+      </c>
+      <c r="G397" t="n">
+        <v>1</v>
+      </c>
+      <c r="H397" t="n">
+        <v>1</v>
+      </c>
+      <c r="I397" t="n">
+        <v>1</v>
+      </c>
+      <c r="J397">
+        <f>J396*G397*H397*I397</f>
+        <v/>
+      </c>
+      <c r="K397">
+        <f>IF(J397=0,0,F397/J397)</f>
+        <v/>
+      </c>
+      <c r="L397" t="n">
+        <v>1</v>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>Cargo Run</t>
+        </is>
+      </c>
+      <c r="CI397" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ397" t="inlineStr">
+        <is>
+          <t>A big crate every lap</t>
+        </is>
+      </c>
+      <c r="FC397" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Door Gun</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>4</v>
+      </c>
+      <c r="E398">
+        <f>E386</f>
+        <v/>
+      </c>
+      <c r="F398">
+        <f>F386</f>
+        <v/>
+      </c>
+      <c r="G398" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H398" t="n">
+        <v>1</v>
+      </c>
+      <c r="I398" t="n">
+        <v>1</v>
+      </c>
+      <c r="L398" t="n">
+        <v>1</v>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>Rocket Pods</t>
+        </is>
+      </c>
+      <c r="Z398" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA398" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI398" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ398" t="inlineStr">
+        <is>
+          <t>Rockets that splash</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Door Gun</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>4</v>
+      </c>
+      <c r="E399">
+        <f>E386</f>
+        <v/>
+      </c>
+      <c r="F399">
+        <f>F386</f>
+        <v/>
+      </c>
+      <c r="G399" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H399" t="n">
+        <v>1</v>
+      </c>
+      <c r="I399" t="n">
+        <v>1</v>
+      </c>
+      <c r="L399" t="n">
+        <v>1</v>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>Tracer Belt</t>
+        </is>
+      </c>
+      <c r="T399" t="n">
+        <v>15</v>
+      </c>
+      <c r="CI399" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ399" t="inlineStr">
+        <is>
+          <t>Hit dinos are marked +15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Door Gun</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>5</v>
+      </c>
+      <c r="E400">
+        <f>E387</f>
+        <v/>
+      </c>
+      <c r="F400">
+        <f>F387</f>
+        <v/>
+      </c>
+      <c r="G400" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H400" t="n">
+        <v>1</v>
+      </c>
+      <c r="I400" t="n">
+        <v>1</v>
+      </c>
+      <c r="L400" t="n">
+        <v>1</v>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>Bombing Run</t>
+        </is>
+      </c>
+      <c r="CI400" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ400" t="inlineStr">
+        <is>
+          <t>Bombs the whole track once a round</t>
+        </is>
+      </c>
+      <c r="CS400" t="n">
+        <v>12</v>
+      </c>
+      <c r="FK400" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Door Gun</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>5</v>
+      </c>
+      <c r="E401">
+        <f>E387</f>
+        <v/>
+      </c>
+      <c r="F401">
+        <f>F387</f>
+        <v/>
+      </c>
+      <c r="G401" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H401" t="n">
+        <v>1</v>
+      </c>
+      <c r="I401" t="n">
+        <v>1</v>
+      </c>
+      <c r="L401" t="n">
+        <v>1</v>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>Sky Hook</t>
+        </is>
+      </c>
+      <c r="CI401" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ401" t="inlineStr">
+        <is>
+          <t>Snatches the smallest dino every 5 s</t>
+        </is>
+      </c>
+      <c r="FL401" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Searchlight</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>4</v>
+      </c>
+      <c r="E402">
+        <f>E391</f>
+        <v/>
+      </c>
+      <c r="F402">
+        <f>F391</f>
+        <v/>
+      </c>
+      <c r="G402" t="n">
+        <v>1</v>
+      </c>
+      <c r="H402" t="n">
+        <v>1</v>
+      </c>
+      <c r="I402" t="n">
+        <v>1</v>
+      </c>
+      <c r="L402" t="n">
+        <v>1</v>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>Tracking Beam</t>
+        </is>
+      </c>
+      <c r="AL402" t="n">
+        <v>14</v>
+      </c>
+      <c r="CI402" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ402" t="inlineStr">
+        <is>
+          <t>The light follows the biggest dino</t>
+        </is>
+      </c>
+      <c r="CU402" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Searchlight</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>4</v>
+      </c>
+      <c r="E403">
+        <f>E391</f>
+        <v/>
+      </c>
+      <c r="F403">
+        <f>F391</f>
+        <v/>
+      </c>
+      <c r="G403" t="n">
+        <v>1</v>
+      </c>
+      <c r="H403" t="n">
+        <v>1</v>
+      </c>
+      <c r="I403" t="n">
+        <v>1</v>
+      </c>
+      <c r="L403" t="n">
+        <v>1</v>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>Blinding Glare</t>
+        </is>
+      </c>
+      <c r="AL403" t="n">
+        <v>15</v>
+      </c>
+      <c r="CI403" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ403" t="inlineStr">
+        <is>
+          <t>Dinos in the light miss throws</t>
+        </is>
+      </c>
+      <c r="FH403" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Searchlight</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>5</v>
+      </c>
+      <c r="E404">
+        <f>E392</f>
+        <v/>
+      </c>
+      <c r="F404">
+        <f>F392</f>
+        <v/>
+      </c>
+      <c r="G404" t="n">
+        <v>1</v>
+      </c>
+      <c r="H404" t="n">
+        <v>1</v>
+      </c>
+      <c r="I404" t="n">
+        <v>1</v>
+      </c>
+      <c r="L404" t="n">
+        <v>1</v>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>Lighthouse</t>
+        </is>
+      </c>
+      <c r="AC404" t="n">
+        <v>10</v>
+      </c>
+      <c r="CI404" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ404" t="inlineStr">
+        <is>
+          <t>Towers near its path +10% damage</t>
+        </is>
+      </c>
+      <c r="FI404" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Searchlight</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>5</v>
+      </c>
+      <c r="E405">
+        <f>E392</f>
+        <v/>
+      </c>
+      <c r="F405">
+        <f>F392</f>
+        <v/>
+      </c>
+      <c r="G405" t="n">
+        <v>1</v>
+      </c>
+      <c r="H405" t="n">
+        <v>1</v>
+      </c>
+      <c r="I405" t="n">
+        <v>1</v>
+      </c>
+      <c r="L405" t="n">
+        <v>1</v>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>Spotter's Map</t>
+        </is>
+      </c>
+      <c r="AL405" t="n">
+        <v>22</v>
+      </c>
+      <c r="CI405" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ405" t="inlineStr">
+        <is>
+          <t>See every dino through walls</t>
+        </is>
+      </c>
+      <c r="FJ405" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>4</v>
+      </c>
+      <c r="E406">
+        <f>E396</f>
+        <v/>
+      </c>
+      <c r="F406">
+        <f>F396</f>
+        <v/>
+      </c>
+      <c r="G406" t="n">
+        <v>1</v>
+      </c>
+      <c r="H406" t="n">
+        <v>1</v>
+      </c>
+      <c r="I406" t="n">
+        <v>1</v>
+      </c>
+      <c r="L406" t="n">
+        <v>1</v>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>Rebuild Kits</t>
+        </is>
+      </c>
+      <c r="CI406" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ406" t="inlineStr">
+        <is>
+          <t>Fixes a Trampled tower each lap</t>
+        </is>
+      </c>
+      <c r="FD406" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>4</v>
+      </c>
+      <c r="E407">
+        <f>E396</f>
+        <v/>
+      </c>
+      <c r="F407">
+        <f>F396</f>
+        <v/>
+      </c>
+      <c r="G407" t="n">
+        <v>1</v>
+      </c>
+      <c r="H407" t="n">
+        <v>1</v>
+      </c>
+      <c r="I407" t="n">
+        <v>1</v>
+      </c>
+      <c r="L407" t="n">
+        <v>1</v>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>Spare Parts</t>
+        </is>
+      </c>
+      <c r="AR407" t="n">
+        <v>1900</v>
+      </c>
+      <c r="CI407" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ407" t="inlineStr">
+        <is>
+          <t>A crate heals the closest tower</t>
+        </is>
+      </c>
+      <c r="FE407" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>5</v>
+      </c>
+      <c r="E408">
+        <f>E397</f>
+        <v/>
+      </c>
+      <c r="F408">
+        <f>F397</f>
+        <v/>
+      </c>
+      <c r="G408" t="n">
+        <v>1</v>
+      </c>
+      <c r="H408" t="n">
+        <v>1</v>
+      </c>
+      <c r="I408" t="n">
+        <v>1</v>
+      </c>
+      <c r="L408" t="n">
+        <v>1</v>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>Paratroopers</t>
+        </is>
+      </c>
+      <c r="CI408" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ408" t="inlineStr">
+        <is>
+          <t>Drops 2 rangers a round</t>
+        </is>
+      </c>
+      <c r="FF408" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Spotter Blimp</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>5</v>
+      </c>
+      <c r="E409">
+        <f>E397</f>
+        <v/>
+      </c>
+      <c r="F409">
+        <f>F397</f>
+        <v/>
+      </c>
+      <c r="G409" t="n">
+        <v>1</v>
+      </c>
+      <c r="H409" t="n">
+        <v>1</v>
+      </c>
+      <c r="I409" t="n">
+        <v>1</v>
+      </c>
+      <c r="L409" t="n">
+        <v>1</v>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>Airlift</t>
+        </is>
+      </c>
+      <c r="AR409" t="n">
+        <v>2700</v>
+      </c>
+      <c r="CI409" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ409" t="inlineStr">
+        <is>
+          <t>Fixes the first Trampled tower each round</t>
+        </is>
+      </c>
+      <c r="FG409" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -13023,112 +13023,112 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="A244" s="81" t="inlineStr">
         <is>
           <t>SPOTTER BLIMP</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
+      <c r="A245" s="81" t="inlineStr">
         <is>
           <t>Blimp speed (studs/s)</t>
         </is>
       </c>
-      <c r="B245" t="n">
+      <c r="B245" s="81" t="n">
         <v>40</v>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="C245" s="81" t="inlineStr">
         <is>
           <t>the blimp's flying speed along its side's track (x Blimp speed x); a lap = spawn end to exit end and back (Shared/Blimp)</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
+      <c r="A246" s="81" t="inlineStr">
         <is>
           <t>Paratrooper HP</t>
         </is>
       </c>
-      <c r="B246" t="n">
+      <c r="B246" s="81" t="n">
         <v>80</v>
       </c>
-      <c r="C246" t="inlineStr">
+      <c r="C246" s="81" t="inlineStr">
         <is>
           <t>a Paratroopers ranger's HP (the 9g walker, fight mode)</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
+      <c r="A247" s="81" t="inlineStr">
         <is>
           <t>Paratrooper damage</t>
         </is>
       </c>
-      <c r="B247" t="n">
+      <c r="B247" s="81" t="n">
         <v>40</v>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="C247" s="81" t="inlineStr">
         <is>
           <t>a paratrooper's shot (x the team's level)</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
+      <c r="A248" s="81" t="inlineStr">
         <is>
           <t>Paratrooper rate</t>
         </is>
       </c>
-      <c r="B248" t="n">
+      <c r="B248" s="81" t="n">
         <v>1.5</v>
       </c>
-      <c r="C248" t="inlineStr">
+      <c r="C248" s="81" t="inlineStr">
         <is>
           <t>shots a second per paratrooper</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
+      <c r="A249" s="81" t="inlineStr">
         <is>
           <t>Paratrooper reach</t>
         </is>
       </c>
-      <c r="B249" t="n">
+      <c r="B249" s="81" t="n">
         <v>14</v>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="C249" s="81" t="inlineStr">
         <is>
           <t>studs: paratroopers hunt dinos within this of where they land</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
+      <c r="A250" s="81" t="inlineStr">
         <is>
           <t>Paratrooper speed</t>
         </is>
       </c>
-      <c r="B250" t="n">
+      <c r="B250" s="81" t="n">
         <v>14</v>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="C250" s="81" t="inlineStr">
         <is>
           <t>studs/s a paratrooper walks</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
+      <c r="A251" s="81" t="inlineStr">
         <is>
           <t>Hook max sizes</t>
         </is>
       </c>
-      <c r="B251" t="n">
+      <c r="B251" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="C251" t="inlineStr">
+      <c r="C251" s="81" t="inlineStr">
         <is>
           <t>Sky Hook takes only a non-boss dino with at most this many sizes left</t>
         </is>
@@ -14354,72 +14354,72 @@
       <c r="Z21" s="81" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="81" t="inlineStr">
         <is>
           <t>Flies your track: a door gun, a searchlight or cargo</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="81" t="n">
         <v>600</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22">
+      <c r="F22" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="81">
         <f>D22*E22*F22</f>
         <v/>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="81" t="n">
         <v>14</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="81" t="inlineStr">
         <is>
           <t>Its mooring mast is placed like any tower; the blimp flies your track there and back. Can't be damaged (#148).</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="81" t="n">
         <v>400</v>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" s="81" t="inlineStr">
         <is>
           <t>BLIMP</t>
         </is>
       </c>
-      <c r="P22" t="n">
+      <c r="P22" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R22" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T22" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -14445,7 +14445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FM409"/>
+  <dimension ref="A1:FL409"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -15370,57 +15370,57 @@
           <t>Aura range %</t>
         </is>
       </c>
-      <c r="FB4" t="inlineStr">
+      <c r="FB4" s="81" t="inlineStr">
         <is>
           <t>Blimp speed x</t>
         </is>
       </c>
-      <c r="FC4" t="inlineStr">
+      <c r="FC4" s="81" t="inlineStr">
         <is>
           <t>Lap chests</t>
         </is>
       </c>
-      <c r="FD4" t="inlineStr">
+      <c r="FD4" s="81" t="inlineStr">
         <is>
           <t>Lap repairs</t>
         </is>
       </c>
-      <c r="FE4" t="inlineStr">
+      <c r="FE4" s="81" t="inlineStr">
         <is>
           <t>Crate heal %</t>
         </is>
       </c>
-      <c r="FF4" t="inlineStr">
+      <c r="FF4" s="81" t="inlineStr">
         <is>
           <t>Paratroopers</t>
         </is>
       </c>
-      <c r="FG4" t="inlineStr">
+      <c r="FG4" s="81" t="inlineStr">
         <is>
           <t>Airlift</t>
         </is>
       </c>
-      <c r="FH4" t="inlineStr">
+      <c r="FH4" s="81" t="inlineStr">
         <is>
           <t>Throw miss %</t>
         </is>
       </c>
-      <c r="FI4" t="inlineStr">
+      <c r="FI4" s="81" t="inlineStr">
         <is>
           <t>Aura reach x</t>
         </is>
       </c>
-      <c r="FJ4" t="inlineStr">
+      <c r="FJ4" s="81" t="inlineStr">
         <is>
           <t>Dino outlines</t>
         </is>
       </c>
-      <c r="FK4" t="inlineStr">
+      <c r="FK4" s="81" t="inlineStr">
         <is>
           <t>Bombing run</t>
         </is>
       </c>
-      <c r="FL4" t="inlineStr">
+      <c r="FL4" s="81" t="inlineStr">
         <is>
           <t>Hook every (s)</t>
         </is>
@@ -43536,1665 +43536,1665 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" t="inlineStr">
+      <c r="A383" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr">
+      <c r="B383" s="81" t="inlineStr">
         <is>
           <t>Door Gun</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr">
+      <c r="C383" s="81" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="D383" t="n">
-        <v>1</v>
-      </c>
-      <c r="E383">
+      <c r="D383" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E383" s="81">
         <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D383),0)</f>
         <v/>
       </c>
-      <c r="F383">
+      <c r="F383" s="81">
         <f>'Towers'!$C$22+E383</f>
         <v/>
       </c>
-      <c r="G383" t="n">
+      <c r="G383" s="81" t="n">
         <v>1.5</v>
       </c>
-      <c r="H383" t="n">
+      <c r="H383" s="81" t="n">
         <v>1.2</v>
       </c>
-      <c r="I383" t="n">
-        <v>1</v>
-      </c>
-      <c r="J383">
+      <c r="I383" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J383" s="81">
         <f>'Towers'!$G$22*G383*H383*I383</f>
         <v/>
       </c>
-      <c r="K383">
+      <c r="K383" s="81">
         <f>IF(J383=0,0,F383/J383)</f>
         <v/>
       </c>
-      <c r="L383" t="n">
-        <v>1</v>
-      </c>
-      <c r="M383" t="inlineStr">
+      <c r="L383" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M383" s="81" t="inlineStr">
         <is>
           <t>Belt Gun</t>
         </is>
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr">
+      <c r="A384" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B384" t="inlineStr">
+      <c r="B384" s="81" t="inlineStr">
         <is>
           <t>Door Gun</t>
         </is>
       </c>
-      <c r="C384" t="inlineStr">
+      <c r="C384" s="81" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="D384" t="n">
+      <c r="D384" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="E384">
+      <c r="E384" s="81">
         <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D384),0)</f>
         <v/>
       </c>
-      <c r="F384">
+      <c r="F384" s="81">
         <f>F383+E384</f>
         <v/>
       </c>
-      <c r="G384" t="n">
+      <c r="G384" s="81" t="n">
         <v>1.5</v>
       </c>
-      <c r="H384" t="n">
+      <c r="H384" s="81" t="n">
         <v>1.2</v>
       </c>
-      <c r="I384" t="n">
-        <v>1</v>
-      </c>
-      <c r="J384">
+      <c r="I384" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J384" s="81">
         <f>'Towers'!$G$22*G384*H384*I384</f>
         <v/>
       </c>
-      <c r="K384">
+      <c r="K384" s="81">
         <f>IF(J384=0,0,F384/J384)</f>
         <v/>
       </c>
-      <c r="L384" t="n">
-        <v>1</v>
-      </c>
-      <c r="M384" t="inlineStr">
+      <c r="L384" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M384" s="81" t="inlineStr">
         <is>
           <t>Twin Mount</t>
         </is>
       </c>
-      <c r="Q384" t="n">
+      <c r="Q384" s="81" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr">
+      <c r="A385" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr">
+      <c r="B385" s="81" t="inlineStr">
         <is>
           <t>Door Gun</t>
         </is>
       </c>
-      <c r="C385" t="inlineStr">
+      <c r="C385" s="81" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="D385" t="n">
+      <c r="D385" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="E385">
+      <c r="E385" s="81">
         <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D385),0)</f>
         <v/>
       </c>
-      <c r="F385">
+      <c r="F385" s="81">
         <f>F384+E385</f>
         <v/>
       </c>
-      <c r="G385" t="n">
+      <c r="G385" s="81" t="n">
         <v>2.6</v>
       </c>
-      <c r="H385" t="n">
+      <c r="H385" s="81" t="n">
         <v>1.2</v>
       </c>
-      <c r="I385" t="n">
-        <v>1</v>
-      </c>
-      <c r="J385">
+      <c r="I385" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J385" s="81">
         <f>'Towers'!$G$22*G385*H385*I385</f>
         <v/>
       </c>
-      <c r="K385">
+      <c r="K385" s="81">
         <f>IF(J385=0,0,F385/J385)</f>
         <v/>
       </c>
-      <c r="L385" t="n">
-        <v>1</v>
-      </c>
-      <c r="M385" t="inlineStr">
-        <is>
-          <t>Strafing Run</t>
-        </is>
-      </c>
-      <c r="Q385" t="n">
+      <c r="L385" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M385" s="81" t="inlineStr">
+        <is>
+          <t>Treetop Pass</t>
+        </is>
+      </c>
+      <c r="Q385" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="R385" t="n">
+      <c r="R385" s="81" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr">
+      <c r="A386" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B386" t="inlineStr">
+      <c r="B386" s="81" t="inlineStr">
         <is>
           <t>Door Gun</t>
         </is>
       </c>
-      <c r="C386" t="inlineStr">
+      <c r="C386" s="81" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="D386" t="n">
+      <c r="D386" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E386">
+      <c r="E386" s="81">
         <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D386),0)</f>
         <v/>
       </c>
-      <c r="F386">
+      <c r="F386" s="81">
         <f>F385+E386</f>
         <v/>
       </c>
-      <c r="G386" t="n">
+      <c r="G386" s="81" t="n">
         <v>1.7</v>
       </c>
-      <c r="H386" t="n">
-        <v>1</v>
-      </c>
-      <c r="I386" t="n">
-        <v>1</v>
-      </c>
-      <c r="J386">
+      <c r="H386" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I386" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J386" s="81">
         <f>J385*G386*H386*I386</f>
         <v/>
       </c>
-      <c r="K386">
+      <c r="K386" s="81">
         <f>IF(J386=0,0,F386/J386)</f>
         <v/>
       </c>
-      <c r="L386" t="n">
-        <v>1</v>
-      </c>
-      <c r="M386" t="inlineStr">
+      <c r="L386" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M386" s="81" t="inlineStr">
         <is>
           <t>Heavy Mount</t>
         </is>
       </c>
-      <c r="N386" t="inlineStr">
+      <c r="N386" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="BJ386" t="n">
+      <c r="BJ386" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="CI386" t="inlineStr">
+      <c r="CI386" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ386" t="inlineStr">
+      <c r="CJ386" s="81" t="inlineStr">
         <is>
           <t>Shoots through armour, breaks 2</t>
         </is>
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr">
+      <c r="A387" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr">
+      <c r="B387" s="81" t="inlineStr">
         <is>
           <t>Door Gun</t>
         </is>
       </c>
-      <c r="C387" t="inlineStr">
+      <c r="C387" s="81" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="D387" t="n">
+      <c r="D387" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E387">
+      <c r="E387" s="81">
         <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D387),0)</f>
         <v/>
       </c>
-      <c r="F387">
+      <c r="F387" s="81">
         <f>F386+E387</f>
         <v/>
       </c>
-      <c r="G387" t="n">
+      <c r="G387" s="81" t="n">
         <v>0.78</v>
       </c>
-      <c r="H387" t="n">
-        <v>1</v>
-      </c>
-      <c r="I387" t="n">
-        <v>1</v>
-      </c>
-      <c r="J387">
+      <c r="H387" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I387" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J387" s="81">
         <f>J386*G387*H387*I387</f>
         <v/>
       </c>
-      <c r="K387">
+      <c r="K387" s="81">
         <f>IF(J387=0,0,F387/J387)</f>
         <v/>
       </c>
-      <c r="L387" t="n">
-        <v>1</v>
-      </c>
-      <c r="M387" t="inlineStr">
+      <c r="L387" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M387" s="81" t="inlineStr">
         <is>
           <t>Gunship</t>
         </is>
       </c>
-      <c r="Q387" t="n">
+      <c r="Q387" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="Z387" t="n">
+      <c r="Z387" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="AA387" t="n">
-        <v>1</v>
-      </c>
-      <c r="CI387" t="inlineStr">
+      <c r="AA387" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI387" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ387" t="inlineStr">
+      <c r="CJ387" s="81" t="inlineStr">
         <is>
           <t>Faster, four guns and rockets</t>
         </is>
       </c>
-      <c r="FB387" t="n">
+      <c r="FB387" s="81" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="inlineStr">
+      <c r="A388" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
+      <c r="B388" s="81" t="inlineStr">
         <is>
           <t>Searchlight</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr">
+      <c r="C388" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D388" t="n">
-        <v>1</v>
-      </c>
-      <c r="E388">
+      <c r="D388" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E388" s="81">
         <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D388),0)</f>
         <v/>
       </c>
-      <c r="F388">
+      <c r="F388" s="81">
         <f>'Towers'!$C$22+E388</f>
         <v/>
       </c>
-      <c r="G388" t="n">
-        <v>1</v>
-      </c>
-      <c r="H388" t="n">
-        <v>1</v>
-      </c>
-      <c r="I388" t="n">
-        <v>1</v>
-      </c>
-      <c r="J388">
+      <c r="G388" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H388" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I388" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J388" s="81">
         <f>'Towers'!$G$22*G388*H388*I388</f>
         <v/>
       </c>
-      <c r="K388">
+      <c r="K388" s="81">
         <f>IF(J388=0,0,F388/J388)</f>
         <v/>
       </c>
-      <c r="L388" t="n">
-        <v>1</v>
-      </c>
-      <c r="M388" t="inlineStr">
+      <c r="L388" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M388" s="81" t="inlineStr">
         <is>
           <t>Spotlight</t>
         </is>
       </c>
-      <c r="AL388" t="n">
+      <c r="AL388" s="81" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
+      <c r="A389" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
+      <c r="B389" s="81" t="inlineStr">
         <is>
           <t>Searchlight</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr">
+      <c r="C389" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D389" t="n">
+      <c r="D389" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="E389">
+      <c r="E389" s="81">
         <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D389),0)</f>
         <v/>
       </c>
-      <c r="F389">
+      <c r="F389" s="81">
         <f>F388+E389</f>
         <v/>
       </c>
-      <c r="G389" t="n">
-        <v>1</v>
-      </c>
-      <c r="H389" t="n">
-        <v>1</v>
-      </c>
-      <c r="I389" t="n">
-        <v>1</v>
-      </c>
-      <c r="J389">
+      <c r="G389" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H389" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I389" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J389" s="81">
         <f>'Towers'!$G$22*G389*H389*I389</f>
         <v/>
       </c>
-      <c r="K389">
+      <c r="K389" s="81">
         <f>IF(J389=0,0,F389/J389)</f>
         <v/>
       </c>
-      <c r="L389" t="n">
+      <c r="L389" s="81" t="n">
         <v>1.3</v>
       </c>
-      <c r="M389" t="inlineStr">
+      <c r="M389" s="81" t="inlineStr">
         <is>
           <t>Wide Beam</t>
         </is>
       </c>
-      <c r="AL389" t="n">
+      <c r="AL389" s="81" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
+      <c r="A390" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr">
+      <c r="B390" s="81" t="inlineStr">
         <is>
           <t>Searchlight</t>
         </is>
       </c>
-      <c r="C390" t="inlineStr">
+      <c r="C390" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D390" t="n">
+      <c r="D390" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="E390">
+      <c r="E390" s="81">
         <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D390),0)</f>
         <v/>
       </c>
-      <c r="F390">
+      <c r="F390" s="81">
         <f>F389+E390</f>
         <v/>
       </c>
-      <c r="G390" t="n">
-        <v>1</v>
-      </c>
-      <c r="H390" t="n">
-        <v>1</v>
-      </c>
-      <c r="I390" t="n">
-        <v>1</v>
-      </c>
-      <c r="J390">
+      <c r="G390" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H390" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I390" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J390" s="81">
         <f>'Towers'!$G$22*G390*H390*I390</f>
         <v/>
       </c>
-      <c r="K390">
+      <c r="K390" s="81">
         <f>IF(J390=0,0,F390/J390)</f>
         <v/>
       </c>
-      <c r="L390" t="n">
+      <c r="L390" s="81" t="n">
         <v>1.3</v>
       </c>
-      <c r="M390" t="inlineStr">
+      <c r="M390" s="81" t="inlineStr">
         <is>
           <t>Night Hunt</t>
         </is>
       </c>
-      <c r="AL390" t="n">
+      <c r="AL390" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="FA390" t="n">
+      <c r="FA390" s="81" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="inlineStr">
+      <c r="A391" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
+      <c r="B391" s="81" t="inlineStr">
         <is>
           <t>Searchlight</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr">
+      <c r="C391" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D391" t="n">
+      <c r="D391" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E391">
+      <c r="E391" s="81">
         <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D391),0)</f>
         <v/>
       </c>
-      <c r="F391">
+      <c r="F391" s="81">
         <f>F390+E391</f>
         <v/>
       </c>
-      <c r="G391" t="n">
-        <v>1</v>
-      </c>
-      <c r="H391" t="n">
-        <v>1</v>
-      </c>
-      <c r="I391" t="n">
-        <v>1</v>
-      </c>
-      <c r="J391">
+      <c r="G391" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H391" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I391" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J391" s="81">
         <f>J390*G391*H391*I391</f>
         <v/>
       </c>
-      <c r="K391">
+      <c r="K391" s="81">
         <f>IF(J391=0,0,F391/J391)</f>
         <v/>
       </c>
-      <c r="L391" t="n">
+      <c r="L391" s="81" t="n">
         <v>1.6</v>
       </c>
-      <c r="M391" t="inlineStr">
+      <c r="M391" s="81" t="inlineStr">
         <is>
           <t>Floodlights</t>
         </is>
       </c>
-      <c r="CI391" t="inlineStr">
+      <c r="CI391" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ391" t="inlineStr">
+      <c r="CJ391" s="81" t="inlineStr">
         <is>
           <t>Lights a much wider circle</t>
         </is>
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="inlineStr">
+      <c r="A392" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr">
+      <c r="B392" s="81" t="inlineStr">
         <is>
           <t>Searchlight</t>
         </is>
       </c>
-      <c r="C392" t="inlineStr">
+      <c r="C392" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D392" t="n">
+      <c r="D392" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E392">
+      <c r="E392" s="81">
         <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D392),0)</f>
         <v/>
       </c>
-      <c r="F392">
+      <c r="F392" s="81">
         <f>F391+E392</f>
         <v/>
       </c>
-      <c r="G392" t="n">
-        <v>1</v>
-      </c>
-      <c r="H392" t="n">
-        <v>1</v>
-      </c>
-      <c r="I392" t="n">
-        <v>1</v>
-      </c>
-      <c r="J392">
+      <c r="G392" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H392" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I392" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J392" s="81">
         <f>J391*G392*H392*I392</f>
         <v/>
       </c>
-      <c r="K392">
+      <c r="K392" s="81">
         <f>IF(J392=0,0,F392/J392)</f>
         <v/>
       </c>
-      <c r="L392" t="n">
-        <v>1</v>
-      </c>
-      <c r="M392" t="inlineStr">
+      <c r="L392" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M392" s="81" t="inlineStr">
         <is>
           <t>All-Seeing Eye</t>
         </is>
       </c>
-      <c r="AL392" t="n">
+      <c r="AL392" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="CI392" t="inlineStr">
+      <c r="CI392" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ392" t="inlineStr">
+      <c r="CJ392" s="81" t="inlineStr">
         <is>
           <t>Every dino under the blimp marked +25%</t>
         </is>
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr">
+      <c r="A393" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr">
+      <c r="B393" s="81" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="C393" t="inlineStr">
+      <c r="C393" s="81" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D393" t="n">
-        <v>1</v>
-      </c>
-      <c r="E393">
+      <c r="D393" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E393" s="81">
         <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D393),0)</f>
         <v/>
       </c>
-      <c r="F393">
+      <c r="F393" s="81">
         <f>'Towers'!$C$22+E393</f>
         <v/>
       </c>
-      <c r="G393" t="n">
-        <v>1</v>
-      </c>
-      <c r="H393" t="n">
-        <v>1</v>
-      </c>
-      <c r="I393" t="n">
-        <v>1</v>
-      </c>
-      <c r="J393">
+      <c r="G393" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H393" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I393" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J393" s="81">
         <f>'Towers'!$G$22*G393*H393*I393</f>
         <v/>
       </c>
-      <c r="K393">
+      <c r="K393" s="81">
         <f>IF(J393=0,0,F393/J393)</f>
         <v/>
       </c>
-      <c r="L393" t="n">
-        <v>1</v>
-      </c>
-      <c r="M393" t="inlineStr">
+      <c r="L393" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M393" s="81" t="inlineStr">
         <is>
           <t>Supply Crates</t>
         </is>
       </c>
-      <c r="AQ393" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR393" t="n">
+      <c r="AQ393" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR393" s="81" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="inlineStr">
+      <c r="A394" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
+      <c r="B394" s="81" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr">
+      <c r="C394" s="81" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D394" t="n">
+      <c r="D394" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="E394">
+      <c r="E394" s="81">
         <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D394),0)</f>
         <v/>
       </c>
-      <c r="F394">
+      <c r="F394" s="81">
         <f>F393+E394</f>
         <v/>
       </c>
-      <c r="G394" t="n">
-        <v>1</v>
-      </c>
-      <c r="H394" t="n">
-        <v>1</v>
-      </c>
-      <c r="I394" t="n">
-        <v>1</v>
-      </c>
-      <c r="J394">
+      <c r="G394" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H394" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I394" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J394" s="81">
         <f>'Towers'!$G$22*G394*H394*I394</f>
         <v/>
       </c>
-      <c r="K394">
+      <c r="K394" s="81">
         <f>IF(J394=0,0,F394/J394)</f>
         <v/>
       </c>
-      <c r="L394" t="n">
-        <v>1</v>
-      </c>
-      <c r="M394" t="inlineStr">
+      <c r="L394" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M394" s="81" t="inlineStr">
         <is>
           <t>Ammo Drop</t>
         </is>
       </c>
-      <c r="AQ394" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR394" t="n">
+      <c r="AQ394" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR394" s="81" t="n">
         <v>550</v>
       </c>
-      <c r="AY394" t="n">
+      <c r="AY394" s="81" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr">
+      <c r="A395" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr">
+      <c r="B395" s="81" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="C395" t="inlineStr">
+      <c r="C395" s="81" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D395" t="n">
+      <c r="D395" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="E395">
+      <c r="E395" s="81">
         <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D395),0)</f>
         <v/>
       </c>
-      <c r="F395">
+      <c r="F395" s="81">
         <f>F394+E395</f>
         <v/>
       </c>
-      <c r="G395" t="n">
-        <v>1</v>
-      </c>
-      <c r="H395" t="n">
-        <v>1</v>
-      </c>
-      <c r="I395" t="n">
-        <v>1</v>
-      </c>
-      <c r="J395">
+      <c r="G395" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H395" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I395" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J395" s="81">
         <f>'Towers'!$G$22*G395*H395*I395</f>
         <v/>
       </c>
-      <c r="K395">
+      <c r="K395" s="81">
         <f>IF(J395=0,0,F395/J395)</f>
         <v/>
       </c>
-      <c r="L395" t="n">
-        <v>1</v>
-      </c>
-      <c r="M395" t="inlineStr">
+      <c r="L395" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M395" s="81" t="inlineStr">
         <is>
           <t>Med Drop</t>
         </is>
       </c>
-      <c r="AQ395" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR395" t="n">
+      <c r="AQ395" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR395" s="81" t="n">
         <v>1550</v>
       </c>
-      <c r="AY395" t="n">
+      <c r="AY395" s="81" t="n">
         <v>0.8</v>
       </c>
-      <c r="BE395" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF395" t="n">
+      <c r="BE395" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF395" s="81" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr">
+      <c r="A396" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr">
+      <c r="B396" s="81" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="C396" t="inlineStr">
+      <c r="C396" s="81" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D396" t="n">
+      <c r="D396" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E396">
+      <c r="E396" s="81">
         <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D396),0)</f>
         <v/>
       </c>
-      <c r="F396">
+      <c r="F396" s="81">
         <f>F395+E396</f>
         <v/>
       </c>
-      <c r="G396" t="n">
-        <v>1</v>
-      </c>
-      <c r="H396" t="n">
-        <v>1</v>
-      </c>
-      <c r="I396" t="n">
-        <v>1</v>
-      </c>
-      <c r="J396">
+      <c r="G396" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H396" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I396" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J396" s="81">
         <f>J395*G396*H396*I396</f>
         <v/>
       </c>
-      <c r="K396">
+      <c r="K396" s="81">
         <f>IF(J396=0,0,F396/J396)</f>
         <v/>
       </c>
-      <c r="L396" t="n">
-        <v>1</v>
-      </c>
-      <c r="M396" t="inlineStr">
+      <c r="L396" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M396" s="81" t="inlineStr">
         <is>
           <t>Heavy Cargo</t>
         </is>
       </c>
-      <c r="AR396" t="n">
+      <c r="AR396" s="81" t="n">
         <v>2000</v>
       </c>
-      <c r="CI396" t="inlineStr">
+      <c r="CI396" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ396" t="inlineStr">
+      <c r="CJ396" s="81" t="inlineStr">
         <is>
           <t>Bigger crates</t>
         </is>
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="inlineStr">
+      <c r="A397" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
+      <c r="B397" s="81" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr">
+      <c r="C397" s="81" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D397" t="n">
+      <c r="D397" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E397">
+      <c r="E397" s="81">
         <f>ROUND('Towers'!$C$22*POWER('Tuning'!$B$12,D397),0)</f>
         <v/>
       </c>
-      <c r="F397">
+      <c r="F397" s="81">
         <f>F396+E397</f>
         <v/>
       </c>
-      <c r="G397" t="n">
-        <v>1</v>
-      </c>
-      <c r="H397" t="n">
-        <v>1</v>
-      </c>
-      <c r="I397" t="n">
-        <v>1</v>
-      </c>
-      <c r="J397">
+      <c r="G397" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H397" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I397" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J397" s="81">
         <f>J396*G397*H397*I397</f>
         <v/>
       </c>
-      <c r="K397">
+      <c r="K397" s="81">
         <f>IF(J397=0,0,F397/J397)</f>
         <v/>
       </c>
-      <c r="L397" t="n">
-        <v>1</v>
-      </c>
-      <c r="M397" t="inlineStr">
+      <c r="L397" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M397" s="81" t="inlineStr">
         <is>
           <t>Cargo Run</t>
         </is>
       </c>
-      <c r="CI397" t="inlineStr">
+      <c r="CI397" s="81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ397" t="inlineStr">
+      <c r="CJ397" s="81" t="inlineStr">
         <is>
           <t>A big crate every lap</t>
         </is>
       </c>
-      <c r="FC397" t="inlineStr">
+      <c r="FC397" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="inlineStr">
+      <c r="A398" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr">
+      <c r="B398" s="81" t="inlineStr">
         <is>
           <t>Door Gun</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr">
+      <c r="C398" s="81" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="D398" t="n">
+      <c r="D398" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E398">
+      <c r="E398" s="81">
         <f>E386</f>
         <v/>
       </c>
-      <c r="F398">
+      <c r="F398" s="81">
         <f>F386</f>
         <v/>
       </c>
-      <c r="G398" t="n">
+      <c r="G398" s="81" t="n">
         <v>1.4</v>
       </c>
-      <c r="H398" t="n">
-        <v>1</v>
-      </c>
-      <c r="I398" t="n">
-        <v>1</v>
-      </c>
-      <c r="L398" t="n">
-        <v>1</v>
-      </c>
-      <c r="M398" t="inlineStr">
+      <c r="H398" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I398" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L398" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M398" s="81" t="inlineStr">
         <is>
           <t>Rocket Pods</t>
         </is>
       </c>
-      <c r="Z398" t="n">
+      <c r="Z398" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="AA398" t="n">
-        <v>1</v>
-      </c>
-      <c r="CI398" t="inlineStr">
+      <c r="AA398" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI398" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ398" t="inlineStr">
+      <c r="CJ398" s="81" t="inlineStr">
         <is>
           <t>Rockets that splash</t>
         </is>
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr">
+      <c r="A399" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
+      <c r="B399" s="81" t="inlineStr">
         <is>
           <t>Door Gun</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr">
+      <c r="C399" s="81" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="D399" t="n">
+      <c r="D399" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E399">
+      <c r="E399" s="81">
         <f>E386</f>
         <v/>
       </c>
-      <c r="F399">
+      <c r="F399" s="81">
         <f>F386</f>
         <v/>
       </c>
-      <c r="G399" t="n">
+      <c r="G399" s="81" t="n">
         <v>1.75</v>
       </c>
-      <c r="H399" t="n">
-        <v>1</v>
-      </c>
-      <c r="I399" t="n">
-        <v>1</v>
-      </c>
-      <c r="L399" t="n">
-        <v>1</v>
-      </c>
-      <c r="M399" t="inlineStr">
+      <c r="H399" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I399" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L399" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M399" s="81" t="inlineStr">
         <is>
           <t>Tracer Belt</t>
         </is>
       </c>
-      <c r="T399" t="n">
+      <c r="T399" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="CI399" t="inlineStr">
+      <c r="CI399" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ399" t="inlineStr">
+      <c r="CJ399" s="81" t="inlineStr">
         <is>
           <t>Hit dinos are marked +15%</t>
         </is>
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr">
+      <c r="A400" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
+      <c r="B400" s="81" t="inlineStr">
         <is>
           <t>Door Gun</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr">
+      <c r="C400" s="81" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="D400" t="n">
+      <c r="D400" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E400">
+      <c r="E400" s="81">
         <f>E387</f>
         <v/>
       </c>
-      <c r="F400">
+      <c r="F400" s="81">
         <f>F387</f>
         <v/>
       </c>
-      <c r="G400" t="n">
+      <c r="G400" s="81" t="n">
         <v>1.6</v>
       </c>
-      <c r="H400" t="n">
-        <v>1</v>
-      </c>
-      <c r="I400" t="n">
-        <v>1</v>
-      </c>
-      <c r="L400" t="n">
-        <v>1</v>
-      </c>
-      <c r="M400" t="inlineStr">
+      <c r="H400" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I400" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L400" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M400" s="81" t="inlineStr">
         <is>
           <t>Bombing Run</t>
         </is>
       </c>
-      <c r="CI400" t="inlineStr">
+      <c r="CI400" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ400" t="inlineStr">
+      <c r="CJ400" s="81" t="inlineStr">
         <is>
           <t>Bombs the whole track once a round</t>
         </is>
       </c>
-      <c r="CS400" t="n">
+      <c r="CS400" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="FK400" t="inlineStr">
+      <c r="FK400" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="inlineStr">
+      <c r="A401" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
+      <c r="B401" s="81" t="inlineStr">
         <is>
           <t>Door Gun</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr">
+      <c r="C401" s="81" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="D401" t="n">
+      <c r="D401" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E401">
+      <c r="E401" s="81">
         <f>E387</f>
         <v/>
       </c>
-      <c r="F401">
+      <c r="F401" s="81">
         <f>F387</f>
         <v/>
       </c>
-      <c r="G401" t="n">
+      <c r="G401" s="81" t="n">
         <v>1.75</v>
       </c>
-      <c r="H401" t="n">
-        <v>1</v>
-      </c>
-      <c r="I401" t="n">
-        <v>1</v>
-      </c>
-      <c r="L401" t="n">
-        <v>1</v>
-      </c>
-      <c r="M401" t="inlineStr">
+      <c r="H401" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I401" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L401" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M401" s="81" t="inlineStr">
         <is>
           <t>Sky Hook</t>
         </is>
       </c>
-      <c r="CI401" t="inlineStr">
+      <c r="CI401" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ401" t="inlineStr">
+      <c r="CJ401" s="81" t="inlineStr">
         <is>
           <t>Snatches the smallest dino every 5 s</t>
         </is>
       </c>
-      <c r="FL401" t="n">
+      <c r="FL401" s="81" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr">
+      <c r="A402" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
+      <c r="B402" s="81" t="inlineStr">
         <is>
           <t>Searchlight</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr">
+      <c r="C402" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D402" t="n">
+      <c r="D402" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E402">
+      <c r="E402" s="81">
         <f>E391</f>
         <v/>
       </c>
-      <c r="F402">
+      <c r="F402" s="81">
         <f>F391</f>
         <v/>
       </c>
-      <c r="G402" t="n">
-        <v>1</v>
-      </c>
-      <c r="H402" t="n">
-        <v>1</v>
-      </c>
-      <c r="I402" t="n">
-        <v>1</v>
-      </c>
-      <c r="L402" t="n">
-        <v>1</v>
-      </c>
-      <c r="M402" t="inlineStr">
+      <c r="G402" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H402" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I402" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L402" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M402" s="81" t="inlineStr">
         <is>
           <t>Tracking Beam</t>
         </is>
       </c>
-      <c r="AL402" t="n">
+      <c r="AL402" s="81" t="n">
         <v>14</v>
       </c>
-      <c r="CI402" t="inlineStr">
+      <c r="CI402" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ402" t="inlineStr">
+      <c r="CJ402" s="81" t="inlineStr">
         <is>
           <t>The light follows the biggest dino</t>
         </is>
       </c>
-      <c r="CU402" t="inlineStr">
+      <c r="CU402" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr">
+      <c r="A403" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
+      <c r="B403" s="81" t="inlineStr">
         <is>
           <t>Searchlight</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr">
+      <c r="C403" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D403" t="n">
+      <c r="D403" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E403">
+      <c r="E403" s="81">
         <f>E391</f>
         <v/>
       </c>
-      <c r="F403">
+      <c r="F403" s="81">
         <f>F391</f>
         <v/>
       </c>
-      <c r="G403" t="n">
-        <v>1</v>
-      </c>
-      <c r="H403" t="n">
-        <v>1</v>
-      </c>
-      <c r="I403" t="n">
-        <v>1</v>
-      </c>
-      <c r="L403" t="n">
-        <v>1</v>
-      </c>
-      <c r="M403" t="inlineStr">
+      <c r="G403" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H403" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I403" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L403" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M403" s="81" t="inlineStr">
         <is>
           <t>Blinding Glare</t>
         </is>
       </c>
-      <c r="AL403" t="n">
+      <c r="AL403" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="CI403" t="inlineStr">
+      <c r="CI403" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ403" t="inlineStr">
+      <c r="CJ403" s="81" t="inlineStr">
         <is>
           <t>Dinos in the light miss throws</t>
         </is>
       </c>
-      <c r="FH403" t="n">
+      <c r="FH403" s="81" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="inlineStr">
+      <c r="A404" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr">
+      <c r="B404" s="81" t="inlineStr">
         <is>
           <t>Searchlight</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr">
+      <c r="C404" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D404" t="n">
+      <c r="D404" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E404">
+      <c r="E404" s="81">
         <f>E392</f>
         <v/>
       </c>
-      <c r="F404">
+      <c r="F404" s="81">
         <f>F392</f>
         <v/>
       </c>
-      <c r="G404" t="n">
-        <v>1</v>
-      </c>
-      <c r="H404" t="n">
-        <v>1</v>
-      </c>
-      <c r="I404" t="n">
-        <v>1</v>
-      </c>
-      <c r="L404" t="n">
-        <v>1</v>
-      </c>
-      <c r="M404" t="inlineStr">
+      <c r="G404" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H404" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I404" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L404" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M404" s="81" t="inlineStr">
         <is>
           <t>Lighthouse</t>
         </is>
       </c>
-      <c r="AC404" t="n">
+      <c r="AC404" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="CI404" t="inlineStr">
+      <c r="CI404" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ404" t="inlineStr">
+      <c r="CJ404" s="81" t="inlineStr">
         <is>
           <t>Towers near its path +10% damage</t>
         </is>
       </c>
-      <c r="FI404" t="n">
+      <c r="FI404" s="81" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="inlineStr">
+      <c r="A405" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr">
+      <c r="B405" s="81" t="inlineStr">
         <is>
           <t>Searchlight</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr">
+      <c r="C405" s="81" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="D405" t="n">
+      <c r="D405" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E405">
+      <c r="E405" s="81">
         <f>E392</f>
         <v/>
       </c>
-      <c r="F405">
+      <c r="F405" s="81">
         <f>F392</f>
         <v/>
       </c>
-      <c r="G405" t="n">
-        <v>1</v>
-      </c>
-      <c r="H405" t="n">
-        <v>1</v>
-      </c>
-      <c r="I405" t="n">
-        <v>1</v>
-      </c>
-      <c r="L405" t="n">
-        <v>1</v>
-      </c>
-      <c r="M405" t="inlineStr">
+      <c r="G405" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H405" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I405" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L405" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M405" s="81" t="inlineStr">
         <is>
           <t>Spotter's Map</t>
         </is>
       </c>
-      <c r="AL405" t="n">
+      <c r="AL405" s="81" t="n">
         <v>22</v>
       </c>
-      <c r="CI405" t="inlineStr">
+      <c r="CI405" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ405" t="inlineStr">
+      <c r="CJ405" s="81" t="inlineStr">
         <is>
           <t>See every dino through walls</t>
         </is>
       </c>
-      <c r="FJ405" t="inlineStr">
+      <c r="FJ405" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="inlineStr">
+      <c r="A406" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr">
+      <c r="B406" s="81" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="C406" t="inlineStr">
+      <c r="C406" s="81" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D406" t="n">
+      <c r="D406" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E406">
+      <c r="E406" s="81">
         <f>E396</f>
         <v/>
       </c>
-      <c r="F406">
+      <c r="F406" s="81">
         <f>F396</f>
         <v/>
       </c>
-      <c r="G406" t="n">
-        <v>1</v>
-      </c>
-      <c r="H406" t="n">
-        <v>1</v>
-      </c>
-      <c r="I406" t="n">
-        <v>1</v>
-      </c>
-      <c r="L406" t="n">
-        <v>1</v>
-      </c>
-      <c r="M406" t="inlineStr">
+      <c r="G406" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H406" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I406" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L406" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M406" s="81" t="inlineStr">
         <is>
           <t>Rebuild Kits</t>
         </is>
       </c>
-      <c r="CI406" t="inlineStr">
+      <c r="CI406" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ406" t="inlineStr">
+      <c r="CJ406" s="81" t="inlineStr">
         <is>
           <t>Fixes a Trampled tower each lap</t>
         </is>
       </c>
-      <c r="FD406" t="n">
+      <c r="FD406" s="81" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="inlineStr">
+      <c r="A407" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr">
+      <c r="B407" s="81" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr">
+      <c r="C407" s="81" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D407" t="n">
+      <c r="D407" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="E407">
+      <c r="E407" s="81">
         <f>E396</f>
         <v/>
       </c>
-      <c r="F407">
+      <c r="F407" s="81">
         <f>F396</f>
         <v/>
       </c>
-      <c r="G407" t="n">
-        <v>1</v>
-      </c>
-      <c r="H407" t="n">
-        <v>1</v>
-      </c>
-      <c r="I407" t="n">
-        <v>1</v>
-      </c>
-      <c r="L407" t="n">
-        <v>1</v>
-      </c>
-      <c r="M407" t="inlineStr">
+      <c r="G407" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H407" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I407" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L407" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M407" s="81" t="inlineStr">
         <is>
           <t>Spare Parts</t>
         </is>
       </c>
-      <c r="AR407" t="n">
+      <c r="AR407" s="81" t="n">
         <v>1900</v>
       </c>
-      <c r="CI407" t="inlineStr">
+      <c r="CI407" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ407" t="inlineStr">
+      <c r="CJ407" s="81" t="inlineStr">
         <is>
           <t>A crate heals the closest tower</t>
         </is>
       </c>
-      <c r="FE407" t="n">
+      <c r="FE407" s="81" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr">
+      <c r="A408" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr">
+      <c r="B408" s="81" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr">
+      <c r="C408" s="81" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D408" t="n">
+      <c r="D408" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E408">
+      <c r="E408" s="81">
         <f>E397</f>
         <v/>
       </c>
-      <c r="F408">
+      <c r="F408" s="81">
         <f>F397</f>
         <v/>
       </c>
-      <c r="G408" t="n">
-        <v>1</v>
-      </c>
-      <c r="H408" t="n">
-        <v>1</v>
-      </c>
-      <c r="I408" t="n">
-        <v>1</v>
-      </c>
-      <c r="L408" t="n">
-        <v>1</v>
-      </c>
-      <c r="M408" t="inlineStr">
+      <c r="G408" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H408" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I408" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L408" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M408" s="81" t="inlineStr">
         <is>
           <t>Paratroopers</t>
         </is>
       </c>
-      <c r="CI408" t="inlineStr">
+      <c r="CI408" s="81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="CJ408" t="inlineStr">
+      <c r="CJ408" s="81" t="inlineStr">
         <is>
           <t>Drops 2 rangers a round</t>
         </is>
       </c>
-      <c r="FF408" t="n">
+      <c r="FF408" s="81" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr">
+      <c r="A409" s="81" t="inlineStr">
         <is>
           <t>Spotter Blimp</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr">
+      <c r="B409" s="81" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr">
+      <c r="C409" s="81" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D409" t="n">
+      <c r="D409" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="E409">
+      <c r="E409" s="81">
         <f>E397</f>
         <v/>
       </c>
-      <c r="F409">
+      <c r="F409" s="81">
         <f>F397</f>
         <v/>
       </c>
-      <c r="G409" t="n">
-        <v>1</v>
-      </c>
-      <c r="H409" t="n">
-        <v>1</v>
-      </c>
-      <c r="I409" t="n">
-        <v>1</v>
-      </c>
-      <c r="L409" t="n">
-        <v>1</v>
-      </c>
-      <c r="M409" t="inlineStr">
+      <c r="G409" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H409" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I409" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L409" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M409" s="81" t="inlineStr">
         <is>
           <t>Airlift</t>
         </is>
       </c>
-      <c r="AR409" t="n">
+      <c r="AR409" s="81" t="n">
         <v>2700</v>
       </c>
-      <c r="CI409" t="inlineStr">
+      <c r="CI409" s="81" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="CJ409" t="inlineStr">
+      <c r="CJ409" s="81" t="inlineStr">
         <is>
           <t>Fixes the first Trampled tower each round</t>
         </is>
       </c>
-      <c r="FG409" t="inlineStr">
+      <c r="FG409" s="81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9500,7 +9500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E266"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -13131,6 +13131,208 @@
       <c r="C251" s="81" t="inlineStr">
         <is>
           <t>Sky Hook takes only a non-boss dino with at most this many sizes left</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="81" t="inlineStr">
+        <is>
+          <t>METEOR BEACON</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="81" t="inlineStr">
+        <is>
+          <t>Bunch radius (studs)</t>
+        </is>
+      </c>
+      <c r="B254" s="81" t="n">
+        <v>8</v>
+      </c>
+      <c r="C254" s="81" t="inlineStr">
+        <is>
+          <t>studs: a meteor aims at the track point with the most dinos within this (a boss counts 3; Shared/Meteor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="81" t="inlineStr">
+        <is>
+          <t>Strike warning (s)</t>
+        </is>
+      </c>
+      <c r="B255" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C255" s="81" t="inlineStr">
+        <is>
+          <t>s the red warning ring shows before a meteor lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="81" t="inlineStr">
+        <is>
+          <t>Crater radius</t>
+        </is>
+      </c>
+      <c r="B256" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="C256" s="81" t="inlineStr">
+        <is>
+          <t>studs: the burning crater a strike's densest-point meteor leaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="81" t="inlineStr">
+        <is>
+          <t>Crater (s)</t>
+        </is>
+      </c>
+      <c r="B257" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="C257" s="81" t="inlineStr">
+        <is>
+          <t>s a crater lasts when the build sets no Crater (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="81" t="inlineStr">
+        <is>
+          <t>Crater burn DPS</t>
+        </is>
+      </c>
+      <c r="B258" s="81" t="n">
+        <v>10</v>
+      </c>
+      <c r="C258" s="81" t="inlineStr">
+        <is>
+          <t>a crater's burn a second when the build sets no Burn DPS (x the team's level)</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="81" t="inlineStr">
+        <is>
+          <t>Small meteor x</t>
+        </is>
+      </c>
+      <c r="B259" s="81" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C259" s="81" t="inlineStr">
+        <is>
+          <t>x the meteor's damage for each small meteor (Sky Rocks, Endless Rain, Starfall)</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="81" t="inlineStr">
+        <is>
+          <t>Small splash x</t>
+        </is>
+      </c>
+      <c r="B260" s="81" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C260" s="81" t="inlineStr">
+        <is>
+          <t>x the splash radius for each small meteor</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="81" t="inlineStr">
+        <is>
+          <t>Extinction min bunch</t>
+        </is>
+      </c>
+      <c r="B261" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="C261" s="81" t="inlineStr">
+        <is>
+          <t>Extinction Event fires itself on a boss or this many dinos in the bunch (else at the last spawn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="81" t="inlineStr">
+        <is>
+          <t>Extinction x</t>
+        </is>
+      </c>
+      <c r="B262" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="C262" s="81" t="inlineStr">
+        <is>
+          <t>x the meteor's damage on every dino on your side (Extinction Event, once per round played)</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="81" t="inlineStr">
+        <is>
+          <t>Extinction breaks</t>
+        </is>
+      </c>
+      <c r="B263" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="C263" s="81" t="inlineStr">
+        <is>
+          <t>sizes the Extinction Event breaks on the densest bunch's dinos (the rest break 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="81" t="inlineStr">
+        <is>
+          <t>Starfall meteors</t>
+        </is>
+      </c>
+      <c r="B264" s="81" t="n">
+        <v>20</v>
+      </c>
+      <c r="C264" s="81" t="inlineStr">
+        <is>
+          <t>Starfall: small meteors on the densest points across your side, in place of the strike</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="81" t="inlineStr">
+        <is>
+          <t>Fire line gap (studs)</t>
+        </is>
+      </c>
+      <c r="B265" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="C265" s="81" t="inlineStr">
+        <is>
+          <t>Fire Line: craters this close along the track join into one burning strip while both last</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="81" t="inlineStr">
+        <is>
+          <t>Streak length (studs)</t>
+        </is>
+      </c>
+      <c r="B266" s="81" t="n">
+        <v>10</v>
+      </c>
+      <c r="C266" s="81" t="inlineStr">
+        <is>
+          <t>Cinder Trail: each small meteor leaves a burning strip this long for 3 s</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -14425,6 +14627,73 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B23" s="81" t="inlineStr">
+        <is>
+          <t>Meteors on the biggest bunch: area hits and burning craters</t>
+        </is>
+      </c>
+      <c r="C23" s="81" t="n">
+        <v>600</v>
+      </c>
+      <c r="D23" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="E23" s="81" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F23" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" s="81">
+        <f>D23*E23*F23</f>
+        <v/>
+      </c>
+      <c r="H23" s="81" t="n">
+        <v>999</v>
+      </c>
+      <c r="I23" s="81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J23" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="81" t="inlineStr">
+        <is>
+          <t>Every 8 s calls a meteor on the biggest bunch of dinos on your side: area hit + burning crater. Ground only.</t>
+        </is>
+      </c>
+      <c r="L23" s="81" t="n">
+        <v>8</v>
+      </c>
+      <c r="M23" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="81" t="n">
+        <v>600</v>
+      </c>
+      <c r="O23" s="81" t="inlineStr">
+        <is>
+          <t>METEOR</t>
+        </is>
+      </c>
+      <c r="P23" s="81" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q23" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="81" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811" footer="0.511811"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -14445,7 +14714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FL409"/>
+  <dimension ref="A1:FZ436"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -15423,6 +15692,76 @@
       <c r="FL4" s="81" t="inlineStr">
         <is>
           <t>Hook every (s)</t>
+        </is>
+      </c>
+      <c r="FM4" s="81" t="inlineStr">
+        <is>
+          <t>Meteors</t>
+        </is>
+      </c>
+      <c r="FN4" s="81" t="inlineStr">
+        <is>
+          <t>Scatter</t>
+        </is>
+      </c>
+      <c r="FO4" s="81" t="inlineStr">
+        <is>
+          <t>Meteor every (s)</t>
+        </is>
+      </c>
+      <c r="FP4" s="81" t="inlineStr">
+        <is>
+          <t>Starfall every (s)</t>
+        </is>
+      </c>
+      <c r="FQ4" s="81" t="inlineStr">
+        <is>
+          <t>Crater (s)</t>
+        </is>
+      </c>
+      <c r="FR4" s="81" t="inlineStr">
+        <is>
+          <t>Crater amp %</t>
+        </is>
+      </c>
+      <c r="FS4" s="81" t="inlineStr">
+        <is>
+          <t>Bite miss %</t>
+        </is>
+      </c>
+      <c r="FT4" s="81" t="inlineStr">
+        <is>
+          <t>Crater freeze (s)</t>
+        </is>
+      </c>
+      <c r="FU4" s="81" t="inlineStr">
+        <is>
+          <t>Fire line</t>
+        </is>
+      </c>
+      <c r="FV4" s="81" t="inlineStr">
+        <is>
+          <t>Burn streak</t>
+        </is>
+      </c>
+      <c r="FW4" s="81" t="inlineStr">
+        <is>
+          <t>Extinction</t>
+        </is>
+      </c>
+      <c r="FX4" s="81" t="inlineStr">
+        <is>
+          <t>Side slow %</t>
+        </is>
+      </c>
+      <c r="FY4" s="81" t="inlineStr">
+        <is>
+          <t>Side slow (s)</t>
+        </is>
+      </c>
+      <c r="FZ4" s="81" t="inlineStr">
+        <is>
+          <t>Biggest breaks +</t>
         </is>
       </c>
     </row>
@@ -45198,6 +45537,1654 @@
         <is>
           <t>Yes</t>
         </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B410" s="81" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="C410" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D410" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E410" s="81">
+        <f>ROUND('Towers'!$C$23*POWER('Tuning'!$B$12,D410),0)</f>
+        <v/>
+      </c>
+      <c r="F410" s="81">
+        <f>'Towers'!$C$23+E410</f>
+        <v/>
+      </c>
+      <c r="G410" s="81" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H410" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I410" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J410" s="81">
+        <f>'Towers'!$G$23*G410*H410*I410</f>
+        <v/>
+      </c>
+      <c r="K410" s="81">
+        <f>IF(J410=0,0,F410/J410)</f>
+        <v/>
+      </c>
+      <c r="L410" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M410" s="81" t="inlineStr">
+        <is>
+          <t>Heavier Rock</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B411" s="81" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="C411" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D411" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E411" s="81">
+        <f>ROUND('Towers'!$C$23*POWER('Tuning'!$B$12,D411),0)</f>
+        <v/>
+      </c>
+      <c r="F411" s="81">
+        <f>F410+E411</f>
+        <v/>
+      </c>
+      <c r="G411" s="81" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H411" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I411" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J411" s="81">
+        <f>'Towers'!$G$23*G411*H411*I411</f>
+        <v/>
+      </c>
+      <c r="K411" s="81">
+        <f>IF(J411=0,0,F411/J411)</f>
+        <v/>
+      </c>
+      <c r="L411" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M411" s="81" t="inlineStr">
+        <is>
+          <t>Iron Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B412" s="81" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="C412" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D412" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E412" s="81">
+        <f>ROUND('Towers'!$C$23*POWER('Tuning'!$B$12,D412),0)</f>
+        <v/>
+      </c>
+      <c r="F412" s="81">
+        <f>F411+E412</f>
+        <v/>
+      </c>
+      <c r="G412" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="H412" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I412" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J412" s="81">
+        <f>'Towers'!$G$23*G412*H412*I412</f>
+        <v/>
+      </c>
+      <c r="K412" s="81">
+        <f>IF(J412=0,0,F412/J412)</f>
+        <v/>
+      </c>
+      <c r="L412" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M412" s="81" t="inlineStr">
+        <is>
+          <t>Ground Zero</t>
+        </is>
+      </c>
+      <c r="BJ412" s="81" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B413" s="81" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="C413" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D413" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E413" s="81">
+        <f>ROUND('Towers'!$C$23*POWER('Tuning'!$B$12,D413),0)</f>
+        <v/>
+      </c>
+      <c r="F413" s="81">
+        <f>F412+E413</f>
+        <v/>
+      </c>
+      <c r="G413" s="81" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H413" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I413" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J413" s="81">
+        <f>J412*G413*H413*I413</f>
+        <v/>
+      </c>
+      <c r="K413" s="81">
+        <f>IF(J413=0,0,F413/J413)</f>
+        <v/>
+      </c>
+      <c r="L413" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M413" s="81" t="inlineStr">
+        <is>
+          <t>Planet Killer</t>
+        </is>
+      </c>
+      <c r="P413" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ413" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI413" s="81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ413" s="81" t="inlineStr">
+        <is>
+          <t>Breaks 3, ×2 on bosses</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B414" s="81" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="C414" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D414" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E414" s="81">
+        <f>ROUND('Towers'!$C$23*POWER('Tuning'!$B$12,D414),0)</f>
+        <v/>
+      </c>
+      <c r="F414" s="81">
+        <f>F413+E414</f>
+        <v/>
+      </c>
+      <c r="G414" s="81" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H414" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I414" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J414" s="81">
+        <f>J413*G414*H414*I414</f>
+        <v/>
+      </c>
+      <c r="K414" s="81">
+        <f>IF(J414=0,0,F414/J414)</f>
+        <v/>
+      </c>
+      <c r="L414" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M414" s="81" t="inlineStr">
+        <is>
+          <t>Extinction Event</t>
+        </is>
+      </c>
+      <c r="CI414" s="81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ414" s="81" t="inlineStr">
+        <is>
+          <t>One giant meteor a round, fires itself</t>
+        </is>
+      </c>
+      <c r="FW414" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B415" s="81" t="inlineStr">
+        <is>
+          <t>Sky Rocks</t>
+        </is>
+      </c>
+      <c r="C415" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D415" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E415" s="81">
+        <f>ROUND('Towers'!$C$23*POWER('Tuning'!$B$12,D415),0)</f>
+        <v/>
+      </c>
+      <c r="F415" s="81">
+        <f>'Towers'!$C$23+E415</f>
+        <v/>
+      </c>
+      <c r="G415" s="81" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H415" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I415" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J415" s="81">
+        <f>'Towers'!$G$23*G415*H415*I415</f>
+        <v/>
+      </c>
+      <c r="K415" s="81">
+        <f>IF(J415=0,0,F415/J415)</f>
+        <v/>
+      </c>
+      <c r="L415" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M415" s="81" t="inlineStr">
+        <is>
+          <t>Rock Chunks</t>
+        </is>
+      </c>
+      <c r="FM415" s="81" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B416" s="81" t="inlineStr">
+        <is>
+          <t>Sky Rocks</t>
+        </is>
+      </c>
+      <c r="C416" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D416" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E416" s="81">
+        <f>ROUND('Towers'!$C$23*POWER('Tuning'!$B$12,D416),0)</f>
+        <v/>
+      </c>
+      <c r="F416" s="81">
+        <f>F415+E416</f>
+        <v/>
+      </c>
+      <c r="G416" s="81" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H416" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I416" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J416" s="81">
+        <f>'Towers'!$G$23*G416*H416*I416</f>
+        <v/>
+      </c>
+      <c r="K416" s="81">
+        <f>IF(J416=0,0,F416/J416)</f>
+        <v/>
+      </c>
+      <c r="L416" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M416" s="81" t="inlineStr">
+        <is>
+          <t>Twin Fall</t>
+        </is>
+      </c>
+      <c r="FM416" s="81" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B417" s="81" t="inlineStr">
+        <is>
+          <t>Sky Rocks</t>
+        </is>
+      </c>
+      <c r="C417" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D417" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E417" s="81">
+        <f>ROUND('Towers'!$C$23*POWER('Tuning'!$B$12,D417),0)</f>
+        <v/>
+      </c>
+      <c r="F417" s="81">
+        <f>F416+E417</f>
+        <v/>
+      </c>
+      <c r="G417" s="81" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H417" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I417" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J417" s="81">
+        <f>'Towers'!$G$23*G417*H417*I417</f>
+        <v/>
+      </c>
+      <c r="K417" s="81">
+        <f>IF(J417=0,0,F417/J417)</f>
+        <v/>
+      </c>
+      <c r="L417" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M417" s="81" t="inlineStr">
+        <is>
+          <t>Fireball Flurry</t>
+        </is>
+      </c>
+      <c r="FM417" s="81" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B418" s="81" t="inlineStr">
+        <is>
+          <t>Sky Rocks</t>
+        </is>
+      </c>
+      <c r="C418" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D418" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E418" s="81">
+        <f>ROUND('Towers'!$C$23*POWER('Tuning'!$B$12,D418),0)</f>
+        <v/>
+      </c>
+      <c r="F418" s="81">
+        <f>F417+E418</f>
+        <v/>
+      </c>
+      <c r="G418" s="81" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H418" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I418" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J418" s="81">
+        <f>J417*G418*H418*I418</f>
+        <v/>
+      </c>
+      <c r="K418" s="81">
+        <f>IF(J418=0,0,F418/J418)</f>
+        <v/>
+      </c>
+      <c r="L418" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M418" s="81" t="inlineStr">
+        <is>
+          <t>Endless Rain</t>
+        </is>
+      </c>
+      <c r="CI418" s="81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ418" s="81" t="inlineStr">
+        <is>
+          <t>A small meteor every 4 s</t>
+        </is>
+      </c>
+      <c r="FO418" s="81" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B419" s="81" t="inlineStr">
+        <is>
+          <t>Sky Rocks</t>
+        </is>
+      </c>
+      <c r="C419" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D419" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E419" s="81">
+        <f>ROUND('Towers'!$C$23*POWER('Tuning'!$B$12,D419),0)</f>
+        <v/>
+      </c>
+      <c r="F419" s="81">
+        <f>F418+E419</f>
+        <v/>
+      </c>
+      <c r="G419" s="81" t="n">
+        <v>3.388</v>
+      </c>
+      <c r="H419" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I419" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J419" s="81">
+        <f>J418*G419*H419*I419</f>
+        <v/>
+      </c>
+      <c r="K419" s="81">
+        <f>IF(J419=0,0,F419/J419)</f>
+        <v/>
+      </c>
+      <c r="L419" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M419" s="81" t="inlineStr">
+        <is>
+          <t>Starfall</t>
+        </is>
+      </c>
+      <c r="CI419" s="81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ419" s="81" t="inlineStr">
+        <is>
+          <t>20 meteors across your side every 15 s</t>
+        </is>
+      </c>
+      <c r="FP419" s="81" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B420" s="81" t="inlineStr">
+        <is>
+          <t>Aftermath</t>
+        </is>
+      </c>
+      <c r="C420" s="81" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D420" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E420" s="81">
+        <f>ROUND('Towers'!$C$23*POWER('Tuning'!$B$12,D420),0)</f>
+        <v/>
+      </c>
+      <c r="F420" s="81">
+        <f>'Towers'!$C$23+E420</f>
+        <v/>
+      </c>
+      <c r="G420" s="81" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H420" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I420" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J420" s="81">
+        <f>'Towers'!$G$23*G420*H420*I420</f>
+        <v/>
+      </c>
+      <c r="K420" s="81">
+        <f>IF(J420=0,0,F420/J420)</f>
+        <v/>
+      </c>
+      <c r="L420" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M420" s="81" t="inlineStr">
+        <is>
+          <t>Hot Crater</t>
+        </is>
+      </c>
+      <c r="X420" s="81" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B421" s="81" t="inlineStr">
+        <is>
+          <t>Aftermath</t>
+        </is>
+      </c>
+      <c r="C421" s="81" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D421" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E421" s="81">
+        <f>ROUND('Towers'!$C$23*POWER('Tuning'!$B$12,D421),0)</f>
+        <v/>
+      </c>
+      <c r="F421" s="81">
+        <f>F420+E421</f>
+        <v/>
+      </c>
+      <c r="G421" s="81" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H421" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I421" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J421" s="81">
+        <f>'Towers'!$G$23*G421*H421*I421</f>
+        <v/>
+      </c>
+      <c r="K421" s="81">
+        <f>IF(J421=0,0,F421/J421)</f>
+        <v/>
+      </c>
+      <c r="L421" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M421" s="81" t="inlineStr">
+        <is>
+          <t>Ash Cloud</t>
+        </is>
+      </c>
+      <c r="X421" s="81" t="n">
+        <v>20</v>
+      </c>
+      <c r="FH421" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="FS421" s="81" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B422" s="81" t="inlineStr">
+        <is>
+          <t>Aftermath</t>
+        </is>
+      </c>
+      <c r="C422" s="81" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D422" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E422" s="81">
+        <f>ROUND('Towers'!$C$23*POWER('Tuning'!$B$12,D422),0)</f>
+        <v/>
+      </c>
+      <c r="F422" s="81">
+        <f>F421+E422</f>
+        <v/>
+      </c>
+      <c r="G422" s="81" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H422" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I422" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J422" s="81">
+        <f>'Towers'!$G$23*G422*H422*I422</f>
+        <v/>
+      </c>
+      <c r="K422" s="81">
+        <f>IF(J422=0,0,F422/J422)</f>
+        <v/>
+      </c>
+      <c r="L422" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M422" s="81" t="inlineStr">
+        <is>
+          <t>Shockwave Ring</t>
+        </is>
+      </c>
+      <c r="W422" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="X422" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="FH422" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="FS422" s="81" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B423" s="81" t="inlineStr">
+        <is>
+          <t>Aftermath</t>
+        </is>
+      </c>
+      <c r="C423" s="81" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D423" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E423" s="81">
+        <f>ROUND('Towers'!$C$23*POWER('Tuning'!$B$12,D423),0)</f>
+        <v/>
+      </c>
+      <c r="F423" s="81">
+        <f>F422+E423</f>
+        <v/>
+      </c>
+      <c r="G423" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H423" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I423" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J423" s="81">
+        <f>J422*G423*H423*I423</f>
+        <v/>
+      </c>
+      <c r="K423" s="81">
+        <f>IF(J423=0,0,F423/J423)</f>
+        <v/>
+      </c>
+      <c r="L423" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M423" s="81" t="inlineStr">
+        <is>
+          <t>Long Burn</t>
+        </is>
+      </c>
+      <c r="X423" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="CI423" s="81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ423" s="81" t="inlineStr">
+        <is>
+          <t>Craters last 8 s, hotter</t>
+        </is>
+      </c>
+      <c r="FQ423" s="81" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B424" s="81" t="inlineStr">
+        <is>
+          <t>Aftermath</t>
+        </is>
+      </c>
+      <c r="C424" s="81" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D424" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E424" s="81">
+        <f>ROUND('Towers'!$C$23*POWER('Tuning'!$B$12,D424),0)</f>
+        <v/>
+      </c>
+      <c r="F424" s="81">
+        <f>F423+E424</f>
+        <v/>
+      </c>
+      <c r="G424" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H424" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I424" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J424" s="81">
+        <f>J423*G424*H424*I424</f>
+        <v/>
+      </c>
+      <c r="K424" s="81">
+        <f>IF(J424=0,0,F424/J424)</f>
+        <v/>
+      </c>
+      <c r="L424" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M424" s="81" t="inlineStr">
+        <is>
+          <t>Fire Line</t>
+        </is>
+      </c>
+      <c r="X424" s="81" t="n">
+        <v>54</v>
+      </c>
+      <c r="CI424" s="81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ424" s="81" t="inlineStr">
+        <is>
+          <t>Craters join into one burning strip</t>
+        </is>
+      </c>
+      <c r="FU424" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B425" s="81" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="C425" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D425" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E425" s="81">
+        <f>E413</f>
+        <v/>
+      </c>
+      <c r="F425" s="81">
+        <f>F413</f>
+        <v/>
+      </c>
+      <c r="G425" s="81" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H425" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I425" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L425" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M425" s="81" t="inlineStr">
+        <is>
+          <t>Plate Cracker</t>
+        </is>
+      </c>
+      <c r="N425" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CI425" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ425" s="81" t="inlineStr">
+        <is>
+          <t>Meteors cut through armour</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B426" s="81" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="C426" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D426" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E426" s="81">
+        <f>E413</f>
+        <v/>
+      </c>
+      <c r="F426" s="81">
+        <f>F413</f>
+        <v/>
+      </c>
+      <c r="G426" s="81" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H426" s="81" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I426" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L426" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M426" s="81" t="inlineStr">
+        <is>
+          <t>Quick Call</t>
+        </is>
+      </c>
+      <c r="CI426" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ426" s="81" t="inlineStr">
+        <is>
+          <t>Meteors fall 50% more often</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B427" s="81" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="C427" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D427" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E427" s="81">
+        <f>E414</f>
+        <v/>
+      </c>
+      <c r="F427" s="81">
+        <f>F414</f>
+        <v/>
+      </c>
+      <c r="G427" s="81" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H427" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I427" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L427" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M427" s="81" t="inlineStr">
+        <is>
+          <t>Dino Killer</t>
+        </is>
+      </c>
+      <c r="CI427" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ427" s="81" t="inlineStr">
+        <is>
+          <t>Breaks the biggest dino it hits 2 extra sizes</t>
+        </is>
+      </c>
+      <c r="FZ427" s="81" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B428" s="81" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="C428" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D428" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E428" s="81">
+        <f>E414</f>
+        <v/>
+      </c>
+      <c r="F428" s="81">
+        <f>F414</f>
+        <v/>
+      </c>
+      <c r="G428" s="81" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H428" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I428" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L428" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M428" s="81" t="inlineStr">
+        <is>
+          <t>Impact Winter</t>
+        </is>
+      </c>
+      <c r="CI428" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ428" s="81" t="inlineStr">
+        <is>
+          <t>Every dino on your side slowed after each hit</t>
+        </is>
+      </c>
+      <c r="FX428" s="81" t="n">
+        <v>30</v>
+      </c>
+      <c r="FY428" s="81" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B429" s="81" t="inlineStr">
+        <is>
+          <t>Sky Rocks</t>
+        </is>
+      </c>
+      <c r="C429" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D429" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E429" s="81">
+        <f>E418</f>
+        <v/>
+      </c>
+      <c r="F429" s="81">
+        <f>F418</f>
+        <v/>
+      </c>
+      <c r="G429" s="81" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H429" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I429" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L429" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M429" s="81" t="inlineStr">
+        <is>
+          <t>Scatter Field</t>
+        </is>
+      </c>
+      <c r="CI429" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ429" s="81" t="inlineStr">
+        <is>
+          <t>Meteors land all along the track</t>
+        </is>
+      </c>
+      <c r="FN429" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B430" s="81" t="inlineStr">
+        <is>
+          <t>Sky Rocks</t>
+        </is>
+      </c>
+      <c r="C430" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D430" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E430" s="81">
+        <f>E418</f>
+        <v/>
+      </c>
+      <c r="F430" s="81">
+        <f>F418</f>
+        <v/>
+      </c>
+      <c r="G430" s="81" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H430" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I430" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L430" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M430" s="81" t="inlineStr">
+        <is>
+          <t>Cinder Trail</t>
+        </is>
+      </c>
+      <c r="X430" s="81" t="n">
+        <v>20</v>
+      </c>
+      <c r="CI430" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ430" s="81" t="inlineStr">
+        <is>
+          <t>Small meteors leave a burning streak</t>
+        </is>
+      </c>
+      <c r="FV430" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B431" s="81" t="inlineStr">
+        <is>
+          <t>Sky Rocks</t>
+        </is>
+      </c>
+      <c r="C431" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D431" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E431" s="81">
+        <f>E419</f>
+        <v/>
+      </c>
+      <c r="F431" s="81">
+        <f>F419</f>
+        <v/>
+      </c>
+      <c r="G431" s="81" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H431" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I431" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L431" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M431" s="81" t="inlineStr">
+        <is>
+          <t>Comet Tail</t>
+        </is>
+      </c>
+      <c r="CI431" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ431" s="81" t="inlineStr">
+        <is>
+          <t>A comet sweeps the whole track once a round</t>
+        </is>
+      </c>
+      <c r="CS431" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="FK431" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B432" s="81" t="inlineStr">
+        <is>
+          <t>Sky Rocks</t>
+        </is>
+      </c>
+      <c r="C432" s="81" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D432" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E432" s="81">
+        <f>E419</f>
+        <v/>
+      </c>
+      <c r="F432" s="81">
+        <f>F419</f>
+        <v/>
+      </c>
+      <c r="G432" s="81" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H432" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I432" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L432" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M432" s="81" t="inlineStr">
+        <is>
+          <t>Shooting Stars</t>
+        </is>
+      </c>
+      <c r="CI432" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ432" s="81" t="inlineStr">
+        <is>
+          <t>Meteors can hit flyers</t>
+        </is>
+      </c>
+      <c r="DW432" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B433" s="81" t="inlineStr">
+        <is>
+          <t>Aftermath</t>
+        </is>
+      </c>
+      <c r="C433" s="81" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D433" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E433" s="81">
+        <f>E423</f>
+        <v/>
+      </c>
+      <c r="F433" s="81">
+        <f>F423</f>
+        <v/>
+      </c>
+      <c r="G433" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H433" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I433" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L433" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M433" s="81" t="inlineStr">
+        <is>
+          <t>Glass Crater</t>
+        </is>
+      </c>
+      <c r="X433" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM433" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CI433" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ433" s="81" t="inlineStr">
+        <is>
+          <t>Craters strip armour</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B434" s="81" t="inlineStr">
+        <is>
+          <t>Aftermath</t>
+        </is>
+      </c>
+      <c r="C434" s="81" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D434" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E434" s="81">
+        <f>E423</f>
+        <v/>
+      </c>
+      <c r="F434" s="81">
+        <f>F423</f>
+        <v/>
+      </c>
+      <c r="G434" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H434" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I434" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L434" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M434" s="81" t="inlineStr">
+        <is>
+          <t>Scorch Marks</t>
+        </is>
+      </c>
+      <c r="X434" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="CI434" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ434" s="81" t="inlineStr">
+        <is>
+          <t>Dinos crossing a crater take +15%</t>
+        </is>
+      </c>
+      <c r="FR434" s="81" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B435" s="81" t="inlineStr">
+        <is>
+          <t>Aftermath</t>
+        </is>
+      </c>
+      <c r="C435" s="81" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D435" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E435" s="81">
+        <f>E424</f>
+        <v/>
+      </c>
+      <c r="F435" s="81">
+        <f>F424</f>
+        <v/>
+      </c>
+      <c r="G435" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H435" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I435" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L435" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M435" s="81" t="inlineStr">
+        <is>
+          <t>Blinding Dust</t>
+        </is>
+      </c>
+      <c r="X435" s="81" t="n">
+        <v>55</v>
+      </c>
+      <c r="CI435" s="81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ435" s="81" t="inlineStr">
+        <is>
+          <t>Dinos in the ash can't bite or throw</t>
+        </is>
+      </c>
+      <c r="FH435" s="81" t="n">
+        <v>100</v>
+      </c>
+      <c r="FS435" s="81" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="81" t="inlineStr">
+        <is>
+          <t>Meteor Beacon</t>
+        </is>
+      </c>
+      <c r="B436" s="81" t="inlineStr">
+        <is>
+          <t>Aftermath</t>
+        </is>
+      </c>
+      <c r="C436" s="81" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D436" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E436" s="81">
+        <f>E424</f>
+        <v/>
+      </c>
+      <c r="F436" s="81">
+        <f>F424</f>
+        <v/>
+      </c>
+      <c r="G436" s="81" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H436" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I436" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L436" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M436" s="81" t="inlineStr">
+        <is>
+          <t>New Ice Age</t>
+        </is>
+      </c>
+      <c r="CI436" s="81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ436" s="81" t="inlineStr">
+        <is>
+          <t>Craters freeze dinos solid for 2 s</t>
+        </is>
+      </c>
+      <c r="FT436" s="81" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Storm-Split-Balance.xlsx
+++ b/Storm-Split-Balance.xlsx
@@ -9500,7 +9500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E266"/>
+  <dimension ref="A1:E281"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="81" min="1" max="1"/>
@@ -10178,6 +10178,7 @@
       </c>
       <c r="E38" s="17" t="n"/>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="31" t="inlineStr">
         <is>
@@ -10248,6 +10249,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="31" t="inlineStr">
         <is>
@@ -10398,6 +10400,7 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
         <is>
@@ -10448,6 +10451,7 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="31" t="inlineStr">
         <is>
@@ -10518,6 +10522,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
@@ -10568,6 +10573,7 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
@@ -10758,6 +10764,7 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
@@ -10905,6 +10912,7 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" s="31" t="inlineStr">
         <is>
@@ -11012,6 +11020,7 @@
         </is>
       </c>
     </row>
+    <row r="93"/>
     <row r="94" s="90">
       <c r="A94" s="31" t="inlineStr">
         <is>
@@ -11039,6 +11048,7 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" s="31" t="inlineStr">
         <is>
@@ -11066,6 +11076,7 @@
         </is>
       </c>
     </row>
+    <row r="99"/>
     <row r="100">
       <c r="A100" s="99" t="inlineStr">
         <is>
@@ -11113,6 +11124,7 @@
         </is>
       </c>
     </row>
+    <row r="103"/>
     <row r="104">
       <c r="A104" s="99" t="inlineStr">
         <is>
@@ -11203,6 +11215,7 @@
         </is>
       </c>
     </row>
+    <row r="109"/>
     <row r="110">
       <c r="A110" s="99" t="inlineStr">
         <is>
@@ -11385,6 +11398,7 @@
         </is>
       </c>
     </row>
+    <row r="123"/>
     <row r="124">
       <c r="A124" s="99" t="inlineStr">
         <is>
@@ -11438,6 +11452,7 @@
         </is>
       </c>
     </row>
+    <row r="128"/>
     <row r="129">
       <c r="A129" s="99" t="inlineStr">
         <is>
@@ -11577,6 +11592,7 @@
         </is>
       </c>
     </row>
+    <row r="140"/>
     <row r="141">
       <c r="A141" s="99" t="inlineStr">
         <is>
@@ -12319,6 +12335,7 @@
         </is>
       </c>
     </row>
+    <row r="191"/>
     <row r="192">
       <c r="A192" s="81" t="inlineStr">
         <is>
@@ -12431,6 +12448,7 @@
         </is>
       </c>
     </row>
+    <row r="200"/>
     <row r="201">
       <c r="A201" s="81" t="inlineStr">
         <is>
@@ -12835,6 +12853,7 @@
         </is>
       </c>
     </row>
+    <row r="229"/>
     <row r="230">
       <c r="A230" s="81" t="inlineStr">
         <is>
@@ -13022,6 +13041,7 @@
         </is>
       </c>
     </row>
+    <row r="243"/>
     <row r="244">
       <c r="A244" s="81" t="inlineStr">
         <is>
@@ -13134,6 +13154,7 @@
         </is>
       </c>
     </row>
+    <row r="252"/>
     <row r="253">
       <c r="A253" s="81" t="inlineStr">
         <is>
@@ -13333,6 +13354,208 @@
       <c r="C266" s="81" t="inlineStr">
         <is>
           <t>Cinder Trail: each small meteor leaves a burning strip this long for 3 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>VOLCANO VENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Flow length (studs)</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>24</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>studs of track a Volcano Vent's lava covers, centred on the track point nearest it (x Flow length x; Shared/Vent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Flow (s)</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>6</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>s the lava stays down when the build sets no Flow (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Flow burn DPS</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>8</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>lava burn a second on each dino in it (x Damage x x the team's level)</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Flow shove (studs/s)</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>3</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>studs a second the lava shoves a dino off its path (not a slow; bosses aren't shoved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Shove max (studs)</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>4</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>the furthest the lava shoves a dino off its path (it walks back after the flow)</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Geyser x</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>x the eruption's damage for a Geyser burst between eruptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Crust (s)</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>6</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>s a flow's stretch stays crust after the lava (Obsidian)</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Crust slow %</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>30</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>dinos on the crust are slowed this much</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Lava bomb x</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>x the eruption's damage for each Lava Bombs bomb</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Lava bombs</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>6</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>bombs Lava Bombs throws at the biggest dinos in range each eruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Extra vent x</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Ring of Fire: each small vent's eruption, x the main one's size</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Supervolcano (s)</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>4</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Supervolcano: once per round played every dino on your side is in lava this long</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Ash (s)</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>5</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Ash Blanket: s the ash after each eruption makes dinos on your side miss throws</t>
         </is>
       </c>
     </row>
@@ -13356,7 +13579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:AA24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -13559,6 +13782,11 @@
           <t>Walkers</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Near track (studs)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.65" customHeight="1" s="90">
       <c r="A5" s="43" t="inlineStr">
@@ -14692,6 +14920,76 @@
       </c>
       <c r="R23" s="81" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Lava on one stretch of track: burns, shoves, crust</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>600</v>
+      </c>
+      <c r="D24" t="n">
+        <v>30</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24">
+        <f>D24*E24*F24</f>
+        <v/>
+      </c>
+      <c r="H24" t="n">
+        <v>20</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Erupts every 12 s: lava floods its stretch of track for 6 s; dinos burn and are shoved aside.</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>600</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>VENT</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -14714,7 +15012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FZ436"/>
+  <dimension ref="A1:GN463"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="81" min="1" max="1"/>
@@ -15762,6 +16060,76 @@
       <c r="FZ4" s="81" t="inlineStr">
         <is>
           <t>Biggest breaks +</t>
+        </is>
+      </c>
+      <c r="GA4" t="inlineStr">
+        <is>
+          <t>Flow (s)</t>
+        </is>
+      </c>
+      <c r="GB4" t="inlineStr">
+        <is>
+          <t>Flow length x</t>
+        </is>
+      </c>
+      <c r="GC4" t="inlineStr">
+        <is>
+          <t>Burn breaks</t>
+        </is>
+      </c>
+      <c r="GD4" t="inlineStr">
+        <is>
+          <t>Geyser every (s)</t>
+        </is>
+      </c>
+      <c r="GE4" t="inlineStr">
+        <is>
+          <t>Extra vents</t>
+        </is>
+      </c>
+      <c r="GF4" t="inlineStr">
+        <is>
+          <t>Lava bombs</t>
+        </is>
+      </c>
+      <c r="GG4" t="inlineStr">
+        <is>
+          <t>Boss erupt</t>
+        </is>
+      </c>
+      <c r="GH4" t="inlineStr">
+        <is>
+          <t>Side throw miss %</t>
+        </is>
+      </c>
+      <c r="GI4" t="inlineStr">
+        <is>
+          <t>Supervolcano</t>
+        </is>
+      </c>
+      <c r="GJ4" t="inlineStr">
+        <is>
+          <t>Crust</t>
+        </is>
+      </c>
+      <c r="GK4" t="inlineStr">
+        <is>
+          <t>Crust DPS</t>
+        </is>
+      </c>
+      <c r="GL4" t="inlineStr">
+        <is>
+          <t>Maze (studs)</t>
+        </is>
+      </c>
+      <c r="GM4" t="inlineStr">
+        <is>
+          <t>Freeze flow (s)</t>
+        </is>
+      </c>
+      <c r="GN4" t="inlineStr">
+        <is>
+          <t>Throw resist %</t>
         </is>
       </c>
     </row>
@@ -47184,6 +47552,1630 @@
         </is>
       </c>
       <c r="FT436" s="81" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Magma</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>1</v>
+      </c>
+      <c r="E437">
+        <f>ROUND('Towers'!$C$24*POWER('Tuning'!$B$12,D437),0)</f>
+        <v/>
+      </c>
+      <c r="F437">
+        <f>'Towers'!$C$24+E437</f>
+        <v/>
+      </c>
+      <c r="G437" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H437" t="n">
+        <v>1</v>
+      </c>
+      <c r="I437" t="n">
+        <v>1</v>
+      </c>
+      <c r="J437">
+        <f>'Towers'!$G$24*G437*H437*I437</f>
+        <v/>
+      </c>
+      <c r="K437">
+        <f>IF(J437=0,0,F437/J437)</f>
+        <v/>
+      </c>
+      <c r="L437" t="n">
+        <v>1</v>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>Hot Rock</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Magma</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>2</v>
+      </c>
+      <c r="E438">
+        <f>ROUND('Towers'!$C$24*POWER('Tuning'!$B$12,D438),0)</f>
+        <v/>
+      </c>
+      <c r="F438">
+        <f>F437+E438</f>
+        <v/>
+      </c>
+      <c r="G438" t="n">
+        <v>3</v>
+      </c>
+      <c r="H438" t="n">
+        <v>1</v>
+      </c>
+      <c r="I438" t="n">
+        <v>1</v>
+      </c>
+      <c r="J438">
+        <f>'Towers'!$G$24*G438*H438*I438</f>
+        <v/>
+      </c>
+      <c r="K438">
+        <f>IF(J438=0,0,F438/J438)</f>
+        <v/>
+      </c>
+      <c r="L438" t="n">
+        <v>1</v>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>Searing Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Magma</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>3</v>
+      </c>
+      <c r="E439">
+        <f>ROUND('Towers'!$C$24*POWER('Tuning'!$B$12,D439),0)</f>
+        <v/>
+      </c>
+      <c r="F439">
+        <f>F438+E439</f>
+        <v/>
+      </c>
+      <c r="G439" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H439" t="n">
+        <v>1</v>
+      </c>
+      <c r="I439" t="n">
+        <v>1</v>
+      </c>
+      <c r="J439">
+        <f>'Towers'!$G$24*G439*H439*I439</f>
+        <v/>
+      </c>
+      <c r="K439">
+        <f>IF(J439=0,0,F439/J439)</f>
+        <v/>
+      </c>
+      <c r="L439" t="n">
+        <v>1</v>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>Lava Lake</t>
+        </is>
+      </c>
+      <c r="GA439" t="n">
+        <v>10</v>
+      </c>
+      <c r="GC439" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Magma</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>4</v>
+      </c>
+      <c r="E440">
+        <f>ROUND('Towers'!$C$24*POWER('Tuning'!$B$12,D440),0)</f>
+        <v/>
+      </c>
+      <c r="F440">
+        <f>F439+E440</f>
+        <v/>
+      </c>
+      <c r="G440" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H440" t="n">
+        <v>1</v>
+      </c>
+      <c r="I440" t="n">
+        <v>1</v>
+      </c>
+      <c r="J440">
+        <f>J439*G440*H440*I440</f>
+        <v/>
+      </c>
+      <c r="K440">
+        <f>IF(J440=0,0,F440/J440)</f>
+        <v/>
+      </c>
+      <c r="L440" t="n">
+        <v>1</v>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>White Hot</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CI440" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ440" t="inlineStr">
+        <is>
+          <t>Lava melts armour</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Magma</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>5</v>
+      </c>
+      <c r="E441">
+        <f>ROUND('Towers'!$C$24*POWER('Tuning'!$B$12,D441),0)</f>
+        <v/>
+      </c>
+      <c r="F441">
+        <f>F440+E441</f>
+        <v/>
+      </c>
+      <c r="G441" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H441" t="n">
+        <v>1</v>
+      </c>
+      <c r="I441" t="n">
+        <v>1</v>
+      </c>
+      <c r="J441">
+        <f>J440*G441*H441*I441</f>
+        <v/>
+      </c>
+      <c r="K441">
+        <f>IF(J441=0,0,F441/J441)</f>
+        <v/>
+      </c>
+      <c r="L441" t="n">
+        <v>1</v>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>Supervolcano</t>
+        </is>
+      </c>
+      <c r="CI441" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ441" t="inlineStr">
+        <is>
+          <t>Floods the whole track once a round</t>
+        </is>
+      </c>
+      <c r="GI441" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Pressure</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>1</v>
+      </c>
+      <c r="E442">
+        <f>ROUND('Towers'!$C$24*POWER('Tuning'!$B$12,D442),0)</f>
+        <v/>
+      </c>
+      <c r="F442">
+        <f>'Towers'!$C$24+E442</f>
+        <v/>
+      </c>
+      <c r="G442" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H442" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I442" t="n">
+        <v>1</v>
+      </c>
+      <c r="J442">
+        <f>'Towers'!$G$24*G442*H442*I442</f>
+        <v/>
+      </c>
+      <c r="K442">
+        <f>IF(J442=0,0,F442/J442)</f>
+        <v/>
+      </c>
+      <c r="L442" t="n">
+        <v>1</v>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>Shorter Fuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Pressure</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>2</v>
+      </c>
+      <c r="E443">
+        <f>ROUND('Towers'!$C$24*POWER('Tuning'!$B$12,D443),0)</f>
+        <v/>
+      </c>
+      <c r="F443">
+        <f>F442+E443</f>
+        <v/>
+      </c>
+      <c r="G443" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H443" t="n">
+        <v>2</v>
+      </c>
+      <c r="I443" t="n">
+        <v>1</v>
+      </c>
+      <c r="J443">
+        <f>'Towers'!$G$24*G443*H443*I443</f>
+        <v/>
+      </c>
+      <c r="K443">
+        <f>IF(J443=0,0,F443/J443)</f>
+        <v/>
+      </c>
+      <c r="L443" t="n">
+        <v>1</v>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>Twin Vents</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Pressure</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>3</v>
+      </c>
+      <c r="E444">
+        <f>ROUND('Towers'!$C$24*POWER('Tuning'!$B$12,D444),0)</f>
+        <v/>
+      </c>
+      <c r="F444">
+        <f>F443+E444</f>
+        <v/>
+      </c>
+      <c r="G444" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H444" t="n">
+        <v>2</v>
+      </c>
+      <c r="I444" t="n">
+        <v>1</v>
+      </c>
+      <c r="J444">
+        <f>'Towers'!$G$24*G444*H444*I444</f>
+        <v/>
+      </c>
+      <c r="K444">
+        <f>IF(J444=0,0,F444/J444)</f>
+        <v/>
+      </c>
+      <c r="L444" t="n">
+        <v>1</v>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>Geyser</t>
+        </is>
+      </c>
+      <c r="GD444" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Pressure</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>4</v>
+      </c>
+      <c r="E445">
+        <f>ROUND('Towers'!$C$24*POWER('Tuning'!$B$12,D445),0)</f>
+        <v/>
+      </c>
+      <c r="F445">
+        <f>F444+E445</f>
+        <v/>
+      </c>
+      <c r="G445" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H445" t="n">
+        <v>1</v>
+      </c>
+      <c r="I445" t="n">
+        <v>1</v>
+      </c>
+      <c r="J445">
+        <f>J444*G445*H445*I445</f>
+        <v/>
+      </c>
+      <c r="K445">
+        <f>IF(J445=0,0,F445/J445)</f>
+        <v/>
+      </c>
+      <c r="L445" t="n">
+        <v>1</v>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>Steam Burst</t>
+        </is>
+      </c>
+      <c r="W445" t="n">
+        <v>6</v>
+      </c>
+      <c r="CI445" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ445" t="inlineStr">
+        <is>
+          <t>Eruptions knock small dinos back</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Pressure</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>5</v>
+      </c>
+      <c r="E446">
+        <f>ROUND('Towers'!$C$24*POWER('Tuning'!$B$12,D446),0)</f>
+        <v/>
+      </c>
+      <c r="F446">
+        <f>F445+E446</f>
+        <v/>
+      </c>
+      <c r="G446" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H446" t="n">
+        <v>1</v>
+      </c>
+      <c r="I446" t="n">
+        <v>1</v>
+      </c>
+      <c r="J446">
+        <f>J445*G446*H446*I446</f>
+        <v/>
+      </c>
+      <c r="K446">
+        <f>IF(J446=0,0,F446/J446)</f>
+        <v/>
+      </c>
+      <c r="L446" t="n">
+        <v>1</v>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>Ring of Fire</t>
+        </is>
+      </c>
+      <c r="CI446" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ446" t="inlineStr">
+        <is>
+          <t>3 small vents erupt in turn</t>
+        </is>
+      </c>
+      <c r="GE446" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Obsidian</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>1</v>
+      </c>
+      <c r="E447">
+        <f>ROUND('Towers'!$C$24*POWER('Tuning'!$B$12,D447),0)</f>
+        <v/>
+      </c>
+      <c r="F447">
+        <f>'Towers'!$C$24+E447</f>
+        <v/>
+      </c>
+      <c r="G447" t="n">
+        <v>1</v>
+      </c>
+      <c r="H447" t="n">
+        <v>1</v>
+      </c>
+      <c r="I447" t="n">
+        <v>1</v>
+      </c>
+      <c r="J447">
+        <f>'Towers'!$G$24*G447*H447*I447</f>
+        <v/>
+      </c>
+      <c r="K447">
+        <f>IF(J447=0,0,F447/J447)</f>
+        <v/>
+      </c>
+      <c r="L447" t="n">
+        <v>1</v>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>Cooling Crust</t>
+        </is>
+      </c>
+      <c r="GJ447" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Obsidian</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>2</v>
+      </c>
+      <c r="E448">
+        <f>ROUND('Towers'!$C$24*POWER('Tuning'!$B$12,D448),0)</f>
+        <v/>
+      </c>
+      <c r="F448">
+        <f>F447+E448</f>
+        <v/>
+      </c>
+      <c r="G448" t="n">
+        <v>1</v>
+      </c>
+      <c r="H448" t="n">
+        <v>1</v>
+      </c>
+      <c r="I448" t="n">
+        <v>1</v>
+      </c>
+      <c r="J448">
+        <f>'Towers'!$G$24*G448*H448*I448</f>
+        <v/>
+      </c>
+      <c r="K448">
+        <f>IF(J448=0,0,F448/J448)</f>
+        <v/>
+      </c>
+      <c r="L448" t="n">
+        <v>1</v>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>Sharp Glass</t>
+        </is>
+      </c>
+      <c r="AM448" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GJ448" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Obsidian</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>3</v>
+      </c>
+      <c r="E449">
+        <f>ROUND('Towers'!$C$24*POWER('Tuning'!$B$12,D449),0)</f>
+        <v/>
+      </c>
+      <c r="F449">
+        <f>F448+E449</f>
+        <v/>
+      </c>
+      <c r="G449" t="n">
+        <v>1</v>
+      </c>
+      <c r="H449" t="n">
+        <v>1</v>
+      </c>
+      <c r="I449" t="n">
+        <v>1</v>
+      </c>
+      <c r="J449">
+        <f>'Towers'!$G$24*G449*H449*I449</f>
+        <v/>
+      </c>
+      <c r="K449">
+        <f>IF(J449=0,0,F449/J449)</f>
+        <v/>
+      </c>
+      <c r="L449" t="n">
+        <v>1</v>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>Obsidian Wall</t>
+        </is>
+      </c>
+      <c r="AM449" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DL449" t="n">
+        <v>2</v>
+      </c>
+      <c r="GJ449" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Obsidian</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>4</v>
+      </c>
+      <c r="E450">
+        <f>ROUND('Towers'!$C$24*POWER('Tuning'!$B$12,D450),0)</f>
+        <v/>
+      </c>
+      <c r="F450">
+        <f>F449+E450</f>
+        <v/>
+      </c>
+      <c r="G450" t="n">
+        <v>1</v>
+      </c>
+      <c r="H450" t="n">
+        <v>1</v>
+      </c>
+      <c r="I450" t="n">
+        <v>1</v>
+      </c>
+      <c r="J450">
+        <f>J449*G450*H450*I450</f>
+        <v/>
+      </c>
+      <c r="K450">
+        <f>IF(J450=0,0,F450/J450)</f>
+        <v/>
+      </c>
+      <c r="L450" t="n">
+        <v>1</v>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>Jagged Crust</t>
+        </is>
+      </c>
+      <c r="CI450" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ450" t="inlineStr">
+        <is>
+          <t>The crust cuts dinos</t>
+        </is>
+      </c>
+      <c r="GK450" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Obsidian</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>5</v>
+      </c>
+      <c r="E451">
+        <f>ROUND('Towers'!$C$24*POWER('Tuning'!$B$12,D451),0)</f>
+        <v/>
+      </c>
+      <c r="F451">
+        <f>F450+E451</f>
+        <v/>
+      </c>
+      <c r="G451" t="n">
+        <v>1</v>
+      </c>
+      <c r="H451" t="n">
+        <v>1</v>
+      </c>
+      <c r="I451" t="n">
+        <v>1</v>
+      </c>
+      <c r="J451">
+        <f>J450*G451*H451*I451</f>
+        <v/>
+      </c>
+      <c r="K451">
+        <f>IF(J451=0,0,F451/J451)</f>
+        <v/>
+      </c>
+      <c r="L451" t="n">
+        <v>1</v>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>Glass Maze</t>
+        </is>
+      </c>
+      <c r="CI451" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CJ451" t="inlineStr">
+        <is>
+          <t>The crust makes dinos walk 12 studs further</t>
+        </is>
+      </c>
+      <c r="GL451" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Magma</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>4</v>
+      </c>
+      <c r="E452">
+        <f>E440</f>
+        <v/>
+      </c>
+      <c r="F452">
+        <f>F440</f>
+        <v/>
+      </c>
+      <c r="G452" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H452" t="n">
+        <v>1</v>
+      </c>
+      <c r="I452" t="n">
+        <v>1</v>
+      </c>
+      <c r="L452" t="n">
+        <v>1</v>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>Rivers of Fire</t>
+        </is>
+      </c>
+      <c r="CI452" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ452" t="inlineStr">
+        <is>
+          <t>The lava runs 20 studs further</t>
+        </is>
+      </c>
+      <c r="GB452" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Magma</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>4</v>
+      </c>
+      <c r="E453">
+        <f>E440</f>
+        <v/>
+      </c>
+      <c r="F453">
+        <f>F440</f>
+        <v/>
+      </c>
+      <c r="G453" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H453" t="n">
+        <v>1</v>
+      </c>
+      <c r="I453" t="n">
+        <v>1</v>
+      </c>
+      <c r="L453" t="n">
+        <v>1</v>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>Ember Rain</t>
+        </is>
+      </c>
+      <c r="CI453" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ453" t="inlineStr">
+        <is>
+          <t>Embers hit low flyers</t>
+        </is>
+      </c>
+      <c r="DW453" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Magma</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>5</v>
+      </c>
+      <c r="E454">
+        <f>E441</f>
+        <v/>
+      </c>
+      <c r="F454">
+        <f>F441</f>
+        <v/>
+      </c>
+      <c r="G454" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H454" t="n">
+        <v>1</v>
+      </c>
+      <c r="I454" t="n">
+        <v>1</v>
+      </c>
+      <c r="L454" t="n">
+        <v>1</v>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>Lava Bombs</t>
+        </is>
+      </c>
+      <c r="CI454" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ454" t="inlineStr">
+        <is>
+          <t>Throws 6 lava bombs at big dinos</t>
+        </is>
+      </c>
+      <c r="GF454" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Magma</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>5</v>
+      </c>
+      <c r="E455">
+        <f>E441</f>
+        <v/>
+      </c>
+      <c r="F455">
+        <f>F441</f>
+        <v/>
+      </c>
+      <c r="G455" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H455" t="n">
+        <v>1</v>
+      </c>
+      <c r="I455" t="n">
+        <v>2</v>
+      </c>
+      <c r="L455" t="n">
+        <v>1</v>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>Fire Mountain</t>
+        </is>
+      </c>
+      <c r="CI455" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ455" t="inlineStr">
+        <is>
+          <t>Eruptions twice as big</t>
+        </is>
+      </c>
+      <c r="GB455" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Pressure</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>4</v>
+      </c>
+      <c r="E456">
+        <f>E445</f>
+        <v/>
+      </c>
+      <c r="F456">
+        <f>F445</f>
+        <v/>
+      </c>
+      <c r="G456" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H456" t="n">
+        <v>1</v>
+      </c>
+      <c r="I456" t="n">
+        <v>1</v>
+      </c>
+      <c r="L456" t="n">
+        <v>1</v>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>Rumble</t>
+        </is>
+      </c>
+      <c r="AE456" t="n">
+        <v>20</v>
+      </c>
+      <c r="CI456" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ456" t="inlineStr">
+        <is>
+          <t>Dinos nearby stumble: −20% speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Pressure</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>4</v>
+      </c>
+      <c r="E457">
+        <f>E445</f>
+        <v/>
+      </c>
+      <c r="F457">
+        <f>F445</f>
+        <v/>
+      </c>
+      <c r="G457" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H457" t="n">
+        <v>1</v>
+      </c>
+      <c r="I457" t="n">
+        <v>1</v>
+      </c>
+      <c r="L457" t="n">
+        <v>1</v>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>Pressure Valve</t>
+        </is>
+      </c>
+      <c r="CI457" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ457" t="inlineStr">
+        <is>
+          <t>Erupts early when a boss comes</t>
+        </is>
+      </c>
+      <c r="GG457" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Pressure</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>5</v>
+      </c>
+      <c r="E458">
+        <f>E446</f>
+        <v/>
+      </c>
+      <c r="F458">
+        <f>F446</f>
+        <v/>
+      </c>
+      <c r="G458" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H458" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I458" t="n">
+        <v>1</v>
+      </c>
+      <c r="L458" t="n">
+        <v>1</v>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>Old Faithful</t>
+        </is>
+      </c>
+      <c r="CI458" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ458" t="inlineStr">
+        <is>
+          <t>Erupts 2.5× as often, smaller</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Pressure</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>5</v>
+      </c>
+      <c r="E459">
+        <f>E446</f>
+        <v/>
+      </c>
+      <c r="F459">
+        <f>F446</f>
+        <v/>
+      </c>
+      <c r="G459" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H459" t="n">
+        <v>1</v>
+      </c>
+      <c r="I459" t="n">
+        <v>1</v>
+      </c>
+      <c r="L459" t="n">
+        <v>1</v>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>Ash Blanket</t>
+        </is>
+      </c>
+      <c r="CI459" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ459" t="inlineStr">
+        <is>
+          <t>Ash makes dinos miss 30% of throws</t>
+        </is>
+      </c>
+      <c r="GH459" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Obsidian</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>4</v>
+      </c>
+      <c r="E460">
+        <f>E450</f>
+        <v/>
+      </c>
+      <c r="F460">
+        <f>F450</f>
+        <v/>
+      </c>
+      <c r="G460" t="n">
+        <v>1</v>
+      </c>
+      <c r="H460" t="n">
+        <v>1</v>
+      </c>
+      <c r="I460" t="n">
+        <v>1</v>
+      </c>
+      <c r="L460" t="n">
+        <v>1</v>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>Black Glass</t>
+        </is>
+      </c>
+      <c r="CI460" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ460" t="inlineStr">
+        <is>
+          <t>Nearby towers see 15% further</t>
+        </is>
+      </c>
+      <c r="FA460" t="n">
+        <v>15</v>
+      </c>
+      <c r="GK460" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Obsidian</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>4</v>
+      </c>
+      <c r="E461">
+        <f>E450</f>
+        <v/>
+      </c>
+      <c r="F461">
+        <f>F450</f>
+        <v/>
+      </c>
+      <c r="G461" t="n">
+        <v>1</v>
+      </c>
+      <c r="H461" t="n">
+        <v>1</v>
+      </c>
+      <c r="I461" t="n">
+        <v>1</v>
+      </c>
+      <c r="L461" t="n">
+        <v>1</v>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>Heat Shimmer</t>
+        </is>
+      </c>
+      <c r="CI461" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ461" t="inlineStr">
+        <is>
+          <t>Dinos on the crust can't throw</t>
+        </is>
+      </c>
+      <c r="FH461" t="n">
+        <v>100</v>
+      </c>
+      <c r="GK461" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Volcano Vent</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Obsidian</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>5</v>
+      </c>
+      <c r="E462">
+        <f>E451</f>
+        <v/>
+      </c>
+      <c r="F462">
+        <f>F451</f>
+        <v/>
+      </c>
+      <c r="G462" t="n">
+        <v>1</v>
+      </c>
+      <c r="H462" t="n">
+        <v>1</v>
+      </c>
+      <c r="I462" t="n">
+        <v>1</v>
+      </c>
+      <c r="L462" t="n">
+        <v>1</v>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>Obsidian Armour</t>
+        </is>
+      </c>
+      <c r="CI462" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r=